--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K361"/>
+  <dimension ref="A1:L361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,25 +465,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>HILEIHN</t>
+          <t>HILEIHN_PC1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>HIUR</t>
+          <t>HIUR_PC1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LBSSA15</t>
+          <t>LBSSA15_PC1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>SMU15000007072100001SA_PC1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Mandatory Quarantine</t>
         </is>
@@ -517,12 +522,15 @@
       <c r="I2" t="n">
         <v>0.73964</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2" t="n">
+        <v>6.87323</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -554,12 +562,15 @@
       <c r="I3" t="n">
         <v>0.59084</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="J3" t="n">
+        <v>4.15367</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -591,12 +602,15 @@
       <c r="I4" t="n">
         <v>0.73855</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="J4" t="n">
+        <v>7.55398</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -628,12 +642,15 @@
       <c r="I5" t="n">
         <v>0.58997</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="J5" t="n">
+        <v>0.74259</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -665,12 +682,15 @@
       <c r="I6" t="n">
         <v>0.73855</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="J6" t="n">
+        <v>1.77784</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -702,12 +722,15 @@
       <c r="I7" t="n">
         <v>0.88757</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+      <c r="J7" t="n">
+        <v>2.02157</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -739,12 +762,15 @@
       <c r="I8" t="n">
         <v>0.88757</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8" t="n">
+        <v>4.61385</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -776,12 +802,15 @@
       <c r="I9" t="n">
         <v>0.73855</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" t="n">
+        <v>7.05482</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -813,12 +842,15 @@
       <c r="I10" t="n">
         <v>0.58997</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10" t="n">
+        <v>8.03481</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -850,12 +882,15 @@
       <c r="I11" t="n">
         <v>0.44183</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="J11" t="n">
+        <v>5.90081</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -887,12 +922,15 @@
       <c r="I12" t="n">
         <v>0.44183</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
+        <v>3.00194</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -924,12 +962,15 @@
       <c r="I13" t="n">
         <v>0.29412</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
+        <v>3.56805</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -961,12 +1002,15 @@
       <c r="I14" t="n">
         <v>0.14684</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
+        <v>2.00281</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -998,12 +1042,15 @@
       <c r="I15" t="n">
         <v>0.29369</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15" t="n">
+        <v>3.20213</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1035,12 +1082,15 @@
       <c r="I16" t="n">
         <v>0.14663</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
+        <v>4.71972</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1072,12 +1122,15 @@
       <c r="I17" t="n">
         <v>0.29326</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
+      <c r="J17" t="n">
+        <v>5.26354</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1109,12 +1162,15 @@
       <c r="I18" t="n">
         <v>0.43988</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
+      <c r="J18" t="n">
+        <v>4.22933</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1146,12 +1202,15 @@
       <c r="I19" t="n">
         <v>0.58651</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
+      <c r="J19" t="n">
+        <v>3.76165</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,12 +1242,15 @@
       <c r="I20" t="n">
         <v>0.73314</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
+      <c r="J20" t="n">
+        <v>0.94789</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1220,12 +1282,15 @@
       <c r="I21" t="n">
         <v>0.8797700000000001</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
+      <c r="J21" t="n">
+        <v>-1.13358</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1257,12 +1322,15 @@
       <c r="I22" t="n">
         <v>0.8797700000000001</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
+      <c r="J22" t="n">
+        <v>-2.8686</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,12 +1362,15 @@
       <c r="I23" t="n">
         <v>0.8797700000000001</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
+      <c r="J23" t="n">
+        <v>-2.60379</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1331,12 +1402,15 @@
       <c r="I24" t="n">
         <v>0.73314</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
+      <c r="J24" t="n">
+        <v>-2.90647</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1368,12 +1442,15 @@
       <c r="I25" t="n">
         <v>0.73314</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
+      <c r="J25" t="n">
+        <v>-3.72218</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,12 +1482,15 @@
       <c r="I26" t="n">
         <v>0.73314</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
+      <c r="J26" t="n">
+        <v>-6.68686</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,12 +1522,15 @@
       <c r="I27" t="n">
         <v>0.43924</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
+      <c r="J27" t="n">
+        <v>-7.29507</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1479,12 +1562,15 @@
       <c r="I28" t="n">
         <v>0.43924</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
+      <c r="J28" t="n">
+        <v>-7.18887</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,12 +1602,15 @@
       <c r="I29" t="n">
         <v>0.2924</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
+      <c r="J29" t="n">
+        <v>-8.49579</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1553,12 +1642,15 @@
       <c r="I30" t="n">
         <v>0.14599</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
+      <c r="J30" t="n">
+        <v>-7.96439</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,12 +1682,15 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
+      <c r="J31" t="n">
+        <v>-7.24745</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1627,12 +1722,15 @@
       <c r="I32" t="n">
         <v>-0.14556</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" t="n">
+        <v>-7.5816</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1664,12 +1762,15 @@
       <c r="I33" t="n">
         <v>-0.43605</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" t="n">
+        <v>-8.440099999999999</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1701,12 +1802,15 @@
       <c r="I34" t="n">
         <v>-0.5814</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
+      <c r="J34" t="n">
+        <v>-7.62422</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1738,12 +1842,15 @@
       <c r="I35" t="n">
         <v>-0.7267400000000001</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
+      <c r="J35" t="n">
+        <v>-5.89477</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1775,12 +1882,15 @@
       <c r="I36" t="n">
         <v>-0.43668</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
+      <c r="J36" t="n">
+        <v>-7.24322</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1812,12 +1922,15 @@
       <c r="I37" t="n">
         <v>-0.58224</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
+      <c r="J37" t="n">
+        <v>-7.38131</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1849,12 +1962,15 @@
       <c r="I38" t="n">
         <v>-0.58224</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
+      <c r="J38" t="n">
+        <v>-3.30781</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1886,12 +2002,15 @@
       <c r="I39" t="n">
         <v>-0.58309</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
+      <c r="J39" t="n">
+        <v>-2.16373</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1923,12 +2042,15 @@
       <c r="I40" t="n">
         <v>-0.58309</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
+      <c r="J40" t="n">
+        <v>-1.56239</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1960,12 +2082,15 @@
       <c r="I41" t="n">
         <v>-0.87464</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
+      <c r="J41" t="n">
+        <v>-0.60228</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1997,12 +2122,15 @@
       <c r="I42" t="n">
         <v>-1.02041</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
+      <c r="J42" t="n">
+        <v>-1.01636</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2034,12 +2162,15 @@
       <c r="I43" t="n">
         <v>-1.16618</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
+      <c r="J43" t="n">
+        <v>-1.00361</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2071,12 +2202,15 @@
       <c r="I44" t="n">
         <v>-1.16618</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
+      <c r="J44" t="n">
+        <v>1.32015</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2108,12 +2242,15 @@
       <c r="I45" t="n">
         <v>-1.0219</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
+      <c r="J45" t="n">
+        <v>0.68588</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2145,12 +2282,15 @@
       <c r="I46" t="n">
         <v>-0.87719</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
+      <c r="J46" t="n">
+        <v>1.35223</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2182,12 +2322,15 @@
       <c r="I47" t="n">
         <v>-0.58565</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
+      <c r="J47" t="n">
+        <v>1.09793</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2219,12 +2362,15 @@
       <c r="I48" t="n">
         <v>-0.73099</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
+      <c r="J48" t="n">
+        <v>2.6756</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2256,12 +2402,15 @@
       <c r="I49" t="n">
         <v>-0.58565</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
+      <c r="J49" t="n">
+        <v>2.51899</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,12 +2442,15 @@
       <c r="I50" t="n">
         <v>-0.73206</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
+      <c r="J50" t="n">
+        <v>1.41031</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2330,12 +2482,15 @@
       <c r="I51" t="n">
         <v>-0.58651</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
+      <c r="J51" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2367,12 +2522,15 @@
       <c r="I52" t="n">
         <v>-0.73314</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
+      <c r="J52" t="n">
+        <v>-0.83586</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2404,12 +2562,15 @@
       <c r="I53" t="n">
         <v>-0.44118</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
+      <c r="J53" t="n">
+        <v>-0.6408700000000001</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2441,12 +2602,15 @@
       <c r="I54" t="n">
         <v>-0.29455</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
+      <c r="J54" t="n">
+        <v>-0.46422</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2478,12 +2642,15 @@
       <c r="I55" t="n">
         <v>-0.14749</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
+      <c r="J55" t="n">
+        <v>-1.2576</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2515,12 +2682,15 @@
       <c r="I56" t="n">
         <v>-0.29499</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
+      <c r="J56" t="n">
+        <v>-2.05585</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2552,12 +2722,15 @@
       <c r="I57" t="n">
         <v>-0.44248</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="J57" t="n">
+        <v>-0.07042</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2589,12 +2762,15 @@
       <c r="I58" t="n">
         <v>-0.44248</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
+      <c r="J58" t="n">
+        <v>-0.9904500000000001</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2626,12 +2802,15 @@
       <c r="I59" t="n">
         <v>-0.73638</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
+      <c r="J59" t="n">
+        <v>-2.11234</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2663,12 +2842,15 @@
       <c r="I60" t="n">
         <v>-0.88365</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
+      <c r="J60" t="n">
+        <v>-1.08805</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2700,12 +2882,15 @@
       <c r="I61" t="n">
         <v>-0.73638</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
+      <c r="J61" t="n">
+        <v>-1.03275</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2737,12 +2922,15 @@
       <c r="I62" t="n">
         <v>-0.58997</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
+      <c r="J62" t="n">
+        <v>-0.74471</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2774,12 +2962,15 @@
       <c r="I63" t="n">
         <v>-0.44248</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
+      <c r="J63" t="n">
+        <v>1.2471</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2811,12 +3002,15 @@
       <c r="I64" t="n">
         <v>-0.14771</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
+      <c r="J64" t="n">
+        <v>1.93804</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2848,12 +3042,15 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
+      <c r="J65" t="n">
+        <v>0.72118</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2885,12 +3082,15 @@
       <c r="I66" t="n">
         <v>0.14771</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
+      <c r="J66" t="n">
+        <v>1.0878</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2922,12 +3122,15 @@
       <c r="I67" t="n">
         <v>0.14771</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
+      <c r="J67" t="n">
+        <v>2.17111</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2959,12 +3162,15 @@
       <c r="I68" t="n">
         <v>0.29586</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
+      <c r="J68" t="n">
+        <v>2.45751</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2996,12 +3202,15 @@
       <c r="I69" t="n">
         <v>0.44444</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
+      <c r="J69" t="n">
+        <v>2.30566</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3033,12 +3242,15 @@
       <c r="I70" t="n">
         <v>0.44444</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
+      <c r="J70" t="n">
+        <v>2.95779</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3070,12 +3282,15 @@
       <c r="I71" t="n">
         <v>0.7418400000000001</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
+      <c r="J71" t="n">
+        <v>3.13813</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3107,12 +3322,15 @@
       <c r="I72" t="n">
         <v>0.89153</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
+      <c r="J72" t="n">
+        <v>2.07499</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3144,12 +3362,15 @@
       <c r="I73" t="n">
         <v>0.7418400000000001</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
+      <c r="J73" t="n">
+        <v>3.72548</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3181,12 +3402,15 @@
       <c r="I74" t="n">
         <v>0.7418400000000001</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
+      <c r="J74" t="n">
+        <v>3.27738</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3218,12 +3442,15 @@
       <c r="I75" t="n">
         <v>0.59259</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
+      <c r="J75" t="n">
+        <v>1.52746</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3255,12 +3482,15 @@
       <c r="I76" t="n">
         <v>0.44379</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
+      <c r="J76" t="n">
+        <v>1.24683</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3292,12 +3522,15 @@
       <c r="I77" t="n">
         <v>0.14771</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
+      <c r="J77" t="n">
+        <v>1.24298</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3329,12 +3562,15 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
+      <c r="J78" t="n">
+        <v>-0.03912</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3366,12 +3602,15 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
+      <c r="J79" t="n">
+        <v>-1.36338</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3403,12 +3642,15 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
+      <c r="J80" t="n">
+        <v>-1.24423</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3440,12 +3682,15 @@
       <c r="I81" t="n">
         <v>-0.14749</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
+      <c r="J81" t="n">
+        <v>-1.38608</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3477,12 +3722,15 @@
       <c r="I82" t="n">
         <v>-0.29499</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
+      <c r="J82" t="n">
+        <v>-1.8118</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3514,12 +3762,15 @@
       <c r="I83" t="n">
         <v>-0.44183</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
+      <c r="J83" t="n">
+        <v>-1.15059</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3551,12 +3802,15 @@
       <c r="I84" t="n">
         <v>-0.5891</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
+      <c r="J84" t="n">
+        <v>-1.29216</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3588,12 +3842,15 @@
       <c r="I85" t="n">
         <v>-0.73638</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
+      <c r="J85" t="n">
+        <v>-2.01288</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3625,12 +3882,15 @@
       <c r="I86" t="n">
         <v>-0.73638</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
+      <c r="J86" t="n">
+        <v>-1.71983</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3662,12 +3922,15 @@
       <c r="I87" t="n">
         <v>-0.88365</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
+      <c r="J87" t="n">
+        <v>-1.27068</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3699,12 +3962,15 @@
       <c r="I88" t="n">
         <v>-0.88365</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
+      <c r="J88" t="n">
+        <v>-0.97194</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3736,12 +4002,15 @@
       <c r="I89" t="n">
         <v>-0.73746</v>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
+      <c r="J89" t="n">
+        <v>-0.57021</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3773,12 +4042,15 @@
       <c r="I90" t="n">
         <v>-0.73746</v>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
+      <c r="J90" t="n">
+        <v>0.17421</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3810,12 +4082,15 @@
       <c r="I91" t="n">
         <v>-0.58997</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
+      <c r="J91" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3847,12 +4122,15 @@
       <c r="I92" t="n">
         <v>-0.58997</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
+      <c r="J92" t="n">
+        <v>-0.22581</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3884,12 +4162,15 @@
       <c r="I93" t="n">
         <v>-0.44313</v>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
+      <c r="J93" t="n">
+        <v>-0.9389999999999999</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3921,12 +4202,15 @@
       <c r="I94" t="n">
         <v>-0.14793</v>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
+      <c r="J94" t="n">
+        <v>-1.3879</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3958,12 +4242,15 @@
       <c r="I95" t="n">
         <v>-0.14793</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
+      <c r="J95" t="n">
+        <v>-2.02748</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3995,12 +4282,15 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
+      <c r="J96" t="n">
+        <v>-1.27398</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4032,12 +4322,15 @@
       <c r="I97" t="n">
         <v>0</v>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
+      <c r="J97" t="n">
+        <v>-1.95338</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4069,12 +4362,15 @@
       <c r="I98" t="n">
         <v>0</v>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
+      <c r="J98" t="n">
+        <v>-1.95983</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4106,12 +4402,15 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
+      <c r="J99" t="n">
+        <v>-2.02135</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4143,12 +4442,15 @@
       <c r="I100" t="n">
         <v>0</v>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
+      <c r="J100" t="n">
+        <v>-2.2275</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4180,12 +4482,15 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
+      <c r="J101" t="n">
+        <v>-1.59591</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4217,12 +4522,15 @@
       <c r="I102" t="n">
         <v>0</v>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
+      <c r="J102" t="n">
+        <v>-1.13134</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4254,12 +4562,15 @@
       <c r="I103" t="n">
         <v>0</v>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
+      <c r="J103" t="n">
+        <v>-0.70105</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4291,12 +4602,15 @@
       <c r="I104" t="n">
         <v>0</v>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
+      <c r="J104" t="n">
+        <v>-1.63677</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4328,12 +4642,15 @@
       <c r="I105" t="n">
         <v>0</v>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
+      <c r="J105" t="n">
+        <v>-1.31027</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4365,12 +4682,15 @@
       <c r="I106" t="n">
         <v>-0.14815</v>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
+      <c r="J106" t="n">
+        <v>-1.71536</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4402,12 +4722,15 @@
       <c r="I107" t="n">
         <v>-0.14815</v>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
+      <c r="J107" t="n">
+        <v>0.61221</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4439,12 +4762,15 @@
       <c r="I108" t="n">
         <v>-0.14815</v>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
+      <c r="J108" t="n">
+        <v>1.6503</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4476,12 +4802,15 @@
       <c r="I109" t="n">
         <v>0</v>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
+      <c r="J109" t="n">
+        <v>2.32905</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,12 +4842,15 @@
       <c r="I110" t="n">
         <v>0.14837</v>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
+      <c r="J110" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4550,12 +4882,15 @@
       <c r="I111" t="n">
         <v>0.29718</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
+      <c r="J111" t="n">
+        <v>0.90567</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4587,12 +4922,15 @@
       <c r="I112" t="n">
         <v>0.44577</v>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
+      <c r="J112" t="n">
+        <v>1.75485</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4624,12 +4962,15 @@
       <c r="I113" t="n">
         <v>0.29718</v>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
+      <c r="J113" t="n">
+        <v>2.68801</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4661,12 +5002,15 @@
       <c r="I114" t="n">
         <v>0.14859</v>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
+      <c r="J114" t="n">
+        <v>2.87432</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4698,12 +5042,15 @@
       <c r="I115" t="n">
         <v>-0.14837</v>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
+      <c r="J115" t="n">
+        <v>3.30693</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4735,12 +5082,15 @@
       <c r="I116" t="n">
         <v>-0.29674</v>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
+      <c r="J116" t="n">
+        <v>3.93853</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4772,12 +5122,15 @@
       <c r="I117" t="n">
         <v>-0.4451</v>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K117" t="n">
+      <c r="J117" t="n">
+        <v>3.90911</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4809,12 +5162,15 @@
       <c r="I118" t="n">
         <v>-0.5934700000000001</v>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K118" t="n">
+      <c r="J118" t="n">
+        <v>5.25938</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4846,12 +5202,15 @@
       <c r="I119" t="n">
         <v>-0.4451</v>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K119" t="n">
+      <c r="J119" t="n">
+        <v>3.59819</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4883,12 +5242,15 @@
       <c r="I120" t="n">
         <v>-0.4451</v>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
+      <c r="J120" t="n">
+        <v>1.88625</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4920,12 +5282,15 @@
       <c r="I121" t="n">
         <v>-0.29674</v>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K121" t="n">
+      <c r="J121" t="n">
+        <v>1.4736</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4957,12 +5322,15 @@
       <c r="I122" t="n">
         <v>-0.2963</v>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K122" t="n">
+      <c r="J122" t="n">
+        <v>3.3177</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4994,12 +5362,15 @@
       <c r="I123" t="n">
         <v>-0.14815</v>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K123" t="n">
+      <c r="J123" t="n">
+        <v>3.28843</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5031,12 +5402,15 @@
       <c r="I124" t="n">
         <v>-0.29586</v>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K124" t="n">
+      <c r="J124" t="n">
+        <v>2.21633</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5068,12 +5442,15 @@
       <c r="I125" t="n">
         <v>-0.2963</v>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K125" t="n">
+      <c r="J125" t="n">
+        <v>0.8649</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5105,12 +5482,15 @@
       <c r="I126" t="n">
         <v>-0.14837</v>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K126" t="n">
+      <c r="J126" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5142,12 +5522,15 @@
       <c r="I127" t="n">
         <v>-0.14859</v>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K127" t="n">
+      <c r="J127" t="n">
+        <v>-0.36777</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5179,12 +5562,15 @@
       <c r="I128" t="n">
         <v>-0.14881</v>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K128" t="n">
+      <c r="J128" t="n">
+        <v>-0.16223</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5216,12 +5602,15 @@
       <c r="I129" t="n">
         <v>-0.14903</v>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K129" t="n">
+      <c r="J129" t="n">
+        <v>0.60939</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5253,12 +5642,15 @@
       <c r="I130" t="n">
         <v>0</v>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K130" t="n">
+      <c r="J130" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5290,12 +5682,15 @@
       <c r="I131" t="n">
         <v>-0.29806</v>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K131" t="n">
+      <c r="J131" t="n">
+        <v>-6.44729</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5327,12 +5722,15 @@
       <c r="I132" t="n">
         <v>-0.59613</v>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K132" t="n">
+      <c r="J132" t="n">
+        <v>-7.12007</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5364,12 +5762,15 @@
       <c r="I133" t="n">
         <v>-0.89286</v>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K133" t="n">
+      <c r="J133" t="n">
+        <v>-7.8633</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5401,12 +5802,15 @@
       <c r="I134" t="n">
         <v>-1.3373</v>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K134" t="n">
+      <c r="J134" t="n">
+        <v>-7.87933</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5438,12 +5842,15 @@
       <c r="I135" t="n">
         <v>-1.63205</v>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K135" t="n">
+      <c r="J135" t="n">
+        <v>-7.84518</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5475,12 +5882,15 @@
       <c r="I136" t="n">
         <v>-1.92878</v>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K136" t="n">
+      <c r="J136" t="n">
+        <v>-7.1485</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5512,12 +5922,15 @@
       <c r="I137" t="n">
         <v>-1.93165</v>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K137" t="n">
+      <c r="J137" t="n">
+        <v>-6.829</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5549,12 +5962,15 @@
       <c r="I138" t="n">
         <v>-2.08024</v>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K138" t="n">
+      <c r="J138" t="n">
+        <v>-6.62404</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5586,12 +6002,15 @@
       <c r="I139" t="n">
         <v>-1.93452</v>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K139" t="n">
+      <c r="J139" t="n">
+        <v>-5.48699</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5623,12 +6042,15 @@
       <c r="I140" t="n">
         <v>-1.93741</v>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K140" t="n">
+      <c r="J140" t="n">
+        <v>-5.06328</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5660,12 +6082,15 @@
       <c r="I141" t="n">
         <v>-1.79104</v>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K141" t="n">
+      <c r="J141" t="n">
+        <v>-5.3158</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5697,12 +6122,15 @@
       <c r="I142" t="n">
         <v>-1.9403</v>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K142" t="n">
+      <c r="J142" t="n">
+        <v>-5.4778</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5734,12 +6162,15 @@
       <c r="I143" t="n">
         <v>-1.9432</v>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K143" t="n">
+      <c r="J143" t="n">
+        <v>-0.53771</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5771,12 +6202,15 @@
       <c r="I144" t="n">
         <v>-1.64918</v>
       </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K144" t="n">
+      <c r="J144" t="n">
+        <v>1.45738</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5808,12 +6242,15 @@
       <c r="I145" t="n">
         <v>-1.65165</v>
       </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K145" t="n">
+      <c r="J145" t="n">
+        <v>2.53959</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5845,12 +6282,15 @@
       <c r="I146" t="n">
         <v>-1.35542</v>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K146" t="n">
+      <c r="J146" t="n">
+        <v>3.67652</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5882,12 +6322,15 @@
       <c r="I147" t="n">
         <v>-1.20664</v>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K147" t="n">
+      <c r="J147" t="n">
+        <v>3.14865</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5919,12 +6362,15 @@
       <c r="I148" t="n">
         <v>-0.75643</v>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K148" t="n">
+      <c r="J148" t="n">
+        <v>2.77778</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5956,12 +6402,15 @@
       <c r="I149" t="n">
         <v>-0.45455</v>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K149" t="n">
+      <c r="J149" t="n">
+        <v>2.01723</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5993,12 +6442,15 @@
       <c r="I150" t="n">
         <v>-0.30349</v>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K150" t="n">
+      <c r="J150" t="n">
+        <v>1.69822</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6030,12 +6482,15 @@
       <c r="I151" t="n">
         <v>-0.30349</v>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K151" t="n">
+      <c r="J151" t="n">
+        <v>0.24066</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6067,12 +6522,15 @@
       <c r="I152" t="n">
         <v>-0.15198</v>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K152" t="n">
+      <c r="J152" t="n">
+        <v>0.63305</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6104,12 +6562,15 @@
       <c r="I153" t="n">
         <v>-0.30395</v>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K153" t="n">
+      <c r="J153" t="n">
+        <v>0.9598100000000001</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6141,12 +6602,15 @@
       <c r="I154" t="n">
         <v>-0.30441</v>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K154" t="n">
+      <c r="J154" t="n">
+        <v>1.1216</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6178,12 +6642,15 @@
       <c r="I155" t="n">
         <v>-0.30488</v>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K155" t="n">
+      <c r="J155" t="n">
+        <v>2.58983</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6215,12 +6682,15 @@
       <c r="I156" t="n">
         <v>-0.45732</v>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
+      <c r="J156" t="n">
+        <v>1.93557</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6252,12 +6722,15 @@
       <c r="I157" t="n">
         <v>-0.30534</v>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K157" t="n">
+      <c r="J157" t="n">
+        <v>2.43277</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6289,12 +6762,15 @@
       <c r="I158" t="n">
         <v>-0.45802</v>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K158" t="n">
+      <c r="J158" t="n">
+        <v>1.34564</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6326,12 +6802,15 @@
       <c r="I159" t="n">
         <v>-0.61069</v>
       </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K159" t="n">
+      <c r="J159" t="n">
+        <v>1.65367</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6363,12 +6842,15 @@
       <c r="I160" t="n">
         <v>-0.9146300000000001</v>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K160" t="n">
+      <c r="J160" t="n">
+        <v>1.57829</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6400,12 +6882,15 @@
       <c r="I161" t="n">
         <v>-1.06545</v>
       </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K161" t="n">
+      <c r="J161" t="n">
+        <v>2.46817</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6437,12 +6922,15 @@
       <c r="I162" t="n">
         <v>-1.21766</v>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K162" t="n">
+      <c r="J162" t="n">
+        <v>3.24552</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6474,12 +6962,15 @@
       <c r="I163" t="n">
         <v>-1.21766</v>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K163" t="n">
+      <c r="J163" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6511,12 +7002,15 @@
       <c r="I164" t="n">
         <v>-1.36986</v>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K164" t="n">
+      <c r="J164" t="n">
+        <v>3.68896</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6548,12 +7042,15 @@
       <c r="I165" t="n">
         <v>-1.06707</v>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K165" t="n">
+      <c r="J165" t="n">
+        <v>2.90109</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6585,12 +7082,15 @@
       <c r="I166" t="n">
         <v>-0.91603</v>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K166" t="n">
+      <c r="J166" t="n">
+        <v>2.53596</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6622,12 +7122,15 @@
       <c r="I167" t="n">
         <v>-0.76453</v>
       </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K167" t="n">
+      <c r="J167" t="n">
+        <v>3.64588</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6659,12 +7162,15 @@
       <c r="I168" t="n">
         <v>-0.45942</v>
       </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K168" t="n">
+      <c r="J168" t="n">
+        <v>3.48912</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6696,12 +7202,15 @@
       <c r="I169" t="n">
         <v>-0.30628</v>
       </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K169" t="n">
+      <c r="J169" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6733,12 +7242,15 @@
       <c r="I170" t="n">
         <v>-0.15337</v>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K170" t="n">
+      <c r="J170" t="n">
+        <v>2.85953</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6770,12 +7282,15 @@
       <c r="I171" t="n">
         <v>0.15361</v>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K171" t="n">
+      <c r="J171" t="n">
+        <v>2.90367</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6807,12 +7322,15 @@
       <c r="I172" t="n">
         <v>0.46154</v>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K172" t="n">
+      <c r="J172" t="n">
+        <v>3.17376</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6844,12 +7362,15 @@
       <c r="I173" t="n">
         <v>0.61538</v>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K173" t="n">
+      <c r="J173" t="n">
+        <v>2.84697</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6881,12 +7402,15 @@
       <c r="I174" t="n">
         <v>1.07858</v>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K174" t="n">
+      <c r="J174" t="n">
+        <v>2.57144</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6918,12 +7442,15 @@
       <c r="I175" t="n">
         <v>1.23267</v>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K175" t="n">
+      <c r="J175" t="n">
+        <v>2.85247</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6955,12 +7482,15 @@
       <c r="I176" t="n">
         <v>1.54321</v>
       </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K176" t="n">
+      <c r="J176" t="n">
+        <v>2.54939</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6992,12 +7522,15 @@
       <c r="I177" t="n">
         <v>1.69492</v>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K177" t="n">
+      <c r="J177" t="n">
+        <v>2.89893</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7029,12 +7562,15 @@
       <c r="I178" t="n">
         <v>1.69492</v>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K178" t="n">
+      <c r="J178" t="n">
+        <v>3.8442</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7066,12 +7602,15 @@
       <c r="I179" t="n">
         <v>1.54083</v>
       </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K179" t="n">
+      <c r="J179" t="n">
+        <v>2.50148</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7103,12 +7642,15 @@
       <c r="I180" t="n">
         <v>1.38462</v>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K180" t="n">
+      <c r="J180" t="n">
+        <v>1.78988</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,12 +7682,15 @@
       <c r="I181" t="n">
         <v>1.07527</v>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K181" t="n">
+      <c r="J181" t="n">
+        <v>1.81115</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7177,12 +7722,15 @@
       <c r="I182" t="n">
         <v>1.07527</v>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K182" t="n">
+      <c r="J182" t="n">
+        <v>1.44836</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7214,12 +7762,15 @@
       <c r="I183" t="n">
         <v>0.92025</v>
       </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K183" t="n">
+      <c r="J183" t="n">
+        <v>1.73084</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7251,12 +7802,15 @@
       <c r="I184" t="n">
         <v>0.7657</v>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K184" t="n">
+      <c r="J184" t="n">
+        <v>1.24422</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7288,12 +7842,15 @@
       <c r="I185" t="n">
         <v>0.6116200000000001</v>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K185" t="n">
+      <c r="J185" t="n">
+        <v>1.47007</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7325,12 +7882,15 @@
       <c r="I186" t="n">
         <v>0.30488</v>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K186" t="n">
+      <c r="J186" t="n">
+        <v>1.51105</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7362,12 +7922,15 @@
       <c r="I187" t="n">
         <v>0.30441</v>
       </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K187" t="n">
+      <c r="J187" t="n">
+        <v>1.01777</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7399,12 +7962,15 @@
       <c r="I188" t="n">
         <v>0.15198</v>
       </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K188" t="n">
+      <c r="J188" t="n">
+        <v>1.00864</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7436,12 +8002,15 @@
       <c r="I189" t="n">
         <v>-0.15152</v>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K189" t="n">
+      <c r="J189" t="n">
+        <v>1.05815</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7473,12 +8042,15 @@
       <c r="I190" t="n">
         <v>0</v>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K190" t="n">
+      <c r="J190" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7510,12 +8082,15 @@
       <c r="I191" t="n">
         <v>0.15175</v>
       </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K191" t="n">
+      <c r="J191" t="n">
+        <v>0.89528</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7547,12 +8122,15 @@
       <c r="I192" t="n">
         <v>0.15175</v>
       </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K192" t="n">
+      <c r="J192" t="n">
+        <v>1.49478</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7584,12 +8162,15 @@
       <c r="I193" t="n">
         <v>0.30395</v>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K193" t="n">
+      <c r="J193" t="n">
+        <v>1.29025</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7621,12 +8202,15 @@
       <c r="I194" t="n">
         <v>0.30395</v>
       </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K194" t="n">
+      <c r="J194" t="n">
+        <v>1.42028</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7658,12 +8242,15 @@
       <c r="I195" t="n">
         <v>0.15198</v>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K195" t="n">
+      <c r="J195" t="n">
+        <v>0.9156</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7695,12 +8282,15 @@
       <c r="I196" t="n">
         <v>0</v>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K196" t="n">
+      <c r="J196" t="n">
+        <v>1.2688</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7732,12 +8322,15 @@
       <c r="I197" t="n">
         <v>-0.15198</v>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K197" t="n">
+      <c r="J197" t="n">
+        <v>0.67027</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7769,12 +8362,15 @@
       <c r="I198" t="n">
         <v>-0.45593</v>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K198" t="n">
+      <c r="J198" t="n">
+        <v>0.25298</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7806,12 +8402,15 @@
       <c r="I199" t="n">
         <v>-0.75873</v>
       </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K199" t="n">
+      <c r="J199" t="n">
+        <v>1.03614</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7843,12 +8442,15 @@
       <c r="I200" t="n">
         <v>-1.06222</v>
       </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K200" t="n">
+      <c r="J200" t="n">
+        <v>-0.23673</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7880,12 +8482,15 @@
       <c r="I201" t="n">
         <v>-1.06222</v>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K201" t="n">
+      <c r="J201" t="n">
+        <v>-0.20489</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7917,12 +8522,15 @@
       <c r="I202" t="n">
         <v>-1.36364</v>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K202" t="n">
+      <c r="J202" t="n">
+        <v>-0.66879</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7954,12 +8562,15 @@
       <c r="I203" t="n">
         <v>-1.21212</v>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K203" t="n">
+      <c r="J203" t="n">
+        <v>-0.90621</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7991,12 +8602,15 @@
       <c r="I204" t="n">
         <v>-1.21212</v>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K204" t="n">
+      <c r="J204" t="n">
+        <v>-1.05949</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8028,12 +8642,15 @@
       <c r="I205" t="n">
         <v>-1.06061</v>
       </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K205" t="n">
+      <c r="J205" t="n">
+        <v>-0.99823</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8065,12 +8682,15 @@
       <c r="I206" t="n">
         <v>-0.90909</v>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K206" t="n">
+      <c r="J206" t="n">
+        <v>-0.3367</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8102,12 +8722,15 @@
       <c r="I207" t="n">
         <v>-0.60698</v>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K207" t="n">
+      <c r="J207" t="n">
+        <v>0.17643</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8139,12 +8762,15 @@
       <c r="I208" t="n">
         <v>-0.45593</v>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K208" t="n">
+      <c r="J208" t="n">
+        <v>-1.01265</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8176,12 +8802,15 @@
       <c r="I209" t="n">
         <v>-0.15221</v>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K209" t="n">
+      <c r="J209" t="n">
+        <v>-0.79127</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8213,12 +8842,15 @@
       <c r="I210" t="n">
         <v>0.15267</v>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K210" t="n">
+      <c r="J210" t="n">
+        <v>-0.95663</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8250,12 +8882,15 @@
       <c r="I211" t="n">
         <v>0.30581</v>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K211" t="n">
+      <c r="J211" t="n">
+        <v>-3.18673</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8287,12 +8922,15 @@
       <c r="I212" t="n">
         <v>0.46012</v>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K212" t="n">
+      <c r="J212" t="n">
+        <v>-3.24895</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8324,12 +8962,15 @@
       <c r="I213" t="n">
         <v>0.30675</v>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K213" t="n">
+      <c r="J213" t="n">
+        <v>-4.50816</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8361,12 +9002,15 @@
       <c r="I214" t="n">
         <v>0.30722</v>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K214" t="n">
+      <c r="J214" t="n">
+        <v>-5.03658</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8398,12 +9042,15 @@
       <c r="I215" t="n">
         <v>-0.15337</v>
       </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K215" t="n">
+      <c r="J215" t="n">
+        <v>-6.3027</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8435,12 +9082,15 @@
       <c r="I216" t="n">
         <v>-0.46012</v>
       </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K216" t="n">
+      <c r="J216" t="n">
+        <v>-7.64559</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8472,12 +9122,15 @@
       <c r="I217" t="n">
         <v>-0.91884</v>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K217" t="n">
+      <c r="J217" t="n">
+        <v>-7.87333</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8509,12 +9162,15 @@
       <c r="I218" t="n">
         <v>-1.37615</v>
       </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K218" t="n">
+      <c r="J218" t="n">
+        <v>-8.35885</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8546,12 +9202,15 @@
       <c r="I219" t="n">
         <v>-1.67939</v>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K219" t="n">
+      <c r="J219" t="n">
+        <v>-9.30184</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8583,12 +9242,15 @@
       <c r="I220" t="n">
         <v>-1.98473</v>
       </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K220" t="n">
+      <c r="J220" t="n">
+        <v>-9.053039999999999</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8620,12 +9282,15 @@
       <c r="I221" t="n">
         <v>-2.13415</v>
       </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K221" t="n">
+      <c r="J221" t="n">
+        <v>-10.13441</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8657,12 +9322,15 @@
       <c r="I222" t="n">
         <v>-2.28659</v>
       </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K222" t="n">
+      <c r="J222" t="n">
+        <v>-10.12145</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8694,12 +9362,15 @@
       <c r="I223" t="n">
         <v>-2.28659</v>
       </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K223" t="n">
+      <c r="J223" t="n">
+        <v>-8.699949999999999</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8731,12 +9402,15 @@
       <c r="I224" t="n">
         <v>-2.29008</v>
       </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K224" t="n">
+      <c r="J224" t="n">
+        <v>-7.54205</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8768,12 +9442,15 @@
       <c r="I225" t="n">
         <v>-2.29358</v>
       </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K225" t="n">
+      <c r="J225" t="n">
+        <v>-7.08702</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8805,12 +9482,15 @@
       <c r="I226" t="n">
         <v>-2.29709</v>
       </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K226" t="n">
+      <c r="J226" t="n">
+        <v>-6.15032</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8842,12 +9522,15 @@
       <c r="I227" t="n">
         <v>-2.30415</v>
       </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K227" t="n">
+      <c r="J227" t="n">
+        <v>-5.44062</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8879,12 +9562,15 @@
       <c r="I228" t="n">
         <v>-2.15716</v>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K228" t="n">
+      <c r="J228" t="n">
+        <v>-4.18348</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8916,12 +9602,15 @@
       <c r="I229" t="n">
         <v>-1.85471</v>
       </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K229" t="n">
+      <c r="J229" t="n">
+        <v>-4.2065</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8953,12 +9642,15 @@
       <c r="I230" t="n">
         <v>-1.70543</v>
       </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K230" t="n">
+      <c r="J230" t="n">
+        <v>-4.39894</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8990,12 +9682,15 @@
       <c r="I231" t="n">
         <v>-1.39752</v>
       </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K231" t="n">
+      <c r="J231" t="n">
+        <v>-3.84445</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9027,12 +9722,15 @@
       <c r="I232" t="n">
         <v>-1.09034</v>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K232" t="n">
+      <c r="J232" t="n">
+        <v>-3.53798</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9064,12 +9762,15 @@
       <c r="I233" t="n">
         <v>-1.09034</v>
       </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K233" t="n">
+      <c r="J233" t="n">
+        <v>-1.63804</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9101,12 +9802,15 @@
       <c r="I234" t="n">
         <v>-1.09204</v>
       </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K234" t="n">
+      <c r="J234" t="n">
+        <v>-1.38277</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9138,12 +9842,15 @@
       <c r="I235" t="n">
         <v>-1.24805</v>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K235" t="n">
+      <c r="J235" t="n">
+        <v>-1.35654</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9175,12 +9882,15 @@
       <c r="I236" t="n">
         <v>-1.25</v>
       </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K236" t="n">
+      <c r="J236" t="n">
+        <v>-1.42158</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9212,12 +9922,15 @@
       <c r="I237" t="n">
         <v>-1.25196</v>
       </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K237" t="n">
+      <c r="J237" t="n">
+        <v>-0.25725</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9249,12 +9962,15 @@
       <c r="I238" t="n">
         <v>-1.09718</v>
       </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K238" t="n">
+      <c r="J238" t="n">
+        <v>0.24352</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9286,12 +10002,15 @@
       <c r="I239" t="n">
         <v>-0.78616</v>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K239" t="n">
+      <c r="J239" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9323,12 +10042,15 @@
       <c r="I240" t="n">
         <v>-0.47244</v>
       </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K240" t="n">
+      <c r="J240" t="n">
+        <v>1.67509</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9360,12 +10082,15 @@
       <c r="I241" t="n">
         <v>-0.47244</v>
       </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K241" t="n">
+      <c r="J241" t="n">
+        <v>2.18762</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9397,12 +10122,15 @@
       <c r="I242" t="n">
         <v>-0.31546</v>
       </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K242" t="n">
+      <c r="J242" t="n">
+        <v>2.30198</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9434,12 +10162,15 @@
       <c r="I243" t="n">
         <v>-0.31496</v>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K243" t="n">
+      <c r="J243" t="n">
+        <v>2.64173</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9471,12 +10202,15 @@
       <c r="I244" t="n">
         <v>-0.47244</v>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K244" t="n">
+      <c r="J244" t="n">
+        <v>3.88744</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9508,12 +10242,15 @@
       <c r="I245" t="n">
         <v>-0.47244</v>
       </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K245" t="n">
+      <c r="J245" t="n">
+        <v>2.90206</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9545,12 +10282,15 @@
       <c r="I246" t="n">
         <v>-0.47319</v>
       </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K246" t="n">
+      <c r="J246" t="n">
+        <v>3.10311</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9582,12 +10322,15 @@
       <c r="I247" t="n">
         <v>-0.31596</v>
       </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K247" t="n">
+      <c r="J247" t="n">
+        <v>3.46116</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9619,12 +10362,15 @@
       <c r="I248" t="n">
         <v>-0.31646</v>
       </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K248" t="n">
+      <c r="J248" t="n">
+        <v>3.43722</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9656,12 +10402,15 @@
       <c r="I249" t="n">
         <v>-0.31696</v>
       </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K249" t="n">
+      <c r="J249" t="n">
+        <v>4.28998</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9693,12 +10442,15 @@
       <c r="I250" t="n">
         <v>-0.47544</v>
       </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K250" t="n">
+      <c r="J250" t="n">
+        <v>5.36587</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9730,12 +10482,15 @@
       <c r="I251" t="n">
         <v>-0.79239</v>
       </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K251" t="n">
+      <c r="J251" t="n">
+        <v>4.6915</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9767,12 +10522,15 @@
       <c r="I252" t="n">
         <v>-1.26582</v>
       </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K252" t="n">
+      <c r="J252" t="n">
+        <v>4.78751</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9804,12 +10562,15 @@
       <c r="I253" t="n">
         <v>-1.58228</v>
       </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K253" t="n">
+      <c r="J253" t="n">
+        <v>4.94873</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9841,12 +10602,15 @@
       <c r="I254" t="n">
         <v>-1.89873</v>
       </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K254" t="n">
+      <c r="J254" t="n">
+        <v>5.60819</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9878,12 +10642,15 @@
       <c r="I255" t="n">
         <v>-2.36967</v>
       </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K255" t="n">
+      <c r="J255" t="n">
+        <v>5.94848</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9915,12 +10682,15 @@
       <c r="I256" t="n">
         <v>-2.53165</v>
       </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K256" t="n">
+      <c r="J256" t="n">
+        <v>5.66685</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9952,12 +10722,15 @@
       <c r="I257" t="n">
         <v>-2.8481</v>
       </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K257" t="n">
+      <c r="J257" t="n">
+        <v>6.14195</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9989,12 +10762,15 @@
       <c r="I258" t="n">
         <v>-2.85261</v>
       </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K258" t="n">
+      <c r="J258" t="n">
+        <v>6.59275</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10026,12 +10802,15 @@
       <c r="I259" t="n">
         <v>-3.01109</v>
       </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K259" t="n">
+      <c r="J259" t="n">
+        <v>6.62995</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10063,12 +10842,15 @@
       <c r="I260" t="n">
         <v>-3.01587</v>
       </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K260" t="n">
+      <c r="J260" t="n">
+        <v>6.90737</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10100,12 +10882,15 @@
       <c r="I261" t="n">
         <v>-3.02067</v>
       </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K261" t="n">
+      <c r="J261" t="n">
+        <v>5.46892</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10137,12 +10922,15 @@
       <c r="I262" t="n">
         <v>-2.86624</v>
       </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K262" t="n">
+      <c r="J262" t="n">
+        <v>4.06068</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10174,12 +10962,15 @@
       <c r="I263" t="n">
         <v>-2.55591</v>
       </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K263" t="n">
+      <c r="J263" t="n">
+        <v>3.98664</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10211,12 +11002,15 @@
       <c r="I264" t="n">
         <v>-2.40385</v>
       </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K264" t="n">
+      <c r="J264" t="n">
+        <v>3.80942</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10248,12 +11042,15 @@
       <c r="I265" t="n">
         <v>-2.2508</v>
       </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K265" t="n">
+      <c r="J265" t="n">
+        <v>3.70184</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10285,12 +11082,15 @@
       <c r="I266" t="n">
         <v>-2.09677</v>
       </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K266" t="n">
+      <c r="J266" t="n">
+        <v>2.87385</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10322,12 +11122,15 @@
       <c r="I267" t="n">
         <v>-1.94175</v>
       </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K267" t="n">
+      <c r="J267" t="n">
+        <v>2.68867</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10359,12 +11162,15 @@
       <c r="I268" t="n">
         <v>-1.62338</v>
       </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K268" t="n">
+      <c r="J268" t="n">
+        <v>2.18501</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10396,12 +11202,15 @@
       <c r="I269" t="n">
         <v>-1.30293</v>
       </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K269" t="n">
+      <c r="J269" t="n">
+        <v>2.61295</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10433,12 +11242,15 @@
       <c r="I270" t="n">
         <v>-1.14192</v>
       </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K270" t="n">
+      <c r="J270" t="n">
+        <v>2.24409</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10470,12 +11282,15 @@
       <c r="I271" t="n">
         <v>-0.81699</v>
       </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K271" t="n">
+      <c r="J271" t="n">
+        <v>2.02556</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10507,12 +11322,15 @@
       <c r="I272" t="n">
         <v>-0.491</v>
       </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K272" t="n">
+      <c r="J272" t="n">
+        <v>2.06781</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10544,12 +11362,15 @@
       <c r="I273" t="n">
         <v>-0.32787</v>
       </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K273" t="n">
+      <c r="J273" t="n">
+        <v>2.87077</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10581,12 +11402,15 @@
       <c r="I274" t="n">
         <v>-0.16393</v>
       </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K274" t="n">
+      <c r="J274" t="n">
+        <v>2.13198</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10618,12 +11442,15 @@
       <c r="I275" t="n">
         <v>0</v>
       </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K275" t="n">
+      <c r="J275" t="n">
+        <v>2.59061</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10655,12 +11482,15 @@
       <c r="I276" t="n">
         <v>0.32841</v>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K276" t="n">
+      <c r="J276" t="n">
+        <v>2.64213</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10692,12 +11522,15 @@
       <c r="I277" t="n">
         <v>0.65789</v>
       </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K277" t="n">
+      <c r="J277" t="n">
+        <v>2.55371</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10729,12 +11562,15 @@
       <c r="I278" t="n">
         <v>0.98847</v>
       </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K278" t="n">
+      <c r="J278" t="n">
+        <v>3.57057</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10766,12 +11602,15 @@
       <c r="I279" t="n">
         <v>1.32013</v>
       </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K279" t="n">
+      <c r="J279" t="n">
+        <v>3.10631</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10803,12 +11642,15 @@
       <c r="I280" t="n">
         <v>1.48515</v>
       </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K280" t="n">
+      <c r="J280" t="n">
+        <v>3.13352</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10840,12 +11682,15 @@
       <c r="I281" t="n">
         <v>1.65017</v>
       </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K281" t="n">
+      <c r="J281" t="n">
+        <v>2.52939</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10877,12 +11722,15 @@
       <c r="I282" t="n">
         <v>1.65017</v>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K282" t="n">
+      <c r="J282" t="n">
+        <v>2.46755</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10914,12 +11762,15 @@
       <c r="I283" t="n">
         <v>1.64745</v>
       </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K283" t="n">
+      <c r="J283" t="n">
+        <v>1.70802</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10951,12 +11802,15 @@
       <c r="I284" t="n">
         <v>1.48026</v>
       </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K284" t="n">
+      <c r="J284" t="n">
+        <v>1.26787</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10988,12 +11842,15 @@
       <c r="I285" t="n">
         <v>1.64474</v>
       </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K285" t="n">
+      <c r="J285" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11025,12 +11882,15 @@
       <c r="I286" t="n">
         <v>1.47783</v>
       </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K286" t="n">
+      <c r="J286" t="n">
+        <v>1.35733</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11062,12 +11922,15 @@
       <c r="I287" t="n">
         <v>1.31148</v>
       </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K287" t="n">
+      <c r="J287" t="n">
+        <v>1.27691</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11099,12 +11962,15 @@
       <c r="I288" t="n">
         <v>0.982</v>
       </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K288" t="n">
+      <c r="J288" t="n">
+        <v>0.5296999999999999</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11136,12 +12002,15 @@
       <c r="I289" t="n">
         <v>0.81699</v>
       </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K289" t="n">
+      <c r="J289" t="n">
+        <v>-0.27377</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11173,12 +12042,15 @@
       <c r="I290" t="n">
         <v>0.6525300000000001</v>
       </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K290" t="n">
+      <c r="J290" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11210,12 +12082,15 @@
       <c r="I291" t="n">
         <v>0.4886</v>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K291" t="n">
+      <c r="J291" t="n">
+        <v>-0.23617</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11247,12 +12122,15 @@
       <c r="I292" t="n">
         <v>0.3252</v>
       </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K292" t="n">
+      <c r="J292" t="n">
+        <v>-0.7377899999999999</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11284,12 +12162,15 @@
       <c r="I293" t="n">
         <v>0.16234</v>
       </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K293" t="n">
+      <c r="J293" t="n">
+        <v>-0.52172</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11321,12 +12202,15 @@
       <c r="I294" t="n">
         <v>0.16234</v>
       </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K294" t="n">
+      <c r="J294" t="n">
+        <v>-0.8229</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11358,12 +12242,15 @@
       <c r="I295" t="n">
         <v>0</v>
       </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K295" t="n">
+      <c r="J295" t="n">
+        <v>-0.05906</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11395,12 +12282,15 @@
       <c r="I296" t="n">
         <v>0</v>
       </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K296" t="n">
+      <c r="J296" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11432,12 +12322,15 @@
       <c r="I297" t="n">
         <v>-0.16181</v>
       </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K297" t="n">
+      <c r="J297" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11469,12 +12362,15 @@
       <c r="I298" t="n">
         <v>-0.16181</v>
       </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K298" t="n">
+      <c r="J298" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11506,12 +12402,15 @@
       <c r="I299" t="n">
         <v>-0.16181</v>
       </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K299" t="n">
+      <c r="J299" t="n">
+        <v>-0.008840000000000001</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11543,12 +12442,15 @@
       <c r="I300" t="n">
         <v>0.16207</v>
       </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K300" t="n">
+      <c r="J300" t="n">
+        <v>1.00172</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11580,12 +12482,15 @@
       <c r="I301" t="n">
         <v>0.32415</v>
       </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K301" t="n">
+      <c r="J301" t="n">
+        <v>1.95501</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11617,12 +12522,15 @@
       <c r="I302" t="n">
         <v>0.32415</v>
       </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K302" t="n">
+      <c r="J302" t="n">
+        <v>1.47719</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L302" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11654,12 +12562,15 @@
       <c r="I303" t="n">
         <v>0.32415</v>
       </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K303" t="n">
+      <c r="J303" t="n">
+        <v>1.98082</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11691,12 +12602,15 @@
       <c r="I304" t="n">
         <v>0.48622</v>
       </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K304" t="n">
+      <c r="J304" t="n">
+        <v>2.73019</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L304" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11728,12 +12642,15 @@
       <c r="I305" t="n">
         <v>0.48622</v>
       </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K305" t="n">
+      <c r="J305" t="n">
+        <v>2.50477</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11765,12 +12682,15 @@
       <c r="I306" t="n">
         <v>0.48622</v>
       </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K306" t="n">
+      <c r="J306" t="n">
+        <v>2.97813</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11802,12 +12722,15 @@
       <c r="I307" t="n">
         <v>0.6483</v>
       </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K307" t="n">
+      <c r="J307" t="n">
+        <v>3.47011</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11839,12 +12762,15 @@
       <c r="I308" t="n">
         <v>0.6483</v>
       </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K308" t="n">
+      <c r="J308" t="n">
+        <v>3.01415</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L308" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11876,12 +12802,15 @@
       <c r="I309" t="n">
         <v>0.81037</v>
       </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K309" t="n">
+      <c r="J309" t="n">
+        <v>3.06809</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11913,12 +12842,15 @@
       <c r="I310" t="n">
         <v>0.81037</v>
       </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K310" t="n">
+      <c r="J310" t="n">
+        <v>2.6111</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L310" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11950,12 +12882,15 @@
       <c r="I311" t="n">
         <v>0.97245</v>
       </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K311" t="n">
+      <c r="J311" t="n">
+        <v>2.99353</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L311" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11987,12 +12922,15 @@
       <c r="I312" t="n">
         <v>0.80906</v>
       </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K312" t="n">
+      <c r="J312" t="n">
+        <v>2.74941</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12024,12 +12962,15 @@
       <c r="I313" t="n">
         <v>0.6462</v>
       </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K313" t="n">
+      <c r="J313" t="n">
+        <v>2.39374</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12061,12 +13002,15 @@
       <c r="I314" t="n">
         <v>0.6462</v>
       </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K314" t="n">
+      <c r="J314" t="n">
+        <v>1.92627</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12098,12 +13042,15 @@
       <c r="I315" t="n">
         <v>0.6462</v>
       </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K315" t="n">
+      <c r="J315" t="n">
+        <v>2.41007</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12135,12 +13082,15 @@
       <c r="I316" t="n">
         <v>0.64516</v>
       </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K316" t="n">
+      <c r="J316" t="n">
+        <v>2.62675</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12172,12 +13122,15 @@
       <c r="I317" t="n">
         <v>0.48387</v>
       </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K317" t="n">
+      <c r="J317" t="n">
+        <v>3.43649</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12209,12 +13162,15 @@
       <c r="I318" t="n">
         <v>0.48387</v>
       </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K318" t="n">
+      <c r="J318" t="n">
+        <v>3.3741</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L318" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12246,12 +13202,15 @@
       <c r="I319" t="n">
         <v>0.16103</v>
       </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K319" t="n">
+      <c r="J319" t="n">
+        <v>3.14975</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L319" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12283,12 +13242,15 @@
       <c r="I320" t="n">
         <v>0</v>
       </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K320" t="n">
+      <c r="J320" t="n">
+        <v>3.12855</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L320" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12320,12 +13282,15 @@
       <c r="I321" t="n">
         <v>-0.48232</v>
       </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K321" t="n">
+      <c r="J321" t="n">
+        <v>3.1808</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L321" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12357,12 +13322,15 @@
       <c r="I322" t="n">
         <v>-0.6430900000000001</v>
       </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K322" t="n">
+      <c r="J322" t="n">
+        <v>3.7925</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L322" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12394,12 +13362,15 @@
       <c r="I323" t="n">
         <v>-0.96308</v>
       </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K323" t="n">
+      <c r="J323" t="n">
+        <v>3.92538</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L323" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12431,12 +13402,15 @@
       <c r="I324" t="n">
         <v>-1.1236</v>
       </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K324" t="n">
+      <c r="J324" t="n">
+        <v>3.68468</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L324" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12468,12 +13442,15 @@
       <c r="I325" t="n">
         <v>-1.1236</v>
       </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K325" t="n">
+      <c r="J325" t="n">
+        <v>3.30291</v>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12505,12 +13482,15 @@
       <c r="I326" t="n">
         <v>-1.1236</v>
       </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K326" t="n">
+      <c r="J326" t="n">
+        <v>2.86511</v>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L326" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12542,12 +13522,15 @@
       <c r="I327" t="n">
         <v>-0.96308</v>
       </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K327" t="n">
+      <c r="J327" t="n">
+        <v>2.05802</v>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L327" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12579,12 +13562,15 @@
       <c r="I328" t="n">
         <v>-0.96154</v>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K328" t="n">
+      <c r="J328" t="n">
+        <v>1.82602</v>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L328" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12616,12 +13602,15 @@
       <c r="I329" t="n">
         <v>-0.80257</v>
       </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K329" t="n">
+      <c r="J329" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L329" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12653,12 +13642,15 @@
       <c r="I330" t="n">
         <v>-0.80257</v>
       </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K330" t="n">
+      <c r="J330" t="n">
+        <v>1.15674</v>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L330" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12690,12 +13682,15 @@
       <c r="I331" t="n">
         <v>-0.80386</v>
       </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K331" t="n">
+      <c r="J331" t="n">
+        <v>0.72941</v>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L331" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12727,12 +13722,15 @@
       <c r="I332" t="n">
         <v>-0.80515</v>
       </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K332" t="n">
+      <c r="J332" t="n">
+        <v>1.13298</v>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L332" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12764,12 +13762,15 @@
       <c r="I333" t="n">
         <v>-0.6462</v>
       </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K333" t="n">
+      <c r="J333" t="n">
+        <v>1.19602</v>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L333" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12801,12 +13802,15 @@
       <c r="I334" t="n">
         <v>-0.80906</v>
       </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K334" t="n">
+      <c r="J334" t="n">
+        <v>1.05157</v>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L334" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12838,12 +13842,15 @@
       <c r="I335" t="n">
         <v>-0.81037</v>
       </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K335" t="n">
+      <c r="J335" t="n">
+        <v>1.72674</v>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L335" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12875,12 +13882,15 @@
       <c r="I336" t="n">
         <v>-0.81169</v>
       </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K336" t="n">
+      <c r="J336" t="n">
+        <v>-2.43287</v>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L336" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12912,12 +13922,15 @@
       <c r="I337" t="n">
         <v>-0.81169</v>
       </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K337" t="n">
+      <c r="J337" t="n">
+        <v>2.74486</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L337" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12949,12 +13962,15 @@
       <c r="I338" t="n">
         <v>-0.97403</v>
       </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K338" t="n">
+      <c r="J338" t="n">
+        <v>-0.53278</v>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L338" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12986,12 +14002,15 @@
       <c r="I339" t="n">
         <v>-1.2966</v>
       </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K339" t="n">
+      <c r="J339" t="n">
+        <v>-0.09285</v>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L339" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13023,12 +14042,15 @@
       <c r="I340" t="n">
         <v>-1.45631</v>
       </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K340" t="n">
+      <c r="J340" t="n">
+        <v>-0.52616</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L340" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13060,12 +14082,15 @@
       <c r="I341" t="n">
         <v>-1.45631</v>
       </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K341" t="n">
+      <c r="J341" t="n">
+        <v>-1.22507</v>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L341" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13097,12 +14122,15 @@
       <c r="I342" t="n">
         <v>-1.45631</v>
       </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K342" t="n">
+      <c r="J342" t="n">
+        <v>-1.44273</v>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L342" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13134,12 +14162,15 @@
       <c r="I343" t="n">
         <v>-1.2966</v>
       </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K343" t="n">
+      <c r="J343" t="n">
+        <v>-1.09171</v>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L343" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13171,12 +14202,15 @@
       <c r="I344" t="n">
         <v>-0.97403</v>
       </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K344" t="n">
+      <c r="J344" t="n">
+        <v>-0.75704</v>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L344" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13208,12 +14242,15 @@
       <c r="I345" t="n">
         <v>-0.65041</v>
       </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K345" t="n">
+      <c r="J345" t="n">
+        <v>-0.69376</v>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L345" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13245,12 +14282,15 @@
       <c r="I346" t="n">
         <v>-0.16313</v>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K346" t="n">
+      <c r="J346" t="n">
+        <v>-0.13945</v>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L346" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13282,12 +14322,15 @@
       <c r="I347" t="n">
         <v>0.1634</v>
       </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K347" t="n">
+      <c r="J347" t="n">
+        <v>-1.0381</v>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L347" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13319,12 +14362,15 @@
       <c r="I348" t="n">
         <v>0.491</v>
       </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K348" t="n">
+      <c r="J348" t="n">
+        <v>2.99158</v>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L348" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13356,12 +14402,15 @@
       <c r="I349" t="n">
         <v>0.65466</v>
       </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K349" t="n">
+      <c r="J349" t="n">
+        <v>-1.39386</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13393,12 +14442,15 @@
       <c r="I350" t="n">
         <v>0.65574</v>
       </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K350" t="n">
+      <c r="J350" t="n">
+        <v>2.56005</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L350" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13430,12 +14482,15 @@
       <c r="I351" t="n">
         <v>0.65681</v>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K351" t="n">
+      <c r="J351" t="n">
+        <v>1.78134</v>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L351" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13467,12 +14522,15 @@
       <c r="I352" t="n">
         <v>0.65681</v>
       </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K352" t="n">
+      <c r="J352" t="n">
+        <v>1.56742</v>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L352" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13504,12 +14562,15 @@
       <c r="I353" t="n">
         <v>-5.41872</v>
       </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K353" t="n">
+      <c r="J353" t="n">
+        <v>-49.2774</v>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L353" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13541,12 +14602,15 @@
       <c r="I354" t="n">
         <v>-2.95567</v>
       </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K354" t="n">
+      <c r="J354" t="n">
+        <v>-69.48389</v>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L354" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13578,12 +14642,15 @@
       <c r="I355" t="n">
         <v>-2.95567</v>
       </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K355" t="n">
+      <c r="J355" t="n">
+        <v>-70.07268000000001</v>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L355" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13615,12 +14682,15 @@
       <c r="I356" t="n">
         <v>-1.63934</v>
       </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K356" t="n">
+      <c r="J356" t="n">
+        <v>-74.73842</v>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L356" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13652,12 +14722,15 @@
       <c r="I357" t="n">
         <v>-2.12766</v>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K357" t="n">
+      <c r="J357" t="n">
+        <v>-74.86150000000001</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13689,12 +14762,15 @@
       <c r="I358" t="n">
         <v>-9.64052</v>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K358" t="n">
+      <c r="J358" t="n">
+        <v>-76.53857000000001</v>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L358" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13726,12 +14802,15 @@
       <c r="I359" t="n">
         <v>-6.68842</v>
       </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K359" t="n">
+      <c r="J359" t="n">
+        <v>-66.67775</v>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L359" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13763,12 +14842,15 @@
       <c r="I360" t="n">
         <v>-5.21173</v>
       </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K360" t="n">
+      <c r="J360" t="n">
+        <v>-56.85972</v>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L360" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13800,12 +14882,15 @@
       <c r="I361" t="n">
         <v>-3.90244</v>
       </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="K361" t="n">
+      <c r="J361" t="n">
+        <v>-53.25212</v>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="L361" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -465,22 +465,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>HILEIHN_PC1</t>
+          <t>Total Leisure eMP</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>HIUR_PC1</t>
+          <t>Unemp Rate</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LBSSA15_PC1</t>
+          <t>LFP</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SMU15000007072100001SA_PC1</t>
+          <t>Accomodation Emp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L361"/>
+  <dimension ref="A1:M361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,10 +485,15 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Econ Activity Index</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Mandatory Quarantine</t>
         </is>
@@ -525,12 +530,15 @@
       <c r="J2" t="n">
         <v>6.87323</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
+      <c r="K2" t="n">
+        <v>2.30506</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -565,12 +573,15 @@
       <c r="J3" t="n">
         <v>4.15367</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
+      <c r="K3" t="n">
+        <v>2.43806</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -605,12 +616,15 @@
       <c r="J4" t="n">
         <v>7.55398</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="K4" t="n">
+        <v>2.13186</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -645,12 +659,15 @@
       <c r="J5" t="n">
         <v>0.74259</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
+        <v>2.02259</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -685,12 +702,15 @@
       <c r="J6" t="n">
         <v>1.77784</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="K6" t="n">
+        <v>1.97981</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,12 +745,15 @@
       <c r="J7" t="n">
         <v>2.02157</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>1.71466</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -765,12 +788,15 @@
       <c r="J8" t="n">
         <v>4.61385</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
+        <v>1.47327</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -805,12 +831,15 @@
       <c r="J9" t="n">
         <v>7.05482</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+      <c r="K9" t="n">
+        <v>1.21046</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -845,12 +874,15 @@
       <c r="J10" t="n">
         <v>8.03481</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+      <c r="K10" t="n">
+        <v>0.70021</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -885,12 +917,15 @@
       <c r="J11" t="n">
         <v>5.90081</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+      <c r="K11" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -925,12 +960,15 @@
       <c r="J12" t="n">
         <v>3.00194</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
+      <c r="K12" t="n">
+        <v>0.05167</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -965,12 +1003,15 @@
       <c r="J13" t="n">
         <v>3.56805</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
+      <c r="K13" t="n">
+        <v>-0.19352</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,12 +1046,15 @@
       <c r="J14" t="n">
         <v>2.00281</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
+        <v>-0.7725</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,12 +1089,15 @@
       <c r="J15" t="n">
         <v>3.20213</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
+        <v>-1.00347</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1085,12 +1132,15 @@
       <c r="J16" t="n">
         <v>4.71972</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
+      <c r="K16" t="n">
+        <v>-1.21118</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1125,12 +1175,15 @@
       <c r="J17" t="n">
         <v>5.26354</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>-1.68641</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1165,12 +1218,15 @@
       <c r="J18" t="n">
         <v>4.22933</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
+      <c r="K18" t="n">
+        <v>-1.97994</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1205,12 +1261,15 @@
       <c r="J19" t="n">
         <v>3.76165</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+      <c r="K19" t="n">
+        <v>-2.26483</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1245,12 +1304,15 @@
       <c r="J20" t="n">
         <v>0.94789</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
+      <c r="K20" t="n">
+        <v>-2.53116</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1285,12 +1347,15 @@
       <c r="J21" t="n">
         <v>-1.13358</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="K21" t="n">
+        <v>-2.58488</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1325,12 +1390,15 @@
       <c r="J22" t="n">
         <v>-2.8686</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+      <c r="K22" t="n">
+        <v>-2.39506</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1365,12 +1433,15 @@
       <c r="J23" t="n">
         <v>-2.60379</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
+      <c r="K23" t="n">
+        <v>-2.39814</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,12 +1476,15 @@
       <c r="J24" t="n">
         <v>-2.90647</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="K24" t="n">
+        <v>-2.19468</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1445,12 +1519,15 @@
       <c r="J25" t="n">
         <v>-3.72218</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="K25" t="n">
+        <v>-1.93899</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1485,12 +1562,15 @@
       <c r="J26" t="n">
         <v>-6.68686</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="K26" t="n">
+        <v>-1.50513</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1525,12 +1605,15 @@
       <c r="J27" t="n">
         <v>-7.29507</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+      <c r="K27" t="n">
+        <v>-0.97466</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,12 +1648,15 @@
       <c r="J28" t="n">
         <v>-7.18887</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
+      <c r="K28" t="n">
+        <v>-0.46954</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1605,12 +1691,15 @@
       <c r="J29" t="n">
         <v>-8.49579</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+      <c r="K29" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1645,12 +1734,15 @@
       <c r="J30" t="n">
         <v>-7.96439</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
+      <c r="K30" t="n">
+        <v>0.61647</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1685,12 +1777,15 @@
       <c r="J31" t="n">
         <v>-7.24745</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
+      <c r="K31" t="n">
+        <v>1.11916</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1725,12 +1820,15 @@
       <c r="J32" t="n">
         <v>-7.5816</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
+        <v>1.3314</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1765,12 +1863,15 @@
       <c r="J33" t="n">
         <v>-8.440099999999999</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
+      <c r="K33" t="n">
+        <v>1.54455</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1805,12 +1906,15 @@
       <c r="J34" t="n">
         <v>-7.62422</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
+      <c r="K34" t="n">
+        <v>1.56992</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1845,12 +1949,15 @@
       <c r="J35" t="n">
         <v>-5.89477</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
+      <c r="K35" t="n">
+        <v>1.61162</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1885,12 +1992,15 @@
       <c r="J36" t="n">
         <v>-7.24322</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
+      <c r="K36" t="n">
+        <v>1.34636</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1925,12 +2035,15 @@
       <c r="J37" t="n">
         <v>-7.38131</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
+      <c r="K37" t="n">
+        <v>1.02821</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1965,12 +2078,15 @@
       <c r="J38" t="n">
         <v>-3.30781</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
+      <c r="K38" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2005,12 +2121,15 @@
       <c r="J39" t="n">
         <v>-2.16373</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
+      <c r="K39" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,12 +2164,15 @@
       <c r="J40" t="n">
         <v>-1.56239</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
+      <c r="K40" t="n">
+        <v>-0.23588</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2085,12 +2207,15 @@
       <c r="J41" t="n">
         <v>-0.60228</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
+      <c r="K41" t="n">
+        <v>-0.75708</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2125,12 +2250,15 @@
       <c r="J42" t="n">
         <v>-1.01636</v>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
+      <c r="K42" t="n">
+        <v>-1.082</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2165,12 +2293,15 @@
       <c r="J43" t="n">
         <v>-1.00361</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
+      <c r="K43" t="n">
+        <v>-1.06771</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2205,12 +2336,15 @@
       <c r="J44" t="n">
         <v>1.32015</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
+      <c r="K44" t="n">
+        <v>-1.27488</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2245,12 +2379,15 @@
       <c r="J45" t="n">
         <v>0.68588</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
+      <c r="K45" t="n">
+        <v>-1.24805</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2285,12 +2422,15 @@
       <c r="J46" t="n">
         <v>1.35223</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
+      <c r="K46" t="n">
+        <v>-1.22094</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2325,12 +2465,15 @@
       <c r="J47" t="n">
         <v>1.09793</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
+      <c r="K47" t="n">
+        <v>-1.00104</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2365,12 +2508,15 @@
       <c r="J48" t="n">
         <v>2.6756</v>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
+      <c r="K48" t="n">
+        <v>-0.4298</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2405,12 +2551,15 @@
       <c r="J49" t="n">
         <v>2.51899</v>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
+      <c r="K49" t="n">
+        <v>0.11743</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2445,12 +2594,15 @@
       <c r="J50" t="n">
         <v>1.41031</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
+      <c r="K50" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2485,12 +2637,15 @@
       <c r="J51" t="n">
         <v>0.18329</v>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
+      <c r="K51" t="n">
+        <v>0.87892</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2525,12 +2680,15 @@
       <c r="J52" t="n">
         <v>-0.83586</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
+      <c r="K52" t="n">
+        <v>0.88007</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2565,12 +2723,15 @@
       <c r="J53" t="n">
         <v>-0.6408700000000001</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
+      <c r="K53" t="n">
+        <v>0.84177</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2605,12 +2766,15 @@
       <c r="J54" t="n">
         <v>-0.46422</v>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
+      <c r="K54" t="n">
+        <v>0.88297</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2645,12 +2809,15 @@
       <c r="J55" t="n">
         <v>-1.2576</v>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
+      <c r="K55" t="n">
+        <v>0.61858</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2685,12 +2852,15 @@
       <c r="J56" t="n">
         <v>-2.05585</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
+      <c r="K56" t="n">
+        <v>0.57979</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2725,12 +2895,15 @@
       <c r="J57" t="n">
         <v>-0.07042</v>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
+      <c r="K57" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2765,12 +2938,15 @@
       <c r="J58" t="n">
         <v>-0.9904500000000001</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
+      <c r="K58" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2805,12 +2981,15 @@
       <c r="J59" t="n">
         <v>-2.11234</v>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
+      <c r="K59" t="n">
+        <v>-0.01313</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2845,12 +3024,15 @@
       <c r="J60" t="n">
         <v>-1.08805</v>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
+      <c r="K60" t="n">
+        <v>-0.30085</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2885,12 +3067,15 @@
       <c r="J61" t="n">
         <v>-1.03275</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
+      <c r="K61" t="n">
+        <v>-0.5734399999999999</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2925,12 +3110,15 @@
       <c r="J62" t="n">
         <v>-0.74471</v>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
+      <c r="K62" t="n">
+        <v>-0.80708</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2965,12 +3153,15 @@
       <c r="J63" t="n">
         <v>1.2471</v>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
+      <c r="K63" t="n">
+        <v>-0.76723</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3005,12 +3196,15 @@
       <c r="J64" t="n">
         <v>1.93804</v>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
+      <c r="K64" t="n">
+        <v>-0.52083</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3045,12 +3239,15 @@
       <c r="J65" t="n">
         <v>0.72118</v>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
+      <c r="K65" t="n">
+        <v>-0.28694</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3085,12 +3282,15 @@
       <c r="J66" t="n">
         <v>1.0878</v>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
+      <c r="K66" t="n">
+        <v>-0.01306</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3125,12 +3325,15 @@
       <c r="J67" t="n">
         <v>2.17111</v>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
+      <c r="K67" t="n">
+        <v>0.23545</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3165,12 +3368,15 @@
       <c r="J68" t="n">
         <v>2.45751</v>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
+      <c r="K68" t="n">
+        <v>0.79916</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3205,12 +3411,15 @@
       <c r="J69" t="n">
         <v>2.30566</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
+      <c r="K69" t="n">
+        <v>1.11563</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3245,12 +3454,15 @@
       <c r="J70" t="n">
         <v>2.95779</v>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
+      <c r="K70" t="n">
+        <v>1.12802</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3285,12 +3497,15 @@
       <c r="J71" t="n">
         <v>3.13813</v>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
+      <c r="K71" t="n">
+        <v>1.15577</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3325,12 +3540,15 @@
       <c r="J72" t="n">
         <v>2.07499</v>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
+      <c r="K72" t="n">
+        <v>0.91839</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3365,12 +3583,15 @@
       <c r="J73" t="n">
         <v>3.72548</v>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
+      <c r="K73" t="n">
+        <v>0.95688</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3405,12 +3626,15 @@
       <c r="J74" t="n">
         <v>3.27738</v>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
+      <c r="K74" t="n">
+        <v>0.95801</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3445,12 +3669,15 @@
       <c r="J75" t="n">
         <v>1.52746</v>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
+      <c r="K75" t="n">
+        <v>0.93042</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3485,12 +3712,15 @@
       <c r="J76" t="n">
         <v>1.24683</v>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
+      <c r="K76" t="n">
+        <v>0.92932</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3525,12 +3755,15 @@
       <c r="J77" t="n">
         <v>1.24298</v>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
+      <c r="K77" t="n">
+        <v>0.96795</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3565,12 +3798,15 @@
       <c r="J78" t="n">
         <v>-0.03912</v>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
+      <c r="K78" t="n">
+        <v>1.21505</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3605,12 +3841,15 @@
       <c r="J79" t="n">
         <v>-1.36338</v>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
+      <c r="K79" t="n">
+        <v>1.22667</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3645,12 +3884,15 @@
       <c r="J80" t="n">
         <v>-1.24423</v>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
+      <c r="K80" t="n">
+        <v>0.93579</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3685,12 +3927,15 @@
       <c r="J81" t="n">
         <v>-1.38608</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
+      <c r="K81" t="n">
+        <v>1.19418</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3725,12 +3970,15 @@
       <c r="J82" t="n">
         <v>-1.8118</v>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
+      <c r="K82" t="n">
+        <v>1.45266</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3765,12 +4013,15 @@
       <c r="J83" t="n">
         <v>-1.15059</v>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
+      <c r="K83" t="n">
+        <v>1.71384</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3805,12 +4056,15 @@
       <c r="J84" t="n">
         <v>-1.29216</v>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
+      <c r="K84" t="n">
+        <v>2.22309</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3845,12 +4099,15 @@
       <c r="J85" t="n">
         <v>-2.01288</v>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
+      <c r="K85" t="n">
+        <v>2.2202</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3885,12 +4142,15 @@
       <c r="J86" t="n">
         <v>-1.71983</v>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
+      <c r="K86" t="n">
+        <v>2.46978</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3925,12 +4185,15 @@
       <c r="J87" t="n">
         <v>-1.27068</v>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
+      <c r="K87" t="n">
+        <v>2.46689</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3965,12 +4228,15 @@
       <c r="J88" t="n">
         <v>-0.97194</v>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
+      <c r="K88" t="n">
+        <v>2.46401</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4005,12 +4271,15 @@
       <c r="J89" t="n">
         <v>-0.57021</v>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
+      <c r="K89" t="n">
+        <v>2.50032</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4045,12 +4314,15 @@
       <c r="J90" t="n">
         <v>0.17421</v>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
+      <c r="K90" t="n">
+        <v>2.01368</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4085,12 +4357,15 @@
       <c r="J91" t="n">
         <v>0.38878</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
+      <c r="K91" t="n">
+        <v>1.97241</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4125,12 +4400,15 @@
       <c r="J92" t="n">
         <v>-0.22581</v>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
+      <c r="K92" t="n">
+        <v>1.75122</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4165,12 +4443,15 @@
       <c r="J93" t="n">
         <v>-0.9389999999999999</v>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
+      <c r="K93" t="n">
+        <v>1.48794</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4205,12 +4486,15 @@
       <c r="J94" t="n">
         <v>-1.3879</v>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L94" t="n">
+      <c r="K94" t="n">
+        <v>1.26566</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4245,12 +4529,15 @@
       <c r="J95" t="n">
         <v>-2.02748</v>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
+      <c r="K95" t="n">
+        <v>1.1999</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4285,12 +4572,15 @@
       <c r="J96" t="n">
         <v>-1.27398</v>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
+      <c r="K96" t="n">
+        <v>1.20819</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4325,12 +4615,15 @@
       <c r="J97" t="n">
         <v>-1.95338</v>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
+      <c r="K97" t="n">
+        <v>1.46069</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4365,12 +4658,15 @@
       <c r="J98" t="n">
         <v>-1.95983</v>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
+      <c r="K98" t="n">
+        <v>1.67449</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4405,12 +4701,15 @@
       <c r="J99" t="n">
         <v>-2.02135</v>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
+      <c r="K99" t="n">
+        <v>1.96401</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4445,12 +4744,15 @@
       <c r="J100" t="n">
         <v>-2.2275</v>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
+      <c r="K100" t="n">
+        <v>2.25288</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4485,12 +4787,15 @@
       <c r="J101" t="n">
         <v>-1.59591</v>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L101" t="n">
+      <c r="K101" t="n">
+        <v>2.3003</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4525,12 +4830,15 @@
       <c r="J102" t="n">
         <v>-1.13134</v>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
+      <c r="K102" t="n">
+        <v>2.79641</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4565,12 +4873,15 @@
       <c r="J103" t="n">
         <v>-0.70105</v>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L103" t="n">
+      <c r="K103" t="n">
+        <v>3.12263</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4605,12 +4916,15 @@
       <c r="J104" t="n">
         <v>-1.63677</v>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
+      <c r="K104" t="n">
+        <v>3.4042</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4645,12 +4959,15 @@
       <c r="J105" t="n">
         <v>-1.31027</v>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
+      <c r="K105" t="n">
+        <v>3.72851</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4685,12 +5002,15 @@
       <c r="J106" t="n">
         <v>-1.71536</v>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
+      <c r="K106" t="n">
+        <v>4.01464</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4725,12 +5045,15 @@
       <c r="J107" t="n">
         <v>0.61221</v>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
+      <c r="K107" t="n">
+        <v>4.36428</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4765,12 +5088,15 @@
       <c r="J108" t="n">
         <v>1.6503</v>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
+      <c r="K108" t="n">
+        <v>4.39809</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4805,12 +5131,15 @@
       <c r="J109" t="n">
         <v>2.32905</v>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
+      <c r="K109" t="n">
+        <v>4.68202</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4845,12 +5174,15 @@
       <c r="J110" t="n">
         <v>0.6664099999999999</v>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
+      <c r="K110" t="n">
+        <v>4.75359</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4885,12 +5217,15 @@
       <c r="J111" t="n">
         <v>0.90567</v>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
+      <c r="K111" t="n">
+        <v>4.511</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4925,12 +5260,15 @@
       <c r="J112" t="n">
         <v>1.75485</v>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
+      <c r="K112" t="n">
+        <v>4.54264</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4965,12 +5303,15 @@
       <c r="J113" t="n">
         <v>2.68801</v>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
+      <c r="K113" t="n">
+        <v>4.54658</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5005,12 +5346,15 @@
       <c r="J114" t="n">
         <v>2.87432</v>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L114" t="n">
+      <c r="K114" t="n">
+        <v>4.57903</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5045,12 +5389,15 @@
       <c r="J115" t="n">
         <v>3.30693</v>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L115" t="n">
+      <c r="K115" t="n">
+        <v>4.36435</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5085,12 +5432,15 @@
       <c r="J116" t="n">
         <v>3.93853</v>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
+      <c r="K116" t="n">
+        <v>4.5894</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5125,12 +5475,15 @@
       <c r="J117" t="n">
         <v>3.90911</v>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
+      <c r="K117" t="n">
+        <v>4.53272</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5165,12 +5518,15 @@
       <c r="J118" t="n">
         <v>5.25938</v>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
+      <c r="K118" t="n">
+        <v>4.33305</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5205,12 +5561,15 @@
       <c r="J119" t="n">
         <v>3.59819</v>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
+      <c r="K119" t="n">
+        <v>4.29055</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5245,12 +5604,15 @@
       <c r="J120" t="n">
         <v>1.88625</v>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
+      <c r="K120" t="n">
+        <v>4.02022</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5285,12 +5647,15 @@
       <c r="J121" t="n">
         <v>1.4736</v>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L121" t="n">
+      <c r="K121" t="n">
+        <v>3.51591</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5325,12 +5690,15 @@
       <c r="J122" t="n">
         <v>3.3177</v>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
+      <c r="K122" t="n">
+        <v>2.90615</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5365,12 +5733,15 @@
       <c r="J123" t="n">
         <v>3.28843</v>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L123" t="n">
+      <c r="K123" t="n">
+        <v>2.90131</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5405,12 +5776,15 @@
       <c r="J124" t="n">
         <v>2.21633</v>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
+      <c r="K124" t="n">
+        <v>2.36798</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5445,12 +5819,15 @@
       <c r="J125" t="n">
         <v>0.8649</v>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
+      <c r="K125" t="n">
+        <v>2.26897</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5485,12 +5862,15 @@
       <c r="J126" t="n">
         <v>0.27475</v>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
+      <c r="K126" t="n">
+        <v>1.95386</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5525,12 +5905,15 @@
       <c r="J127" t="n">
         <v>-0.36777</v>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
+      <c r="K127" t="n">
+        <v>1.91472</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5565,12 +5948,15 @@
       <c r="J128" t="n">
         <v>-0.16223</v>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
+      <c r="K128" t="n">
+        <v>1.63819</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5605,12 +5991,15 @@
       <c r="J129" t="n">
         <v>0.60939</v>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
+      <c r="K129" t="n">
+        <v>1.13067</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5645,12 +6034,15 @@
       <c r="J130" t="n">
         <v>0.37904</v>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
+      <c r="K130" t="n">
+        <v>0.8027</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5685,12 +6077,15 @@
       <c r="J131" t="n">
         <v>-6.44729</v>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
+      <c r="K131" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5725,12 +6120,15 @@
       <c r="J132" t="n">
         <v>-7.12007</v>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
+      <c r="K132" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5765,12 +6163,15 @@
       <c r="J133" t="n">
         <v>-7.8633</v>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
+      <c r="K133" t="n">
+        <v>-0.06932000000000001</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5805,12 +6206,15 @@
       <c r="J134" t="n">
         <v>-7.87933</v>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
+      <c r="K134" t="n">
+        <v>0.53241</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5845,12 +6249,15 @@
       <c r="J135" t="n">
         <v>-7.84518</v>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
+      <c r="K135" t="n">
+        <v>0.51999</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5885,12 +6292,15 @@
       <c r="J136" t="n">
         <v>-7.1485</v>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
+      <c r="K136" t="n">
+        <v>1.04094</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5925,12 +6335,15 @@
       <c r="J137" t="n">
         <v>-6.829</v>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
+      <c r="K137" t="n">
+        <v>1.2942</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5965,12 +6378,15 @@
       <c r="J138" t="n">
         <v>-6.62404</v>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
+      <c r="K138" t="n">
+        <v>1.68552</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6005,12 +6421,15 @@
       <c r="J139" t="n">
         <v>-5.48699</v>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
+      <c r="K139" t="n">
+        <v>2.04011</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6045,12 +6464,15 @@
       <c r="J140" t="n">
         <v>-5.06328</v>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
+      <c r="K140" t="n">
+        <v>2.02625</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6085,12 +6507,15 @@
       <c r="J141" t="n">
         <v>-5.3158</v>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
+      <c r="K141" t="n">
+        <v>2.5242</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6125,12 +6550,15 @@
       <c r="J142" t="n">
         <v>-5.4778</v>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
+      <c r="K142" t="n">
+        <v>2.83901</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6165,12 +6593,15 @@
       <c r="J143" t="n">
         <v>-0.53771</v>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
+      <c r="K143" t="n">
+        <v>3.30254</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6205,12 +6636,15 @@
       <c r="J144" t="n">
         <v>1.45738</v>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
+      <c r="K144" t="n">
+        <v>3.63258</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6245,12 +6679,15 @@
       <c r="J145" t="n">
         <v>2.53959</v>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
+      <c r="K145" t="n">
+        <v>4</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6285,12 +6722,15 @@
       <c r="J146" t="n">
         <v>3.67652</v>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
+      <c r="K146" t="n">
+        <v>3.75317</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6325,12 +6765,15 @@
       <c r="J147" t="n">
         <v>3.14865</v>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
+      <c r="K147" t="n">
+        <v>3.73606</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6365,12 +6808,15 @@
       <c r="J148" t="n">
         <v>2.77778</v>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
+      <c r="K148" t="n">
+        <v>3.17079</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6405,12 +6851,15 @@
       <c r="J149" t="n">
         <v>2.01723</v>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
+      <c r="K149" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6445,12 +6894,15 @@
       <c r="J150" t="n">
         <v>1.69822</v>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L150" t="n">
+      <c r="K150" t="n">
+        <v>2.0663</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6485,12 +6937,15 @@
       <c r="J151" t="n">
         <v>0.24066</v>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
+      <c r="K151" t="n">
+        <v>1.67175</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6525,12 +6980,15 @@
       <c r="J152" t="n">
         <v>0.63305</v>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
+      <c r="K152" t="n">
+        <v>1.48951</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6565,12 +7023,15 @@
       <c r="J153" t="n">
         <v>0.9598100000000001</v>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
+      <c r="K153" t="n">
+        <v>1.21417</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6605,12 +7066,15 @@
       <c r="J154" t="n">
         <v>1.1216</v>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L154" t="n">
+      <c r="K154" t="n">
+        <v>1.4252</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6645,12 +7109,15 @@
       <c r="J155" t="n">
         <v>2.58983</v>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L155" t="n">
+      <c r="K155" t="n">
+        <v>1.45316</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6685,12 +7152,15 @@
       <c r="J156" t="n">
         <v>1.93557</v>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L156" t="n">
+      <c r="K156" t="n">
+        <v>1.45122</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6725,12 +7195,15 @@
       <c r="J157" t="n">
         <v>2.43277</v>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L157" t="n">
+      <c r="K157" t="n">
+        <v>1.4562</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6765,12 +7238,15 @@
       <c r="J158" t="n">
         <v>1.34564</v>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L158" t="n">
+      <c r="K158" t="n">
+        <v>1.69774</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6805,12 +7281,15 @@
       <c r="J159" t="n">
         <v>1.65367</v>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
+      <c r="K159" t="n">
+        <v>1.97252</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6845,12 +7324,15 @@
       <c r="J160" t="n">
         <v>1.57829</v>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L160" t="n">
+      <c r="K160" t="n">
+        <v>2.50749</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6885,12 +7367,15 @@
       <c r="J161" t="n">
         <v>2.46817</v>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L161" t="n">
+      <c r="K161" t="n">
+        <v>3.11146</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6925,12 +7410,15 @@
       <c r="J162" t="n">
         <v>3.24552</v>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L162" t="n">
+      <c r="K162" t="n">
+        <v>3.6485</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6965,12 +7453,15 @@
       <c r="J163" t="n">
         <v>4.06</v>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
+      <c r="K163" t="n">
+        <v>3.95512</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7005,12 +7496,15 @@
       <c r="J164" t="n">
         <v>3.68896</v>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L164" t="n">
+      <c r="K164" t="n">
+        <v>4.25839</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7045,12 +7539,15 @@
       <c r="J165" t="n">
         <v>2.90109</v>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L165" t="n">
+      <c r="K165" t="n">
+        <v>4.29857</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7085,12 +7582,15 @@
       <c r="J166" t="n">
         <v>2.53596</v>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L166" t="n">
+      <c r="K166" t="n">
+        <v>4.06063</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7125,12 +7625,15 @@
       <c r="J167" t="n">
         <v>3.64588</v>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L167" t="n">
+      <c r="K167" t="n">
+        <v>3.83429</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7165,12 +7668,15 @@
       <c r="J168" t="n">
         <v>3.48912</v>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
+      <c r="K168" t="n">
+        <v>4.12632</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7205,12 +7711,15 @@
       <c r="J169" t="n">
         <v>2.889</v>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L169" t="n">
+      <c r="K169" t="n">
+        <v>3.83478</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7245,12 +7754,15 @@
       <c r="J170" t="n">
         <v>2.85953</v>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L170" t="n">
+      <c r="K170" t="n">
+        <v>3.55701</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7285,12 +7797,15 @@
       <c r="J171" t="n">
         <v>2.90367</v>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
+      <c r="K171" t="n">
+        <v>3.53184</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7325,12 +7840,15 @@
       <c r="J172" t="n">
         <v>3.17376</v>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L172" t="n">
+      <c r="K172" t="n">
+        <v>3.53934</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7365,12 +7883,15 @@
       <c r="J173" t="n">
         <v>2.84697</v>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L173" t="n">
+      <c r="K173" t="n">
+        <v>3.55642</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7405,12 +7926,15 @@
       <c r="J174" t="n">
         <v>2.57144</v>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L174" t="n">
+      <c r="K174" t="n">
+        <v>3.30543</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7445,12 +7969,15 @@
       <c r="J175" t="n">
         <v>2.85247</v>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L175" t="n">
+      <c r="K175" t="n">
+        <v>3.03516</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7485,12 +8012,15 @@
       <c r="J176" t="n">
         <v>2.54939</v>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L176" t="n">
+      <c r="K176" t="n">
+        <v>2.99669</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7525,12 +8055,15 @@
       <c r="J177" t="n">
         <v>2.89893</v>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L177" t="n">
+      <c r="K177" t="n">
+        <v>3.03514</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7565,12 +8098,15 @@
       <c r="J178" t="n">
         <v>3.8442</v>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L178" t="n">
+      <c r="K178" t="n">
+        <v>2.99841</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7605,12 +8141,15 @@
       <c r="J179" t="n">
         <v>2.50148</v>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L179" t="n">
+      <c r="K179" t="n">
+        <v>2.92869</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7645,12 +8184,15 @@
       <c r="J180" t="n">
         <v>1.78988</v>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L180" t="n">
+      <c r="K180" t="n">
+        <v>2.5996</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7685,12 +8227,15 @@
       <c r="J181" t="n">
         <v>1.81115</v>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L181" t="n">
+      <c r="K181" t="n">
+        <v>2.91231</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7725,12 +8270,15 @@
       <c r="J182" t="n">
         <v>1.44836</v>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L182" t="n">
+      <c r="K182" t="n">
+        <v>2.89748</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7765,12 +8313,15 @@
       <c r="J183" t="n">
         <v>1.73084</v>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L183" t="n">
+      <c r="K183" t="n">
+        <v>2.6871</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7805,12 +8356,15 @@
       <c r="J184" t="n">
         <v>1.24422</v>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L184" t="n">
+      <c r="K184" t="n">
+        <v>2.43571</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7845,12 +8399,15 @@
       <c r="J185" t="n">
         <v>1.47007</v>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L185" t="n">
+      <c r="K185" t="n">
+        <v>1.87324</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7885,12 +8442,15 @@
       <c r="J186" t="n">
         <v>1.51105</v>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L186" t="n">
+      <c r="K186" t="n">
+        <v>1.83877</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7925,12 +8485,15 @@
       <c r="J187" t="n">
         <v>1.01777</v>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L187" t="n">
+      <c r="K187" t="n">
+        <v>2.09522</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7965,12 +8528,15 @@
       <c r="J188" t="n">
         <v>1.00864</v>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L188" t="n">
+      <c r="K188" t="n">
+        <v>2.29861</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8005,12 +8571,15 @@
       <c r="J189" t="n">
         <v>1.05815</v>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L189" t="n">
+      <c r="K189" t="n">
+        <v>2.56331</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8045,12 +8614,15 @@
       <c r="J190" t="n">
         <v>0.38503</v>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L190" t="n">
+      <c r="K190" t="n">
+        <v>2.8595</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8085,12 +8657,15 @@
       <c r="J191" t="n">
         <v>0.89528</v>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L191" t="n">
+      <c r="K191" t="n">
+        <v>3.06186</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8125,12 +8700,15 @@
       <c r="J192" t="n">
         <v>1.49478</v>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L192" t="n">
+      <c r="K192" t="n">
+        <v>3.16201</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8165,12 +8743,15 @@
       <c r="J193" t="n">
         <v>1.29025</v>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L193" t="n">
+      <c r="K193" t="n">
+        <v>2.85041</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8205,12 +8786,15 @@
       <c r="J194" t="n">
         <v>1.42028</v>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L194" t="n">
+      <c r="K194" t="n">
+        <v>2.60086</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M194" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8245,12 +8829,15 @@
       <c r="J195" t="n">
         <v>0.9156</v>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L195" t="n">
+      <c r="K195" t="n">
+        <v>2.29991</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M195" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8285,12 +8872,15 @@
       <c r="J196" t="n">
         <v>1.2688</v>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L196" t="n">
+      <c r="K196" t="n">
+        <v>2.24513</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8325,12 +8915,15 @@
       <c r="J197" t="n">
         <v>0.67027</v>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L197" t="n">
+      <c r="K197" t="n">
+        <v>2.1657</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M197" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8365,12 +8958,15 @@
       <c r="J198" t="n">
         <v>0.25298</v>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L198" t="n">
+      <c r="K198" t="n">
+        <v>2.20341</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M198" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8405,12 +9001,15 @@
       <c r="J199" t="n">
         <v>1.03614</v>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L199" t="n">
+      <c r="K199" t="n">
+        <v>1.69664</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8445,12 +9044,15 @@
       <c r="J200" t="n">
         <v>-0.23673</v>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L200" t="n">
+      <c r="K200" t="n">
+        <v>1.38664</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8485,12 +9087,15 @@
       <c r="J201" t="n">
         <v>-0.20489</v>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L201" t="n">
+      <c r="K201" t="n">
+        <v>0.80621</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8525,12 +9130,15 @@
       <c r="J202" t="n">
         <v>-0.66879</v>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L202" t="n">
+      <c r="K202" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8565,12 +9173,15 @@
       <c r="J203" t="n">
         <v>-0.90621</v>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L203" t="n">
+      <c r="K203" t="n">
+        <v>-0.19006</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M203" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8605,12 +9216,15 @@
       <c r="J204" t="n">
         <v>-1.05949</v>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L204" t="n">
+      <c r="K204" t="n">
+        <v>-0.55911</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M204" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8645,12 +9259,15 @@
       <c r="J205" t="n">
         <v>-0.99823</v>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L205" t="n">
+      <c r="K205" t="n">
+        <v>-0.55827</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8685,12 +9302,15 @@
       <c r="J206" t="n">
         <v>-0.3367</v>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L206" t="n">
+      <c r="K206" t="n">
+        <v>-0.33932</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M206" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8725,12 +9345,15 @@
       <c r="J207" t="n">
         <v>0.17643</v>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L207" t="n">
+      <c r="K207" t="n">
+        <v>-0.32974</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8765,12 +9388,15 @@
       <c r="J208" t="n">
         <v>-1.01265</v>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L208" t="n">
+      <c r="K208" t="n">
+        <v>-0.58888</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8805,12 +9431,15 @@
       <c r="J209" t="n">
         <v>-0.79127</v>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L209" t="n">
+      <c r="K209" t="n">
+        <v>-0.57994</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8845,12 +9474,15 @@
       <c r="J210" t="n">
         <v>-0.95663</v>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L210" t="n">
+      <c r="K210" t="n">
+        <v>-1.14782</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8885,12 +9517,15 @@
       <c r="J211" t="n">
         <v>-3.18673</v>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L211" t="n">
+      <c r="K211" t="n">
+        <v>-1.73826</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8925,12 +9560,15 @@
       <c r="J212" t="n">
         <v>-3.24895</v>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L212" t="n">
+      <c r="K212" t="n">
+        <v>-2.26615</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8965,12 +9603,15 @@
       <c r="J213" t="n">
         <v>-4.50816</v>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L213" t="n">
+      <c r="K213" t="n">
+        <v>-2.51924</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9005,12 +9646,15 @@
       <c r="J214" t="n">
         <v>-5.03658</v>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L214" t="n">
+      <c r="K214" t="n">
+        <v>-3.16253</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9045,12 +9689,15 @@
       <c r="J215" t="n">
         <v>-6.3027</v>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L215" t="n">
+      <c r="K215" t="n">
+        <v>-3.73822</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9085,12 +9732,15 @@
       <c r="J216" t="n">
         <v>-7.64559</v>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L216" t="n">
+      <c r="K216" t="n">
+        <v>-4.17671</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9125,12 +9775,15 @@
       <c r="J217" t="n">
         <v>-7.87333</v>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L217" t="n">
+      <c r="K217" t="n">
+        <v>-5.06266</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9165,12 +9818,15 @@
       <c r="J218" t="n">
         <v>-8.35885</v>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L218" t="n">
+      <c r="K218" t="n">
+        <v>-5.83817</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9205,12 +9861,15 @@
       <c r="J219" t="n">
         <v>-9.30184</v>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L219" t="n">
+      <c r="K219" t="n">
+        <v>-6.41604</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9245,12 +9904,15 @@
       <c r="J220" t="n">
         <v>-9.053039999999999</v>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L220" t="n">
+      <c r="K220" t="n">
+        <v>-6.72691</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9285,12 +9947,15 @@
       <c r="J221" t="n">
         <v>-10.13441</v>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L221" t="n">
+      <c r="K221" t="n">
+        <v>-6.77864</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9325,12 +9990,15 @@
       <c r="J222" t="n">
         <v>-10.12145</v>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L222" t="n">
+      <c r="K222" t="n">
+        <v>-6.5933</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9365,12 +10033,15 @@
       <c r="J223" t="n">
         <v>-8.699949999999999</v>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L223" t="n">
+      <c r="K223" t="n">
+        <v>-6.07971</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9405,12 +10076,15 @@
       <c r="J224" t="n">
         <v>-7.54205</v>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L224" t="n">
+      <c r="K224" t="n">
+        <v>-5.60776</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9445,12 +10119,15 @@
       <c r="J225" t="n">
         <v>-7.08702</v>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L225" t="n">
+      <c r="K225" t="n">
+        <v>-5.37381</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9485,12 +10162,15 @@
       <c r="J226" t="n">
         <v>-6.15032</v>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L226" t="n">
+      <c r="K226" t="n">
+        <v>-4.60934</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9525,12 +10205,15 @@
       <c r="J227" t="n">
         <v>-5.44062</v>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L227" t="n">
+      <c r="K227" t="n">
+        <v>-3.8001</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9565,12 +10248,15 @@
       <c r="J228" t="n">
         <v>-4.18348</v>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L228" t="n">
+      <c r="K228" t="n">
+        <v>-3.35289</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9605,12 +10291,15 @@
       <c r="J229" t="n">
         <v>-4.2065</v>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L229" t="n">
+      <c r="K229" t="n">
+        <v>-2.5132</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9645,12 +10334,15 @@
       <c r="J230" t="n">
         <v>-4.39894</v>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L230" t="n">
+      <c r="K230" t="n">
+        <v>-1.64841</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9685,12 +10377,15 @@
       <c r="J231" t="n">
         <v>-3.84445</v>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L231" t="n">
+      <c r="K231" t="n">
+        <v>-0.84628</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9725,12 +10420,15 @@
       <c r="J232" t="n">
         <v>-3.53798</v>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L232" t="n">
+      <c r="K232" t="n">
+        <v>-0.25834</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9765,12 +10463,15 @@
       <c r="J233" t="n">
         <v>-1.63804</v>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L233" t="n">
+      <c r="K233" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9805,12 +10506,15 @@
       <c r="J234" t="n">
         <v>-1.38277</v>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L234" t="n">
+      <c r="K234" t="n">
+        <v>0.70263</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9845,12 +10549,15 @@
       <c r="J235" t="n">
         <v>-1.35654</v>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L235" t="n">
+      <c r="K235" t="n">
+        <v>1.19073</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9885,12 +10592,15 @@
       <c r="J236" t="n">
         <v>-1.42158</v>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L236" t="n">
+      <c r="K236" t="n">
+        <v>1.34185</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9925,12 +10635,15 @@
       <c r="J237" t="n">
         <v>-0.25725</v>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L237" t="n">
+      <c r="K237" t="n">
+        <v>1.59315</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9965,12 +10678,15 @@
       <c r="J238" t="n">
         <v>0.24352</v>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L238" t="n">
+      <c r="K238" t="n">
+        <v>1.44095</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10005,12 +10721,15 @@
       <c r="J239" t="n">
         <v>1.33084</v>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L239" t="n">
+      <c r="K239" t="n">
+        <v>1.48268</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10045,12 +10764,15 @@
       <c r="J240" t="n">
         <v>1.67509</v>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L240" t="n">
+      <c r="K240" t="n">
+        <v>1.84302</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10085,12 +10807,15 @@
       <c r="J241" t="n">
         <v>2.18762</v>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L241" t="n">
+      <c r="K241" t="n">
+        <v>1.83059</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10125,12 +10850,15 @@
       <c r="J242" t="n">
         <v>2.30198</v>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L242" t="n">
+      <c r="K242" t="n">
+        <v>2.02206</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10165,12 +10893,15 @@
       <c r="J243" t="n">
         <v>2.64173</v>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L243" t="n">
+      <c r="K243" t="n">
+        <v>2.11755</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10205,12 +10936,15 @@
       <c r="J244" t="n">
         <v>3.88744</v>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L244" t="n">
+      <c r="K244" t="n">
+        <v>2.14764</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10245,12 +10979,15 @@
       <c r="J245" t="n">
         <v>2.90206</v>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L245" t="n">
+      <c r="K245" t="n">
+        <v>1.87077</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M245" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10285,12 +11022,15 @@
       <c r="J246" t="n">
         <v>3.10311</v>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L246" t="n">
+      <c r="K246" t="n">
+        <v>1.57793</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M246" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10325,12 +11065,15 @@
       <c r="J247" t="n">
         <v>3.46116</v>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L247" t="n">
+      <c r="K247" t="n">
+        <v>1.06975</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10365,12 +11108,15 @@
       <c r="J248" t="n">
         <v>3.43722</v>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L248" t="n">
+      <c r="K248" t="n">
+        <v>1.05713</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10405,12 +11151,15 @@
       <c r="J249" t="n">
         <v>4.28998</v>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L249" t="n">
+      <c r="K249" t="n">
+        <v>0.82142</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10445,12 +11194,15 @@
       <c r="J250" t="n">
         <v>5.36587</v>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L250" t="n">
+      <c r="K250" t="n">
+        <v>1.08939</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M250" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10485,12 +11237,15 @@
       <c r="J251" t="n">
         <v>4.6915</v>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L251" t="n">
+      <c r="K251" t="n">
+        <v>1.32238</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M251" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10525,12 +11280,15 @@
       <c r="J252" t="n">
         <v>4.78751</v>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L252" t="n">
+      <c r="K252" t="n">
+        <v>1.54354</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10565,12 +11323,15 @@
       <c r="J253" t="n">
         <v>4.94873</v>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L253" t="n">
+      <c r="K253" t="n">
+        <v>2.12743</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10605,12 +11366,15 @@
       <c r="J254" t="n">
         <v>5.60819</v>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L254" t="n">
+      <c r="K254" t="n">
+        <v>2.03498</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10645,12 +11409,15 @@
       <c r="J255" t="n">
         <v>5.94848</v>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L255" t="n">
+      <c r="K255" t="n">
+        <v>2.40161</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10685,12 +11452,15 @@
       <c r="J256" t="n">
         <v>5.66685</v>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L256" t="n">
+      <c r="K256" t="n">
+        <v>2.43001</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10725,12 +11495,15 @@
       <c r="J257" t="n">
         <v>6.14195</v>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L257" t="n">
+      <c r="K257" t="n">
+        <v>2.76517</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10765,12 +11538,15 @@
       <c r="J258" t="n">
         <v>6.59275</v>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L258" t="n">
+      <c r="K258" t="n">
+        <v>3.32875</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10805,12 +11581,15 @@
       <c r="J259" t="n">
         <v>6.62995</v>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L259" t="n">
+      <c r="K259" t="n">
+        <v>3.91617</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10845,12 +11624,15 @@
       <c r="J260" t="n">
         <v>6.90737</v>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L260" t="n">
+      <c r="K260" t="n">
+        <v>4.4273</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10885,12 +11667,15 @@
       <c r="J261" t="n">
         <v>5.46892</v>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L261" t="n">
+      <c r="K261" t="n">
+        <v>5.34335</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10925,12 +11710,15 @@
       <c r="J262" t="n">
         <v>4.06068</v>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L262" t="n">
+      <c r="K262" t="n">
+        <v>5.82145</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10965,12 +11753,15 @@
       <c r="J263" t="n">
         <v>3.98664</v>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L263" t="n">
+      <c r="K263" t="n">
+        <v>5.86254</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11005,12 +11796,15 @@
       <c r="J264" t="n">
         <v>3.80942</v>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L264" t="n">
+      <c r="K264" t="n">
+        <v>5.93354</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11045,12 +11839,15 @@
       <c r="J265" t="n">
         <v>3.70184</v>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L265" t="n">
+      <c r="K265" t="n">
+        <v>5.63483</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11085,12 +11882,15 @@
       <c r="J266" t="n">
         <v>2.87385</v>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L266" t="n">
+      <c r="K266" t="n">
+        <v>5.64039</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11125,12 +11925,15 @@
       <c r="J267" t="n">
         <v>2.68867</v>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L267" t="n">
+      <c r="K267" t="n">
+        <v>5.62042</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11165,12 +11968,15 @@
       <c r="J268" t="n">
         <v>2.18501</v>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L268" t="n">
+      <c r="K268" t="n">
+        <v>5.869</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11205,12 +12011,15 @@
       <c r="J269" t="n">
         <v>2.61295</v>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L269" t="n">
+      <c r="K269" t="n">
+        <v>5.81288</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11245,12 +12054,15 @@
       <c r="J270" t="n">
         <v>2.24409</v>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L270" t="n">
+      <c r="K270" t="n">
+        <v>5.57374</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11285,12 +12097,15 @@
       <c r="J271" t="n">
         <v>2.02556</v>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L271" t="n">
+      <c r="K271" t="n">
+        <v>5.55103</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11325,12 +12140,15 @@
       <c r="J272" t="n">
         <v>2.06781</v>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L272" t="n">
+      <c r="K272" t="n">
+        <v>5.03896</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11365,12 +12183,15 @@
       <c r="J273" t="n">
         <v>2.87077</v>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L273" t="n">
+      <c r="K273" t="n">
+        <v>4.37927</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11405,12 +12226,15 @@
       <c r="J274" t="n">
         <v>2.13198</v>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L274" t="n">
+      <c r="K274" t="n">
+        <v>3.65415</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11445,12 +12269,15 @@
       <c r="J275" t="n">
         <v>2.59061</v>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L275" t="n">
+      <c r="K275" t="n">
+        <v>3.37045</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11485,12 +12312,15 @@
       <c r="J276" t="n">
         <v>2.64213</v>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L276" t="n">
+      <c r="K276" t="n">
+        <v>2.99852</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11525,12 +12355,15 @@
       <c r="J277" t="n">
         <v>2.55371</v>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L277" t="n">
+      <c r="K277" t="n">
+        <v>3.04674</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11565,12 +12398,15 @@
       <c r="J278" t="n">
         <v>3.57057</v>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L278" t="n">
+      <c r="K278" t="n">
+        <v>2.88102</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11605,12 +12441,15 @@
       <c r="J279" t="n">
         <v>3.10631</v>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L279" t="n">
+      <c r="K279" t="n">
+        <v>2.72914</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11645,12 +12484,15 @@
       <c r="J280" t="n">
         <v>3.13352</v>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L280" t="n">
+      <c r="K280" t="n">
+        <v>2.72798</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11685,12 +12527,15 @@
       <c r="J281" t="n">
         <v>2.52939</v>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L281" t="n">
+      <c r="K281" t="n">
+        <v>2.48471</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11725,12 +12570,15 @@
       <c r="J282" t="n">
         <v>2.46755</v>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L282" t="n">
+      <c r="K282" t="n">
+        <v>2.7027</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11765,12 +12613,15 @@
       <c r="J283" t="n">
         <v>1.70802</v>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L283" t="n">
+      <c r="K283" t="n">
+        <v>2.45103</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11805,12 +12656,15 @@
       <c r="J284" t="n">
         <v>1.26787</v>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L284" t="n">
+      <c r="K284" t="n">
+        <v>2.66834</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11845,12 +12699,15 @@
       <c r="J285" t="n">
         <v>0.5518</v>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L285" t="n">
+      <c r="K285" t="n">
+        <v>2.99269</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11885,12 +12742,15 @@
       <c r="J286" t="n">
         <v>1.35733</v>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L286" t="n">
+      <c r="K286" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11925,12 +12785,15 @@
       <c r="J287" t="n">
         <v>1.27691</v>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L287" t="n">
+      <c r="K287" t="n">
+        <v>3.50101</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11965,12 +12828,15 @@
       <c r="J288" t="n">
         <v>0.5296999999999999</v>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L288" t="n">
+      <c r="K288" t="n">
+        <v>3.8432</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12005,12 +12871,15 @@
       <c r="J289" t="n">
         <v>-0.27377</v>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L289" t="n">
+      <c r="K289" t="n">
+        <v>3.50206</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12045,12 +12914,15 @@
       <c r="J290" t="n">
         <v>-0.04054</v>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L290" t="n">
+      <c r="K290" t="n">
+        <v>3.83255</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12085,12 +12957,15 @@
       <c r="J291" t="n">
         <v>-0.23617</v>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L291" t="n">
+      <c r="K291" t="n">
+        <v>3.85641</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12125,12 +13000,15 @@
       <c r="J292" t="n">
         <v>-0.7377899999999999</v>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L292" t="n">
+      <c r="K292" t="n">
+        <v>3.61343</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12165,12 +13043,15 @@
       <c r="J293" t="n">
         <v>-0.52172</v>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L293" t="n">
+      <c r="K293" t="n">
+        <v>3.87347</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12205,12 +13086,15 @@
       <c r="J294" t="n">
         <v>-0.8229</v>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L294" t="n">
+      <c r="K294" t="n">
+        <v>3.87663</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12245,12 +13129,15 @@
       <c r="J295" t="n">
         <v>-0.05906</v>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L295" t="n">
+      <c r="K295" t="n">
+        <v>4.15372</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12285,12 +13172,15 @@
       <c r="J296" t="n">
         <v>0.27712</v>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L296" t="n">
+      <c r="K296" t="n">
+        <v>4.17527</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12325,12 +13215,15 @@
       <c r="J297" t="n">
         <v>0.31426</v>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L297" t="n">
+      <c r="K297" t="n">
+        <v>3.95216</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12365,12 +13258,15 @@
       <c r="J298" t="n">
         <v>0.38244</v>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L298" t="n">
+      <c r="K298" t="n">
+        <v>4.13285</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12405,12 +13301,15 @@
       <c r="J299" t="n">
         <v>-0.008840000000000001</v>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L299" t="n">
+      <c r="K299" t="n">
+        <v>3.93086</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12445,12 +13344,15 @@
       <c r="J300" t="n">
         <v>1.00172</v>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L300" t="n">
+      <c r="K300" t="n">
+        <v>3.58993</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12485,12 +13387,15 @@
       <c r="J301" t="n">
         <v>1.95501</v>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L301" t="n">
+      <c r="K301" t="n">
+        <v>3.94749</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12525,12 +13430,15 @@
       <c r="J302" t="n">
         <v>1.47719</v>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L302" t="n">
+      <c r="K302" t="n">
+        <v>3.58063</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12565,12 +13473,15 @@
       <c r="J303" t="n">
         <v>1.98082</v>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L303" t="n">
+      <c r="K303" t="n">
+        <v>3.34647</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12605,12 +13516,15 @@
       <c r="J304" t="n">
         <v>2.73019</v>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L304" t="n">
+      <c r="K304" t="n">
+        <v>3.55149</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12645,12 +13559,15 @@
       <c r="J305" t="n">
         <v>2.50477</v>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L305" t="n">
+      <c r="K305" t="n">
+        <v>3.30051</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12685,12 +13602,15 @@
       <c r="J306" t="n">
         <v>2.97813</v>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L306" t="n">
+      <c r="K306" t="n">
+        <v>3.0237</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12725,12 +13645,15 @@
       <c r="J307" t="n">
         <v>3.47011</v>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L307" t="n">
+      <c r="K307" t="n">
+        <v>2.72201</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12765,12 +13688,15 @@
       <c r="J308" t="n">
         <v>3.01415</v>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L308" t="n">
+      <c r="K308" t="n">
+        <v>2.738</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12805,12 +13731,15 @@
       <c r="J309" t="n">
         <v>3.06809</v>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L309" t="n">
+      <c r="K309" t="n">
+        <v>2.73234</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12845,12 +13774,15 @@
       <c r="J310" t="n">
         <v>2.6111</v>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L310" t="n">
+      <c r="K310" t="n">
+        <v>2.76832</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12885,12 +13817,15 @@
       <c r="J311" t="n">
         <v>2.99353</v>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L311" t="n">
+      <c r="K311" t="n">
+        <v>2.69134</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M311" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12925,12 +13860,15 @@
       <c r="J312" t="n">
         <v>2.74941</v>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L312" t="n">
+      <c r="K312" t="n">
+        <v>2.99214</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12965,12 +13903,15 @@
       <c r="J313" t="n">
         <v>2.39374</v>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L313" t="n">
+      <c r="K313" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13005,12 +13946,15 @@
       <c r="J314" t="n">
         <v>1.92627</v>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L314" t="n">
+      <c r="K314" t="n">
+        <v>3.01253</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M314" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13045,12 +13989,15 @@
       <c r="J315" t="n">
         <v>2.41007</v>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L315" t="n">
+      <c r="K315" t="n">
+        <v>3.23811</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13085,12 +14032,15 @@
       <c r="J316" t="n">
         <v>2.62675</v>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L316" t="n">
+      <c r="K316" t="n">
+        <v>3.03191</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13125,12 +14075,15 @@
       <c r="J317" t="n">
         <v>3.43649</v>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L317" t="n">
+      <c r="K317" t="n">
+        <v>3.27449</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13165,12 +14118,15 @@
       <c r="J318" t="n">
         <v>3.3741</v>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L318" t="n">
+      <c r="K318" t="n">
+        <v>3.52547</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M318" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13205,12 +14161,15 @@
       <c r="J319" t="n">
         <v>3.14975</v>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L319" t="n">
+      <c r="K319" t="n">
+        <v>3.82076</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13245,12 +14204,15 @@
       <c r="J320" t="n">
         <v>3.12855</v>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L320" t="n">
+      <c r="K320" t="n">
+        <v>3.52415</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M320" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13285,12 +14247,15 @@
       <c r="J321" t="n">
         <v>3.1808</v>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L321" t="n">
+      <c r="K321" t="n">
+        <v>3.64829</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13325,12 +14290,15 @@
       <c r="J322" t="n">
         <v>3.7925</v>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L322" t="n">
+      <c r="K322" t="n">
+        <v>3.73987</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M322" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13365,12 +14333,15 @@
       <c r="J323" t="n">
         <v>3.92538</v>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L323" t="n">
+      <c r="K323" t="n">
+        <v>3.76143</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M323" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13405,12 +14376,15 @@
       <c r="J324" t="n">
         <v>3.68468</v>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L324" t="n">
+      <c r="K324" t="n">
+        <v>3.45157</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M324" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13445,12 +14419,15 @@
       <c r="J325" t="n">
         <v>3.30291</v>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L325" t="n">
+      <c r="K325" t="n">
+        <v>3.22302</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13485,12 +14462,15 @@
       <c r="J326" t="n">
         <v>2.86511</v>
       </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L326" t="n">
+      <c r="K326" t="n">
+        <v>2.9158</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M326" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13525,12 +14505,15 @@
       <c r="J327" t="n">
         <v>2.05802</v>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L327" t="n">
+      <c r="K327" t="n">
+        <v>2.63814</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M327" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13565,12 +14548,15 @@
       <c r="J328" t="n">
         <v>1.82602</v>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L328" t="n">
+      <c r="K328" t="n">
+        <v>2.3593</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M328" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13605,12 +14591,15 @@
       <c r="J329" t="n">
         <v>1.16177</v>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L329" t="n">
+      <c r="K329" t="n">
+        <v>2.05965</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M329" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13645,12 +14634,15 @@
       <c r="J330" t="n">
         <v>1.15674</v>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L330" t="n">
+      <c r="K330" t="n">
+        <v>1.53244</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M330" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13685,12 +14677,15 @@
       <c r="J331" t="n">
         <v>0.72941</v>
       </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L331" t="n">
+      <c r="K331" t="n">
+        <v>1.00907</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M331" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13725,12 +14720,15 @@
       <c r="J332" t="n">
         <v>1.13298</v>
       </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L332" t="n">
+      <c r="K332" t="n">
+        <v>0.9569</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M332" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13765,12 +14763,15 @@
       <c r="J333" t="n">
         <v>1.19602</v>
       </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L333" t="n">
+      <c r="K333" t="n">
+        <v>0.54022</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M333" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13805,12 +14806,15 @@
       <c r="J334" t="n">
         <v>1.05157</v>
       </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L334" t="n">
+      <c r="K334" t="n">
+        <v>-0.05882</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M334" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13845,12 +14849,15 @@
       <c r="J335" t="n">
         <v>1.72674</v>
       </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L335" t="n">
+      <c r="K335" t="n">
+        <v>-0.08391</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M335" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13885,12 +14892,15 @@
       <c r="J336" t="n">
         <v>-2.43287</v>
       </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L336" t="n">
+      <c r="K336" t="n">
+        <v>-0.2934</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M336" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13925,12 +14935,15 @@
       <c r="J337" t="n">
         <v>2.74486</v>
       </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L337" t="n">
+      <c r="K337" t="n">
+        <v>-0.32647</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M337" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13965,12 +14978,15 @@
       <c r="J338" t="n">
         <v>-0.53278</v>
       </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L338" t="n">
+      <c r="K338" t="n">
+        <v>-0.36044</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M338" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14005,12 +15021,15 @@
       <c r="J339" t="n">
         <v>-0.09285</v>
       </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L339" t="n">
+      <c r="K339" t="n">
+        <v>-0.10884</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M339" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14045,12 +15064,15 @@
       <c r="J340" t="n">
         <v>-0.52616</v>
       </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L340" t="n">
+      <c r="K340" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M340" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14085,12 +15107,15 @@
       <c r="J341" t="n">
         <v>-1.22507</v>
       </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L341" t="n">
+      <c r="K341" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M341" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14125,12 +15150,15 @@
       <c r="J342" t="n">
         <v>-1.44273</v>
       </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L342" t="n">
+      <c r="K342" t="n">
+        <v>0.69596</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M342" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14165,12 +15193,15 @@
       <c r="J343" t="n">
         <v>-1.09171</v>
       </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L343" t="n">
+      <c r="K343" t="n">
+        <v>1.1501</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M343" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14205,12 +15236,15 @@
       <c r="J344" t="n">
         <v>-0.75704</v>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L344" t="n">
+      <c r="K344" t="n">
+        <v>1.20785</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M344" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14245,12 +15279,15 @@
       <c r="J345" t="n">
         <v>-0.69376</v>
       </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L345" t="n">
+      <c r="K345" t="n">
+        <v>1.66233</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M345" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14285,12 +15322,15 @@
       <c r="J346" t="n">
         <v>-0.13945</v>
       </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L346" t="n">
+      <c r="K346" t="n">
+        <v>2.05163</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M346" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14325,12 +15365,15 @@
       <c r="J347" t="n">
         <v>-1.0381</v>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L347" t="n">
+      <c r="K347" t="n">
+        <v>2.04082</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M347" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14365,12 +15408,15 @@
       <c r="J348" t="n">
         <v>2.99158</v>
       </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L348" t="n">
+      <c r="K348" t="n">
+        <v>2.53069</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M348" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14405,12 +15451,15 @@
       <c r="J349" t="n">
         <v>-1.39386</v>
       </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L349" t="n">
+      <c r="K349" t="n">
+        <v>2.79667</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14445,12 +15494,15 @@
       <c r="J350" t="n">
         <v>2.56005</v>
       </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L350" t="n">
+      <c r="K350" t="n">
+        <v>3.17153</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M350" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14485,12 +15537,15 @@
       <c r="J351" t="n">
         <v>1.78134</v>
       </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L351" t="n">
+      <c r="K351" t="n">
+        <v>2.90839</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M351" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14525,12 +15580,15 @@
       <c r="J352" t="n">
         <v>1.56742</v>
       </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L352" t="n">
+      <c r="K352" t="n">
+        <v>3.0298</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M352" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14565,12 +15623,15 @@
       <c r="J353" t="n">
         <v>-49.2774</v>
       </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L353" t="n">
+      <c r="K353" t="n">
+        <v>-38.87406</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M353" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14605,12 +15666,15 @@
       <c r="J354" t="n">
         <v>-69.48389</v>
       </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L354" t="n">
+      <c r="K354" t="n">
+        <v>-38.42118</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M354" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14645,12 +15709,15 @@
       <c r="J355" t="n">
         <v>-70.07268000000001</v>
       </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L355" t="n">
+      <c r="K355" t="n">
+        <v>-33.27247</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M355" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14685,12 +15752,15 @@
       <c r="J356" t="n">
         <v>-74.73842</v>
       </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L356" t="n">
+      <c r="K356" t="n">
+        <v>-30.14255</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M356" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14725,12 +15795,15 @@
       <c r="J357" t="n">
         <v>-74.86150000000001</v>
       </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L357" t="n">
+      <c r="K357" t="n">
+        <v>-25.53473</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M357" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14765,12 +15838,15 @@
       <c r="J358" t="n">
         <v>-76.53857000000001</v>
       </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L358" t="n">
+      <c r="K358" t="n">
+        <v>-26.06081</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M358" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14805,12 +15881,15 @@
       <c r="J359" t="n">
         <v>-66.67775</v>
       </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L359" t="n">
+      <c r="K359" t="n">
+        <v>-22.15638</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M359" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14845,12 +15924,15 @@
       <c r="J360" t="n">
         <v>-56.85972</v>
       </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L360" t="n">
+      <c r="K360" t="n">
+        <v>-20.3936</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M360" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14885,12 +15967,15 @@
       <c r="J361" t="n">
         <v>-53.25212</v>
       </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="L361" t="n">
+      <c r="K361" t="n">
+        <v>-19.73039</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="M361" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Total Leisure eMP</t>
+          <t>Total Leisure Emp</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Accomodation Emp</t>
+          <t>Accommodation Emp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -507,7 +507,7 @@
         <v>-0.05562146031940518</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07118643009229353</v>
+        <v>-7.118643009229353e-08</v>
       </c>
       <c r="D2" t="n">
         <v>-0.105255635500261</v>
@@ -550,7 +550,7 @@
         <v>-0.227175122022969</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2300346783839634</v>
+        <v>-2.300346783839634e-07</v>
       </c>
       <c r="D3" t="n">
         <v>-0.2372997475969882</v>
@@ -593,7 +593,7 @@
         <v>-0.1391888075470618</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09632595965665702</v>
+        <v>-9.632595965665702e-08</v>
       </c>
       <c r="D4" t="n">
         <v>-0.2048538865822255</v>
@@ -636,7 +636,7 @@
         <v>-0.01876615744290178</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06091600917809226</v>
+        <v>-6.091600917809226e-08</v>
       </c>
       <c r="D5" t="n">
         <v>-0.094213355257183</v>
@@ -679,7 +679,7 @@
         <v>-0.0004911077516509543</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.02013216073307122</v>
+        <v>-2.013216073307122e-08</v>
       </c>
       <c r="D6" t="n">
         <v>-0.08609623032346503</v>
@@ -722,7 +722,7 @@
         <v>-0.01072625587287468</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.03003448325447811</v>
+        <v>-3.003448325447811e-08</v>
       </c>
       <c r="D7" t="n">
         <v>-0.01150245487945256</v>
@@ -765,7 +765,7 @@
         <v>0.00977785731502423</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.005423953364236955</v>
+        <v>-5.423953364236955e-09</v>
       </c>
       <c r="D8" t="n">
         <v>-0.02776840419061655</v>
@@ -808,7 +808,7 @@
         <v>0.0006800432941356238</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01187027285764575</v>
+        <v>-1.187027285764575e-08</v>
       </c>
       <c r="D9" t="n">
         <v>-0.01921698343885891</v>
@@ -851,7 +851,7 @@
         <v>0.08240233734436475</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04792415916542181</v>
+        <v>4.792415916542181e-08</v>
       </c>
       <c r="D10" t="n">
         <v>-0.0008777921183718007</v>
@@ -894,7 +894,7 @@
         <v>-0.005088794248391038</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.03033027652902853</v>
+        <v>-3.033027652902853e-08</v>
       </c>
       <c r="D11" t="n">
         <v>-0.06094810504278536</v>
@@ -937,7 +937,7 @@
         <v>-0.01360584095772477</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04060849962991753</v>
+        <v>-4.060849962991753e-08</v>
       </c>
       <c r="D12" t="n">
         <v>-0.04253235129099697</v>
@@ -980,7 +980,7 @@
         <v>0.008125877859907593</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.003662422956330791</v>
+        <v>-3.662422956330791e-09</v>
       </c>
       <c r="D13" t="n">
         <v>0.02354873067353758</v>
@@ -1023,7 +1023,7 @@
         <v>0.02142066006510213</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05929072030741334</v>
+        <v>5.929072030741334e-08</v>
       </c>
       <c r="D14" t="n">
         <v>0.01638493926864748</v>
@@ -1066,7 +1066,7 @@
         <v>0.3050052641219847</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3186834718580622</v>
+        <v>3.186834718580623e-07</v>
       </c>
       <c r="D15" t="n">
         <v>0.1895223333141141</v>
@@ -1109,7 +1109,7 @@
         <v>0.09250301821468021</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05780137009605757</v>
+        <v>5.780137009605757e-08</v>
       </c>
       <c r="D16" t="n">
         <v>0.09187967725337676</v>
@@ -1152,7 +1152,7 @@
         <v>-0.04263083338861806</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04066338975223815</v>
+        <v>4.066338975223815e-08</v>
       </c>
       <c r="D17" t="n">
         <v>0.002592341756559202</v>
@@ -1195,7 +1195,7 @@
         <v>-0.01064984194902796</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02292775407560077</v>
+        <v>2.292775407560077e-08</v>
       </c>
       <c r="D18" t="n">
         <v>0.01054652305300863</v>
@@ -1238,7 +1238,7 @@
         <v>-0.03654769213362397</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004733203438172184</v>
+        <v>4.733203438172185e-09</v>
       </c>
       <c r="D19" t="n">
         <v>-0.07066991477090612</v>
@@ -1281,7 +1281,7 @@
         <v>-0.09559638688035743</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.04640193663211833</v>
+        <v>-4.640193663211834e-08</v>
       </c>
       <c r="D20" t="n">
         <v>-0.07309561930818209</v>
@@ -1324,7 +1324,7 @@
         <v>-0.09179837823231274</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.04149301352783408</v>
+        <v>-4.149301352783407e-08</v>
       </c>
       <c r="D21" t="n">
         <v>-0.06331011031501144</v>
@@ -1367,7 +1367,7 @@
         <v>-0.04531838793117737</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001193620392825334</v>
+        <v>1.193620392825334e-10</v>
       </c>
       <c r="D22" t="n">
         <v>0.006249686943978094</v>
@@ -1410,7 +1410,7 @@
         <v>-0.001812776148229833</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06140167106671335</v>
+        <v>6.140167106671335e-08</v>
       </c>
       <c r="D23" t="n">
         <v>0.04868788484384634</v>
@@ -1453,7 +1453,7 @@
         <v>0.0003069113043918659</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06478041885750851</v>
+        <v>6.478041885750852e-08</v>
       </c>
       <c r="D24" t="n">
         <v>0.04272761934656444</v>
@@ -1496,7 +1496,7 @@
         <v>-0.0432226680298482</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000613115844179335</v>
+        <v>6.131158441793349e-10</v>
       </c>
       <c r="D25" t="n">
         <v>0.003655624507340693</v>
@@ -1539,7 +1539,7 @@
         <v>-0.03116176491001976</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.004885856534412536</v>
+        <v>-4.885856534412536e-09</v>
       </c>
       <c r="D26" t="n">
         <v>-0.001786018141027523</v>
@@ -1582,7 +1582,7 @@
         <v>-0.09795857328607882</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.06019117593464318</v>
+        <v>-6.019117593464318e-08</v>
       </c>
       <c r="D27" t="n">
         <v>-0.03642002806588807</v>
@@ -1625,7 +1625,7 @@
         <v>-0.007561651690826787</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007643659941757752</v>
+        <v>7.643659941757753e-09</v>
       </c>
       <c r="D28" t="n">
         <v>-0.001300385202684606</v>
@@ -1668,7 +1668,7 @@
         <v>-0.0572285373040673</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.03165872275791548</v>
+        <v>-3.165872275791548e-08</v>
       </c>
       <c r="D29" t="n">
         <v>-0.009793700806175365</v>
@@ -1711,7 +1711,7 @@
         <v>-0.06022044237851465</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0230176928418494</v>
+        <v>-2.30176928418494e-08</v>
       </c>
       <c r="D30" t="n">
         <v>-0.01189816484847495</v>
@@ -1754,7 +1754,7 @@
         <v>-0.113887309809152</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07580239567177538</v>
+        <v>-7.580239567177538e-08</v>
       </c>
       <c r="D31" t="n">
         <v>0.009744807105642739</v>
@@ -1797,7 +1797,7 @@
         <v>-0.05035096196250322</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.01693394770197787</v>
+        <v>-1.693394770197787e-08</v>
       </c>
       <c r="D32" t="n">
         <v>0.008322335605747799</v>
@@ -1840,7 +1840,7 @@
         <v>-0.04593883543070443</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.01989540963936609</v>
+        <v>-1.989540963936609e-08</v>
       </c>
       <c r="D33" t="n">
         <v>0.02596714375496334</v>
@@ -1883,7 +1883,7 @@
         <v>-0.103468347643029</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06913116175105183</v>
+        <v>-6.913116175105183e-08</v>
       </c>
       <c r="D34" t="n">
         <v>-0.07808310309707645</v>
@@ -1926,7 +1926,7 @@
         <v>-0.0463598937019073</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02767754523463184</v>
+        <v>-2.767754523463184e-08</v>
       </c>
       <c r="D35" t="n">
         <v>-0.04942717628094351</v>
@@ -1969,7 +1969,7 @@
         <v>-0.07368041525382085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.05742712013994977</v>
+        <v>-5.742712013994978e-08</v>
       </c>
       <c r="D36" t="n">
         <v>-0.05384286848409436</v>
@@ -2012,7 +2012,7 @@
         <v>-0.05452911255385229</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.02387584097782125</v>
+        <v>-2.387584097782125e-08</v>
       </c>
       <c r="D37" t="n">
         <v>0.01297939992277497</v>
@@ -2055,7 +2055,7 @@
         <v>-0.06443979738749195</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.04714917419355391</v>
+        <v>-4.714917419355391e-08</v>
       </c>
       <c r="D38" t="n">
         <v>-0.03210746885871929</v>
@@ -2098,7 +2098,7 @@
         <v>0.06967505649970418</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07317747267312624</v>
+        <v>7.317747267312624e-08</v>
       </c>
       <c r="D39" t="n">
         <v>0.09217562127172174</v>
@@ -2141,7 +2141,7 @@
         <v>0.05410420226358736</v>
       </c>
       <c r="C40" t="n">
-        <v>0.07895886771980809</v>
+        <v>7.895886771980809e-08</v>
       </c>
       <c r="D40" t="n">
         <v>0.121080752724475</v>
@@ -2184,7 +2184,7 @@
         <v>0.05476351554569603</v>
       </c>
       <c r="C41" t="n">
-        <v>0.04777762930496121</v>
+        <v>4.777762930496121e-08</v>
       </c>
       <c r="D41" t="n">
         <v>0.07468806064258549</v>
@@ -2227,7 +2227,7 @@
         <v>-0.005736351883284807</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01333051292257448</v>
+        <v>1.333051292257448e-08</v>
       </c>
       <c r="D42" t="n">
         <v>0.06160192177917256</v>
@@ -2270,7 +2270,7 @@
         <v>0.07461663123077145</v>
       </c>
       <c r="C43" t="n">
-        <v>0.09524792671642368</v>
+        <v>9.524792671642369e-08</v>
       </c>
       <c r="D43" t="n">
         <v>0.07626805039141882</v>
@@ -2313,7 +2313,7 @@
         <v>0.0513503868917593</v>
       </c>
       <c r="C44" t="n">
-        <v>0.06685091373230434</v>
+        <v>6.685091373230434e-08</v>
       </c>
       <c r="D44" t="n">
         <v>0.06606036290333028</v>
@@ -2356,7 +2356,7 @@
         <v>0.07912327707954248</v>
       </c>
       <c r="C45" t="n">
-        <v>0.09164325959552189</v>
+        <v>9.164325959552189e-08</v>
       </c>
       <c r="D45" t="n">
         <v>0.05167644457031173</v>
@@ -2399,7 +2399,7 @@
         <v>0.06391221526109159</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07610533841541622</v>
+        <v>7.610533841541622e-08</v>
       </c>
       <c r="D46" t="n">
         <v>0.09864722433250317</v>
@@ -2442,7 +2442,7 @@
         <v>0.01854505197708156</v>
       </c>
       <c r="C47" t="n">
-        <v>0.02702122547908936</v>
+        <v>2.702122547908936e-08</v>
       </c>
       <c r="D47" t="n">
         <v>0.04490065236863727</v>
@@ -2485,7 +2485,7 @@
         <v>0.08897850681038899</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1015002123162896</v>
+        <v>1.015002123162896e-07</v>
       </c>
       <c r="D48" t="n">
         <v>0.06304256747518933</v>
@@ -2528,7 +2528,7 @@
         <v>0.08593802953054008</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09126135359424481</v>
+        <v>9.126135359424481e-08</v>
       </c>
       <c r="D49" t="n">
         <v>0.01017341874661604</v>
@@ -2571,7 +2571,7 @@
         <v>0.06919151852058092</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0512324066122507</v>
+        <v>5.12324066122507e-08</v>
       </c>
       <c r="D50" t="n">
         <v>0.05696332959231087</v>
@@ -2614,7 +2614,7 @@
         <v>-0.04569387920802059</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.04599050128757598</v>
+        <v>-4.599050128757598e-08</v>
       </c>
       <c r="D51" t="n">
         <v>-0.04420578325011526</v>
@@ -2657,7 +2657,7 @@
         <v>-0.007752103878618133</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.04759670776575775</v>
+        <v>-4.759670776575775e-08</v>
       </c>
       <c r="D52" t="n">
         <v>-0.0636885712757993</v>
@@ -2700,7 +2700,7 @@
         <v>-0.01715018083734154</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.002239849848333475</v>
+        <v>-2.239849848333475e-09</v>
       </c>
       <c r="D53" t="n">
         <v>-0.0497801353444135</v>
@@ -2743,7 +2743,7 @@
         <v>0.05642807065958011</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02967282938413218</v>
+        <v>2.967282938413218e-08</v>
       </c>
       <c r="D54" t="n">
         <v>-0.03426270406881116</v>
@@ -2786,7 +2786,7 @@
         <v>0.05019149478502305</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01879201689619125</v>
+        <v>1.879201689619125e-08</v>
       </c>
       <c r="D55" t="n">
         <v>-0.01597560382754437</v>
@@ -2829,7 +2829,7 @@
         <v>0.07028296975146153</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02775791089354818</v>
+        <v>2.775791089354818e-08</v>
       </c>
       <c r="D56" t="n">
         <v>0.01166221548134105</v>
@@ -2872,7 +2872,7 @@
         <v>0.03815437399116117</v>
       </c>
       <c r="C57" t="n">
-        <v>0.007580186173425707</v>
+        <v>7.580186173425707e-09</v>
       </c>
       <c r="D57" t="n">
         <v>-0.005079878835415497</v>
@@ -2915,7 +2915,7 @@
         <v>0.04757658055244818</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01439612157056591</v>
+        <v>1.439612157056591e-08</v>
       </c>
       <c r="D58" t="n">
         <v>-0.003783902472771272</v>
@@ -2958,7 +2958,7 @@
         <v>0.04826108784789596</v>
       </c>
       <c r="C59" t="n">
-        <v>0.02878723071323219</v>
+        <v>2.878723071323219e-08</v>
       </c>
       <c r="D59" t="n">
         <v>0.0172807672638231</v>
@@ -3001,7 +3001,7 @@
         <v>0.01230203803209662</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.01537815745437043</v>
+        <v>-1.537815745437043e-08</v>
       </c>
       <c r="D60" t="n">
         <v>0.005618673032467658</v>
@@ -3044,7 +3044,7 @@
         <v>0.0312737285104876</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.004511475028776357</v>
+        <v>-4.511475028776357e-09</v>
       </c>
       <c r="D61" t="n">
         <v>0.01201103456145058</v>
@@ -3087,7 +3087,7 @@
         <v>0.04145582300331419</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00309485034572643</v>
+        <v>3.09485034572643e-09</v>
       </c>
       <c r="D62" t="n">
         <v>0.01350906694164045</v>
@@ -3130,7 +3130,7 @@
         <v>0.1433875242306482</v>
       </c>
       <c r="C63" t="n">
-        <v>0.103360199365198</v>
+        <v>1.03360199365198e-07</v>
       </c>
       <c r="D63" t="n">
         <v>0.0467511280200732</v>
@@ -3173,7 +3173,7 @@
         <v>0.04273608088184955</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02252455250776331</v>
+        <v>2.252455250776331e-08</v>
       </c>
       <c r="D64" t="n">
         <v>0.008215994901124235</v>
@@ -3216,7 +3216,7 @@
         <v>0.03275473572003285</v>
       </c>
       <c r="C65" t="n">
-        <v>0.01704477537002336</v>
+        <v>1.704477537002336e-08</v>
       </c>
       <c r="D65" t="n">
         <v>0.03280998199901664</v>
@@ -3259,7 +3259,7 @@
         <v>0.03858906129386508</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0382959789311863</v>
+        <v>3.82959789311863e-08</v>
       </c>
       <c r="D66" t="n">
         <v>0.01286567192921462</v>
@@ -3302,7 +3302,7 @@
         <v>0.05934571728489013</v>
       </c>
       <c r="C67" t="n">
-        <v>0.04107792653221898</v>
+        <v>4.107792653221898e-08</v>
       </c>
       <c r="D67" t="n">
         <v>0.02545573176680516</v>
@@ -3345,7 +3345,7 @@
         <v>0.00639109929685544</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.00732375266194718</v>
+        <v>-7.32375266194718e-09</v>
       </c>
       <c r="D68" t="n">
         <v>-0.01892295976600478</v>
@@ -3388,7 +3388,7 @@
         <v>0.01433069604564907</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01125418316354088</v>
+        <v>1.125418316354088e-08</v>
       </c>
       <c r="D69" t="n">
         <v>-0.0171885270721337</v>
@@ -3431,7 +3431,7 @@
         <v>0.01576344632730997</v>
       </c>
       <c r="C70" t="n">
-        <v>0.01153667968167982</v>
+        <v>1.153667968167982e-08</v>
       </c>
       <c r="D70" t="n">
         <v>-0.04055959404796405</v>
@@ -3474,7 +3474,7 @@
         <v>-0.01679039515064407</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.03674542622317012</v>
+        <v>-3.674542622317012e-08</v>
       </c>
       <c r="D71" t="n">
         <v>-0.04729275973090707</v>
@@ -3517,7 +3517,7 @@
         <v>-0.01389754019249045</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.02420144717333628</v>
+        <v>-2.420144717333628e-08</v>
       </c>
       <c r="D72" t="n">
         <v>-0.06959092382949639</v>
@@ -3560,7 +3560,7 @@
         <v>-0.02843881335463994</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.05058352381140041</v>
+        <v>-5.058352381140041e-08</v>
       </c>
       <c r="D73" t="n">
         <v>-0.05903623414602144</v>
@@ -3603,7 +3603,7 @@
         <v>-0.01380814097202465</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.05159421332644853</v>
+        <v>-5.159421332644853e-08</v>
       </c>
       <c r="D74" t="n">
         <v>-0.0441190605003402</v>
@@ -3646,7 +3646,7 @@
         <v>-0.0489232143653251</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.07687984714614515</v>
+        <v>-7.687984714614516e-08</v>
       </c>
       <c r="D75" t="n">
         <v>-0.04628946299703884</v>
@@ -3689,7 +3689,7 @@
         <v>0.003111789848805557</v>
       </c>
       <c r="C76" t="n">
-        <v>0.02158495714987607</v>
+        <v>2.158495714987607e-08</v>
       </c>
       <c r="D76" t="n">
         <v>-0.006055545550082253</v>
@@ -3732,7 +3732,7 @@
         <v>0.06176113655933668</v>
       </c>
       <c r="C77" t="n">
-        <v>0.01332229021478848</v>
+        <v>1.332229021478848e-08</v>
       </c>
       <c r="D77" t="n">
         <v>0.01264672773202924</v>
@@ -3775,7 +3775,7 @@
         <v>-0.01449182209278377</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.02494980134405522</v>
+        <v>-2.494980134405522e-08</v>
       </c>
       <c r="D78" t="n">
         <v>-0.01622944807369964</v>
@@ -3818,7 +3818,7 @@
         <v>-0.04717241995209009</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.05896910317957504</v>
+        <v>-5.896910317957504e-08</v>
       </c>
       <c r="D79" t="n">
         <v>-0.07180526080578908</v>
@@ -3861,7 +3861,7 @@
         <v>-0.006245675354644153</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.01614375882897146</v>
+        <v>-1.614375882897146e-08</v>
       </c>
       <c r="D80" t="n">
         <v>-0.03633010574542572</v>
@@ -3904,7 +3904,7 @@
         <v>-0.008750814884429969</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.01845831606714177</v>
+        <v>-1.845831606714177e-08</v>
       </c>
       <c r="D81" t="n">
         <v>-0.02833444540908103</v>
@@ -3947,7 +3947,7 @@
         <v>0.0482335659690567</v>
       </c>
       <c r="C82" t="n">
-        <v>0.03414472210323583</v>
+        <v>3.414472210323582e-08</v>
       </c>
       <c r="D82" t="n">
         <v>0.005079058090834865</v>
@@ -3990,7 +3990,7 @@
         <v>0.04821903583741638</v>
       </c>
       <c r="C83" t="n">
-        <v>0.04867794542908266</v>
+        <v>4.867794542908266e-08</v>
       </c>
       <c r="D83" t="n">
         <v>-0.004164349218704233</v>
@@ -4033,7 +4033,7 @@
         <v>0.03662444052073854</v>
       </c>
       <c r="C84" t="n">
-        <v>0.02933698265351947</v>
+        <v>2.933698265351947e-08</v>
       </c>
       <c r="D84" t="n">
         <v>0.02125846439191981</v>
@@ -4076,7 +4076,7 @@
         <v>0.02280795247697198</v>
       </c>
       <c r="C85" t="n">
-        <v>0.003314292916577921</v>
+        <v>3.314292916577921e-09</v>
       </c>
       <c r="D85" t="n">
         <v>-0.008513173577745059</v>
@@ -4119,7 +4119,7 @@
         <v>0.0228027778910842</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1439288344599774</v>
+        <v>1.439288344599774e-07</v>
       </c>
       <c r="D86" t="n">
         <v>-0.00443368049161863</v>
@@ -4162,7 +4162,7 @@
         <v>-0.01247529193302566</v>
       </c>
       <c r="C87" t="n">
-        <v>0.03839807107466786</v>
+        <v>3.839807107466786e-08</v>
       </c>
       <c r="D87" t="n">
         <v>-0.03344300033442704</v>
@@ -4205,7 +4205,7 @@
         <v>-0.03044016390062387</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.04768755963951576</v>
+        <v>-4.768755963951576e-08</v>
       </c>
       <c r="D88" t="n">
         <v>-0.04817259829236065</v>
@@ -4248,7 +4248,7 @@
         <v>-0.0140766312563998</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.008320564981053269</v>
+        <v>-8.320564981053268e-09</v>
       </c>
       <c r="D89" t="n">
         <v>-0.04982729628682281</v>
@@ -4291,7 +4291,7 @@
         <v>-0.005070210288793731</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.03552172454329416</v>
+        <v>-3.552172454329416e-08</v>
       </c>
       <c r="D90" t="n">
         <v>-0.0260732695660959</v>
@@ -4334,7 +4334,7 @@
         <v>-0.02379304191495302</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.00120176052440002</v>
+        <v>-1.20176052440002e-09</v>
       </c>
       <c r="D91" t="n">
         <v>-0.01868495056988106</v>
@@ -4377,7 +4377,7 @@
         <v>-0.01915198805927909</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.002782062763923343</v>
+        <v>-2.782062763923343e-09</v>
       </c>
       <c r="D92" t="n">
         <v>-0.02414521061576802</v>
@@ -4420,7 +4420,7 @@
         <v>-0.03679332463321705</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.02691824492001293</v>
+        <v>-2.691824492001293e-08</v>
       </c>
       <c r="D93" t="n">
         <v>-0.03370942005762634</v>
@@ -4463,7 +4463,7 @@
         <v>-0.0644643494016619</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.0834414818789716</v>
+        <v>-8.344148187897161e-08</v>
       </c>
       <c r="D94" t="n">
         <v>-0.04139666442692613</v>
@@ -4506,7 +4506,7 @@
         <v>-0.04221755789513371</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.05369553597123899</v>
+        <v>-5.369553597123899e-08</v>
       </c>
       <c r="D95" t="n">
         <v>-0.0132031258632348</v>
@@ -4549,7 +4549,7 @@
         <v>-0.03159904673123726</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.01829384637128884</v>
+        <v>-1.829384637128883e-08</v>
       </c>
       <c r="D96" t="n">
         <v>-0.03480527844743986</v>
@@ -4592,7 +4592,7 @@
         <v>-0.02616494059232977</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1039268349979092</v>
+        <v>1.039268349979092e-07</v>
       </c>
       <c r="D97" t="n">
         <v>-0.03690584617753112</v>
@@ -4635,7 +4635,7 @@
         <v>-0.01800693674157539</v>
       </c>
       <c r="C98" t="n">
-        <v>0.01414515059271881</v>
+        <v>1.414515059271881e-08</v>
       </c>
       <c r="D98" t="n">
         <v>-0.02523776373152942</v>
@@ -4678,7 +4678,7 @@
         <v>0.02103950846025615</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03088861109458119</v>
+        <v>3.088861109458119e-08</v>
       </c>
       <c r="D99" t="n">
         <v>0.000611291399214009</v>
@@ -4721,7 +4721,7 @@
         <v>0.01031768438745528</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04180532897020561</v>
+        <v>4.180532897020561e-08</v>
       </c>
       <c r="D100" t="n">
         <v>-0.001255691670250303</v>
@@ -4764,7 +4764,7 @@
         <v>-0.01378609163355082</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.01661710271477324</v>
+        <v>-1.661710271477323e-08</v>
       </c>
       <c r="D101" t="n">
         <v>-0.01989933987517223</v>
@@ -4807,7 +4807,7 @@
         <v>-0.004617014516962503</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03617098800325702</v>
+        <v>3.617098800325702e-08</v>
       </c>
       <c r="D102" t="n">
         <v>-0.0238724013859053</v>
@@ -4850,7 +4850,7 @@
         <v>0.02638951388967681</v>
       </c>
       <c r="C103" t="n">
-        <v>0.04538846330880131</v>
+        <v>4.538846330880131e-08</v>
       </c>
       <c r="D103" t="n">
         <v>-0.0076454246157317</v>
@@ -4893,7 +4893,7 @@
         <v>0.0424583860747918</v>
       </c>
       <c r="C104" t="n">
-        <v>0.07669000171891738</v>
+        <v>7.669000171891737e-08</v>
       </c>
       <c r="D104" t="n">
         <v>0.01205429173177297</v>
@@ -4936,7 +4936,7 @@
         <v>0.04626207456999842</v>
       </c>
       <c r="C105" t="n">
-        <v>0.05333564026405901</v>
+        <v>5.333564026405901e-08</v>
       </c>
       <c r="D105" t="n">
         <v>0.02819459332646113</v>
@@ -4979,7 +4979,7 @@
         <v>0.04441317870454231</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0822571748540184</v>
+        <v>8.22571748540184e-08</v>
       </c>
       <c r="D106" t="n">
         <v>0.04776982217714654</v>
@@ -5022,7 +5022,7 @@
         <v>0.0758745294293075</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1302897989008336</v>
+        <v>1.302897989008336e-07</v>
       </c>
       <c r="D107" t="n">
         <v>0.04098668347672563</v>
@@ -5065,7 +5065,7 @@
         <v>0.06676790237802765</v>
       </c>
       <c r="C108" t="n">
-        <v>0.06070003939976454</v>
+        <v>6.070003939976453e-08</v>
       </c>
       <c r="D108" t="n">
         <v>0.05111618799587347</v>
@@ -5108,7 +5108,7 @@
         <v>-0.03501606612731356</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.02424863703965863</v>
+        <v>-2.424863703965863e-08</v>
       </c>
       <c r="D109" t="n">
         <v>-0.0385404045683394</v>
@@ -5151,7 +5151,7 @@
         <v>-0.02908171637944201</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.04356695049772863</v>
+        <v>-4.356695049772863e-08</v>
       </c>
       <c r="D110" t="n">
         <v>-0.02784144443563674</v>
@@ -5194,7 +5194,7 @@
         <v>0.03962576868127154</v>
       </c>
       <c r="C111" t="n">
-        <v>0.04652696131883993</v>
+        <v>4.652696131883993e-08</v>
       </c>
       <c r="D111" t="n">
         <v>0.03217351225189624</v>
@@ -5237,7 +5237,7 @@
         <v>0.06499415498188532</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0656349562320595</v>
+        <v>6.56349562320595e-08</v>
       </c>
       <c r="D112" t="n">
         <v>0.0750795481378117</v>
@@ -5280,7 +5280,7 @@
         <v>0.05536070844120267</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1091790567679578</v>
+        <v>1.091790567679578e-07</v>
       </c>
       <c r="D113" t="n">
         <v>0.08215577804360819</v>
@@ -5323,7 +5323,7 @@
         <v>0.07123971436492416</v>
       </c>
       <c r="C114" t="n">
-        <v>0.07811741444507381</v>
+        <v>7.811741444507381e-08</v>
       </c>
       <c r="D114" t="n">
         <v>0.1068368944616918</v>
@@ -5366,7 +5366,7 @@
         <v>0.06914609921474035</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0655064732887245</v>
+        <v>6.550647328872449e-08</v>
       </c>
       <c r="D115" t="n">
         <v>0.1285773323529276</v>
@@ -5409,7 +5409,7 @@
         <v>0.01412431708194339</v>
       </c>
       <c r="C116" t="n">
-        <v>0.007701959463753738</v>
+        <v>7.701959463753738e-09</v>
       </c>
       <c r="D116" t="n">
         <v>0.0731251426268027</v>
@@ -5452,7 +5452,7 @@
         <v>-0.001334916194190128</v>
       </c>
       <c r="C117" t="n">
-        <v>0.006029834919858201</v>
+        <v>6.029834919858201e-09</v>
       </c>
       <c r="D117" t="n">
         <v>0.02760587136484771</v>
@@ -5495,7 +5495,7 @@
         <v>0.01605790432531995</v>
       </c>
       <c r="C118" t="n">
-        <v>0.005616480965633164</v>
+        <v>5.616480965633163e-09</v>
       </c>
       <c r="D118" t="n">
         <v>0.03236479560634775</v>
@@ -5538,7 +5538,7 @@
         <v>0.0002486174958054033</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.02738537359662963</v>
+        <v>-2.738537359662963e-08</v>
       </c>
       <c r="D119" t="n">
         <v>0.03957046363911942</v>
@@ -5581,7 +5581,7 @@
         <v>-0.007336395215860048</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00409745914707238</v>
+        <v>4.09745914707238e-09</v>
       </c>
       <c r="D120" t="n">
         <v>0.05623537978247084</v>
@@ -5624,7 +5624,7 @@
         <v>0.0740420472704979</v>
       </c>
       <c r="C121" t="n">
-        <v>0.03126587092685051</v>
+        <v>3.126587092685051e-08</v>
       </c>
       <c r="D121" t="n">
         <v>0.1198084075145711</v>
@@ -5667,7 +5667,7 @@
         <v>0.06978751872334499</v>
       </c>
       <c r="C122" t="n">
-        <v>0.05558402730370493</v>
+        <v>5.558402730370493e-08</v>
       </c>
       <c r="D122" t="n">
         <v>0.0997614528520947</v>
@@ -5710,7 +5710,7 @@
         <v>-0.04030055230549567</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.04149284372079387</v>
+        <v>-4.149284372079387e-08</v>
       </c>
       <c r="D123" t="n">
         <v>0.0276978294436514</v>
@@ -5753,7 +5753,7 @@
         <v>-0.01957370288276628</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.01293885828774721</v>
+        <v>-1.293885828774721e-08</v>
       </c>
       <c r="D124" t="n">
         <v>-0.04048454897881237</v>
@@ -5796,7 +5796,7 @@
         <v>-0.02357840083562435</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.01949198292364251</v>
+        <v>-1.949198292364252e-08</v>
       </c>
       <c r="D125" t="n">
         <v>-0.05717436180233093</v>
@@ -5839,7 +5839,7 @@
         <v>-0.05132198643160768</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.04657556519689043</v>
+        <v>-4.657556519689044e-08</v>
       </c>
       <c r="D126" t="n">
         <v>-0.07672029172410511</v>
@@ -5882,7 +5882,7 @@
         <v>-0.04560466957907472</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.02549834046155974</v>
+        <v>-2.549834046155974e-08</v>
       </c>
       <c r="D127" t="n">
         <v>-0.09954512775922586</v>
@@ -5925,7 +5925,7 @@
         <v>-0.02637317529330596</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.001625008943992867</v>
+        <v>-1.625008943992867e-09</v>
       </c>
       <c r="D128" t="n">
         <v>-0.07524736295634049</v>
@@ -5968,7 +5968,7 @@
         <v>0.01493723178567286</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02914576282039105</v>
+        <v>2.914576282039105e-08</v>
       </c>
       <c r="D129" t="n">
         <v>-0.0337019044764274</v>
@@ -6011,7 +6011,7 @@
         <v>-0.3211260084380412</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.2565157988197249</v>
+        <v>-2.565157988197248e-07</v>
       </c>
       <c r="D130" t="n">
         <v>-0.2376242285390279</v>
@@ -6054,7 +6054,7 @@
         <v>-0.2979367111357416</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.2385575109277954</v>
+        <v>-2.385575109277954e-07</v>
       </c>
       <c r="D131" t="n">
         <v>-0.2450161810218342</v>
@@ -6097,7 +6097,7 @@
         <v>-0.2652529921983906</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.1709875367166298</v>
+        <v>-1.709875367166298e-07</v>
       </c>
       <c r="D132" t="n">
         <v>-0.2281237548467879</v>
@@ -6140,7 +6140,7 @@
         <v>-0.163288712590307</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.1258164934311191</v>
+        <v>-1.258164934311191e-07</v>
       </c>
       <c r="D133" t="n">
         <v>-0.1625349928669745</v>
@@ -6183,7 +6183,7 @@
         <v>-0.1606181569250243</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1176720116367297</v>
+        <v>-1.176720116367297e-07</v>
       </c>
       <c r="D134" t="n">
         <v>-0.1497776793513668</v>
@@ -6226,7 +6226,7 @@
         <v>-0.08043000788744059</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.04047570613370211</v>
+        <v>-4.04757061337021e-08</v>
       </c>
       <c r="D135" t="n">
         <v>-0.1067955925886961</v>
@@ -6269,7 +6269,7 @@
         <v>-0.09756207549320783</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.05835673559820775</v>
+        <v>-5.835673559820776e-08</v>
       </c>
       <c r="D136" t="n">
         <v>-0.07449273169386161</v>
@@ -6312,7 +6312,7 @@
         <v>-0.09440852523947929</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.09153220920096272</v>
+        <v>-9.153220920096273e-08</v>
       </c>
       <c r="D137" t="n">
         <v>-0.05647275379597505</v>
@@ -6355,7 +6355,7 @@
         <v>-0.02925241201437456</v>
       </c>
       <c r="C138" t="n">
-        <v>0.01190575215746925</v>
+        <v>1.190575215746925e-08</v>
       </c>
       <c r="D138" t="n">
         <v>-0.02312090818987766</v>
@@ -6398,7 +6398,7 @@
         <v>-0.009086286746829764</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.049386225006394e-05</v>
+        <v>-8.049386225006394e-11</v>
       </c>
       <c r="D139" t="n">
         <v>0.002647749967994217</v>
@@ -6441,7 +6441,7 @@
         <v>-0.05289190342390859</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.02690306903047934</v>
+        <v>-2.690306903047934e-08</v>
       </c>
       <c r="D140" t="n">
         <v>-0.02486813569589807</v>
@@ -6484,7 +6484,7 @@
         <v>-0.04770926965302213</v>
       </c>
       <c r="C141" t="n">
-        <v>0.008301820634488033</v>
+        <v>8.301820634488033e-09</v>
       </c>
       <c r="D141" t="n">
         <v>-0.01004233211537309</v>
@@ -6527,7 +6527,7 @@
         <v>0.3016131711873009</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3917053468602678</v>
+        <v>3.917053468602678e-07</v>
       </c>
       <c r="D142" t="n">
         <v>0.1555090722367229</v>
@@ -6570,7 +6570,7 @@
         <v>0.3135068080887156</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3109770965982719</v>
+        <v>3.109770965982719e-07</v>
       </c>
       <c r="D143" t="n">
         <v>0.208737713936997</v>
@@ -6613,7 +6613,7 @@
         <v>0.2643281906218475</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2270115551395635</v>
+        <v>2.270115551395635e-07</v>
       </c>
       <c r="D144" t="n">
         <v>0.1597189618426085</v>
@@ -6656,7 +6656,7 @@
         <v>0.1528767999722598</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1352633805387151</v>
+        <v>1.352633805387151e-07</v>
       </c>
       <c r="D145" t="n">
         <v>0.1493538442592246</v>
@@ -6699,7 +6699,7 @@
         <v>0.1174718154184673</v>
       </c>
       <c r="C146" t="n">
-        <v>0.06048379792005698</v>
+        <v>6.048379792005699e-08</v>
       </c>
       <c r="D146" t="n">
         <v>0.09312137274185606</v>
@@ -6742,7 +6742,7 @@
         <v>0.005073849879098313</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.0003752293474912349</v>
+        <v>-3.752293474912349e-10</v>
       </c>
       <c r="D147" t="n">
         <v>0.03303251744698232</v>
@@ -6785,7 +6785,7 @@
         <v>-0.008974814015424104</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.0341228207942702</v>
+        <v>-3.41228207942702e-08</v>
       </c>
       <c r="D148" t="n">
         <v>0.02064439223716308</v>
@@ -6828,7 +6828,7 @@
         <v>-0.02983634348907205</v>
       </c>
       <c r="C149" t="n">
-        <v>0.03667869656925005</v>
+        <v>3.667869656925004e-08</v>
       </c>
       <c r="D149" t="n">
         <v>0.02525818846052719</v>
@@ -6871,7 +6871,7 @@
         <v>-0.07488167445562122</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.0488769387256881</v>
+        <v>-4.88769387256881e-08</v>
       </c>
       <c r="D150" t="n">
         <v>-0.01908265837392842</v>
@@ -6914,7 +6914,7 @@
         <v>-0.07608653597156712</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.05562242703890352</v>
+        <v>-5.562242703890352e-08</v>
       </c>
       <c r="D151" t="n">
         <v>-0.02322739465162538</v>
@@ -6957,7 +6957,7 @@
         <v>0.003513401855108178</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.004042351088964669</v>
+        <v>-4.042351088964669e-09</v>
       </c>
       <c r="D152" t="n">
         <v>0.04469245126102406</v>
@@ -7000,7 +7000,7 @@
         <v>0.01492872359551001</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.006951342290008267</v>
+        <v>-6.951342290008267e-09</v>
       </c>
       <c r="D153" t="n">
         <v>0.06078267356546641</v>
@@ -7043,7 +7043,7 @@
         <v>0.02712264724930513</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.08773653637340917</v>
+        <v>-8.773653637340917e-08</v>
       </c>
       <c r="D154" t="n">
         <v>0.07801214109110344</v>
@@ -7086,7 +7086,7 @@
         <v>-0.003749719127072337</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.03927633201968594</v>
+        <v>-3.927633201968595e-08</v>
       </c>
       <c r="D155" t="n">
         <v>0.03639219731231469</v>
@@ -7129,7 +7129,7 @@
         <v>0.01565593404197729</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.04693970428817384</v>
+        <v>-4.693970428817384e-08</v>
       </c>
       <c r="D156" t="n">
         <v>0.04943323825180768</v>
@@ -7172,7 +7172,7 @@
         <v>0.02444381889983505</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.00887495549905426</v>
+        <v>-8.87495549905426e-09</v>
       </c>
       <c r="D157" t="n">
         <v>0.08068033764190274</v>
@@ -7215,7 +7215,7 @@
         <v>0.001692178166633473</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02462254925445406</v>
+        <v>2.462254925445406e-08</v>
       </c>
       <c r="D158" t="n">
         <v>0.07125304189870896</v>
@@ -7258,7 +7258,7 @@
         <v>0.07983270788494723</v>
       </c>
       <c r="C159" t="n">
-        <v>0.07120620369416275</v>
+        <v>7.120620369416275e-08</v>
       </c>
       <c r="D159" t="n">
         <v>0.07747162842630306</v>
@@ -7301,7 +7301,7 @@
         <v>0.07065338931225584</v>
       </c>
       <c r="C160" t="n">
-        <v>0.07085371325592771</v>
+        <v>7.085371325592771e-08</v>
       </c>
       <c r="D160" t="n">
         <v>0.1017509864099093</v>
@@ -7344,7 +7344,7 @@
         <v>0.1372206589458198</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08035797104149744</v>
+        <v>8.035797104149744e-08</v>
       </c>
       <c r="D161" t="n">
         <v>0.1128245627821238</v>
@@ -7387,7 +7387,7 @@
         <v>0.1571317758438826</v>
       </c>
       <c r="C162" t="n">
-        <v>0.105538806289821</v>
+        <v>1.05538806289821e-07</v>
       </c>
       <c r="D162" t="n">
         <v>0.1230942350575253</v>
@@ -7430,7 +7430,7 @@
         <v>0.1226499358420212</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08329550227842675</v>
+        <v>8.329550227842674e-08</v>
       </c>
       <c r="D163" t="n">
         <v>0.1293968760041335</v>
@@ -7473,7 +7473,7 @@
         <v>0.1041417237101241</v>
       </c>
       <c r="C164" t="n">
-        <v>0.06991994092160869</v>
+        <v>6.991994092160869e-08</v>
       </c>
       <c r="D164" t="n">
         <v>0.08570257624191013</v>
@@ -7516,7 +7516,7 @@
         <v>0.03437222310497168</v>
       </c>
       <c r="C165" t="n">
-        <v>0.01123831927127728</v>
+        <v>1.123831927127728e-08</v>
       </c>
       <c r="D165" t="n">
         <v>0.01943724853967677</v>
@@ -7559,7 +7559,7 @@
         <v>0.1021212339476347</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1147989569360854</v>
+        <v>1.147989569360854e-07</v>
       </c>
       <c r="D166" t="n">
         <v>0.06387024416775744</v>
@@ -7602,7 +7602,7 @@
         <v>0.1035079960663401</v>
       </c>
       <c r="C167" t="n">
-        <v>0.08270022372578101</v>
+        <v>8.270022372578101e-08</v>
       </c>
       <c r="D167" t="n">
         <v>0.06605049130828755</v>
@@ -7645,7 +7645,7 @@
         <v>0.05391510092157215</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0634096140342415</v>
+        <v>6.34096140342415e-08</v>
       </c>
       <c r="D168" t="n">
         <v>0.0393923409435224</v>
@@ -7688,7 +7688,7 @@
         <v>0.05175738078806558</v>
       </c>
       <c r="C169" t="n">
-        <v>0.05627817430364468</v>
+        <v>5.627817430364468e-08</v>
       </c>
       <c r="D169" t="n">
         <v>-0.0222413364993469</v>
@@ -7731,7 +7731,7 @@
         <v>0.1117714454721539</v>
       </c>
       <c r="C170" t="n">
-        <v>0.09626130145517409</v>
+        <v>9.626130145517409e-08</v>
       </c>
       <c r="D170" t="n">
         <v>0.05714778319008063</v>
@@ -7774,7 +7774,7 @@
         <v>0.06827443790013832</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0625102008963756</v>
+        <v>6.25102008963756e-08</v>
       </c>
       <c r="D171" t="n">
         <v>0.03858991040824455</v>
@@ -7817,7 +7817,7 @@
         <v>0.1095948538294929</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1449907583694159</v>
+        <v>1.449907583694159e-07</v>
       </c>
       <c r="D172" t="n">
         <v>0.05551702200287689</v>
@@ -7860,7 +7860,7 @@
         <v>0.03631902308073376</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01085901866780881</v>
+        <v>1.085901866780881e-08</v>
       </c>
       <c r="D173" t="n">
         <v>0.01332933527129132</v>
@@ -7903,7 +7903,7 @@
         <v>0.0525303615786008</v>
       </c>
       <c r="C174" t="n">
-        <v>0.04066235554000119</v>
+        <v>4.066235554000119e-08</v>
       </c>
       <c r="D174" t="n">
         <v>0.05561866797054993</v>
@@ -7946,7 +7946,7 @@
         <v>0.07255001689963736</v>
       </c>
       <c r="C175" t="n">
-        <v>0.08172664128279084</v>
+        <v>8.172664128279084e-08</v>
       </c>
       <c r="D175" t="n">
         <v>0.03141492139115321</v>
@@ -7989,7 +7989,7 @@
         <v>0.08020760708113217</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0965454924506155</v>
+        <v>9.65454924506155e-08</v>
       </c>
       <c r="D176" t="n">
         <v>0.02711826052307931</v>
@@ -8032,7 +8032,7 @@
         <v>0.08034493344905269</v>
       </c>
       <c r="C177" t="n">
-        <v>0.09890633707253871</v>
+        <v>9.890633707253871e-08</v>
       </c>
       <c r="D177" t="n">
         <v>0.03268581619251854</v>
@@ -8075,7 +8075,7 @@
         <v>0.0724485310672609</v>
       </c>
       <c r="C178" t="n">
-        <v>0.06628862177904571</v>
+        <v>6.628862177904571e-08</v>
       </c>
       <c r="D178" t="n">
         <v>0.04614084429571941</v>
@@ -8118,7 +8118,7 @@
         <v>0.05902564658347798</v>
       </c>
       <c r="C179" t="n">
-        <v>0.09002582102395729</v>
+        <v>9.002582102395728e-08</v>
       </c>
       <c r="D179" t="n">
         <v>0.03156309010414526</v>
@@ -8161,7 +8161,7 @@
         <v>0.06354347675797589</v>
       </c>
       <c r="C180" t="n">
-        <v>0.06841856768422061</v>
+        <v>6.84185676842206e-08</v>
       </c>
       <c r="D180" t="n">
         <v>0.04978813204319343</v>
@@ -8204,7 +8204,7 @@
         <v>0.05911247618623894</v>
       </c>
       <c r="C181" t="n">
-        <v>0.05568287126152294</v>
+        <v>5.568287126152294e-08</v>
       </c>
       <c r="D181" t="n">
         <v>0.06776189101923524</v>
@@ -8247,7 +8247,7 @@
         <v>0.04811157355155959</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0488260330876924</v>
+        <v>4.88260330876924e-08</v>
       </c>
       <c r="D182" t="n">
         <v>0.008926992659982202</v>
@@ -8290,7 +8290,7 @@
         <v>0.02334741225555192</v>
       </c>
       <c r="C183" t="n">
-        <v>0.04759249475307969</v>
+        <v>4.759249475307969e-08</v>
       </c>
       <c r="D183" t="n">
         <v>0.01648502992151935</v>
@@ -8333,7 +8333,7 @@
         <v>0.001403954578198752</v>
       </c>
       <c r="C184" t="n">
-        <v>0.004171511286559904</v>
+        <v>4.171511286559904e-09</v>
       </c>
       <c r="D184" t="n">
         <v>-0.01607618578744641</v>
@@ -8376,7 +8376,7 @@
         <v>0.05721346539842154</v>
       </c>
       <c r="C185" t="n">
-        <v>0.06790196429193185</v>
+        <v>6.790196429193185e-08</v>
       </c>
       <c r="D185" t="n">
         <v>0.01984228284700706</v>
@@ -8419,7 +8419,7 @@
         <v>0.01002036466409284</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0351482181387861</v>
+        <v>3.514821813878611e-08</v>
       </c>
       <c r="D186" t="n">
         <v>-0.01493585626273553</v>
@@ -8462,7 +8462,7 @@
         <v>0.0247316719568611</v>
       </c>
       <c r="C187" t="n">
-        <v>0.02536184563893928</v>
+        <v>2.536184563893929e-08</v>
       </c>
       <c r="D187" t="n">
         <v>-0.009858782684233236</v>
@@ -8505,7 +8505,7 @@
         <v>-0.006755032933864147</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.007034907144295777</v>
+        <v>-7.034907144295777e-09</v>
       </c>
       <c r="D188" t="n">
         <v>-0.01472972730514777</v>
@@ -8548,7 +8548,7 @@
         <v>0.001608238080834212</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.006602695701804495</v>
+        <v>-6.602695701804496e-09</v>
       </c>
       <c r="D189" t="n">
         <v>-0.02148707790844151</v>
@@ -8591,7 +8591,7 @@
         <v>0.009039912413623785</v>
       </c>
       <c r="C190" t="n">
-        <v>0.03709965956193373</v>
+        <v>3.709965956193373e-08</v>
       </c>
       <c r="D190" t="n">
         <v>-0.03383764652969745</v>
@@ -8634,7 +8634,7 @@
         <v>-0.02486288999066355</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.02041426292909243</v>
+        <v>-2.041426292909243e-08</v>
       </c>
       <c r="D191" t="n">
         <v>-0.05334040875715973</v>
@@ -8677,7 +8677,7 @@
         <v>0.02858340341849042</v>
       </c>
       <c r="C192" t="n">
-        <v>0.03293184164758056</v>
+        <v>3.293184164758056e-08</v>
       </c>
       <c r="D192" t="n">
         <v>-0.02611337828558613</v>
@@ -8720,7 +8720,7 @@
         <v>0.0274174299127985</v>
       </c>
       <c r="C193" t="n">
-        <v>0.01663008304598312</v>
+        <v>1.663008304598312e-08</v>
       </c>
       <c r="D193" t="n">
         <v>-0.05950078647924617</v>
@@ -8763,7 +8763,7 @@
         <v>-0.04620531710128961</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.04468282422925796</v>
+        <v>-4.468282422925796e-08</v>
       </c>
       <c r="D194" t="n">
         <v>-0.07839306331812967</v>
@@ -8806,7 +8806,7 @@
         <v>-0.01878797153402578</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.0231134516851913</v>
+        <v>-2.31134516851913e-08</v>
       </c>
       <c r="D195" t="n">
         <v>-0.08193828609917064</v>
@@ -8849,7 +8849,7 @@
         <v>0.04110029532286386</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.01004349432469465</v>
+        <v>-1.004349432469465e-08</v>
       </c>
       <c r="D196" t="n">
         <v>-0.05385643727194278</v>
@@ -8892,7 +8892,7 @@
         <v>-0.0155428946423416</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0451966298383446</v>
+        <v>4.51966298383446e-08</v>
       </c>
       <c r="D197" t="n">
         <v>-0.07804618815174746</v>
@@ -8935,7 +8935,7 @@
         <v>0.002877952353288471</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01046877753687081</v>
+        <v>1.046877753687081e-08</v>
       </c>
       <c r="D198" t="n">
         <v>-0.08252312546330798</v>
@@ -8978,7 +8978,7 @@
         <v>-0.003558176829783544</v>
       </c>
       <c r="C199" t="n">
-        <v>0.008236704575432574</v>
+        <v>8.236704575432573e-09</v>
       </c>
       <c r="D199" t="n">
         <v>-0.06362407216148325</v>
@@ -9021,7 +9021,7 @@
         <v>-0.02253988260949014</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.01844044918377197</v>
+        <v>-1.844044918377197e-08</v>
       </c>
       <c r="D200" t="n">
         <v>-0.06196112417757693</v>
@@ -9064,7 +9064,7 @@
         <v>0.05233296209100602</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05120477082152797</v>
+        <v>5.120477082152797e-08</v>
       </c>
       <c r="D201" t="n">
         <v>-0.03412964255087703</v>
@@ -9107,7 +9107,7 @@
         <v>-0.003926171257286226</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.01659150562034706</v>
+        <v>-1.659150562034706e-08</v>
       </c>
       <c r="D202" t="n">
         <v>-0.03854813750418706</v>
@@ -9150,7 +9150,7 @@
         <v>-0.00728143803247816</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.001944138940801587</v>
+        <v>-1.944138940801587e-09</v>
       </c>
       <c r="D203" t="n">
         <v>-0.02726758152673436</v>
@@ -9193,7 +9193,7 @@
         <v>-0.007509611437269359</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.01039446827677271</v>
+        <v>-1.039446827677271e-08</v>
       </c>
       <c r="D204" t="n">
         <v>-0.03889558548897765</v>
@@ -9236,7 +9236,7 @@
         <v>-0.02094323937936493</v>
       </c>
       <c r="C205" t="n">
-        <v>0.02041685951640448</v>
+        <v>2.041685951640448e-08</v>
       </c>
       <c r="D205" t="n">
         <v>-0.02536389404720585</v>
@@ -9279,7 +9279,7 @@
         <v>0.01246948526709835</v>
       </c>
       <c r="C206" t="n">
-        <v>0.02408341972851624</v>
+        <v>2.408341972851624e-08</v>
       </c>
       <c r="D206" t="n">
         <v>0.01851432529216535</v>
@@ -9322,7 +9322,7 @@
         <v>0.03002176970737613</v>
       </c>
       <c r="C207" t="n">
-        <v>0.02927480190973664</v>
+        <v>2.927480190973664e-08</v>
       </c>
       <c r="D207" t="n">
         <v>0.02998281813554038</v>
@@ -9365,7 +9365,7 @@
         <v>-0.06082686830440542</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00174180463676632</v>
+        <v>1.74180463676632e-09</v>
       </c>
       <c r="D208" t="n">
         <v>-0.009469203466134113</v>
@@ -9408,7 +9408,7 @@
         <v>-0.06811880830654959</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.1160786919335504</v>
+        <v>-1.160786919335504e-07</v>
       </c>
       <c r="D209" t="n">
         <v>-0.02560710767360697</v>
@@ -9451,7 +9451,7 @@
         <v>-0.0680672049307165</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.07389258890952322</v>
+        <v>-7.389258890952321e-08</v>
       </c>
       <c r="D210" t="n">
         <v>-0.01766981957113922</v>
@@ -9494,7 +9494,7 @@
         <v>-0.1323409256319059</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.1079073021856527</v>
+        <v>-1.079073021856527e-07</v>
       </c>
       <c r="D211" t="n">
         <v>-0.08058309631555927</v>
@@ -9537,7 +9537,7 @@
         <v>-0.1339330699421756</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.1140657736934125</v>
+        <v>-1.140657736934125e-07</v>
       </c>
       <c r="D212" t="n">
         <v>-0.0797504383412555</v>
@@ -9580,7 +9580,7 @@
         <v>-0.1689712351865271</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.147456732843727</v>
+        <v>-1.47456732843727e-07</v>
       </c>
       <c r="D213" t="n">
         <v>-0.07923859572226777</v>
@@ -9623,7 +9623,7 @@
         <v>-0.1906959767142196</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.1501543711390292</v>
+        <v>-1.501543711390292e-07</v>
       </c>
       <c r="D214" t="n">
         <v>-0.1528790867287751</v>
@@ -9666,7 +9666,7 @@
         <v>-0.1285413523995804</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.1056363595195786</v>
+        <v>-1.056363595195786e-07</v>
       </c>
       <c r="D215" t="n">
         <v>-0.09144317523615664</v>
@@ -9709,7 +9709,7 @@
         <v>-0.1548985676614889</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.1170131427828616</v>
+        <v>-1.170131427828616e-07</v>
       </c>
       <c r="D216" t="n">
         <v>-0.1157927040279122</v>
@@ -9752,7 +9752,7 @@
         <v>-0.1685900324730294</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.1549385927279598</v>
+        <v>-1.549385927279598e-07</v>
       </c>
       <c r="D217" t="n">
         <v>-0.1363618416291017</v>
@@ -9795,7 +9795,7 @@
         <v>-0.1298393744155487</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1150170932982409</v>
+        <v>-1.150170932982409e-07</v>
       </c>
       <c r="D218" t="n">
         <v>-0.165837270643708</v>
@@ -9838,7 +9838,7 @@
         <v>-0.1366611359196844</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.139176089124798</v>
+        <v>-1.39176089124798e-07</v>
       </c>
       <c r="D219" t="n">
         <v>-0.1385969577451233</v>
@@ -9881,7 +9881,7 @@
         <v>-0.1437666613127794</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1713213709797221</v>
+        <v>-1.713213709797221e-07</v>
       </c>
       <c r="D220" t="n">
         <v>-0.1505031371326965</v>
@@ -9924,7 +9924,7 @@
         <v>-0.05607629423935312</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.0108850491595156</v>
+        <v>-1.08850491595156e-08</v>
       </c>
       <c r="D221" t="n">
         <v>-0.09462734230216641</v>
@@ -9967,7 +9967,7 @@
         <v>-0.0674273283244925</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.05886925890515782</v>
+        <v>-5.886925890515782e-08</v>
       </c>
       <c r="D222" t="n">
         <v>-0.109076845788136</v>
@@ -10010,7 +10010,7 @@
         <v>-0.05004057134176887</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.02739716381698809</v>
+        <v>-2.739716381698809e-08</v>
       </c>
       <c r="D223" t="n">
         <v>-0.09634135738945682</v>
@@ -10053,7 +10053,7 @@
         <v>0.01238303773556049</v>
       </c>
       <c r="C224" t="n">
-        <v>0.0108404841009635</v>
+        <v>1.08404841009635e-08</v>
       </c>
       <c r="D224" t="n">
         <v>-0.07462783611814106</v>
@@ -10096,7 +10096,7 @@
         <v>0.007393279041932876</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.005758008782836943</v>
+        <v>-5.758008782836943e-09</v>
       </c>
       <c r="D225" t="n">
         <v>-0.06245220890424819</v>
@@ -10139,7 +10139,7 @@
         <v>0.07281628239529692</v>
       </c>
       <c r="C226" t="n">
-        <v>0.03639767664879412</v>
+        <v>3.639767664879412e-08</v>
       </c>
       <c r="D226" t="n">
         <v>0.0101367080309247</v>
@@ -10182,7 +10182,7 @@
         <v>-0.004205937915913172</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.02688160855645494</v>
+        <v>-2.688160855645494e-08</v>
       </c>
       <c r="D227" t="n">
         <v>-0.01413414194396667</v>
@@ -10225,7 +10225,7 @@
         <v>-0.01616194191503662</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.02359563993691216</v>
+        <v>-2.359563993691216e-08</v>
       </c>
       <c r="D228" t="n">
         <v>-0.0314536663580085</v>
@@ -10268,7 +10268,7 @@
         <v>0.03320304464339241</v>
       </c>
       <c r="C229" t="n">
-        <v>0.02476194368747242</v>
+        <v>2.476194368747242e-08</v>
       </c>
       <c r="D229" t="n">
         <v>0.02607487980993461</v>
@@ -10311,7 +10311,7 @@
         <v>0.0158548805361618</v>
       </c>
       <c r="C230" t="n">
-        <v>0.01927317472215462</v>
+        <v>1.927317472215462e-08</v>
       </c>
       <c r="D230" t="n">
         <v>0.04396810138198037</v>
@@ -10354,7 +10354,7 @@
         <v>0.01002928379945422</v>
       </c>
       <c r="C231" t="n">
-        <v>0.02368349846464746</v>
+        <v>2.368349846464746e-08</v>
       </c>
       <c r="D231" t="n">
         <v>0.04679997686476223</v>
@@ -10397,7 +10397,7 @@
         <v>0.08176322925189972</v>
       </c>
       <c r="C232" t="n">
-        <v>0.09268131211317798</v>
+        <v>9.268131211317798e-08</v>
       </c>
       <c r="D232" t="n">
         <v>0.07804859946507348</v>
@@ -10440,7 +10440,7 @@
         <v>0.04198462363799682</v>
       </c>
       <c r="C233" t="n">
-        <v>0.002069853019512458</v>
+        <v>2.069853019512458e-09</v>
       </c>
       <c r="D233" t="n">
         <v>0.04391995346243749</v>
@@ -10483,7 +10483,7 @@
         <v>0.06532595396757124</v>
       </c>
       <c r="C234" t="n">
-        <v>0.08890011059311553</v>
+        <v>8.890011059311554e-08</v>
       </c>
       <c r="D234" t="n">
         <v>0.07538672582184103</v>
@@ -10526,7 +10526,7 @@
         <v>0.1050227507059129</v>
       </c>
       <c r="C235" t="n">
-        <v>0.05793963413675463</v>
+        <v>5.793963413675462e-08</v>
       </c>
       <c r="D235" t="n">
         <v>0.1503729996385548</v>
@@ -10569,7 +10569,7 @@
         <v>0.09740526995515331</v>
       </c>
       <c r="C236" t="n">
-        <v>0.109583139706517</v>
+        <v>1.09583139706517e-07</v>
       </c>
       <c r="D236" t="n">
         <v>0.1547742570162507</v>
@@ -10612,7 +10612,7 @@
         <v>0.07109960158616824</v>
       </c>
       <c r="C237" t="n">
-        <v>0.1037989673645838</v>
+        <v>1.037989673645838e-07</v>
       </c>
       <c r="D237" t="n">
         <v>0.09824052958552909</v>
@@ -10655,7 +10655,7 @@
         <v>0.08562459548074774</v>
       </c>
       <c r="C238" t="n">
-        <v>0.09383723484646356</v>
+        <v>9.383723484646355e-08</v>
       </c>
       <c r="D238" t="n">
         <v>0.1076203751859086</v>
@@ -10698,7 +10698,7 @@
         <v>0.1382959439814357</v>
       </c>
       <c r="C239" t="n">
-        <v>0.145747902057852</v>
+        <v>1.45747902057852e-07</v>
       </c>
       <c r="D239" t="n">
         <v>0.07345433788965039</v>
@@ -10741,7 +10741,7 @@
         <v>0.1221347049002142</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1257720635420425</v>
+        <v>1.257720635420425e-07</v>
       </c>
       <c r="D240" t="n">
         <v>0.1060976480010944</v>
@@ -10784,7 +10784,7 @@
         <v>0.09117919211185854</v>
       </c>
       <c r="C241" t="n">
-        <v>0.08174008184300141</v>
+        <v>8.174008184300141e-08</v>
       </c>
       <c r="D241" t="n">
         <v>0.1000506758041204</v>
@@ -10827,7 +10827,7 @@
         <v>0.1166625330416708</v>
       </c>
       <c r="C242" t="n">
-        <v>0.1138098288262852</v>
+        <v>1.138098288262852e-07</v>
       </c>
       <c r="D242" t="n">
         <v>0.1014177525634576</v>
@@ -10870,7 +10870,7 @@
         <v>0.1225935409865535</v>
       </c>
       <c r="C243" t="n">
-        <v>0.124453048619231</v>
+        <v>1.24453048619231e-07</v>
       </c>
       <c r="D243" t="n">
         <v>0.07812125073101028</v>
@@ -10913,7 +10913,7 @@
         <v>0.03990005044528866</v>
       </c>
       <c r="C244" t="n">
-        <v>0.07191453446553786</v>
+        <v>7.191453446553787e-08</v>
       </c>
       <c r="D244" t="n">
         <v>0.06052646459148581</v>
@@ -10956,7 +10956,7 @@
         <v>0.03850785559369396</v>
       </c>
       <c r="C245" t="n">
-        <v>0.07422214939710536</v>
+        <v>7.422214939710536e-08</v>
       </c>
       <c r="D245" t="n">
         <v>0.04814095014480779</v>
@@ -10999,7 +10999,7 @@
         <v>0.001941199755403744</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.006881005195007561</v>
+        <v>-6.881005195007561e-09</v>
       </c>
       <c r="D246" t="n">
         <v>0.01821786103165723</v>
@@ -11042,7 +11042,7 @@
         <v>-0.003259899185758308</v>
       </c>
       <c r="C247" t="n">
-        <v>0.02261945142372523</v>
+        <v>2.261945142372523e-08</v>
       </c>
       <c r="D247" t="n">
         <v>-0.01613702249509386</v>
@@ -11085,7 +11085,7 @@
         <v>-0.01542230263887567</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.02325908267393884</v>
+        <v>-2.325908267393884e-08</v>
       </c>
       <c r="D248" t="n">
         <v>-0.03090282388185794</v>
@@ -11128,7 +11128,7 @@
         <v>0.0144833089292391</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.002355169030637039</v>
+        <v>-2.355169030637039e-09</v>
       </c>
       <c r="D249" t="n">
         <v>0.02497926009125817</v>
@@ -11171,7 +11171,7 @@
         <v>0.04817683432839903</v>
       </c>
       <c r="C250" t="n">
-        <v>0.04678615334283576</v>
+        <v>4.678615334283576e-08</v>
       </c>
       <c r="D250" t="n">
         <v>0.06337564785684013</v>
@@ -11214,7 +11214,7 @@
         <v>0.008303809079122537</v>
       </c>
       <c r="C251" t="n">
-        <v>0.01477657197210713</v>
+        <v>1.477657197210713e-08</v>
       </c>
       <c r="D251" t="n">
         <v>0.02659409229258847</v>
@@ -11257,7 +11257,7 @@
         <v>0.03660185791849613</v>
       </c>
       <c r="C252" t="n">
-        <v>0.02985280301847459</v>
+        <v>2.985280301847459e-08</v>
       </c>
       <c r="D252" t="n">
         <v>0.039483946110072</v>
@@ -11300,7 +11300,7 @@
         <v>0.07117710391463228</v>
       </c>
       <c r="C253" t="n">
-        <v>0.08443535038248529</v>
+        <v>8.443535038248528e-08</v>
       </c>
       <c r="D253" t="n">
         <v>0.03625809686479164</v>
@@ -11343,7 +11343,7 @@
         <v>0.07365214682268229</v>
       </c>
       <c r="C254" t="n">
-        <v>0.07324055137747054</v>
+        <v>7.324055137747054e-08</v>
       </c>
       <c r="D254" t="n">
         <v>0.05745492857886414</v>
@@ -11386,7 +11386,7 @@
         <v>0.05447688862985522</v>
       </c>
       <c r="C255" t="n">
-        <v>0.05902160428961123</v>
+        <v>5.902160428961123e-08</v>
       </c>
       <c r="D255" t="n">
         <v>0.02549896497209159</v>
@@ -11429,7 +11429,7 @@
         <v>0.1169260369515444</v>
       </c>
       <c r="C256" t="n">
-        <v>0.09870546556088611</v>
+        <v>9.870546556088611e-08</v>
       </c>
       <c r="D256" t="n">
         <v>0.05665534819237394</v>
@@ -11472,7 +11472,7 @@
         <v>0.08785099197577129</v>
       </c>
       <c r="C257" t="n">
-        <v>0.08537419444554373</v>
+        <v>8.537419444554373e-08</v>
       </c>
       <c r="D257" t="n">
         <v>0.05102600017245051</v>
@@ -11515,7 +11515,7 @@
         <v>0.1192384274705727</v>
       </c>
       <c r="C258" t="n">
-        <v>0.1174520973265138</v>
+        <v>1.174520973265138e-07</v>
       </c>
       <c r="D258" t="n">
         <v>0.08783663898528737</v>
@@ -11558,7 +11558,7 @@
         <v>0.11446600575159</v>
       </c>
       <c r="C259" t="n">
-        <v>0.09112896710121565</v>
+        <v>9.112896710121565e-08</v>
       </c>
       <c r="D259" t="n">
         <v>0.07830446161609883</v>
@@ -11601,7 +11601,7 @@
         <v>0.0884960977265592</v>
       </c>
       <c r="C260" t="n">
-        <v>0.09290597596026728</v>
+        <v>9.290597596026729e-08</v>
       </c>
       <c r="D260" t="n">
         <v>0.08072700729430005</v>
@@ -11644,7 +11644,7 @@
         <v>0.1252766492784214</v>
       </c>
       <c r="C261" t="n">
-        <v>0.102982473989669</v>
+        <v>1.02982473989669e-07</v>
       </c>
       <c r="D261" t="n">
         <v>0.05621256225451754</v>
@@ -11687,7 +11687,7 @@
         <v>0.06800399785729572</v>
       </c>
       <c r="C262" t="n">
-        <v>0.06492418147981338</v>
+        <v>6.492418147981338e-08</v>
       </c>
       <c r="D262" t="n">
         <v>-0.008176158675285428</v>
@@ -11730,7 +11730,7 @@
         <v>0.09094094215499648</v>
       </c>
       <c r="C263" t="n">
-        <v>0.07446105009342729</v>
+        <v>7.44610500934273e-08</v>
       </c>
       <c r="D263" t="n">
         <v>0.03153466522347537</v>
@@ -11773,7 +11773,7 @@
         <v>0.1340884606913195</v>
       </c>
       <c r="C264" t="n">
-        <v>0.1122644364547656</v>
+        <v>1.122644364547656e-07</v>
       </c>
       <c r="D264" t="n">
         <v>0.04655799550792006</v>
@@ -11816,7 +11816,7 @@
         <v>0.08051810189784581</v>
       </c>
       <c r="C265" t="n">
-        <v>0.05782081560706254</v>
+        <v>5.782081560706253e-08</v>
       </c>
       <c r="D265" t="n">
         <v>0.02716916294732363</v>
@@ -11859,7 +11859,7 @@
         <v>0.02583496886206849</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.001924203004195046</v>
+        <v>-1.924203004195046e-09</v>
       </c>
       <c r="D266" t="n">
         <v>0.02193771530865063</v>
@@ -11902,7 +11902,7 @@
         <v>0.05106135023096825</v>
       </c>
       <c r="C267" t="n">
-        <v>0.01665031881611179</v>
+        <v>1.665031881611179e-08</v>
       </c>
       <c r="D267" t="n">
         <v>0.03454386275544596</v>
@@ -11945,7 +11945,7 @@
         <v>0.05822645824546679</v>
       </c>
       <c r="C268" t="n">
-        <v>0.03406630501793262</v>
+        <v>3.406630501793262e-08</v>
       </c>
       <c r="D268" t="n">
         <v>0.009105918666783674</v>
@@ -11988,7 +11988,7 @@
         <v>0.0238684106524516</v>
       </c>
       <c r="C269" t="n">
-        <v>0.007189397189474089</v>
+        <v>7.189397189474089e-09</v>
       </c>
       <c r="D269" t="n">
         <v>0.02949557564385952</v>
@@ -12031,7 +12031,7 @@
         <v>0.02700325205104259</v>
       </c>
       <c r="C270" t="n">
-        <v>0.003546777387537281</v>
+        <v>3.546777387537281e-09</v>
       </c>
       <c r="D270" t="n">
         <v>-0.01518029222767259</v>
@@ -12074,7 +12074,7 @@
         <v>0.04102823757040852</v>
       </c>
       <c r="C271" t="n">
-        <v>0.03271670702470497</v>
+        <v>3.271670702470497e-08</v>
       </c>
       <c r="D271" t="n">
         <v>-0.0117125574806336</v>
@@ -12117,7 +12117,7 @@
         <v>0.0380241093376219</v>
       </c>
       <c r="C272" t="n">
-        <v>0.02824579172849906</v>
+        <v>2.824579172849906e-08</v>
       </c>
       <c r="D272" t="n">
         <v>-0.02926481791735602</v>
@@ -12160,7 +12160,7 @@
         <v>0.02047932537386288</v>
       </c>
       <c r="C273" t="n">
-        <v>0.02703547866816791</v>
+        <v>2.703547866816791e-08</v>
       </c>
       <c r="D273" t="n">
         <v>-0.001125718736767256</v>
@@ -12203,7 +12203,7 @@
         <v>-0.0013967557059269</v>
       </c>
       <c r="C274" t="n">
-        <v>0.002207406341990348</v>
+        <v>2.207406341990348e-09</v>
       </c>
       <c r="D274" t="n">
         <v>0.0003492681109842355</v>
@@ -12246,7 +12246,7 @@
         <v>-0.003207261782844362</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.00472578431880899</v>
+        <v>-4.72578431880899e-09</v>
       </c>
       <c r="D275" t="n">
         <v>-0.02022566075332288</v>
@@ -12289,7 +12289,7 @@
         <v>-0.03988745706072305</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.04152270181218087</v>
+        <v>-4.152270181218087e-08</v>
       </c>
       <c r="D276" t="n">
         <v>-0.03715190241320476</v>
@@ -12332,7 +12332,7 @@
         <v>-0.0335977939453902</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.03721698083349578</v>
+        <v>-3.721698083349578e-08</v>
       </c>
       <c r="D277" t="n">
         <v>-0.03386670997398411</v>
@@ -12375,7 +12375,7 @@
         <v>0.03267400609230675</v>
       </c>
       <c r="C278" t="n">
-        <v>0.03589726468039656</v>
+        <v>3.589726468039656e-08</v>
       </c>
       <c r="D278" t="n">
         <v>-0.0162163747555073</v>
@@ -12418,7 +12418,7 @@
         <v>-0.00118178649757128</v>
       </c>
       <c r="C279" t="n">
-        <v>0.004800319367258332</v>
+        <v>4.800319367258332e-09</v>
       </c>
       <c r="D279" t="n">
         <v>-0.003347431432068393</v>
@@ -12461,7 +12461,7 @@
         <v>-0.01843770045572424</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.02143309110954994</v>
+        <v>-2.143309110954994e-08</v>
       </c>
       <c r="D280" t="n">
         <v>-0.007994992367717169</v>
@@ -12504,7 +12504,7 @@
         <v>0.02177146027128529</v>
       </c>
       <c r="C281" t="n">
-        <v>0.01841871992387278</v>
+        <v>1.841871992387278e-08</v>
       </c>
       <c r="D281" t="n">
         <v>-0.03089934422089546</v>
@@ -12547,7 +12547,7 @@
         <v>0.0119906287137117</v>
       </c>
       <c r="C282" t="n">
-        <v>0.01625980916141145</v>
+        <v>1.625980916141145e-08</v>
       </c>
       <c r="D282" t="n">
         <v>0.002861040679217552</v>
@@ -12590,7 +12590,7 @@
         <v>0.01116867338422756</v>
       </c>
       <c r="C283" t="n">
-        <v>0.005712768615540487</v>
+        <v>5.712768615540486e-09</v>
       </c>
       <c r="D283" t="n">
         <v>0.001498130003839471</v>
@@ -12633,7 +12633,7 @@
         <v>0.0253086624616603</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0005377514698984287</v>
+        <v>-5.377514698984287e-10</v>
       </c>
       <c r="D284" t="n">
         <v>0.02829244701264844</v>
@@ -12676,7 +12676,7 @@
         <v>0.004713074011657437</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.007783124821529652</v>
+        <v>-7.783124821529653e-09</v>
       </c>
       <c r="D285" t="n">
         <v>-0.01489860113452579</v>
@@ -12719,7 +12719,7 @@
         <v>0.04658752230467544</v>
       </c>
       <c r="C286" t="n">
-        <v>0.01836271241758403</v>
+        <v>1.836271241758402e-08</v>
       </c>
       <c r="D286" t="n">
         <v>0.02953083546730495</v>
@@ -12762,7 +12762,7 @@
         <v>0.05816305571528346</v>
       </c>
       <c r="C287" t="n">
-        <v>0.03936736780516248</v>
+        <v>3.936736780516248e-08</v>
       </c>
       <c r="D287" t="n">
         <v>0.04864381197979695</v>
@@ -12805,7 +12805,7 @@
         <v>0.03481089525225634</v>
       </c>
       <c r="C288" t="n">
-        <v>0.02924721239557271</v>
+        <v>2.924721239557271e-08</v>
       </c>
       <c r="D288" t="n">
         <v>0.02107533850769761</v>
@@ -12848,7 +12848,7 @@
         <v>0.06843333982594535</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0598250125291766</v>
+        <v>5.982501252917661e-08</v>
       </c>
       <c r="D289" t="n">
         <v>0.0223260254751616</v>
@@ -12891,7 +12891,7 @@
         <v>0.008761466545507801</v>
       </c>
       <c r="C290" t="n">
-        <v>0.01185217726573762</v>
+        <v>1.185217726573762e-08</v>
       </c>
       <c r="D290" t="n">
         <v>-0.02208771855578739</v>
@@ -12934,7 +12934,7 @@
         <v>0.03298028870279213</v>
       </c>
       <c r="C291" t="n">
-        <v>0.03351274961961059</v>
+        <v>3.35127496196106e-08</v>
       </c>
       <c r="D291" t="n">
         <v>-0.01251589789513929</v>
@@ -12977,7 +12977,7 @@
         <v>0.06314907075575027</v>
       </c>
       <c r="C292" t="n">
-        <v>0.05590874372075838</v>
+        <v>5.590874372075838e-08</v>
       </c>
       <c r="D292" t="n">
         <v>0.02178769830584604</v>
@@ -13020,7 +13020,7 @@
         <v>0.03545188947865219</v>
       </c>
       <c r="C293" t="n">
-        <v>0.02389758570113432</v>
+        <v>2.389758570113431e-08</v>
       </c>
       <c r="D293" t="n">
         <v>0.02532719483097323</v>
@@ -13063,7 +13063,7 @@
         <v>0.0836924401644692</v>
       </c>
       <c r="C294" t="n">
-        <v>0.05934059988893314</v>
+        <v>5.934059988893314e-08</v>
       </c>
       <c r="D294" t="n">
         <v>0.04199954387806892</v>
@@ -13106,7 +13106,7 @@
         <v>0.06580369122344365</v>
       </c>
       <c r="C295" t="n">
-        <v>0.05390703131980179</v>
+        <v>5.390703131980179e-08</v>
       </c>
       <c r="D295" t="n">
         <v>0.06110291894376974</v>
@@ -13149,7 +13149,7 @@
         <v>0.05118680360620087</v>
       </c>
       <c r="C296" t="n">
-        <v>0.05699099198300606</v>
+        <v>5.699099198300606e-08</v>
       </c>
       <c r="D296" t="n">
         <v>0.001167878717958981</v>
@@ -13192,7 +13192,7 @@
         <v>0.03875228811278908</v>
       </c>
       <c r="C297" t="n">
-        <v>0.03991269924559249</v>
+        <v>3.991269924559249e-08</v>
       </c>
       <c r="D297" t="n">
         <v>0.02955164633677843</v>
@@ -13235,7 +13235,7 @@
         <v>0.02454716518148237</v>
       </c>
       <c r="C298" t="n">
-        <v>0.01081115240720942</v>
+        <v>1.081115240720942e-08</v>
       </c>
       <c r="D298" t="n">
         <v>0.004371781129176133</v>
@@ -13278,7 +13278,7 @@
         <v>0.03298433728859718</v>
       </c>
       <c r="C299" t="n">
-        <v>0.02777044801185236</v>
+        <v>2.777044801185236e-08</v>
       </c>
       <c r="D299" t="n">
         <v>0.01825031025128387</v>
@@ -13321,7 +13321,7 @@
         <v>0.04507386817870995</v>
       </c>
       <c r="C300" t="n">
-        <v>0.03663906644519321</v>
+        <v>3.663906644519321e-08</v>
       </c>
       <c r="D300" t="n">
         <v>0.03901322631013682</v>
@@ -13364,7 +13364,7 @@
         <v>0.04774522760947697</v>
       </c>
       <c r="C301" t="n">
-        <v>0.03147561656173092</v>
+        <v>3.147561656173092e-08</v>
       </c>
       <c r="D301" t="n">
         <v>0.05331745518014097</v>
@@ -13407,7 +13407,7 @@
         <v>0.05336380009538866</v>
       </c>
       <c r="C302" t="n">
-        <v>0.03377411742877423</v>
+        <v>3.377411742877423e-08</v>
       </c>
       <c r="D302" t="n">
         <v>0.04101074181332542</v>
@@ -13450,7 +13450,7 @@
         <v>0.05235040447155748</v>
       </c>
       <c r="C303" t="n">
-        <v>0.03221353623964363</v>
+        <v>3.221353623964362e-08</v>
       </c>
       <c r="D303" t="n">
         <v>0.01621144324312662</v>
@@ -13493,7 +13493,7 @@
         <v>0.01069391546143206</v>
       </c>
       <c r="C304" t="n">
-        <v>0.005282433788493579</v>
+        <v>5.282433788493579e-09</v>
       </c>
       <c r="D304" t="n">
         <v>-0.006741055249131711</v>
@@ -13536,7 +13536,7 @@
         <v>0.01076295803963223</v>
       </c>
       <c r="C305" t="n">
-        <v>0.001589416570332958</v>
+        <v>1.589416570332958e-09</v>
       </c>
       <c r="D305" t="n">
         <v>0.02198689027007572</v>
@@ -13579,7 +13579,7 @@
         <v>0.006425467793484962</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0004784092237797299</v>
+        <v>4.784092237797299e-10</v>
       </c>
       <c r="D306" t="n">
         <v>-0.01261613960311925</v>
@@ -13622,7 +13622,7 @@
         <v>0.02179122487909946</v>
       </c>
       <c r="C307" t="n">
-        <v>0.01356348012598785</v>
+        <v>1.356348012598785e-08</v>
       </c>
       <c r="D307" t="n">
         <v>-0.02600368830965816</v>
@@ -13665,7 +13665,7 @@
         <v>0.01738037130226378</v>
       </c>
       <c r="C308" t="n">
-        <v>0.002692624512282249</v>
+        <v>2.692624512282249e-09</v>
       </c>
       <c r="D308" t="n">
         <v>0.01605709819745593</v>
@@ -13708,7 +13708,7 @@
         <v>0.0315065052806982</v>
       </c>
       <c r="C309" t="n">
-        <v>0.02229988549865602</v>
+        <v>2.229988549865603e-08</v>
       </c>
       <c r="D309" t="n">
         <v>0.005621748801291071</v>
@@ -13751,7 +13751,7 @@
         <v>0.05760639480092444</v>
       </c>
       <c r="C310" t="n">
-        <v>0.06605984965448575</v>
+        <v>6.605984965448574e-08</v>
       </c>
       <c r="D310" t="n">
         <v>0.02765365279777066</v>
@@ -13794,7 +13794,7 @@
         <v>0.0392183953272558</v>
       </c>
       <c r="C311" t="n">
-        <v>0.03167353210164303</v>
+        <v>3.167353210164303e-08</v>
       </c>
       <c r="D311" t="n">
         <v>0.006449098348123794</v>
@@ -13837,7 +13837,7 @@
         <v>0.04030672935637236</v>
       </c>
       <c r="C312" t="n">
-        <v>0.02312771068015218</v>
+        <v>2.312771068015218e-08</v>
       </c>
       <c r="D312" t="n">
         <v>-0.01061366387585427</v>
@@ -13880,7 +13880,7 @@
         <v>0.03256952397658175</v>
       </c>
       <c r="C313" t="n">
-        <v>0.02328857894111613</v>
+        <v>2.328857894111613e-08</v>
       </c>
       <c r="D313" t="n">
         <v>0.0004675393706392583</v>
@@ -13923,7 +13923,7 @@
         <v>0.04284273075992617</v>
       </c>
       <c r="C314" t="n">
-        <v>0.03904035837362874</v>
+        <v>3.904035837362873e-08</v>
       </c>
       <c r="D314" t="n">
         <v>0.01486728282430261</v>
@@ -13966,7 +13966,7 @@
         <v>0.01695417566818946</v>
       </c>
       <c r="C315" t="n">
-        <v>0.02794702492713119</v>
+        <v>2.794702492713119e-08</v>
       </c>
       <c r="D315" t="n">
         <v>0.009317167916605751</v>
@@ -14009,7 +14009,7 @@
         <v>0.02667460736765204</v>
       </c>
       <c r="C316" t="n">
-        <v>0.02932911382026648</v>
+        <v>2.932911382026648e-08</v>
       </c>
       <c r="D316" t="n">
         <v>0.003985254669233163</v>
@@ -14052,7 +14052,7 @@
         <v>0.08786087073308191</v>
       </c>
       <c r="C317" t="n">
-        <v>0.09064674858859423</v>
+        <v>9.064674858859423e-08</v>
       </c>
       <c r="D317" t="n">
         <v>0.00387501551756908</v>
@@ -14095,7 +14095,7 @@
         <v>0.04393080703505214</v>
       </c>
       <c r="C318" t="n">
-        <v>0.05428876992000031</v>
+        <v>5.428876992000032e-08</v>
       </c>
       <c r="D318" t="n">
         <v>0.02155649256478576</v>
@@ -14138,7 +14138,7 @@
         <v>0.04180576220044174</v>
       </c>
       <c r="C319" t="n">
-        <v>0.03362364189456657</v>
+        <v>3.362364189456657e-08</v>
       </c>
       <c r="D319" t="n">
         <v>0.02726818385755503</v>
@@ -14181,7 +14181,7 @@
         <v>0.06696785105276204</v>
       </c>
       <c r="C320" t="n">
-        <v>0.06734312555106525</v>
+        <v>6.734312555106525e-08</v>
       </c>
       <c r="D320" t="n">
         <v>0.02221111410746235</v>
@@ -14224,7 +14224,7 @@
         <v>0.05938480459757534</v>
       </c>
       <c r="C321" t="n">
-        <v>0.04638316396427</v>
+        <v>4.638316396427e-08</v>
       </c>
       <c r="D321" t="n">
         <v>0.01457379056003649</v>
@@ -14267,7 +14267,7 @@
         <v>0.05567042878888717</v>
       </c>
       <c r="C322" t="n">
-        <v>0.03517921613197572</v>
+        <v>3.517921613197572e-08</v>
       </c>
       <c r="D322" t="n">
         <v>0.0005306793799160214</v>
@@ -14310,7 +14310,7 @@
         <v>0.04357806509517181</v>
       </c>
       <c r="C323" t="n">
-        <v>0.05143917803260556</v>
+        <v>5.143917803260556e-08</v>
       </c>
       <c r="D323" t="n">
         <v>0.008422528722962896</v>
@@ -14353,7 +14353,7 @@
         <v>0.07531085086948486</v>
       </c>
       <c r="C324" t="n">
-        <v>0.06857079026611124</v>
+        <v>6.857079026611123e-08</v>
       </c>
       <c r="D324" t="n">
         <v>0.03827018156259188</v>
@@ -14396,7 +14396,7 @@
         <v>0.06088998948339919</v>
       </c>
       <c r="C325" t="n">
-        <v>0.05483179174550989</v>
+        <v>5.483179174550989e-08</v>
       </c>
       <c r="D325" t="n">
         <v>0.001554156349438118</v>
@@ -14439,7 +14439,7 @@
         <v>0.05855143370621407</v>
       </c>
       <c r="C326" t="n">
-        <v>0.05011562899930411</v>
+        <v>5.01156289993041e-08</v>
       </c>
       <c r="D326" t="n">
         <v>0.007945457523386157</v>
@@ -14482,7 +14482,7 @@
         <v>0.09917462619523709</v>
       </c>
       <c r="C327" t="n">
-        <v>0.09494403871826451</v>
+        <v>9.494403871826451e-08</v>
       </c>
       <c r="D327" t="n">
         <v>0.02694518187304729</v>
@@ -14525,7 +14525,7 @@
         <v>0.1041945739232606</v>
       </c>
       <c r="C328" t="n">
-        <v>0.09144565002825389</v>
+        <v>9.144565002825389e-08</v>
       </c>
       <c r="D328" t="n">
         <v>0.03150291537392014</v>
@@ -14568,7 +14568,7 @@
         <v>0.04000070077434925</v>
       </c>
       <c r="C329" t="n">
-        <v>0.03086214975340962</v>
+        <v>3.086214975340961e-08</v>
       </c>
       <c r="D329" t="n">
         <v>0.02842464902553576</v>
@@ -14611,7 +14611,7 @@
         <v>0.06295765901860073</v>
       </c>
       <c r="C330" t="n">
-        <v>0.05629002415840167</v>
+        <v>5.629002415840168e-08</v>
       </c>
       <c r="D330" t="n">
         <v>0.01317507669097662</v>
@@ -14654,7 +14654,7 @@
         <v>0.05954587173771553</v>
       </c>
       <c r="C331" t="n">
-        <v>0.07414486981490342</v>
+        <v>7.414486981490342e-08</v>
       </c>
       <c r="D331" t="n">
         <v>-0.01078216469543902</v>
@@ -14697,7 +14697,7 @@
         <v>0.04173061339683226</v>
       </c>
       <c r="C332" t="n">
-        <v>0.03974569170531494</v>
+        <v>3.974569170531495e-08</v>
       </c>
       <c r="D332" t="n">
         <v>-0.0162738837456452</v>
@@ -14740,7 +14740,7 @@
         <v>0.0383663930201219</v>
       </c>
       <c r="C333" t="n">
-        <v>0.03745083874855903</v>
+        <v>3.745083874855903e-08</v>
       </c>
       <c r="D333" t="n">
         <v>-0.03156114157040391</v>
@@ -14783,7 +14783,7 @@
         <v>0.02929350137982034</v>
       </c>
       <c r="C334" t="n">
-        <v>0.04881230093075906</v>
+        <v>4.881230093075905e-08</v>
       </c>
       <c r="D334" t="n">
         <v>-0.01617719829323117</v>
@@ -14826,7 +14826,7 @@
         <v>0.03734027008490792</v>
       </c>
       <c r="C335" t="n">
-        <v>0.01694221529529982</v>
+        <v>1.694221529529982e-08</v>
       </c>
       <c r="D335" t="n">
         <v>-0.02581536718973865</v>
@@ -14869,7 +14869,7 @@
         <v>0.03722559718300422</v>
       </c>
       <c r="C336" t="n">
-        <v>0.03655399016192296</v>
+        <v>3.655399016192296e-08</v>
       </c>
       <c r="D336" t="n">
         <v>-0.03337600238135141</v>
@@ -14912,7 +14912,7 @@
         <v>0.02009657186433711</v>
       </c>
       <c r="C337" t="n">
-        <v>0.01177394468593107</v>
+        <v>1.177394468593107e-08</v>
       </c>
       <c r="D337" t="n">
         <v>-0.031415298688663</v>
@@ -14955,7 +14955,7 @@
         <v>0.0329378619107501</v>
       </c>
       <c r="C338" t="n">
-        <v>0.02205230130594282</v>
+        <v>2.205230130594282e-08</v>
       </c>
       <c r="D338" t="n">
         <v>-0.0236268761464844</v>
@@ -14998,7 +14998,7 @@
         <v>0.006754604595028413</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.01812370272725283</v>
+        <v>-1.812370272725283e-08</v>
       </c>
       <c r="D339" t="n">
         <v>-0.02147175121416189</v>
@@ -15041,7 +15041,7 @@
         <v>0.03608718603085159</v>
       </c>
       <c r="C340" t="n">
-        <v>0.006104598874596467</v>
+        <v>6.104598874596467e-09</v>
       </c>
       <c r="D340" t="n">
         <v>-0.02717902758988677</v>
@@ -15084,7 +15084,7 @@
         <v>0.04786722032880442</v>
       </c>
       <c r="C341" t="n">
-        <v>0.01377554566792671</v>
+        <v>1.377554566792671e-08</v>
       </c>
       <c r="D341" t="n">
         <v>-0.0304898844296887</v>
@@ -15127,7 +15127,7 @@
         <v>0.05707966553002475</v>
       </c>
       <c r="C342" t="n">
-        <v>0.02861031361499267</v>
+        <v>2.861031361499267e-08</v>
       </c>
       <c r="D342" t="n">
         <v>-0.007315978393046985</v>
@@ -15170,7 +15170,7 @@
         <v>0.05796758007875713</v>
       </c>
       <c r="C343" t="n">
-        <v>0.01542678259431263</v>
+        <v>1.542678259431263e-08</v>
       </c>
       <c r="D343" t="n">
         <v>0.02358318998354969</v>
@@ -15213,7 +15213,7 @@
         <v>0.05832493748071754</v>
       </c>
       <c r="C344" t="n">
-        <v>0.03787456707214698</v>
+        <v>3.787456707214698e-08</v>
       </c>
       <c r="D344" t="n">
         <v>0.008976182008715528</v>
@@ -15256,7 +15256,7 @@
         <v>0.1028063804631847</v>
       </c>
       <c r="C345" t="n">
-        <v>0.07473286693445225</v>
+        <v>7.473286693445224e-08</v>
       </c>
       <c r="D345" t="n">
         <v>0.07746571937349511</v>
@@ -15299,7 +15299,7 @@
         <v>0.02174380955818633</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.004339839449503669</v>
+        <v>-4.339839449503669e-09</v>
       </c>
       <c r="D346" t="n">
         <v>0.01640061130985315</v>
@@ -15342,7 +15342,7 @@
         <v>0.05187470834096608</v>
       </c>
       <c r="C347" t="n">
-        <v>0.02981661709703376</v>
+        <v>2.981661709703376e-08</v>
       </c>
       <c r="D347" t="n">
         <v>0.04059041109093364</v>
@@ -15385,7 +15385,7 @@
         <v>0.03565456337568573</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.009885449197875706</v>
+        <v>-9.885449197875706e-09</v>
       </c>
       <c r="D348" t="n">
         <v>0.04254119250717769</v>
@@ -15428,7 +15428,7 @@
         <v>0.06733495705622539</v>
       </c>
       <c r="C349" t="n">
-        <v>0.05748503177485431</v>
+        <v>5.748503177485431e-08</v>
       </c>
       <c r="D349" t="n">
         <v>0.06314668992932382</v>
@@ -15471,7 +15471,7 @@
         <v>0.0537102070343296</v>
       </c>
       <c r="C350" t="n">
-        <v>0.03221290638624019</v>
+        <v>3.221290638624019e-08</v>
       </c>
       <c r="D350" t="n">
         <v>0.06187877584876689</v>
@@ -15514,7 +15514,7 @@
         <v>0.06036670691439472</v>
       </c>
       <c r="C351" t="n">
-        <v>0.05009954463559962</v>
+        <v>5.009954463559963e-08</v>
       </c>
       <c r="D351" t="n">
         <v>0.01678606627330637</v>
@@ -15557,7 +15557,7 @@
         <v>-0.5325129567640501</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.4915659183123405</v>
+        <v>-4.915659183123406e-07</v>
       </c>
       <c r="D352" t="n">
         <v>-0.4432484992891549</v>
@@ -15600,7 +15600,7 @@
         <v>-0.9940227326538874</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.9811541009962225</v>
+        <v>-9.811541009962225e-07</v>
       </c>
       <c r="D353" t="n">
         <v>-0.8869152333499032</v>
@@ -15643,7 +15643,7 @@
         <v>-0.9880358947158148</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.9597695620011115</v>
+        <v>-9.597695620011115e-07</v>
       </c>
       <c r="D354" t="n">
         <v>-0.8216074906229978</v>
@@ -15686,7 +15686,7 @@
         <v>-0.9813346953108211</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.9435071657721545</v>
+        <v>-9.435071657721546e-07</v>
       </c>
       <c r="D355" t="n">
         <v>-0.8141615023146667</v>
@@ -15729,7 +15729,7 @@
         <v>-0.9774518389800343</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.9363734028934001</v>
+        <v>-9.363734028934001e-07</v>
       </c>
       <c r="D356" t="n">
         <v>-0.756449246190539</v>
@@ -15772,7 +15772,7 @@
         <v>-0.9746065489675475</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.9099913804652259</v>
+        <v>-9.099913804652259e-07</v>
       </c>
       <c r="D357" t="n">
         <v>-0.7418974448420637</v>
@@ -15815,7 +15815,7 @@
         <v>-0.9743005116124162</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.8990927728658881</v>
+        <v>-8.99092772865888e-07</v>
       </c>
       <c r="D358" t="n">
         <v>-0.7497533428419089</v>
@@ -15858,7 +15858,7 @@
         <v>-0.9007588640345942</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.8142262153916584</v>
+        <v>-8.142262153916584e-07</v>
       </c>
       <c r="D359" t="n">
         <v>-0.7496984249241102</v>
@@ -15901,7 +15901,7 @@
         <v>-0.7676648845887606</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.6575406980184264</v>
+        <v>-6.575406980184264e-07</v>
       </c>
       <c r="D360" t="n">
         <v>-0.7185394972249413</v>
@@ -15944,7 +15944,7 @@
         <v>-0.7481522300126002</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.66511323920903</v>
+        <v>-6.6511323920903e-07</v>
       </c>
       <c r="D361" t="n">
         <v>-0.7013204008362499</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -507,7 +507,7 @@
         <v>-0.05562146031940518</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.118643009229353e-08</v>
+        <v>-0.07118643009229364</v>
       </c>
       <c r="D2" t="n">
         <v>-0.105255635500261</v>
@@ -550,7 +550,7 @@
         <v>-0.227175122022969</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.300346783839634e-07</v>
+        <v>-0.2300346783839635</v>
       </c>
       <c r="D3" t="n">
         <v>-0.2372997475969882</v>
@@ -593,7 +593,7 @@
         <v>-0.1391888075470618</v>
       </c>
       <c r="C4" t="n">
-        <v>-9.632595965665702e-08</v>
+        <v>-0.09632595965665713</v>
       </c>
       <c r="D4" t="n">
         <v>-0.2048538865822255</v>
@@ -636,7 +636,7 @@
         <v>-0.01876615744290178</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.091600917809226e-08</v>
+        <v>-0.06091600917809226</v>
       </c>
       <c r="D5" t="n">
         <v>-0.094213355257183</v>
@@ -679,7 +679,7 @@
         <v>-0.0004911077516509543</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.013216073307122e-08</v>
+        <v>-0.02013216073307111</v>
       </c>
       <c r="D6" t="n">
         <v>-0.08609623032346503</v>
@@ -722,7 +722,7 @@
         <v>-0.01072625587287468</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.003448325447811e-08</v>
+        <v>-0.03003448325447811</v>
       </c>
       <c r="D7" t="n">
         <v>-0.01150245487945256</v>
@@ -765,7 +765,7 @@
         <v>0.00977785731502423</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.423953364236955e-09</v>
+        <v>-0.005423953364236955</v>
       </c>
       <c r="D8" t="n">
         <v>-0.02776840419061655</v>
@@ -808,7 +808,7 @@
         <v>0.0006800432941356238</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.187027285764575e-08</v>
+        <v>-0.01187027285764575</v>
       </c>
       <c r="D9" t="n">
         <v>-0.01921698343885891</v>
@@ -851,7 +851,7 @@
         <v>0.08240233734436475</v>
       </c>
       <c r="C10" t="n">
-        <v>4.792415916542181e-08</v>
+        <v>0.04792415916542159</v>
       </c>
       <c r="D10" t="n">
         <v>-0.0008777921183718007</v>
@@ -894,7 +894,7 @@
         <v>-0.005088794248391038</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.033027652902853e-08</v>
+        <v>-0.03033027652902864</v>
       </c>
       <c r="D11" t="n">
         <v>-0.06094810504278536</v>
@@ -937,7 +937,7 @@
         <v>-0.01360584095772477</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.060849962991753e-08</v>
+        <v>-0.04060849962991753</v>
       </c>
       <c r="D12" t="n">
         <v>-0.04253235129099697</v>
@@ -980,7 +980,7 @@
         <v>0.008125877859907593</v>
       </c>
       <c r="C13" t="n">
-        <v>-3.662422956330791e-09</v>
+        <v>-0.00366242295633068</v>
       </c>
       <c r="D13" t="n">
         <v>0.02354873067353758</v>
@@ -1023,7 +1023,7 @@
         <v>0.02142066006510213</v>
       </c>
       <c r="C14" t="n">
-        <v>5.929072030741334e-08</v>
+        <v>0.05929072030741334</v>
       </c>
       <c r="D14" t="n">
         <v>0.01638493926864748</v>
@@ -1066,7 +1066,7 @@
         <v>0.3050052641219847</v>
       </c>
       <c r="C15" t="n">
-        <v>3.186834718580623e-07</v>
+        <v>0.3186834718580622</v>
       </c>
       <c r="D15" t="n">
         <v>0.1895223333141141</v>
@@ -1109,7 +1109,7 @@
         <v>0.09250301821468021</v>
       </c>
       <c r="C16" t="n">
-        <v>5.780137009605757e-08</v>
+        <v>0.05780137009605757</v>
       </c>
       <c r="D16" t="n">
         <v>0.09187967725337676</v>
@@ -1152,7 +1152,7 @@
         <v>-0.04263083338861806</v>
       </c>
       <c r="C17" t="n">
-        <v>4.066338975223815e-08</v>
+        <v>0.04066338975223815</v>
       </c>
       <c r="D17" t="n">
         <v>0.002592341756559202</v>
@@ -1195,7 +1195,7 @@
         <v>-0.01064984194902796</v>
       </c>
       <c r="C18" t="n">
-        <v>2.292775407560077e-08</v>
+        <v>0.02292775407560077</v>
       </c>
       <c r="D18" t="n">
         <v>0.01054652305300863</v>
@@ -1238,7 +1238,7 @@
         <v>-0.03654769213362397</v>
       </c>
       <c r="C19" t="n">
-        <v>4.733203438172185e-09</v>
+        <v>0.004733203438172184</v>
       </c>
       <c r="D19" t="n">
         <v>-0.07066991477090612</v>
@@ -1281,7 +1281,7 @@
         <v>-0.09559638688035743</v>
       </c>
       <c r="C20" t="n">
-        <v>-4.640193663211834e-08</v>
+        <v>-0.04640193663211833</v>
       </c>
       <c r="D20" t="n">
         <v>-0.07309561930818209</v>
@@ -1324,7 +1324,7 @@
         <v>-0.09179837823231274</v>
       </c>
       <c r="C21" t="n">
-        <v>-4.149301352783407e-08</v>
+        <v>-0.04149301352783419</v>
       </c>
       <c r="D21" t="n">
         <v>-0.06331011031501144</v>
@@ -1367,7 +1367,7 @@
         <v>-0.04531838793117737</v>
       </c>
       <c r="C22" t="n">
-        <v>1.193620392825334e-10</v>
+        <v>0.0001193620392825334</v>
       </c>
       <c r="D22" t="n">
         <v>0.006249686943978094</v>
@@ -1410,7 +1410,7 @@
         <v>-0.001812776148229833</v>
       </c>
       <c r="C23" t="n">
-        <v>6.140167106671335e-08</v>
+        <v>0.06140167106671335</v>
       </c>
       <c r="D23" t="n">
         <v>0.04868788484384634</v>
@@ -1453,7 +1453,7 @@
         <v>0.0003069113043918659</v>
       </c>
       <c r="C24" t="n">
-        <v>6.478041885750852e-08</v>
+        <v>0.06478041885750851</v>
       </c>
       <c r="D24" t="n">
         <v>0.04272761934656444</v>
@@ -1496,7 +1496,7 @@
         <v>-0.0432226680298482</v>
       </c>
       <c r="C25" t="n">
-        <v>6.131158441793349e-10</v>
+        <v>0.0006131158441791129</v>
       </c>
       <c r="D25" t="n">
         <v>0.003655624507340693</v>
@@ -1539,7 +1539,7 @@
         <v>-0.03116176491001976</v>
       </c>
       <c r="C26" t="n">
-        <v>-4.885856534412536e-09</v>
+        <v>-0.004885856534412314</v>
       </c>
       <c r="D26" t="n">
         <v>-0.001786018141027523</v>
@@ -1582,7 +1582,7 @@
         <v>-0.09795857328607882</v>
       </c>
       <c r="C27" t="n">
-        <v>-6.019117593464318e-08</v>
+        <v>-0.06019117593464307</v>
       </c>
       <c r="D27" t="n">
         <v>-0.03642002806588807</v>
@@ -1625,7 +1625,7 @@
         <v>-0.007561651690826787</v>
       </c>
       <c r="C28" t="n">
-        <v>7.643659941757753e-09</v>
+        <v>0.007643659941757974</v>
       </c>
       <c r="D28" t="n">
         <v>-0.001300385202684606</v>
@@ -1668,7 +1668,7 @@
         <v>-0.0572285373040673</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.165872275791548e-08</v>
+        <v>-0.03165872275791559</v>
       </c>
       <c r="D29" t="n">
         <v>-0.009793700806175365</v>
@@ -1711,7 +1711,7 @@
         <v>-0.06022044237851465</v>
       </c>
       <c r="C30" t="n">
-        <v>-2.30176928418494e-08</v>
+        <v>-0.02301769284184929</v>
       </c>
       <c r="D30" t="n">
         <v>-0.01189816484847495</v>
@@ -1754,7 +1754,7 @@
         <v>-0.113887309809152</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.580239567177538e-08</v>
+        <v>-0.07580239567177538</v>
       </c>
       <c r="D31" t="n">
         <v>0.009744807105642739</v>
@@ -1797,7 +1797,7 @@
         <v>-0.05035096196250322</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.693394770197787e-08</v>
+        <v>-0.01693394770197787</v>
       </c>
       <c r="D32" t="n">
         <v>0.008322335605747799</v>
@@ -1840,7 +1840,7 @@
         <v>-0.04593883543070443</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.989540963936609e-08</v>
+        <v>-0.01989540963936631</v>
       </c>
       <c r="D33" t="n">
         <v>0.02596714375496334</v>
@@ -1883,7 +1883,7 @@
         <v>-0.103468347643029</v>
       </c>
       <c r="C34" t="n">
-        <v>-6.913116175105183e-08</v>
+        <v>-0.06913116175105172</v>
       </c>
       <c r="D34" t="n">
         <v>-0.07808310309707645</v>
@@ -1926,7 +1926,7 @@
         <v>-0.0463598937019073</v>
       </c>
       <c r="C35" t="n">
-        <v>-2.767754523463184e-08</v>
+        <v>-0.02767754523463173</v>
       </c>
       <c r="D35" t="n">
         <v>-0.04942717628094351</v>
@@ -1969,7 +1969,7 @@
         <v>-0.07368041525382085</v>
       </c>
       <c r="C36" t="n">
-        <v>-5.742712013994978e-08</v>
+        <v>-0.05742712013994966</v>
       </c>
       <c r="D36" t="n">
         <v>-0.05384286848409436</v>
@@ -2012,7 +2012,7 @@
         <v>-0.05452911255385229</v>
       </c>
       <c r="C37" t="n">
-        <v>-2.387584097782125e-08</v>
+        <v>-0.02387584097782114</v>
       </c>
       <c r="D37" t="n">
         <v>0.01297939992277497</v>
@@ -2055,7 +2055,7 @@
         <v>-0.06443979738749195</v>
       </c>
       <c r="C38" t="n">
-        <v>-4.714917419355391e-08</v>
+        <v>-0.04714917419355391</v>
       </c>
       <c r="D38" t="n">
         <v>-0.03210746885871929</v>
@@ -2098,7 +2098,7 @@
         <v>0.06967505649970418</v>
       </c>
       <c r="C39" t="n">
-        <v>7.317747267312624e-08</v>
+        <v>0.07317747267312624</v>
       </c>
       <c r="D39" t="n">
         <v>0.09217562127172174</v>
@@ -2141,7 +2141,7 @@
         <v>0.05410420226358736</v>
       </c>
       <c r="C40" t="n">
-        <v>7.895886771980809e-08</v>
+        <v>0.07895886771980809</v>
       </c>
       <c r="D40" t="n">
         <v>0.121080752724475</v>
@@ -2184,7 +2184,7 @@
         <v>0.05476351554569603</v>
       </c>
       <c r="C41" t="n">
-        <v>4.777762930496121e-08</v>
+        <v>0.04777762930496121</v>
       </c>
       <c r="D41" t="n">
         <v>0.07468806064258549</v>
@@ -2227,7 +2227,7 @@
         <v>-0.005736351883284807</v>
       </c>
       <c r="C42" t="n">
-        <v>1.333051292257448e-08</v>
+        <v>0.01333051292257448</v>
       </c>
       <c r="D42" t="n">
         <v>0.06160192177917256</v>
@@ -2270,7 +2270,7 @@
         <v>0.07461663123077145</v>
       </c>
       <c r="C43" t="n">
-        <v>9.524792671642369e-08</v>
+        <v>0.09524792671642368</v>
       </c>
       <c r="D43" t="n">
         <v>0.07626805039141882</v>
@@ -2313,7 +2313,7 @@
         <v>0.0513503868917593</v>
       </c>
       <c r="C44" t="n">
-        <v>6.685091373230434e-08</v>
+        <v>0.06685091373230434</v>
       </c>
       <c r="D44" t="n">
         <v>0.06606036290333028</v>
@@ -2356,7 +2356,7 @@
         <v>0.07912327707954248</v>
       </c>
       <c r="C45" t="n">
-        <v>9.164325959552189e-08</v>
+        <v>0.09164325959552211</v>
       </c>
       <c r="D45" t="n">
         <v>0.05167644457031173</v>
@@ -2399,7 +2399,7 @@
         <v>0.06391221526109159</v>
       </c>
       <c r="C46" t="n">
-        <v>7.610533841541622e-08</v>
+        <v>0.07610533841541622</v>
       </c>
       <c r="D46" t="n">
         <v>0.09864722433250317</v>
@@ -2442,7 +2442,7 @@
         <v>0.01854505197708156</v>
       </c>
       <c r="C47" t="n">
-        <v>2.702122547908936e-08</v>
+        <v>0.02702122547908936</v>
       </c>
       <c r="D47" t="n">
         <v>0.04490065236863727</v>
@@ -2485,7 +2485,7 @@
         <v>0.08897850681038899</v>
       </c>
       <c r="C48" t="n">
-        <v>1.015002123162896e-07</v>
+        <v>0.1015002123162896</v>
       </c>
       <c r="D48" t="n">
         <v>0.06304256747518933</v>
@@ -2528,7 +2528,7 @@
         <v>0.08593802953054008</v>
       </c>
       <c r="C49" t="n">
-        <v>9.126135359424481e-08</v>
+        <v>0.09126135359424481</v>
       </c>
       <c r="D49" t="n">
         <v>0.01017341874661604</v>
@@ -2571,7 +2571,7 @@
         <v>0.06919151852058092</v>
       </c>
       <c r="C50" t="n">
-        <v>5.12324066122507e-08</v>
+        <v>0.05123240661225048</v>
       </c>
       <c r="D50" t="n">
         <v>0.05696332959231087</v>
@@ -2614,7 +2614,7 @@
         <v>-0.04569387920802059</v>
       </c>
       <c r="C51" t="n">
-        <v>-4.599050128757598e-08</v>
+        <v>-0.04599050128757587</v>
       </c>
       <c r="D51" t="n">
         <v>-0.04420578325011526</v>
@@ -2657,7 +2657,7 @@
         <v>-0.007752103878618133</v>
       </c>
       <c r="C52" t="n">
-        <v>-4.759670776575775e-08</v>
+        <v>-0.04759670776575753</v>
       </c>
       <c r="D52" t="n">
         <v>-0.0636885712757993</v>
@@ -2700,7 +2700,7 @@
         <v>-0.01715018083734154</v>
       </c>
       <c r="C53" t="n">
-        <v>-2.239849848333475e-09</v>
+        <v>-0.002239849848333364</v>
       </c>
       <c r="D53" t="n">
         <v>-0.0497801353444135</v>
@@ -2743,7 +2743,7 @@
         <v>0.05642807065958011</v>
       </c>
       <c r="C54" t="n">
-        <v>2.967282938413218e-08</v>
+        <v>0.02967282938413218</v>
       </c>
       <c r="D54" t="n">
         <v>-0.03426270406881116</v>
@@ -2786,7 +2786,7 @@
         <v>0.05019149478502305</v>
       </c>
       <c r="C55" t="n">
-        <v>1.879201689619125e-08</v>
+        <v>0.01879201689619125</v>
       </c>
       <c r="D55" t="n">
         <v>-0.01597560382754437</v>
@@ -2829,7 +2829,7 @@
         <v>0.07028296975146153</v>
       </c>
       <c r="C56" t="n">
-        <v>2.775791089354818e-08</v>
+        <v>0.02775791089354818</v>
       </c>
       <c r="D56" t="n">
         <v>0.01166221548134105</v>
@@ -2872,7 +2872,7 @@
         <v>0.03815437399116117</v>
       </c>
       <c r="C57" t="n">
-        <v>7.580186173425707e-09</v>
+        <v>0.007580186173425485</v>
       </c>
       <c r="D57" t="n">
         <v>-0.005079878835415497</v>
@@ -2915,7 +2915,7 @@
         <v>0.04757658055244818</v>
       </c>
       <c r="C58" t="n">
-        <v>1.439612157056591e-08</v>
+        <v>0.01439612157056569</v>
       </c>
       <c r="D58" t="n">
         <v>-0.003783902472771272</v>
@@ -2958,7 +2958,7 @@
         <v>0.04826108784789596</v>
       </c>
       <c r="C59" t="n">
-        <v>2.878723071323219e-08</v>
+        <v>0.02878723071323219</v>
       </c>
       <c r="D59" t="n">
         <v>0.0172807672638231</v>
@@ -3001,7 +3001,7 @@
         <v>0.01230203803209662</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.537815745437043e-08</v>
+        <v>-0.01537815745437043</v>
       </c>
       <c r="D60" t="n">
         <v>0.005618673032467658</v>
@@ -3044,7 +3044,7 @@
         <v>0.0312737285104876</v>
       </c>
       <c r="C61" t="n">
-        <v>-4.511475028776357e-09</v>
+        <v>-0.004511475028776357</v>
       </c>
       <c r="D61" t="n">
         <v>0.01201103456145058</v>
@@ -3087,7 +3087,7 @@
         <v>0.04145582300331419</v>
       </c>
       <c r="C62" t="n">
-        <v>3.09485034572643e-09</v>
+        <v>0.00309485034572643</v>
       </c>
       <c r="D62" t="n">
         <v>0.01350906694164045</v>
@@ -3130,7 +3130,7 @@
         <v>0.1433875242306482</v>
       </c>
       <c r="C63" t="n">
-        <v>1.03360199365198e-07</v>
+        <v>0.1033601993651978</v>
       </c>
       <c r="D63" t="n">
         <v>0.0467511280200732</v>
@@ -3173,7 +3173,7 @@
         <v>0.04273608088184955</v>
       </c>
       <c r="C64" t="n">
-        <v>2.252455250776331e-08</v>
+        <v>0.02252455250776308</v>
       </c>
       <c r="D64" t="n">
         <v>0.008215994901124235</v>
@@ -3216,7 +3216,7 @@
         <v>0.03275473572003285</v>
       </c>
       <c r="C65" t="n">
-        <v>1.704477537002336e-08</v>
+        <v>0.01704477537002314</v>
       </c>
       <c r="D65" t="n">
         <v>0.03280998199901664</v>
@@ -3259,7 +3259,7 @@
         <v>0.03858906129386508</v>
       </c>
       <c r="C66" t="n">
-        <v>3.82959789311863e-08</v>
+        <v>0.0382959789311863</v>
       </c>
       <c r="D66" t="n">
         <v>0.01286567192921462</v>
@@ -3302,7 +3302,7 @@
         <v>0.05934571728489013</v>
       </c>
       <c r="C67" t="n">
-        <v>4.107792653221898e-08</v>
+        <v>0.04107792653221898</v>
       </c>
       <c r="D67" t="n">
         <v>0.02545573176680516</v>
@@ -3345,7 +3345,7 @@
         <v>0.00639109929685544</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.32375266194718e-09</v>
+        <v>-0.00732375266194718</v>
       </c>
       <c r="D68" t="n">
         <v>-0.01892295976600478</v>
@@ -3388,7 +3388,7 @@
         <v>0.01433069604564907</v>
       </c>
       <c r="C69" t="n">
-        <v>1.125418316354088e-08</v>
+        <v>0.01125418316354088</v>
       </c>
       <c r="D69" t="n">
         <v>-0.0171885270721337</v>
@@ -3431,7 +3431,7 @@
         <v>0.01576344632730997</v>
       </c>
       <c r="C70" t="n">
-        <v>1.153667968167982e-08</v>
+        <v>0.01153667968167982</v>
       </c>
       <c r="D70" t="n">
         <v>-0.04055959404796405</v>
@@ -3474,7 +3474,7 @@
         <v>-0.01679039515064407</v>
       </c>
       <c r="C71" t="n">
-        <v>-3.674542622317012e-08</v>
+        <v>-0.03674542622317012</v>
       </c>
       <c r="D71" t="n">
         <v>-0.04729275973090707</v>
@@ -3517,7 +3517,7 @@
         <v>-0.01389754019249045</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.420144717333628e-08</v>
+        <v>-0.02420144717333617</v>
       </c>
       <c r="D72" t="n">
         <v>-0.06959092382949639</v>
@@ -3560,7 +3560,7 @@
         <v>-0.02843881335463994</v>
       </c>
       <c r="C73" t="n">
-        <v>-5.058352381140041e-08</v>
+        <v>-0.05058352381140052</v>
       </c>
       <c r="D73" t="n">
         <v>-0.05903623414602144</v>
@@ -3603,7 +3603,7 @@
         <v>-0.01380814097202465</v>
       </c>
       <c r="C74" t="n">
-        <v>-5.159421332644853e-08</v>
+        <v>-0.05159421332644842</v>
       </c>
       <c r="D74" t="n">
         <v>-0.0441190605003402</v>
@@ -3646,7 +3646,7 @@
         <v>-0.0489232143653251</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.687984714614516e-08</v>
+        <v>-0.07687984714614504</v>
       </c>
       <c r="D75" t="n">
         <v>-0.04628946299703884</v>
@@ -3689,7 +3689,7 @@
         <v>0.003111789848805557</v>
       </c>
       <c r="C76" t="n">
-        <v>2.158495714987607e-08</v>
+        <v>0.02158495714987607</v>
       </c>
       <c r="D76" t="n">
         <v>-0.006055545550082253</v>
@@ -3732,7 +3732,7 @@
         <v>0.06176113655933668</v>
       </c>
       <c r="C77" t="n">
-        <v>1.332229021478848e-08</v>
+        <v>0.01332229021478848</v>
       </c>
       <c r="D77" t="n">
         <v>0.01264672773202924</v>
@@ -3775,7 +3775,7 @@
         <v>-0.01449182209278377</v>
       </c>
       <c r="C78" t="n">
-        <v>-2.494980134405522e-08</v>
+        <v>-0.02494980134405522</v>
       </c>
       <c r="D78" t="n">
         <v>-0.01622944807369964</v>
@@ -3818,7 +3818,7 @@
         <v>-0.04717241995209009</v>
       </c>
       <c r="C79" t="n">
-        <v>-5.896910317957504e-08</v>
+        <v>-0.05896910317957493</v>
       </c>
       <c r="D79" t="n">
         <v>-0.07180526080578908</v>
@@ -3861,7 +3861,7 @@
         <v>-0.006245675354644153</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.614375882897146e-08</v>
+        <v>-0.01614375882897146</v>
       </c>
       <c r="D80" t="n">
         <v>-0.03633010574542572</v>
@@ -3904,7 +3904,7 @@
         <v>-0.008750814884429969</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.845831606714177e-08</v>
+        <v>-0.01845831606714166</v>
       </c>
       <c r="D81" t="n">
         <v>-0.02833444540908103</v>
@@ -3947,7 +3947,7 @@
         <v>0.0482335659690567</v>
       </c>
       <c r="C82" t="n">
-        <v>3.414472210323582e-08</v>
+        <v>0.03414472210323583</v>
       </c>
       <c r="D82" t="n">
         <v>0.005079058090834865</v>
@@ -3990,7 +3990,7 @@
         <v>0.04821903583741638</v>
       </c>
       <c r="C83" t="n">
-        <v>4.867794542908266e-08</v>
+        <v>0.04867794542908266</v>
       </c>
       <c r="D83" t="n">
         <v>-0.004164349218704233</v>
@@ -4033,7 +4033,7 @@
         <v>0.03662444052073854</v>
       </c>
       <c r="C84" t="n">
-        <v>2.933698265351947e-08</v>
+        <v>0.02933698265351925</v>
       </c>
       <c r="D84" t="n">
         <v>0.02125846439191981</v>
@@ -4076,7 +4076,7 @@
         <v>0.02280795247697198</v>
       </c>
       <c r="C85" t="n">
-        <v>3.314292916577921e-09</v>
+        <v>0.003314292916577921</v>
       </c>
       <c r="D85" t="n">
         <v>-0.008513173577745059</v>
@@ -4119,7 +4119,7 @@
         <v>0.0228027778910842</v>
       </c>
       <c r="C86" t="n">
-        <v>1.439288344599774e-07</v>
+        <v>0.1439288344599772</v>
       </c>
       <c r="D86" t="n">
         <v>-0.00443368049161863</v>
@@ -4162,7 +4162,7 @@
         <v>-0.01247529193302566</v>
       </c>
       <c r="C87" t="n">
-        <v>3.839807107466786e-08</v>
+        <v>0.03839807107466786</v>
       </c>
       <c r="D87" t="n">
         <v>-0.03344300033442704</v>
@@ -4205,7 +4205,7 @@
         <v>-0.03044016390062387</v>
       </c>
       <c r="C88" t="n">
-        <v>-4.768755963951576e-08</v>
+        <v>-0.04768755963951576</v>
       </c>
       <c r="D88" t="n">
         <v>-0.04817259829236065</v>
@@ -4248,7 +4248,7 @@
         <v>-0.0140766312563998</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.320564981053268e-09</v>
+        <v>-0.008320564981053158</v>
       </c>
       <c r="D89" t="n">
         <v>-0.04982729628682281</v>
@@ -4291,7 +4291,7 @@
         <v>-0.005070210288793731</v>
       </c>
       <c r="C90" t="n">
-        <v>-3.552172454329416e-08</v>
+        <v>-0.03552172454329416</v>
       </c>
       <c r="D90" t="n">
         <v>-0.0260732695660959</v>
@@ -4334,7 +4334,7 @@
         <v>-0.02379304191495302</v>
       </c>
       <c r="C91" t="n">
-        <v>-1.20176052440002e-09</v>
+        <v>-0.00120176052440002</v>
       </c>
       <c r="D91" t="n">
         <v>-0.01868495056988106</v>
@@ -4377,7 +4377,7 @@
         <v>-0.01915198805927909</v>
       </c>
       <c r="C92" t="n">
-        <v>-2.782062763923343e-09</v>
+        <v>-0.002782062763923454</v>
       </c>
       <c r="D92" t="n">
         <v>-0.02414521061576802</v>
@@ -4420,7 +4420,7 @@
         <v>-0.03679332463321705</v>
       </c>
       <c r="C93" t="n">
-        <v>-2.691824492001293e-08</v>
+        <v>-0.02691824492001305</v>
       </c>
       <c r="D93" t="n">
         <v>-0.03370942005762634</v>
@@ -4463,7 +4463,7 @@
         <v>-0.0644643494016619</v>
       </c>
       <c r="C94" t="n">
-        <v>-8.344148187897161e-08</v>
+        <v>-0.08344148187897149</v>
       </c>
       <c r="D94" t="n">
         <v>-0.04139666442692613</v>
@@ -4506,7 +4506,7 @@
         <v>-0.04221755789513371</v>
       </c>
       <c r="C95" t="n">
-        <v>-5.369553597123899e-08</v>
+        <v>-0.05369553597123911</v>
       </c>
       <c r="D95" t="n">
         <v>-0.0132031258632348</v>
@@ -4549,7 +4549,7 @@
         <v>-0.03159904673123726</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.829384637128883e-08</v>
+        <v>-0.01829384637128861</v>
       </c>
       <c r="D96" t="n">
         <v>-0.03480527844743986</v>
@@ -4592,7 +4592,7 @@
         <v>-0.02616494059232977</v>
       </c>
       <c r="C97" t="n">
-        <v>1.039268349979092e-07</v>
+        <v>0.1039268349979094</v>
       </c>
       <c r="D97" t="n">
         <v>-0.03690584617753112</v>
@@ -4635,7 +4635,7 @@
         <v>-0.01800693674157539</v>
       </c>
       <c r="C98" t="n">
-        <v>1.414515059271881e-08</v>
+        <v>0.01414515059271881</v>
       </c>
       <c r="D98" t="n">
         <v>-0.02523776373152942</v>
@@ -4678,7 +4678,7 @@
         <v>0.02103950846025615</v>
       </c>
       <c r="C99" t="n">
-        <v>3.088861109458119e-08</v>
+        <v>0.03088861109458119</v>
       </c>
       <c r="D99" t="n">
         <v>0.000611291399214009</v>
@@ -4721,7 +4721,7 @@
         <v>0.01031768438745528</v>
       </c>
       <c r="C100" t="n">
-        <v>4.180532897020561e-08</v>
+        <v>0.04180532897020561</v>
       </c>
       <c r="D100" t="n">
         <v>-0.001255691670250303</v>
@@ -4764,7 +4764,7 @@
         <v>-0.01378609163355082</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.661710271477323e-08</v>
+        <v>-0.01661710271477312</v>
       </c>
       <c r="D101" t="n">
         <v>-0.01989933987517223</v>
@@ -4807,7 +4807,7 @@
         <v>-0.004617014516962503</v>
       </c>
       <c r="C102" t="n">
-        <v>3.617098800325702e-08</v>
+        <v>0.03617098800325702</v>
       </c>
       <c r="D102" t="n">
         <v>-0.0238724013859053</v>
@@ -4850,7 +4850,7 @@
         <v>0.02638951388967681</v>
       </c>
       <c r="C103" t="n">
-        <v>4.538846330880131e-08</v>
+        <v>0.04538846330880131</v>
       </c>
       <c r="D103" t="n">
         <v>-0.0076454246157317</v>
@@ -4893,7 +4893,7 @@
         <v>0.0424583860747918</v>
       </c>
       <c r="C104" t="n">
-        <v>7.669000171891737e-08</v>
+        <v>0.07669000171891738</v>
       </c>
       <c r="D104" t="n">
         <v>0.01205429173177297</v>
@@ -4936,7 +4936,7 @@
         <v>0.04626207456999842</v>
       </c>
       <c r="C105" t="n">
-        <v>5.333564026405901e-08</v>
+        <v>0.05333564026405901</v>
       </c>
       <c r="D105" t="n">
         <v>0.02819459332646113</v>
@@ -4979,7 +4979,7 @@
         <v>0.04441317870454231</v>
       </c>
       <c r="C106" t="n">
-        <v>8.22571748540184e-08</v>
+        <v>0.0822571748540184</v>
       </c>
       <c r="D106" t="n">
         <v>0.04776982217714654</v>
@@ -5022,7 +5022,7 @@
         <v>0.0758745294293075</v>
       </c>
       <c r="C107" t="n">
-        <v>1.302897989008336e-07</v>
+        <v>0.1302897989008336</v>
       </c>
       <c r="D107" t="n">
         <v>0.04098668347672563</v>
@@ -5065,7 +5065,7 @@
         <v>0.06676790237802765</v>
       </c>
       <c r="C108" t="n">
-        <v>6.070003939976453e-08</v>
+        <v>0.06070003939976432</v>
       </c>
       <c r="D108" t="n">
         <v>0.05111618799587347</v>
@@ -5108,7 +5108,7 @@
         <v>-0.03501606612731356</v>
       </c>
       <c r="C109" t="n">
-        <v>-2.424863703965863e-08</v>
+        <v>-0.02424863703965863</v>
       </c>
       <c r="D109" t="n">
         <v>-0.0385404045683394</v>
@@ -5151,7 +5151,7 @@
         <v>-0.02908171637944201</v>
       </c>
       <c r="C110" t="n">
-        <v>-4.356695049772863e-08</v>
+        <v>-0.04356695049772852</v>
       </c>
       <c r="D110" t="n">
         <v>-0.02784144443563674</v>
@@ -5194,7 +5194,7 @@
         <v>0.03962576868127154</v>
       </c>
       <c r="C111" t="n">
-        <v>4.652696131883993e-08</v>
+        <v>0.04652696131883971</v>
       </c>
       <c r="D111" t="n">
         <v>0.03217351225189624</v>
@@ -5237,7 +5237,7 @@
         <v>0.06499415498188532</v>
       </c>
       <c r="C112" t="n">
-        <v>6.56349562320595e-08</v>
+        <v>0.0656349562320595</v>
       </c>
       <c r="D112" t="n">
         <v>0.0750795481378117</v>
@@ -5280,7 +5280,7 @@
         <v>0.05536070844120267</v>
       </c>
       <c r="C113" t="n">
-        <v>1.091790567679578e-07</v>
+        <v>0.1091790567679578</v>
       </c>
       <c r="D113" t="n">
         <v>0.08215577804360819</v>
@@ -5323,7 +5323,7 @@
         <v>0.07123971436492416</v>
       </c>
       <c r="C114" t="n">
-        <v>7.811741444507381e-08</v>
+        <v>0.07811741444507381</v>
       </c>
       <c r="D114" t="n">
         <v>0.1068368944616918</v>
@@ -5366,7 +5366,7 @@
         <v>0.06914609921474035</v>
       </c>
       <c r="C115" t="n">
-        <v>6.550647328872449e-08</v>
+        <v>0.0655064732887245</v>
       </c>
       <c r="D115" t="n">
         <v>0.1285773323529276</v>
@@ -5409,7 +5409,7 @@
         <v>0.01412431708194339</v>
       </c>
       <c r="C116" t="n">
-        <v>7.701959463753738e-09</v>
+        <v>0.007701959463753738</v>
       </c>
       <c r="D116" t="n">
         <v>0.0731251426268027</v>
@@ -5452,7 +5452,7 @@
         <v>-0.001334916194190128</v>
       </c>
       <c r="C117" t="n">
-        <v>6.029834919858201e-09</v>
+        <v>0.006029834919857979</v>
       </c>
       <c r="D117" t="n">
         <v>0.02760587136484771</v>
@@ -5495,7 +5495,7 @@
         <v>0.01605790432531995</v>
       </c>
       <c r="C118" t="n">
-        <v>5.616480965633163e-09</v>
+        <v>0.005616480965633164</v>
       </c>
       <c r="D118" t="n">
         <v>0.03236479560634775</v>
@@ -5538,7 +5538,7 @@
         <v>0.0002486174958054033</v>
       </c>
       <c r="C119" t="n">
-        <v>-2.738537359662963e-08</v>
+        <v>-0.02738537359662963</v>
       </c>
       <c r="D119" t="n">
         <v>0.03957046363911942</v>
@@ -5581,7 +5581,7 @@
         <v>-0.007336395215860048</v>
       </c>
       <c r="C120" t="n">
-        <v>4.09745914707238e-09</v>
+        <v>0.004097459147072602</v>
       </c>
       <c r="D120" t="n">
         <v>0.05623537978247084</v>
@@ -5624,7 +5624,7 @@
         <v>0.0740420472704979</v>
       </c>
       <c r="C121" t="n">
-        <v>3.126587092685051e-08</v>
+        <v>0.03126587092685051</v>
       </c>
       <c r="D121" t="n">
         <v>0.1198084075145711</v>
@@ -5667,7 +5667,7 @@
         <v>0.06978751872334499</v>
       </c>
       <c r="C122" t="n">
-        <v>5.558402730370493e-08</v>
+        <v>0.05558402730370471</v>
       </c>
       <c r="D122" t="n">
         <v>0.0997614528520947</v>
@@ -5710,7 +5710,7 @@
         <v>-0.04030055230549567</v>
       </c>
       <c r="C123" t="n">
-        <v>-4.149284372079387e-08</v>
+        <v>-0.04149284372079387</v>
       </c>
       <c r="D123" t="n">
         <v>0.0276978294436514</v>
@@ -5753,7 +5753,7 @@
         <v>-0.01957370288276628</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.293885828774721e-08</v>
+        <v>-0.01293885828774721</v>
       </c>
       <c r="D124" t="n">
         <v>-0.04048454897881237</v>
@@ -5796,7 +5796,7 @@
         <v>-0.02357840083562435</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.949198292364252e-08</v>
+        <v>-0.01949198292364251</v>
       </c>
       <c r="D125" t="n">
         <v>-0.05717436180233093</v>
@@ -5839,7 +5839,7 @@
         <v>-0.05132198643160768</v>
       </c>
       <c r="C126" t="n">
-        <v>-4.657556519689044e-08</v>
+        <v>-0.04657556519689043</v>
       </c>
       <c r="D126" t="n">
         <v>-0.07672029172410511</v>
@@ -5882,7 +5882,7 @@
         <v>-0.04560466957907472</v>
       </c>
       <c r="C127" t="n">
-        <v>-2.549834046155974e-08</v>
+        <v>-0.02549834046155985</v>
       </c>
       <c r="D127" t="n">
         <v>-0.09954512775922586</v>
@@ -5925,7 +5925,7 @@
         <v>-0.02637317529330596</v>
       </c>
       <c r="C128" t="n">
-        <v>-1.625008943992867e-09</v>
+        <v>-0.001625008943992867</v>
       </c>
       <c r="D128" t="n">
         <v>-0.07524736295634049</v>
@@ -5968,7 +5968,7 @@
         <v>0.01493723178567286</v>
       </c>
       <c r="C129" t="n">
-        <v>2.914576282039105e-08</v>
+        <v>0.02914576282039105</v>
       </c>
       <c r="D129" t="n">
         <v>-0.0337019044764274</v>
@@ -6011,7 +6011,7 @@
         <v>-0.3211260084380412</v>
       </c>
       <c r="C130" t="n">
-        <v>-2.565157988197248e-07</v>
+        <v>-0.2565157988197249</v>
       </c>
       <c r="D130" t="n">
         <v>-0.2376242285390279</v>
@@ -6054,7 +6054,7 @@
         <v>-0.2979367111357416</v>
       </c>
       <c r="C131" t="n">
-        <v>-2.385575109277954e-07</v>
+        <v>-0.2385575109277954</v>
       </c>
       <c r="D131" t="n">
         <v>-0.2450161810218342</v>
@@ -6097,7 +6097,7 @@
         <v>-0.2652529921983906</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.709875367166298e-07</v>
+        <v>-0.1709875367166299</v>
       </c>
       <c r="D132" t="n">
         <v>-0.2281237548467879</v>
@@ -6140,7 +6140,7 @@
         <v>-0.163288712590307</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.258164934311191e-07</v>
+        <v>-0.1258164934311191</v>
       </c>
       <c r="D133" t="n">
         <v>-0.1625349928669745</v>
@@ -6183,7 +6183,7 @@
         <v>-0.1606181569250243</v>
       </c>
       <c r="C134" t="n">
-        <v>-1.176720116367297e-07</v>
+        <v>-0.1176720116367297</v>
       </c>
       <c r="D134" t="n">
         <v>-0.1497776793513668</v>
@@ -6226,7 +6226,7 @@
         <v>-0.08043000788744059</v>
       </c>
       <c r="C135" t="n">
-        <v>-4.04757061337021e-08</v>
+        <v>-0.04047570613370199</v>
       </c>
       <c r="D135" t="n">
         <v>-0.1067955925886961</v>
@@ -6269,7 +6269,7 @@
         <v>-0.09756207549320783</v>
       </c>
       <c r="C136" t="n">
-        <v>-5.835673559820776e-08</v>
+        <v>-0.05835673559820775</v>
       </c>
       <c r="D136" t="n">
         <v>-0.07449273169386161</v>
@@ -6312,7 +6312,7 @@
         <v>-0.09440852523947929</v>
       </c>
       <c r="C137" t="n">
-        <v>-9.153220920096273e-08</v>
+        <v>-0.09153220920096272</v>
       </c>
       <c r="D137" t="n">
         <v>-0.05647275379597505</v>
@@ -6355,7 +6355,7 @@
         <v>-0.02925241201437456</v>
       </c>
       <c r="C138" t="n">
-        <v>1.190575215746925e-08</v>
+        <v>0.01190575215746925</v>
       </c>
       <c r="D138" t="n">
         <v>-0.02312090818987766</v>
@@ -6398,7 +6398,7 @@
         <v>-0.009086286746829764</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.049386225006394e-11</v>
+        <v>-8.049386225017496e-05</v>
       </c>
       <c r="D139" t="n">
         <v>0.002647749967994217</v>
@@ -6441,7 +6441,7 @@
         <v>-0.05289190342390859</v>
       </c>
       <c r="C140" t="n">
-        <v>-2.690306903047934e-08</v>
+        <v>-0.02690306903047923</v>
       </c>
       <c r="D140" t="n">
         <v>-0.02486813569589807</v>
@@ -6484,7 +6484,7 @@
         <v>-0.04770926965302213</v>
       </c>
       <c r="C141" t="n">
-        <v>8.301820634488033e-09</v>
+        <v>0.008301820634488255</v>
       </c>
       <c r="D141" t="n">
         <v>-0.01004233211537309</v>
@@ -6527,7 +6527,7 @@
         <v>0.3016131711873009</v>
       </c>
       <c r="C142" t="n">
-        <v>3.917053468602678e-07</v>
+        <v>0.3917053468602678</v>
       </c>
       <c r="D142" t="n">
         <v>0.1555090722367229</v>
@@ -6570,7 +6570,7 @@
         <v>0.3135068080887156</v>
       </c>
       <c r="C143" t="n">
-        <v>3.109770965982719e-07</v>
+        <v>0.3109770965982719</v>
       </c>
       <c r="D143" t="n">
         <v>0.208737713936997</v>
@@ -6613,7 +6613,7 @@
         <v>0.2643281906218475</v>
       </c>
       <c r="C144" t="n">
-        <v>2.270115551395635e-07</v>
+        <v>0.2270115551395633</v>
       </c>
       <c r="D144" t="n">
         <v>0.1597189618426085</v>
@@ -6656,7 +6656,7 @@
         <v>0.1528767999722598</v>
       </c>
       <c r="C145" t="n">
-        <v>1.352633805387151e-07</v>
+        <v>0.1352633805387153</v>
       </c>
       <c r="D145" t="n">
         <v>0.1493538442592246</v>
@@ -6699,7 +6699,7 @@
         <v>0.1174718154184673</v>
       </c>
       <c r="C146" t="n">
-        <v>6.048379792005699e-08</v>
+        <v>0.0604837979200572</v>
       </c>
       <c r="D146" t="n">
         <v>0.09312137274185606</v>
@@ -6742,7 +6742,7 @@
         <v>0.005073849879098313</v>
       </c>
       <c r="C147" t="n">
-        <v>-3.752293474912349e-10</v>
+        <v>-0.000375229347491346</v>
       </c>
       <c r="D147" t="n">
         <v>0.03303251744698232</v>
@@ -6785,7 +6785,7 @@
         <v>-0.008974814015424104</v>
       </c>
       <c r="C148" t="n">
-        <v>-3.41228207942702e-08</v>
+        <v>-0.03412282079427031</v>
       </c>
       <c r="D148" t="n">
         <v>0.02064439223716308</v>
@@ -6828,7 +6828,7 @@
         <v>-0.02983634348907205</v>
       </c>
       <c r="C149" t="n">
-        <v>3.667869656925004e-08</v>
+        <v>0.03667869656924982</v>
       </c>
       <c r="D149" t="n">
         <v>0.02525818846052719</v>
@@ -6871,7 +6871,7 @@
         <v>-0.07488167445562122</v>
       </c>
       <c r="C150" t="n">
-        <v>-4.88769387256881e-08</v>
+        <v>-0.0488769387256881</v>
       </c>
       <c r="D150" t="n">
         <v>-0.01908265837392842</v>
@@ -6914,7 +6914,7 @@
         <v>-0.07608653597156712</v>
       </c>
       <c r="C151" t="n">
-        <v>-5.562242703890352e-08</v>
+        <v>-0.05562242703890352</v>
       </c>
       <c r="D151" t="n">
         <v>-0.02322739465162538</v>
@@ -6957,7 +6957,7 @@
         <v>0.003513401855108178</v>
       </c>
       <c r="C152" t="n">
-        <v>-4.042351088964669e-09</v>
+        <v>-0.004042351088964558</v>
       </c>
       <c r="D152" t="n">
         <v>0.04469245126102406</v>
@@ -7000,7 +7000,7 @@
         <v>0.01492872359551001</v>
       </c>
       <c r="C153" t="n">
-        <v>-6.951342290008267e-09</v>
+        <v>-0.006951342290008156</v>
       </c>
       <c r="D153" t="n">
         <v>0.06078267356546641</v>
@@ -7043,7 +7043,7 @@
         <v>0.02712264724930513</v>
       </c>
       <c r="C154" t="n">
-        <v>-8.773653637340917e-08</v>
+        <v>-0.08773653637340928</v>
       </c>
       <c r="D154" t="n">
         <v>0.07801214109110344</v>
@@ -7086,7 +7086,7 @@
         <v>-0.003749719127072337</v>
       </c>
       <c r="C155" t="n">
-        <v>-3.927633201968595e-08</v>
+        <v>-0.03927633201968583</v>
       </c>
       <c r="D155" t="n">
         <v>0.03639219731231469</v>
@@ -7129,7 +7129,7 @@
         <v>0.01565593404197729</v>
       </c>
       <c r="C156" t="n">
-        <v>-4.693970428817384e-08</v>
+        <v>-0.04693970428817384</v>
       </c>
       <c r="D156" t="n">
         <v>0.04943323825180768</v>
@@ -7172,7 +7172,7 @@
         <v>0.02444381889983505</v>
       </c>
       <c r="C157" t="n">
-        <v>-8.87495549905426e-09</v>
+        <v>-0.008874955499054371</v>
       </c>
       <c r="D157" t="n">
         <v>0.08068033764190274</v>
@@ -7215,7 +7215,7 @@
         <v>0.001692178166633473</v>
       </c>
       <c r="C158" t="n">
-        <v>2.462254925445406e-08</v>
+        <v>0.02462254925445406</v>
       </c>
       <c r="D158" t="n">
         <v>0.07125304189870896</v>
@@ -7258,7 +7258,7 @@
         <v>0.07983270788494723</v>
       </c>
       <c r="C159" t="n">
-        <v>7.120620369416275e-08</v>
+        <v>0.07120620369416297</v>
       </c>
       <c r="D159" t="n">
         <v>0.07747162842630306</v>
@@ -7301,7 +7301,7 @@
         <v>0.07065338931225584</v>
       </c>
       <c r="C160" t="n">
-        <v>7.085371325592771e-08</v>
+        <v>0.07085371325592771</v>
       </c>
       <c r="D160" t="n">
         <v>0.1017509864099093</v>
@@ -7344,7 +7344,7 @@
         <v>0.1372206589458198</v>
       </c>
       <c r="C161" t="n">
-        <v>8.035797104149744e-08</v>
+        <v>0.08035797104149767</v>
       </c>
       <c r="D161" t="n">
         <v>0.1128245627821238</v>
@@ -7387,7 +7387,7 @@
         <v>0.1571317758438826</v>
       </c>
       <c r="C162" t="n">
-        <v>1.05538806289821e-07</v>
+        <v>0.1055388062898208</v>
       </c>
       <c r="D162" t="n">
         <v>0.1230942350575253</v>
@@ -7430,7 +7430,7 @@
         <v>0.1226499358420212</v>
       </c>
       <c r="C163" t="n">
-        <v>8.329550227842674e-08</v>
+        <v>0.08329550227842697</v>
       </c>
       <c r="D163" t="n">
         <v>0.1293968760041335</v>
@@ -7473,7 +7473,7 @@
         <v>0.1041417237101241</v>
       </c>
       <c r="C164" t="n">
-        <v>6.991994092160869e-08</v>
+        <v>0.06991994092160869</v>
       </c>
       <c r="D164" t="n">
         <v>0.08570257624191013</v>
@@ -7516,7 +7516,7 @@
         <v>0.03437222310497168</v>
       </c>
       <c r="C165" t="n">
-        <v>1.123831927127728e-08</v>
+        <v>0.01123831927127728</v>
       </c>
       <c r="D165" t="n">
         <v>0.01943724853967677</v>
@@ -7559,7 +7559,7 @@
         <v>0.1021212339476347</v>
       </c>
       <c r="C166" t="n">
-        <v>1.147989569360854e-07</v>
+        <v>0.1147989569360854</v>
       </c>
       <c r="D166" t="n">
         <v>0.06387024416775744</v>
@@ -7602,7 +7602,7 @@
         <v>0.1035079960663401</v>
       </c>
       <c r="C167" t="n">
-        <v>8.270022372578101e-08</v>
+        <v>0.08270022372578079</v>
       </c>
       <c r="D167" t="n">
         <v>0.06605049130828755</v>
@@ -7645,7 +7645,7 @@
         <v>0.05391510092157215</v>
       </c>
       <c r="C168" t="n">
-        <v>6.34096140342415e-08</v>
+        <v>0.0634096140342415</v>
       </c>
       <c r="D168" t="n">
         <v>0.0393923409435224</v>
@@ -7688,7 +7688,7 @@
         <v>0.05175738078806558</v>
       </c>
       <c r="C169" t="n">
-        <v>5.627817430364468e-08</v>
+        <v>0.05627817430364468</v>
       </c>
       <c r="D169" t="n">
         <v>-0.0222413364993469</v>
@@ -7731,7 +7731,7 @@
         <v>0.1117714454721539</v>
       </c>
       <c r="C170" t="n">
-        <v>9.626130145517409e-08</v>
+        <v>0.09626130145517386</v>
       </c>
       <c r="D170" t="n">
         <v>0.05714778319008063</v>
@@ -7774,7 +7774,7 @@
         <v>0.06827443790013832</v>
       </c>
       <c r="C171" t="n">
-        <v>6.25102008963756e-08</v>
+        <v>0.0625102008963756</v>
       </c>
       <c r="D171" t="n">
         <v>0.03858991040824455</v>
@@ -7817,7 +7817,7 @@
         <v>0.1095948538294929</v>
       </c>
       <c r="C172" t="n">
-        <v>1.449907583694159e-07</v>
+        <v>0.1449907583694159</v>
       </c>
       <c r="D172" t="n">
         <v>0.05551702200287689</v>
@@ -7860,7 +7860,7 @@
         <v>0.03631902308073376</v>
       </c>
       <c r="C173" t="n">
-        <v>1.085901866780881e-08</v>
+        <v>0.01085901866780881</v>
       </c>
       <c r="D173" t="n">
         <v>0.01332933527129132</v>
@@ -7903,7 +7903,7 @@
         <v>0.0525303615786008</v>
       </c>
       <c r="C174" t="n">
-        <v>4.066235554000119e-08</v>
+        <v>0.04066235554000119</v>
       </c>
       <c r="D174" t="n">
         <v>0.05561866797054993</v>
@@ -7946,7 +7946,7 @@
         <v>0.07255001689963736</v>
       </c>
       <c r="C175" t="n">
-        <v>8.172664128279084e-08</v>
+        <v>0.08172664128279084</v>
       </c>
       <c r="D175" t="n">
         <v>0.03141492139115321</v>
@@ -7989,7 +7989,7 @@
         <v>0.08020760708113217</v>
       </c>
       <c r="C176" t="n">
-        <v>9.65454924506155e-08</v>
+        <v>0.09654549245061528</v>
       </c>
       <c r="D176" t="n">
         <v>0.02711826052307931</v>
@@ -8032,7 +8032,7 @@
         <v>0.08034493344905269</v>
       </c>
       <c r="C177" t="n">
-        <v>9.890633707253871e-08</v>
+        <v>0.09890633707253871</v>
       </c>
       <c r="D177" t="n">
         <v>0.03268581619251854</v>
@@ -8075,7 +8075,7 @@
         <v>0.0724485310672609</v>
       </c>
       <c r="C178" t="n">
-        <v>6.628862177904571e-08</v>
+        <v>0.06628862177904593</v>
       </c>
       <c r="D178" t="n">
         <v>0.04614084429571941</v>
@@ -8118,7 +8118,7 @@
         <v>0.05902564658347798</v>
       </c>
       <c r="C179" t="n">
-        <v>9.002582102395728e-08</v>
+        <v>0.09002582102395729</v>
       </c>
       <c r="D179" t="n">
         <v>0.03156309010414526</v>
@@ -8161,7 +8161,7 @@
         <v>0.06354347675797589</v>
       </c>
       <c r="C180" t="n">
-        <v>6.84185676842206e-08</v>
+        <v>0.06841856768422061</v>
       </c>
       <c r="D180" t="n">
         <v>0.04978813204319343</v>
@@ -8204,7 +8204,7 @@
         <v>0.05911247618623894</v>
       </c>
       <c r="C181" t="n">
-        <v>5.568287126152294e-08</v>
+        <v>0.05568287126152294</v>
       </c>
       <c r="D181" t="n">
         <v>0.06776189101923524</v>
@@ -8247,7 +8247,7 @@
         <v>0.04811157355155959</v>
       </c>
       <c r="C182" t="n">
-        <v>4.88260330876924e-08</v>
+        <v>0.04882603308769262</v>
       </c>
       <c r="D182" t="n">
         <v>0.008926992659982202</v>
@@ -8290,7 +8290,7 @@
         <v>0.02334741225555192</v>
       </c>
       <c r="C183" t="n">
-        <v>4.759249475307969e-08</v>
+        <v>0.04759249475307969</v>
       </c>
       <c r="D183" t="n">
         <v>0.01648502992151935</v>
@@ -8333,7 +8333,7 @@
         <v>0.001403954578198752</v>
       </c>
       <c r="C184" t="n">
-        <v>4.171511286559904e-09</v>
+        <v>0.004171511286560126</v>
       </c>
       <c r="D184" t="n">
         <v>-0.01607618578744641</v>
@@ -8376,7 +8376,7 @@
         <v>0.05721346539842154</v>
       </c>
       <c r="C185" t="n">
-        <v>6.790196429193185e-08</v>
+        <v>0.06790196429193163</v>
       </c>
       <c r="D185" t="n">
         <v>0.01984228284700706</v>
@@ -8419,7 +8419,7 @@
         <v>0.01002036466409284</v>
       </c>
       <c r="C186" t="n">
-        <v>3.514821813878611e-08</v>
+        <v>0.0351482181387861</v>
       </c>
       <c r="D186" t="n">
         <v>-0.01493585626273553</v>
@@ -8462,7 +8462,7 @@
         <v>0.0247316719568611</v>
       </c>
       <c r="C187" t="n">
-        <v>2.536184563893929e-08</v>
+        <v>0.02536184563893951</v>
       </c>
       <c r="D187" t="n">
         <v>-0.009858782684233236</v>
@@ -8505,7 +8505,7 @@
         <v>-0.006755032933864147</v>
       </c>
       <c r="C188" t="n">
-        <v>-7.034907144295777e-09</v>
+        <v>-0.007034907144295777</v>
       </c>
       <c r="D188" t="n">
         <v>-0.01472972730514777</v>
@@ -8548,7 +8548,7 @@
         <v>0.001608238080834212</v>
       </c>
       <c r="C189" t="n">
-        <v>-6.602695701804496e-09</v>
+        <v>-0.006602695701804606</v>
       </c>
       <c r="D189" t="n">
         <v>-0.02148707790844151</v>
@@ -8591,7 +8591,7 @@
         <v>0.009039912413623785</v>
       </c>
       <c r="C190" t="n">
-        <v>3.709965956193373e-08</v>
+        <v>0.03709965956193373</v>
       </c>
       <c r="D190" t="n">
         <v>-0.03383764652969745</v>
@@ -8634,7 +8634,7 @@
         <v>-0.02486288999066355</v>
       </c>
       <c r="C191" t="n">
-        <v>-2.041426292909243e-08</v>
+        <v>-0.02041426292909232</v>
       </c>
       <c r="D191" t="n">
         <v>-0.05334040875715973</v>
@@ -8677,7 +8677,7 @@
         <v>0.02858340341849042</v>
       </c>
       <c r="C192" t="n">
-        <v>3.293184164758056e-08</v>
+        <v>0.03293184164758056</v>
       </c>
       <c r="D192" t="n">
         <v>-0.02611337828558613</v>
@@ -8720,7 +8720,7 @@
         <v>0.0274174299127985</v>
       </c>
       <c r="C193" t="n">
-        <v>1.663008304598312e-08</v>
+        <v>0.01663008304598312</v>
       </c>
       <c r="D193" t="n">
         <v>-0.05950078647924617</v>
@@ -8763,7 +8763,7 @@
         <v>-0.04620531710128961</v>
       </c>
       <c r="C194" t="n">
-        <v>-4.468282422925796e-08</v>
+        <v>-0.04468282422925796</v>
       </c>
       <c r="D194" t="n">
         <v>-0.07839306331812967</v>
@@ -8806,7 +8806,7 @@
         <v>-0.01878797153402578</v>
       </c>
       <c r="C195" t="n">
-        <v>-2.31134516851913e-08</v>
+        <v>-0.02311345168519141</v>
       </c>
       <c r="D195" t="n">
         <v>-0.08193828609917064</v>
@@ -8849,7 +8849,7 @@
         <v>0.04110029532286386</v>
       </c>
       <c r="C196" t="n">
-        <v>-1.004349432469465e-08</v>
+        <v>-0.01004349432469476</v>
       </c>
       <c r="D196" t="n">
         <v>-0.05385643727194278</v>
@@ -8892,7 +8892,7 @@
         <v>-0.0155428946423416</v>
       </c>
       <c r="C197" t="n">
-        <v>4.51966298383446e-08</v>
+        <v>0.0451966298383446</v>
       </c>
       <c r="D197" t="n">
         <v>-0.07804618815174746</v>
@@ -8935,7 +8935,7 @@
         <v>0.002877952353288471</v>
       </c>
       <c r="C198" t="n">
-        <v>1.046877753687081e-08</v>
+        <v>0.01046877753687081</v>
       </c>
       <c r="D198" t="n">
         <v>-0.08252312546330798</v>
@@ -8978,7 +8978,7 @@
         <v>-0.003558176829783544</v>
       </c>
       <c r="C199" t="n">
-        <v>8.236704575432573e-09</v>
+        <v>0.008236704575432574</v>
       </c>
       <c r="D199" t="n">
         <v>-0.06362407216148325</v>
@@ -9021,7 +9021,7 @@
         <v>-0.02253988260949014</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.844044918377197e-08</v>
+        <v>-0.01844044918377197</v>
       </c>
       <c r="D200" t="n">
         <v>-0.06196112417757693</v>
@@ -9064,7 +9064,7 @@
         <v>0.05233296209100602</v>
       </c>
       <c r="C201" t="n">
-        <v>5.120477082152797e-08</v>
+        <v>0.05120477082152819</v>
       </c>
       <c r="D201" t="n">
         <v>-0.03412964255087703</v>
@@ -9107,7 +9107,7 @@
         <v>-0.003926171257286226</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.659150562034706e-08</v>
+        <v>-0.01659150562034706</v>
       </c>
       <c r="D202" t="n">
         <v>-0.03854813750418706</v>
@@ -9150,7 +9150,7 @@
         <v>-0.00728143803247816</v>
       </c>
       <c r="C203" t="n">
-        <v>-1.944138940801587e-09</v>
+        <v>-0.001944138940801698</v>
       </c>
       <c r="D203" t="n">
         <v>-0.02726758152673436</v>
@@ -9193,7 +9193,7 @@
         <v>-0.007509611437269359</v>
       </c>
       <c r="C204" t="n">
-        <v>-1.039446827677271e-08</v>
+        <v>-0.01039446827677282</v>
       </c>
       <c r="D204" t="n">
         <v>-0.03889558548897765</v>
@@ -9236,7 +9236,7 @@
         <v>-0.02094323937936493</v>
       </c>
       <c r="C205" t="n">
-        <v>2.041685951640448e-08</v>
+        <v>0.02041685951640448</v>
       </c>
       <c r="D205" t="n">
         <v>-0.02536389404720585</v>
@@ -9279,7 +9279,7 @@
         <v>0.01246948526709835</v>
       </c>
       <c r="C206" t="n">
-        <v>2.408341972851624e-08</v>
+        <v>0.02408341972851624</v>
       </c>
       <c r="D206" t="n">
         <v>0.01851432529216535</v>
@@ -9322,7 +9322,7 @@
         <v>0.03002176970737613</v>
       </c>
       <c r="C207" t="n">
-        <v>2.927480190973664e-08</v>
+        <v>0.02927480190973686</v>
       </c>
       <c r="D207" t="n">
         <v>0.02998281813554038</v>
@@ -9365,7 +9365,7 @@
         <v>-0.06082686830440542</v>
       </c>
       <c r="C208" t="n">
-        <v>1.74180463676632e-09</v>
+        <v>0.00174180463676632</v>
       </c>
       <c r="D208" t="n">
         <v>-0.009469203466134113</v>
@@ -9408,7 +9408,7 @@
         <v>-0.06811880830654959</v>
       </c>
       <c r="C209" t="n">
-        <v>-1.160786919335504e-07</v>
+        <v>-0.1160786919335502</v>
       </c>
       <c r="D209" t="n">
         <v>-0.02560710767360697</v>
@@ -9451,7 +9451,7 @@
         <v>-0.0680672049307165</v>
       </c>
       <c r="C210" t="n">
-        <v>-7.389258890952321e-08</v>
+        <v>-0.07389258890952322</v>
       </c>
       <c r="D210" t="n">
         <v>-0.01766981957113922</v>
@@ -9494,7 +9494,7 @@
         <v>-0.1323409256319059</v>
       </c>
       <c r="C211" t="n">
-        <v>-1.079073021856527e-07</v>
+        <v>-0.1079073021856526</v>
       </c>
       <c r="D211" t="n">
         <v>-0.08058309631555927</v>
@@ -9537,7 +9537,7 @@
         <v>-0.1339330699421756</v>
       </c>
       <c r="C212" t="n">
-        <v>-1.140657736934125e-07</v>
+        <v>-0.1140657736934124</v>
       </c>
       <c r="D212" t="n">
         <v>-0.0797504383412555</v>
@@ -9580,7 +9580,7 @@
         <v>-0.1689712351865271</v>
       </c>
       <c r="C213" t="n">
-        <v>-1.47456732843727e-07</v>
+        <v>-0.1474567328437271</v>
       </c>
       <c r="D213" t="n">
         <v>-0.07923859572226777</v>
@@ -9623,7 +9623,7 @@
         <v>-0.1906959767142196</v>
       </c>
       <c r="C214" t="n">
-        <v>-1.501543711390292e-07</v>
+        <v>-0.1501543711390293</v>
       </c>
       <c r="D214" t="n">
         <v>-0.1528790867287751</v>
@@ -9666,7 +9666,7 @@
         <v>-0.1285413523995804</v>
       </c>
       <c r="C215" t="n">
-        <v>-1.056363595195786e-07</v>
+        <v>-0.1056363595195786</v>
       </c>
       <c r="D215" t="n">
         <v>-0.09144317523615664</v>
@@ -9709,7 +9709,7 @@
         <v>-0.1548985676614889</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.170131427828616e-07</v>
+        <v>-0.1170131427828616</v>
       </c>
       <c r="D216" t="n">
         <v>-0.1157927040279122</v>
@@ -9752,7 +9752,7 @@
         <v>-0.1685900324730294</v>
       </c>
       <c r="C217" t="n">
-        <v>-1.549385927279598e-07</v>
+        <v>-0.1549385927279598</v>
       </c>
       <c r="D217" t="n">
         <v>-0.1363618416291017</v>
@@ -9795,7 +9795,7 @@
         <v>-0.1298393744155487</v>
       </c>
       <c r="C218" t="n">
-        <v>-1.150170932982409e-07</v>
+        <v>-0.1150170932982408</v>
       </c>
       <c r="D218" t="n">
         <v>-0.165837270643708</v>
@@ -9838,7 +9838,7 @@
         <v>-0.1366611359196844</v>
       </c>
       <c r="C219" t="n">
-        <v>-1.39176089124798e-07</v>
+        <v>-0.139176089124798</v>
       </c>
       <c r="D219" t="n">
         <v>-0.1385969577451233</v>
@@ -9881,7 +9881,7 @@
         <v>-0.1437666613127794</v>
       </c>
       <c r="C220" t="n">
-        <v>-1.713213709797221e-07</v>
+        <v>-0.1713213709797221</v>
       </c>
       <c r="D220" t="n">
         <v>-0.1505031371326965</v>
@@ -9924,7 +9924,7 @@
         <v>-0.05607629423935312</v>
       </c>
       <c r="C221" t="n">
-        <v>-1.08850491595156e-08</v>
+        <v>-0.0108850491595156</v>
       </c>
       <c r="D221" t="n">
         <v>-0.09462734230216641</v>
@@ -9967,7 +9967,7 @@
         <v>-0.0674273283244925</v>
       </c>
       <c r="C222" t="n">
-        <v>-5.886925890515782e-08</v>
+        <v>-0.05886925890515793</v>
       </c>
       <c r="D222" t="n">
         <v>-0.109076845788136</v>
@@ -10010,7 +10010,7 @@
         <v>-0.05004057134176887</v>
       </c>
       <c r="C223" t="n">
-        <v>-2.739716381698809e-08</v>
+        <v>-0.0273971638169882</v>
       </c>
       <c r="D223" t="n">
         <v>-0.09634135738945682</v>
@@ -10053,7 +10053,7 @@
         <v>0.01238303773556049</v>
       </c>
       <c r="C224" t="n">
-        <v>1.08404841009635e-08</v>
+        <v>0.0108404841009635</v>
       </c>
       <c r="D224" t="n">
         <v>-0.07462783611814106</v>
@@ -10096,7 +10096,7 @@
         <v>0.007393279041932876</v>
       </c>
       <c r="C225" t="n">
-        <v>-5.758008782836943e-09</v>
+        <v>-0.005758008782836832</v>
       </c>
       <c r="D225" t="n">
         <v>-0.06245220890424819</v>
@@ -10139,7 +10139,7 @@
         <v>0.07281628239529692</v>
       </c>
       <c r="C226" t="n">
-        <v>3.639767664879412e-08</v>
+        <v>0.03639767664879434</v>
       </c>
       <c r="D226" t="n">
         <v>0.0101367080309247</v>
@@ -10182,7 +10182,7 @@
         <v>-0.004205937915913172</v>
       </c>
       <c r="C227" t="n">
-        <v>-2.688160855645494e-08</v>
+        <v>-0.02688160855645483</v>
       </c>
       <c r="D227" t="n">
         <v>-0.01413414194396667</v>
@@ -10225,7 +10225,7 @@
         <v>-0.01616194191503662</v>
       </c>
       <c r="C228" t="n">
-        <v>-2.359563993691216e-08</v>
+        <v>-0.02359563993691216</v>
       </c>
       <c r="D228" t="n">
         <v>-0.0314536663580085</v>
@@ -10268,7 +10268,7 @@
         <v>0.03320304464339241</v>
       </c>
       <c r="C229" t="n">
-        <v>2.476194368747242e-08</v>
+        <v>0.02476194368747242</v>
       </c>
       <c r="D229" t="n">
         <v>0.02607487980993461</v>
@@ -10311,7 +10311,7 @@
         <v>0.0158548805361618</v>
       </c>
       <c r="C230" t="n">
-        <v>1.927317472215462e-08</v>
+        <v>0.0192731747221544</v>
       </c>
       <c r="D230" t="n">
         <v>0.04396810138198037</v>
@@ -10354,7 +10354,7 @@
         <v>0.01002928379945422</v>
       </c>
       <c r="C231" t="n">
-        <v>2.368349846464746e-08</v>
+        <v>0.02368349846464746</v>
       </c>
       <c r="D231" t="n">
         <v>0.04679997686476223</v>
@@ -10397,7 +10397,7 @@
         <v>0.08176322925189972</v>
       </c>
       <c r="C232" t="n">
-        <v>9.268131211317798e-08</v>
+        <v>0.09268131211317798</v>
       </c>
       <c r="D232" t="n">
         <v>0.07804859946507348</v>
@@ -10440,7 +10440,7 @@
         <v>0.04198462363799682</v>
       </c>
       <c r="C233" t="n">
-        <v>2.069853019512458e-09</v>
+        <v>0.002069853019512458</v>
       </c>
       <c r="D233" t="n">
         <v>0.04391995346243749</v>
@@ -10483,7 +10483,7 @@
         <v>0.06532595396757124</v>
       </c>
       <c r="C234" t="n">
-        <v>8.890011059311554e-08</v>
+        <v>0.08890011059311553</v>
       </c>
       <c r="D234" t="n">
         <v>0.07538672582184103</v>
@@ -10526,7 +10526,7 @@
         <v>0.1050227507059129</v>
       </c>
       <c r="C235" t="n">
-        <v>5.793963413675462e-08</v>
+        <v>0.05793963413675463</v>
       </c>
       <c r="D235" t="n">
         <v>0.1503729996385548</v>
@@ -10569,7 +10569,7 @@
         <v>0.09740526995515331</v>
       </c>
       <c r="C236" t="n">
-        <v>1.09583139706517e-07</v>
+        <v>0.1095831397065172</v>
       </c>
       <c r="D236" t="n">
         <v>0.1547742570162507</v>
@@ -10612,7 +10612,7 @@
         <v>0.07109960158616824</v>
       </c>
       <c r="C237" t="n">
-        <v>1.037989673645838e-07</v>
+        <v>0.1037989673645838</v>
       </c>
       <c r="D237" t="n">
         <v>0.09824052958552909</v>
@@ -10655,7 +10655,7 @@
         <v>0.08562459548074774</v>
       </c>
       <c r="C238" t="n">
-        <v>9.383723484646355e-08</v>
+        <v>0.09383723484646334</v>
       </c>
       <c r="D238" t="n">
         <v>0.1076203751859086</v>
@@ -10698,7 +10698,7 @@
         <v>0.1382959439814357</v>
       </c>
       <c r="C239" t="n">
-        <v>1.45747902057852e-07</v>
+        <v>0.145747902057852</v>
       </c>
       <c r="D239" t="n">
         <v>0.07345433788965039</v>
@@ -10741,7 +10741,7 @@
         <v>0.1221347049002142</v>
       </c>
       <c r="C240" t="n">
-        <v>1.257720635420425e-07</v>
+        <v>0.1257720635420425</v>
       </c>
       <c r="D240" t="n">
         <v>0.1060976480010944</v>
@@ -10784,7 +10784,7 @@
         <v>0.09117919211185854</v>
       </c>
       <c r="C241" t="n">
-        <v>8.174008184300141e-08</v>
+        <v>0.08174008184300141</v>
       </c>
       <c r="D241" t="n">
         <v>0.1000506758041204</v>
@@ -10827,7 +10827,7 @@
         <v>0.1166625330416708</v>
       </c>
       <c r="C242" t="n">
-        <v>1.138098288262852e-07</v>
+        <v>0.1138098288262852</v>
       </c>
       <c r="D242" t="n">
         <v>0.1014177525634576</v>
@@ -10870,7 +10870,7 @@
         <v>0.1225935409865535</v>
       </c>
       <c r="C243" t="n">
-        <v>1.24453048619231e-07</v>
+        <v>0.124453048619231</v>
       </c>
       <c r="D243" t="n">
         <v>0.07812125073101028</v>
@@ -10913,7 +10913,7 @@
         <v>0.03990005044528866</v>
       </c>
       <c r="C244" t="n">
-        <v>7.191453446553787e-08</v>
+        <v>0.07191453446553786</v>
       </c>
       <c r="D244" t="n">
         <v>0.06052646459148581</v>
@@ -10956,7 +10956,7 @@
         <v>0.03850785559369396</v>
       </c>
       <c r="C245" t="n">
-        <v>7.422214939710536e-08</v>
+        <v>0.07422214939710536</v>
       </c>
       <c r="D245" t="n">
         <v>0.04814095014480779</v>
@@ -10999,7 +10999,7 @@
         <v>0.001941199755403744</v>
       </c>
       <c r="C246" t="n">
-        <v>-6.881005195007561e-09</v>
+        <v>-0.006881005195007561</v>
       </c>
       <c r="D246" t="n">
         <v>0.01821786103165723</v>
@@ -11042,7 +11042,7 @@
         <v>-0.003259899185758308</v>
       </c>
       <c r="C247" t="n">
-        <v>2.261945142372523e-08</v>
+        <v>0.02261945142372523</v>
       </c>
       <c r="D247" t="n">
         <v>-0.01613702249509386</v>
@@ -11085,7 +11085,7 @@
         <v>-0.01542230263887567</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.325908267393884e-08</v>
+        <v>-0.02325908267393884</v>
       </c>
       <c r="D248" t="n">
         <v>-0.03090282388185794</v>
@@ -11128,7 +11128,7 @@
         <v>0.0144833089292391</v>
       </c>
       <c r="C249" t="n">
-        <v>-2.355169030637039e-09</v>
+        <v>-0.00235516903063715</v>
       </c>
       <c r="D249" t="n">
         <v>0.02497926009125817</v>
@@ -11171,7 +11171,7 @@
         <v>0.04817683432839903</v>
       </c>
       <c r="C250" t="n">
-        <v>4.678615334283576e-08</v>
+        <v>0.04678615334283598</v>
       </c>
       <c r="D250" t="n">
         <v>0.06337564785684013</v>
@@ -11214,7 +11214,7 @@
         <v>0.008303809079122537</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477657197210713e-08</v>
+        <v>0.01477657197210713</v>
       </c>
       <c r="D251" t="n">
         <v>0.02659409229258847</v>
@@ -11257,7 +11257,7 @@
         <v>0.03660185791849613</v>
       </c>
       <c r="C252" t="n">
-        <v>2.985280301847459e-08</v>
+        <v>0.02985280301847459</v>
       </c>
       <c r="D252" t="n">
         <v>0.039483946110072</v>
@@ -11300,7 +11300,7 @@
         <v>0.07117710391463228</v>
       </c>
       <c r="C253" t="n">
-        <v>8.443535038248528e-08</v>
+        <v>0.08443535038248529</v>
       </c>
       <c r="D253" t="n">
         <v>0.03625809686479164</v>
@@ -11343,7 +11343,7 @@
         <v>0.07365214682268229</v>
       </c>
       <c r="C254" t="n">
-        <v>7.324055137747054e-08</v>
+        <v>0.07324055137747054</v>
       </c>
       <c r="D254" t="n">
         <v>0.05745492857886414</v>
@@ -11386,7 +11386,7 @@
         <v>0.05447688862985522</v>
       </c>
       <c r="C255" t="n">
-        <v>5.902160428961123e-08</v>
+        <v>0.05902160428961123</v>
       </c>
       <c r="D255" t="n">
         <v>0.02549896497209159</v>
@@ -11429,7 +11429,7 @@
         <v>0.1169260369515444</v>
       </c>
       <c r="C256" t="n">
-        <v>9.870546556088611e-08</v>
+        <v>0.09870546556088611</v>
       </c>
       <c r="D256" t="n">
         <v>0.05665534819237394</v>
@@ -11472,7 +11472,7 @@
         <v>0.08785099197577129</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537419444554373e-08</v>
+        <v>0.08537419444554351</v>
       </c>
       <c r="D257" t="n">
         <v>0.05102600017245051</v>
@@ -11515,7 +11515,7 @@
         <v>0.1192384274705727</v>
       </c>
       <c r="C258" t="n">
-        <v>1.174520973265138e-07</v>
+        <v>0.1174520973265136</v>
       </c>
       <c r="D258" t="n">
         <v>0.08783663898528737</v>
@@ -11558,7 +11558,7 @@
         <v>0.11446600575159</v>
       </c>
       <c r="C259" t="n">
-        <v>9.112896710121565e-08</v>
+        <v>0.09112896710121565</v>
       </c>
       <c r="D259" t="n">
         <v>0.07830446161609883</v>
@@ -11601,7 +11601,7 @@
         <v>0.0884960977265592</v>
       </c>
       <c r="C260" t="n">
-        <v>9.290597596026729e-08</v>
+        <v>0.09290597596026728</v>
       </c>
       <c r="D260" t="n">
         <v>0.08072700729430005</v>
@@ -11644,7 +11644,7 @@
         <v>0.1252766492784214</v>
       </c>
       <c r="C261" t="n">
-        <v>1.02982473989669e-07</v>
+        <v>0.102982473989669</v>
       </c>
       <c r="D261" t="n">
         <v>0.05621256225451754</v>
@@ -11687,7 +11687,7 @@
         <v>0.06800399785729572</v>
       </c>
       <c r="C262" t="n">
-        <v>6.492418147981338e-08</v>
+        <v>0.06492418147981338</v>
       </c>
       <c r="D262" t="n">
         <v>-0.008176158675285428</v>
@@ -11730,7 +11730,7 @@
         <v>0.09094094215499648</v>
       </c>
       <c r="C263" t="n">
-        <v>7.44610500934273e-08</v>
+        <v>0.07446105009342752</v>
       </c>
       <c r="D263" t="n">
         <v>0.03153466522347537</v>
@@ -11773,7 +11773,7 @@
         <v>0.1340884606913195</v>
       </c>
       <c r="C264" t="n">
-        <v>1.122644364547656e-07</v>
+        <v>0.1122644364547654</v>
       </c>
       <c r="D264" t="n">
         <v>0.04655799550792006</v>
@@ -11816,7 +11816,7 @@
         <v>0.08051810189784581</v>
       </c>
       <c r="C265" t="n">
-        <v>5.782081560706253e-08</v>
+        <v>0.05782081560706254</v>
       </c>
       <c r="D265" t="n">
         <v>0.02716916294732363</v>
@@ -11859,7 +11859,7 @@
         <v>0.02583496886206849</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.924203004195046e-09</v>
+        <v>-0.001924203004195046</v>
       </c>
       <c r="D266" t="n">
         <v>0.02193771530865063</v>
@@ -11902,7 +11902,7 @@
         <v>0.05106135023096825</v>
       </c>
       <c r="C267" t="n">
-        <v>1.665031881611179e-08</v>
+        <v>0.01665031881611179</v>
       </c>
       <c r="D267" t="n">
         <v>0.03454386275544596</v>
@@ -11945,7 +11945,7 @@
         <v>0.05822645824546679</v>
       </c>
       <c r="C268" t="n">
-        <v>3.406630501793262e-08</v>
+        <v>0.03406630501793262</v>
       </c>
       <c r="D268" t="n">
         <v>0.009105918666783674</v>
@@ -11988,7 +11988,7 @@
         <v>0.0238684106524516</v>
       </c>
       <c r="C269" t="n">
-        <v>7.189397189474089e-09</v>
+        <v>0.007189397189474089</v>
       </c>
       <c r="D269" t="n">
         <v>0.02949557564385952</v>
@@ -12031,7 +12031,7 @@
         <v>0.02700325205104259</v>
       </c>
       <c r="C270" t="n">
-        <v>3.546777387537281e-09</v>
+        <v>0.003546777387537281</v>
       </c>
       <c r="D270" t="n">
         <v>-0.01518029222767259</v>
@@ -12074,7 +12074,7 @@
         <v>0.04102823757040852</v>
       </c>
       <c r="C271" t="n">
-        <v>3.271670702470497e-08</v>
+        <v>0.03271670702470497</v>
       </c>
       <c r="D271" t="n">
         <v>-0.0117125574806336</v>
@@ -12117,7 +12117,7 @@
         <v>0.0380241093376219</v>
       </c>
       <c r="C272" t="n">
-        <v>2.824579172849906e-08</v>
+        <v>0.02824579172849906</v>
       </c>
       <c r="D272" t="n">
         <v>-0.02926481791735602</v>
@@ -12160,7 +12160,7 @@
         <v>0.02047932537386288</v>
       </c>
       <c r="C273" t="n">
-        <v>2.703547866816791e-08</v>
+        <v>0.02703547866816791</v>
       </c>
       <c r="D273" t="n">
         <v>-0.001125718736767256</v>
@@ -12203,7 +12203,7 @@
         <v>-0.0013967557059269</v>
       </c>
       <c r="C274" t="n">
-        <v>2.207406341990348e-09</v>
+        <v>0.002207406341990348</v>
       </c>
       <c r="D274" t="n">
         <v>0.0003492681109842355</v>
@@ -12246,7 +12246,7 @@
         <v>-0.003207261782844362</v>
       </c>
       <c r="C275" t="n">
-        <v>-4.72578431880899e-09</v>
+        <v>-0.004725784318809101</v>
       </c>
       <c r="D275" t="n">
         <v>-0.02022566075332288</v>
@@ -12289,7 +12289,7 @@
         <v>-0.03988745706072305</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.152270181218087e-08</v>
+        <v>-0.04152270181218076</v>
       </c>
       <c r="D276" t="n">
         <v>-0.03715190241320476</v>
@@ -12332,7 +12332,7 @@
         <v>-0.0335977939453902</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.721698083349578e-08</v>
+        <v>-0.03721698083349578</v>
       </c>
       <c r="D277" t="n">
         <v>-0.03386670997398411</v>
@@ -12375,7 +12375,7 @@
         <v>0.03267400609230675</v>
       </c>
       <c r="C278" t="n">
-        <v>3.589726468039656e-08</v>
+        <v>0.03589726468039656</v>
       </c>
       <c r="D278" t="n">
         <v>-0.0162163747555073</v>
@@ -12418,7 +12418,7 @@
         <v>-0.00118178649757128</v>
       </c>
       <c r="C279" t="n">
-        <v>4.800319367258332e-09</v>
+        <v>0.004800319367258332</v>
       </c>
       <c r="D279" t="n">
         <v>-0.003347431432068393</v>
@@ -12461,7 +12461,7 @@
         <v>-0.01843770045572424</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.143309110954994e-08</v>
+        <v>-0.02143309110954994</v>
       </c>
       <c r="D280" t="n">
         <v>-0.007994992367717169</v>
@@ -12504,7 +12504,7 @@
         <v>0.02177146027128529</v>
       </c>
       <c r="C281" t="n">
-        <v>1.841871992387278e-08</v>
+        <v>0.01841871992387278</v>
       </c>
       <c r="D281" t="n">
         <v>-0.03089934422089546</v>
@@ -12547,7 +12547,7 @@
         <v>0.0119906287137117</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625980916141145e-08</v>
+        <v>0.01625980916141145</v>
       </c>
       <c r="D282" t="n">
         <v>0.002861040679217552</v>
@@ -12590,7 +12590,7 @@
         <v>0.01116867338422756</v>
       </c>
       <c r="C283" t="n">
-        <v>5.712768615540486e-09</v>
+        <v>0.005712768615540487</v>
       </c>
       <c r="D283" t="n">
         <v>0.001498130003839471</v>
@@ -12633,7 +12633,7 @@
         <v>0.0253086624616603</v>
       </c>
       <c r="C284" t="n">
-        <v>-5.377514698984287e-10</v>
+        <v>-0.0005377514698985397</v>
       </c>
       <c r="D284" t="n">
         <v>0.02829244701264844</v>
@@ -12676,7 +12676,7 @@
         <v>0.004713074011657437</v>
       </c>
       <c r="C285" t="n">
-        <v>-7.783124821529653e-09</v>
+        <v>-0.007783124821529652</v>
       </c>
       <c r="D285" t="n">
         <v>-0.01489860113452579</v>
@@ -12719,7 +12719,7 @@
         <v>0.04658752230467544</v>
       </c>
       <c r="C286" t="n">
-        <v>1.836271241758402e-08</v>
+        <v>0.01836271241758403</v>
       </c>
       <c r="D286" t="n">
         <v>0.02953083546730495</v>
@@ -12762,7 +12762,7 @@
         <v>0.05816305571528346</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936736780516248e-08</v>
+        <v>0.03936736780516248</v>
       </c>
       <c r="D287" t="n">
         <v>0.04864381197979695</v>
@@ -12805,7 +12805,7 @@
         <v>0.03481089525225634</v>
       </c>
       <c r="C288" t="n">
-        <v>2.924721239557271e-08</v>
+        <v>0.02924721239557271</v>
       </c>
       <c r="D288" t="n">
         <v>0.02107533850769761</v>
@@ -12848,7 +12848,7 @@
         <v>0.06843333982594535</v>
       </c>
       <c r="C289" t="n">
-        <v>5.982501252917661e-08</v>
+        <v>0.0598250125291766</v>
       </c>
       <c r="D289" t="n">
         <v>0.0223260254751616</v>
@@ -12891,7 +12891,7 @@
         <v>0.008761466545507801</v>
       </c>
       <c r="C290" t="n">
-        <v>1.185217726573762e-08</v>
+        <v>0.0118521772657374</v>
       </c>
       <c r="D290" t="n">
         <v>-0.02208771855578739</v>
@@ -12934,7 +12934,7 @@
         <v>0.03298028870279213</v>
       </c>
       <c r="C291" t="n">
-        <v>3.35127496196106e-08</v>
+        <v>0.03351274961961082</v>
       </c>
       <c r="D291" t="n">
         <v>-0.01251589789513929</v>
@@ -12977,7 +12977,7 @@
         <v>0.06314907075575027</v>
       </c>
       <c r="C292" t="n">
-        <v>5.590874372075838e-08</v>
+        <v>0.05590874372075838</v>
       </c>
       <c r="D292" t="n">
         <v>0.02178769830584604</v>
@@ -13020,7 +13020,7 @@
         <v>0.03545188947865219</v>
       </c>
       <c r="C293" t="n">
-        <v>2.389758570113431e-08</v>
+        <v>0.02389758570113432</v>
       </c>
       <c r="D293" t="n">
         <v>0.02532719483097323</v>
@@ -13063,7 +13063,7 @@
         <v>0.0836924401644692</v>
       </c>
       <c r="C294" t="n">
-        <v>5.934059988893314e-08</v>
+        <v>0.05934059988893314</v>
       </c>
       <c r="D294" t="n">
         <v>0.04199954387806892</v>
@@ -13106,7 +13106,7 @@
         <v>0.06580369122344365</v>
       </c>
       <c r="C295" t="n">
-        <v>5.390703131980179e-08</v>
+        <v>0.05390703131980179</v>
       </c>
       <c r="D295" t="n">
         <v>0.06110291894376974</v>
@@ -13149,7 +13149,7 @@
         <v>0.05118680360620087</v>
       </c>
       <c r="C296" t="n">
-        <v>5.699099198300606e-08</v>
+        <v>0.05699099198300606</v>
       </c>
       <c r="D296" t="n">
         <v>0.001167878717958981</v>
@@ -13192,7 +13192,7 @@
         <v>0.03875228811278908</v>
       </c>
       <c r="C297" t="n">
-        <v>3.991269924559249e-08</v>
+        <v>0.03991269924559249</v>
       </c>
       <c r="D297" t="n">
         <v>0.02955164633677843</v>
@@ -13235,7 +13235,7 @@
         <v>0.02454716518148237</v>
       </c>
       <c r="C298" t="n">
-        <v>1.081115240720942e-08</v>
+        <v>0.0108111524072092</v>
       </c>
       <c r="D298" t="n">
         <v>0.004371781129176133</v>
@@ -13278,7 +13278,7 @@
         <v>0.03298433728859718</v>
       </c>
       <c r="C299" t="n">
-        <v>2.777044801185236e-08</v>
+        <v>0.02777044801185236</v>
       </c>
       <c r="D299" t="n">
         <v>0.01825031025128387</v>
@@ -13321,7 +13321,7 @@
         <v>0.04507386817870995</v>
       </c>
       <c r="C300" t="n">
-        <v>3.663906644519321e-08</v>
+        <v>0.03663906644519321</v>
       </c>
       <c r="D300" t="n">
         <v>0.03901322631013682</v>
@@ -13364,7 +13364,7 @@
         <v>0.04774522760947697</v>
       </c>
       <c r="C301" t="n">
-        <v>3.147561656173092e-08</v>
+        <v>0.03147561656173092</v>
       </c>
       <c r="D301" t="n">
         <v>0.05331745518014097</v>
@@ -13407,7 +13407,7 @@
         <v>0.05336380009538866</v>
       </c>
       <c r="C302" t="n">
-        <v>3.377411742877423e-08</v>
+        <v>0.03377411742877423</v>
       </c>
       <c r="D302" t="n">
         <v>0.04101074181332542</v>
@@ -13450,7 +13450,7 @@
         <v>0.05235040447155748</v>
       </c>
       <c r="C303" t="n">
-        <v>3.221353623964362e-08</v>
+        <v>0.03221353623964363</v>
       </c>
       <c r="D303" t="n">
         <v>0.01621144324312662</v>
@@ -13493,7 +13493,7 @@
         <v>0.01069391546143206</v>
       </c>
       <c r="C304" t="n">
-        <v>5.282433788493579e-09</v>
+        <v>0.005282433788493579</v>
       </c>
       <c r="D304" t="n">
         <v>-0.006741055249131711</v>
@@ -13536,7 +13536,7 @@
         <v>0.01076295803963223</v>
       </c>
       <c r="C305" t="n">
-        <v>1.589416570332958e-09</v>
+        <v>0.001589416570332736</v>
       </c>
       <c r="D305" t="n">
         <v>0.02198689027007572</v>
@@ -13579,7 +13579,7 @@
         <v>0.006425467793484962</v>
       </c>
       <c r="C306" t="n">
-        <v>4.784092237797299e-10</v>
+        <v>0.0004784092237797299</v>
       </c>
       <c r="D306" t="n">
         <v>-0.01261613960311925</v>
@@ -13622,7 +13622,7 @@
         <v>0.02179122487909946</v>
       </c>
       <c r="C307" t="n">
-        <v>1.356348012598785e-08</v>
+        <v>0.01356348012598785</v>
       </c>
       <c r="D307" t="n">
         <v>-0.02600368830965816</v>
@@ -13665,7 +13665,7 @@
         <v>0.01738037130226378</v>
       </c>
       <c r="C308" t="n">
-        <v>2.692624512282249e-09</v>
+        <v>0.002692624512282471</v>
       </c>
       <c r="D308" t="n">
         <v>0.01605709819745593</v>
@@ -13708,7 +13708,7 @@
         <v>0.0315065052806982</v>
       </c>
       <c r="C309" t="n">
-        <v>2.229988549865603e-08</v>
+        <v>0.02229988549865602</v>
       </c>
       <c r="D309" t="n">
         <v>0.005621748801291071</v>
@@ -13751,7 +13751,7 @@
         <v>0.05760639480092444</v>
       </c>
       <c r="C310" t="n">
-        <v>6.605984965448574e-08</v>
+        <v>0.06605984965448597</v>
       </c>
       <c r="D310" t="n">
         <v>0.02765365279777066</v>
@@ -13794,7 +13794,7 @@
         <v>0.0392183953272558</v>
       </c>
       <c r="C311" t="n">
-        <v>3.167353210164303e-08</v>
+        <v>0.03167353210164303</v>
       </c>
       <c r="D311" t="n">
         <v>0.006449098348123794</v>
@@ -13837,7 +13837,7 @@
         <v>0.04030672935637236</v>
       </c>
       <c r="C312" t="n">
-        <v>2.312771068015218e-08</v>
+        <v>0.02312771068015196</v>
       </c>
       <c r="D312" t="n">
         <v>-0.01061366387585427</v>
@@ -13880,7 +13880,7 @@
         <v>0.03256952397658175</v>
       </c>
       <c r="C313" t="n">
-        <v>2.328857894111613e-08</v>
+        <v>0.02328857894111613</v>
       </c>
       <c r="D313" t="n">
         <v>0.0004675393706392583</v>
@@ -13923,7 +13923,7 @@
         <v>0.04284273075992617</v>
       </c>
       <c r="C314" t="n">
-        <v>3.904035837362873e-08</v>
+        <v>0.03904035837362874</v>
       </c>
       <c r="D314" t="n">
         <v>0.01486728282430261</v>
@@ -13966,7 +13966,7 @@
         <v>0.01695417566818946</v>
       </c>
       <c r="C315" t="n">
-        <v>2.794702492713119e-08</v>
+        <v>0.02794702492713141</v>
       </c>
       <c r="D315" t="n">
         <v>0.009317167916605751</v>
@@ -14009,7 +14009,7 @@
         <v>0.02667460736765204</v>
       </c>
       <c r="C316" t="n">
-        <v>2.932911382026648e-08</v>
+        <v>0.02932911382026671</v>
       </c>
       <c r="D316" t="n">
         <v>0.003985254669233163</v>
@@ -14052,7 +14052,7 @@
         <v>0.08786087073308191</v>
       </c>
       <c r="C317" t="n">
-        <v>9.064674858859423e-08</v>
+        <v>0.09064674858859445</v>
       </c>
       <c r="D317" t="n">
         <v>0.00387501551756908</v>
@@ -14095,7 +14095,7 @@
         <v>0.04393080703505214</v>
       </c>
       <c r="C318" t="n">
-        <v>5.428876992000032e-08</v>
+        <v>0.05428876992000031</v>
       </c>
       <c r="D318" t="n">
         <v>0.02155649256478576</v>
@@ -14138,7 +14138,7 @@
         <v>0.04180576220044174</v>
       </c>
       <c r="C319" t="n">
-        <v>3.362364189456657e-08</v>
+        <v>0.03362364189456635</v>
       </c>
       <c r="D319" t="n">
         <v>0.02726818385755503</v>
@@ -14181,7 +14181,7 @@
         <v>0.06696785105276204</v>
       </c>
       <c r="C320" t="n">
-        <v>6.734312555106525e-08</v>
+        <v>0.06734312555106525</v>
       </c>
       <c r="D320" t="n">
         <v>0.02221111410746235</v>
@@ -14224,7 +14224,7 @@
         <v>0.05938480459757534</v>
       </c>
       <c r="C321" t="n">
-        <v>4.638316396427e-08</v>
+        <v>0.04638316396427</v>
       </c>
       <c r="D321" t="n">
         <v>0.01457379056003649</v>
@@ -14267,7 +14267,7 @@
         <v>0.05567042878888717</v>
       </c>
       <c r="C322" t="n">
-        <v>3.517921613197572e-08</v>
+        <v>0.03517921613197572</v>
       </c>
       <c r="D322" t="n">
         <v>0.0005306793799160214</v>
@@ -14310,7 +14310,7 @@
         <v>0.04357806509517181</v>
       </c>
       <c r="C323" t="n">
-        <v>5.143917803260556e-08</v>
+        <v>0.05143917803260534</v>
       </c>
       <c r="D323" t="n">
         <v>0.008422528722962896</v>
@@ -14353,7 +14353,7 @@
         <v>0.07531085086948486</v>
       </c>
       <c r="C324" t="n">
-        <v>6.857079026611123e-08</v>
+        <v>0.06857079026611124</v>
       </c>
       <c r="D324" t="n">
         <v>0.03827018156259188</v>
@@ -14396,7 +14396,7 @@
         <v>0.06088998948339919</v>
       </c>
       <c r="C325" t="n">
-        <v>5.483179174550989e-08</v>
+        <v>0.05483179174550989</v>
       </c>
       <c r="D325" t="n">
         <v>0.001554156349438118</v>
@@ -14439,7 +14439,7 @@
         <v>0.05855143370621407</v>
       </c>
       <c r="C326" t="n">
-        <v>5.01156289993041e-08</v>
+        <v>0.05011562899930411</v>
       </c>
       <c r="D326" t="n">
         <v>0.007945457523386157</v>
@@ -14482,7 +14482,7 @@
         <v>0.09917462619523709</v>
       </c>
       <c r="C327" t="n">
-        <v>9.494403871826451e-08</v>
+        <v>0.09494403871826451</v>
       </c>
       <c r="D327" t="n">
         <v>0.02694518187304729</v>
@@ -14525,7 +14525,7 @@
         <v>0.1041945739232606</v>
       </c>
       <c r="C328" t="n">
-        <v>9.144565002825389e-08</v>
+        <v>0.09144565002825411</v>
       </c>
       <c r="D328" t="n">
         <v>0.03150291537392014</v>
@@ -14568,7 +14568,7 @@
         <v>0.04000070077434925</v>
       </c>
       <c r="C329" t="n">
-        <v>3.086214975340961e-08</v>
+        <v>0.03086214975340962</v>
       </c>
       <c r="D329" t="n">
         <v>0.02842464902553576</v>
@@ -14611,7 +14611,7 @@
         <v>0.06295765901860073</v>
       </c>
       <c r="C330" t="n">
-        <v>5.629002415840168e-08</v>
+        <v>0.05629002415840167</v>
       </c>
       <c r="D330" t="n">
         <v>0.01317507669097662</v>
@@ -14654,7 +14654,7 @@
         <v>0.05954587173771553</v>
       </c>
       <c r="C331" t="n">
-        <v>7.414486981490342e-08</v>
+        <v>0.07414486981490342</v>
       </c>
       <c r="D331" t="n">
         <v>-0.01078216469543902</v>
@@ -14697,7 +14697,7 @@
         <v>0.04173061339683226</v>
       </c>
       <c r="C332" t="n">
-        <v>3.974569170531495e-08</v>
+        <v>0.03974569170531494</v>
       </c>
       <c r="D332" t="n">
         <v>-0.0162738837456452</v>
@@ -14740,7 +14740,7 @@
         <v>0.0383663930201219</v>
       </c>
       <c r="C333" t="n">
-        <v>3.745083874855903e-08</v>
+        <v>0.03745083874855926</v>
       </c>
       <c r="D333" t="n">
         <v>-0.03156114157040391</v>
@@ -14783,7 +14783,7 @@
         <v>0.02929350137982034</v>
       </c>
       <c r="C334" t="n">
-        <v>4.881230093075905e-08</v>
+        <v>0.04881230093075928</v>
       </c>
       <c r="D334" t="n">
         <v>-0.01617719829323117</v>
@@ -14826,7 +14826,7 @@
         <v>0.03734027008490792</v>
       </c>
       <c r="C335" t="n">
-        <v>1.694221529529982e-08</v>
+        <v>0.01694221529529982</v>
       </c>
       <c r="D335" t="n">
         <v>-0.02581536718973865</v>
@@ -14869,7 +14869,7 @@
         <v>0.03722559718300422</v>
       </c>
       <c r="C336" t="n">
-        <v>3.655399016192296e-08</v>
+        <v>0.03655399016192296</v>
       </c>
       <c r="D336" t="n">
         <v>-0.03337600238135141</v>
@@ -14912,7 +14912,7 @@
         <v>0.02009657186433711</v>
       </c>
       <c r="C337" t="n">
-        <v>1.177394468593107e-08</v>
+        <v>0.01177394468593107</v>
       </c>
       <c r="D337" t="n">
         <v>-0.031415298688663</v>
@@ -14955,7 +14955,7 @@
         <v>0.0329378619107501</v>
       </c>
       <c r="C338" t="n">
-        <v>2.205230130594282e-08</v>
+        <v>0.02205230130594305</v>
       </c>
       <c r="D338" t="n">
         <v>-0.0236268761464844</v>
@@ -14998,7 +14998,7 @@
         <v>0.006754604595028413</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.812370272725283e-08</v>
+        <v>-0.01812370272725283</v>
       </c>
       <c r="D339" t="n">
         <v>-0.02147175121416189</v>
@@ -15041,7 +15041,7 @@
         <v>0.03608718603085159</v>
       </c>
       <c r="C340" t="n">
-        <v>6.104598874596467e-09</v>
+        <v>0.006104598874596467</v>
       </c>
       <c r="D340" t="n">
         <v>-0.02717902758988677</v>
@@ -15084,7 +15084,7 @@
         <v>0.04786722032880442</v>
       </c>
       <c r="C341" t="n">
-        <v>1.377554566792671e-08</v>
+        <v>0.01377554566792694</v>
       </c>
       <c r="D341" t="n">
         <v>-0.0304898844296887</v>
@@ -15127,7 +15127,7 @@
         <v>0.05707966553002475</v>
       </c>
       <c r="C342" t="n">
-        <v>2.861031361499267e-08</v>
+        <v>0.02861031361499267</v>
       </c>
       <c r="D342" t="n">
         <v>-0.007315978393046985</v>
@@ -15170,7 +15170,7 @@
         <v>0.05796758007875713</v>
       </c>
       <c r="C343" t="n">
-        <v>1.542678259431263e-08</v>
+        <v>0.01542678259431263</v>
       </c>
       <c r="D343" t="n">
         <v>0.02358318998354969</v>
@@ -15213,7 +15213,7 @@
         <v>0.05832493748071754</v>
       </c>
       <c r="C344" t="n">
-        <v>3.787456707214698e-08</v>
+        <v>0.03787456707214698</v>
       </c>
       <c r="D344" t="n">
         <v>0.008976182008715528</v>
@@ -15256,7 +15256,7 @@
         <v>0.1028063804631847</v>
       </c>
       <c r="C345" t="n">
-        <v>7.473286693445224e-08</v>
+        <v>0.07473286693445202</v>
       </c>
       <c r="D345" t="n">
         <v>0.07746571937349511</v>
@@ -15299,7 +15299,7 @@
         <v>0.02174380955818633</v>
       </c>
       <c r="C346" t="n">
-        <v>-4.339839449503669e-09</v>
+        <v>-0.00433983944950378</v>
       </c>
       <c r="D346" t="n">
         <v>0.01640061130985315</v>
@@ -15342,7 +15342,7 @@
         <v>0.05187470834096608</v>
       </c>
       <c r="C347" t="n">
-        <v>2.981661709703376e-08</v>
+        <v>0.02981661709703376</v>
       </c>
       <c r="D347" t="n">
         <v>0.04059041109093364</v>
@@ -15385,7 +15385,7 @@
         <v>0.03565456337568573</v>
       </c>
       <c r="C348" t="n">
-        <v>-9.885449197875706e-09</v>
+        <v>-0.009885449197875817</v>
       </c>
       <c r="D348" t="n">
         <v>0.04254119250717769</v>
@@ -15428,7 +15428,7 @@
         <v>0.06733495705622539</v>
       </c>
       <c r="C349" t="n">
-        <v>5.748503177485431e-08</v>
+        <v>0.05748503177485431</v>
       </c>
       <c r="D349" t="n">
         <v>0.06314668992932382</v>
@@ -15471,7 +15471,7 @@
         <v>0.0537102070343296</v>
       </c>
       <c r="C350" t="n">
-        <v>3.221290638624019e-08</v>
+        <v>0.03221290638624019</v>
       </c>
       <c r="D350" t="n">
         <v>0.06187877584876689</v>
@@ -15514,7 +15514,7 @@
         <v>0.06036670691439472</v>
       </c>
       <c r="C351" t="n">
-        <v>5.009954463559963e-08</v>
+        <v>0.05009954463559962</v>
       </c>
       <c r="D351" t="n">
         <v>0.01678606627330637</v>
@@ -15557,7 +15557,7 @@
         <v>-0.5325129567640501</v>
       </c>
       <c r="C352" t="n">
-        <v>-4.915659183123406e-07</v>
+        <v>-0.4915659183123405</v>
       </c>
       <c r="D352" t="n">
         <v>-0.4432484992891549</v>
@@ -15600,7 +15600,7 @@
         <v>-0.9940227326538874</v>
       </c>
       <c r="C353" t="n">
-        <v>-9.811541009962225e-07</v>
+        <v>-0.9811541009962225</v>
       </c>
       <c r="D353" t="n">
         <v>-0.8869152333499032</v>
@@ -15643,7 +15643,7 @@
         <v>-0.9880358947158148</v>
       </c>
       <c r="C354" t="n">
-        <v>-9.597695620011115e-07</v>
+        <v>-0.9597695620011115</v>
       </c>
       <c r="D354" t="n">
         <v>-0.8216074906229978</v>
@@ -15686,7 +15686,7 @@
         <v>-0.9813346953108211</v>
       </c>
       <c r="C355" t="n">
-        <v>-9.435071657721546e-07</v>
+        <v>-0.9435071657721545</v>
       </c>
       <c r="D355" t="n">
         <v>-0.8141615023146667</v>
@@ -15729,7 +15729,7 @@
         <v>-0.9774518389800343</v>
       </c>
       <c r="C356" t="n">
-        <v>-9.363734028934001e-07</v>
+        <v>-0.9363734028934001</v>
       </c>
       <c r="D356" t="n">
         <v>-0.756449246190539</v>
@@ -15772,7 +15772,7 @@
         <v>-0.9746065489675475</v>
       </c>
       <c r="C357" t="n">
-        <v>-9.099913804652259e-07</v>
+        <v>-0.9099913804652259</v>
       </c>
       <c r="D357" t="n">
         <v>-0.7418974448420637</v>
@@ -15815,7 +15815,7 @@
         <v>-0.9743005116124162</v>
       </c>
       <c r="C358" t="n">
-        <v>-8.99092772865888e-07</v>
+        <v>-0.8990927728658881</v>
       </c>
       <c r="D358" t="n">
         <v>-0.7497533428419089</v>
@@ -15858,7 +15858,7 @@
         <v>-0.9007588640345942</v>
       </c>
       <c r="C359" t="n">
-        <v>-8.142262153916584e-07</v>
+        <v>-0.8142262153916584</v>
       </c>
       <c r="D359" t="n">
         <v>-0.7496984249241102</v>
@@ -15901,7 +15901,7 @@
         <v>-0.7676648845887606</v>
       </c>
       <c r="C360" t="n">
-        <v>-6.575406980184264e-07</v>
+        <v>-0.6575406980184264</v>
       </c>
       <c r="D360" t="n">
         <v>-0.7185394972249413</v>
@@ -15944,7 +15944,7 @@
         <v>-0.7481522300126002</v>
       </c>
       <c r="C361" t="n">
-        <v>-6.6511323920903e-07</v>
+        <v>-0.6651132392090299</v>
       </c>
       <c r="D361" t="n">
         <v>-0.7013204008362499</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -504,19 +504,19 @@
         <v>33239</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.05562146031940518</v>
+        <v>-5.562146031940518</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07118643009229364</v>
+        <v>-7.118643009229353</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.105255635500261</v>
+        <v>-10.5255635500261</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003668183745440645</v>
+        <v>-0.3668183745440645</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1122677020219779</v>
+        <v>-11.22677020219779</v>
       </c>
       <c r="G2" t="n">
         <v>3.73932</v>
@@ -547,19 +547,19 @@
         <v>33270</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.227175122022969</v>
+        <v>-22.71751220229689</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2300346783839635</v>
+        <v>-23.00346783839634</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2372997475969882</v>
+        <v>-23.72997475969882</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03601355775964588</v>
+        <v>-3.601355775964588</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2698734086329838</v>
+        <v>-26.98734086329838</v>
       </c>
       <c r="G3" t="n">
         <v>1.90074</v>
@@ -590,19 +590,19 @@
         <v>33298</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1391888075470618</v>
+        <v>-13.91888075470618</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09632595965665713</v>
+        <v>-9.632595965665702</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2048538865822255</v>
+        <v>-20.48538865822255</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009800207663124283</v>
+        <v>0.09800207663124283</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2102913007393755</v>
+        <v>-21.02913007393755</v>
       </c>
       <c r="G4" t="n">
         <v>3.33333</v>
@@ -633,19 +633,19 @@
         <v>33329</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01876615744290178</v>
+        <v>-1.876615744290178</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06091600917809226</v>
+        <v>-6.091600917809226</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.094213355257183</v>
+        <v>-9.4213355257183</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03097765232319394</v>
+        <v>-3.097765232319394</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1208572257666354</v>
+        <v>-12.08572257666354</v>
       </c>
       <c r="G5" t="n">
         <v>0.10493</v>
@@ -676,19 +676,19 @@
         <v>33359</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0004911077516509543</v>
+        <v>-0.04911077516509543</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.02013216073307111</v>
+        <v>-2.013216073307122</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08609623032346503</v>
+        <v>-8.609623032346503</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005936935349836414</v>
+        <v>-0.5936935349836414</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09210603222320357</v>
+        <v>-9.210603222320357</v>
       </c>
       <c r="G6" t="n">
         <v>0.73452</v>
@@ -719,19 +719,19 @@
         <v>33390</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.01072625587287468</v>
+        <v>-1.072625587287468</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.03003448325447811</v>
+        <v>-3.003448325447811</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01150245487945256</v>
+        <v>-1.150245487945256</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01320462853000226</v>
+        <v>-1.320462853000226</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01267372920918186</v>
+        <v>-1.267372920918186</v>
       </c>
       <c r="G7" t="n">
         <v>1.25</v>
@@ -762,19 +762,19 @@
         <v>33420</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00977785731502423</v>
+        <v>0.977785731502423</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.005423953364236955</v>
+        <v>-0.5423953364236955</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02776840419061655</v>
+        <v>-2.776840419061655</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02997333469760788</v>
+        <v>2.997333469760788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007490060888079908</v>
+        <v>0.7490060888079908</v>
       </c>
       <c r="G8" t="n">
         <v>2.93194</v>
@@ -805,19 +805,19 @@
         <v>33451</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0006800432941356238</v>
+        <v>0.06800432941356238</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01187027285764575</v>
+        <v>-1.187027285764575</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.01921698343885891</v>
+        <v>-1.921698343885891</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0006918049179420738</v>
+        <v>0.06918049179420738</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01585909464054669</v>
+        <v>-1.585909464054669</v>
       </c>
       <c r="G9" t="n">
         <v>3.42679</v>
@@ -848,19 +848,19 @@
         <v>33482</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08240233734436475</v>
+        <v>8.240233734436476</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04792415916542159</v>
+        <v>4.792415916542181</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0008777921183718007</v>
+        <v>-0.08777921183718007</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.006919677853071793</v>
+        <v>-0.6919677853071793</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008486054005102384</v>
+        <v>0.8486054005102384</v>
       </c>
       <c r="G10" t="n">
         <v>3.78151</v>
@@ -891,19 +891,19 @@
         <v>33512</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.005088794248391038</v>
+        <v>-0.5088794248391038</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.03033027652902864</v>
+        <v>-3.033027652902853</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.06094810504278536</v>
+        <v>-6.094810504278536</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01544919103522302</v>
+        <v>-1.544919103522302</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08722018936138742</v>
+        <v>-8.722018936138742</v>
       </c>
       <c r="G11" t="n">
         <v>2.09864</v>
@@ -934,19 +934,19 @@
         <v>33543</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.01360584095772477</v>
+        <v>-1.360584095772477</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04060849962991753</v>
+        <v>-4.060849962991753</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04253235129099697</v>
+        <v>-4.253235129099697</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01944246175883257</v>
+        <v>-1.944246175883257</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07125002662267643</v>
+        <v>-7.125002662267644</v>
       </c>
       <c r="G12" t="n">
         <v>0.72165</v>
@@ -977,19 +977,19 @@
         <v>33573</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008125877859907593</v>
+        <v>0.8125877859907593</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.00366242295633068</v>
+        <v>-0.3662422956330791</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02354873067353758</v>
+        <v>2.354873067353758</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01908933834458071</v>
+        <v>1.908933834458071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05349388326506777</v>
+        <v>5.349388326506777</v>
       </c>
       <c r="G13" t="n">
         <v>1.33197</v>
@@ -1020,19 +1020,19 @@
         <v>33604</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02142066006510213</v>
+        <v>2.142066006510213</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05929072030741334</v>
+        <v>5.929072030741334</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01638493926864748</v>
+        <v>1.638493926864748</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009159119606286126</v>
+        <v>0.9159119606286126</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01492895393209093</v>
+        <v>1.492895393209093</v>
       </c>
       <c r="G14" t="n">
         <v>2.05973</v>
@@ -1063,19 +1063,19 @@
         <v>33635</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3050052641219847</v>
+        <v>30.50052641219847</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3186834718580622</v>
+        <v>31.86834718580622</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1895223333141141</v>
+        <v>18.95223333141141</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04240107098043788</v>
+        <v>4.240107098043788</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2410870646582701</v>
+        <v>24.10870646582701</v>
       </c>
       <c r="G15" t="n">
         <v>2.90155</v>
@@ -1106,19 +1106,19 @@
         <v>33664</v>
       </c>
       <c r="B16" t="n">
-        <v>0.09250301821468021</v>
+        <v>9.250301821468021</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05780137009605757</v>
+        <v>5.780137009605757</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09187967725337676</v>
+        <v>9.187967725337675</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01914277529063479</v>
+        <v>1.914277529063479</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1141401455687168</v>
+        <v>11.41401455687168</v>
       </c>
       <c r="G16" t="n">
         <v>3.53798</v>
@@ -1149,19 +1149,19 @@
         <v>33695</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.04263083338861806</v>
+        <v>-4.263083338861806</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04066338975223815</v>
+        <v>4.066338975223815</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002592341756559202</v>
+        <v>0.2592341756559202</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05303788496138462</v>
+        <v>5.303788496138462</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04897229227926214</v>
+        <v>4.897229227926214</v>
       </c>
       <c r="G17" t="n">
         <v>4.29769</v>
@@ -1192,19 +1192,19 @@
         <v>33725</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.01064984194902796</v>
+        <v>-1.064984194902796</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02292775407560077</v>
+        <v>2.292775407560077</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01054652305300863</v>
+        <v>1.054652305300863</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02376663743373908</v>
+        <v>2.376663743373908</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04155419432055707</v>
+        <v>4.155419432055707</v>
       </c>
       <c r="G18" t="n">
         <v>3.75</v>
@@ -1235,19 +1235,19 @@
         <v>33756</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.03654769213362397</v>
+        <v>-3.654769213362397</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004733203438172184</v>
+        <v>0.4733203438172184</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07066991477090612</v>
+        <v>-7.066991477090612</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0504147773514998</v>
+        <v>5.04147773514998</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02357409526061094</v>
+        <v>-2.357409526061094</v>
       </c>
       <c r="G19" t="n">
         <v>2.57202</v>
@@ -1278,19 +1278,19 @@
         <v>33786</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.09559638688035743</v>
+        <v>-9.559638688035744</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.04640193663211833</v>
+        <v>-4.640193663211834</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07309561930818209</v>
+        <v>-7.309561930818209</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008072778016649185</v>
+        <v>0.8072778016649185</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07328206112446911</v>
+        <v>-7.328206112446911</v>
       </c>
       <c r="G20" t="n">
         <v>1.11902</v>
@@ -1321,19 +1321,19 @@
         <v>33817</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.09179837823231274</v>
+        <v>-9.179837823231274</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.04149301352783419</v>
+        <v>-4.149301352783407</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06331011031501144</v>
+        <v>-6.331011031501143</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03984461026348551</v>
+        <v>3.984461026348551</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.02552714001366396</v>
+        <v>-2.552714001366396</v>
       </c>
       <c r="G21" t="n">
         <v>0.1004</v>
@@ -1364,19 +1364,19 @@
         <v>33848</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.04531838793117737</v>
+        <v>-4.531838793117737</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001193620392825334</v>
+        <v>0.01193620392825334</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006249686943978094</v>
+        <v>0.6249686943978094</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04891020456370065</v>
+        <v>4.891020456370065</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06992538322064568</v>
+        <v>6.992538322064568</v>
       </c>
       <c r="G22" t="n">
         <v>-0.40486</v>
@@ -1407,19 +1407,19 @@
         <v>33878</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.001812776148229833</v>
+        <v>-0.1812776148229833</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06140167106671335</v>
+        <v>6.140167106671335</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04868788484384634</v>
+        <v>4.868788484384634</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03082933820142286</v>
+        <v>3.082933820142286</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08486219575436671</v>
+        <v>8.486219575436671</v>
       </c>
       <c r="G23" t="n">
         <v>-1.33607</v>
@@ -1450,19 +1450,19 @@
         <v>33909</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0003069113043918659</v>
+        <v>0.03069113043918659</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06478041885750851</v>
+        <v>6.478041885750851</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04272761934656444</v>
+        <v>4.272761934656444</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04981784601544992</v>
+        <v>4.981784601544992</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09101397187279803</v>
+        <v>9.101397187279803</v>
       </c>
       <c r="G24" t="n">
         <v>-1.63767</v>
@@ -1493,19 +1493,19 @@
         <v>33939</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0432226680298482</v>
+        <v>-4.32226680298482</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0006131158441791129</v>
+        <v>0.0613115844179335</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003655624507340693</v>
+        <v>0.3655624507340693</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01002931362063708</v>
+        <v>1.002931362063708</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01858226057687151</v>
+        <v>1.858226057687151</v>
       </c>
       <c r="G25" t="n">
         <v>-1.71891</v>
@@ -1536,19 +1536,19 @@
         <v>33970</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.03116176491001976</v>
+        <v>-3.116176491001976</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.004885856534412314</v>
+        <v>-0.4885856534412536</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001786018141027523</v>
+        <v>-0.1786018141027523</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.009122707451509893</v>
+        <v>-0.9122707451509893</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.02275511624505966</v>
+        <v>-2.275511624505966</v>
       </c>
       <c r="G26" t="n">
         <v>-4.33905</v>
@@ -1579,19 +1579,19 @@
         <v>34001</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.09795857328607882</v>
+        <v>-9.795857328607882</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.06019117593464307</v>
+        <v>-6.019117593464318</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.03642002806588807</v>
+        <v>-3.642002806588807</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0009819712118100954</v>
+        <v>-0.09819712118100954</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04126988319346037</v>
+        <v>-4.126988319346037</v>
       </c>
       <c r="G27" t="n">
         <v>-4.22961</v>
@@ -1622,19 +1622,19 @@
         <v>34029</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.007561651690826787</v>
+        <v>-0.7561651690826787</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007643659941757974</v>
+        <v>0.7643659941757752</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001300385202684606</v>
+        <v>-0.1300385202684606</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.007867384640071418</v>
+        <v>-0.7867384640071418</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002244971678464269</v>
+        <v>0.2244971678464269</v>
       </c>
       <c r="G28" t="n">
         <v>-4.52261</v>
@@ -1665,19 +1665,19 @@
         <v>34060</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0572285373040673</v>
+        <v>-5.72285373040673</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.03165872275791559</v>
+        <v>-3.165872275791548</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.009793700806175365</v>
+        <v>-0.9793700806175365</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.01591521021889175</v>
+        <v>-1.591521021889175</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.02756368440952472</v>
+        <v>-2.756368440952472</v>
       </c>
       <c r="G29" t="n">
         <v>-4.92462</v>
@@ -1708,19 +1708,19 @@
         <v>34090</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.06022044237851465</v>
+        <v>-6.022044237851465</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.02301769284184929</v>
+        <v>-2.30176928418494</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.01189816484847495</v>
+        <v>-1.189816484847495</v>
       </c>
       <c r="E30" t="n">
-        <v>0.009781222483478125</v>
+        <v>0.9781222483478125</v>
       </c>
       <c r="F30" t="n">
-        <v>0.003001226266655221</v>
+        <v>0.3001226266655221</v>
       </c>
       <c r="G30" t="n">
         <v>-4.71888</v>
@@ -1751,19 +1751,19 @@
         <v>34121</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.113887309809152</v>
+        <v>-11.3887309809152</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07580239567177538</v>
+        <v>-7.580239567177538</v>
       </c>
       <c r="D31" t="n">
-        <v>0.009744807105642739</v>
+        <v>0.9744807105642739</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0104965364174251</v>
+        <v>-1.04965364174251</v>
       </c>
       <c r="F31" t="n">
-        <v>0.003344157697125594</v>
+        <v>0.3344157697125594</v>
       </c>
       <c r="G31" t="n">
         <v>-4.71414</v>
@@ -1794,19 +1794,19 @@
         <v>34151</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.05035096196250322</v>
+        <v>-5.035096196250322</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.01693394770197787</v>
+        <v>-1.693394770197787</v>
       </c>
       <c r="D32" t="n">
-        <v>0.008322335605747799</v>
+        <v>0.8322335605747799</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0008024298090449911</v>
+        <v>0.08024298090449911</v>
       </c>
       <c r="F32" t="n">
-        <v>0.003263126668644256</v>
+        <v>0.3263126668644256</v>
       </c>
       <c r="G32" t="n">
         <v>-5.03018</v>
@@ -1837,19 +1837,19 @@
         <v>34182</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.04593883543070443</v>
+        <v>-4.593883543070443</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.01989540963936631</v>
+        <v>-1.989540963936609</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02596714375496334</v>
+        <v>2.596714375496334</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.01832357513665572</v>
+        <v>-1.832357513665572</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0114085631115437</v>
+        <v>1.14085631115437</v>
       </c>
       <c r="G33" t="n">
         <v>-5.21565</v>
@@ -1880,19 +1880,19 @@
         <v>34213</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.103468347643029</v>
+        <v>-10.3468347643029</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06913116175105172</v>
+        <v>-6.913116175105182</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07808310309707645</v>
+        <v>-7.808310309707645</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01992885619167395</v>
+        <v>-1.992885619167395</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.09908802241063408</v>
+        <v>-9.908802241063409</v>
       </c>
       <c r="G34" t="n">
         <v>-4.6748</v>
@@ -1923,19 +1923,19 @@
         <v>34243</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.0463598937019073</v>
+        <v>-4.63598937019073</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02767754523463173</v>
+        <v>-2.767754523463184</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.04942717628094351</v>
+        <v>-4.942717628094351</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.01893316551580793</v>
+        <v>-1.893316551580793</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0671716054842989</v>
+        <v>-6.71716054842989</v>
       </c>
       <c r="G35" t="n">
         <v>-2.5</v>
@@ -1966,19 +1966,19 @@
         <v>34274</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.07368041525382085</v>
+        <v>-7.368041525382085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.05742712013994966</v>
+        <v>-5.742712013994977</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.05384286848409436</v>
+        <v>-5.384286848409436</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0329023654339472</v>
+        <v>-3.29023654339472</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.09994852249628061</v>
+        <v>-9.99485224962806</v>
       </c>
       <c r="G36" t="n">
         <v>-3.12175</v>
@@ -2009,19 +2009,19 @@
         <v>34304</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.05452911255385229</v>
+        <v>-5.452911255385229</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.02387584097782114</v>
+        <v>-2.387584097782125</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01297939992277497</v>
+        <v>1.297939992277497</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.02678284773288309</v>
+        <v>-2.678284773288309</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.01800648015634698</v>
+        <v>-1.800648015634698</v>
       </c>
       <c r="G37" t="n">
         <v>-4.01235</v>
@@ -2052,19 +2052,19 @@
         <v>34335</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.06443979738749195</v>
+        <v>-6.443979738749195</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.04714917419355391</v>
+        <v>-4.714917419355391</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.03210746885871929</v>
+        <v>-3.210746885871929</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0246182993695554</v>
+        <v>-2.46182993695554</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06615787572254328</v>
+        <v>-6.615787572254328</v>
       </c>
       <c r="G38" t="n">
         <v>-1.05485</v>
@@ -2095,19 +2095,19 @@
         <v>34366</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06967505649970418</v>
+        <v>6.967505649970418</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07317747267312624</v>
+        <v>7.317747267312624</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09217562127172174</v>
+        <v>9.217562127172174</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0194376110326121</v>
+        <v>-1.94376110326121</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07049581441647934</v>
+        <v>7.049581441647934</v>
       </c>
       <c r="G39" t="n">
         <v>-1.15668</v>
@@ -2138,19 +2138,19 @@
         <v>34394</v>
       </c>
       <c r="B40" t="n">
-        <v>0.05410420226358736</v>
+        <v>5.410420226358736</v>
       </c>
       <c r="C40" t="n">
-        <v>0.07895886771980809</v>
+        <v>7.895886771980809</v>
       </c>
       <c r="D40" t="n">
-        <v>0.121080752724475</v>
+        <v>12.1080752724475</v>
       </c>
       <c r="E40" t="n">
-        <v>0.007010449107410999</v>
+        <v>0.7010449107410999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1499902994591469</v>
+        <v>14.99902994591469</v>
       </c>
       <c r="G40" t="n">
         <v>-0.52632</v>
@@ -2181,19 +2181,19 @@
         <v>34425</v>
       </c>
       <c r="B41" t="n">
-        <v>0.05476351554569603</v>
+        <v>5.476351554569603</v>
       </c>
       <c r="C41" t="n">
-        <v>0.04777762930496121</v>
+        <v>4.777762930496121</v>
       </c>
       <c r="D41" t="n">
-        <v>0.07468806064258549</v>
+        <v>7.468806064258549</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01847428775918347</v>
+        <v>1.847428775918347</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0952064773868273</v>
+        <v>9.52064773868273</v>
       </c>
       <c r="G41" t="n">
         <v>-0.84567</v>
@@ -2224,19 +2224,19 @@
         <v>34455</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.005736351883284807</v>
+        <v>-0.5736351883284807</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01333051292257448</v>
+        <v>1.333051292257448</v>
       </c>
       <c r="D42" t="n">
-        <v>0.06160192177917256</v>
+        <v>6.160192177917256</v>
       </c>
       <c r="E42" t="n">
-        <v>0.008362858341480095</v>
+        <v>0.8362858341480095</v>
       </c>
       <c r="F42" t="n">
-        <v>0.06902561525041628</v>
+        <v>6.902561525041628</v>
       </c>
       <c r="G42" t="n">
         <v>-0.84299</v>
@@ -2267,19 +2267,19 @@
         <v>34486</v>
       </c>
       <c r="B43" t="n">
-        <v>0.07461663123077145</v>
+        <v>7.461663123077145</v>
       </c>
       <c r="C43" t="n">
-        <v>0.09524792671642368</v>
+        <v>9.524792671642368</v>
       </c>
       <c r="D43" t="n">
-        <v>0.07626805039141882</v>
+        <v>7.626805039141882</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.003264141004135079</v>
+        <v>-0.3264141004135079</v>
       </c>
       <c r="F43" t="n">
-        <v>0.077279214556085</v>
+        <v>7.7279214556085</v>
       </c>
       <c r="G43" t="n">
         <v>0.21053</v>
@@ -2310,19 +2310,19 @@
         <v>34516</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0513503868917593</v>
+        <v>5.13503868917593</v>
       </c>
       <c r="C44" t="n">
-        <v>0.06685091373230434</v>
+        <v>6.685091373230434</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06606036290333028</v>
+        <v>6.606036290333028</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002044853498483379</v>
+        <v>0.2044853498483379</v>
       </c>
       <c r="F44" t="n">
-        <v>0.07020007884880752</v>
+        <v>7.020007884880752</v>
       </c>
       <c r="G44" t="n">
         <v>1.69492</v>
@@ -2353,19 +2353,19 @@
         <v>34547</v>
       </c>
       <c r="B45" t="n">
-        <v>0.07912327707954248</v>
+        <v>7.912327707954248</v>
       </c>
       <c r="C45" t="n">
-        <v>0.09164325959552211</v>
+        <v>9.164325959552189</v>
       </c>
       <c r="D45" t="n">
-        <v>0.05167644457031173</v>
+        <v>5.167644457031173</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03429264414250954</v>
+        <v>3.429264414250954</v>
       </c>
       <c r="F45" t="n">
-        <v>0.08173690932311617</v>
+        <v>8.173690932311617</v>
       </c>
       <c r="G45" t="n">
         <v>1.37566</v>
@@ -2396,19 +2396,19 @@
         <v>34578</v>
       </c>
       <c r="B46" t="n">
-        <v>0.06391221526109159</v>
+        <v>6.391221526109159</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07610533841541622</v>
+        <v>7.610533841541622</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09864722433250317</v>
+        <v>9.864722433250318</v>
       </c>
       <c r="E46" t="n">
-        <v>0.04186516123627926</v>
+        <v>4.186516123627926</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1545054904575005</v>
+        <v>15.45054904575005</v>
       </c>
       <c r="G46" t="n">
         <v>1.91898</v>
@@ -2439,19 +2439,19 @@
         <v>34608</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01854505197708156</v>
+        <v>1.854505197708156</v>
       </c>
       <c r="C47" t="n">
-        <v>0.02702122547908936</v>
+        <v>2.702122547908936</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04490065236863727</v>
+        <v>4.490065236863727</v>
       </c>
       <c r="E47" t="n">
-        <v>0.05572350576461216</v>
+        <v>5.572350576461216</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1069773761804473</v>
+        <v>10.69773761804473</v>
       </c>
       <c r="G47" t="n">
         <v>1.06838</v>
@@ -2482,19 +2482,19 @@
         <v>34639</v>
       </c>
       <c r="B48" t="n">
-        <v>0.08897850681038899</v>
+        <v>8.8978506810389</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1015002123162896</v>
+        <v>10.15002123162896</v>
       </c>
       <c r="D48" t="n">
-        <v>0.06304256747518933</v>
+        <v>6.304256747518933</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05148722814194873</v>
+        <v>5.148722814194873</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1115120773931446</v>
+        <v>11.15120773931446</v>
       </c>
       <c r="G48" t="n">
         <v>2.25564</v>
@@ -2525,19 +2525,19 @@
         <v>34669</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08593802953054008</v>
+        <v>8.593802953054009</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09126135359424481</v>
+        <v>9.126135359424481</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01017341874661604</v>
+        <v>1.017341874661604</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05821776520918864</v>
+        <v>5.821776520918864</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06931285733840142</v>
+        <v>6.931285733840142</v>
       </c>
       <c r="G49" t="n">
         <v>3.21543</v>
@@ -2568,19 +2568,19 @@
         <v>34700</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06919151852058092</v>
+        <v>6.919151852058092</v>
       </c>
       <c r="C50" t="n">
-        <v>0.05123240661225048</v>
+        <v>5.12324066122507</v>
       </c>
       <c r="D50" t="n">
-        <v>0.05696332959231087</v>
+        <v>5.696332959231087</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0781390585465398</v>
+        <v>7.81390585465398</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1426146167403874</v>
+        <v>14.26146167403875</v>
       </c>
       <c r="G50" t="n">
         <v>1.49254</v>
@@ -2611,19 +2611,19 @@
         <v>34731</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.04569387920802059</v>
+        <v>-4.569387920802059</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.04599050128757587</v>
+        <v>-4.599050128757598</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.04420578325011526</v>
+        <v>-4.420578325011526</v>
       </c>
       <c r="E51" t="n">
-        <v>0.03973432023820855</v>
+        <v>3.973432023820855</v>
       </c>
       <c r="F51" t="n">
-        <v>0.00216610547296292</v>
+        <v>0.216610547296292</v>
       </c>
       <c r="G51" t="n">
         <v>1.80851</v>
@@ -2654,19 +2654,19 @@
         <v>34759</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.007752103878618133</v>
+        <v>-0.7752103878618133</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.04759670776575753</v>
+        <v>-4.759670776575775</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0636885712757993</v>
+        <v>-6.36885712757993</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03167110770545345</v>
+        <v>3.167110770545345</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.03156100395248818</v>
+        <v>-3.156100395248818</v>
       </c>
       <c r="G52" t="n">
         <v>1.37566</v>
@@ -2697,19 +2697,19 @@
         <v>34790</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.01715018083734154</v>
+        <v>-1.715018083734154</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.002239849848333364</v>
+        <v>-0.2239849848333475</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0497801353444135</v>
+        <v>-4.978013534441351</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02964315088836256</v>
+        <v>2.964315088836256</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.02486700612809534</v>
+        <v>-2.486700612809534</v>
       </c>
       <c r="G53" t="n">
         <v>1.59915</v>
@@ -2740,19 +2740,19 @@
         <v>34820</v>
       </c>
       <c r="B54" t="n">
-        <v>0.05642807065958011</v>
+        <v>5.642807065958011</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02967282938413218</v>
+        <v>2.967282938413218</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.03426270406881116</v>
+        <v>-3.426270406881116</v>
       </c>
       <c r="E54" t="n">
-        <v>0.04643174574997633</v>
+        <v>4.643174574997633</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.002381889463321407</v>
+        <v>-0.2381889463321407</v>
       </c>
       <c r="G54" t="n">
         <v>0.63762</v>
@@ -2783,19 +2783,19 @@
         <v>34851</v>
       </c>
       <c r="B55" t="n">
-        <v>0.05019149478502305</v>
+        <v>5.019149478502305</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01879201689619125</v>
+        <v>1.879201689619125</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.01597560382754437</v>
+        <v>-1.597560382754437</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05300185896603282</v>
+        <v>5.300185896603282</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03902222435558977</v>
+        <v>3.902222435558977</v>
       </c>
       <c r="G55" t="n">
         <v>1.15546</v>
@@ -2826,19 +2826,19 @@
         <v>34881</v>
       </c>
       <c r="B56" t="n">
-        <v>0.07028296975146153</v>
+        <v>7.028296975146153</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02775791089354818</v>
+        <v>2.775791089354818</v>
       </c>
       <c r="D56" t="n">
-        <v>0.01166221548134105</v>
+        <v>1.166221548134105</v>
       </c>
       <c r="E56" t="n">
-        <v>0.05888138458811598</v>
+        <v>5.888138458811598</v>
       </c>
       <c r="F56" t="n">
-        <v>0.079843155613883</v>
+        <v>7.9843155613883</v>
       </c>
       <c r="G56" t="n">
         <v>-0.10417</v>
@@ -2869,19 +2869,19 @@
         <v>34912</v>
       </c>
       <c r="B57" t="n">
-        <v>0.03815437399116117</v>
+        <v>3.815437399116117</v>
       </c>
       <c r="C57" t="n">
-        <v>0.007580186173425485</v>
+        <v>0.7580186173425707</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.005079878835415497</v>
+        <v>-0.5079878835415497</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02027979994802154</v>
+        <v>2.027979994802154</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0009804617801885129</v>
+        <v>0.09804617801885129</v>
       </c>
       <c r="G57" t="n">
         <v>0.41754</v>
@@ -2912,19 +2912,19 @@
         <v>34943</v>
       </c>
       <c r="B58" t="n">
-        <v>0.04757658055244818</v>
+        <v>4.757658055244818</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01439612157056569</v>
+        <v>1.439612157056591</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.003783902472771272</v>
+        <v>-0.3783902472771272</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02446837991854545</v>
+        <v>2.446837991854545</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01512762392825473</v>
+        <v>1.512762392825473</v>
       </c>
       <c r="G58" t="n">
         <v>0.20921</v>
@@ -2955,19 +2955,19 @@
         <v>34973</v>
       </c>
       <c r="B59" t="n">
-        <v>0.04826108784789596</v>
+        <v>4.826108784789596</v>
       </c>
       <c r="C59" t="n">
-        <v>0.02878723071323219</v>
+        <v>2.878723071323219</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0172807672638231</v>
+        <v>1.72807672638231</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04667012275621296</v>
+        <v>4.667012275621296</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06351482216225834</v>
+        <v>6.351482216225834</v>
       </c>
       <c r="G59" t="n">
         <v>-0.21142</v>
@@ -2998,19 +2998,19 @@
         <v>35004</v>
       </c>
       <c r="B60" t="n">
-        <v>0.01230203803209662</v>
+        <v>1.230203803209662</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.01537815745437043</v>
+        <v>-1.537815745437043</v>
       </c>
       <c r="D60" t="n">
-        <v>0.005618673032467658</v>
+        <v>0.5618673032467658</v>
       </c>
       <c r="E60" t="n">
-        <v>0.05263071058632107</v>
+        <v>5.263071058632107</v>
       </c>
       <c r="F60" t="n">
-        <v>0.04385754139686027</v>
+        <v>4.385754139686027</v>
       </c>
       <c r="G60" t="n">
         <v>-0.10504</v>
@@ -3041,19 +3041,19 @@
         <v>35034</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0312737285104876</v>
+        <v>3.12737285104876</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.004511475028776357</v>
+        <v>-0.4511475028776357</v>
       </c>
       <c r="D61" t="n">
-        <v>0.01201103456145058</v>
+        <v>1.201103456145058</v>
       </c>
       <c r="E61" t="n">
-        <v>0.04265036443056291</v>
+        <v>4.265036443056291</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05261735291467717</v>
+        <v>5.261735291467717</v>
       </c>
       <c r="G61" t="n">
         <v>-0.31153</v>
@@ -3084,19 +3084,19 @@
         <v>35065</v>
       </c>
       <c r="B62" t="n">
-        <v>0.04145582300331419</v>
+        <v>4.145582300331419</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00309485034572643</v>
+        <v>0.309485034572643</v>
       </c>
       <c r="D62" t="n">
-        <v>0.01350906694164045</v>
+        <v>1.350906694164045</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0514306098350763</v>
+        <v>5.14306098350763</v>
       </c>
       <c r="F62" t="n">
-        <v>0.07038131617383514</v>
+        <v>7.038131617383514</v>
       </c>
       <c r="G62" t="n">
         <v>-0.52521</v>
@@ -3127,19 +3127,19 @@
         <v>35096</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1433875242306482</v>
+        <v>14.33875242306481</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1033601993651978</v>
+        <v>10.3360199365198</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0467511280200732</v>
+        <v>4.67511280200732</v>
       </c>
       <c r="E63" t="n">
-        <v>0.08557550103127687</v>
+        <v>8.557550103127687</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1619575108694431</v>
+        <v>16.19575108694431</v>
       </c>
       <c r="G63" t="n">
         <v>0.31348</v>
@@ -3170,19 +3170,19 @@
         <v>35125</v>
       </c>
       <c r="B64" t="n">
-        <v>0.04273608088184955</v>
+        <v>4.273608088184955</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02252455250776308</v>
+        <v>2.252455250776331</v>
       </c>
       <c r="D64" t="n">
-        <v>0.008215994901124235</v>
+        <v>0.8215994901124235</v>
       </c>
       <c r="E64" t="n">
-        <v>0.06544435036411311</v>
+        <v>6.544435036411311</v>
       </c>
       <c r="F64" t="n">
-        <v>0.08828039450560232</v>
+        <v>8.828039450560233</v>
       </c>
       <c r="G64" t="n">
         <v>0.5219200000000001</v>
@@ -3213,19 +3213,19 @@
         <v>35156</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03275473572003285</v>
+        <v>3.275473572003285</v>
       </c>
       <c r="C65" t="n">
-        <v>0.01704477537002314</v>
+        <v>1.704477537002336</v>
       </c>
       <c r="D65" t="n">
-        <v>0.03280998199901664</v>
+        <v>3.280998199901664</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0588065231936834</v>
+        <v>5.88065231936834</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1056384487514677</v>
+        <v>10.56384487514677</v>
       </c>
       <c r="G65" t="n">
         <v>-0.52466</v>
@@ -3256,19 +3256,19 @@
         <v>35186</v>
       </c>
       <c r="B66" t="n">
-        <v>0.03858906129386508</v>
+        <v>3.858906129386508</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0382959789311863</v>
+        <v>3.82959789311863</v>
       </c>
       <c r="D66" t="n">
-        <v>0.01286567192921462</v>
+        <v>1.286567192921462</v>
       </c>
       <c r="E66" t="n">
-        <v>0.03651982448064373</v>
+        <v>3.651982448064373</v>
       </c>
       <c r="F66" t="n">
-        <v>0.03879490639438266</v>
+        <v>3.879490639438266</v>
       </c>
       <c r="G66" t="n">
         <v>0.42239</v>
@@ -3299,19 +3299,19 @@
         <v>35217</v>
       </c>
       <c r="B67" t="n">
-        <v>0.05934571728489013</v>
+        <v>5.934571728489013</v>
       </c>
       <c r="C67" t="n">
-        <v>0.04107792653221898</v>
+        <v>4.107792653221898</v>
       </c>
       <c r="D67" t="n">
-        <v>0.02545573176680516</v>
+        <v>2.545573176680516</v>
       </c>
       <c r="E67" t="n">
-        <v>0.062572327591504</v>
+        <v>6.2572327591504</v>
       </c>
       <c r="F67" t="n">
-        <v>0.09437459560692774</v>
+        <v>9.437459560692773</v>
       </c>
       <c r="G67" t="n">
         <v>-0.31153</v>
@@ -3342,19 +3342,19 @@
         <v>35247</v>
       </c>
       <c r="B68" t="n">
-        <v>0.00639109929685544</v>
+        <v>0.639109929685544</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.00732375266194718</v>
+        <v>-0.732375266194718</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.01892295976600478</v>
+        <v>-1.892295976600478</v>
       </c>
       <c r="E68" t="n">
-        <v>0.04974678993402182</v>
+        <v>4.974678993402182</v>
       </c>
       <c r="F68" t="n">
-        <v>0.03579372977188622</v>
+        <v>3.579372977188622</v>
       </c>
       <c r="G68" t="n">
         <v>0.4171</v>
@@ -3385,19 +3385,19 @@
         <v>35278</v>
       </c>
       <c r="B69" t="n">
-        <v>0.01433069604564907</v>
+        <v>1.433069604564907</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01125418316354088</v>
+        <v>1.125418316354088</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.0171885270721337</v>
+        <v>-1.71885270721337</v>
       </c>
       <c r="E69" t="n">
-        <v>0.06871874737433159</v>
+        <v>6.871874737433159</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04554615074566692</v>
+        <v>4.554615074566692</v>
       </c>
       <c r="G69" t="n">
         <v>1.0395</v>
@@ -3428,19 +3428,19 @@
         <v>35309</v>
       </c>
       <c r="B70" t="n">
-        <v>0.01576344632730997</v>
+        <v>1.576344632730997</v>
       </c>
       <c r="C70" t="n">
-        <v>0.01153667968167982</v>
+        <v>1.153667968167982</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.04055959404796405</v>
+        <v>-4.055959404796406</v>
       </c>
       <c r="E70" t="n">
-        <v>0.07437269360291987</v>
+        <v>7.437269360291987</v>
       </c>
       <c r="F70" t="n">
-        <v>0.02512197752574297</v>
+        <v>2.512197752574297</v>
       </c>
       <c r="G70" t="n">
         <v>1.46138</v>
@@ -3471,19 +3471,19 @@
         <v>35339</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.01679039515064407</v>
+        <v>-1.679039515064407</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.03674542622317012</v>
+        <v>-3.674542622317012</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.04729275973090707</v>
+        <v>-4.729275973090708</v>
       </c>
       <c r="E71" t="n">
-        <v>0.05313311821312161</v>
+        <v>5.313311821312161</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.007361142421014155</v>
+        <v>-0.7361142421014155</v>
       </c>
       <c r="G71" t="n">
         <v>1.80085</v>
@@ -3514,19 +3514,19 @@
         <v>35370</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.01389754019249045</v>
+        <v>-1.389754019249045</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.02420144717333617</v>
+        <v>-2.420144717333628</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.06959092382949639</v>
+        <v>-6.959092382949638</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0541911512784834</v>
+        <v>5.41911512784834</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.04262735827191411</v>
+        <v>-4.262735827191411</v>
       </c>
       <c r="G72" t="n">
         <v>1.57729</v>
@@ -3557,19 +3557,19 @@
         <v>35400</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.02843881335463994</v>
+        <v>-2.843881335463994</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.05058352381140052</v>
+        <v>-5.058352381140041</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.05903623414602144</v>
+        <v>-5.903623414602144</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0802142130938539</v>
+        <v>8.02142130938539</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01121778456297018</v>
+        <v>1.121778456297018</v>
       </c>
       <c r="G73" t="n">
         <v>1.77083</v>
@@ -3600,19 +3600,19 @@
         <v>35431</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.01380814097202465</v>
+        <v>-1.380814097202465</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.05159421332644842</v>
+        <v>-5.159421332644854</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0441190605003402</v>
+        <v>-4.41190605003402</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0724595315301122</v>
+        <v>7.24595315301122</v>
       </c>
       <c r="F74" t="n">
-        <v>0.02057520430190762</v>
+        <v>2.057520430190762</v>
       </c>
       <c r="G74" t="n">
         <v>1.26716</v>
@@ -3643,19 +3643,19 @@
         <v>35462</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.0489232143653251</v>
+        <v>-4.89232143653251</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.07687984714614504</v>
+        <v>-7.687984714614515</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.04628946299703884</v>
+        <v>-4.628946299703884</v>
       </c>
       <c r="E75" t="n">
-        <v>0.06031019929367254</v>
+        <v>6.031019929367254</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0188936572240741</v>
+        <v>1.88936572240741</v>
       </c>
       <c r="G75" t="n">
         <v>0.52083</v>
@@ -3686,19 +3686,19 @@
         <v>35490</v>
       </c>
       <c r="B76" t="n">
-        <v>0.003111789848805557</v>
+        <v>0.3111789848805557</v>
       </c>
       <c r="C76" t="n">
-        <v>0.02158495714987607</v>
+        <v>2.158495714987607</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.006055545550082253</v>
+        <v>-0.6055545550082253</v>
       </c>
       <c r="E76" t="n">
-        <v>0.08509881577005185</v>
+        <v>8.509881577005185</v>
       </c>
       <c r="F76" t="n">
-        <v>0.09243406206370008</v>
+        <v>9.243406206370008</v>
       </c>
       <c r="G76" t="n">
         <v>0.41537</v>
@@ -3729,19 +3729,19 @@
         <v>35521</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06176113655933668</v>
+        <v>6.176113655933668</v>
       </c>
       <c r="C77" t="n">
-        <v>0.01332229021478848</v>
+        <v>1.332229021478848</v>
       </c>
       <c r="D77" t="n">
-        <v>0.01264672773202924</v>
+        <v>1.264672773202924</v>
       </c>
       <c r="E77" t="n">
-        <v>0.07232462735668199</v>
+        <v>7.232462735668199</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1060102432278109</v>
+        <v>10.60102432278109</v>
       </c>
       <c r="G77" t="n">
         <v>1.16034</v>
@@ -3772,19 +3772,19 @@
         <v>35551</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.01449182209278377</v>
+        <v>-1.449182209278377</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.02494980134405522</v>
+        <v>-2.494980134405522</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.01622944807369964</v>
+        <v>-1.622944807369964</v>
       </c>
       <c r="E78" t="n">
-        <v>0.08213219305355346</v>
+        <v>8.213219305355345</v>
       </c>
       <c r="F78" t="n">
-        <v>0.06333829888743159</v>
+        <v>6.333829888743159</v>
       </c>
       <c r="G78" t="n">
         <v>0.63091</v>
@@ -3815,19 +3815,19 @@
         <v>35582</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.04717241995209009</v>
+        <v>-4.71724199520901</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.05896910317957493</v>
+        <v>-5.896910317957504</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.07180526080578908</v>
+        <v>-7.180526080578908</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0751479368865724</v>
+        <v>7.51479368865724</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.004023705552089862</v>
+        <v>-0.4023705552089862</v>
       </c>
       <c r="G79" t="n">
         <v>0.20833</v>
@@ -3858,19 +3858,19 @@
         <v>35612</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.006245675354644153</v>
+        <v>-0.6245675354644153</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.01614375882897146</v>
+        <v>-1.614375882897146</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.03633010574542572</v>
+        <v>-3.633010574542572</v>
       </c>
       <c r="E80" t="n">
-        <v>0.08529106069041847</v>
+        <v>8.529106069041848</v>
       </c>
       <c r="F80" t="n">
-        <v>0.05728572531327458</v>
+        <v>5.728572531327458</v>
       </c>
       <c r="G80" t="n">
         <v>-0.62305</v>
@@ -3901,19 +3901,19 @@
         <v>35643</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.008750814884429969</v>
+        <v>-0.8750814884429969</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.01845831606714166</v>
+        <v>-1.845831606714177</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.02833444540908103</v>
+        <v>-2.833444540908103</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0874713599883421</v>
+        <v>8.74713599883421</v>
       </c>
       <c r="F81" t="n">
-        <v>0.06172724057293921</v>
+        <v>6.172724057293921</v>
       </c>
       <c r="G81" t="n">
         <v>-0.8230499999999999</v>
@@ -3944,19 +3944,19 @@
         <v>35674</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0482335659690567</v>
+        <v>4.82335659690567</v>
       </c>
       <c r="C82" t="n">
-        <v>0.03414472210323583</v>
+        <v>3.414472210323583</v>
       </c>
       <c r="D82" t="n">
-        <v>0.005079058090834865</v>
+        <v>0.5079058090834865</v>
       </c>
       <c r="E82" t="n">
-        <v>0.07177632882185359</v>
+        <v>7.177632882185359</v>
       </c>
       <c r="F82" t="n">
-        <v>0.07461475693585884</v>
+        <v>7.461475693585884</v>
       </c>
       <c r="G82" t="n">
         <v>-1.33745</v>
@@ -3987,19 +3987,19 @@
         <v>35704</v>
       </c>
       <c r="B83" t="n">
-        <v>0.04821903583741638</v>
+        <v>4.821903583741638</v>
       </c>
       <c r="C83" t="n">
-        <v>0.04867794542908266</v>
+        <v>4.867794542908266</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.004164349218704233</v>
+        <v>-0.4164349218704233</v>
       </c>
       <c r="E83" t="n">
-        <v>0.05472675561740936</v>
+        <v>5.472675561740936</v>
       </c>
       <c r="F83" t="n">
-        <v>0.04630156018304787</v>
+        <v>4.630156018304787</v>
       </c>
       <c r="G83" t="n">
         <v>-0.62435</v>
@@ -4030,19 +4030,19 @@
         <v>35735</v>
       </c>
       <c r="B84" t="n">
-        <v>0.03662444052073854</v>
+        <v>3.662444052073854</v>
       </c>
       <c r="C84" t="n">
-        <v>0.02933698265351925</v>
+        <v>2.933698265351947</v>
       </c>
       <c r="D84" t="n">
-        <v>0.02125846439191981</v>
+        <v>2.125846439191981</v>
       </c>
       <c r="E84" t="n">
-        <v>0.06513239674283833</v>
+        <v>6.513239674283833</v>
       </c>
       <c r="F84" t="n">
-        <v>0.07227789180117172</v>
+        <v>7.227789180117172</v>
       </c>
       <c r="G84" t="n">
         <v>-0.5175999999999999</v>
@@ -4073,19 +4073,19 @@
         <v>35765</v>
       </c>
       <c r="B85" t="n">
-        <v>0.02280795247697198</v>
+        <v>2.280795247697198</v>
       </c>
       <c r="C85" t="n">
-        <v>0.003314292916577921</v>
+        <v>0.3314292916577921</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.008513173577745059</v>
+        <v>-0.8513173577745059</v>
       </c>
       <c r="E85" t="n">
-        <v>0.04696469145487692</v>
+        <v>4.696469145487692</v>
       </c>
       <c r="F85" t="n">
-        <v>0.03716767905234697</v>
+        <v>3.716767905234697</v>
       </c>
       <c r="G85" t="n">
         <v>-0.71648</v>
@@ -4116,19 +4116,19 @@
         <v>35796</v>
       </c>
       <c r="B86" t="n">
-        <v>0.0228027778910842</v>
+        <v>2.28027778910842</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1439288344599772</v>
+        <v>14.39288344599774</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.00443368049161863</v>
+        <v>-0.443368049161863</v>
       </c>
       <c r="E86" t="n">
-        <v>0.04849453569360684</v>
+        <v>4.849453569360684</v>
       </c>
       <c r="F86" t="n">
-        <v>0.03209905292209325</v>
+        <v>3.209905292209325</v>
       </c>
       <c r="G86" t="n">
         <v>-0.4171</v>
@@ -4159,19 +4159,19 @@
         <v>35827</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.01247529193302566</v>
+        <v>-1.247529193302566</v>
       </c>
       <c r="C87" t="n">
-        <v>0.03839807107466786</v>
+        <v>3.839807107466786</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.03344300033442704</v>
+        <v>-3.344300033442704</v>
       </c>
       <c r="E87" t="n">
-        <v>0.05110229971021063</v>
+        <v>5.110229971021063</v>
       </c>
       <c r="F87" t="n">
-        <v>0.01680331806087598</v>
+        <v>1.680331806087598</v>
       </c>
       <c r="G87" t="n">
         <v>-0.20725</v>
@@ -4202,19 +4202,19 @@
         <v>35855</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.03044016390062387</v>
+        <v>-3.044016390062387</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.04768755963951576</v>
+        <v>-4.768755963951577</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.04817259829236065</v>
+        <v>-4.817259829236065</v>
       </c>
       <c r="E88" t="n">
-        <v>0.03989319340027242</v>
+        <v>3.989319340027242</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.007687364734611402</v>
+        <v>-0.7687364734611402</v>
       </c>
       <c r="G88" t="n">
         <v>0.10341</v>
@@ -4245,19 +4245,19 @@
         <v>35886</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.0140766312563998</v>
+        <v>-1.40766312563998</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.008320564981053158</v>
+        <v>-0.8320564981053269</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.04982729628682281</v>
+        <v>-4.98272962868228</v>
       </c>
       <c r="E89" t="n">
-        <v>0.04916198069369626</v>
+        <v>4.916198069369626</v>
       </c>
       <c r="F89" t="n">
-        <v>0.006213323300235052</v>
+        <v>0.6213323300235052</v>
       </c>
       <c r="G89" t="n">
         <v>0.4171</v>
@@ -4288,19 +4288,19 @@
         <v>35916</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.005070210288793731</v>
+        <v>-0.5070210288793731</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.03552172454329416</v>
+        <v>-3.552172454329416</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.0260732695660959</v>
+        <v>-2.60732695660959</v>
       </c>
       <c r="E90" t="n">
-        <v>0.03774808829034915</v>
+        <v>3.774808829034915</v>
       </c>
       <c r="F90" t="n">
-        <v>0.01316207185299789</v>
+        <v>1.316207185299789</v>
       </c>
       <c r="G90" t="n">
         <v>1.14943</v>
@@ -4331,19 +4331,19 @@
         <v>35947</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.02379304191495302</v>
+        <v>-2.379304191495302</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.00120176052440002</v>
+        <v>-0.120176052440002</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.01868495056988106</v>
+        <v>-1.868495056988106</v>
       </c>
       <c r="E91" t="n">
-        <v>0.02887257128139153</v>
+        <v>2.887257128139153</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01010284629239311</v>
+        <v>1.010284629239311</v>
       </c>
       <c r="G91" t="n">
         <v>0.6237</v>
@@ -4374,19 +4374,19 @@
         <v>35977</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.01915198805927909</v>
+        <v>-1.915198805927909</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.002782062763923454</v>
+        <v>-0.2782062763923343</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.02414521061576802</v>
+        <v>-2.414521061576802</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01892202345723804</v>
+        <v>1.892202345723804</v>
       </c>
       <c r="F92" t="n">
-        <v>0.004009085746734753</v>
+        <v>0.4009085746734753</v>
       </c>
       <c r="G92" t="n">
         <v>0.73145</v>
@@ -4417,19 +4417,19 @@
         <v>36008</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.03679332463321705</v>
+        <v>-3.679332463321705</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.02691824492001305</v>
+        <v>-2.691824492001293</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.03370942005762634</v>
+        <v>-3.370942005762634</v>
       </c>
       <c r="E93" t="n">
-        <v>0.02059437119423846</v>
+        <v>2.059437119423846</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.01159958146519524</v>
+        <v>-1.159958146519524</v>
       </c>
       <c r="G93" t="n">
         <v>0.41494</v>
@@ -4460,19 +4460,19 @@
         <v>36039</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.0644643494016619</v>
+        <v>-6.44643494016619</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.08344148187897149</v>
+        <v>-8.34414818789716</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.04139666442692613</v>
+        <v>-4.139666442692613</v>
       </c>
       <c r="E94" t="n">
-        <v>0.01583035446290215</v>
+        <v>1.583035446290215</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.03536723902238315</v>
+        <v>-3.536723902238315</v>
       </c>
       <c r="G94" t="n">
         <v>0.8342000000000001</v>
@@ -4503,19 +4503,19 @@
         <v>36069</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.04221755789513371</v>
+        <v>-4.22175578951337</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.05369553597123911</v>
+        <v>-5.369553597123899</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.0132031258632348</v>
+        <v>-1.32031258632348</v>
       </c>
       <c r="E95" t="n">
-        <v>0.03224434810320598</v>
+        <v>3.224434810320598</v>
       </c>
       <c r="F95" t="n">
-        <v>0.02472348777444644</v>
+        <v>2.472348777444644</v>
       </c>
       <c r="G95" t="n">
         <v>0.20942</v>
@@ -4546,19 +4546,19 @@
         <v>36100</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.03159904673123726</v>
+        <v>-3.159904673123726</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.01829384637128861</v>
+        <v>-1.829384637128884</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.03480527844743986</v>
+        <v>-3.480527844743986</v>
       </c>
       <c r="E96" t="n">
-        <v>0.005534475507164016</v>
+        <v>0.5534475507164016</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.03844003065753288</v>
+        <v>-3.844003065753288</v>
       </c>
       <c r="G96" t="n">
         <v>0.41623</v>
@@ -4589,19 +4589,19 @@
         <v>36130</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.02616494059232977</v>
+        <v>-2.616494059232977</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1039268349979094</v>
+        <v>10.39268349979092</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.03690584617753112</v>
+        <v>-3.690584617753112</v>
       </c>
       <c r="E97" t="n">
-        <v>0.02648082114152284</v>
+        <v>2.648082114152284</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.006445087426995566</v>
+        <v>-0.6445087426995566</v>
       </c>
       <c r="G97" t="n">
         <v>0.10309</v>
@@ -4632,19 +4632,19 @@
         <v>36161</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.01800693674157539</v>
+        <v>-1.800693674157539</v>
       </c>
       <c r="C98" t="n">
-        <v>0.01414515059271881</v>
+        <v>1.414515059271881</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.02523776373152942</v>
+        <v>-2.523776373152942</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.006013092479170035</v>
+        <v>-0.6013092479170035</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.0435641093220881</v>
+        <v>-4.35641093220881</v>
       </c>
       <c r="G98" t="n">
         <v>-0.20942</v>
@@ -4675,19 +4675,19 @@
         <v>36192</v>
       </c>
       <c r="B99" t="n">
-        <v>0.02103950846025615</v>
+        <v>2.103950846025615</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03088861109458119</v>
+        <v>3.088861109458119</v>
       </c>
       <c r="D99" t="n">
-        <v>0.000611291399214009</v>
+        <v>0.0611291399214009</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.003380219402653872</v>
+        <v>-0.3380219402653872</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.005011667463340364</v>
+        <v>-0.5011667463340364</v>
       </c>
       <c r="G99" t="n">
         <v>-0.20768</v>
@@ -4718,19 +4718,19 @@
         <v>36220</v>
       </c>
       <c r="B100" t="n">
-        <v>0.01031768438745528</v>
+        <v>1.031768438745528</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04180532897020561</v>
+        <v>4.180532897020561</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.001255691670250303</v>
+        <v>-0.1255691670250303</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.003166750601485524</v>
+        <v>-0.3166750601485524</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.00528088864608911</v>
+        <v>-0.528088864608911</v>
       </c>
       <c r="G100" t="n">
         <v>0.51653</v>
@@ -4761,19 +4761,19 @@
         <v>36251</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.01378609163355082</v>
+        <v>-1.378609163355082</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.01661710271477312</v>
+        <v>-1.661710271477324</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.01989933987517223</v>
+        <v>-1.989933987517223</v>
       </c>
       <c r="E101" t="n">
-        <v>0.006028635436212681</v>
+        <v>0.6028635436212681</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.01445035583979615</v>
+        <v>-1.445035583979615</v>
       </c>
       <c r="G101" t="n">
         <v>0.62305</v>
@@ -4804,19 +4804,19 @@
         <v>36281</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.004617014516962503</v>
+        <v>-0.4617014516962503</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03617098800325702</v>
+        <v>3.617098800325702</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.0238724013859053</v>
+        <v>-2.38724013859053</v>
       </c>
       <c r="E102" t="n">
-        <v>0.01766290482593957</v>
+        <v>1.766290482593957</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.003769194769926432</v>
+        <v>-0.3769194769926432</v>
       </c>
       <c r="G102" t="n">
         <v>0.20661</v>
@@ -4847,19 +4847,19 @@
         <v>36312</v>
       </c>
       <c r="B103" t="n">
-        <v>0.02638951388967681</v>
+        <v>2.638951388967681</v>
       </c>
       <c r="C103" t="n">
-        <v>0.04538846330880131</v>
+        <v>4.538846330880131</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.0076454246157317</v>
+        <v>-0.76454246157317</v>
       </c>
       <c r="E103" t="n">
-        <v>0.01713276719908552</v>
+        <v>1.713276719908552</v>
       </c>
       <c r="F103" t="n">
-        <v>0.01449742268041221</v>
+        <v>1.449742268041221</v>
       </c>
       <c r="G103" t="n">
         <v>1.13636</v>
@@ -4890,19 +4890,19 @@
         <v>36342</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0424583860747918</v>
+        <v>4.24583860747918</v>
       </c>
       <c r="C104" t="n">
-        <v>0.07669000171891738</v>
+        <v>7.669000171891738</v>
       </c>
       <c r="D104" t="n">
-        <v>0.01205429173177297</v>
+        <v>1.205429173177297</v>
       </c>
       <c r="E104" t="n">
-        <v>0.02613291395590611</v>
+        <v>2.613291395590611</v>
       </c>
       <c r="F104" t="n">
-        <v>0.05148543224400415</v>
+        <v>5.148543224400415</v>
       </c>
       <c r="G104" t="n">
         <v>1.03734</v>
@@ -4933,19 +4933,19 @@
         <v>36373</v>
       </c>
       <c r="B105" t="n">
-        <v>0.04626207456999842</v>
+        <v>4.626207456999842</v>
       </c>
       <c r="C105" t="n">
-        <v>0.05333564026405901</v>
+        <v>5.333564026405901</v>
       </c>
       <c r="D105" t="n">
-        <v>0.02819459332646113</v>
+        <v>2.819459332646113</v>
       </c>
       <c r="E105" t="n">
-        <v>0.02029229425754364</v>
+        <v>2.029229425754364</v>
       </c>
       <c r="F105" t="n">
-        <v>0.04723260385312966</v>
+        <v>4.723260385312966</v>
       </c>
       <c r="G105" t="n">
         <v>0.82645</v>
@@ -4976,19 +4976,19 @@
         <v>36404</v>
       </c>
       <c r="B106" t="n">
-        <v>0.04441317870454231</v>
+        <v>4.441317870454231</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0822571748540184</v>
+        <v>8.225717485401841</v>
       </c>
       <c r="D106" t="n">
-        <v>0.04776982217714654</v>
+        <v>4.776982217714654</v>
       </c>
       <c r="E106" t="n">
-        <v>0.03662390643250135</v>
+        <v>3.662390643250135</v>
       </c>
       <c r="F106" t="n">
-        <v>0.07187150583129243</v>
+        <v>7.187150583129243</v>
       </c>
       <c r="G106" t="n">
         <v>0.62048</v>
@@ -5019,19 +5019,19 @@
         <v>36434</v>
       </c>
       <c r="B107" t="n">
-        <v>0.0758745294293075</v>
+        <v>7.58745294293075</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1302897989008336</v>
+        <v>13.02897989008336</v>
       </c>
       <c r="D107" t="n">
-        <v>0.04098668347672563</v>
+        <v>4.098668347672563</v>
       </c>
       <c r="E107" t="n">
-        <v>0.05051305789971039</v>
+        <v>5.051305789971039</v>
       </c>
       <c r="F107" t="n">
-        <v>0.086495118534065</v>
+        <v>8.6495118534065</v>
       </c>
       <c r="G107" t="n">
         <v>1.88088</v>
@@ -5062,19 +5062,19 @@
         <v>36465</v>
       </c>
       <c r="B108" t="n">
-        <v>0.06676790237802765</v>
+        <v>6.676790237802765</v>
       </c>
       <c r="C108" t="n">
-        <v>0.06070003939976432</v>
+        <v>6.070003939976454</v>
       </c>
       <c r="D108" t="n">
-        <v>0.05111618799587347</v>
+        <v>5.111618799587347</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0603989756983252</v>
+        <v>6.03989756983252</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1087659304384447</v>
+        <v>10.87659304384447</v>
       </c>
       <c r="G108" t="n">
         <v>1.86528</v>
@@ -5105,19 +5105,19 @@
         <v>36495</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.03501606612731356</v>
+        <v>-3.501606612731356</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.02424863703965863</v>
+        <v>-2.424863703965863</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.0385404045683394</v>
+        <v>-3.85404045683394</v>
       </c>
       <c r="E109" t="n">
-        <v>0.07469437876899976</v>
+        <v>7.469437876899976</v>
       </c>
       <c r="F109" t="n">
-        <v>0.03724623812097261</v>
+        <v>3.724623812097261</v>
       </c>
       <c r="G109" t="n">
         <v>2.05973</v>
@@ -5148,19 +5148,19 @@
         <v>36526</v>
       </c>
       <c r="B110" t="n">
-        <v>-0.02908171637944201</v>
+        <v>-2.908171637944201</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.04356695049772852</v>
+        <v>-4.356695049772863</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.02784144443563674</v>
+        <v>-2.784144443563674</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0924628395579612</v>
+        <v>9.24628395579612</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05328647176479495</v>
+        <v>5.328647176479495</v>
       </c>
       <c r="G110" t="n">
         <v>2.51836</v>
@@ -5191,19 +5191,19 @@
         <v>36557</v>
       </c>
       <c r="B111" t="n">
-        <v>0.03962576868127154</v>
+        <v>3.962576868127154</v>
       </c>
       <c r="C111" t="n">
-        <v>0.04652696131883971</v>
+        <v>4.652696131883993</v>
       </c>
       <c r="D111" t="n">
-        <v>0.03217351225189624</v>
+        <v>3.217351225189624</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0761335285981537</v>
+        <v>7.61335285981537</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1127679873081209</v>
+        <v>11.27679873081209</v>
       </c>
       <c r="G111" t="n">
         <v>2.70552</v>
@@ -5234,19 +5234,19 @@
         <v>36586</v>
       </c>
       <c r="B112" t="n">
-        <v>0.06499415498188532</v>
+        <v>6.499415498188532</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0656349562320595</v>
+        <v>6.56349562320595</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0750795481378117</v>
+        <v>7.50795481378117</v>
       </c>
       <c r="E112" t="n">
-        <v>0.08432126948445506</v>
+        <v>8.432126948445507</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1712885055447986</v>
+        <v>17.12885055447986</v>
       </c>
       <c r="G112" t="n">
         <v>2.56937</v>
@@ -5277,19 +5277,19 @@
         <v>36617</v>
       </c>
       <c r="B113" t="n">
-        <v>0.05536070844120267</v>
+        <v>5.536070844120267</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1091790567679578</v>
+        <v>10.91790567679578</v>
       </c>
       <c r="D113" t="n">
-        <v>0.08215577804360819</v>
+        <v>8.215577804360819</v>
       </c>
       <c r="E113" t="n">
-        <v>0.07252683837569474</v>
+        <v>7.252683837569474</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1622719638731658</v>
+        <v>16.22719638731658</v>
       </c>
       <c r="G113" t="n">
         <v>3.09598</v>
@@ -5320,19 +5320,19 @@
         <v>36647</v>
       </c>
       <c r="B114" t="n">
-        <v>0.07123971436492416</v>
+        <v>7.123971436492416</v>
       </c>
       <c r="C114" t="n">
-        <v>0.07811741444507381</v>
+        <v>7.811741444507381</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1068368944616918</v>
+        <v>10.68368944616918</v>
       </c>
       <c r="E114" t="n">
-        <v>0.07941020300864521</v>
+        <v>7.941020300864521</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2035933697698749</v>
+        <v>20.35933697698749</v>
       </c>
       <c r="G114" t="n">
         <v>3.50515</v>
@@ -5363,19 +5363,19 @@
         <v>36678</v>
       </c>
       <c r="B115" t="n">
-        <v>0.06914609921474035</v>
+        <v>6.914609921474035</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0655064732887245</v>
+        <v>6.55064732887245</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1285773323529276</v>
+        <v>12.85773323529276</v>
       </c>
       <c r="E115" t="n">
-        <v>0.06514259150852508</v>
+        <v>6.514259150852508</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2245111236011343</v>
+        <v>22.45111236011343</v>
       </c>
       <c r="G115" t="n">
         <v>3.88151</v>
@@ -5406,19 +5406,19 @@
         <v>36708</v>
       </c>
       <c r="B116" t="n">
-        <v>0.01412431708194339</v>
+        <v>1.412431708194339</v>
       </c>
       <c r="C116" t="n">
-        <v>0.007701959463753738</v>
+        <v>0.7701959463753738</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0731251426268027</v>
+        <v>7.31251426268027</v>
       </c>
       <c r="E116" t="n">
-        <v>0.07196718392885959</v>
+        <v>7.196718392885959</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1747113461286061</v>
+        <v>17.47113461286061</v>
       </c>
       <c r="G116" t="n">
         <v>4.20945</v>
@@ -5449,19 +5449,19 @@
         <v>36739</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.001334916194190128</v>
+        <v>-0.1334916194190128</v>
       </c>
       <c r="C117" t="n">
-        <v>0.006029834919857979</v>
+        <v>0.6029834919858201</v>
       </c>
       <c r="D117" t="n">
-        <v>0.02760587136484771</v>
+        <v>2.760587136484771</v>
       </c>
       <c r="E117" t="n">
-        <v>0.06494267726252434</v>
+        <v>6.494267726252434</v>
       </c>
       <c r="F117" t="n">
-        <v>0.108451988572668</v>
+        <v>10.8451988572668</v>
       </c>
       <c r="G117" t="n">
         <v>4.30328</v>
@@ -5492,19 +5492,19 @@
         <v>36770</v>
       </c>
       <c r="B118" t="n">
-        <v>0.01605790432531995</v>
+        <v>1.605790432531995</v>
       </c>
       <c r="C118" t="n">
-        <v>0.005616480965633164</v>
+        <v>0.5616480965633164</v>
       </c>
       <c r="D118" t="n">
-        <v>0.03236479560634775</v>
+        <v>3.236479560634775</v>
       </c>
       <c r="E118" t="n">
-        <v>0.07000846350079715</v>
+        <v>7.000846350079715</v>
       </c>
       <c r="F118" t="n">
-        <v>0.08823613191868507</v>
+        <v>8.823613191868507</v>
       </c>
       <c r="G118" t="n">
         <v>4.72765</v>
@@ -5535,19 +5535,19 @@
         <v>36800</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0002486174958054033</v>
+        <v>0.02486174958054033</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.02738537359662963</v>
+        <v>-2.738537359662963</v>
       </c>
       <c r="D119" t="n">
-        <v>0.03957046363911942</v>
+        <v>3.957046363911942</v>
       </c>
       <c r="E119" t="n">
-        <v>0.04960600885138877</v>
+        <v>4.960600885138877</v>
       </c>
       <c r="F119" t="n">
-        <v>0.07366926541297358</v>
+        <v>7.366926541297358</v>
       </c>
       <c r="G119" t="n">
         <v>4</v>
@@ -5578,19 +5578,19 @@
         <v>36831</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.007336395215860048</v>
+        <v>-0.7336395215860048</v>
       </c>
       <c r="C120" t="n">
-        <v>0.004097459147072602</v>
+        <v>0.409745914707238</v>
       </c>
       <c r="D120" t="n">
-        <v>0.05623537978247084</v>
+        <v>5.623537978247084</v>
       </c>
       <c r="E120" t="n">
-        <v>0.08064305930528182</v>
+        <v>8.064305930528182</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1334198450412811</v>
+        <v>13.34198450412811</v>
       </c>
       <c r="G120" t="n">
         <v>3.56053</v>
@@ -5621,19 +5621,19 @@
         <v>36861</v>
       </c>
       <c r="B121" t="n">
-        <v>0.0740420472704979</v>
+        <v>7.40420472704979</v>
       </c>
       <c r="C121" t="n">
-        <v>0.03126587092685051</v>
+        <v>3.126587092685051</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1198084075145711</v>
+        <v>11.98084075145711</v>
       </c>
       <c r="E121" t="n">
-        <v>0.02382700508574609</v>
+        <v>2.382700508574609</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1287012258660858</v>
+        <v>12.87012258660858</v>
       </c>
       <c r="G121" t="n">
         <v>3.63269</v>
@@ -5664,19 +5664,19 @@
         <v>36892</v>
       </c>
       <c r="B122" t="n">
-        <v>0.06978751872334499</v>
+        <v>6.978751872334499</v>
       </c>
       <c r="C122" t="n">
-        <v>0.05558402730370471</v>
+        <v>5.558402730370493</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0997614528520947</v>
+        <v>9.976145285209469</v>
       </c>
       <c r="E122" t="n">
-        <v>0.04444360443181061</v>
+        <v>4.444360443181061</v>
       </c>
       <c r="F122" t="n">
-        <v>0.1382120081385243</v>
+        <v>13.82120081385243</v>
       </c>
       <c r="G122" t="n">
         <v>3.07062</v>
@@ -5707,19 +5707,19 @@
         <v>36923</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.04030055230549567</v>
+        <v>-4.030055230549568</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.04149284372079387</v>
+        <v>-4.149284372079387</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0276978294436514</v>
+        <v>2.76978294436514</v>
       </c>
       <c r="E123" t="n">
-        <v>0.06311450423323728</v>
+        <v>6.311450423323728</v>
       </c>
       <c r="F123" t="n">
-        <v>0.08246739088900434</v>
+        <v>8.246739088900434</v>
       </c>
       <c r="G123" t="n">
         <v>3.03951</v>
@@ -5750,19 +5750,19 @@
         <v>36951</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.01957370288276628</v>
+        <v>-1.957370288276628</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.01293885828774721</v>
+        <v>-1.293885828774721</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.04048454897881237</v>
+        <v>-4.048454897881237</v>
       </c>
       <c r="E124" t="n">
-        <v>0.03326057332283461</v>
+        <v>3.326057332283461</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.01283187399696206</v>
+        <v>-1.283187399696206</v>
       </c>
       <c r="G124" t="n">
         <v>2.40481</v>
@@ -5793,19 +5793,19 @@
         <v>36982</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.02357840083562435</v>
+        <v>-2.357840083562435</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.01949198292364251</v>
+        <v>-1.949198292364251</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.05717436180233093</v>
+        <v>-5.717436180233094</v>
       </c>
       <c r="E125" t="n">
-        <v>0.05323511868710051</v>
+        <v>5.323511868710051</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.006825035341955998</v>
+        <v>-0.6825035341955998</v>
       </c>
       <c r="G125" t="n">
         <v>1.8018</v>
@@ -5836,19 +5836,19 @@
         <v>37012</v>
       </c>
       <c r="B126" t="n">
-        <v>-0.05132198643160768</v>
+        <v>-5.132198643160768</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.04657556519689043</v>
+        <v>-4.657556519689043</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.07672029172410511</v>
+        <v>-7.672029172410511</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0373989635428893</v>
+        <v>3.73989635428893</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.03611357239653923</v>
+        <v>-3.611357239653923</v>
       </c>
       <c r="G126" t="n">
         <v>1.49402</v>
@@ -5879,19 +5879,19 @@
         <v>37043</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.04560466957907472</v>
+        <v>-4.560466957907472</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.02549834046155985</v>
+        <v>-2.549834046155974</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.09954512775922586</v>
+        <v>-9.954512775922586</v>
       </c>
       <c r="E127" t="n">
-        <v>0.04659101067845905</v>
+        <v>4.659101067845905</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.03954027155706596</v>
+        <v>-3.954027155706596</v>
       </c>
       <c r="G127" t="n">
         <v>0.7866300000000001</v>
@@ -5922,19 +5922,19 @@
         <v>37073</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.02637317529330596</v>
+        <v>-2.637317529330596</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.001625008943992867</v>
+        <v>-0.1625008943992867</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.07524736295634049</v>
+        <v>-7.52473629563405</v>
       </c>
       <c r="E128" t="n">
-        <v>0.03455979343431403</v>
+        <v>3.455979343431403</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.015120222163301</v>
+        <v>-1.5120222163301</v>
       </c>
       <c r="G128" t="n">
         <v>0.29557</v>
@@ -5965,19 +5965,19 @@
         <v>37104</v>
       </c>
       <c r="B129" t="n">
-        <v>0.01493723178567286</v>
+        <v>1.493723178567286</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02914576282039105</v>
+        <v>2.914576282039105</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0337019044764274</v>
+        <v>-3.37019044764274</v>
       </c>
       <c r="E129" t="n">
-        <v>0.04222767251297155</v>
+        <v>4.222767251297155</v>
       </c>
       <c r="F129" t="n">
-        <v>0.04022633257739439</v>
+        <v>4.022633257739439</v>
       </c>
       <c r="G129" t="n">
         <v>0.68762</v>
@@ -6008,19 +6008,19 @@
         <v>37135</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.3211260084380412</v>
+        <v>-32.11260084380412</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.2565157988197249</v>
+        <v>-25.65157988197249</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.2376242285390279</v>
+        <v>-23.76242285390279</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.01055298598711041</v>
+        <v>-1.055298598711041</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.2517763622048853</v>
+        <v>-25.17763622048853</v>
       </c>
       <c r="G130" t="n">
         <v>-0.09814000000000001</v>
@@ -6051,19 +6051,19 @@
         <v>37165</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.2979367111357416</v>
+        <v>-29.79367111357416</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.2385575109277954</v>
+        <v>-23.85575109277954</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.2450161810218342</v>
+        <v>-24.50161810218342</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.00493056445856821</v>
+        <v>-0.493056445856821</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.2595588329101972</v>
+        <v>-25.95588329101972</v>
       </c>
       <c r="G131" t="n">
         <v>-4.63511</v>
@@ -6094,19 +6094,19 @@
         <v>37196</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.2652529921983906</v>
+        <v>-26.52529921983906</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.1709875367166299</v>
+        <v>-17.09875367166298</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2281237548467879</v>
+        <v>-22.81237548467879</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.04126357921941393</v>
+        <v>-4.126357921941393</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.2731972271349014</v>
+        <v>-27.31972271349014</v>
       </c>
       <c r="G132" t="n">
         <v>-5.40275</v>
@@ -6137,19 +6137,19 @@
         <v>37226</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.163288712590307</v>
+        <v>-16.3288712590307</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.1258164934311191</v>
+        <v>-12.58164934311191</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.1625349928669745</v>
+        <v>-16.25349928669745</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.02046194294066006</v>
+        <v>-2.046194294066006</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.1814523518690192</v>
+        <v>-18.14523518690192</v>
       </c>
       <c r="G133" t="n">
         <v>-5.84226</v>
@@ -6180,19 +6180,19 @@
         <v>37257</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.1606181569250243</v>
+        <v>-16.06181569250244</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1176720116367297</v>
+        <v>-11.76720116367297</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.1497776793513668</v>
+        <v>-14.97776793513668</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.05105279953188835</v>
+        <v>-5.105279953188835</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.2022880448888372</v>
+        <v>-20.22880448888372</v>
       </c>
       <c r="G134" t="n">
         <v>-4.56802</v>
@@ -6223,19 +6223,19 @@
         <v>37288</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.08043000788744059</v>
+        <v>-8.04300078874406</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.04047570613370199</v>
+        <v>-4.04757061337021</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.1067955925886961</v>
+        <v>-10.67955925886961</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.05357301146058546</v>
+        <v>-5.357301146058546</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.1748126701986912</v>
+        <v>-17.48126701986912</v>
       </c>
       <c r="G135" t="n">
         <v>-4.42478</v>
@@ -6266,19 +6266,19 @@
         <v>37316</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.09756207549320783</v>
+        <v>-9.756207549320784</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.05835673559820775</v>
+        <v>-5.835673559820775</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.07449273169386161</v>
+        <v>-7.449273169386162</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.01993795923905595</v>
+        <v>-1.993795923905595</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.09488974235579994</v>
+        <v>-9.488974235579995</v>
       </c>
       <c r="G136" t="n">
         <v>-3.91389</v>
@@ -6309,19 +6309,19 @@
         <v>37347</v>
       </c>
       <c r="B137" t="n">
-        <v>-0.09440852523947929</v>
+        <v>-9.440852523947928</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.09153220920096272</v>
+        <v>-9.153220920096272</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.05647275379597505</v>
+        <v>-5.647275379597505</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.04625227846217483</v>
+        <v>-4.625227846217483</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.1085543620644486</v>
+        <v>-10.85543620644486</v>
       </c>
       <c r="G137" t="n">
         <v>-3.44149</v>
@@ -6352,19 +6352,19 @@
         <v>37377</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.02925241201437456</v>
+        <v>-2.925241201437456</v>
       </c>
       <c r="C138" t="n">
-        <v>0.01190575215746925</v>
+        <v>1.190575215746925</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.02312090818987766</v>
+        <v>-2.312090818987766</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.04818296756438911</v>
+        <v>-4.818296756438912</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.07460711750988547</v>
+        <v>-7.460711750988547</v>
       </c>
       <c r="G138" t="n">
         <v>-2.64966</v>
@@ -6395,19 +6395,19 @@
         <v>37408</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.009086286746829764</v>
+        <v>-0.9086286746829764</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.049386225017496e-05</v>
+        <v>-0.008049386225006394</v>
       </c>
       <c r="D139" t="n">
-        <v>0.002647749967994217</v>
+        <v>0.2647749967994217</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.04025092533760954</v>
+        <v>-4.025092533760954</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.02941036832222188</v>
+        <v>-2.941036832222188</v>
       </c>
       <c r="G139" t="n">
         <v>-2.2439</v>
@@ -6438,19 +6438,19 @@
         <v>37438</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.05289190342390859</v>
+        <v>-5.289190342390859</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.02690306903047923</v>
+        <v>-2.690306903047934</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.02486813569589807</v>
+        <v>-2.486813569589807</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.03706870162812559</v>
+        <v>-3.706870162812559</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.0453707377205973</v>
+        <v>-4.537073772059729</v>
       </c>
       <c r="G140" t="n">
         <v>-1.96464</v>
@@ -6481,19 +6481,19 @@
         <v>37469</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.04770926965302213</v>
+        <v>-4.770926965302213</v>
       </c>
       <c r="C141" t="n">
-        <v>0.008301820634488255</v>
+        <v>0.8301820634488033</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.01004233211537309</v>
+        <v>-1.004233211537309</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.03300208288270756</v>
+        <v>-3.300208288270756</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.02685496881056437</v>
+        <v>-2.685496881056437</v>
       </c>
       <c r="G141" t="n">
         <v>-2.43902</v>
@@ -6524,19 +6524,19 @@
         <v>37500</v>
       </c>
       <c r="B142" t="n">
-        <v>0.3016131711873009</v>
+        <v>30.16131711873009</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3917053468602678</v>
+        <v>39.17053468602678</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1555090722367229</v>
+        <v>15.55090722367229</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0004099653998825836</v>
+        <v>0.04099653998825836</v>
       </c>
       <c r="F142" t="n">
-        <v>0.1490492507073942</v>
+        <v>14.90492507073942</v>
       </c>
       <c r="G142" t="n">
         <v>-2.25933</v>
@@ -6567,19 +6567,19 @@
         <v>37530</v>
       </c>
       <c r="B143" t="n">
-        <v>0.3135068080887156</v>
+        <v>31.35068080887156</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3109770965982719</v>
+        <v>31.09770965982719</v>
       </c>
       <c r="D143" t="n">
-        <v>0.208737713936997</v>
+        <v>20.8737713936997</v>
       </c>
       <c r="E143" t="n">
-        <v>0.004444086010580328</v>
+        <v>0.4444086010580328</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2197643297588241</v>
+        <v>21.97643297588241</v>
       </c>
       <c r="G143" t="n">
         <v>2.06825</v>
@@ -6610,19 +6610,19 @@
         <v>37561</v>
       </c>
       <c r="B144" t="n">
-        <v>0.2643281906218475</v>
+        <v>26.43281906218476</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2270115551395633</v>
+        <v>22.70115551395635</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1597189618426085</v>
+        <v>15.97189618426085</v>
       </c>
       <c r="E144" t="n">
-        <v>0.01049531699619544</v>
+        <v>1.049531699619544</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1663717604399921</v>
+        <v>16.63717604399921</v>
       </c>
       <c r="G144" t="n">
         <v>3.63448</v>
@@ -6653,19 +6653,19 @@
         <v>37591</v>
       </c>
       <c r="B145" t="n">
-        <v>0.1528767999722598</v>
+        <v>15.28767999722598</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1352633805387153</v>
+        <v>13.52633805387151</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1493538442592246</v>
+        <v>14.93538442592246</v>
       </c>
       <c r="E145" t="n">
-        <v>0.01802905374836983</v>
+        <v>1.802905374836983</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1911551107967715</v>
+        <v>19.11551107967715</v>
       </c>
       <c r="G145" t="n">
         <v>3.61944</v>
@@ -6696,19 +6696,19 @@
         <v>37622</v>
       </c>
       <c r="B146" t="n">
-        <v>0.1174718154184673</v>
+        <v>11.74718154184673</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0604837979200572</v>
+        <v>6.048379792005698</v>
       </c>
       <c r="D146" t="n">
-        <v>0.09312137274185606</v>
+        <v>9.312137274185606</v>
       </c>
       <c r="E146" t="n">
-        <v>0.05682983985760215</v>
+        <v>5.682983985760215</v>
       </c>
       <c r="F146" t="n">
-        <v>0.1652328297762562</v>
+        <v>16.52328297762562</v>
       </c>
       <c r="G146" t="n">
         <v>3.43392</v>
@@ -6739,19 +6739,19 @@
         <v>37653</v>
       </c>
       <c r="B147" t="n">
-        <v>0.005073849879098313</v>
+        <v>0.5073849879098313</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.000375229347491346</v>
+        <v>-0.03752293474912349</v>
       </c>
       <c r="D147" t="n">
-        <v>0.03303251744698232</v>
+        <v>3.303251744698232</v>
       </c>
       <c r="E147" t="n">
-        <v>0.03478823384021879</v>
+        <v>3.478823384021879</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0477863218005119</v>
+        <v>4.77863218005119</v>
       </c>
       <c r="G147" t="n">
         <v>2.98354</v>
@@ -6782,19 +6782,19 @@
         <v>37681</v>
       </c>
       <c r="B148" t="n">
-        <v>-0.008974814015424104</v>
+        <v>-0.8974814015424104</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.03412282079427031</v>
+        <v>-3.41228207942702</v>
       </c>
       <c r="D148" t="n">
-        <v>0.02064439223716308</v>
+        <v>2.064439223716308</v>
       </c>
       <c r="E148" t="n">
-        <v>0.02010234908396891</v>
+        <v>2.010234908396891</v>
       </c>
       <c r="F148" t="n">
-        <v>0.03540358694737544</v>
+        <v>3.540358694737544</v>
       </c>
       <c r="G148" t="n">
         <v>2.95316</v>
@@ -6825,19 +6825,19 @@
         <v>37712</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.02983634348907205</v>
+        <v>-2.983634348907205</v>
       </c>
       <c r="C149" t="n">
-        <v>0.03667869656924982</v>
+        <v>3.667869656925005</v>
       </c>
       <c r="D149" t="n">
-        <v>0.02525818846052719</v>
+        <v>2.525818846052719</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0332977748230423</v>
+        <v>3.32977748230423</v>
       </c>
       <c r="F149" t="n">
-        <v>0.05686979115563129</v>
+        <v>5.686979115563129</v>
       </c>
       <c r="G149" t="n">
         <v>1.93483</v>
@@ -6868,19 +6868,19 @@
         <v>37742</v>
       </c>
       <c r="B150" t="n">
-        <v>-0.07488167445562122</v>
+        <v>-7.488167445562121</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.0488769387256881</v>
+        <v>-4.887693872568811</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.01908265837392842</v>
+        <v>-1.908265837392842</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0359946363557373</v>
+        <v>3.59946363557373</v>
       </c>
       <c r="F150" t="n">
-        <v>0.008334413024454257</v>
+        <v>0.8334413024454257</v>
       </c>
       <c r="G150" t="n">
         <v>1.5121</v>
@@ -6911,19 +6911,19 @@
         <v>37773</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.07608653597156712</v>
+        <v>-7.608653597156712</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.05562242703890352</v>
+        <v>-5.562242703890352</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.02322739465162538</v>
+        <v>-2.322739465162538</v>
       </c>
       <c r="E151" t="n">
-        <v>0.03074913999142459</v>
+        <v>3.074913999142459</v>
       </c>
       <c r="F151" t="n">
-        <v>0.01001064523915174</v>
+        <v>1.001064523915174</v>
       </c>
       <c r="G151" t="n">
         <v>0.998</v>
@@ -6954,19 +6954,19 @@
         <v>37803</v>
       </c>
       <c r="B152" t="n">
-        <v>0.003513401855108178</v>
+        <v>0.3513401855108178</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.004042351088964558</v>
+        <v>-0.4042351088964669</v>
       </c>
       <c r="D152" t="n">
-        <v>0.04469245126102406</v>
+        <v>4.469245126102406</v>
       </c>
       <c r="E152" t="n">
-        <v>0.02066269850825719</v>
+        <v>2.066269850825719</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0817790775667453</v>
+        <v>8.177907756674529</v>
       </c>
       <c r="G152" t="n">
         <v>1.80361</v>
@@ -6997,19 +6997,19 @@
         <v>37834</v>
       </c>
       <c r="B153" t="n">
-        <v>0.01492872359551001</v>
+        <v>1.492872359551001</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.006951342290008156</v>
+        <v>-0.6951342290008267</v>
       </c>
       <c r="D153" t="n">
-        <v>0.06078267356546641</v>
+        <v>6.078267356546641</v>
       </c>
       <c r="E153" t="n">
-        <v>0.01580424990894347</v>
+        <v>1.580424990894347</v>
       </c>
       <c r="F153" t="n">
-        <v>0.07346371640021476</v>
+        <v>7.346371640021476</v>
       </c>
       <c r="G153" t="n">
         <v>2.3</v>
@@ -7040,19 +7040,19 @@
         <v>37865</v>
       </c>
       <c r="B154" t="n">
-        <v>0.02712264724930513</v>
+        <v>2.712264724930513</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.08773653637340928</v>
+        <v>-8.773653637340917</v>
       </c>
       <c r="D154" t="n">
-        <v>0.07801214109110344</v>
+        <v>7.801214109110344</v>
       </c>
       <c r="E154" t="n">
-        <v>0.03959509980200426</v>
+        <v>3.959509980200426</v>
       </c>
       <c r="F154" t="n">
-        <v>0.1216609848861465</v>
+        <v>12.16609848861465</v>
       </c>
       <c r="G154" t="n">
         <v>2.61307</v>
@@ -7083,19 +7083,19 @@
         <v>37895</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.003749719127072337</v>
+        <v>-0.3749719127072337</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.03927633201968583</v>
+        <v>-3.927633201968594</v>
       </c>
       <c r="D155" t="n">
-        <v>0.03639219731231469</v>
+        <v>3.639219731231469</v>
       </c>
       <c r="E155" t="n">
-        <v>0.02615864436535253</v>
+        <v>2.615864436535253</v>
       </c>
       <c r="F155" t="n">
-        <v>0.06045265715551817</v>
+        <v>6.045265715551817</v>
       </c>
       <c r="G155" t="n">
         <v>2.9382</v>
@@ -7126,19 +7126,19 @@
         <v>37926</v>
       </c>
       <c r="B156" t="n">
-        <v>0.01565593404197729</v>
+        <v>1.565593404197729</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.04693970428817384</v>
+        <v>-4.693970428817384</v>
       </c>
       <c r="D156" t="n">
-        <v>0.04943323825180768</v>
+        <v>4.943323825180768</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0344658177278474</v>
+        <v>3.44658177278474</v>
       </c>
       <c r="F156" t="n">
-        <v>0.08246325891903794</v>
+        <v>8.246325891903794</v>
       </c>
       <c r="G156" t="n">
         <v>2.40481</v>
@@ -7169,19 +7169,19 @@
         <v>37956</v>
       </c>
       <c r="B157" t="n">
-        <v>0.02444381889983505</v>
+        <v>2.444381889983505</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.008874955499054371</v>
+        <v>-0.887495549905426</v>
       </c>
       <c r="D157" t="n">
-        <v>0.08068033764190274</v>
+        <v>8.068033764190275</v>
       </c>
       <c r="E157" t="n">
-        <v>0.03190075243470991</v>
+        <v>3.190075243470991</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1293225285213986</v>
+        <v>12.93225285213986</v>
       </c>
       <c r="G157" t="n">
         <v>3.69261</v>
@@ -7212,19 +7212,19 @@
         <v>37987</v>
       </c>
       <c r="B158" t="n">
-        <v>0.001692178166633473</v>
+        <v>0.1692178166633473</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02462254925445406</v>
+        <v>2.462254925445406</v>
       </c>
       <c r="D158" t="n">
-        <v>0.07125304189870896</v>
+        <v>7.125304189870896</v>
       </c>
       <c r="E158" t="n">
-        <v>0.01261550140923018</v>
+        <v>1.261550140923018</v>
       </c>
       <c r="F158" t="n">
-        <v>0.07732474790243948</v>
+        <v>7.732474790243948</v>
       </c>
       <c r="G158" t="n">
         <v>3.21932</v>
@@ -7255,19 +7255,19 @@
         <v>38018</v>
       </c>
       <c r="B159" t="n">
-        <v>0.07983270788494723</v>
+        <v>7.983270788494723</v>
       </c>
       <c r="C159" t="n">
-        <v>0.07120620369416297</v>
+        <v>7.120620369416275</v>
       </c>
       <c r="D159" t="n">
-        <v>0.07747162842630306</v>
+        <v>7.747162842630306</v>
       </c>
       <c r="E159" t="n">
-        <v>0.02475046150703175</v>
+        <v>2.475046150703175</v>
       </c>
       <c r="F159" t="n">
-        <v>0.08905474642629141</v>
+        <v>8.905474642629141</v>
       </c>
       <c r="G159" t="n">
         <v>3.6963</v>
@@ -7298,19 +7298,19 @@
         <v>38047</v>
       </c>
       <c r="B160" t="n">
-        <v>0.07065338931225584</v>
+        <v>7.065338931225584</v>
       </c>
       <c r="C160" t="n">
-        <v>0.07085371325592771</v>
+        <v>7.085371325592771</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1017509864099093</v>
+        <v>10.17509864099093</v>
       </c>
       <c r="E160" t="n">
-        <v>0.03052217519402767</v>
+        <v>3.052217519402767</v>
       </c>
       <c r="F160" t="n">
-        <v>0.1276381225106382</v>
+        <v>12.76381225106382</v>
       </c>
       <c r="G160" t="n">
         <v>3.26409</v>
@@ -7341,19 +7341,19 @@
         <v>38078</v>
       </c>
       <c r="B161" t="n">
-        <v>0.1372206589458198</v>
+        <v>13.72206589458198</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08035797104149767</v>
+        <v>8.035797104149744</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1128245627821238</v>
+        <v>11.28245627821238</v>
       </c>
       <c r="E161" t="n">
-        <v>0.03367010693792616</v>
+        <v>3.367010693792616</v>
       </c>
       <c r="F161" t="n">
-        <v>0.152379816537932</v>
+        <v>15.2379816537932</v>
       </c>
       <c r="G161" t="n">
         <v>4.3956</v>
@@ -7384,19 +7384,19 @@
         <v>38108</v>
       </c>
       <c r="B162" t="n">
-        <v>0.1571317758438826</v>
+        <v>15.71317758438826</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1055388062898208</v>
+        <v>10.5538806289821</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1230942350575253</v>
+        <v>12.30942350575253</v>
       </c>
       <c r="E162" t="n">
-        <v>0.03821285195074919</v>
+        <v>3.821285195074919</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1664188174412682</v>
+        <v>16.64188174412682</v>
       </c>
       <c r="G162" t="n">
         <v>4.1708</v>
@@ -7427,19 +7427,19 @@
         <v>38139</v>
       </c>
       <c r="B163" t="n">
-        <v>0.1226499358420212</v>
+        <v>12.26499358420212</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08329550227842697</v>
+        <v>8.329550227842674</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1293968760041335</v>
+        <v>12.93968760041335</v>
       </c>
       <c r="E163" t="n">
-        <v>0.04861592633808898</v>
+        <v>4.861592633808898</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2054290671596808</v>
+        <v>20.54290671596808</v>
       </c>
       <c r="G163" t="n">
         <v>4.8419</v>
@@ -7470,19 +7470,19 @@
         <v>38169</v>
       </c>
       <c r="B164" t="n">
-        <v>0.1041417237101241</v>
+        <v>10.41417237101241</v>
       </c>
       <c r="C164" t="n">
-        <v>0.06991994092160869</v>
+        <v>6.991994092160869</v>
       </c>
       <c r="D164" t="n">
-        <v>0.08570257624191013</v>
+        <v>8.570257624191013</v>
       </c>
       <c r="E164" t="n">
-        <v>0.06629506489873127</v>
+        <v>6.629506489873127</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1765793328318617</v>
+        <v>17.65793328318617</v>
       </c>
       <c r="G164" t="n">
         <v>4.92126</v>
@@ -7513,19 +7513,19 @@
         <v>38200</v>
       </c>
       <c r="B165" t="n">
-        <v>0.03437222310497168</v>
+        <v>3.437222310497168</v>
       </c>
       <c r="C165" t="n">
-        <v>0.01123831927127728</v>
+        <v>1.123831927127728</v>
       </c>
       <c r="D165" t="n">
-        <v>0.01943724853967677</v>
+        <v>1.943724853967677</v>
       </c>
       <c r="E165" t="n">
-        <v>0.06266236785080359</v>
+        <v>6.266236785080359</v>
       </c>
       <c r="F165" t="n">
-        <v>0.07746415362663539</v>
+        <v>7.746415362663539</v>
       </c>
       <c r="G165" t="n">
         <v>4.59433</v>
@@ -7556,19 +7556,19 @@
         <v>38231</v>
       </c>
       <c r="B166" t="n">
-        <v>0.1021212339476347</v>
+        <v>10.21212339476347</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1147989569360854</v>
+        <v>11.47989569360854</v>
       </c>
       <c r="D166" t="n">
-        <v>0.06387024416775744</v>
+        <v>6.387024416775744</v>
       </c>
       <c r="E166" t="n">
-        <v>0.04101651887738056</v>
+        <v>4.101651887738056</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1052294979473154</v>
+        <v>10.52294979473154</v>
       </c>
       <c r="G166" t="n">
         <v>4.60333</v>
@@ -7599,19 +7599,19 @@
         <v>38261</v>
       </c>
       <c r="B167" t="n">
-        <v>0.1035079960663401</v>
+        <v>10.35079960663401</v>
       </c>
       <c r="C167" t="n">
-        <v>0.08270022372578079</v>
+        <v>8.270022372578101</v>
       </c>
       <c r="D167" t="n">
-        <v>0.06605049130828755</v>
+        <v>6.605049130828755</v>
       </c>
       <c r="E167" t="n">
-        <v>0.06046375100021284</v>
+        <v>6.046375100021284</v>
       </c>
       <c r="F167" t="n">
-        <v>0.1281305450721697</v>
+        <v>12.81305450721697</v>
       </c>
       <c r="G167" t="n">
         <v>4.62598</v>
@@ -7642,19 +7642,19 @@
         <v>38292</v>
       </c>
       <c r="B168" t="n">
-        <v>0.05391510092157215</v>
+        <v>5.391510092157215</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0634096140342415</v>
+        <v>6.34096140342415</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0393923409435224</v>
+        <v>3.93923409435224</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0640008320958434</v>
+        <v>6.40008320958434</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1049739137748271</v>
+        <v>10.49739137748271</v>
       </c>
       <c r="G168" t="n">
         <v>4.59883</v>
@@ -7685,19 +7685,19 @@
         <v>38322</v>
       </c>
       <c r="B169" t="n">
-        <v>0.05175738078806558</v>
+        <v>5.175738078806558</v>
       </c>
       <c r="C169" t="n">
-        <v>0.05627817430364468</v>
+        <v>5.627817430364468</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.0222413364993469</v>
+        <v>-2.22413364993469</v>
       </c>
       <c r="E169" t="n">
-        <v>0.07304857157006217</v>
+        <v>7.304857157006217</v>
       </c>
       <c r="F169" t="n">
-        <v>0.04599792001675307</v>
+        <v>4.599792001675307</v>
       </c>
       <c r="G169" t="n">
         <v>3.36862</v>
@@ -7728,19 +7728,19 @@
         <v>38353</v>
       </c>
       <c r="B170" t="n">
-        <v>0.1117714454721539</v>
+        <v>11.17714454721539</v>
       </c>
       <c r="C170" t="n">
-        <v>0.09626130145517386</v>
+        <v>9.626130145517408</v>
       </c>
       <c r="D170" t="n">
-        <v>0.05714778319008063</v>
+        <v>5.714778319008063</v>
       </c>
       <c r="E170" t="n">
-        <v>0.068592110450864</v>
+        <v>6.8592110450864</v>
       </c>
       <c r="F170" t="n">
-        <v>0.1194433428194195</v>
+        <v>11.94433428194195</v>
       </c>
       <c r="G170" t="n">
         <v>3.02144</v>
@@ -7771,19 +7771,19 @@
         <v>38384</v>
       </c>
       <c r="B171" t="n">
-        <v>0.06827443790013832</v>
+        <v>6.827443790013832</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0625102008963756</v>
+        <v>6.25102008963756</v>
       </c>
       <c r="D171" t="n">
-        <v>0.03858991040824455</v>
+        <v>3.858991040824455</v>
       </c>
       <c r="E171" t="n">
-        <v>0.09149214223596602</v>
+        <v>9.149214223596601</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1260636045677059</v>
+        <v>12.60636045677059</v>
       </c>
       <c r="G171" t="n">
         <v>2.6975</v>
@@ -7814,19 +7814,19 @@
         <v>38412</v>
       </c>
       <c r="B172" t="n">
-        <v>0.1095948538294929</v>
+        <v>10.95948538294929</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1449907583694159</v>
+        <v>14.49907583694159</v>
       </c>
       <c r="D172" t="n">
-        <v>0.05551702200287689</v>
+        <v>5.551702200287689</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1035932389009726</v>
+        <v>10.35932389009726</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1549063330738147</v>
+        <v>15.49063330738147</v>
       </c>
       <c r="G172" t="n">
         <v>3.2567</v>
@@ -7857,19 +7857,19 @@
         <v>38443</v>
       </c>
       <c r="B173" t="n">
-        <v>0.03631902308073376</v>
+        <v>3.631902308073376</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01085901866780881</v>
+        <v>1.085901866780881</v>
       </c>
       <c r="D173" t="n">
-        <v>0.01332933527129132</v>
+        <v>1.332933527129132</v>
       </c>
       <c r="E173" t="n">
-        <v>0.03636247223968159</v>
+        <v>3.636247223968159</v>
       </c>
       <c r="F173" t="n">
-        <v>0.04719587223238819</v>
+        <v>4.719587223238819</v>
       </c>
       <c r="G173" t="n">
         <v>3.15789</v>
@@ -7900,19 +7900,19 @@
         <v>38473</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0525303615786008</v>
+        <v>5.25303615786008</v>
       </c>
       <c r="C174" t="n">
-        <v>0.04066235554000119</v>
+        <v>4.066235554000119</v>
       </c>
       <c r="D174" t="n">
-        <v>0.05561866797054993</v>
+        <v>5.561866797054993</v>
       </c>
       <c r="E174" t="n">
-        <v>0.07276437495749266</v>
+        <v>7.276437495749266</v>
       </c>
       <c r="F174" t="n">
-        <v>0.1363407357839799</v>
+        <v>13.63407357839799</v>
       </c>
       <c r="G174" t="n">
         <v>3.14585</v>
@@ -7943,19 +7943,19 @@
         <v>38504</v>
       </c>
       <c r="B175" t="n">
-        <v>0.07255001689963736</v>
+        <v>7.255001689963736</v>
       </c>
       <c r="C175" t="n">
-        <v>0.08172664128279084</v>
+        <v>8.172664128279084</v>
       </c>
       <c r="D175" t="n">
-        <v>0.03141492139115321</v>
+        <v>3.141492139115321</v>
       </c>
       <c r="E175" t="n">
-        <v>0.08126006245126893</v>
+        <v>8.126006245126893</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1262174704655739</v>
+        <v>12.62174704655738</v>
       </c>
       <c r="G175" t="n">
         <v>3.29877</v>
@@ -7986,19 +7986,19 @@
         <v>38534</v>
       </c>
       <c r="B176" t="n">
-        <v>0.08020760708113217</v>
+        <v>8.020760708113217</v>
       </c>
       <c r="C176" t="n">
-        <v>0.09654549245061528</v>
+        <v>9.654549245061549</v>
       </c>
       <c r="D176" t="n">
-        <v>0.02711826052307931</v>
+        <v>2.711826052307931</v>
       </c>
       <c r="E176" t="n">
-        <v>0.08828314361542722</v>
+        <v>8.828314361542722</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1255303213727477</v>
+        <v>12.55303213727477</v>
       </c>
       <c r="G176" t="n">
         <v>2.53283</v>
@@ -8029,19 +8029,19 @@
         <v>38565</v>
       </c>
       <c r="B177" t="n">
-        <v>0.08034493344905269</v>
+        <v>8.034493344905268</v>
       </c>
       <c r="C177" t="n">
-        <v>0.09890633707253871</v>
+        <v>9.890633707253871</v>
       </c>
       <c r="D177" t="n">
-        <v>0.03268581619251854</v>
+        <v>3.268581619251854</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1121426652037443</v>
+        <v>11.21426652037443</v>
       </c>
       <c r="F177" t="n">
-        <v>0.148627470063688</v>
+        <v>14.8627470063688</v>
       </c>
       <c r="G177" t="n">
         <v>2.42991</v>
@@ -8072,19 +8072,19 @@
         <v>38596</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0724485310672609</v>
+        <v>7.24485310672609</v>
       </c>
       <c r="C178" t="n">
-        <v>0.06628862177904593</v>
+        <v>6.628862177904571</v>
       </c>
       <c r="D178" t="n">
-        <v>0.04614084429571941</v>
+        <v>4.614084429571941</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1286037962933977</v>
+        <v>12.86037962933977</v>
       </c>
       <c r="F178" t="n">
-        <v>0.1845978481954149</v>
+        <v>18.45978481954149</v>
       </c>
       <c r="G178" t="n">
         <v>2.52809</v>
@@ -8115,19 +8115,19 @@
         <v>38626</v>
       </c>
       <c r="B179" t="n">
-        <v>0.05902564658347798</v>
+        <v>5.902564658347798</v>
       </c>
       <c r="C179" t="n">
-        <v>0.09002582102395729</v>
+        <v>9.002582102395728</v>
       </c>
       <c r="D179" t="n">
-        <v>0.03156309010414526</v>
+        <v>3.156309010414526</v>
       </c>
       <c r="E179" t="n">
-        <v>0.130907243785005</v>
+        <v>13.0907243785005</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1623013021488935</v>
+        <v>16.23013021488935</v>
       </c>
       <c r="G179" t="n">
         <v>1.78739</v>
@@ -8158,19 +8158,19 @@
         <v>38657</v>
       </c>
       <c r="B180" t="n">
-        <v>0.06354347675797589</v>
+        <v>6.354347675797589</v>
       </c>
       <c r="C180" t="n">
-        <v>0.06841856768422061</v>
+        <v>6.841856768422061</v>
       </c>
       <c r="D180" t="n">
-        <v>0.04978813204319343</v>
+        <v>4.978813204319343</v>
       </c>
       <c r="E180" t="n">
-        <v>0.148501455004304</v>
+        <v>14.8501455004304</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2156256963068264</v>
+        <v>21.56256963068264</v>
       </c>
       <c r="G180" t="n">
         <v>1.49673</v>
@@ -8201,19 +8201,19 @@
         <v>38687</v>
       </c>
       <c r="B181" t="n">
-        <v>0.05911247618623894</v>
+        <v>5.911247618623894</v>
       </c>
       <c r="C181" t="n">
-        <v>0.05568287126152294</v>
+        <v>5.568287126152294</v>
       </c>
       <c r="D181" t="n">
-        <v>0.06776189101923524</v>
+        <v>6.776189101923524</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1199769881406512</v>
+        <v>11.99769881406512</v>
       </c>
       <c r="F181" t="n">
-        <v>0.2096781158378598</v>
+        <v>20.96781158378598</v>
       </c>
       <c r="G181" t="n">
         <v>1.95531</v>
@@ -8244,19 +8244,19 @@
         <v>38718</v>
       </c>
       <c r="B182" t="n">
-        <v>0.04811157355155959</v>
+        <v>4.811157355155959</v>
       </c>
       <c r="C182" t="n">
-        <v>0.04882603308769262</v>
+        <v>4.88260330876924</v>
       </c>
       <c r="D182" t="n">
-        <v>0.008926992659982202</v>
+        <v>0.8926992659982202</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1327306891466808</v>
+        <v>13.27306891466808</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1376768596430391</v>
+        <v>13.76768596430391</v>
       </c>
       <c r="G182" t="n">
         <v>2.17597</v>
@@ -8287,19 +8287,19 @@
         <v>38749</v>
       </c>
       <c r="B183" t="n">
-        <v>0.02334741225555192</v>
+        <v>2.334741225555192</v>
       </c>
       <c r="C183" t="n">
-        <v>0.04759249475307969</v>
+        <v>4.759249475307969</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01648502992151935</v>
+        <v>1.648502992151935</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1410393083528965</v>
+        <v>14.10393083528965</v>
       </c>
       <c r="F183" t="n">
-        <v>0.1634797080891974</v>
+        <v>16.34797080891974</v>
       </c>
       <c r="G183" t="n">
         <v>2.43902</v>
@@ -8330,19 +8330,19 @@
         <v>38777</v>
       </c>
       <c r="B184" t="n">
-        <v>0.001403954578198752</v>
+        <v>0.1403954578198752</v>
       </c>
       <c r="C184" t="n">
-        <v>0.004171511286560126</v>
+        <v>0.4171511286559904</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.01607618578744641</v>
+        <v>-1.607618578744641</v>
       </c>
       <c r="E184" t="n">
-        <v>0.1099435331578777</v>
+        <v>10.99435331578777</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0779728120801193</v>
+        <v>7.79728120801193</v>
       </c>
       <c r="G184" t="n">
         <v>1.94805</v>
@@ -8373,19 +8373,19 @@
         <v>38808</v>
       </c>
       <c r="B185" t="n">
-        <v>0.05721346539842154</v>
+        <v>5.721346539842154</v>
       </c>
       <c r="C185" t="n">
-        <v>0.06790196429193163</v>
+        <v>6.790196429193185</v>
       </c>
       <c r="D185" t="n">
-        <v>0.01984228284700706</v>
+        <v>1.984228284700706</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1935293156408264</v>
+        <v>19.35293156408264</v>
       </c>
       <c r="F185" t="n">
-        <v>0.2160129174543164</v>
+        <v>21.60129174543164</v>
       </c>
       <c r="G185" t="n">
         <v>1.48423</v>
@@ -8416,19 +8416,19 @@
         <v>38838</v>
       </c>
       <c r="B186" t="n">
-        <v>0.01002036466409284</v>
+        <v>1.002036466409284</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0351482181387861</v>
+        <v>3.51482181387861</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.01493585626273553</v>
+        <v>-1.493585626273553</v>
       </c>
       <c r="E186" t="n">
-        <v>0.153148504692094</v>
+        <v>15.3148504692094</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1276197083224031</v>
+        <v>12.76197083224031</v>
       </c>
       <c r="G186" t="n">
         <v>1.66359</v>
@@ -8459,19 +8459,19 @@
         <v>38869</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0247316719568611</v>
+        <v>2.47316719568611</v>
       </c>
       <c r="C187" t="n">
-        <v>0.02536184563893951</v>
+        <v>2.536184563893928</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.009858782684233236</v>
+        <v>-0.9858782684233236</v>
       </c>
       <c r="E187" t="n">
-        <v>0.141761338908776</v>
+        <v>14.1761338908776</v>
       </c>
       <c r="F187" t="n">
-        <v>0.1304505677387227</v>
+        <v>13.04505677387226</v>
       </c>
       <c r="G187" t="n">
         <v>1.55109</v>
@@ -8502,19 +8502,19 @@
         <v>38899</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.006755032933864147</v>
+        <v>-0.6755032933864147</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.007034907144295777</v>
+        <v>-0.7034907144295777</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.01472972730514777</v>
+        <v>-1.472972730514777</v>
       </c>
       <c r="E188" t="n">
-        <v>0.142925020558591</v>
+        <v>14.2925020558591</v>
       </c>
       <c r="F188" t="n">
-        <v>0.1296475823955872</v>
+        <v>12.96475823955872</v>
       </c>
       <c r="G188" t="n">
         <v>1.64684</v>
@@ -8545,19 +8545,19 @@
         <v>38930</v>
       </c>
       <c r="B189" t="n">
-        <v>0.001608238080834212</v>
+        <v>0.1608238080834212</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.006602695701804606</v>
+        <v>-0.6602695701804495</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.02148707790844151</v>
+        <v>-2.148707790844151</v>
       </c>
       <c r="E189" t="n">
-        <v>0.1214193297408683</v>
+        <v>12.14193297408683</v>
       </c>
       <c r="F189" t="n">
-        <v>0.09748014052022724</v>
+        <v>9.748014052022725</v>
       </c>
       <c r="G189" t="n">
         <v>1.73358</v>
@@ -8588,19 +8588,19 @@
         <v>38961</v>
       </c>
       <c r="B190" t="n">
-        <v>0.009039912413623785</v>
+        <v>0.9039912413623785</v>
       </c>
       <c r="C190" t="n">
-        <v>0.03709965956193373</v>
+        <v>3.709965956193373</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.03383764652969745</v>
+        <v>-3.383764652969745</v>
       </c>
       <c r="E190" t="n">
-        <v>0.09125972532512616</v>
+        <v>9.125972532512616</v>
       </c>
       <c r="F190" t="n">
-        <v>0.05659224332828128</v>
+        <v>5.659224332828128</v>
       </c>
       <c r="G190" t="n">
         <v>1.55251</v>
@@ -8631,19 +8631,19 @@
         <v>38991</v>
       </c>
       <c r="B191" t="n">
-        <v>-0.02486288999066355</v>
+        <v>-2.486288999066355</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.02041426292909232</v>
+        <v>-2.041426292909243</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.05334040875715973</v>
+        <v>-5.334040875715973</v>
       </c>
       <c r="E191" t="n">
-        <v>0.0728031379719134</v>
+        <v>7.28031379719134</v>
       </c>
       <c r="F191" t="n">
-        <v>0.006719498449566652</v>
+        <v>0.6719498449566652</v>
       </c>
       <c r="G191" t="n">
         <v>2.03327</v>
@@ -8674,19 +8674,19 @@
         <v>39022</v>
       </c>
       <c r="B192" t="n">
-        <v>0.02858340341849042</v>
+        <v>2.858340341849042</v>
       </c>
       <c r="C192" t="n">
-        <v>0.03293184164758056</v>
+        <v>3.293184164758056</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.02611337828558613</v>
+        <v>-2.611337828558613</v>
       </c>
       <c r="E192" t="n">
-        <v>0.06503350642620997</v>
+        <v>6.503350642620997</v>
       </c>
       <c r="F192" t="n">
-        <v>0.04220355076477489</v>
+        <v>4.220355076477489</v>
       </c>
       <c r="G192" t="n">
         <v>2.39631</v>
@@ -8717,19 +8717,19 @@
         <v>39052</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0274174299127985</v>
+        <v>2.74174299127985</v>
       </c>
       <c r="C193" t="n">
-        <v>0.01663008304598312</v>
+        <v>1.663008304598312</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.05950078647924617</v>
+        <v>-5.950078647924617</v>
       </c>
       <c r="E193" t="n">
-        <v>0.09088025962909829</v>
+        <v>9.088025962909828</v>
       </c>
       <c r="F193" t="n">
-        <v>0.03850094793227266</v>
+        <v>3.850094793227266</v>
       </c>
       <c r="G193" t="n">
         <v>2.00913</v>
@@ -8760,19 +8760,19 @@
         <v>39083</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.04620531710128961</v>
+        <v>-4.620531710128962</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.04468282422925796</v>
+        <v>-4.468282422925796</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.07839306331812967</v>
+        <v>-7.839306331812967</v>
       </c>
       <c r="E194" t="n">
-        <v>0.09314013597873028</v>
+        <v>9.314013597873029</v>
       </c>
       <c r="F194" t="n">
-        <v>0.01428147475770691</v>
+        <v>1.428147475770691</v>
       </c>
       <c r="G194" t="n">
         <v>2.40741</v>
@@ -8803,19 +8803,19 @@
         <v>39114</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.01878797153402578</v>
+        <v>-1.878797153402578</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.02311345168519141</v>
+        <v>-2.31134516851913</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.08193828609917064</v>
+        <v>-8.193828609917064</v>
       </c>
       <c r="E195" t="n">
-        <v>0.06758396519558363</v>
+        <v>6.758396519558363</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.01985901425396974</v>
+        <v>-1.985901425396974</v>
       </c>
       <c r="G195" t="n">
         <v>2.47253</v>
@@ -8846,19 +8846,19 @@
         <v>39142</v>
       </c>
       <c r="B196" t="n">
-        <v>0.04110029532286386</v>
+        <v>4.110029532286386</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.01004349432469476</v>
+        <v>-1.004349432469465</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.05385643727194278</v>
+        <v>-5.385643727194278</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0752600482182062</v>
+        <v>7.52600482182062</v>
       </c>
       <c r="F196" t="n">
-        <v>0.01512570749276998</v>
+        <v>1.512570749276998</v>
       </c>
       <c r="G196" t="n">
         <v>2.54777</v>
@@ -8889,19 +8889,19 @@
         <v>39173</v>
       </c>
       <c r="B197" t="n">
-        <v>-0.0155428946423416</v>
+        <v>-1.55428946423416</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0451966298383446</v>
+        <v>4.51966298383446</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.07804618815174746</v>
+        <v>-7.804618815174747</v>
       </c>
       <c r="E197" t="n">
-        <v>0.06292884131873233</v>
+        <v>6.292884131873233</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.02528432993228447</v>
+        <v>-2.528432993228447</v>
       </c>
       <c r="G197" t="n">
         <v>2.83364</v>
@@ -8932,19 +8932,19 @@
         <v>39203</v>
       </c>
       <c r="B198" t="n">
-        <v>0.002877952353288471</v>
+        <v>0.2877952353288471</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01046877753687081</v>
+        <v>1.046877753687081</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.08252312546330798</v>
+        <v>-8.252312546330797</v>
       </c>
       <c r="E198" t="n">
-        <v>0.07551897488887094</v>
+        <v>7.551897488887094</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.02181659150545812</v>
+        <v>-2.181659150545812</v>
       </c>
       <c r="G198" t="n">
         <v>2.72727</v>
@@ -8975,19 +8975,19 @@
         <v>39234</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.003558176829783544</v>
+        <v>-0.3558176829783544</v>
       </c>
       <c r="C199" t="n">
-        <v>0.008236704575432574</v>
+        <v>0.8236704575432574</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.06362407216148325</v>
+        <v>-6.362407216148325</v>
       </c>
       <c r="E199" t="n">
-        <v>0.07335945684916201</v>
+        <v>7.335945684916201</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.004197705527898998</v>
+        <v>-0.4197705527898998</v>
       </c>
       <c r="G199" t="n">
         <v>2.51572</v>
@@ -9018,19 +9018,19 @@
         <v>39264</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.02253988260949014</v>
+        <v>-2.253988260949014</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.01844044918377197</v>
+        <v>-1.844044918377197</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.06196112417757693</v>
+        <v>-6.196112417757693</v>
       </c>
       <c r="E200" t="n">
-        <v>0.06370384755968073</v>
+        <v>6.370384755968073</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.0135072087228667</v>
+        <v>-1.35072087228667</v>
       </c>
       <c r="G200" t="n">
         <v>1.62016</v>
@@ -9061,19 +9061,19 @@
         <v>39295</v>
       </c>
       <c r="B201" t="n">
-        <v>0.05233296209100602</v>
+        <v>5.233296209100602</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05120477082152819</v>
+        <v>5.120477082152797</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.03412964255087703</v>
+        <v>-3.412964255087703</v>
       </c>
       <c r="E201" t="n">
-        <v>0.05949848919340472</v>
+        <v>5.949848919340472</v>
       </c>
       <c r="F201" t="n">
-        <v>0.01845467838291937</v>
+        <v>1.845467838291937</v>
       </c>
       <c r="G201" t="n">
         <v>1.79372</v>
@@ -9104,19 +9104,19 @@
         <v>39326</v>
       </c>
       <c r="B202" t="n">
-        <v>-0.003926171257286226</v>
+        <v>-0.3926171257286226</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.01659150562034706</v>
+        <v>-1.659150562034706</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.03854813750418706</v>
+        <v>-3.854813750418706</v>
       </c>
       <c r="E202" t="n">
-        <v>0.07112118358408592</v>
+        <v>7.112118358408592</v>
       </c>
       <c r="F202" t="n">
-        <v>0.03342016397209635</v>
+        <v>3.342016397209635</v>
       </c>
       <c r="G202" t="n">
         <v>1.07914</v>
@@ -9147,19 +9147,19 @@
         <v>39356</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.00728143803247816</v>
+        <v>-0.728143803247816</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.001944138940801698</v>
+        <v>-0.1944138940801587</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.02726758152673436</v>
+        <v>-2.726758152673436</v>
       </c>
       <c r="E203" t="n">
-        <v>0.07943472036207466</v>
+        <v>7.943472036207466</v>
       </c>
       <c r="F203" t="n">
-        <v>0.05785368079819886</v>
+        <v>5.785368079819886</v>
       </c>
       <c r="G203" t="n">
         <v>0.4529</v>
@@ -9190,19 +9190,19 @@
         <v>39387</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.007509611437269359</v>
+        <v>-0.7509611437269359</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.01039446827677282</v>
+        <v>-1.039446827677271</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.03889558548897765</v>
+        <v>-3.889558548897765</v>
       </c>
       <c r="E204" t="n">
-        <v>0.06292141128376971</v>
+        <v>6.292141128376971</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0237656940662927</v>
+        <v>2.37656940662927</v>
       </c>
       <c r="G204" t="n">
         <v>0.27003</v>
@@ -9233,19 +9233,19 @@
         <v>39417</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.02094323937936493</v>
+        <v>-2.094323937936493</v>
       </c>
       <c r="C205" t="n">
-        <v>0.02041685951640448</v>
+        <v>2.041685951640448</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.02536389404720585</v>
+        <v>-2.536389404720585</v>
       </c>
       <c r="E205" t="n">
-        <v>0.05819276917764493</v>
+        <v>5.819276917764493</v>
       </c>
       <c r="F205" t="n">
-        <v>0.04539661156354691</v>
+        <v>4.539661156354691</v>
       </c>
       <c r="G205" t="n">
         <v>0.17905</v>
@@ -9276,19 +9276,19 @@
         <v>39448</v>
       </c>
       <c r="B206" t="n">
-        <v>0.01246948526709835</v>
+        <v>1.246948526709835</v>
       </c>
       <c r="C206" t="n">
-        <v>0.02408341972851624</v>
+        <v>2.408341972851624</v>
       </c>
       <c r="D206" t="n">
-        <v>0.01851432529216535</v>
+        <v>1.851432529216535</v>
       </c>
       <c r="E206" t="n">
-        <v>0.05707459256729797</v>
+        <v>5.707459256729797</v>
       </c>
       <c r="F206" t="n">
-        <v>0.08946082836094638</v>
+        <v>8.946082836094638</v>
       </c>
       <c r="G206" t="n">
         <v>0.36166</v>
@@ -9319,19 +9319,19 @@
         <v>39479</v>
       </c>
       <c r="B207" t="n">
-        <v>0.03002176970737613</v>
+        <v>3.002176970737613</v>
       </c>
       <c r="C207" t="n">
-        <v>0.02927480190973686</v>
+        <v>2.927480190973664</v>
       </c>
       <c r="D207" t="n">
-        <v>0.02998281813554038</v>
+        <v>2.998281813554038</v>
       </c>
       <c r="E207" t="n">
-        <v>0.05506652501256082</v>
+        <v>5.506652501256082</v>
       </c>
       <c r="F207" t="n">
-        <v>0.09399828024626089</v>
+        <v>9.399828024626089</v>
       </c>
       <c r="G207" t="n">
         <v>0.2681</v>
@@ -9362,19 +9362,19 @@
         <v>39508</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.06082686830440542</v>
+        <v>-6.082686830440542</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00174180463676632</v>
+        <v>0.174180463676632</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.009469203466134113</v>
+        <v>-0.9469203466134113</v>
       </c>
       <c r="E208" t="n">
-        <v>0.07992563989370227</v>
+        <v>7.992563989370227</v>
       </c>
       <c r="F208" t="n">
-        <v>0.06818517166124383</v>
+        <v>6.818517166124383</v>
       </c>
       <c r="G208" t="n">
         <v>-0.35492</v>
@@ -9405,19 +9405,19 @@
         <v>39539</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.06811880830654959</v>
+        <v>-6.811880830654959</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.1160786919335502</v>
+        <v>-11.60786919335504</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.02560710767360697</v>
+        <v>-2.560710767360697</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.009312881582945631</v>
+        <v>-0.9312881582945631</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.03356594601767271</v>
+        <v>-3.356594601767271</v>
       </c>
       <c r="G209" t="n">
         <v>-1.24444</v>
@@ -9448,19 +9448,19 @@
         <v>39569</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.0680672049307165</v>
+        <v>-6.80672049307165</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.07389258890952322</v>
+        <v>-7.389258890952322</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.01766981957113922</v>
+        <v>-1.766981957113922</v>
       </c>
       <c r="E210" t="n">
-        <v>0.02138833125316308</v>
+        <v>2.138833125316308</v>
       </c>
       <c r="F210" t="n">
-        <v>0.006709136730799203</v>
+        <v>0.6709136730799203</v>
       </c>
       <c r="G210" t="n">
         <v>-1.59292</v>
@@ -9491,19 +9491,19 @@
         <v>39600</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.1323409256319059</v>
+        <v>-13.23409256319059</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.1079073021856526</v>
+        <v>-10.79073021856527</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.08058309631555927</v>
+        <v>-8.058309631555927</v>
       </c>
       <c r="E211" t="n">
-        <v>0.02756397157890156</v>
+        <v>2.756397157890156</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.07331651329005984</v>
+        <v>-7.331651329005984</v>
       </c>
       <c r="G211" t="n">
         <v>-2.45399</v>
@@ -9534,19 +9534,19 @@
         <v>39630</v>
       </c>
       <c r="B212" t="n">
-        <v>-0.1339330699421756</v>
+        <v>-13.39330699421756</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.1140657736934124</v>
+        <v>-11.40657736934125</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.0797504383412555</v>
+        <v>-7.97504383412555</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.0002973149770898464</v>
+        <v>-0.02973149770898464</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.09078354550090006</v>
+        <v>-9.078354550090006</v>
       </c>
       <c r="G212" t="n">
         <v>-1.94863</v>
@@ -9577,19 +9577,19 @@
         <v>39661</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.1689712351865271</v>
+        <v>-16.89712351865271</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.1474567328437271</v>
+        <v>-14.7456732843727</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.07923859572226777</v>
+        <v>-7.923859572226776</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.001823734992015602</v>
+        <v>-0.1823734992015602</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.08902020865251326</v>
+        <v>-8.902020865251325</v>
       </c>
       <c r="G213" t="n">
         <v>-2.99559</v>
@@ -9620,19 +9620,19 @@
         <v>39692</v>
       </c>
       <c r="B214" t="n">
-        <v>-0.1906959767142196</v>
+        <v>-19.06959767142196</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.1501543711390293</v>
+        <v>-15.01543711390292</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.1528790867287751</v>
+        <v>-15.28790867287752</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.02549613103350357</v>
+        <v>-2.549613103350357</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.1662694963880869</v>
+        <v>-16.62694963880869</v>
       </c>
       <c r="G214" t="n">
         <v>-3.55872</v>
@@ -9663,19 +9663,19 @@
         <v>39722</v>
       </c>
       <c r="B215" t="n">
-        <v>-0.1285413523995804</v>
+        <v>-12.85413523995804</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.1056363595195786</v>
+        <v>-10.56363595195786</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.09144317523615664</v>
+        <v>-9.144317523615664</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.04572110558857057</v>
+        <v>-4.572110558857057</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.1184334639921252</v>
+        <v>-11.84334639921252</v>
       </c>
       <c r="G215" t="n">
         <v>-4.23805</v>
@@ -9706,19 +9706,19 @@
         <v>39753</v>
       </c>
       <c r="B216" t="n">
-        <v>-0.1548985676614889</v>
+        <v>-15.48985676614889</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.1170131427828616</v>
+        <v>-11.70131427828616</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.1157927040279122</v>
+        <v>-11.57927040279122</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.05273469830253574</v>
+        <v>-5.273469830253575</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.1558023029759235</v>
+        <v>-15.58023029759235</v>
       </c>
       <c r="G216" t="n">
         <v>-5.1167</v>
@@ -9749,19 +9749,19 @@
         <v>39783</v>
       </c>
       <c r="B217" t="n">
-        <v>-0.1685900324730294</v>
+        <v>-16.85900324730294</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.1549385927279598</v>
+        <v>-15.49385927279598</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.1363618416291017</v>
+        <v>-13.63618416291017</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.06091463523165919</v>
+        <v>-6.091463523165919</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.1744289793004997</v>
+        <v>-17.44289793004997</v>
       </c>
       <c r="G217" t="n">
         <v>-5.89812</v>
@@ -9792,19 +9792,19 @@
         <v>39814</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.1298393744155487</v>
+        <v>-12.98393744155487</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1150170932982408</v>
+        <v>-11.5017093298241</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.165837270643708</v>
+        <v>-16.5837270643708</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.08115021649612375</v>
+        <v>-8.115021649612375</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.2304190601188397</v>
+        <v>-23.04190601188397</v>
       </c>
       <c r="G218" t="n">
         <v>-6.3964</v>
@@ -9835,19 +9835,19 @@
         <v>39845</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.1366611359196844</v>
+        <v>-13.66611359196844</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.139176089124798</v>
+        <v>-13.9176089124798</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.1385969577451233</v>
+        <v>-13.85969577451233</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.1124037472245694</v>
+        <v>-11.24037472245694</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.2372074314062635</v>
+        <v>-23.72074314062635</v>
       </c>
       <c r="G219" t="n">
         <v>-7.21925</v>
@@ -9878,19 +9878,19 @@
         <v>39873</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.1437666613127794</v>
+        <v>-14.37666613127794</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1713213709797221</v>
+        <v>-17.13213709797221</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.1505031371326965</v>
+        <v>-15.05031371326965</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.1502860229843904</v>
+        <v>-15.02860229843904</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.2932905286710945</v>
+        <v>-29.32905286710945</v>
       </c>
       <c r="G220" t="n">
         <v>-7.03473</v>
@@ -9921,19 +9921,19 @@
         <v>39904</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.05607629423935312</v>
+        <v>-5.607629423935312</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.0108850491595156</v>
+        <v>-1.08850491595156</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.09462734230216641</v>
+        <v>-9.46273423021664</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.08496399105041874</v>
+        <v>-8.496399105041874</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.17453165438471</v>
+        <v>-17.453165438471</v>
       </c>
       <c r="G221" t="n">
         <v>-6.84068</v>
@@ -9964,19 +9964,19 @@
         <v>39934</v>
       </c>
       <c r="B222" t="n">
-        <v>-0.0674273283244925</v>
+        <v>-6.742732832449249</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.05886925890515793</v>
+        <v>-5.886925890515782</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.109076845788136</v>
+        <v>-10.9076845788136</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.123101378074428</v>
+        <v>-12.3101378074428</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.2231175179897388</v>
+        <v>-22.31175179897388</v>
       </c>
       <c r="G222" t="n">
         <v>-6.65468</v>
@@ -10007,19 +10007,19 @@
         <v>39965</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.05004057134176887</v>
+        <v>-5.004057134176887</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.0273971638169882</v>
+        <v>-2.739716381698809</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.09634135738945682</v>
+        <v>-9.634135738945682</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.1528231019569505</v>
+        <v>-15.28231019569505</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.2509888951859062</v>
+        <v>-25.09888951859062</v>
       </c>
       <c r="G223" t="n">
         <v>-6.37916</v>
@@ -10050,19 +10050,19 @@
         <v>39995</v>
       </c>
       <c r="B224" t="n">
-        <v>0.01238303773556049</v>
+        <v>1.238303773556049</v>
       </c>
       <c r="C224" t="n">
-        <v>0.0108404841009635</v>
+        <v>1.08404841009635</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.07462783611814106</v>
+        <v>-7.462783611814105</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.1507906010825107</v>
+        <v>-15.07906010825107</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.2222988292419306</v>
+        <v>-22.22988292419306</v>
       </c>
       <c r="G224" t="n">
         <v>-6.23306</v>
@@ -10093,19 +10093,19 @@
         <v>40026</v>
       </c>
       <c r="B225" t="n">
-        <v>0.007393279041932876</v>
+        <v>0.7393279041932876</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.005758008782836832</v>
+        <v>-0.5758008782836943</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.06245220890424819</v>
+        <v>-6.245220890424818</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.1466833067014324</v>
+        <v>-14.66833067014324</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.2138702914722391</v>
+        <v>-21.38702914722391</v>
       </c>
       <c r="G225" t="n">
         <v>-5.35876</v>
@@ -10136,19 +10136,19 @@
         <v>40057</v>
       </c>
       <c r="B226" t="n">
-        <v>0.07281628239529692</v>
+        <v>7.281628239529692</v>
       </c>
       <c r="C226" t="n">
-        <v>0.03639767664879434</v>
+        <v>3.639767664879412</v>
       </c>
       <c r="D226" t="n">
-        <v>0.0101367080309247</v>
+        <v>1.01367080309247</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.1059213937054651</v>
+        <v>-10.59213937054651</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.09243000456361439</v>
+        <v>-9.24300045636144</v>
       </c>
       <c r="G226" t="n">
         <v>-4.33579</v>
@@ -10179,19 +10179,19 @@
         <v>40087</v>
       </c>
       <c r="B227" t="n">
-        <v>-0.004205937915913172</v>
+        <v>-0.4205937915913172</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.02688160855645483</v>
+        <v>-2.688160855645494</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.01413414194396667</v>
+        <v>-1.413414194396667</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.08439862532305353</v>
+        <v>-8.439862532305353</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.08306102079601829</v>
+        <v>-8.306102079601828</v>
       </c>
       <c r="G227" t="n">
         <v>-3.48399</v>
@@ -10222,19 +10222,19 @@
         <v>40118</v>
       </c>
       <c r="B228" t="n">
-        <v>-0.01616194191503662</v>
+        <v>-1.616194191503662</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.02359563993691216</v>
+        <v>-2.359563993691216</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.0314536663580085</v>
+        <v>-3.14536663580085</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.09737004804240357</v>
+        <v>-9.737004804240357</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.1208111387651347</v>
+        <v>-12.08111387651347</v>
       </c>
       <c r="G228" t="n">
         <v>-3.12204</v>
@@ -10265,19 +10265,19 @@
         <v>40148</v>
       </c>
       <c r="B229" t="n">
-        <v>0.03320304464339241</v>
+        <v>3.320304464339241</v>
       </c>
       <c r="C229" t="n">
-        <v>0.02476194368747242</v>
+        <v>2.476194368747242</v>
       </c>
       <c r="D229" t="n">
-        <v>0.02607487980993461</v>
+        <v>2.607487980993461</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.09344789487809535</v>
+        <v>-9.344789487809535</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.05361943423754456</v>
+        <v>-5.361943423754456</v>
       </c>
       <c r="G229" t="n">
         <v>-2.18424</v>
@@ -10308,19 +10308,19 @@
         <v>40179</v>
       </c>
       <c r="B230" t="n">
-        <v>0.0158548805361618</v>
+        <v>1.58548805361618</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0192731747221544</v>
+        <v>1.927317472215462</v>
       </c>
       <c r="D230" t="n">
-        <v>0.04396810138198037</v>
+        <v>4.396810138198037</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.1031983939364424</v>
+        <v>-10.31983939364424</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.05713763442603892</v>
+        <v>-5.713763442603891</v>
       </c>
       <c r="G230" t="n">
         <v>-2.21367</v>
@@ -10351,19 +10351,19 @@
         <v>40210</v>
       </c>
       <c r="B231" t="n">
-        <v>0.01002928379945422</v>
+        <v>1.002928379945422</v>
       </c>
       <c r="C231" t="n">
-        <v>0.02368349846464746</v>
+        <v>2.368349846464746</v>
       </c>
       <c r="D231" t="n">
-        <v>0.04679997686476223</v>
+        <v>4.679997686476223</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.07142941784832779</v>
+        <v>-7.142941784832779</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.02770022086357049</v>
+        <v>-2.770022086357049</v>
       </c>
       <c r="G231" t="n">
         <v>-1.72911</v>
@@ -10394,19 +10394,19 @@
         <v>40238</v>
       </c>
       <c r="B232" t="n">
-        <v>0.08176322925189972</v>
+        <v>8.176322925189972</v>
       </c>
       <c r="C232" t="n">
-        <v>0.09268131211317798</v>
+        <v>9.268131211317797</v>
       </c>
       <c r="D232" t="n">
-        <v>0.07804859946507348</v>
+        <v>7.804859946507348</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.04731582681644397</v>
+        <v>-4.731582681644397</v>
       </c>
       <c r="F232" t="n">
-        <v>0.02618913476564266</v>
+        <v>2.618913476564266</v>
       </c>
       <c r="G232" t="n">
         <v>-1.81992</v>
@@ -10437,19 +10437,19 @@
         <v>40269</v>
       </c>
       <c r="B233" t="n">
-        <v>0.04198462363799682</v>
+        <v>4.198462363799682</v>
       </c>
       <c r="C233" t="n">
-        <v>0.002069853019512458</v>
+        <v>0.2069853019512458</v>
       </c>
       <c r="D233" t="n">
-        <v>0.04391995346243749</v>
+        <v>4.391995346243749</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.0223822867760588</v>
+        <v>-2.23822867760588</v>
       </c>
       <c r="F233" t="n">
-        <v>0.02013419785596771</v>
+        <v>2.013419785596771</v>
       </c>
       <c r="G233" t="n">
         <v>-0.96618</v>
@@ -10480,19 +10480,19 @@
         <v>40299</v>
       </c>
       <c r="B234" t="n">
-        <v>0.06532595396757124</v>
+        <v>6.532595396757124</v>
       </c>
       <c r="C234" t="n">
-        <v>0.08890011059311553</v>
+        <v>8.890011059311554</v>
       </c>
       <c r="D234" t="n">
-        <v>0.07538672582184103</v>
+        <v>7.538672582184103</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.03183678270488488</v>
+        <v>-3.183678270488488</v>
       </c>
       <c r="F234" t="n">
-        <v>0.03707327406577354</v>
+        <v>3.707327406577354</v>
       </c>
       <c r="G234" t="n">
         <v>-1.34875</v>
@@ -10523,19 +10523,19 @@
         <v>40330</v>
       </c>
       <c r="B235" t="n">
-        <v>0.1050227507059129</v>
+        <v>10.50227507059129</v>
       </c>
       <c r="C235" t="n">
-        <v>0.05793963413675463</v>
+        <v>5.793963413675463</v>
       </c>
       <c r="D235" t="n">
-        <v>0.1503729996385548</v>
+        <v>15.03729996385548</v>
       </c>
       <c r="E235" t="n">
-        <v>-0.007827936417875936</v>
+        <v>-0.7827936417875936</v>
       </c>
       <c r="F235" t="n">
-        <v>0.1413877227079847</v>
+        <v>14.13877227079847</v>
       </c>
       <c r="G235" t="n">
         <v>-1.43954</v>
@@ -10566,19 +10566,19 @@
         <v>40360</v>
       </c>
       <c r="B236" t="n">
-        <v>0.09740526995515331</v>
+        <v>9.740526995515332</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1095831397065172</v>
+        <v>10.9583139706517</v>
       </c>
       <c r="D236" t="n">
-        <v>0.1547742570162507</v>
+        <v>15.47742570162507</v>
       </c>
       <c r="E236" t="n">
-        <v>0.02171909435118202</v>
+        <v>2.171909435118202</v>
       </c>
       <c r="F236" t="n">
-        <v>0.1822575968948419</v>
+        <v>18.22575968948419</v>
       </c>
       <c r="G236" t="n">
         <v>-0.67437</v>
@@ -10609,19 +10609,19 @@
         <v>40391</v>
       </c>
       <c r="B237" t="n">
-        <v>0.07109960158616824</v>
+        <v>7.109960158616824</v>
       </c>
       <c r="C237" t="n">
-        <v>0.1037989673645838</v>
+        <v>10.37989673645838</v>
       </c>
       <c r="D237" t="n">
-        <v>0.09824052958552909</v>
+        <v>9.824052958552908</v>
       </c>
       <c r="E237" t="n">
-        <v>0.02612225469835505</v>
+        <v>2.612225469835505</v>
       </c>
       <c r="F237" t="n">
-        <v>0.1126891382182498</v>
+        <v>11.26891382182498</v>
       </c>
       <c r="G237" t="n">
         <v>-0.38388</v>
@@ -10652,19 +10652,19 @@
         <v>40422</v>
       </c>
       <c r="B238" t="n">
-        <v>0.08562459548074774</v>
+        <v>8.562459548074774</v>
       </c>
       <c r="C238" t="n">
-        <v>0.09383723484646334</v>
+        <v>9.383723484646357</v>
       </c>
       <c r="D238" t="n">
-        <v>0.1076203751859086</v>
+        <v>10.76203751859086</v>
       </c>
       <c r="E238" t="n">
-        <v>0.006800085448124049</v>
+        <v>0.6800085448124049</v>
       </c>
       <c r="F238" t="n">
-        <v>0.1106857074971799</v>
+        <v>11.06857074971799</v>
       </c>
       <c r="G238" t="n">
         <v>-0.19286</v>
@@ -10695,19 +10695,19 @@
         <v>40452</v>
       </c>
       <c r="B239" t="n">
-        <v>0.1382959439814357</v>
+        <v>13.82959439814357</v>
       </c>
       <c r="C239" t="n">
-        <v>0.145747902057852</v>
+        <v>14.5747902057852</v>
       </c>
       <c r="D239" t="n">
-        <v>0.07345433788965039</v>
+        <v>7.345433788965039</v>
       </c>
       <c r="E239" t="n">
-        <v>0.003992505561819959</v>
+        <v>0.3992505561819959</v>
       </c>
       <c r="F239" t="n">
-        <v>0.06349040089166724</v>
+        <v>6.349040089166724</v>
       </c>
       <c r="G239" t="n">
         <v>1.17073</v>
@@ -10738,19 +10738,19 @@
         <v>40483</v>
       </c>
       <c r="B240" t="n">
-        <v>0.1221347049002142</v>
+        <v>12.21347049002142</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1257720635420425</v>
+        <v>12.57720635420425</v>
       </c>
       <c r="D240" t="n">
-        <v>0.1060976480010944</v>
+        <v>10.60976480010945</v>
       </c>
       <c r="E240" t="n">
-        <v>0.04218373257457486</v>
+        <v>4.218373257457486</v>
       </c>
       <c r="F240" t="n">
-        <v>0.1557568344155418</v>
+        <v>15.57568344155418</v>
       </c>
       <c r="G240" t="n">
         <v>1.95313</v>
@@ -10781,19 +10781,19 @@
         <v>40513</v>
       </c>
       <c r="B241" t="n">
-        <v>0.09117919211185854</v>
+        <v>9.117919211185853</v>
       </c>
       <c r="C241" t="n">
-        <v>0.08174008184300141</v>
+        <v>8.174008184300142</v>
       </c>
       <c r="D241" t="n">
-        <v>0.1000506758041204</v>
+        <v>10.00506758041204</v>
       </c>
       <c r="E241" t="n">
-        <v>0.04570848590892407</v>
+        <v>4.570848590892407</v>
       </c>
       <c r="F241" t="n">
-        <v>0.160610294300134</v>
+        <v>16.0610294300134</v>
       </c>
       <c r="G241" t="n">
         <v>2.13592</v>
@@ -10824,19 +10824,19 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>0.1166625330416708</v>
+        <v>11.66625330416709</v>
       </c>
       <c r="C242" t="n">
-        <v>0.1138098288262852</v>
+        <v>11.38098288262852</v>
       </c>
       <c r="D242" t="n">
-        <v>0.1014177525634576</v>
+        <v>10.14177525634576</v>
       </c>
       <c r="E242" t="n">
-        <v>0.07262289885416084</v>
+        <v>7.262289885416084</v>
       </c>
       <c r="F242" t="n">
-        <v>0.2028409601772081</v>
+        <v>20.28409601772081</v>
       </c>
       <c r="G242" t="n">
         <v>2.85433</v>
@@ -10867,19 +10867,19 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>0.1225935409865535</v>
+        <v>12.25935409865535</v>
       </c>
       <c r="C243" t="n">
-        <v>0.124453048619231</v>
+        <v>12.4453048619231</v>
       </c>
       <c r="D243" t="n">
-        <v>0.07812125073101028</v>
+        <v>7.812125073101028</v>
       </c>
       <c r="E243" t="n">
-        <v>0.08994905489355953</v>
+        <v>8.994905489355954</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1853821730100376</v>
+        <v>18.53821730100375</v>
       </c>
       <c r="G243" t="n">
         <v>2.54154</v>
@@ -10910,19 +10910,19 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>0.03990005044528866</v>
+        <v>3.990005044528866</v>
       </c>
       <c r="C244" t="n">
-        <v>0.07191453446553786</v>
+        <v>7.191453446553786</v>
       </c>
       <c r="D244" t="n">
-        <v>0.06052646459148581</v>
+        <v>6.052646459148581</v>
       </c>
       <c r="E244" t="n">
-        <v>0.08710603495536295</v>
+        <v>8.710603495536295</v>
       </c>
       <c r="F244" t="n">
-        <v>0.162326661382471</v>
+        <v>16.2326661382471</v>
       </c>
       <c r="G244" t="n">
         <v>3.31707</v>
@@ -10953,19 +10953,19 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>0.03850785559369396</v>
+        <v>3.850785559369396</v>
       </c>
       <c r="C245" t="n">
-        <v>0.07422214939710536</v>
+        <v>7.422214939710536</v>
       </c>
       <c r="D245" t="n">
-        <v>0.04814095014480779</v>
+        <v>4.814095014480779</v>
       </c>
       <c r="E245" t="n">
-        <v>0.08576280299131578</v>
+        <v>8.576280299131579</v>
       </c>
       <c r="F245" t="n">
-        <v>0.1394462886009298</v>
+        <v>13.94462886009298</v>
       </c>
       <c r="G245" t="n">
         <v>2.92683</v>
@@ -10996,19 +10996,19 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.001941199755403744</v>
+        <v>0.1941199755403744</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.006881005195007561</v>
+        <v>-0.6881005195007561</v>
       </c>
       <c r="D246" t="n">
-        <v>0.01821786103165723</v>
+        <v>1.821786103165723</v>
       </c>
       <c r="E246" t="n">
-        <v>0.09481645389781512</v>
+        <v>9.481645389781512</v>
       </c>
       <c r="F246" t="n">
-        <v>0.1182500420932786</v>
+        <v>11.82500420932786</v>
       </c>
       <c r="G246" t="n">
         <v>3.125</v>
@@ -11039,19 +11039,19 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.003259899185758308</v>
+        <v>-0.3259899185758308</v>
       </c>
       <c r="C247" t="n">
-        <v>0.02261945142372523</v>
+        <v>2.261945142372523</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.01613702249509386</v>
+        <v>-1.613702249509386</v>
       </c>
       <c r="E247" t="n">
-        <v>0.09099938023603049</v>
+        <v>9.099938023603048</v>
       </c>
       <c r="F247" t="n">
-        <v>0.08047097541414283</v>
+        <v>8.047097541414283</v>
       </c>
       <c r="G247" t="n">
         <v>3.11587</v>
@@ -11082,19 +11082,19 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-0.01542230263887567</v>
+        <v>-1.542230263887567</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.02325908267393884</v>
+        <v>-2.325908267393884</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.03090282388185794</v>
+        <v>-3.090282388185794</v>
       </c>
       <c r="E248" t="n">
-        <v>0.08143297689088835</v>
+        <v>8.143297689088836</v>
       </c>
       <c r="F248" t="n">
-        <v>0.04402541385019254</v>
+        <v>4.402541385019254</v>
       </c>
       <c r="G248" t="n">
         <v>2.9098</v>
@@ -11125,19 +11125,19 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>0.0144833089292391</v>
+        <v>1.44833089292391</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.00235516903063715</v>
+        <v>-0.2355169030637039</v>
       </c>
       <c r="D249" t="n">
-        <v>0.02497926009125817</v>
+        <v>2.497926009125817</v>
       </c>
       <c r="E249" t="n">
-        <v>0.07140901526058352</v>
+        <v>7.140901526058352</v>
       </c>
       <c r="F249" t="n">
-        <v>0.09392992139372436</v>
+        <v>9.392992139372435</v>
       </c>
       <c r="G249" t="n">
         <v>2.98651</v>
@@ -11168,19 +11168,19 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>0.04817683432839903</v>
+        <v>4.817683432839903</v>
       </c>
       <c r="C250" t="n">
-        <v>0.04678615334283598</v>
+        <v>4.678615334283576</v>
       </c>
       <c r="D250" t="n">
-        <v>0.06337564785684013</v>
+        <v>6.337564785684013</v>
       </c>
       <c r="E250" t="n">
-        <v>0.08281862738730728</v>
+        <v>8.281862738730727</v>
       </c>
       <c r="F250" t="n">
-        <v>0.1349262661830506</v>
+        <v>13.49262661830506</v>
       </c>
       <c r="G250" t="n">
         <v>3.57488</v>
@@ -11211,19 +11211,19 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.008303809079122537</v>
+        <v>0.8303809079122537</v>
       </c>
       <c r="C251" t="n">
-        <v>0.01477657197210713</v>
+        <v>1.477657197210713</v>
       </c>
       <c r="D251" t="n">
-        <v>0.02659409229258847</v>
+        <v>2.659409229258847</v>
       </c>
       <c r="E251" t="n">
-        <v>0.08429473218608274</v>
+        <v>8.429473218608274</v>
       </c>
       <c r="F251" t="n">
-        <v>0.09688543425286866</v>
+        <v>9.688543425286866</v>
       </c>
       <c r="G251" t="n">
         <v>2.50723</v>
@@ -11254,19 +11254,19 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>0.03660185791849613</v>
+        <v>3.660185791849613</v>
       </c>
       <c r="C252" t="n">
-        <v>0.02985280301847459</v>
+        <v>2.985280301847459</v>
       </c>
       <c r="D252" t="n">
-        <v>0.039483946110072</v>
+        <v>3.9483946110072</v>
       </c>
       <c r="E252" t="n">
-        <v>0.1020423573868365</v>
+        <v>10.20423573868365</v>
       </c>
       <c r="F252" t="n">
-        <v>0.1440103706322551</v>
+        <v>14.40103706322551</v>
       </c>
       <c r="G252" t="n">
         <v>2.29885</v>
@@ -11297,19 +11297,19 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>0.07117710391463228</v>
+        <v>7.117710391463228</v>
       </c>
       <c r="C253" t="n">
-        <v>0.08443535038248529</v>
+        <v>8.443535038248529</v>
       </c>
       <c r="D253" t="n">
-        <v>0.03625809686479164</v>
+        <v>3.625809686479164</v>
       </c>
       <c r="E253" t="n">
-        <v>0.07930211888163075</v>
+        <v>7.930211888163075</v>
       </c>
       <c r="F253" t="n">
-        <v>0.1198334471005023</v>
+        <v>11.98334471005023</v>
       </c>
       <c r="G253" t="n">
         <v>2.47148</v>
@@ -11340,19 +11340,19 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>0.07365214682268229</v>
+        <v>7.365214682268229</v>
       </c>
       <c r="C254" t="n">
-        <v>0.07324055137747054</v>
+        <v>7.324055137747054</v>
       </c>
       <c r="D254" t="n">
-        <v>0.05745492857886414</v>
+        <v>5.745492857886414</v>
       </c>
       <c r="E254" t="n">
-        <v>0.08195360074678093</v>
+        <v>8.195360074678092</v>
       </c>
       <c r="F254" t="n">
-        <v>0.1605208829938634</v>
+        <v>16.05208829938633</v>
       </c>
       <c r="G254" t="n">
         <v>2.77512</v>
@@ -11383,19 +11383,19 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>0.05447688862985522</v>
+        <v>5.447688862985522</v>
       </c>
       <c r="C255" t="n">
-        <v>0.05902160428961123</v>
+        <v>5.902160428961123</v>
       </c>
       <c r="D255" t="n">
-        <v>0.02549896497209159</v>
+        <v>2.549896497209159</v>
       </c>
       <c r="E255" t="n">
-        <v>0.0640275615899486</v>
+        <v>6.40275615899486</v>
       </c>
       <c r="F255" t="n">
-        <v>0.09442758474681656</v>
+        <v>9.442758474681657</v>
       </c>
       <c r="G255" t="n">
         <v>3.43184</v>
@@ -11426,19 +11426,19 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>0.1169260369515444</v>
+        <v>11.69260369515444</v>
       </c>
       <c r="C256" t="n">
-        <v>0.09870546556088611</v>
+        <v>9.870546556088611</v>
       </c>
       <c r="D256" t="n">
-        <v>0.05665534819237394</v>
+        <v>5.665534819237394</v>
       </c>
       <c r="E256" t="n">
-        <v>0.07167362280866429</v>
+        <v>7.167362280866429</v>
       </c>
       <c r="F256" t="n">
-        <v>0.1380193464833384</v>
+        <v>13.80193464833384</v>
       </c>
       <c r="G256" t="n">
         <v>3.39943</v>
@@ -11469,19 +11469,19 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>0.08785099197577129</v>
+        <v>8.785099197577129</v>
       </c>
       <c r="C257" t="n">
-        <v>0.08537419444554351</v>
+        <v>8.537419444554374</v>
       </c>
       <c r="D257" t="n">
-        <v>0.05102600017245051</v>
+        <v>5.102600017245051</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0745369339921611</v>
+        <v>7.45369339921611</v>
       </c>
       <c r="F257" t="n">
-        <v>0.1220632970664188</v>
+        <v>12.20632970664188</v>
       </c>
       <c r="G257" t="n">
         <v>4.07583</v>
@@ -11512,19 +11512,19 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>0.1192384274705727</v>
+        <v>11.92384274705727</v>
       </c>
       <c r="C258" t="n">
-        <v>0.1174520973265136</v>
+        <v>11.74520973265139</v>
       </c>
       <c r="D258" t="n">
-        <v>0.08783663898528737</v>
+        <v>8.783663898528737</v>
       </c>
       <c r="E258" t="n">
-        <v>0.07927405498168083</v>
+        <v>7.927405498168083</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1768569205895112</v>
+        <v>17.68569205895112</v>
       </c>
       <c r="G258" t="n">
         <v>4.35606</v>
@@ -11555,19 +11555,19 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>0.11446600575159</v>
+        <v>11.446600575159</v>
       </c>
       <c r="C259" t="n">
-        <v>0.09112896710121565</v>
+        <v>9.112896710121564</v>
       </c>
       <c r="D259" t="n">
-        <v>0.07830446161609883</v>
+        <v>7.830446161609883</v>
       </c>
       <c r="E259" t="n">
-        <v>0.08263089960511594</v>
+        <v>8.263089960511593</v>
       </c>
       <c r="F259" t="n">
-        <v>0.1749773369594201</v>
+        <v>17.49773369594201</v>
       </c>
       <c r="G259" t="n">
         <v>5.28801</v>
@@ -11598,19 +11598,19 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>0.0884960977265592</v>
+        <v>8.849609772655921</v>
       </c>
       <c r="C260" t="n">
-        <v>0.09290597596026728</v>
+        <v>9.290597596026728</v>
       </c>
       <c r="D260" t="n">
-        <v>0.08072700729430005</v>
+        <v>8.072700729430004</v>
       </c>
       <c r="E260" t="n">
-        <v>0.08668532644752824</v>
+        <v>8.668532644752824</v>
       </c>
       <c r="F260" t="n">
-        <v>0.1772885720549804</v>
+        <v>17.72885720549804</v>
       </c>
       <c r="G260" t="n">
         <v>5.46654</v>
@@ -11641,19 +11641,19 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>0.1252766492784214</v>
+        <v>12.52766492784214</v>
       </c>
       <c r="C261" t="n">
-        <v>0.102982473989669</v>
+        <v>10.2982473989669</v>
       </c>
       <c r="D261" t="n">
-        <v>0.05621256225451754</v>
+        <v>5.621256225451754</v>
       </c>
       <c r="E261" t="n">
-        <v>0.1041246194179266</v>
+        <v>10.41246194179266</v>
       </c>
       <c r="F261" t="n">
-        <v>0.1647965838208145</v>
+        <v>16.47965838208145</v>
       </c>
       <c r="G261" t="n">
         <v>4.86436</v>
@@ -11684,19 +11684,19 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>0.06800399785729572</v>
+        <v>6.800399785729572</v>
       </c>
       <c r="C262" t="n">
-        <v>0.06492418147981338</v>
+        <v>6.492418147981338</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.008176158675285428</v>
+        <v>-0.8176158675285428</v>
       </c>
       <c r="E262" t="n">
-        <v>0.08713618023532987</v>
+        <v>8.713618023532987</v>
       </c>
       <c r="F262" t="n">
-        <v>0.07270312491495079</v>
+        <v>7.270312491495079</v>
       </c>
       <c r="G262" t="n">
         <v>4.10448</v>
@@ -11727,19 +11727,19 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>0.09094094215499648</v>
+        <v>9.094094215499648</v>
       </c>
       <c r="C263" t="n">
-        <v>0.07446105009342752</v>
+        <v>7.446105009342729</v>
       </c>
       <c r="D263" t="n">
-        <v>0.03153466522347537</v>
+        <v>3.153466522347537</v>
       </c>
       <c r="E263" t="n">
-        <v>0.08713601409864324</v>
+        <v>8.713601409864324</v>
       </c>
       <c r="F263" t="n">
-        <v>0.1103570222020211</v>
+        <v>11.03570222020211</v>
       </c>
       <c r="G263" t="n">
         <v>4.79774</v>
@@ -11770,19 +11770,19 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>0.1340884606913195</v>
+        <v>13.40884606913195</v>
       </c>
       <c r="C264" t="n">
-        <v>0.1122644364547654</v>
+        <v>11.22644364547656</v>
       </c>
       <c r="D264" t="n">
-        <v>0.04655799550792006</v>
+        <v>4.655799550792006</v>
       </c>
       <c r="E264" t="n">
-        <v>0.06297441498966472</v>
+        <v>6.297441498966472</v>
       </c>
       <c r="F264" t="n">
-        <v>0.09952348806129585</v>
+        <v>9.952348806129585</v>
       </c>
       <c r="G264" t="n">
         <v>4.58801</v>
@@ -11813,19 +11813,19 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>0.08051810189784581</v>
+        <v>8.051810189784581</v>
       </c>
       <c r="C265" t="n">
-        <v>0.05782081560706254</v>
+        <v>5.782081560706254</v>
       </c>
       <c r="D265" t="n">
-        <v>0.02716916294732363</v>
+        <v>2.716916294732363</v>
       </c>
       <c r="E265" t="n">
-        <v>0.07341637362815145</v>
+        <v>7.341637362815145</v>
       </c>
       <c r="F265" t="n">
-        <v>0.1055252329897978</v>
+        <v>10.55252329897978</v>
       </c>
       <c r="G265" t="n">
         <v>4.63822</v>
@@ -11856,19 +11856,19 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>0.02583496886206849</v>
+        <v>2.583496886206849</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.001924203004195046</v>
+        <v>-0.1924203004195046</v>
       </c>
       <c r="D266" t="n">
-        <v>0.02193771530865063</v>
+        <v>2.193771530865063</v>
       </c>
       <c r="E266" t="n">
-        <v>0.1202027629113644</v>
+        <v>12.02027629113644</v>
       </c>
       <c r="F266" t="n">
-        <v>0.1553028477810436</v>
+        <v>15.53028477810436</v>
       </c>
       <c r="G266" t="n">
         <v>4.28305</v>
@@ -11899,19 +11899,19 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>0.05106135023096825</v>
+        <v>5.106135023096825</v>
       </c>
       <c r="C267" t="n">
-        <v>0.01665031881611179</v>
+        <v>1.665031881611179</v>
       </c>
       <c r="D267" t="n">
-        <v>0.03454386275544596</v>
+        <v>3.454386275544596</v>
       </c>
       <c r="E267" t="n">
-        <v>0.1354215568601143</v>
+        <v>13.54215568601143</v>
       </c>
       <c r="F267" t="n">
-        <v>0.1782535593890306</v>
+        <v>17.82535593890307</v>
       </c>
       <c r="G267" t="n">
         <v>3.96313</v>
@@ -11942,19 +11942,19 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>0.05822645824546679</v>
+        <v>5.822645824546679</v>
       </c>
       <c r="C268" t="n">
-        <v>0.03406630501793262</v>
+        <v>3.406630501793262</v>
       </c>
       <c r="D268" t="n">
-        <v>0.009105918666783674</v>
+        <v>0.9105918666783674</v>
       </c>
       <c r="E268" t="n">
-        <v>0.1511426735778356</v>
+        <v>15.11426735778356</v>
       </c>
       <c r="F268" t="n">
-        <v>0.165171747870255</v>
+        <v>16.5171747870255</v>
       </c>
       <c r="G268" t="n">
         <v>3.47032</v>
@@ -11985,19 +11985,19 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>0.0238684106524516</v>
+        <v>2.38684106524516</v>
       </c>
       <c r="C269" t="n">
-        <v>0.007189397189474089</v>
+        <v>0.7189397189474089</v>
       </c>
       <c r="D269" t="n">
-        <v>0.02949557564385952</v>
+        <v>2.949557564385952</v>
       </c>
       <c r="E269" t="n">
-        <v>0.1012616007499956</v>
+        <v>10.12616007499956</v>
       </c>
       <c r="F269" t="n">
-        <v>0.1242473303809164</v>
+        <v>12.42473303809164</v>
       </c>
       <c r="G269" t="n">
         <v>3.55191</v>
@@ -12028,19 +12028,19 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>0.02700325205104259</v>
+        <v>2.700325205104259</v>
       </c>
       <c r="C270" t="n">
-        <v>0.003546777387537281</v>
+        <v>0.3546777387537281</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.01518029222767259</v>
+        <v>-1.518029222767259</v>
       </c>
       <c r="E270" t="n">
-        <v>0.1177232286894059</v>
+        <v>11.77232286894059</v>
       </c>
       <c r="F270" t="n">
-        <v>0.1003053325047623</v>
+        <v>10.03053325047622</v>
       </c>
       <c r="G270" t="n">
         <v>3.902</v>
@@ -12071,19 +12071,19 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>0.04102823757040852</v>
+        <v>4.102823757040852</v>
       </c>
       <c r="C271" t="n">
-        <v>0.03271670702470497</v>
+        <v>3.271670702470497</v>
       </c>
       <c r="D271" t="n">
-        <v>-0.0117125574806336</v>
+        <v>-1.17125574806336</v>
       </c>
       <c r="E271" t="n">
-        <v>0.1272699074573509</v>
+        <v>12.72699074573509</v>
       </c>
       <c r="F271" t="n">
-        <v>0.1223517566241541</v>
+        <v>12.23517566241541</v>
       </c>
       <c r="G271" t="n">
         <v>3.2287</v>
@@ -12114,19 +12114,19 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>0.0380241093376219</v>
+        <v>3.80241093376219</v>
       </c>
       <c r="C272" t="n">
-        <v>0.02824579172849906</v>
+        <v>2.824579172849906</v>
       </c>
       <c r="D272" t="n">
-        <v>-0.02926481791735602</v>
+        <v>-2.926481791735602</v>
       </c>
       <c r="E272" t="n">
-        <v>0.1250259260835889</v>
+        <v>12.50259260835889</v>
       </c>
       <c r="F272" t="n">
-        <v>0.09671828508600444</v>
+        <v>9.671828508600445</v>
       </c>
       <c r="G272" t="n">
         <v>3.12779</v>
@@ -12157,19 +12157,19 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>0.02047932537386288</v>
+        <v>2.047932537386288</v>
       </c>
       <c r="C273" t="n">
-        <v>0.02703547866816791</v>
+        <v>2.703547866816791</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.001125718736767256</v>
+        <v>-0.1125718736767256</v>
       </c>
       <c r="E273" t="n">
-        <v>0.1217080980843452</v>
+        <v>12.17080980843452</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1184107940076478</v>
+        <v>11.84107940076478</v>
       </c>
       <c r="G273" t="n">
         <v>3.38983</v>
@@ -12200,19 +12200,19 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.0013967557059269</v>
+        <v>-0.13967557059269</v>
       </c>
       <c r="C274" t="n">
-        <v>0.002207406341990348</v>
+        <v>0.2207406341990348</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0003492681109842355</v>
+        <v>0.03492681109842355</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1193533455920028</v>
+        <v>11.93533455920028</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1217544609466823</v>
+        <v>12.17544609466823</v>
       </c>
       <c r="G274" t="n">
         <v>3.04659</v>
@@ -12243,19 +12243,19 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.003207261782844362</v>
+        <v>-0.3207261782844362</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.004725784318809101</v>
+        <v>-0.472578431880899</v>
       </c>
       <c r="D275" t="n">
-        <v>-0.02022566075332288</v>
+        <v>-2.022566075332288</v>
       </c>
       <c r="E275" t="n">
-        <v>0.1091480364208286</v>
+        <v>10.91480364208286</v>
       </c>
       <c r="F275" t="n">
-        <v>0.08914445192139819</v>
+        <v>8.914445192139819</v>
       </c>
       <c r="G275" t="n">
         <v>3.59066</v>
@@ -12286,19 +12286,19 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-0.03988745706072305</v>
+        <v>-3.988745706072305</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.04152270181218076</v>
+        <v>-4.152270181218087</v>
       </c>
       <c r="D276" t="n">
-        <v>-0.03715190241320476</v>
+        <v>-3.715190241320476</v>
       </c>
       <c r="E276" t="n">
-        <v>0.08911794670301565</v>
+        <v>8.911794670301564</v>
       </c>
       <c r="F276" t="n">
-        <v>0.04409863943221204</v>
+        <v>4.409863943221204</v>
       </c>
       <c r="G276" t="n">
         <v>3.67055</v>
@@ -12329,19 +12329,19 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-0.0335977939453902</v>
+        <v>-3.35977939453902</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.03721698083349578</v>
+        <v>-3.721698083349578</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.03386670997398411</v>
+        <v>-3.386670997398411</v>
       </c>
       <c r="E277" t="n">
-        <v>0.1080416204462631</v>
+        <v>10.80416204462631</v>
       </c>
       <c r="F277" t="n">
-        <v>0.08827771897887482</v>
+        <v>8.827771897887482</v>
       </c>
       <c r="G277" t="n">
         <v>3.45745</v>
@@ -12372,19 +12372,19 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>0.03267400609230675</v>
+        <v>3.267400609230675</v>
       </c>
       <c r="C278" t="n">
-        <v>0.03589726468039656</v>
+        <v>3.589726468039656</v>
       </c>
       <c r="D278" t="n">
-        <v>-0.0162163747555073</v>
+        <v>-1.62163747555073</v>
       </c>
       <c r="E278" t="n">
-        <v>0.06127423963776057</v>
+        <v>6.127423963776057</v>
       </c>
       <c r="F278" t="n">
-        <v>0.04402028610889386</v>
+        <v>4.402028610889386</v>
       </c>
       <c r="G278" t="n">
         <v>3.125</v>
@@ -12415,19 +12415,19 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.00118178649757128</v>
+        <v>-0.118178649757128</v>
       </c>
       <c r="C279" t="n">
-        <v>0.004800319367258332</v>
+        <v>0.4800319367258332</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.003347431432068393</v>
+        <v>-0.3347431432068393</v>
       </c>
       <c r="E279" t="n">
-        <v>0.03998810603262903</v>
+        <v>3.998810603262903</v>
       </c>
       <c r="F279" t="n">
-        <v>0.02954617429174844</v>
+        <v>2.954617429174844</v>
       </c>
       <c r="G279" t="n">
         <v>3.01418</v>
@@ -12458,19 +12458,19 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.01843770045572424</v>
+        <v>-1.843770045572424</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.02143309110954994</v>
+        <v>-2.143309110954994</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.007994992367717169</v>
+        <v>-0.7994992367717169</v>
       </c>
       <c r="E280" t="n">
-        <v>0.004609418439403878</v>
+        <v>0.4609418439403878</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.01198779532100924</v>
+        <v>-1.198779532100924</v>
       </c>
       <c r="G280" t="n">
         <v>3.26567</v>
@@ -12501,19 +12501,19 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>0.02177146027128529</v>
+        <v>2.177146027128529</v>
       </c>
       <c r="C281" t="n">
-        <v>0.01841871992387278</v>
+        <v>1.841871992387278</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.03089934422089546</v>
+        <v>-3.089934422089546</v>
       </c>
       <c r="E281" t="n">
-        <v>0.03986134638673811</v>
+        <v>3.986134638673811</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.001172855387057581</v>
+        <v>-0.1172855387057581</v>
       </c>
       <c r="G281" t="n">
         <v>2.63852</v>
@@ -12544,19 +12544,19 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>0.0119906287137117</v>
+        <v>1.19906287137117</v>
       </c>
       <c r="C282" t="n">
-        <v>0.01625980916141145</v>
+        <v>1.625980916141145</v>
       </c>
       <c r="D282" t="n">
-        <v>0.002861040679217552</v>
+        <v>0.2861040679217552</v>
       </c>
       <c r="E282" t="n">
-        <v>0.009897368571085252</v>
+        <v>0.9897368571085252</v>
       </c>
       <c r="F282" t="n">
-        <v>0.0116762326719495</v>
+        <v>1.16762326719495</v>
       </c>
       <c r="G282" t="n">
         <v>2.35808</v>
@@ -12587,19 +12587,19 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>0.01116867338422756</v>
+        <v>1.116867338422756</v>
       </c>
       <c r="C283" t="n">
-        <v>0.005712768615540487</v>
+        <v>0.5712768615540487</v>
       </c>
       <c r="D283" t="n">
-        <v>0.001498130003839471</v>
+        <v>0.1498130003839471</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.001348458053189394</v>
+        <v>-0.1348458053189394</v>
       </c>
       <c r="F283" t="n">
-        <v>0.006583366471794694</v>
+        <v>0.6583366471794694</v>
       </c>
       <c r="G283" t="n">
         <v>1.56386</v>
@@ -12630,19 +12630,19 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>0.0253086624616603</v>
+        <v>2.53086624616603</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0005377514698985397</v>
+        <v>-0.05377514698984287</v>
       </c>
       <c r="D284" t="n">
-        <v>0.02829244701264844</v>
+        <v>2.829244701264844</v>
       </c>
       <c r="E284" t="n">
-        <v>0.007753605927239393</v>
+        <v>0.7753605927239393</v>
       </c>
       <c r="F284" t="n">
-        <v>0.03647207409992936</v>
+        <v>3.647207409992936</v>
       </c>
       <c r="G284" t="n">
         <v>1.38648</v>
@@ -12673,19 +12673,19 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.004713074011657437</v>
+        <v>0.4713074011657437</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.007783124821529652</v>
+        <v>-0.7783124821529652</v>
       </c>
       <c r="D285" t="n">
-        <v>-0.01489860113452579</v>
+        <v>-1.489860113452579</v>
       </c>
       <c r="E285" t="n">
-        <v>0.002697309336072484</v>
+        <v>0.2697309336072484</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.02393965286651845</v>
+        <v>-2.393965286651845</v>
       </c>
       <c r="G285" t="n">
         <v>1.03538</v>
@@ -12716,19 +12716,19 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>0.04658752230467544</v>
+        <v>4.658752230467544</v>
       </c>
       <c r="C286" t="n">
-        <v>0.01836271241758403</v>
+        <v>1.836271241758403</v>
       </c>
       <c r="D286" t="n">
-        <v>0.02953083546730495</v>
+        <v>2.953083546730495</v>
       </c>
       <c r="E286" t="n">
-        <v>0.0126805752211101</v>
+        <v>1.26805752211101</v>
       </c>
       <c r="F286" t="n">
-        <v>0.04181582055819955</v>
+        <v>4.181582055819955</v>
       </c>
       <c r="G286" t="n">
         <v>1.91304</v>
@@ -12759,19 +12759,19 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>0.05816305571528346</v>
+        <v>5.816305571528346</v>
       </c>
       <c r="C287" t="n">
-        <v>0.03936736780516248</v>
+        <v>3.936736780516248</v>
       </c>
       <c r="D287" t="n">
-        <v>0.04864381197979695</v>
+        <v>4.864381197979695</v>
       </c>
       <c r="E287" t="n">
-        <v>0.02679866638210382</v>
+        <v>2.679866638210382</v>
       </c>
       <c r="F287" t="n">
-        <v>0.08062522233907399</v>
+        <v>8.062522233907398</v>
       </c>
       <c r="G287" t="n">
         <v>1.47314</v>
@@ -12802,19 +12802,19 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>0.03481089525225634</v>
+        <v>3.481089525225634</v>
       </c>
       <c r="C288" t="n">
-        <v>0.02924721239557271</v>
+        <v>2.924721239557271</v>
       </c>
       <c r="D288" t="n">
-        <v>0.02107533850769761</v>
+        <v>2.107533850769761</v>
       </c>
       <c r="E288" t="n">
-        <v>0.03368005906624827</v>
+        <v>3.368005906624827</v>
       </c>
       <c r="F288" t="n">
-        <v>0.05833923359984761</v>
+        <v>5.833923359984761</v>
       </c>
       <c r="G288" t="n">
         <v>1.12263</v>
@@ -12845,19 +12845,19 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>0.06843333982594535</v>
+        <v>6.843333982594535</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0598250125291766</v>
+        <v>5.98250125291766</v>
       </c>
       <c r="D289" t="n">
-        <v>0.0223260254751616</v>
+        <v>2.23260254751616</v>
       </c>
       <c r="E289" t="n">
-        <v>0.03828976912609172</v>
+        <v>3.828976912609172</v>
       </c>
       <c r="F289" t="n">
-        <v>0.08274234768504174</v>
+        <v>8.274234768504174</v>
       </c>
       <c r="G289" t="n">
         <v>0.59983</v>
@@ -12888,19 +12888,19 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.008761466545507801</v>
+        <v>0.8761466545507801</v>
       </c>
       <c r="C290" t="n">
-        <v>0.0118521772657374</v>
+        <v>1.185217726573762</v>
       </c>
       <c r="D290" t="n">
-        <v>-0.02208771855578739</v>
+        <v>-2.208771855578739</v>
       </c>
       <c r="E290" t="n">
-        <v>0.02401785583549021</v>
+        <v>2.401785583549021</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.005598222880354942</v>
+        <v>-0.5598222880354942</v>
       </c>
       <c r="G290" t="n">
         <v>0.77922</v>
@@ -12931,19 +12931,19 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>0.03298028870279213</v>
+        <v>3.298028870279213</v>
       </c>
       <c r="C291" t="n">
-        <v>0.03351274961961082</v>
+        <v>3.351274961961059</v>
       </c>
       <c r="D291" t="n">
-        <v>-0.01251589789513929</v>
+        <v>-1.251589789513929</v>
       </c>
       <c r="E291" t="n">
-        <v>0.03627508120133127</v>
+        <v>3.627508120133127</v>
       </c>
       <c r="F291" t="n">
-        <v>0.01206347769112126</v>
+        <v>1.206347769112126</v>
       </c>
       <c r="G291" t="n">
         <v>0.60241</v>
@@ -12974,19 +12974,19 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>0.06314907075575027</v>
+        <v>6.314907075575027</v>
       </c>
       <c r="C292" t="n">
-        <v>0.05590874372075838</v>
+        <v>5.590874372075838</v>
       </c>
       <c r="D292" t="n">
-        <v>0.02178769830584604</v>
+        <v>2.178769830584604</v>
       </c>
       <c r="E292" t="n">
-        <v>0.04879953815476923</v>
+        <v>4.879953815476923</v>
       </c>
       <c r="F292" t="n">
-        <v>0.06466415316239305</v>
+        <v>6.466415316239305</v>
       </c>
       <c r="G292" t="n">
         <v>0.34188</v>
@@ -13017,19 +13017,19 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>0.03545188947865219</v>
+        <v>3.545188947865219</v>
       </c>
       <c r="C293" t="n">
-        <v>0.02389758570113432</v>
+        <v>2.389758570113432</v>
       </c>
       <c r="D293" t="n">
-        <v>0.02532719483097323</v>
+        <v>2.532719483097323</v>
       </c>
       <c r="E293" t="n">
-        <v>0.0424300668958113</v>
+        <v>4.24300668958113</v>
       </c>
       <c r="F293" t="n">
-        <v>0.06821875781081577</v>
+        <v>6.821875781081577</v>
       </c>
       <c r="G293" t="n">
         <v>0.34276</v>
@@ -13060,19 +13060,19 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>0.0836924401644692</v>
+        <v>8.36924401644692</v>
       </c>
       <c r="C294" t="n">
-        <v>0.05934059988893314</v>
+        <v>5.934059988893314</v>
       </c>
       <c r="D294" t="n">
-        <v>0.04199954387806892</v>
+        <v>4.199954387806892</v>
       </c>
       <c r="E294" t="n">
-        <v>0.06255128194430526</v>
+        <v>6.255128194430526</v>
       </c>
       <c r="F294" t="n">
-        <v>0.1154880351145597</v>
+        <v>11.54880351145597</v>
       </c>
       <c r="G294" t="n">
         <v>0.59727</v>
@@ -13103,19 +13103,19 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>0.06580369122344365</v>
+        <v>6.580369122344365</v>
       </c>
       <c r="C295" t="n">
-        <v>0.05390703131980179</v>
+        <v>5.390703131980179</v>
       </c>
       <c r="D295" t="n">
-        <v>0.06110291894376974</v>
+        <v>6.110291894376974</v>
       </c>
       <c r="E295" t="n">
-        <v>0.06953679655448131</v>
+        <v>6.953679655448131</v>
       </c>
       <c r="F295" t="n">
-        <v>0.1508537326920969</v>
+        <v>15.08537326920969</v>
       </c>
       <c r="G295" t="n">
         <v>1.11206</v>
@@ -13146,19 +13146,19 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>0.05118680360620087</v>
+        <v>5.118680360620087</v>
       </c>
       <c r="C296" t="n">
-        <v>0.05699099198300606</v>
+        <v>5.699099198300606</v>
       </c>
       <c r="D296" t="n">
-        <v>0.001167878717958981</v>
+        <v>0.1167878717958981</v>
       </c>
       <c r="E296" t="n">
-        <v>0.04682280877085487</v>
+        <v>4.682280877085487</v>
       </c>
       <c r="F296" t="n">
-        <v>0.05257264220796709</v>
+        <v>5.257264220796709</v>
       </c>
       <c r="G296" t="n">
         <v>1.53846</v>
@@ -13189,19 +13189,19 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>0.03875228811278908</v>
+        <v>3.875228811278908</v>
       </c>
       <c r="C297" t="n">
-        <v>0.03991269924559249</v>
+        <v>3.991269924559249</v>
       </c>
       <c r="D297" t="n">
-        <v>0.02955164633677843</v>
+        <v>2.955164633677843</v>
       </c>
       <c r="E297" t="n">
-        <v>0.04085445125718756</v>
+        <v>4.085445125718756</v>
       </c>
       <c r="F297" t="n">
-        <v>0.05919019585052454</v>
+        <v>5.919019585052454</v>
       </c>
       <c r="G297" t="n">
         <v>2.13493</v>
@@ -13232,19 +13232,19 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>0.02454716518148237</v>
+        <v>2.454716518148237</v>
       </c>
       <c r="C298" t="n">
-        <v>0.0108111524072092</v>
+        <v>1.081115240720942</v>
       </c>
       <c r="D298" t="n">
-        <v>0.004371781129176133</v>
+        <v>0.4371781129176133</v>
       </c>
       <c r="E298" t="n">
-        <v>0.03051521458573458</v>
+        <v>3.051521458573458</v>
       </c>
       <c r="F298" t="n">
-        <v>0.03245793136343056</v>
+        <v>3.245793136343056</v>
       </c>
       <c r="G298" t="n">
         <v>1.45051</v>
@@ -13275,19 +13275,19 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>0.03298433728859718</v>
+        <v>3.298433728859718</v>
       </c>
       <c r="C299" t="n">
-        <v>0.02777044801185236</v>
+        <v>2.777044801185236</v>
       </c>
       <c r="D299" t="n">
-        <v>0.01825031025128387</v>
+        <v>1.825031025128387</v>
       </c>
       <c r="E299" t="n">
-        <v>0.02811656974509091</v>
+        <v>2.811656974509091</v>
       </c>
       <c r="F299" t="n">
-        <v>0.04355258956633312</v>
+        <v>4.355258956633312</v>
       </c>
       <c r="G299" t="n">
         <v>1.53715</v>
@@ -13318,19 +13318,19 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>0.04507386817870995</v>
+        <v>4.507386817870995</v>
       </c>
       <c r="C300" t="n">
-        <v>0.03663906644519321</v>
+        <v>3.663906644519321</v>
       </c>
       <c r="D300" t="n">
-        <v>0.03901322631013682</v>
+        <v>3.901322631013682</v>
       </c>
       <c r="E300" t="n">
-        <v>0.03749830337962567</v>
+        <v>3.749830337962567</v>
       </c>
       <c r="F300" t="n">
-        <v>0.08065503164147758</v>
+        <v>8.065503164147758</v>
       </c>
       <c r="G300" t="n">
         <v>2.13493</v>
@@ -13361,19 +13361,19 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>0.04774522760947697</v>
+        <v>4.774522760947697</v>
       </c>
       <c r="C301" t="n">
-        <v>0.03147561656173092</v>
+        <v>3.147561656173092</v>
       </c>
       <c r="D301" t="n">
-        <v>0.05331745518014097</v>
+        <v>5.331745518014097</v>
       </c>
       <c r="E301" t="n">
-        <v>0.01882280366944999</v>
+        <v>1.882280366944999</v>
       </c>
       <c r="F301" t="n">
-        <v>0.08795937664020936</v>
+        <v>8.795937664020936</v>
       </c>
       <c r="G301" t="n">
         <v>2.98126</v>
@@ -13404,19 +13404,19 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>0.05336380009538866</v>
+        <v>5.336380009538866</v>
       </c>
       <c r="C302" t="n">
-        <v>0.03377411742877423</v>
+        <v>3.377411742877423</v>
       </c>
       <c r="D302" t="n">
-        <v>0.04101074181332542</v>
+        <v>4.101074181332542</v>
       </c>
       <c r="E302" t="n">
-        <v>0.01196428282588413</v>
+        <v>1.196428282588413</v>
       </c>
       <c r="F302" t="n">
-        <v>0.04938556867702859</v>
+        <v>4.938556867702859</v>
       </c>
       <c r="G302" t="n">
         <v>2.83505</v>
@@ -13447,19 +13447,19 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>0.05235040447155748</v>
+        <v>5.235040447155748</v>
       </c>
       <c r="C303" t="n">
-        <v>0.03221353623964363</v>
+        <v>3.221353623964363</v>
       </c>
       <c r="D303" t="n">
-        <v>0.01621144324312662</v>
+        <v>1.621144324312662</v>
       </c>
       <c r="E303" t="n">
-        <v>0.03115644147601593</v>
+        <v>3.115644147601593</v>
       </c>
       <c r="F303" t="n">
-        <v>0.03542414888719758</v>
+        <v>3.542414888719758</v>
       </c>
       <c r="G303" t="n">
         <v>3.1651</v>
@@ -13490,19 +13490,19 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>0.01069391546143206</v>
+        <v>1.069391546143206</v>
       </c>
       <c r="C304" t="n">
-        <v>0.005282433788493579</v>
+        <v>0.5282433788493579</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.006741055249131711</v>
+        <v>-0.6741055249131711</v>
       </c>
       <c r="E304" t="n">
-        <v>0.03834595941427565</v>
+        <v>3.834595941427565</v>
       </c>
       <c r="F304" t="n">
-        <v>0.02510222301201392</v>
+        <v>2.510222301201392</v>
       </c>
       <c r="G304" t="n">
         <v>3.2368</v>
@@ -13533,19 +13533,19 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>0.01076295803963223</v>
+        <v>1.076295803963223</v>
       </c>
       <c r="C305" t="n">
-        <v>0.001589416570332736</v>
+        <v>0.1589416570332958</v>
       </c>
       <c r="D305" t="n">
-        <v>0.02198689027007572</v>
+        <v>2.198689027007572</v>
       </c>
       <c r="E305" t="n">
-        <v>0.01963705452568854</v>
+        <v>1.963705452568854</v>
       </c>
       <c r="F305" t="n">
-        <v>0.04427161707563054</v>
+        <v>4.427161707563054</v>
       </c>
       <c r="G305" t="n">
         <v>3.67208</v>
@@ -13576,19 +13576,19 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.006425467793484962</v>
+        <v>0.6425467793484962</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0004784092237797299</v>
+        <v>0.04784092237797299</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.01261613960311925</v>
+        <v>-1.261613960311925</v>
       </c>
       <c r="E306" t="n">
-        <v>0.023206050907844</v>
+        <v>2.3206050907844</v>
       </c>
       <c r="F306" t="n">
-        <v>0.01373212451989558</v>
+        <v>1.373212451989558</v>
       </c>
       <c r="G306" t="n">
         <v>3.39271</v>
@@ -13619,19 +13619,19 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>0.02179122487909946</v>
+        <v>2.179122487909946</v>
       </c>
       <c r="C307" t="n">
-        <v>0.01356348012598785</v>
+        <v>1.356348012598785</v>
       </c>
       <c r="D307" t="n">
-        <v>-0.02600368830965816</v>
+        <v>-2.600368830965816</v>
       </c>
       <c r="E307" t="n">
-        <v>0.03142290151672644</v>
+        <v>3.142290151672644</v>
       </c>
       <c r="F307" t="n">
-        <v>0.01070719660349995</v>
+        <v>1.070719660349995</v>
       </c>
       <c r="G307" t="n">
         <v>3.6379</v>
@@ -13662,19 +13662,19 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>0.01738037130226378</v>
+        <v>1.738037130226378</v>
       </c>
       <c r="C308" t="n">
-        <v>0.002692624512282471</v>
+        <v>0.2692624512282249</v>
       </c>
       <c r="D308" t="n">
-        <v>0.01605709819745593</v>
+        <v>1.605709819745593</v>
       </c>
       <c r="E308" t="n">
-        <v>0.04799335551868555</v>
+        <v>4.799335551868555</v>
       </c>
       <c r="F308" t="n">
-        <v>0.06886726952055944</v>
+        <v>6.886726952055944</v>
       </c>
       <c r="G308" t="n">
         <v>3.45118</v>
@@ -13705,19 +13705,19 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>0.0315065052806982</v>
+        <v>3.15065052806982</v>
       </c>
       <c r="C309" t="n">
-        <v>0.02229988549865602</v>
+        <v>2.229988549865602</v>
       </c>
       <c r="D309" t="n">
-        <v>0.005621748801291071</v>
+        <v>0.5621748801291071</v>
       </c>
       <c r="E309" t="n">
-        <v>0.05406119447917734</v>
+        <v>5.406119447917734</v>
       </c>
       <c r="F309" t="n">
-        <v>0.05003015904149954</v>
+        <v>5.003015904149954</v>
       </c>
       <c r="G309" t="n">
         <v>3.51171</v>
@@ -13748,19 +13748,19 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>0.05760639480092444</v>
+        <v>5.760639480092444</v>
       </c>
       <c r="C310" t="n">
-        <v>0.06605984965448597</v>
+        <v>6.605984965448575</v>
       </c>
       <c r="D310" t="n">
-        <v>0.02765365279777066</v>
+        <v>2.765365279777066</v>
       </c>
       <c r="E310" t="n">
-        <v>0.08394610749743325</v>
+        <v>8.394610749743325</v>
       </c>
       <c r="F310" t="n">
-        <v>0.1103031283644527</v>
+        <v>11.03031283644527</v>
       </c>
       <c r="G310" t="n">
         <v>3.61648</v>
@@ -13791,19 +13791,19 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>0.0392183953272558</v>
+        <v>3.92183953272558</v>
       </c>
       <c r="C311" t="n">
-        <v>0.03167353210164303</v>
+        <v>3.167353210164303</v>
       </c>
       <c r="D311" t="n">
-        <v>0.006449098348123794</v>
+        <v>0.6449098348123794</v>
       </c>
       <c r="E311" t="n">
-        <v>0.04879408110110828</v>
+        <v>4.879408110110828</v>
       </c>
       <c r="F311" t="n">
-        <v>0.04953581576758759</v>
+        <v>4.953581576758759</v>
       </c>
       <c r="G311" t="n">
         <v>3.70059</v>
@@ -13834,19 +13834,19 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>0.04030672935637236</v>
+        <v>4.030672935637236</v>
       </c>
       <c r="C312" t="n">
-        <v>0.02312771068015196</v>
+        <v>2.312771068015218</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.01061366387585427</v>
+        <v>-1.061366387585427</v>
       </c>
       <c r="E312" t="n">
-        <v>0.05824666263275935</v>
+        <v>5.824666263275935</v>
       </c>
       <c r="F312" t="n">
-        <v>0.04706509656613789</v>
+        <v>4.706509656613789</v>
       </c>
       <c r="G312" t="n">
         <v>3.26087</v>
@@ -13877,19 +13877,19 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>0.03256952397658175</v>
+        <v>3.256952397658175</v>
       </c>
       <c r="C313" t="n">
-        <v>0.02328857894111613</v>
+        <v>2.328857894111613</v>
       </c>
       <c r="D313" t="n">
-        <v>0.0004675393706392583</v>
+        <v>0.04675393706392583</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0633683603915105</v>
+        <v>6.33683603915105</v>
       </c>
       <c r="F313" t="n">
-        <v>0.07349908592472909</v>
+        <v>7.349908592472909</v>
       </c>
       <c r="G313" t="n">
         <v>3.30852</v>
@@ -13920,19 +13920,19 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>0.04284273075992617</v>
+        <v>4.284273075992617</v>
       </c>
       <c r="C314" t="n">
-        <v>0.03904035837362874</v>
+        <v>3.904035837362874</v>
       </c>
       <c r="D314" t="n">
-        <v>0.01486728282430261</v>
+        <v>1.486728282430261</v>
       </c>
       <c r="E314" t="n">
-        <v>0.08653343966139371</v>
+        <v>8.653343966139371</v>
       </c>
       <c r="F314" t="n">
-        <v>0.1089601368010873</v>
+        <v>10.89601368010873</v>
       </c>
       <c r="G314" t="n">
         <v>3.92648</v>
@@ -13963,19 +13963,19 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>0.01695417566818946</v>
+        <v>1.695417566818946</v>
       </c>
       <c r="C315" t="n">
-        <v>0.02794702492713141</v>
+        <v>2.794702492713119</v>
       </c>
       <c r="D315" t="n">
-        <v>0.009317167916605751</v>
+        <v>0.9317167916605751</v>
       </c>
       <c r="E315" t="n">
-        <v>0.04026048811944127</v>
+        <v>4.026048811944127</v>
       </c>
       <c r="F315" t="n">
-        <v>0.04392910871620126</v>
+        <v>4.392910871620126</v>
       </c>
       <c r="G315" t="n">
         <v>4.22886</v>
@@ -14006,19 +14006,19 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>0.02667460736765204</v>
+        <v>2.667460736765204</v>
       </c>
       <c r="C316" t="n">
-        <v>0.02932911382026671</v>
+        <v>2.932911382026648</v>
       </c>
       <c r="D316" t="n">
-        <v>0.003985254669233163</v>
+        <v>0.3985254669233163</v>
       </c>
       <c r="E316" t="n">
-        <v>0.03650596282030838</v>
+        <v>3.650596282030838</v>
       </c>
       <c r="F316" t="n">
-        <v>0.04020509334308242</v>
+        <v>4.020509334308242</v>
       </c>
       <c r="G316" t="n">
         <v>4.78548</v>
@@ -14049,19 +14049,19 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>0.08786087073308191</v>
+        <v>8.786087073308192</v>
       </c>
       <c r="C317" t="n">
-        <v>0.09064674858859445</v>
+        <v>9.064674858859423</v>
       </c>
       <c r="D317" t="n">
-        <v>0.00387501551756908</v>
+        <v>0.387501551756908</v>
       </c>
       <c r="E317" t="n">
-        <v>0.07316418948683445</v>
+        <v>7.316418948683445</v>
       </c>
       <c r="F317" t="n">
-        <v>0.08937423402856104</v>
+        <v>8.937423402856105</v>
       </c>
       <c r="G317" t="n">
         <v>4.28336</v>
@@ -14092,19 +14092,19 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>0.04393080703505214</v>
+        <v>4.393080703505214</v>
       </c>
       <c r="C318" t="n">
-        <v>0.05428876992000031</v>
+        <v>5.428876992000031</v>
       </c>
       <c r="D318" t="n">
-        <v>0.02155649256478576</v>
+        <v>2.155649256478576</v>
       </c>
       <c r="E318" t="n">
-        <v>0.05212340110491653</v>
+        <v>5.212340110491653</v>
       </c>
       <c r="F318" t="n">
-        <v>0.08451364972978914</v>
+        <v>8.451364972978915</v>
       </c>
       <c r="G318" t="n">
         <v>4.18376</v>
@@ -14135,19 +14135,19 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>0.04180576220044174</v>
+        <v>4.180576220044174</v>
       </c>
       <c r="C319" t="n">
-        <v>0.03362364189456635</v>
+        <v>3.362364189456657</v>
       </c>
       <c r="D319" t="n">
-        <v>0.02726818385755503</v>
+        <v>2.726818385755503</v>
       </c>
       <c r="E319" t="n">
-        <v>0.03719915067424484</v>
+        <v>3.719915067424484</v>
       </c>
       <c r="F319" t="n">
-        <v>0.07056169430981973</v>
+        <v>7.056169430981973</v>
       </c>
       <c r="G319" t="n">
         <v>4.40816</v>
@@ -14178,19 +14178,19 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>0.06696785105276204</v>
+        <v>6.696785105276204</v>
       </c>
       <c r="C320" t="n">
-        <v>0.06734312555106525</v>
+        <v>6.734312555106525</v>
       </c>
       <c r="D320" t="n">
-        <v>0.02221111410746235</v>
+        <v>2.221111410746235</v>
       </c>
       <c r="E320" t="n">
-        <v>0.03062122069966611</v>
+        <v>3.062122069966611</v>
       </c>
       <c r="F320" t="n">
-        <v>0.05673570033464137</v>
+        <v>5.673570033464137</v>
       </c>
       <c r="G320" t="n">
         <v>4.06835</v>
@@ -14221,19 +14221,19 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>0.05938480459757534</v>
+        <v>5.938480459757534</v>
       </c>
       <c r="C321" t="n">
-        <v>0.04638316396427</v>
+        <v>4.638316396427</v>
       </c>
       <c r="D321" t="n">
-        <v>0.01457379056003649</v>
+        <v>1.457379056003649</v>
       </c>
       <c r="E321" t="n">
-        <v>0.02661127550605769</v>
+        <v>2.661127550605769</v>
       </c>
       <c r="F321" t="n">
-        <v>0.02812140782604367</v>
+        <v>2.812140782604367</v>
       </c>
       <c r="G321" t="n">
         <v>3.63489</v>
@@ -14264,19 +14264,19 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>0.05567042878888717</v>
+        <v>5.567042878888717</v>
       </c>
       <c r="C322" t="n">
-        <v>0.03517921613197572</v>
+        <v>3.517921613197572</v>
       </c>
       <c r="D322" t="n">
-        <v>0.0005306793799160214</v>
+        <v>0.05306793799160214</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.005240318420215995</v>
+        <v>-0.5240318420215995</v>
       </c>
       <c r="F322" t="n">
-        <v>-0.01925600768888869</v>
+        <v>-1.925600768888869</v>
       </c>
       <c r="G322" t="n">
         <v>3.49026</v>
@@ -14307,19 +14307,19 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>0.04357806509517181</v>
+        <v>4.357806509517181</v>
       </c>
       <c r="C323" t="n">
-        <v>0.05143917803260534</v>
+        <v>5.143917803260556</v>
       </c>
       <c r="D323" t="n">
-        <v>0.008422528722962896</v>
+        <v>0.8422528722962896</v>
       </c>
       <c r="E323" t="n">
-        <v>0.04167543269776441</v>
+        <v>4.167543269776441</v>
       </c>
       <c r="F323" t="n">
-        <v>0.03912201306772523</v>
+        <v>3.912201306772523</v>
       </c>
       <c r="G323" t="n">
         <v>3.64964</v>
@@ -14350,19 +14350,19 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>0.07531085086948486</v>
+        <v>7.531085086948486</v>
       </c>
       <c r="C324" t="n">
-        <v>0.06857079026611124</v>
+        <v>6.857079026611124</v>
       </c>
       <c r="D324" t="n">
-        <v>0.03827018156259188</v>
+        <v>3.827018156259188</v>
       </c>
       <c r="E324" t="n">
-        <v>0.02183479946776545</v>
+        <v>2.183479946776545</v>
       </c>
       <c r="F324" t="n">
-        <v>0.05540582686539519</v>
+        <v>5.540582686539519</v>
       </c>
       <c r="G324" t="n">
         <v>3.56275</v>
@@ -14393,19 +14393,19 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>0.06088998948339919</v>
+        <v>6.088998948339919</v>
       </c>
       <c r="C325" t="n">
-        <v>0.05483179174550989</v>
+        <v>5.483179174550989</v>
       </c>
       <c r="D325" t="n">
-        <v>0.001554156349438118</v>
+        <v>0.1554156349438118</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0289160318585906</v>
+        <v>2.89160318585906</v>
       </c>
       <c r="F325" t="n">
-        <v>0.03072298813570273</v>
+        <v>3.072298813570273</v>
       </c>
       <c r="G325" t="n">
         <v>3.20256</v>
@@ -14436,19 +14436,19 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>0.05855143370621407</v>
+        <v>5.855143370621407</v>
       </c>
       <c r="C326" t="n">
-        <v>0.05011562899930411</v>
+        <v>5.011562899930411</v>
       </c>
       <c r="D326" t="n">
-        <v>0.007945457523386157</v>
+        <v>0.7945457523386157</v>
       </c>
       <c r="E326" t="n">
-        <v>0.04478531452313073</v>
+        <v>4.478531452313073</v>
       </c>
       <c r="F326" t="n">
-        <v>0.05417273833488068</v>
+        <v>5.417273833488068</v>
       </c>
       <c r="G326" t="n">
         <v>2.41158</v>
@@ -14479,19 +14479,19 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>0.09917462619523709</v>
+        <v>9.917462619523709</v>
       </c>
       <c r="C327" t="n">
-        <v>0.09494403871826451</v>
+        <v>9.494403871826451</v>
       </c>
       <c r="D327" t="n">
-        <v>0.02694518187304729</v>
+        <v>2.694518187304729</v>
       </c>
       <c r="E327" t="n">
-        <v>0.07803337214869899</v>
+        <v>7.803337214869899</v>
       </c>
       <c r="F327" t="n">
-        <v>0.105375030535565</v>
+        <v>10.5375030535565</v>
       </c>
       <c r="G327" t="n">
         <v>1.7502</v>
@@ -14522,19 +14522,19 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>0.1041945739232606</v>
+        <v>10.41945739232606</v>
       </c>
       <c r="C328" t="n">
-        <v>0.09144565002825411</v>
+        <v>9.144565002825388</v>
       </c>
       <c r="D328" t="n">
-        <v>0.03150291537392014</v>
+        <v>3.150291537392014</v>
       </c>
       <c r="E328" t="n">
-        <v>0.07364203646897005</v>
+        <v>7.364203646897005</v>
       </c>
       <c r="F328" t="n">
-        <v>0.1146591975377156</v>
+        <v>11.46591975377156</v>
       </c>
       <c r="G328" t="n">
         <v>1.33858</v>
@@ -14565,19 +14565,19 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>0.04000070077434925</v>
+        <v>4.000070077434925</v>
       </c>
       <c r="C329" t="n">
-        <v>0.03086214975340962</v>
+        <v>3.086214975340962</v>
       </c>
       <c r="D329" t="n">
-        <v>0.02842464902553576</v>
+        <v>2.842464902553576</v>
       </c>
       <c r="E329" t="n">
-        <v>0.03599908389074891</v>
+        <v>3.599908389074891</v>
       </c>
       <c r="F329" t="n">
-        <v>0.07943240685540509</v>
+        <v>7.943240685540509</v>
       </c>
       <c r="G329" t="n">
         <v>0.07899</v>
@@ -14608,19 +14608,19 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>0.06295765901860073</v>
+        <v>6.295765901860073</v>
       </c>
       <c r="C330" t="n">
-        <v>0.05629002415840167</v>
+        <v>5.629002415840167</v>
       </c>
       <c r="D330" t="n">
-        <v>0.01317507669097662</v>
+        <v>1.317507669097662</v>
       </c>
       <c r="E330" t="n">
-        <v>0.05631768108171653</v>
+        <v>5.631768108171653</v>
       </c>
       <c r="F330" t="n">
-        <v>0.08137113847614108</v>
+        <v>8.137113847614108</v>
       </c>
       <c r="G330" t="n">
         <v>0.07874</v>
@@ -14651,19 +14651,19 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>0.05954587173771553</v>
+        <v>5.954587173771553</v>
       </c>
       <c r="C331" t="n">
-        <v>0.07414486981490342</v>
+        <v>7.414486981490342</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.01078216469543902</v>
+        <v>-1.078216469543902</v>
       </c>
       <c r="E331" t="n">
-        <v>0.04981386314041991</v>
+        <v>4.981386314041991</v>
       </c>
       <c r="F331" t="n">
-        <v>0.04666813243096546</v>
+        <v>4.666813243096546</v>
       </c>
       <c r="G331" t="n">
         <v>-0.23456</v>
@@ -14694,19 +14694,19 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>0.04173061339683226</v>
+        <v>4.173061339683226</v>
       </c>
       <c r="C332" t="n">
-        <v>0.03974569170531494</v>
+        <v>3.974569170531494</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.0162738837456452</v>
+        <v>-1.62738837456452</v>
       </c>
       <c r="E332" t="n">
-        <v>0.0451157297877276</v>
+        <v>4.51157297877276</v>
       </c>
       <c r="F332" t="n">
-        <v>0.03624230474045764</v>
+        <v>3.624230474045764</v>
       </c>
       <c r="G332" t="n">
         <v>-0.31274</v>
@@ -14737,19 +14737,19 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>0.0383663930201219</v>
+        <v>3.83663930201219</v>
       </c>
       <c r="C333" t="n">
-        <v>0.03745083874855926</v>
+        <v>3.745083874855903</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.03156114157040391</v>
+        <v>-3.156114157040391</v>
       </c>
       <c r="E333" t="n">
-        <v>0.0443621711152804</v>
+        <v>4.43621711152804</v>
       </c>
       <c r="F333" t="n">
-        <v>0.007179325744210985</v>
+        <v>0.7179325744210985</v>
       </c>
       <c r="G333" t="n">
         <v>-0.38971</v>
@@ -14780,19 +14780,19 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>0.02929350137982034</v>
+        <v>2.929350137982034</v>
       </c>
       <c r="C334" t="n">
-        <v>0.04881230093075928</v>
+        <v>4.881230093075906</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.01617719829323117</v>
+        <v>-1.617719829323117</v>
       </c>
       <c r="E334" t="n">
-        <v>0.05108331509827013</v>
+        <v>5.108331509827013</v>
       </c>
       <c r="F334" t="n">
-        <v>0.0259634611094044</v>
+        <v>2.59634611094044</v>
       </c>
       <c r="G334" t="n">
         <v>-0.78431</v>
@@ -14823,19 +14823,19 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>0.03734027008490792</v>
+        <v>3.734027008490792</v>
       </c>
       <c r="C335" t="n">
-        <v>0.01694221529529982</v>
+        <v>1.694221529529982</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.02581536718973865</v>
+        <v>-2.581536718973865</v>
       </c>
       <c r="E335" t="n">
-        <v>0.03832541237547482</v>
+        <v>3.832541237547482</v>
       </c>
       <c r="F335" t="n">
-        <v>0.002888895836095751</v>
+        <v>0.2888895836095751</v>
       </c>
       <c r="G335" t="n">
         <v>-0.46948</v>
@@ -14866,19 +14866,19 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>0.03722559718300422</v>
+        <v>3.722559718300422</v>
       </c>
       <c r="C336" t="n">
-        <v>0.03655399016192296</v>
+        <v>3.655399016192296</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.03337600238135141</v>
+        <v>-3.337600238135141</v>
       </c>
       <c r="E336" t="n">
-        <v>0.03491855303193958</v>
+        <v>3.491855303193958</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.001589170253252226</v>
+        <v>-0.1589170253252226</v>
       </c>
       <c r="G336" t="n">
         <v>-1.56372</v>
@@ -14909,19 +14909,19 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>0.02009657186433711</v>
+        <v>2.009657186433711</v>
       </c>
       <c r="C337" t="n">
-        <v>0.01177394468593107</v>
+        <v>1.177394468593107</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.031415298688663</v>
+        <v>-3.1415298688663</v>
       </c>
       <c r="E337" t="n">
-        <v>0.03634007251881077</v>
+        <v>3.634007251881077</v>
       </c>
       <c r="F337" t="n">
-        <v>0.002555358508475214</v>
+        <v>0.2555358508475214</v>
       </c>
       <c r="G337" t="n">
         <v>0.07758</v>
@@ -14952,19 +14952,19 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>0.0329378619107501</v>
+        <v>3.29378619107501</v>
       </c>
       <c r="C338" t="n">
-        <v>0.02205230130594305</v>
+        <v>2.205230130594282</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.0236268761464844</v>
+        <v>-2.36268761464844</v>
       </c>
       <c r="E338" t="n">
-        <v>0.01875020616854828</v>
+        <v>1.875020616854828</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.01524383408925667</v>
+        <v>-1.524383408925667</v>
       </c>
       <c r="G338" t="n">
         <v>-0.86342</v>
@@ -14995,19 +14995,19 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.006754604595028413</v>
+        <v>0.6754604595028413</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.01812370272725283</v>
+        <v>-1.812370272725283</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.02147175121416189</v>
+        <v>-2.147175121416189</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.00606131691839551</v>
+        <v>-0.606131691839551</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.03903675752103297</v>
+        <v>-3.903675752103297</v>
       </c>
       <c r="G339" t="n">
         <v>-1.32916</v>
@@ -15038,19 +15038,19 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>0.03608718603085159</v>
+        <v>3.608718603085159</v>
       </c>
       <c r="C340" t="n">
-        <v>0.006104598874596467</v>
+        <v>0.6104598874596467</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.02717902758988677</v>
+        <v>-2.717902758988677</v>
       </c>
       <c r="E340" t="n">
-        <v>-0.01148625169248207</v>
+        <v>-1.148625169248207</v>
       </c>
       <c r="F340" t="n">
-        <v>-0.03769366909050764</v>
+        <v>-3.769366909050764</v>
       </c>
       <c r="G340" t="n">
         <v>-1.2432</v>
@@ -15081,19 +15081,19 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>0.04786722032880442</v>
+        <v>4.786722032880442</v>
       </c>
       <c r="C341" t="n">
-        <v>0.01377554566792694</v>
+        <v>1.377554566792671</v>
       </c>
       <c r="D341" t="n">
-        <v>-0.0304898844296887</v>
+        <v>-3.04898844296887</v>
       </c>
       <c r="E341" t="n">
-        <v>0.01702453840724538</v>
+        <v>1.702453840724538</v>
       </c>
       <c r="F341" t="n">
-        <v>-0.006405689934359637</v>
+        <v>-0.6405689934359637</v>
       </c>
       <c r="G341" t="n">
         <v>-0.31571</v>
@@ -15124,19 +15124,19 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>0.05707966553002475</v>
+        <v>5.707966553002475</v>
       </c>
       <c r="C342" t="n">
-        <v>0.02861031361499267</v>
+        <v>2.861031361499267</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.007315978393046985</v>
+        <v>-0.7315978393046985</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.001299319936844179</v>
+        <v>-0.1299319936844179</v>
       </c>
       <c r="F342" t="n">
-        <v>-0.00401706957670056</v>
+        <v>-0.401706957670056</v>
       </c>
       <c r="G342" t="n">
         <v>-0.47207</v>
@@ -15167,19 +15167,19 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>0.05796758007875713</v>
+        <v>5.796758007875713</v>
       </c>
       <c r="C343" t="n">
-        <v>0.01542678259431263</v>
+        <v>1.542678259431263</v>
       </c>
       <c r="D343" t="n">
-        <v>0.02358318998354969</v>
+        <v>2.358318998354969</v>
       </c>
       <c r="E343" t="n">
-        <v>0.006823074251838479</v>
+        <v>0.6823074251838479</v>
       </c>
       <c r="F343" t="n">
-        <v>0.03872779605436594</v>
+        <v>3.872779605436594</v>
       </c>
       <c r="G343" t="n">
         <v>-0.31348</v>
@@ -15210,19 +15210,19 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>0.05832493748071754</v>
+        <v>5.832493748071754</v>
       </c>
       <c r="C344" t="n">
-        <v>0.03787456707214698</v>
+        <v>3.787456707214698</v>
       </c>
       <c r="D344" t="n">
-        <v>0.008976182008715528</v>
+        <v>0.8976182008715528</v>
       </c>
       <c r="E344" t="n">
-        <v>0.02711150530586881</v>
+        <v>2.711150530586881</v>
       </c>
       <c r="F344" t="n">
-        <v>0.04801890871215964</v>
+        <v>4.801890871215964</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -15253,19 +15253,19 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>0.1028063804631847</v>
+        <v>10.28063804631847</v>
       </c>
       <c r="C345" t="n">
-        <v>0.07473286693445202</v>
+        <v>7.473286693445225</v>
       </c>
       <c r="D345" t="n">
-        <v>0.07746571937349511</v>
+        <v>7.746571937349511</v>
       </c>
       <c r="E345" t="n">
-        <v>0.02755788766256728</v>
+        <v>2.755788766256728</v>
       </c>
       <c r="F345" t="n">
-        <v>0.108000098203086</v>
+        <v>10.8000098203086</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
@@ -15296,19 +15296,19 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>0.02174380955818633</v>
+        <v>2.174380955818633</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.00433983944950378</v>
+        <v>-0.4339839449503669</v>
       </c>
       <c r="D346" t="n">
-        <v>0.01640061130985315</v>
+        <v>1.640061130985315</v>
       </c>
       <c r="E346" t="n">
-        <v>0.02254129972160346</v>
+        <v>2.254129972160346</v>
       </c>
       <c r="F346" t="n">
-        <v>0.03919007356003235</v>
+        <v>3.919007356003235</v>
       </c>
       <c r="G346" t="n">
         <v>0.31621</v>
@@ -15339,19 +15339,19 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>0.05187470834096608</v>
+        <v>5.187470834096608</v>
       </c>
       <c r="C347" t="n">
-        <v>0.02981661709703376</v>
+        <v>2.981661709703376</v>
       </c>
       <c r="D347" t="n">
-        <v>0.04059041109093364</v>
+        <v>4.059041109093364</v>
       </c>
       <c r="E347" t="n">
-        <v>0.02130332236596555</v>
+        <v>2.130332236596555</v>
       </c>
       <c r="F347" t="n">
-        <v>0.0528584931917373</v>
+        <v>5.28584931917373</v>
       </c>
       <c r="G347" t="n">
         <v>-0.70755</v>
@@ -15382,19 +15382,19 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>0.03565456337568573</v>
+        <v>3.565456337568573</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.009885449197875817</v>
+        <v>-0.9885449197875706</v>
       </c>
       <c r="D348" t="n">
-        <v>0.04254119250717769</v>
+        <v>4.254119250717769</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0313162829779523</v>
+        <v>3.13162829779523</v>
       </c>
       <c r="F348" t="n">
-        <v>0.07716941507266006</v>
+        <v>7.716941507266006</v>
       </c>
       <c r="G348" t="n">
         <v>0.87371</v>
@@ -15425,19 +15425,19 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>0.06733495705622539</v>
+        <v>6.733495705622539</v>
       </c>
       <c r="C349" t="n">
-        <v>0.05748503177485431</v>
+        <v>5.748503177485431</v>
       </c>
       <c r="D349" t="n">
-        <v>0.06314668992932382</v>
+        <v>6.314668992932382</v>
       </c>
       <c r="E349" t="n">
-        <v>0.06031644179971885</v>
+        <v>6.031644179971885</v>
       </c>
       <c r="F349" t="n">
-        <v>0.1207670357925119</v>
+        <v>12.07670357925119</v>
       </c>
       <c r="G349" t="n">
         <v>-0.62016</v>
@@ -15468,19 +15468,19 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>0.0537102070343296</v>
+        <v>5.37102070343296</v>
       </c>
       <c r="C350" t="n">
-        <v>0.03221290638624019</v>
+        <v>3.221290638624019</v>
       </c>
       <c r="D350" t="n">
-        <v>0.06187877584876689</v>
+        <v>6.187877584876689</v>
       </c>
       <c r="E350" t="n">
-        <v>0.06709807963687853</v>
+        <v>6.709807963687853</v>
       </c>
       <c r="F350" t="n">
-        <v>0.1124422410330805</v>
+        <v>11.24422410330805</v>
       </c>
       <c r="G350" t="n">
         <v>0.7125899999999999</v>
@@ -15511,19 +15511,19 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>0.06036670691439472</v>
+        <v>6.036670691439472</v>
       </c>
       <c r="C351" t="n">
-        <v>0.05009954463559962</v>
+        <v>5.009954463559962</v>
       </c>
       <c r="D351" t="n">
-        <v>0.01678606627330637</v>
+        <v>1.678606627330637</v>
       </c>
       <c r="E351" t="n">
-        <v>0.08079720541986202</v>
+        <v>8.079720541986202</v>
       </c>
       <c r="F351" t="n">
-        <v>0.08589389707578277</v>
+        <v>8.589389707578277</v>
       </c>
       <c r="G351" t="n">
         <v>0.79239</v>
@@ -15554,19 +15554,19 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-0.5325129567640501</v>
+        <v>-53.25129567640501</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.4915659183123405</v>
+        <v>-49.15659183123405</v>
       </c>
       <c r="D352" t="n">
-        <v>-0.4432484992891549</v>
+        <v>-44.32484992891549</v>
       </c>
       <c r="E352" t="n">
-        <v>-0.01874850721942178</v>
+        <v>-1.874850721942178</v>
       </c>
       <c r="F352" t="n">
-        <v>-0.4503550973431809</v>
+        <v>-45.03550973431809</v>
       </c>
       <c r="G352" t="n">
         <v>-1.49489</v>
@@ -15597,19 +15597,19 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.9940227326538874</v>
+        <v>-99.40227326538874</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.9811541009962225</v>
+        <v>-98.11541009962225</v>
       </c>
       <c r="D353" t="n">
-        <v>-0.8869152333499032</v>
+        <v>-88.69152333499032</v>
       </c>
       <c r="E353" t="n">
-        <v>-0.5250597924443221</v>
+        <v>-52.50597924443221</v>
       </c>
       <c r="F353" t="n">
-        <v>-0.9456918472470968</v>
+        <v>-94.56918472470967</v>
       </c>
       <c r="G353" t="n">
         <v>-52.73159</v>
@@ -15640,19 +15640,19 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-0.9880358947158148</v>
+        <v>-98.80358947158147</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.9597695620011115</v>
+        <v>-95.97695620011115</v>
       </c>
       <c r="D354" t="n">
-        <v>-0.8216074906229978</v>
+        <v>-82.16074906229977</v>
       </c>
       <c r="E354" t="n">
-        <v>-0.5070000119927046</v>
+        <v>-50.70000119927046</v>
       </c>
       <c r="F354" t="n">
-        <v>-0.9114556568617805</v>
+        <v>-91.14556568617806</v>
       </c>
       <c r="G354" t="n">
         <v>-57.3913</v>
@@ -15683,19 +15683,19 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.9813346953108211</v>
+        <v>-98.13346953108211</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.9435071657721545</v>
+        <v>-94.35071657721545</v>
       </c>
       <c r="D355" t="n">
-        <v>-0.8141615023146667</v>
+        <v>-81.41615023146667</v>
       </c>
       <c r="E355" t="n">
-        <v>-0.4298306243935457</v>
+        <v>-42.98306243935457</v>
       </c>
       <c r="F355" t="n">
-        <v>-0.8928591385793068</v>
+        <v>-89.28591385793068</v>
       </c>
       <c r="G355" t="n">
         <v>-51.88679</v>
@@ -15726,19 +15726,19 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-0.9774518389800343</v>
+        <v>-97.74518389800343</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.9363734028934001</v>
+        <v>-93.63734028934002</v>
       </c>
       <c r="D356" t="n">
-        <v>-0.756449246190539</v>
+        <v>-75.6449246190539</v>
       </c>
       <c r="E356" t="n">
-        <v>-0.4311483321218209</v>
+        <v>-43.11483321218209</v>
       </c>
       <c r="F356" t="n">
-        <v>-0.8597972877447285</v>
+        <v>-85.97972877447285</v>
       </c>
       <c r="G356" t="n">
         <v>-52.62745</v>
@@ -15769,19 +15769,19 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-0.9746065489675475</v>
+        <v>-97.46065489675475</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.9099913804652259</v>
+        <v>-90.99913804652259</v>
       </c>
       <c r="D357" t="n">
-        <v>-0.7418974448420637</v>
+        <v>-74.18974448420637</v>
       </c>
       <c r="E357" t="n">
-        <v>-0.4565805623966019</v>
+        <v>-45.6580562396602</v>
       </c>
       <c r="F357" t="n">
-        <v>-0.8595954311968739</v>
+        <v>-85.95954311968738</v>
       </c>
       <c r="G357" t="n">
         <v>-53.12989</v>
@@ -15812,19 +15812,19 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.9743005116124162</v>
+        <v>-97.43005116124162</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.8990927728658881</v>
+        <v>-89.9092772865888</v>
       </c>
       <c r="D358" t="n">
-        <v>-0.7497533428419089</v>
+        <v>-74.97533428419089</v>
       </c>
       <c r="E358" t="n">
-        <v>-0.4017036693883285</v>
+        <v>-40.17036693883285</v>
       </c>
       <c r="F358" t="n">
-        <v>-0.8491312125121274</v>
+        <v>-84.91312125121274</v>
       </c>
       <c r="G358" t="n">
         <v>-58.94405</v>
@@ -15855,19 +15855,19 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-0.9007588640345942</v>
+        <v>-90.07588640345942</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.8142262153916584</v>
+        <v>-81.42262153916585</v>
       </c>
       <c r="D359" t="n">
-        <v>-0.7496984249241102</v>
+        <v>-74.96984249241102</v>
       </c>
       <c r="E359" t="n">
-        <v>-0.3134872106296958</v>
+        <v>-31.34872106296957</v>
       </c>
       <c r="F359" t="n">
-        <v>-0.8289234095396629</v>
+        <v>-82.8923409539663</v>
       </c>
       <c r="G359" t="n">
         <v>-51.38559</v>
@@ -15898,19 +15898,19 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-0.7676648845887606</v>
+        <v>-76.76648845887605</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.6575406980184264</v>
+        <v>-65.75406980184265</v>
       </c>
       <c r="D360" t="n">
-        <v>-0.7185394972249413</v>
+        <v>-71.85394972249412</v>
       </c>
       <c r="E360" t="n">
-        <v>-0.1257641523086165</v>
+        <v>-12.57641523086165</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.752197424002589</v>
+        <v>-75.21974240025891</v>
       </c>
       <c r="G360" t="n">
         <v>-44.88189</v>
@@ -15941,19 +15941,19 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.7481522300126002</v>
+        <v>-74.81522300126002</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.6651132392090299</v>
+        <v>-66.511323920903</v>
       </c>
       <c r="D361" t="n">
-        <v>-0.7013204008362499</v>
+        <v>-70.13204008362499</v>
       </c>
       <c r="E361" t="n">
-        <v>-0.1680542082990163</v>
+        <v>-16.80542082990163</v>
       </c>
       <c r="F361" t="n">
-        <v>-0.7548766169201052</v>
+        <v>-75.48766169201052</v>
       </c>
       <c r="G361" t="n">
         <v>-41.26365</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -531,7 +531,7 @@
         <v>6.87323</v>
       </c>
       <c r="K2" t="n">
-        <v>2.30506</v>
+        <v>2.30536</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         <v>4.15367</v>
       </c>
       <c r="K3" t="n">
-        <v>2.43806</v>
+        <v>2.42488</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>7.55398</v>
       </c>
       <c r="K4" t="n">
-        <v>2.13186</v>
+        <v>2.13214</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         <v>0.74259</v>
       </c>
       <c r="K5" t="n">
-        <v>2.02259</v>
+        <v>2.02286</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>1.77784</v>
       </c>
       <c r="K6" t="n">
-        <v>1.97981</v>
+        <v>1.98007</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>2.02157</v>
       </c>
       <c r="K7" t="n">
-        <v>1.71466</v>
+        <v>1.71488</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>4.61385</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47327</v>
+        <v>1.47346</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>7.05482</v>
       </c>
       <c r="K9" t="n">
-        <v>1.21046</v>
+        <v>1.21062</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>8.03481</v>
       </c>
       <c r="K10" t="n">
-        <v>0.70021</v>
+        <v>0.7003</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>5.90081</v>
       </c>
       <c r="K11" t="n">
-        <v>0.34933</v>
+        <v>0.34938</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>3.56805</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.19352</v>
+        <v>-0.19355</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>2.00281</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7725</v>
+        <v>-0.7726</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>3.20213</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.00347</v>
+        <v>-1.0036</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>4.71972</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.21118</v>
+        <v>-1.21134</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>5.26354</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.68641</v>
+        <v>-1.68662</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>4.22933</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.97994</v>
+        <v>-1.9802</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>3.76165</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.26483</v>
+        <v>-2.26512</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>0.94789</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.53116</v>
+        <v>-2.53148</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>-1.13358</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.58488</v>
+        <v>-2.58521</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>-2.8686</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.39506</v>
+        <v>-2.39536</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>-2.60379</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.39814</v>
+        <v>-2.39845</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>-2.90647</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.19468</v>
+        <v>-2.18205</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>-3.72218</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.93899</v>
+        <v>-1.93924</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>-6.68686</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.50513</v>
+        <v>-1.50532</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>-7.29507</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.97466</v>
+        <v>-0.97479</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-7.18887</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.46954</v>
+        <v>-0.46961</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>-8.49579</v>
       </c>
       <c r="K29" t="n">
-        <v>0.31426</v>
+        <v>0.3143</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>-7.96439</v>
       </c>
       <c r="K30" t="n">
-        <v>0.61647</v>
+        <v>0.62967</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>-7.24745</v>
       </c>
       <c r="K31" t="n">
-        <v>1.11916</v>
+        <v>1.1193</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>-7.5816</v>
       </c>
       <c r="K32" t="n">
-        <v>1.3314</v>
+        <v>1.33158</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>-8.440099999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>1.54455</v>
+        <v>1.55796</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>-7.62422</v>
       </c>
       <c r="K34" t="n">
-        <v>1.56992</v>
+        <v>1.57013</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>-5.89477</v>
       </c>
       <c r="K35" t="n">
-        <v>1.61162</v>
+        <v>1.61184</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>-7.24322</v>
       </c>
       <c r="K36" t="n">
-        <v>1.34636</v>
+        <v>1.33316</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>-7.38131</v>
       </c>
       <c r="K37" t="n">
-        <v>1.02821</v>
+        <v>1.04153</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>-3.30781</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5928099999999999</v>
+        <v>0.59289</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>-2.16373</v>
       </c>
       <c r="K39" t="n">
-        <v>0.03937</v>
+        <v>0.03938</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>-1.56239</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.23588</v>
+        <v>-0.23591</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>-0.60228</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.75708</v>
+        <v>-0.75718</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>-1.01636</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.082</v>
+        <v>-1.09503</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>-1.00361</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.06771</v>
+        <v>-1.06785</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>1.32015</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.27488</v>
+        <v>-1.27505</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>0.68588</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.24805</v>
+        <v>-1.26105</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>1.35223</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.22094</v>
+        <v>-1.2211</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>1.09793</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.00104</v>
+        <v>-0.98817</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>2.6756</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.4298</v>
+        <v>-0.42986</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>2.51899</v>
       </c>
       <c r="K49" t="n">
-        <v>0.11743</v>
+        <v>0.10438</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>1.41031</v>
       </c>
       <c r="K50" t="n">
-        <v>0.60241</v>
+        <v>0.61559</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>0.18329</v>
       </c>
       <c r="K51" t="n">
-        <v>0.87892</v>
+        <v>0.89215</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>-0.83586</v>
       </c>
       <c r="K52" t="n">
-        <v>0.88007</v>
+        <v>0.88019</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>-0.6408700000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>0.84177</v>
+        <v>0.84188</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>-0.46422</v>
       </c>
       <c r="K54" t="n">
-        <v>0.88297</v>
+        <v>0.88309</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>-1.2576</v>
       </c>
       <c r="K55" t="n">
-        <v>0.61858</v>
+        <v>0.6186700000000001</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>-2.05585</v>
       </c>
       <c r="K56" t="n">
-        <v>0.57979</v>
+        <v>0.57986</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>-0.07042</v>
       </c>
       <c r="K57" t="n">
-        <v>0.30279</v>
+        <v>0.30283</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>-0.9904500000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>0.24984</v>
+        <v>0.26302</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>-1.08805</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.30085</v>
+        <v>-0.28781</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>-1.03275</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.5734399999999999</v>
+        <v>-0.56048</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>1.93804</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.52083</v>
+        <v>-0.5209</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>0.72118</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.28694</v>
+        <v>-0.28698</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>1.0878</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.01306</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>2.17111</v>
       </c>
       <c r="K67" t="n">
-        <v>0.23545</v>
+        <v>0.23548</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>2.45751</v>
       </c>
       <c r="K68" t="n">
-        <v>0.79916</v>
+        <v>0.79927</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>2.30566</v>
       </c>
       <c r="K69" t="n">
-        <v>1.11563</v>
+        <v>1.11578</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>3.13813</v>
       </c>
       <c r="K71" t="n">
-        <v>1.15577</v>
+        <v>1.14263</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>2.07499</v>
       </c>
       <c r="K72" t="n">
-        <v>0.91839</v>
+        <v>0.90527</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>3.72548</v>
       </c>
       <c r="K73" t="n">
-        <v>0.95688</v>
+        <v>0.94377</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>1.52746</v>
       </c>
       <c r="K75" t="n">
-        <v>0.93042</v>
+        <v>0.91731</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>1.24683</v>
       </c>
       <c r="K76" t="n">
-        <v>0.92932</v>
+        <v>0.94253</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>1.24298</v>
       </c>
       <c r="K77" t="n">
-        <v>0.96795</v>
+        <v>0.98116</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>-0.03912</v>
       </c>
       <c r="K78" t="n">
-        <v>1.21505</v>
+        <v>1.20199</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>-1.36338</v>
       </c>
       <c r="K79" t="n">
-        <v>1.22667</v>
+        <v>1.22683</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>-1.24423</v>
       </c>
       <c r="K80" t="n">
-        <v>0.93579</v>
+        <v>0.93592</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>-1.38608</v>
       </c>
       <c r="K81" t="n">
-        <v>1.19418</v>
+        <v>1.20732</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>-1.15059</v>
       </c>
       <c r="K83" t="n">
-        <v>1.71384</v>
+        <v>1.72705</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>-1.29216</v>
       </c>
       <c r="K84" t="n">
-        <v>2.22309</v>
+        <v>2.22338</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>-2.01288</v>
       </c>
       <c r="K85" t="n">
-        <v>2.2202</v>
+        <v>2.23348</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>-1.27068</v>
       </c>
       <c r="K87" t="n">
-        <v>2.46689</v>
+        <v>2.46721</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>-0.57021</v>
       </c>
       <c r="K89" t="n">
-        <v>2.50032</v>
+        <v>2.48737</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>0.17421</v>
       </c>
       <c r="K90" t="n">
-        <v>2.01368</v>
+        <v>2.02685</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>0.38878</v>
       </c>
       <c r="K91" t="n">
-        <v>1.97241</v>
+        <v>1.97267</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>-0.22581</v>
       </c>
       <c r="K92" t="n">
-        <v>1.75122</v>
+        <v>1.75145</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>-0.9389999999999999</v>
       </c>
       <c r="K93" t="n">
-        <v>1.48794</v>
+        <v>1.47512</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>-1.3879</v>
       </c>
       <c r="K94" t="n">
-        <v>1.26566</v>
+        <v>1.25288</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>-1.27398</v>
       </c>
       <c r="K96" t="n">
-        <v>1.20819</v>
+        <v>1.22106</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>-2.02135</v>
       </c>
       <c r="K99" t="n">
-        <v>1.96401</v>
+        <v>1.97694</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>-1.59591</v>
       </c>
       <c r="K101" t="n">
-        <v>2.3003</v>
+        <v>2.30059</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>-0.70105</v>
       </c>
       <c r="K103" t="n">
-        <v>3.12263</v>
+        <v>3.13567</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>-1.63677</v>
       </c>
       <c r="K104" t="n">
-        <v>3.4042</v>
+        <v>3.41729</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>-1.31027</v>
       </c>
       <c r="K105" t="n">
-        <v>3.72851</v>
+        <v>3.72898</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>-1.71536</v>
       </c>
       <c r="K106" t="n">
-        <v>4.01464</v>
+        <v>4.01515</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>1.6503</v>
       </c>
       <c r="K108" t="n">
-        <v>4.39809</v>
+        <v>4.38552</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>1.75485</v>
       </c>
       <c r="K112" t="n">
-        <v>4.54264</v>
+        <v>4.53026</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>2.68801</v>
       </c>
       <c r="K113" t="n">
-        <v>4.54658</v>
+        <v>4.5595</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>2.87432</v>
       </c>
       <c r="K114" t="n">
-        <v>4.57903</v>
+        <v>4.56672</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>3.93853</v>
       </c>
       <c r="K116" t="n">
-        <v>4.5894</v>
+        <v>4.57716</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>3.90911</v>
       </c>
       <c r="K117" t="n">
-        <v>4.53272</v>
+        <v>4.53327</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>5.25938</v>
       </c>
       <c r="K118" t="n">
-        <v>4.33305</v>
+        <v>4.34571</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>3.59819</v>
       </c>
       <c r="K119" t="n">
-        <v>4.29055</v>
+        <v>4.27846</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>1.88625</v>
       </c>
       <c r="K120" t="n">
-        <v>4.02022</v>
+        <v>4.03274</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>1.4736</v>
       </c>
       <c r="K121" t="n">
-        <v>3.51591</v>
+        <v>3.50395</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>3.3177</v>
       </c>
       <c r="K122" t="n">
-        <v>2.90615</v>
+        <v>2.89424</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>2.21633</v>
       </c>
       <c r="K124" t="n">
-        <v>2.36798</v>
+        <v>2.38011</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>0.27475</v>
       </c>
       <c r="K126" t="n">
-        <v>1.95386</v>
+        <v>1.95409</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>-0.16223</v>
       </c>
       <c r="K128" t="n">
-        <v>1.63819</v>
+        <v>1.65009</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>0.60939</v>
       </c>
       <c r="K129" t="n">
-        <v>1.13067</v>
+        <v>1.14246</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>-6.44729</v>
       </c>
       <c r="K131" t="n">
-        <v>0.35925</v>
+        <v>0.37089</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>-7.8633</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.06932000000000001</v>
+        <v>-0.05777</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>-7.87933</v>
       </c>
       <c r="K134" t="n">
-        <v>0.53241</v>
+        <v>0.53247</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>-7.1485</v>
       </c>
       <c r="K136" t="n">
-        <v>1.04094</v>
+        <v>1.02938</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>-6.62404</v>
       </c>
       <c r="K138" t="n">
-        <v>1.68552</v>
+        <v>1.69726</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>-5.4778</v>
       </c>
       <c r="K142" t="n">
-        <v>2.83901</v>
+        <v>2.82747</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>-0.53771</v>
       </c>
       <c r="K143" t="n">
-        <v>3.30254</v>
+        <v>3.29099</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>3.67652</v>
       </c>
       <c r="K146" t="n">
-        <v>3.75317</v>
+        <v>3.76511</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>2.77778</v>
       </c>
       <c r="K148" t="n">
-        <v>3.17079</v>
+        <v>3.1826</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>2.01723</v>
       </c>
       <c r="K149" t="n">
-        <v>2.658</v>
+        <v>2.64659</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>1.1216</v>
       </c>
       <c r="K154" t="n">
-        <v>1.4252</v>
+        <v>1.42536</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>2.58983</v>
       </c>
       <c r="K155" t="n">
-        <v>1.45316</v>
+        <v>1.46451</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>2.43277</v>
       </c>
       <c r="K157" t="n">
-        <v>1.4562</v>
+        <v>1.44509</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>2.46817</v>
       </c>
       <c r="K161" t="n">
-        <v>3.11146</v>
+        <v>3.12292</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>3.68896</v>
       </c>
       <c r="K164" t="n">
-        <v>4.25839</v>
+        <v>4.24728</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>2.53596</v>
       </c>
       <c r="K166" t="n">
-        <v>4.06063</v>
+        <v>4.07215</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>3.64588</v>
       </c>
       <c r="K167" t="n">
-        <v>3.83429</v>
+        <v>3.82327</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>2.889</v>
       </c>
       <c r="K169" t="n">
-        <v>3.83478</v>
+        <v>3.8352</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>2.84697</v>
       </c>
       <c r="K173" t="n">
-        <v>3.55642</v>
+        <v>3.54564</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>2.54939</v>
       </c>
       <c r="K176" t="n">
-        <v>2.99669</v>
+        <v>3.00768</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>2.50148</v>
       </c>
       <c r="K179" t="n">
-        <v>2.92869</v>
+        <v>2.93962</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>1.81115</v>
       </c>
       <c r="K181" t="n">
-        <v>2.91231</v>
+        <v>2.92317</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>1.47007</v>
       </c>
       <c r="K185" t="n">
-        <v>1.87324</v>
+        <v>1.88385</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>-3.18673</v>
       </c>
       <c r="K211" t="n">
-        <v>-1.73826</v>
+        <v>-1.72827</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>-8.699949999999999</v>
       </c>
       <c r="K223" t="n">
-        <v>-6.07971</v>
+        <v>-6.08925</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>-4.18348</v>
       </c>
       <c r="K228" t="n">
-        <v>-3.35289</v>
+        <v>-3.34241</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>-4.2065</v>
       </c>
       <c r="K229" t="n">
-        <v>-2.5132</v>
+        <v>-2.50264</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>-1.35654</v>
       </c>
       <c r="K235" t="n">
-        <v>1.19073</v>
+        <v>1.20156</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>-0.25725</v>
       </c>
       <c r="K237" t="n">
-        <v>1.59315</v>
+        <v>1.60399</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>1.67509</v>
       </c>
       <c r="K240" t="n">
-        <v>1.84302</v>
+        <v>1.84282</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>2.18762</v>
       </c>
       <c r="K241" t="n">
-        <v>1.83059</v>
+        <v>1.83039</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>2.64173</v>
       </c>
       <c r="K243" t="n">
-        <v>2.11755</v>
+        <v>2.12835</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>3.46116</v>
       </c>
       <c r="K247" t="n">
-        <v>1.06975</v>
+        <v>1.05894</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>4.28998</v>
       </c>
       <c r="K249" t="n">
-        <v>0.82142</v>
+        <v>0.81067</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>5.36587</v>
       </c>
       <c r="K250" t="n">
-        <v>1.08939</v>
+        <v>1.10007</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>4.6915</v>
       </c>
       <c r="K251" t="n">
-        <v>1.32238</v>
+        <v>1.33305</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>4.78751</v>
       </c>
       <c r="K252" t="n">
-        <v>1.54354</v>
+        <v>1.53273</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>4.94873</v>
       </c>
       <c r="K253" t="n">
-        <v>2.12743</v>
+        <v>2.11657</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>5.60819</v>
       </c>
       <c r="K254" t="n">
-        <v>2.03498</v>
+        <v>2.04557</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>5.94848</v>
       </c>
       <c r="K255" t="n">
-        <v>2.40161</v>
+        <v>2.39078</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>5.46892</v>
       </c>
       <c r="K261" t="n">
-        <v>5.34335</v>
+        <v>5.35393</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>4.06068</v>
       </c>
       <c r="K262" t="n">
-        <v>5.82145</v>
+        <v>5.81027</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>3.98664</v>
       </c>
       <c r="K263" t="n">
-        <v>5.86254</v>
+        <v>5.86192</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>3.80942</v>
       </c>
       <c r="K264" t="n">
-        <v>5.93354</v>
+        <v>5.94402</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>2.87385</v>
       </c>
       <c r="K266" t="n">
-        <v>5.64039</v>
+        <v>5.62941</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>2.18501</v>
       </c>
       <c r="K268" t="n">
-        <v>5.869</v>
+        <v>5.87932</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>2.61295</v>
       </c>
       <c r="K269" t="n">
-        <v>5.81288</v>
+        <v>5.82315</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>2.24409</v>
       </c>
       <c r="K270" t="n">
-        <v>5.57374</v>
+        <v>5.58396</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>2.87077</v>
       </c>
       <c r="K273" t="n">
-        <v>4.37927</v>
+        <v>4.36879</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>2.59061</v>
       </c>
       <c r="K275" t="n">
-        <v>3.37045</v>
+        <v>3.36017</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>2.64213</v>
       </c>
       <c r="K276" t="n">
-        <v>2.99852</v>
+        <v>2.99822</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>3.57057</v>
       </c>
       <c r="K278" t="n">
-        <v>2.88102</v>
+        <v>2.89086</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>3.10631</v>
       </c>
       <c r="K279" t="n">
-        <v>2.72914</v>
+        <v>2.73892</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>3.13352</v>
       </c>
       <c r="K280" t="n">
-        <v>2.72798</v>
+        <v>2.71797</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>2.52939</v>
       </c>
       <c r="K281" t="n">
-        <v>2.48471</v>
+        <v>2.47477</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>2.46755</v>
       </c>
       <c r="K282" t="n">
-        <v>2.7027</v>
+        <v>2.69275</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>1.70802</v>
       </c>
       <c r="K283" t="n">
-        <v>2.45103</v>
+        <v>2.46068</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>0.5518</v>
       </c>
       <c r="K285" t="n">
-        <v>2.99269</v>
+        <v>3.00231</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>0.5296999999999999</v>
       </c>
       <c r="K288" t="n">
-        <v>3.8432</v>
+        <v>3.84283</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>-0.04054</v>
       </c>
       <c r="K290" t="n">
-        <v>3.83255</v>
+        <v>3.82263</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>-0.23617</v>
       </c>
       <c r="K291" t="n">
-        <v>3.85641</v>
+        <v>3.84652</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>-0.7377899999999999</v>
       </c>
       <c r="K292" t="n">
-        <v>3.61343</v>
+        <v>3.62291</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>-0.52172</v>
       </c>
       <c r="K293" t="n">
-        <v>3.87347</v>
+        <v>3.88294</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>-0.8229</v>
       </c>
       <c r="K294" t="n">
-        <v>3.87663</v>
+        <v>3.88606</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>-0.05906</v>
       </c>
       <c r="K295" t="n">
-        <v>4.15372</v>
+        <v>4.14391</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>0.27712</v>
       </c>
       <c r="K296" t="n">
-        <v>4.17527</v>
+        <v>4.18465</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>0.31426</v>
       </c>
       <c r="K297" t="n">
-        <v>3.95216</v>
+        <v>3.95179</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>1.00172</v>
       </c>
       <c r="K300" t="n">
-        <v>3.58993</v>
+        <v>3.58035</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>1.95501</v>
       </c>
       <c r="K301" t="n">
-        <v>3.94749</v>
+        <v>3.95673</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>1.47719</v>
       </c>
       <c r="K302" t="n">
-        <v>3.58063</v>
+        <v>3.58984</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>2.73019</v>
       </c>
       <c r="K304" t="n">
-        <v>3.55149</v>
+        <v>3.55116</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>2.50477</v>
       </c>
       <c r="K305" t="n">
-        <v>3.30051</v>
+        <v>3.30021</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>2.97813</v>
       </c>
       <c r="K306" t="n">
-        <v>3.0237</v>
+        <v>3.02342</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>3.47011</v>
       </c>
       <c r="K307" t="n">
-        <v>2.72201</v>
+        <v>2.73105</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>3.01415</v>
       </c>
       <c r="K308" t="n">
-        <v>2.738</v>
+        <v>2.73775</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>3.06809</v>
       </c>
       <c r="K309" t="n">
-        <v>2.73234</v>
+        <v>2.73209</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>2.6111</v>
       </c>
       <c r="K310" t="n">
-        <v>2.76832</v>
+        <v>2.77728</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>2.99353</v>
       </c>
       <c r="K311" t="n">
-        <v>2.69134</v>
+        <v>2.70029</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>2.39374</v>
       </c>
       <c r="K313" t="n">
-        <v>2.926</v>
+        <v>2.92574</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>1.92627</v>
       </c>
       <c r="K314" t="n">
-        <v>3.01253</v>
+        <v>3.01226</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>2.62675</v>
       </c>
       <c r="K316" t="n">
-        <v>3.03191</v>
+        <v>3.03164</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>3.43649</v>
       </c>
       <c r="K317" t="n">
-        <v>3.27449</v>
+        <v>3.2742</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>3.3741</v>
       </c>
       <c r="K318" t="n">
-        <v>3.52547</v>
+        <v>3.52516</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>3.14975</v>
       </c>
       <c r="K319" t="n">
-        <v>3.82076</v>
+        <v>3.82042</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>3.12855</v>
       </c>
       <c r="K320" t="n">
-        <v>3.52415</v>
+        <v>3.52384</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>3.1808</v>
       </c>
       <c r="K321" t="n">
-        <v>3.64829</v>
+        <v>3.63923</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>3.7925</v>
       </c>
       <c r="K322" t="n">
-        <v>3.73987</v>
+        <v>3.73954</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>3.92538</v>
       </c>
       <c r="K323" t="n">
-        <v>3.76143</v>
+        <v>3.7611</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>3.68468</v>
       </c>
       <c r="K324" t="n">
-        <v>3.45157</v>
+        <v>3.46024</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>3.30291</v>
       </c>
       <c r="K325" t="n">
-        <v>3.22302</v>
+        <v>3.22274</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>2.86511</v>
       </c>
       <c r="K326" t="n">
-        <v>2.9158</v>
+        <v>2.91555</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>2.05802</v>
       </c>
       <c r="K327" t="n">
-        <v>2.63814</v>
+        <v>2.64673</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>1.82602</v>
       </c>
       <c r="K328" t="n">
-        <v>2.3593</v>
+        <v>2.3591</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>1.16177</v>
       </c>
       <c r="K329" t="n">
-        <v>2.05965</v>
+        <v>2.05948</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>1.15674</v>
       </c>
       <c r="K330" t="n">
-        <v>1.53244</v>
+        <v>1.53231</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>0.72941</v>
       </c>
       <c r="K331" t="n">
-        <v>1.00907</v>
+        <v>1.00899</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>1.13298</v>
       </c>
       <c r="K332" t="n">
-        <v>0.9569</v>
+        <v>0.94835</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>1.19602</v>
       </c>
       <c r="K333" t="n">
-        <v>0.54022</v>
+        <v>0.54866</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>-2.43287</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.2934</v>
+        <v>-0.29338</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>2.74486</v>
       </c>
       <c r="K337" t="n">
-        <v>-0.32647</v>
+        <v>-0.32644</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>-0.53278</v>
       </c>
       <c r="K338" t="n">
-        <v>-0.36044</v>
+        <v>-0.36041</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>-0.09285</v>
       </c>
       <c r="K339" t="n">
-        <v>-0.10884</v>
+        <v>-0.10883</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>-0.52616</v>
       </c>
       <c r="K340" t="n">
-        <v>0.14249</v>
+        <v>0.14247</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>-1.22507</v>
       </c>
       <c r="K341" t="n">
-        <v>0.40194</v>
+        <v>0.40191</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>-1.44273</v>
       </c>
       <c r="K342" t="n">
-        <v>0.69596</v>
+        <v>0.6959</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>-1.09171</v>
       </c>
       <c r="K343" t="n">
-        <v>1.1501</v>
+        <v>1.15</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>-0.75704</v>
       </c>
       <c r="K344" t="n">
-        <v>1.20785</v>
+        <v>1.21624</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>-0.69376</v>
       </c>
       <c r="K345" t="n">
-        <v>1.66233</v>
+        <v>1.66219</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>-0.13945</v>
       </c>
       <c r="K346" t="n">
-        <v>2.05163</v>
+        <v>2.05145</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>-1.0381</v>
       </c>
       <c r="K347" t="n">
-        <v>2.04082</v>
+        <v>2.04064</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>2.99158</v>
       </c>
       <c r="K348" t="n">
-        <v>2.53069</v>
+        <v>2.53047</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>-1.39386</v>
       </c>
       <c r="K349" t="n">
-        <v>2.79667</v>
+        <v>2.79644</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>2.56005</v>
       </c>
       <c r="K350" t="n">
-        <v>3.17153</v>
+        <v>3.17127</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>1.78134</v>
       </c>
       <c r="K351" t="n">
-        <v>2.90839</v>
+        <v>2.90815</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>1.56742</v>
       </c>
       <c r="K352" t="n">
-        <v>3.0298</v>
+        <v>3.02954</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>-49.2774</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.87406</v>
+        <v>-38.87916</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>-69.48389</v>
       </c>
       <c r="K354" t="n">
-        <v>-38.42118</v>
+        <v>-38.41799</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>-70.07268000000001</v>
       </c>
       <c r="K355" t="n">
-        <v>-33.27247</v>
+        <v>-33.26971</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>-74.73842</v>
       </c>
       <c r="K356" t="n">
-        <v>-30.14255</v>
+        <v>-30.14005</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>-74.86150000000001</v>
       </c>
       <c r="K357" t="n">
-        <v>-25.53473</v>
+        <v>-25.53262</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>-76.53857000000001</v>
       </c>
       <c r="K358" t="n">
-        <v>-26.06081</v>
+        <v>-26.05866</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>-66.67775</v>
       </c>
       <c r="K359" t="n">
-        <v>-22.15638</v>
+        <v>-22.15456</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>-56.85972</v>
       </c>
       <c r="K360" t="n">
-        <v>-20.3936</v>
+        <v>-20.39193</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>-53.25212</v>
       </c>
       <c r="K361" t="n">
-        <v>-19.73039</v>
+        <v>-19.72878</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66625330416709</v>
+        <v>11.66413553932171</v>
       </c>
       <c r="C242" t="n">
-        <v>11.38098288262852</v>
+        <v>11.37914394126496</v>
       </c>
       <c r="D242" t="n">
-        <v>10.14177525634576</v>
+        <v>10.14543498162801</v>
       </c>
       <c r="E242" t="n">
-        <v>7.262289885416084</v>
+        <v>7.262183868821204</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.25935409865535</v>
+        <v>12.2569394762043</v>
       </c>
       <c r="C243" t="n">
-        <v>12.4453048619231</v>
+        <v>12.44335026147107</v>
       </c>
       <c r="D243" t="n">
-        <v>7.812125073101028</v>
+        <v>7.820798380506711</v>
       </c>
       <c r="E243" t="n">
-        <v>8.994905489355954</v>
+        <v>8.994846680981784</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.990005044528866</v>
+        <v>3.9866593851134</v>
       </c>
       <c r="C244" t="n">
-        <v>7.191453446553786</v>
+        <v>7.190150230366599</v>
       </c>
       <c r="D244" t="n">
-        <v>6.052646459148581</v>
+        <v>6.051273333379537</v>
       </c>
       <c r="E244" t="n">
-        <v>8.710603495536295</v>
+        <v>8.71046286593289</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.850785559369396</v>
+        <v>3.848930119482086</v>
       </c>
       <c r="C245" t="n">
-        <v>7.422214939710536</v>
+        <v>7.420865127108267</v>
       </c>
       <c r="D245" t="n">
-        <v>4.814095014480779</v>
+        <v>4.806639006996449</v>
       </c>
       <c r="E245" t="n">
-        <v>8.576280299131579</v>
+        <v>8.576970772713576</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1941199755403744</v>
+        <v>0.1919509790099472</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6881005195007561</v>
+        <v>-0.6887887861535935</v>
       </c>
       <c r="D246" t="n">
-        <v>1.821786103165723</v>
+        <v>1.811413989725974</v>
       </c>
       <c r="E246" t="n">
-        <v>9.481645389781512</v>
+        <v>9.481912029521444</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,16 +11039,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3259899185758308</v>
+        <v>-0.3239377211504246</v>
       </c>
       <c r="C247" t="n">
-        <v>2.261945142372523</v>
+        <v>2.262178221868605</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.613702249509386</v>
+        <v>-1.62500891141667</v>
       </c>
       <c r="E247" t="n">
-        <v>9.099938023603048</v>
+        <v>9.099672204091602</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.542230263887567</v>
+        <v>-1.542122859692419</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.325908267393884</v>
+        <v>-2.326073188073685</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.090282388185794</v>
+        <v>-3.091911712012352</v>
       </c>
       <c r="E248" t="n">
-        <v>8.143297689088836</v>
+        <v>8.14296684344853</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.44833089292391</v>
+        <v>1.448462816206386</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2355169030637039</v>
+        <v>-0.2359824402951127</v>
       </c>
       <c r="D249" t="n">
-        <v>2.497926009125817</v>
+        <v>2.500126526245938</v>
       </c>
       <c r="E249" t="n">
-        <v>7.140901526058352</v>
+        <v>7.140442191043905</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,16 +11168,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.817683432839903</v>
+        <v>4.817578895554142</v>
       </c>
       <c r="C250" t="n">
-        <v>4.678615334283576</v>
+        <v>4.677159702935918</v>
       </c>
       <c r="D250" t="n">
-        <v>6.337564785684013</v>
+        <v>6.342706597823766</v>
       </c>
       <c r="E250" t="n">
-        <v>8.281862738730727</v>
+        <v>8.281670722906821</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8303809079122537</v>
+        <v>0.8296802119459823</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477657197210713</v>
+        <v>1.476557181038896</v>
       </c>
       <c r="D251" t="n">
-        <v>2.659409229258847</v>
+        <v>2.657911122927659</v>
       </c>
       <c r="E251" t="n">
-        <v>8.429473218608274</v>
+        <v>8.429360840016486</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.660185791849613</v>
+        <v>3.658830351177</v>
       </c>
       <c r="C252" t="n">
-        <v>2.985280301847459</v>
+        <v>2.984687160875898</v>
       </c>
       <c r="D252" t="n">
-        <v>3.9483946110072</v>
+        <v>3.945867355537014</v>
       </c>
       <c r="E252" t="n">
-        <v>10.20423573868365</v>
+        <v>10.20488947387723</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.117710391463228</v>
+        <v>7.116055336712956</v>
       </c>
       <c r="C253" t="n">
-        <v>8.443535038248529</v>
+        <v>8.441868042944778</v>
       </c>
       <c r="D253" t="n">
-        <v>3.625809686479164</v>
+        <v>3.63063193221731</v>
       </c>
       <c r="E253" t="n">
-        <v>7.930211888163075</v>
+        <v>7.929826335525414</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.365214682268229</v>
+        <v>7.365281359156817</v>
       </c>
       <c r="C254" t="n">
-        <v>7.324055137747054</v>
+        <v>7.323731207142203</v>
       </c>
       <c r="D254" t="n">
-        <v>5.745492857886414</v>
+        <v>5.753737798037961</v>
       </c>
       <c r="E254" t="n">
-        <v>8.195360074678092</v>
+        <v>8.195554870273591</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.447688862985522</v>
+        <v>5.447577284141514</v>
       </c>
       <c r="C255" t="n">
-        <v>5.902160428961123</v>
+        <v>5.902186079304306</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549896497209159</v>
+        <v>2.5496167573414</v>
       </c>
       <c r="E255" t="n">
-        <v>6.40275615899486</v>
+        <v>6.402910688139607</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.69260369515444</v>
+        <v>11.69267939491252</v>
       </c>
       <c r="C256" t="n">
-        <v>9.870546556088611</v>
+        <v>9.870047871704358</v>
       </c>
       <c r="D256" t="n">
-        <v>5.665534819237394</v>
+        <v>5.668221117197425</v>
       </c>
       <c r="E256" t="n">
-        <v>7.167362280866429</v>
+        <v>7.16769495670293</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.785099197577129</v>
+        <v>8.783692609095217</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537419444554374</v>
+        <v>8.536753864101332</v>
       </c>
       <c r="D257" t="n">
-        <v>5.102600017245051</v>
+        <v>5.103875682899162</v>
       </c>
       <c r="E257" t="n">
-        <v>7.45369339921611</v>
+        <v>7.453365129835721</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92384274705727</v>
+        <v>11.92274785361991</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74520973265139</v>
+        <v>11.74421204781149</v>
       </c>
       <c r="D258" t="n">
-        <v>8.783663898528737</v>
+        <v>8.78628225027307</v>
       </c>
       <c r="E258" t="n">
-        <v>7.927405498168083</v>
+        <v>7.927439136188053</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.446600575159</v>
+        <v>11.44870823188746</v>
       </c>
       <c r="C259" t="n">
-        <v>9.112896710121564</v>
+        <v>9.113169505109964</v>
       </c>
       <c r="D259" t="n">
-        <v>7.830446161609883</v>
+        <v>7.833268737162702</v>
       </c>
       <c r="E259" t="n">
-        <v>8.263089960511593</v>
+        <v>8.263316664787235</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.849609772655921</v>
+        <v>8.849816587340097</v>
       </c>
       <c r="C260" t="n">
-        <v>9.290597596026728</v>
+        <v>9.290438988105354</v>
       </c>
       <c r="D260" t="n">
-        <v>8.072700729430004</v>
+        <v>8.068875265934516</v>
       </c>
       <c r="E260" t="n">
-        <v>8.668532644752824</v>
+        <v>8.668859823558627</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52766492784214</v>
+        <v>12.52773476709823</v>
       </c>
       <c r="C261" t="n">
-        <v>10.2982473989669</v>
+        <v>10.29754595037129</v>
       </c>
       <c r="D261" t="n">
-        <v>5.621256225451754</v>
+        <v>5.621509916156309</v>
       </c>
       <c r="E261" t="n">
-        <v>10.41246194179266</v>
+        <v>10.41295647616063</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,16 +11684,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.800399785729572</v>
+        <v>6.800382439092068</v>
       </c>
       <c r="C262" t="n">
-        <v>6.492418147981338</v>
+        <v>6.4926719287004</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8176158675285428</v>
+        <v>-0.8224428994861976</v>
       </c>
       <c r="E262" t="n">
-        <v>8.713618023532987</v>
+        <v>8.713576103934951</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.094094215499648</v>
+        <v>9.094036128113414</v>
       </c>
       <c r="C263" t="n">
-        <v>7.446105009342729</v>
+        <v>7.445818589214914</v>
       </c>
       <c r="D263" t="n">
-        <v>3.153466522347537</v>
+        <v>3.149496711978794</v>
       </c>
       <c r="E263" t="n">
-        <v>8.713601409864324</v>
+        <v>8.713258057301299</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.40884606913195</v>
+        <v>13.4087559507174</v>
       </c>
       <c r="C264" t="n">
-        <v>11.22644364547656</v>
+        <v>11.22472825134666</v>
       </c>
       <c r="D264" t="n">
-        <v>4.655799550792006</v>
+        <v>4.656561367290268</v>
       </c>
       <c r="E264" t="n">
-        <v>6.297441498966472</v>
+        <v>6.29647412590626</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.051810189784581</v>
+        <v>8.051695911066915</v>
       </c>
       <c r="C265" t="n">
-        <v>5.782081560706254</v>
+        <v>5.781747539655746</v>
       </c>
       <c r="D265" t="n">
-        <v>2.716916294732363</v>
+        <v>2.715952801444366</v>
       </c>
       <c r="E265" t="n">
-        <v>7.341637362815145</v>
+        <v>7.341020583474456</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.583496886206849</v>
+        <v>2.583091463254239</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.1924203004195046</v>
+        <v>-0.1912854155142973</v>
       </c>
       <c r="D266" t="n">
-        <v>2.193771530865063</v>
+        <v>2.196002033035582</v>
       </c>
       <c r="E266" t="n">
-        <v>12.02027629113644</v>
+        <v>12.02053043608271</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.106135023096825</v>
+        <v>5.105348164337498</v>
       </c>
       <c r="C267" t="n">
-        <v>1.665031881611179</v>
+        <v>1.665301515181095</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454386275544596</v>
+        <v>3.454390362819426</v>
       </c>
       <c r="E267" t="n">
-        <v>13.54215568601143</v>
+        <v>13.54258448826731</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.822645824546679</v>
+        <v>5.822207641870669</v>
       </c>
       <c r="C268" t="n">
-        <v>3.406630501793262</v>
+        <v>3.406175016407964</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9105918666783674</v>
+        <v>0.9116235281249274</v>
       </c>
       <c r="E268" t="n">
-        <v>15.11426735778356</v>
+        <v>15.11466247455921</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.38684106524516</v>
+        <v>2.38548659477269</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7189397189474089</v>
+        <v>0.7192327276471344</v>
       </c>
       <c r="D269" t="n">
-        <v>2.949557564385952</v>
+        <v>2.950804489409142</v>
       </c>
       <c r="E269" t="n">
-        <v>10.12616007499956</v>
+        <v>10.12571727299405</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.700325205104259</v>
+        <v>2.699563854840092</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3546777387537281</v>
+        <v>0.3550156735170562</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.518029222767259</v>
+        <v>-1.516121644751112</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77232286894059</v>
+        <v>11.77205505955776</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.102823757040852</v>
+        <v>4.106185234372228</v>
       </c>
       <c r="C271" t="n">
-        <v>3.271670702470497</v>
+        <v>3.272514010274419</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.17125574806336</v>
+        <v>-1.168113995728171</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72699074573509</v>
+        <v>12.72709295286176</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.80241093376219</v>
+        <v>3.803456541528671</v>
       </c>
       <c r="C272" t="n">
-        <v>2.824579172849906</v>
+        <v>2.824453481162514</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.926481791735602</v>
+        <v>-2.928436964250214</v>
       </c>
       <c r="E272" t="n">
-        <v>12.50259260835889</v>
+        <v>12.5029475525436</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.047932537386288</v>
+        <v>2.04826928707269</v>
       </c>
       <c r="C273" t="n">
-        <v>2.703547866816791</v>
+        <v>2.703435563075951</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1125718736767256</v>
+        <v>-0.1130744319375987</v>
       </c>
       <c r="E273" t="n">
-        <v>12.17080980843452</v>
+        <v>12.1713443693628</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.13967557059269</v>
+        <v>-0.1396425969474535</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2207406341990348</v>
+        <v>0.2207108557370496</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03492681109842355</v>
+        <v>0.0340605841581576</v>
       </c>
       <c r="E274" t="n">
-        <v>11.93533455920028</v>
+        <v>11.93580649836579</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3207261782844362</v>
+        <v>-0.320549796896541</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.472578431880899</v>
+        <v>-0.4724018215598424</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.022566075332288</v>
+        <v>-2.020893191590689</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91480364208286</v>
+        <v>10.91531657047879</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.988745706072305</v>
+        <v>-3.988643543095716</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.152270181218087</v>
+        <v>-4.151047144450438</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.715190241320476</v>
+        <v>-3.716217027826829</v>
       </c>
       <c r="E276" t="n">
-        <v>8.911794670301564</v>
+        <v>8.911737780661833</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.35977939453902</v>
+        <v>-3.35984222346859</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.721698083349578</v>
+        <v>-3.720858000324678</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.386670997398411</v>
+        <v>-3.388273857734614</v>
       </c>
       <c r="E277" t="n">
-        <v>10.80416204462631</v>
+        <v>10.80489978480064</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.267400609230675</v>
+        <v>3.266182364072057</v>
       </c>
       <c r="C278" t="n">
-        <v>3.589726468039656</v>
+        <v>3.588312897247126</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.62163747555073</v>
+        <v>-1.625798511291388</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127423963776057</v>
+        <v>6.12740961722531</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.118178649757128</v>
+        <v>-0.119361217100411</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4800319367258332</v>
+        <v>0.4794768917733672</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3347431432068393</v>
+        <v>-0.3376418332989517</v>
       </c>
       <c r="E279" t="n">
-        <v>3.998810603262903</v>
+        <v>3.998608744615306</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.843770045572424</v>
+        <v>-1.844672981215489</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.143309110954994</v>
+        <v>-2.142901592073687</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7994992367717169</v>
+        <v>-0.801070843838203</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4609418439403878</v>
+        <v>0.4603670650394909</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.177146027128529</v>
+        <v>2.175387328077627</v>
       </c>
       <c r="C281" t="n">
-        <v>1.841871992387278</v>
+        <v>1.841097754354393</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.089934422089546</v>
+        <v>-3.091066331648129</v>
       </c>
       <c r="E281" t="n">
-        <v>3.986134638673811</v>
+        <v>3.985676223464241</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.19906287137117</v>
+        <v>1.198063626895673</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625980916141145</v>
+        <v>1.625317647265567</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2861040679217552</v>
+        <v>0.2886836619601985</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9897368571085252</v>
+        <v>0.9892668931037463</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.116867338422756</v>
+        <v>1.121732448148927</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5712768615540487</v>
+        <v>0.5733067092592137</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1498130003839471</v>
+        <v>0.1559827866278729</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1348458053189394</v>
+        <v>-0.1352059543915929</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.53086624616603</v>
+        <v>2.532762581492931</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05377514698984287</v>
+        <v>-0.0527058516678669</v>
       </c>
       <c r="D284" t="n">
-        <v>2.829244701264844</v>
+        <v>2.829248572920484</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7753605927239393</v>
+        <v>0.7750691128424192</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4713074011657437</v>
+        <v>0.4717123205917106</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7783124821529652</v>
+        <v>-0.7773819375735402</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.489860113452579</v>
+        <v>-1.491988221217611</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2697309336072484</v>
+        <v>0.2694048064056931</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.658752230467544</v>
+        <v>4.658864690669295</v>
       </c>
       <c r="C286" t="n">
-        <v>1.836271241758403</v>
+        <v>1.836134917285559</v>
       </c>
       <c r="D286" t="n">
-        <v>2.953083546730495</v>
+        <v>2.955690723048998</v>
       </c>
       <c r="E286" t="n">
-        <v>1.26805752211101</v>
+        <v>1.268020625516786</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.816305571528346</v>
+        <v>5.816405112246281</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936736780516248</v>
+        <v>3.936288327568338</v>
       </c>
       <c r="D287" t="n">
-        <v>4.864381197979695</v>
+        <v>4.871296070878484</v>
       </c>
       <c r="E287" t="n">
-        <v>2.679866638210382</v>
+        <v>2.680106155787643</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.481089525225634</v>
+        <v>3.480733807609582</v>
       </c>
       <c r="C288" t="n">
-        <v>2.924721239557271</v>
+        <v>2.924189297711632</v>
       </c>
       <c r="D288" t="n">
-        <v>2.107533850769761</v>
+        <v>2.109403820450528</v>
       </c>
       <c r="E288" t="n">
-        <v>3.368005906624827</v>
+        <v>3.368335329948735</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.843333982594535</v>
+        <v>6.842979004964489</v>
       </c>
       <c r="C289" t="n">
-        <v>5.98250125291766</v>
+        <v>5.981600899687334</v>
       </c>
       <c r="D289" t="n">
-        <v>2.23260254751616</v>
+        <v>2.234870657038535</v>
       </c>
       <c r="E289" t="n">
-        <v>3.828976912609172</v>
+        <v>3.829622109295161</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8761466545507801</v>
+        <v>0.8746913845547155</v>
       </c>
       <c r="C290" t="n">
-        <v>1.185217726573762</v>
+        <v>1.18505024651836</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.208771855578739</v>
+        <v>-2.215741702760299</v>
       </c>
       <c r="E290" t="n">
-        <v>2.401785583549021</v>
+        <v>2.401475414146992</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.298028870279213</v>
+        <v>3.296336936091016</v>
       </c>
       <c r="C291" t="n">
-        <v>3.351274961961059</v>
+        <v>3.350677637341315</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.251589789513929</v>
+        <v>-1.259458908317534</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627508120133127</v>
+        <v>3.627450913030428</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.314907075575027</v>
+        <v>6.312842702850019</v>
       </c>
       <c r="C292" t="n">
-        <v>5.590874372075838</v>
+        <v>5.58960534895534</v>
       </c>
       <c r="D292" t="n">
-        <v>2.178769830584604</v>
+        <v>2.173896387517238</v>
       </c>
       <c r="E292" t="n">
-        <v>4.879953815476923</v>
+        <v>4.879886563603586</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.545188947865219</v>
+        <v>3.542891400384729</v>
       </c>
       <c r="C293" t="n">
-        <v>2.389758570113432</v>
+        <v>2.389185997778576</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532719483097323</v>
+        <v>2.532383705481922</v>
       </c>
       <c r="E293" t="n">
-        <v>4.24300668958113</v>
+        <v>4.243071502053164</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.36924401644692</v>
+        <v>8.367393998561568</v>
       </c>
       <c r="C294" t="n">
-        <v>5.934059988893314</v>
+        <v>5.933111448051087</v>
       </c>
       <c r="D294" t="n">
-        <v>4.199954387806892</v>
+        <v>4.202638094986089</v>
       </c>
       <c r="E294" t="n">
-        <v>6.255128194430526</v>
+        <v>6.255420209753604</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.580369122344365</v>
+        <v>6.587530810036468</v>
       </c>
       <c r="C295" t="n">
-        <v>5.390703131980179</v>
+        <v>5.39341256147321</v>
       </c>
       <c r="D295" t="n">
-        <v>6.110291894376974</v>
+        <v>6.116918737561194</v>
       </c>
       <c r="E295" t="n">
-        <v>6.953679655448131</v>
+        <v>6.954135403436901</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.118680360620087</v>
+        <v>5.121424556052157</v>
       </c>
       <c r="C296" t="n">
-        <v>5.699099198300606</v>
+        <v>5.699787258220601</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1167878717958981</v>
+        <v>0.116665678683292</v>
       </c>
       <c r="E296" t="n">
-        <v>4.682280877085487</v>
+        <v>4.682455408621822</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.875228811278908</v>
+        <v>3.875864836824761</v>
       </c>
       <c r="C297" t="n">
-        <v>3.991269924559249</v>
+        <v>3.991566189393403</v>
       </c>
       <c r="D297" t="n">
-        <v>2.955164633677843</v>
+        <v>2.952449532182566</v>
       </c>
       <c r="E297" t="n">
-        <v>4.085445125718756</v>
+        <v>4.085327346884982</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.454716518148237</v>
+        <v>2.455182843208514</v>
       </c>
       <c r="C298" t="n">
-        <v>1.081115240720942</v>
+        <v>1.081718516394115</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4371781129176133</v>
+        <v>0.4378171643498963</v>
       </c>
       <c r="E298" t="n">
-        <v>3.051521458573458</v>
+        <v>3.051579777303193</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.298433728859718</v>
+        <v>3.29852780660973</v>
       </c>
       <c r="C299" t="n">
-        <v>2.777044801185236</v>
+        <v>2.776923421928812</v>
       </c>
       <c r="D299" t="n">
-        <v>1.825031025128387</v>
+        <v>1.828727090665172</v>
       </c>
       <c r="E299" t="n">
-        <v>2.811656974509091</v>
+        <v>2.81148178790589</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.507386817870995</v>
+        <v>4.507148824291041</v>
       </c>
       <c r="C300" t="n">
-        <v>3.663906644519321</v>
+        <v>3.663366517196165</v>
       </c>
       <c r="D300" t="n">
-        <v>3.901322631013682</v>
+        <v>3.904539751263902</v>
       </c>
       <c r="E300" t="n">
-        <v>3.749830337962567</v>
+        <v>3.749958253980878</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.774522760947697</v>
+        <v>4.774012956170615</v>
       </c>
       <c r="C301" t="n">
-        <v>3.147561656173092</v>
+        <v>3.147061090304804</v>
       </c>
       <c r="D301" t="n">
-        <v>5.331745518014097</v>
+        <v>5.337421755280891</v>
       </c>
       <c r="E301" t="n">
-        <v>1.882280366944999</v>
+        <v>1.882203427512041</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.336380009538866</v>
+        <v>5.333938822239714</v>
       </c>
       <c r="C302" t="n">
-        <v>3.377411742877423</v>
+        <v>3.376029845755468</v>
       </c>
       <c r="D302" t="n">
-        <v>4.101074181332542</v>
+        <v>4.099657622411113</v>
       </c>
       <c r="E302" t="n">
-        <v>1.196428282588413</v>
+        <v>1.196128226786874</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.235040447155748</v>
+        <v>5.232475676184145</v>
       </c>
       <c r="C303" t="n">
-        <v>3.221353623964363</v>
+        <v>3.220016491119737</v>
       </c>
       <c r="D303" t="n">
-        <v>1.621144324312662</v>
+        <v>1.615584479312737</v>
       </c>
       <c r="E303" t="n">
-        <v>3.115644147601593</v>
+        <v>3.115392809325668</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.069391546143206</v>
+        <v>1.06661365322267</v>
       </c>
       <c r="C304" t="n">
-        <v>0.5282433788493579</v>
+        <v>0.527380804591937</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6741055249131711</v>
+        <v>-0.6800849329557712</v>
       </c>
       <c r="E304" t="n">
-        <v>3.834595941427565</v>
+        <v>3.834513152060848</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.076295803963223</v>
+        <v>1.073470692332035</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1589416570332958</v>
+        <v>0.1582839158669636</v>
       </c>
       <c r="D305" t="n">
-        <v>2.198689027007572</v>
+        <v>2.199355223074062</v>
       </c>
       <c r="E305" t="n">
-        <v>1.963705452568854</v>
+        <v>1.963544907674075</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6425467793484962</v>
+        <v>0.6398987556194724</v>
       </c>
       <c r="C306" t="n">
-        <v>0.04784092237797299</v>
+        <v>0.04723926447629534</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.261613960311925</v>
+        <v>-1.26268922806676</v>
       </c>
       <c r="E306" t="n">
-        <v>2.3206050907844</v>
+        <v>2.320441003712248</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.179122487909946</v>
+        <v>2.189253214403819</v>
       </c>
       <c r="C307" t="n">
-        <v>1.356348012598785</v>
+        <v>1.362015803784788</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.600368830965816</v>
+        <v>-2.598306211624946</v>
       </c>
       <c r="E307" t="n">
-        <v>3.142290151672644</v>
+        <v>3.142176610305869</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.738037130226378</v>
+        <v>1.742001287556616</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2692624512282249</v>
+        <v>0.2718725485006956</v>
       </c>
       <c r="D308" t="n">
-        <v>1.605709819745593</v>
+        <v>1.607220618499916</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799335551868555</v>
+        <v>4.799310163578485</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.15065052806982</v>
+        <v>3.151905566839441</v>
       </c>
       <c r="C309" t="n">
-        <v>2.229988549865602</v>
+        <v>2.23072510820308</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5621748801291071</v>
+        <v>0.5613617013826566</v>
       </c>
       <c r="E309" t="n">
-        <v>5.406119447917734</v>
+        <v>5.406169580966647</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.760639480092444</v>
+        <v>5.761156202062323</v>
       </c>
       <c r="C310" t="n">
-        <v>6.605984965448575</v>
+        <v>6.604917101322871</v>
       </c>
       <c r="D310" t="n">
-        <v>2.765365279777066</v>
+        <v>2.766224148008734</v>
       </c>
       <c r="E310" t="n">
-        <v>8.394610749743325</v>
+        <v>8.394809457964737</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.92183953272558</v>
+        <v>3.921638192517118</v>
       </c>
       <c r="C311" t="n">
-        <v>3.167353210164303</v>
+        <v>3.166624863163792</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6449098348123794</v>
+        <v>0.6448082791826071</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879408110110828</v>
+        <v>4.879402945409383</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.030672935637236</v>
+        <v>4.030480413239279</v>
       </c>
       <c r="C312" t="n">
-        <v>2.312771068015218</v>
+        <v>2.312819139401978</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.061366387585427</v>
+        <v>-1.060076307130675</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824666263275935</v>
+        <v>5.824698459307132</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.256952397658175</v>
+        <v>3.255876496723409</v>
       </c>
       <c r="C313" t="n">
-        <v>2.328857894111613</v>
+        <v>2.328283252241636</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04675393706392583</v>
+        <v>0.04651505529889022</v>
       </c>
       <c r="E313" t="n">
-        <v>6.33683603915105</v>
+        <v>6.337004881377073</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.284273075992617</v>
+        <v>4.280870412332449</v>
       </c>
       <c r="C314" t="n">
-        <v>3.904035837362874</v>
+        <v>3.90204207327014</v>
       </c>
       <c r="D314" t="n">
-        <v>1.486728282430261</v>
+        <v>1.486473133164656</v>
       </c>
       <c r="E314" t="n">
-        <v>8.653343966139371</v>
+        <v>8.654099506296408</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.695417566818946</v>
+        <v>1.69210020754611</v>
       </c>
       <c r="C315" t="n">
-        <v>2.794702492713119</v>
+        <v>2.793266663314764</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9317167916605751</v>
+        <v>0.929398768095524</v>
       </c>
       <c r="E315" t="n">
-        <v>4.026048811944127</v>
+        <v>4.026214553035445</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.667460736765204</v>
+        <v>2.663489614591952</v>
       </c>
       <c r="C316" t="n">
-        <v>2.932911382026648</v>
+        <v>2.931067677534194</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3985254669233163</v>
+        <v>0.3951649989932138</v>
       </c>
       <c r="E316" t="n">
-        <v>3.650596282030838</v>
+        <v>3.650707115185936</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.786087073308192</v>
+        <v>8.781550433858376</v>
       </c>
       <c r="C317" t="n">
-        <v>9.064674858859423</v>
+        <v>9.061030871850662</v>
       </c>
       <c r="D317" t="n">
-        <v>0.387501551756908</v>
+        <v>0.3890882456791589</v>
       </c>
       <c r="E317" t="n">
-        <v>7.316418948683445</v>
+        <v>7.31681592747766</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.393080703505214</v>
+        <v>4.388750156357846</v>
       </c>
       <c r="C318" t="n">
-        <v>5.428876992000031</v>
+        <v>5.426745017323142</v>
       </c>
       <c r="D318" t="n">
-        <v>2.155649256478576</v>
+        <v>2.155876237899257</v>
       </c>
       <c r="E318" t="n">
-        <v>5.212340110491653</v>
+        <v>5.21254844273713</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.180576220044174</v>
+        <v>4.195805572068401</v>
       </c>
       <c r="C319" t="n">
-        <v>3.362364189456657</v>
+        <v>3.372432010235737</v>
       </c>
       <c r="D319" t="n">
-        <v>2.726818385755503</v>
+        <v>2.731103489499276</v>
       </c>
       <c r="E319" t="n">
-        <v>3.719915067424484</v>
+        <v>3.719646736501181</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.696785105276204</v>
+        <v>6.70279877123956</v>
       </c>
       <c r="C320" t="n">
-        <v>6.734312555106525</v>
+        <v>6.737448771960697</v>
       </c>
       <c r="D320" t="n">
-        <v>2.221111410746235</v>
+        <v>2.225586470392193</v>
       </c>
       <c r="E320" t="n">
-        <v>3.062122069966611</v>
+        <v>3.06178143459146</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.938480459757534</v>
+        <v>5.940580547132179</v>
       </c>
       <c r="C321" t="n">
-        <v>4.638316396427</v>
+        <v>4.639648531501028</v>
       </c>
       <c r="D321" t="n">
-        <v>1.457379056003649</v>
+        <v>1.456914561131661</v>
       </c>
       <c r="E321" t="n">
-        <v>2.661127550605769</v>
+        <v>2.660654702382237</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.567042878888717</v>
+        <v>5.567800262076816</v>
       </c>
       <c r="C322" t="n">
-        <v>3.517921613197572</v>
+        <v>3.518447967887606</v>
       </c>
       <c r="D322" t="n">
-        <v>0.05306793799160214</v>
+        <v>0.05176696023512228</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5240318420215995</v>
+        <v>-0.5248481033391816</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.357806509517181</v>
+        <v>4.357518645060354</v>
       </c>
       <c r="C323" t="n">
-        <v>5.143917803260556</v>
+        <v>5.142997428163198</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8422528722962896</v>
+        <v>0.8392621864982575</v>
       </c>
       <c r="E323" t="n">
-        <v>4.167543269776441</v>
+        <v>4.167263467812532</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.531085086948486</v>
+        <v>7.530497463953711</v>
       </c>
       <c r="C324" t="n">
-        <v>6.857079026611124</v>
+        <v>6.855869521063851</v>
       </c>
       <c r="D324" t="n">
-        <v>3.827018156259188</v>
+        <v>3.827801042999801</v>
       </c>
       <c r="E324" t="n">
-        <v>2.183479946776545</v>
+        <v>2.182968812025621</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.088998948339919</v>
+        <v>6.087071758128282</v>
       </c>
       <c r="C325" t="n">
-        <v>5.483179174550989</v>
+        <v>5.481874184301461</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1554156349438118</v>
+        <v>0.1503669738298852</v>
       </c>
       <c r="E325" t="n">
-        <v>2.89160318585906</v>
+        <v>2.891483701435416</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.855143370621407</v>
+        <v>5.849968951153572</v>
       </c>
       <c r="C326" t="n">
-        <v>5.011562899930411</v>
+        <v>5.008590792978262</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7945457523386157</v>
+        <v>0.7927646448653736</v>
       </c>
       <c r="E326" t="n">
-        <v>4.478531452313073</v>
+        <v>4.479071304120197</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.917462619523709</v>
+        <v>9.911702370517418</v>
       </c>
       <c r="C327" t="n">
-        <v>9.494403871826451</v>
+        <v>9.489640194264304</v>
       </c>
       <c r="D327" t="n">
-        <v>2.694518187304729</v>
+        <v>2.693741657212567</v>
       </c>
       <c r="E327" t="n">
-        <v>7.803337214869899</v>
+        <v>7.803906150491247</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41945739232606</v>
+        <v>10.41313513434003</v>
       </c>
       <c r="C328" t="n">
-        <v>9.144565002825388</v>
+        <v>9.139774390820987</v>
       </c>
       <c r="D328" t="n">
-        <v>3.150291537392014</v>
+        <v>3.151038356959646</v>
       </c>
       <c r="E328" t="n">
-        <v>7.364203646897005</v>
+        <v>7.364618306906068</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.000070077434925</v>
+        <v>3.993981550817516</v>
       </c>
       <c r="C329" t="n">
-        <v>3.086214975340962</v>
+        <v>3.08301901705974</v>
       </c>
       <c r="D329" t="n">
-        <v>2.842464902553576</v>
+        <v>2.844223187267447</v>
       </c>
       <c r="E329" t="n">
-        <v>3.599908389074891</v>
+        <v>3.600234102263089</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.295765901860073</v>
+        <v>6.289365991827944</v>
       </c>
       <c r="C330" t="n">
-        <v>5.629002415840167</v>
+        <v>5.625741731906175</v>
       </c>
       <c r="D330" t="n">
-        <v>1.317507669097662</v>
+        <v>1.31770281312058</v>
       </c>
       <c r="E330" t="n">
-        <v>5.631768108171653</v>
+        <v>5.632036892698911</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.954587173771553</v>
+        <v>5.977540468050813</v>
       </c>
       <c r="C331" t="n">
-        <v>7.414486981490342</v>
+        <v>7.430773285762582</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.078216469543902</v>
+        <v>-1.070689312365636</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981386314041991</v>
+        <v>4.981337839832478</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.173061339683226</v>
+        <v>4.181968216917786</v>
       </c>
       <c r="C332" t="n">
-        <v>3.974569170531494</v>
+        <v>3.980846405336713</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.62738837456452</v>
+        <v>-1.621570342275713</v>
       </c>
       <c r="E332" t="n">
-        <v>4.51157297877276</v>
+        <v>4.511618361274494</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.83663930201219</v>
+        <v>3.840057874906622</v>
       </c>
       <c r="C333" t="n">
-        <v>3.745083874855903</v>
+        <v>3.747406521106345</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.156114157040391</v>
+        <v>-3.153381595054594</v>
       </c>
       <c r="E333" t="n">
-        <v>4.43621711152804</v>
+        <v>4.436327493515702</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.929350137982034</v>
+        <v>2.930319961613503</v>
       </c>
       <c r="C334" t="n">
-        <v>4.881230093075906</v>
+        <v>4.880860571832457</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.617719829323117</v>
+        <v>-1.619057547866032</v>
       </c>
       <c r="E334" t="n">
-        <v>5.108331509827013</v>
+        <v>5.108127798093842</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.734027008490792</v>
+        <v>3.733729659563378</v>
       </c>
       <c r="C335" t="n">
-        <v>1.694221529529982</v>
+        <v>1.692856454797731</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.581536718973865</v>
+        <v>-2.585151904762928</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832541237547482</v>
+        <v>3.83257002224815</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.722559718300422</v>
+        <v>3.721525143497573</v>
       </c>
       <c r="C336" t="n">
-        <v>3.655399016192296</v>
+        <v>3.654203292557034</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.337600238135141</v>
+        <v>-3.339432220793237</v>
       </c>
       <c r="E336" t="n">
-        <v>3.491855303193958</v>
+        <v>3.491745596834739</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>2.009657186433711</v>
+        <v>2.006968217291893</v>
       </c>
       <c r="C337" t="n">
-        <v>1.177394468593107</v>
+        <v>1.175067476344638</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.1415298688663</v>
+        <v>-3.148156875061581</v>
       </c>
       <c r="E337" t="n">
-        <v>3.634007251881077</v>
+        <v>3.634217958397801</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.29378619107501</v>
+        <v>3.286215676239923</v>
       </c>
       <c r="C338" t="n">
-        <v>2.205230130594282</v>
+        <v>2.200069060009247</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.36268761464844</v>
+        <v>-2.366256641533082</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875020616854828</v>
+        <v>1.874920141598069</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6754604595028413</v>
+        <v>0.6679553744755484</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.812370272725283</v>
+        <v>-1.817122363537726</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.147175121416189</v>
+        <v>-2.151869165047848</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.606131691839551</v>
+        <v>-0.6064107766733717</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.608718603085159</v>
+        <v>3.599961705733601</v>
       </c>
       <c r="C340" t="n">
-        <v>0.6104598874596467</v>
+        <v>0.6050004031228795</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.717902758988677</v>
+        <v>-2.719537247988635</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.148625169248207</v>
+        <v>-1.14885138367633</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.786722032880442</v>
+        <v>4.777309525822537</v>
       </c>
       <c r="C341" t="n">
-        <v>1.377554566792671</v>
+        <v>1.370883904466114</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.04898844296887</v>
+        <v>-3.052231994705401</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702453840724538</v>
+        <v>1.702448893405673</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.707966553002475</v>
+        <v>5.698364804732381</v>
       </c>
       <c r="C342" t="n">
-        <v>2.861031361499267</v>
+        <v>2.855425029556269</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7315978393046985</v>
+        <v>-0.7365119753634963</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1299319936844179</v>
+        <v>-0.1299857670260862</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.796758007875713</v>
+        <v>5.830956941078957</v>
       </c>
       <c r="C343" t="n">
-        <v>1.542678259431263</v>
+        <v>1.570987213651387</v>
       </c>
       <c r="D343" t="n">
-        <v>2.358318998354969</v>
+        <v>2.369853309271819</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6823074251838479</v>
+        <v>0.6821502298575588</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.832493748071754</v>
+        <v>5.845789041174831</v>
       </c>
       <c r="C344" t="n">
-        <v>3.787456707214698</v>
+        <v>3.797159027002373</v>
       </c>
       <c r="D344" t="n">
-        <v>0.8976182008715528</v>
+        <v>0.9097426024377464</v>
       </c>
       <c r="E344" t="n">
-        <v>2.711150530586881</v>
+        <v>2.711161116581229</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.28063804631847</v>
+        <v>10.28568771086413</v>
       </c>
       <c r="C345" t="n">
-        <v>7.473286693445225</v>
+        <v>7.476373754715726</v>
       </c>
       <c r="D345" t="n">
-        <v>7.746571937349511</v>
+        <v>7.754180384352938</v>
       </c>
       <c r="E345" t="n">
-        <v>2.755788766256728</v>
+        <v>2.756002186615447</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.174380955818633</v>
+        <v>2.176187913093863</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4339839449503669</v>
+        <v>-0.4339555451200905</v>
       </c>
       <c r="D346" t="n">
-        <v>1.640061130985315</v>
+        <v>1.64248815946122</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254129972160346</v>
+        <v>2.254187099149063</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.187470834096608</v>
+        <v>5.187509255304668</v>
       </c>
       <c r="C347" t="n">
-        <v>2.981661709703376</v>
+        <v>2.979746961710084</v>
       </c>
       <c r="D347" t="n">
-        <v>4.059041109093364</v>
+        <v>4.056609662098487</v>
       </c>
       <c r="E347" t="n">
-        <v>2.130332236596555</v>
+        <v>2.13000504836971</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.565456337568573</v>
+        <v>3.563809027496179</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.9885449197875706</v>
+        <v>-0.9902217463757967</v>
       </c>
       <c r="D348" t="n">
-        <v>4.254119250717769</v>
+        <v>4.251388859809024</v>
       </c>
       <c r="E348" t="n">
-        <v>3.13162829779523</v>
+        <v>3.131712790794072</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.733495705622539</v>
+        <v>6.729473966297195</v>
       </c>
       <c r="C349" t="n">
-        <v>5.748503177485431</v>
+        <v>5.744190011743489</v>
       </c>
       <c r="D349" t="n">
-        <v>6.314668992932382</v>
+        <v>6.30803281768717</v>
       </c>
       <c r="E349" t="n">
-        <v>6.031644179971885</v>
+        <v>6.031576692280116</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.37102070343296</v>
+        <v>5.359516451788293</v>
       </c>
       <c r="C350" t="n">
-        <v>3.221290638624019</v>
+        <v>3.211239386081077</v>
       </c>
       <c r="D350" t="n">
-        <v>6.187877584876689</v>
+        <v>6.18293662343028</v>
       </c>
       <c r="E350" t="n">
-        <v>6.709807963687853</v>
+        <v>6.709190894919859</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.036670691439472</v>
+        <v>6.024875457947099</v>
       </c>
       <c r="C351" t="n">
-        <v>5.009954463559962</v>
+        <v>4.999637360041986</v>
       </c>
       <c r="D351" t="n">
-        <v>1.678606627330637</v>
+        <v>1.67322672676109</v>
       </c>
       <c r="E351" t="n">
-        <v>8.079720541986202</v>
+        <v>8.079498574279098</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.25129567640501</v>
+        <v>-53.25730204644301</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.15659183123405</v>
+        <v>-49.16200988497865</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.32484992891549</v>
+        <v>-44.32528934742422</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.874850721942178</v>
+        <v>-1.874646057648111</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40227326538874</v>
+        <v>-99.4023541634936</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11541009962225</v>
+        <v>-98.1156363733736</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69152333499032</v>
+        <v>-88.69187496442042</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50597924443221</v>
+        <v>-52.5058412797337</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80358947158147</v>
+        <v>-98.80374195675941</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.97695620011115</v>
+        <v>-95.97728545435696</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16074906229977</v>
+        <v>-82.16210606402635</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70000119927046</v>
+        <v>-50.69981154542833</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13346953108211</v>
+        <v>-98.13265454252182</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.35071657721545</v>
+        <v>-94.3483444070967</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41615023146667</v>
+        <v>-81.4135402616682</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98306243935457</v>
+        <v>-42.98296443895493</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74518389800343</v>
+        <v>-97.74478418491439</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.63734028934002</v>
+        <v>-93.63623064463859</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.6449246190539</v>
+        <v>-75.6410413187379</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11483321218209</v>
+        <v>-43.11485718758562</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46065489675475</v>
+        <v>-97.4605015414472</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99913804652259</v>
+        <v>-90.99866131205272</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18974448420637</v>
+        <v>-74.18830410898344</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.6580562396602</v>
+        <v>-45.6578780942826</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43005116124162</v>
+        <v>-97.42997751119337</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.9092772865888</v>
+        <v>-89.90932809237329</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.97533428419089</v>
+        <v>-74.97394533937062</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17036693883285</v>
+        <v>-40.17007727392687</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07588640345942</v>
+        <v>-90.07583923556761</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.42262153916585</v>
+        <v>-81.42335315371349</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.96984249241102</v>
+        <v>-74.9707985908163</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34872106296957</v>
+        <v>-31.34861236515414</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76648845887605</v>
+        <v>-76.76676105394999</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.75406980184265</v>
+        <v>-65.7554469954448</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85394972249412</v>
+        <v>-71.85536775820167</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.57641523086165</v>
+        <v>-12.57580863095149</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.81522300126002</v>
+        <v>-74.81613376888623</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.511323920903</v>
+        <v>-66.51257288463721</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13204008362499</v>
+        <v>-70.13490669416275</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80542082990163</v>
+        <v>-16.80582558663232</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -528,7 +528,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87323</v>
+        <v>6.87342</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -571,10 +571,10 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15367</v>
+        <v>4.15349</v>
       </c>
       <c r="K3" t="n">
-        <v>2.42488</v>
+        <v>2.43838</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55398</v>
+        <v>7.55463</v>
       </c>
       <c r="K4" t="n">
         <v>2.13214</v>
@@ -657,7 +657,7 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74259</v>
+        <v>0.74252</v>
       </c>
       <c r="K5" t="n">
         <v>2.02286</v>
@@ -700,10 +700,10 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77784</v>
+        <v>1.77779</v>
       </c>
       <c r="K6" t="n">
-        <v>1.98007</v>
+        <v>1.99344</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02157</v>
+        <v>2.0214</v>
       </c>
       <c r="K7" t="n">
-        <v>1.71488</v>
+        <v>1.70179</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61385</v>
+        <v>4.61377</v>
       </c>
       <c r="K8" t="n">
         <v>1.47346</v>
@@ -829,7 +829,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05482</v>
+        <v>7.05476</v>
       </c>
       <c r="K9" t="n">
         <v>1.21062</v>
@@ -872,7 +872,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.03481</v>
+        <v>8.034689999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.7003</v>
@@ -915,10 +915,10 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.90081</v>
+        <v>5.90069</v>
       </c>
       <c r="K11" t="n">
-        <v>0.34938</v>
+        <v>0.36237</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.00194</v>
+        <v>3.00204</v>
       </c>
       <c r="K12" t="n">
         <v>0.05167</v>
@@ -1001,7 +1001,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56805</v>
+        <v>3.56814</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1044,7 +1044,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.00281</v>
+        <v>2.00313</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1087,7 +1087,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.20213</v>
+        <v>3.20171</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1130,10 +1130,10 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.71972</v>
+        <v>4.72055</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.21134</v>
+        <v>-1.22423</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26354</v>
+        <v>5.26336</v>
       </c>
       <c r="K17" t="n">
         <v>-1.68662</v>
@@ -1216,7 +1216,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22933</v>
+        <v>4.22922</v>
       </c>
       <c r="K18" t="n">
         <v>-1.9802</v>
@@ -1259,10 +1259,10 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76165</v>
+        <v>3.76141</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.26512</v>
+        <v>-2.25254</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94789</v>
+        <v>0.94779</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53148</v>
@@ -1345,7 +1345,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13358</v>
+        <v>-1.13364</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1388,7 +1388,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.8686</v>
+        <v>-2.86873</v>
       </c>
       <c r="K22" t="n">
         <v>-2.39536</v>
@@ -1431,7 +1431,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.60379</v>
+        <v>-2.60396</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1474,10 +1474,10 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90647</v>
+        <v>-2.90628</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.18205</v>
+        <v>-2.19496</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.72218</v>
+        <v>-3.7221</v>
       </c>
       <c r="K25" t="n">
         <v>-1.93924</v>
@@ -1560,7 +1560,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68686</v>
+        <v>-6.68672</v>
       </c>
       <c r="K26" t="n">
         <v>-1.50532</v>
@@ -1603,7 +1603,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29507</v>
+        <v>-7.29533</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1646,10 +1646,10 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.18887</v>
+        <v>-7.18811</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.46961</v>
+        <v>-0.45662</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.49579</v>
+        <v>-8.49593</v>
       </c>
       <c r="K29" t="n">
         <v>0.3143</v>
@@ -1732,10 +1732,10 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96439</v>
+        <v>-7.96447</v>
       </c>
       <c r="K30" t="n">
-        <v>0.62967</v>
+        <v>0.61656</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24745</v>
+        <v>-7.24768</v>
       </c>
       <c r="K31" t="n">
         <v>1.1193</v>
@@ -1818,7 +1818,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.5816</v>
+        <v>-7.58166</v>
       </c>
       <c r="K32" t="n">
         <v>1.33158</v>
@@ -1861,10 +1861,10 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.440099999999999</v>
+        <v>-8.44014</v>
       </c>
       <c r="K33" t="n">
-        <v>1.55796</v>
+        <v>1.54476</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.62422</v>
+        <v>-7.62433</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1947,7 +1947,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.89477</v>
+        <v>-5.8949</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1990,10 +1990,10 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24322</v>
+        <v>-7.24305</v>
       </c>
       <c r="K36" t="n">
-        <v>1.33316</v>
+        <v>1.34653</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.38131</v>
+        <v>-7.38125</v>
       </c>
       <c r="K37" t="n">
-        <v>1.04153</v>
+        <v>1.02835</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.30781</v>
+        <v>-3.30767</v>
       </c>
       <c r="K38" t="n">
         <v>0.59289</v>
@@ -2119,7 +2119,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.16373</v>
+        <v>-2.16399</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2162,7 +2162,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.56239</v>
+        <v>-1.56165</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2205,7 +2205,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.60228</v>
+        <v>-0.60247</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2248,10 +2248,10 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01636</v>
+        <v>-1.01648</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.09503</v>
+        <v>-1.08214</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.00361</v>
+        <v>-1.0039</v>
       </c>
       <c r="K43" t="n">
         <v>-1.06785</v>
@@ -2334,7 +2334,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.32015</v>
+        <v>1.32006</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2377,10 +2377,10 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68588</v>
+        <v>0.68581</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.26105</v>
+        <v>-1.24821</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35223</v>
+        <v>1.35214</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2463,10 +2463,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09793</v>
+        <v>1.09787</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.98817</v>
+        <v>-1.00117</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.6756</v>
+        <v>2.67589</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2549,10 +2549,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51899</v>
+        <v>2.51927</v>
       </c>
       <c r="K49" t="n">
-        <v>0.10438</v>
+        <v>0.11745</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.41031</v>
+        <v>1.41013</v>
       </c>
       <c r="K50" t="n">
-        <v>0.61559</v>
+        <v>0.60249</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.18329</v>
+        <v>0.18323</v>
       </c>
       <c r="K51" t="n">
-        <v>0.89215</v>
+        <v>0.87903</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.83586</v>
+        <v>-0.83546</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2721,7 +2721,7 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6408700000000001</v>
+        <v>-0.6409899999999999</v>
       </c>
       <c r="K53" t="n">
         <v>0.84188</v>
@@ -2764,7 +2764,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46422</v>
+        <v>-0.46431</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2807,7 +2807,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.2576</v>
+        <v>-1.25783</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2850,7 +2850,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05585</v>
+        <v>-2.05592</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2893,7 +2893,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.07042</v>
+        <v>-0.07045</v>
       </c>
       <c r="K57" t="n">
         <v>0.30283</v>
@@ -2939,7 +2939,7 @@
         <v>-0.9904500000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>0.26302</v>
+        <v>0.24987</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11234</v>
+        <v>-2.11228</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3022,10 +3022,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08805</v>
+        <v>-1.08791</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.28781</v>
+        <v>-0.30089</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03275</v>
+        <v>-1.03248</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.56048</v>
+        <v>-0.57351</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.74471</v>
+        <v>-0.7448399999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.80708</v>
+        <v>-0.80719</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.2471</v>
+        <v>1.24703</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.76723</v>
+        <v>-0.76733</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.93804</v>
+        <v>1.93801</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.72118</v>
+        <v>0.72115</v>
       </c>
       <c r="K65" t="n">
         <v>-0.28698</v>
@@ -3280,7 +3280,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.0878</v>
+        <v>1.08774</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.17111</v>
+        <v>2.17106</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3366,7 +3366,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45751</v>
+        <v>2.45746</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3409,7 +3409,7 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.30566</v>
+        <v>2.30562</v>
       </c>
       <c r="K69" t="n">
         <v>1.11578</v>
@@ -3452,10 +3452,10 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95779</v>
+        <v>2.95784</v>
       </c>
       <c r="K70" t="n">
-        <v>1.12802</v>
+        <v>1.12816</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.13813</v>
+        <v>3.1382</v>
       </c>
       <c r="K71" t="n">
-        <v>1.14263</v>
+        <v>1.15592</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3538,10 +3538,10 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.07499</v>
+        <v>2.07512</v>
       </c>
       <c r="K72" t="n">
-        <v>0.90527</v>
+        <v>0.91851</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3581,10 +3581,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.72548</v>
+        <v>3.72578</v>
       </c>
       <c r="K73" t="n">
-        <v>0.94377</v>
+        <v>0.957</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.27738</v>
+        <v>3.27721</v>
       </c>
       <c r="K74" t="n">
-        <v>0.95801</v>
+        <v>0.95813</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52746</v>
+        <v>1.52735</v>
       </c>
       <c r="K75" t="n">
-        <v>0.91731</v>
+        <v>0.93054</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.24683</v>
+        <v>1.24677</v>
       </c>
       <c r="K76" t="n">
         <v>0.94253</v>
@@ -3753,7 +3753,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.24298</v>
+        <v>1.24293</v>
       </c>
       <c r="K77" t="n">
         <v>0.98116</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03912</v>
+        <v>-0.03916</v>
       </c>
       <c r="K78" t="n">
         <v>1.20199</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.36338</v>
+        <v>-1.36339</v>
       </c>
       <c r="K79" t="n">
         <v>1.22683</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.24423</v>
+        <v>-1.24424</v>
       </c>
       <c r="K80" t="n">
         <v>0.93592</v>
@@ -3925,10 +3925,10 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.38608</v>
+        <v>-1.3861</v>
       </c>
       <c r="K81" t="n">
-        <v>1.20732</v>
+        <v>1.19434</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.8118</v>
+        <v>-1.81176</v>
       </c>
       <c r="K82" t="n">
-        <v>1.45266</v>
+        <v>1.45285</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15059</v>
+        <v>-1.15054</v>
       </c>
       <c r="K83" t="n">
-        <v>1.72705</v>
+        <v>1.71406</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.29216</v>
+        <v>-1.2921</v>
       </c>
       <c r="K84" t="n">
         <v>2.22338</v>
@@ -4097,10 +4097,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01288</v>
+        <v>-2.01275</v>
       </c>
       <c r="K85" t="n">
-        <v>2.23348</v>
+        <v>2.22049</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>-1.71983</v>
       </c>
       <c r="K86" t="n">
-        <v>2.46978</v>
+        <v>2.4701</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27068</v>
+        <v>-1.27078</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4226,10 +4226,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.97194</v>
+        <v>-0.97201</v>
       </c>
       <c r="K88" t="n">
-        <v>2.46401</v>
+        <v>2.45104</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.57021</v>
+        <v>-0.5702199999999999</v>
       </c>
       <c r="K89" t="n">
         <v>2.48737</v>
@@ -4312,10 +4312,10 @@
         <v>-0.73746</v>
       </c>
       <c r="J90" t="n">
-        <v>0.17421</v>
+        <v>0.1742</v>
       </c>
       <c r="K90" t="n">
-        <v>2.02685</v>
+        <v>2.01394</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J91" t="n">
-        <v>0.38878</v>
+        <v>0.38877</v>
       </c>
       <c r="K91" t="n">
         <v>1.97267</v>
@@ -4398,7 +4398,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.22581</v>
+        <v>-0.22582</v>
       </c>
       <c r="K92" t="n">
         <v>1.75145</v>
@@ -4441,10 +4441,10 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.93906</v>
       </c>
       <c r="K93" t="n">
-        <v>1.47512</v>
+        <v>1.48813</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4484,10 +4484,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.3879</v>
+        <v>-1.38794</v>
       </c>
       <c r="K94" t="n">
-        <v>1.25288</v>
+        <v>1.26582</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.02748</v>
+        <v>-2.0274</v>
       </c>
       <c r="K95" t="n">
-        <v>1.1999</v>
+        <v>1.21282</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.27398</v>
+        <v>-1.2739</v>
       </c>
       <c r="K96" t="n">
-        <v>1.22106</v>
+        <v>1.20834</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95338</v>
+        <v>-1.95333</v>
       </c>
       <c r="K97" t="n">
-        <v>1.46069</v>
+        <v>1.47358</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.95983</v>
+        <v>-1.9598</v>
       </c>
       <c r="K98" t="n">
-        <v>1.67449</v>
+        <v>1.68739</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.02135</v>
+        <v>-2.0214</v>
       </c>
       <c r="K99" t="n">
-        <v>1.97694</v>
+        <v>1.96426</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4742,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.2275</v>
+        <v>-2.22754</v>
       </c>
       <c r="K100" t="n">
-        <v>2.25288</v>
+        <v>2.26582</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4828,10 +4828,10 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.13134</v>
+        <v>-1.13135</v>
       </c>
       <c r="K102" t="n">
-        <v>2.79641</v>
+        <v>2.80942</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.70105</v>
+        <v>-0.70106</v>
       </c>
       <c r="K103" t="n">
         <v>3.13567</v>
@@ -4914,10 +4914,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.63677</v>
+        <v>-1.63679</v>
       </c>
       <c r="K104" t="n">
-        <v>3.41729</v>
+        <v>3.40463</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.31027</v>
+        <v>-1.31031</v>
       </c>
       <c r="K105" t="n">
         <v>3.72898</v>
@@ -5000,7 +5000,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.71536</v>
+        <v>-1.71542</v>
       </c>
       <c r="K106" t="n">
         <v>4.01515</v>
@@ -5043,7 +5043,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61221</v>
+        <v>0.61228</v>
       </c>
       <c r="K107" t="n">
         <v>4.36428</v>
@@ -5086,10 +5086,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.6503</v>
+        <v>1.65035</v>
       </c>
       <c r="K108" t="n">
-        <v>4.38552</v>
+        <v>4.39864</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32905</v>
+        <v>2.3291</v>
       </c>
       <c r="K109" t="n">
         <v>4.68202</v>
@@ -5172,7 +5172,7 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.6664099999999999</v>
+        <v>0.66645</v>
       </c>
       <c r="K110" t="n">
         <v>4.75359</v>
@@ -5215,10 +5215,10 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.90567</v>
+        <v>0.90563</v>
       </c>
       <c r="K111" t="n">
-        <v>4.511</v>
+        <v>4.52399</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.75485</v>
+        <v>1.75482</v>
       </c>
       <c r="K112" t="n">
         <v>4.53026</v>
@@ -5301,7 +5301,7 @@
         <v>0.29718</v>
       </c>
       <c r="J113" t="n">
-        <v>2.68801</v>
+        <v>2.68802</v>
       </c>
       <c r="K113" t="n">
         <v>4.5595</v>
@@ -5344,7 +5344,7 @@
         <v>0.14859</v>
       </c>
       <c r="J114" t="n">
-        <v>2.87432</v>
+        <v>2.87431</v>
       </c>
       <c r="K114" t="n">
         <v>4.56672</v>
@@ -5387,7 +5387,7 @@
         <v>-0.14837</v>
       </c>
       <c r="J115" t="n">
-        <v>3.30693</v>
+        <v>3.30692</v>
       </c>
       <c r="K115" t="n">
         <v>4.36435</v>
@@ -5430,10 +5430,10 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.93853</v>
+        <v>3.93852</v>
       </c>
       <c r="K116" t="n">
-        <v>4.57716</v>
+        <v>4.58996</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.90911</v>
+        <v>3.90908</v>
       </c>
       <c r="K117" t="n">
         <v>4.53327</v>
@@ -5516,10 +5516,10 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.25938</v>
+        <v>5.25932</v>
       </c>
       <c r="K118" t="n">
-        <v>4.34571</v>
+        <v>4.33358</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.59819</v>
+        <v>3.59825</v>
       </c>
       <c r="K119" t="n">
         <v>4.27846</v>
@@ -5602,7 +5602,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.88625</v>
+        <v>1.8863</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5645,7 +5645,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.4736</v>
+        <v>1.47363</v>
       </c>
       <c r="K121" t="n">
         <v>3.50395</v>
@@ -5734,7 +5734,7 @@
         <v>3.28843</v>
       </c>
       <c r="K123" t="n">
-        <v>2.90131</v>
+        <v>2.88942</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>-0.29586</v>
       </c>
       <c r="J124" t="n">
-        <v>2.21633</v>
+        <v>2.21631</v>
       </c>
       <c r="K124" t="n">
         <v>2.38011</v>
@@ -5817,7 +5817,7 @@
         <v>-0.2963</v>
       </c>
       <c r="J125" t="n">
-        <v>0.8649</v>
+        <v>0.86489</v>
       </c>
       <c r="K125" t="n">
         <v>2.26897</v>
@@ -5860,7 +5860,7 @@
         <v>-0.14837</v>
       </c>
       <c r="J126" t="n">
-        <v>0.27475</v>
+        <v>0.27474</v>
       </c>
       <c r="K126" t="n">
         <v>1.95409</v>
@@ -5946,7 +5946,7 @@
         <v>-0.14881</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.16223</v>
+        <v>-0.16224</v>
       </c>
       <c r="K128" t="n">
         <v>1.65009</v>
@@ -5989,7 +5989,7 @@
         <v>-0.14903</v>
       </c>
       <c r="J129" t="n">
-        <v>0.60939</v>
+        <v>0.60938</v>
       </c>
       <c r="K129" t="n">
         <v>1.14246</v>
@@ -6035,7 +6035,7 @@
         <v>0.37904</v>
       </c>
       <c r="K130" t="n">
-        <v>0.8027</v>
+        <v>0.81443</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>-0.29806</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.44729</v>
+        <v>-6.44727</v>
       </c>
       <c r="K131" t="n">
         <v>0.37089</v>
@@ -6118,7 +6118,7 @@
         <v>-0.59613</v>
       </c>
       <c r="J132" t="n">
-        <v>-7.12007</v>
+        <v>-7.12005</v>
       </c>
       <c r="K132" t="n">
         <v>0.02314</v>
@@ -6161,7 +6161,7 @@
         <v>-0.89286</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.8633</v>
+        <v>-7.86328</v>
       </c>
       <c r="K133" t="n">
         <v>-0.05777</v>
@@ -6250,7 +6250,7 @@
         <v>-7.84518</v>
       </c>
       <c r="K135" t="n">
-        <v>0.51999</v>
+        <v>0.53161</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>-1.93165</v>
       </c>
       <c r="J137" t="n">
-        <v>-6.829</v>
+        <v>-6.82901</v>
       </c>
       <c r="K137" t="n">
         <v>1.2942</v>
@@ -6422,7 +6422,7 @@
         <v>-5.48699</v>
       </c>
       <c r="K139" t="n">
-        <v>2.04011</v>
+        <v>2.02858</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>-1.9403</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.4778</v>
+        <v>-5.47781</v>
       </c>
       <c r="K142" t="n">
         <v>2.82747</v>
@@ -6634,7 +6634,7 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.45738</v>
+        <v>1.45736</v>
       </c>
       <c r="K144" t="n">
         <v>3.63258</v>
@@ -6677,7 +6677,7 @@
         <v>-1.65165</v>
       </c>
       <c r="J145" t="n">
-        <v>2.53959</v>
+        <v>2.53957</v>
       </c>
       <c r="K145" t="n">
         <v>4</v>
@@ -6720,10 +6720,10 @@
         <v>-1.35542</v>
       </c>
       <c r="J146" t="n">
-        <v>3.67652</v>
+        <v>3.67651</v>
       </c>
       <c r="K146" t="n">
-        <v>3.76511</v>
+        <v>3.7536</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>-1.20664</v>
       </c>
       <c r="J147" t="n">
-        <v>3.14865</v>
+        <v>3.14864</v>
       </c>
       <c r="K147" t="n">
         <v>3.73606</v>
@@ -6806,7 +6806,7 @@
         <v>-0.75643</v>
       </c>
       <c r="J148" t="n">
-        <v>2.77778</v>
+        <v>2.77777</v>
       </c>
       <c r="K148" t="n">
         <v>3.1826</v>
@@ -6849,7 +6849,7 @@
         <v>-0.45455</v>
       </c>
       <c r="J149" t="n">
-        <v>2.01723</v>
+        <v>2.01722</v>
       </c>
       <c r="K149" t="n">
         <v>2.64659</v>
@@ -6892,10 +6892,10 @@
         <v>-0.30349</v>
       </c>
       <c r="J150" t="n">
-        <v>1.69822</v>
+        <v>1.69823</v>
       </c>
       <c r="K150" t="n">
-        <v>2.0663</v>
+        <v>2.05495</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         <v>-0.30349</v>
       </c>
       <c r="J151" t="n">
-        <v>0.24066</v>
+        <v>0.24068</v>
       </c>
       <c r="K151" t="n">
-        <v>1.67175</v>
+        <v>1.68324</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.63305</v>
+        <v>0.63307</v>
       </c>
       <c r="K152" t="n">
-        <v>1.48951</v>
+        <v>1.47822</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>0.9598100000000001</v>
+        <v>0.95986</v>
       </c>
       <c r="K153" t="n">
         <v>1.21417</v>
@@ -7064,7 +7064,7 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.1216</v>
+        <v>1.12166</v>
       </c>
       <c r="K154" t="n">
         <v>1.42536</v>
@@ -7107,10 +7107,10 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.58983</v>
+        <v>2.58975</v>
       </c>
       <c r="K155" t="n">
-        <v>1.46451</v>
+        <v>1.45333</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.93557</v>
+        <v>1.93552</v>
       </c>
       <c r="K156" t="n">
         <v>1.45122</v>
@@ -7193,7 +7193,7 @@
         <v>-0.30534</v>
       </c>
       <c r="J157" t="n">
-        <v>2.43277</v>
+        <v>2.43276</v>
       </c>
       <c r="K157" t="n">
         <v>1.44509</v>
@@ -7236,10 +7236,10 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.34564</v>
+        <v>1.34562</v>
       </c>
       <c r="K158" t="n">
-        <v>1.69774</v>
+        <v>1.70902</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.65367</v>
+        <v>1.65366</v>
       </c>
       <c r="K159" t="n">
         <v>1.97252</v>
@@ -7408,10 +7408,10 @@
         <v>-1.21766</v>
       </c>
       <c r="J162" t="n">
-        <v>3.24552</v>
+        <v>3.24553</v>
       </c>
       <c r="K162" t="n">
-        <v>3.6485</v>
+        <v>3.6489</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J163" t="n">
-        <v>4.06</v>
+        <v>4.06002</v>
       </c>
       <c r="K163" t="n">
         <v>3.95512</v>
@@ -7494,10 +7494,10 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.68896</v>
+        <v>3.68899</v>
       </c>
       <c r="K164" t="n">
-        <v>4.24728</v>
+        <v>4.25887</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.90109</v>
+        <v>2.90114</v>
       </c>
       <c r="K165" t="n">
-        <v>4.29857</v>
+        <v>4.28746</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53596</v>
+        <v>2.53602</v>
       </c>
       <c r="K166" t="n">
         <v>4.07215</v>
@@ -7623,10 +7623,10 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.64588</v>
+        <v>3.64581</v>
       </c>
       <c r="K167" t="n">
-        <v>3.82327</v>
+        <v>3.83471</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.48912</v>
+        <v>3.48906</v>
       </c>
       <c r="K168" t="n">
         <v>4.12632</v>
@@ -7709,7 +7709,7 @@
         <v>-0.30628</v>
       </c>
       <c r="J169" t="n">
-        <v>2.889</v>
+        <v>2.88899</v>
       </c>
       <c r="K169" t="n">
         <v>3.8352</v>
@@ -7752,7 +7752,7 @@
         <v>-0.15337</v>
       </c>
       <c r="J170" t="n">
-        <v>2.85953</v>
+        <v>2.85951</v>
       </c>
       <c r="K170" t="n">
         <v>3.55701</v>
@@ -7795,7 +7795,7 @@
         <v>0.15361</v>
       </c>
       <c r="J171" t="n">
-        <v>2.90367</v>
+        <v>2.90365</v>
       </c>
       <c r="K171" t="n">
         <v>3.53184</v>
@@ -7924,10 +7924,10 @@
         <v>1.07858</v>
       </c>
       <c r="J174" t="n">
-        <v>2.57144</v>
+        <v>2.57146</v>
       </c>
       <c r="K174" t="n">
-        <v>3.30543</v>
+        <v>3.30579</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>1.23267</v>
       </c>
       <c r="J175" t="n">
-        <v>2.85247</v>
+        <v>2.85248</v>
       </c>
       <c r="K175" t="n">
         <v>3.03516</v>
@@ -8010,7 +8010,7 @@
         <v>1.54321</v>
       </c>
       <c r="J176" t="n">
-        <v>2.54939</v>
+        <v>2.54942</v>
       </c>
       <c r="K176" t="n">
         <v>3.00768</v>
@@ -8053,10 +8053,10 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.89893</v>
+        <v>2.89897</v>
       </c>
       <c r="K177" t="n">
-        <v>3.03514</v>
+        <v>3.04612</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.8442</v>
+        <v>3.84427</v>
       </c>
       <c r="K178" t="n">
         <v>2.99841</v>
@@ -8139,7 +8139,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.50148</v>
+        <v>2.50142</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8182,7 +8182,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78988</v>
+        <v>1.78983</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8268,7 +8268,7 @@
         <v>1.07527</v>
       </c>
       <c r="J182" t="n">
-        <v>1.44836</v>
+        <v>1.44835</v>
       </c>
       <c r="K182" t="n">
         <v>2.89748</v>
@@ -8311,7 +8311,7 @@
         <v>0.92025</v>
       </c>
       <c r="J183" t="n">
-        <v>1.73084</v>
+        <v>1.73083</v>
       </c>
       <c r="K183" t="n">
         <v>2.6871</v>
@@ -8397,7 +8397,7 @@
         <v>0.6116200000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>1.47007</v>
+        <v>1.47008</v>
       </c>
       <c r="K185" t="n">
         <v>1.88385</v>
@@ -8440,10 +8440,10 @@
         <v>0.30488</v>
       </c>
       <c r="J186" t="n">
-        <v>1.51105</v>
+        <v>1.51106</v>
       </c>
       <c r="K186" t="n">
-        <v>1.83877</v>
+        <v>1.84935</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>0.30441</v>
       </c>
       <c r="J187" t="n">
-        <v>1.01777</v>
+        <v>1.01778</v>
       </c>
       <c r="K187" t="n">
         <v>2.09522</v>
@@ -8526,7 +8526,7 @@
         <v>0.15198</v>
       </c>
       <c r="J188" t="n">
-        <v>1.00864</v>
+        <v>1.00865</v>
       </c>
       <c r="K188" t="n">
         <v>2.29861</v>
@@ -8569,7 +8569,7 @@
         <v>-0.15152</v>
       </c>
       <c r="J189" t="n">
-        <v>1.05815</v>
+        <v>1.05816</v>
       </c>
       <c r="K189" t="n">
         <v>2.56331</v>
@@ -8655,7 +8655,7 @@
         <v>0.15175</v>
       </c>
       <c r="J191" t="n">
-        <v>0.89528</v>
+        <v>0.89527</v>
       </c>
       <c r="K191" t="n">
         <v>3.06186</v>
@@ -8698,7 +8698,7 @@
         <v>0.15175</v>
       </c>
       <c r="J192" t="n">
-        <v>1.49478</v>
+        <v>1.49477</v>
       </c>
       <c r="K192" t="n">
         <v>3.16201</v>
@@ -8741,7 +8741,7 @@
         <v>0.30395</v>
       </c>
       <c r="J193" t="n">
-        <v>1.29025</v>
+        <v>1.29023</v>
       </c>
       <c r="K193" t="n">
         <v>2.85041</v>
@@ -8784,7 +8784,7 @@
         <v>0.30395</v>
       </c>
       <c r="J194" t="n">
-        <v>1.42028</v>
+        <v>1.42027</v>
       </c>
       <c r="K194" t="n">
         <v>2.60086</v>
@@ -8999,7 +8999,7 @@
         <v>-0.75873</v>
       </c>
       <c r="J199" t="n">
-        <v>1.03614</v>
+        <v>1.03615</v>
       </c>
       <c r="K199" t="n">
         <v>1.69664</v>
@@ -9042,7 +9042,7 @@
         <v>-1.06222</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.23673</v>
+        <v>-0.23672</v>
       </c>
       <c r="K200" t="n">
         <v>1.38664</v>
@@ -9085,7 +9085,7 @@
         <v>-1.06222</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.20489</v>
+        <v>-0.20488</v>
       </c>
       <c r="K201" t="n">
         <v>0.80621</v>
@@ -9647,7 +9647,7 @@
         <v>-5.03658</v>
       </c>
       <c r="K214" t="n">
-        <v>-3.16253</v>
+        <v>-3.15252</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -10160,10 +10160,10 @@
         <v>-2.29709</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.15032</v>
+        <v>-6.15033</v>
       </c>
       <c r="K226" t="n">
-        <v>-4.60934</v>
+        <v>-4.6192</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>-1.70543</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.39894</v>
+        <v>-4.39893</v>
       </c>
       <c r="K230" t="n">
         <v>-1.64841</v>
@@ -10590,7 +10590,7 @@
         <v>-1.25</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.42158</v>
+        <v>-1.42159</v>
       </c>
       <c r="K236" t="n">
         <v>1.34185</v>
@@ -10633,7 +10633,7 @@
         <v>-1.25196</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.25725</v>
+        <v>-0.25726</v>
       </c>
       <c r="K237" t="n">
         <v>1.60399</v>
@@ -10719,7 +10719,7 @@
         <v>-0.78616</v>
       </c>
       <c r="J239" t="n">
-        <v>1.33084</v>
+        <v>1.33085</v>
       </c>
       <c r="K239" t="n">
         <v>1.48268</v>
@@ -10824,10 +10824,10 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66413553932171</v>
+        <v>11.68911330649644</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37914394126496</v>
+        <v>11.37937307453389</v>
       </c>
       <c r="D242" t="n">
         <v>10.14543498162801</v>
@@ -10848,7 +10848,7 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30198</v>
+        <v>2.30201</v>
       </c>
       <c r="K242" t="n">
         <v>2.02206</v>
@@ -10867,10 +10867,10 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.2569394762043</v>
+        <v>12.27654650609951</v>
       </c>
       <c r="C243" t="n">
-        <v>12.44335026147107</v>
+        <v>12.44398934109574</v>
       </c>
       <c r="D243" t="n">
         <v>7.820798380506711</v>
@@ -10910,10 +10910,10 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.9866593851134</v>
+        <v>3.977875906744632</v>
       </c>
       <c r="C244" t="n">
-        <v>7.190150230366599</v>
+        <v>7.189460065581077</v>
       </c>
       <c r="D244" t="n">
         <v>6.051273333379537</v>
@@ -10953,10 +10953,10 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.848930119482086</v>
+        <v>3.844599589489639</v>
       </c>
       <c r="C245" t="n">
-        <v>7.420865127108267</v>
+        <v>7.420828697506776</v>
       </c>
       <c r="D245" t="n">
         <v>4.806639006996449</v>
@@ -10977,10 +10977,10 @@
         <v>-0.47244</v>
       </c>
       <c r="J245" t="n">
-        <v>2.90206</v>
+        <v>2.90205</v>
       </c>
       <c r="K245" t="n">
-        <v>1.87077</v>
+        <v>1.88152</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -10996,10 +10996,10 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1919509790099472</v>
+        <v>0.174418257055553</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6887887861535935</v>
+        <v>-0.690099596383642</v>
       </c>
       <c r="D246" t="n">
         <v>1.811413989725974</v>
@@ -11039,10 +11039,10 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3239377211504246</v>
+        <v>-0.3590411891583267</v>
       </c>
       <c r="C247" t="n">
-        <v>2.262178221868605</v>
+        <v>2.261827670306493</v>
       </c>
       <c r="D247" t="n">
         <v>-1.62500891141667</v>
@@ -11063,7 +11063,7 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46116</v>
+        <v>3.46114</v>
       </c>
       <c r="K247" t="n">
         <v>1.05894</v>
@@ -11082,10 +11082,10 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.542122859692419</v>
+        <v>-1.558968536427696</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.326073188073685</v>
+        <v>-2.326599870244672</v>
       </c>
       <c r="D248" t="n">
         <v>-3.091911712012352</v>
@@ -11106,7 +11106,7 @@
         <v>-0.31646</v>
       </c>
       <c r="J248" t="n">
-        <v>3.43722</v>
+        <v>3.4372</v>
       </c>
       <c r="K248" t="n">
         <v>1.05713</v>
@@ -11125,10 +11125,10 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.448462816206386</v>
+        <v>1.451543310516401</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2359824402951127</v>
+        <v>-0.2370429305133648</v>
       </c>
       <c r="D249" t="n">
         <v>2.500126526245938</v>
@@ -11149,10 +11149,10 @@
         <v>-0.31696</v>
       </c>
       <c r="J249" t="n">
-        <v>4.28998</v>
+        <v>4.28997</v>
       </c>
       <c r="K249" t="n">
-        <v>0.81067</v>
+        <v>0.82133</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11168,10 +11168,10 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.817578895554142</v>
+        <v>4.833632113260689</v>
       </c>
       <c r="C250" t="n">
-        <v>4.677159702935918</v>
+        <v>4.676824619482112</v>
       </c>
       <c r="D250" t="n">
         <v>6.342706597823766</v>
@@ -11192,7 +11192,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36587</v>
+        <v>5.36586</v>
       </c>
       <c r="K250" t="n">
         <v>1.10007</v>
@@ -11211,10 +11211,10 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8296802119459823</v>
+        <v>0.836814420640275</v>
       </c>
       <c r="C251" t="n">
-        <v>1.476557181038896</v>
+        <v>1.476043369311753</v>
       </c>
       <c r="D251" t="n">
         <v>2.657911122927659</v>
@@ -11235,7 +11235,7 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.6915</v>
+        <v>4.69154</v>
       </c>
       <c r="K251" t="n">
         <v>1.33305</v>
@@ -11254,10 +11254,10 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.658830351177</v>
+        <v>3.655411175645695</v>
       </c>
       <c r="C252" t="n">
-        <v>2.984687160875898</v>
+        <v>2.983273299164213</v>
       </c>
       <c r="D252" t="n">
         <v>3.945867355537014</v>
@@ -11278,7 +11278,7 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.78751</v>
+        <v>4.78753</v>
       </c>
       <c r="K252" t="n">
         <v>1.53273</v>
@@ -11297,10 +11297,10 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.116055336712956</v>
+        <v>7.12410902743903</v>
       </c>
       <c r="C253" t="n">
-        <v>8.441868042944778</v>
+        <v>8.441800707981638</v>
       </c>
       <c r="D253" t="n">
         <v>3.63063193221731</v>
@@ -11321,7 +11321,7 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94873</v>
+        <v>4.94874</v>
       </c>
       <c r="K253" t="n">
         <v>2.11657</v>
@@ -11340,10 +11340,10 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.365281359156817</v>
+        <v>7.374043821481857</v>
       </c>
       <c r="C254" t="n">
-        <v>7.323731207142203</v>
+        <v>7.324410676291282</v>
       </c>
       <c r="D254" t="n">
         <v>5.753737798037961</v>
@@ -11364,7 +11364,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.60819</v>
+        <v>5.60823</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11383,10 +11383,10 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.447577284141514</v>
+        <v>5.449987618814034</v>
       </c>
       <c r="C255" t="n">
-        <v>5.902186079304306</v>
+        <v>5.902285441346011</v>
       </c>
       <c r="D255" t="n">
         <v>2.5496167573414</v>
@@ -11426,10 +11426,10 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.69267939491252</v>
+        <v>11.70562412902412</v>
       </c>
       <c r="C256" t="n">
-        <v>9.870047871704358</v>
+        <v>9.870408179800783</v>
       </c>
       <c r="D256" t="n">
         <v>5.668221117197425</v>
@@ -11469,10 +11469,10 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.783692609095217</v>
+        <v>8.775738786770294</v>
       </c>
       <c r="C257" t="n">
-        <v>8.536753864101332</v>
+        <v>8.537647421051918</v>
       </c>
       <c r="D257" t="n">
         <v>5.103875682899162</v>
@@ -11493,10 +11493,10 @@
         <v>-2.8481</v>
       </c>
       <c r="J257" t="n">
-        <v>6.14195</v>
+        <v>6.14194</v>
       </c>
       <c r="K257" t="n">
-        <v>2.76517</v>
+        <v>2.75433</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11512,10 +11512,10 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92274785361991</v>
+        <v>11.92080083298512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74421204781149</v>
+        <v>11.74548844153562</v>
       </c>
       <c r="D258" t="n">
         <v>8.78628225027307</v>
@@ -11536,7 +11536,7 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59275</v>
+        <v>6.59274</v>
       </c>
       <c r="K258" t="n">
         <v>3.32875</v>
@@ -11555,10 +11555,10 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.44870823188746</v>
+        <v>11.45462942192885</v>
       </c>
       <c r="C259" t="n">
-        <v>9.113169505109964</v>
+        <v>9.113716765363321</v>
       </c>
       <c r="D259" t="n">
         <v>7.833268737162702</v>
@@ -11579,10 +11579,10 @@
         <v>-3.01109</v>
       </c>
       <c r="J259" t="n">
-        <v>6.62995</v>
+        <v>6.62992</v>
       </c>
       <c r="K259" t="n">
-        <v>3.91617</v>
+        <v>3.92676</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11598,10 +11598,10 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.849816587340097</v>
+        <v>8.842333246179933</v>
       </c>
       <c r="C260" t="n">
-        <v>9.290438988105354</v>
+        <v>9.291681922094174</v>
       </c>
       <c r="D260" t="n">
         <v>8.068875265934516</v>
@@ -11622,7 +11622,7 @@
         <v>-3.01587</v>
       </c>
       <c r="J260" t="n">
-        <v>6.90737</v>
+        <v>6.90734</v>
       </c>
       <c r="K260" t="n">
         <v>4.4273</v>
@@ -11641,10 +11641,10 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52773476709823</v>
+        <v>12.52692880096462</v>
       </c>
       <c r="C261" t="n">
-        <v>10.29754595037129</v>
+        <v>10.29897066398668</v>
       </c>
       <c r="D261" t="n">
         <v>5.621509916156309</v>
@@ -11665,10 +11665,10 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46892</v>
+        <v>5.46888</v>
       </c>
       <c r="K261" t="n">
-        <v>5.35393</v>
+        <v>5.34278</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11684,10 +11684,10 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.800382439092068</v>
+        <v>6.794376136294922</v>
       </c>
       <c r="C262" t="n">
-        <v>6.4926719287004</v>
+        <v>6.491845963722187</v>
       </c>
       <c r="D262" t="n">
         <v>-0.8224428994861976</v>
@@ -11708,7 +11708,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06068</v>
+        <v>4.06064</v>
       </c>
       <c r="K262" t="n">
         <v>5.81027</v>
@@ -11727,10 +11727,10 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.094036128113414</v>
+        <v>9.093636916397617</v>
       </c>
       <c r="C263" t="n">
-        <v>7.445818589214914</v>
+        <v>7.446232128706032</v>
       </c>
       <c r="D263" t="n">
         <v>3.149496711978794</v>
@@ -11751,7 +11751,7 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.98664</v>
+        <v>3.98677</v>
       </c>
       <c r="K263" t="n">
         <v>5.86192</v>
@@ -11770,10 +11770,10 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.4087559507174</v>
+        <v>13.42229760293836</v>
       </c>
       <c r="C264" t="n">
-        <v>11.22472825134666</v>
+        <v>11.22794659482602</v>
       </c>
       <c r="D264" t="n">
         <v>4.656561367290268</v>
@@ -11794,7 +11794,7 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.80942</v>
+        <v>3.80943</v>
       </c>
       <c r="K264" t="n">
         <v>5.94402</v>
@@ -11813,10 +11813,10 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.051695911066915</v>
+        <v>8.054015075647136</v>
       </c>
       <c r="C265" t="n">
-        <v>5.781747539655746</v>
+        <v>5.782162287273795</v>
       </c>
       <c r="D265" t="n">
         <v>2.715952801444366</v>
@@ -11837,7 +11837,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70184</v>
+        <v>3.70186</v>
       </c>
       <c r="K265" t="n">
         <v>5.63483</v>
@@ -11856,10 +11856,10 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.583091463254239</v>
+        <v>2.580064370440938</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.1912854155142973</v>
+        <v>-0.193199008265299</v>
       </c>
       <c r="D266" t="n">
         <v>2.196002033035582</v>
@@ -11880,10 +11880,10 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87385</v>
+        <v>2.87391</v>
       </c>
       <c r="K266" t="n">
-        <v>5.62941</v>
+        <v>5.6398</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11899,10 +11899,10 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.105348164337498</v>
+        <v>5.100192370174628</v>
       </c>
       <c r="C267" t="n">
-        <v>1.665301515181095</v>
+        <v>1.665188106374371</v>
       </c>
       <c r="D267" t="n">
         <v>3.454390362819426</v>
@@ -11923,7 +11923,7 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68867</v>
+        <v>2.68869</v>
       </c>
       <c r="K267" t="n">
         <v>5.62042</v>
@@ -11942,10 +11942,10 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.822207641870669</v>
+        <v>5.828987054342027</v>
       </c>
       <c r="C268" t="n">
-        <v>3.406175016407964</v>
+        <v>3.406459149236429</v>
       </c>
       <c r="D268" t="n">
         <v>0.9116235281249274</v>
@@ -11985,10 +11985,10 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.38548659477269</v>
+        <v>2.375757299990089</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7192327276471344</v>
+        <v>0.7181679971187238</v>
       </c>
       <c r="D269" t="n">
         <v>2.950804489409142</v>
@@ -12009,7 +12009,7 @@
         <v>-1.30293</v>
       </c>
       <c r="J269" t="n">
-        <v>2.61295</v>
+        <v>2.61293</v>
       </c>
       <c r="K269" t="n">
         <v>5.82315</v>
@@ -12028,10 +12028,10 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.699563854840092</v>
+        <v>2.699686467660989</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3550156735170562</v>
+        <v>0.3531951763503294</v>
       </c>
       <c r="D270" t="n">
         <v>-1.516121644751112</v>
@@ -12052,7 +12052,7 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24409</v>
+        <v>2.24406</v>
       </c>
       <c r="K270" t="n">
         <v>5.58396</v>
@@ -12071,10 +12071,10 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.106185234372228</v>
+        <v>4.117917337361399</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272514010274419</v>
+        <v>3.272528868167313</v>
       </c>
       <c r="D271" t="n">
         <v>-1.168113995728171</v>
@@ -12095,10 +12095,10 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.02556</v>
+        <v>2.02544</v>
       </c>
       <c r="K271" t="n">
-        <v>5.55103</v>
+        <v>5.54028</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12114,10 +12114,10 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.803456541528671</v>
+        <v>3.808453791943722</v>
       </c>
       <c r="C272" t="n">
-        <v>2.824453481162514</v>
+        <v>2.825870227905769</v>
       </c>
       <c r="D272" t="n">
         <v>-2.928436964250214</v>
@@ -12138,7 +12138,7 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.06781</v>
+        <v>2.06774</v>
       </c>
       <c r="K272" t="n">
         <v>5.03896</v>
@@ -12157,10 +12157,10 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.04826928707269</v>
+        <v>2.044718954209523</v>
       </c>
       <c r="C273" t="n">
-        <v>2.703435563075951</v>
+        <v>2.703649900494898</v>
       </c>
       <c r="D273" t="n">
         <v>-0.1130744319375987</v>
@@ -12181,7 +12181,7 @@
         <v>-0.32787</v>
       </c>
       <c r="J273" t="n">
-        <v>2.87077</v>
+        <v>2.87071</v>
       </c>
       <c r="K273" t="n">
         <v>4.36879</v>
@@ -12200,10 +12200,10 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1396425969474535</v>
+        <v>-0.1455883840135286</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2207108557370496</v>
+        <v>0.2202494481804429</v>
       </c>
       <c r="D274" t="n">
         <v>0.0340605841581576</v>
@@ -12224,10 +12224,10 @@
         <v>-0.16393</v>
       </c>
       <c r="J274" t="n">
-        <v>2.13198</v>
+        <v>2.13197</v>
       </c>
       <c r="K274" t="n">
-        <v>3.65415</v>
+        <v>3.66414</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.320549796896541</v>
+        <v>-0.3202473682087592</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4724018215598424</v>
+        <v>-0.4730857855368975</v>
       </c>
       <c r="D275" t="n">
         <v>-2.020893191590689</v>
@@ -12267,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.59061</v>
+        <v>2.59078</v>
       </c>
       <c r="K275" t="n">
         <v>3.36017</v>
@@ -12286,10 +12286,10 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.988643543095716</v>
+        <v>-3.993504255110503</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.151047144450438</v>
+        <v>-4.153405723170822</v>
       </c>
       <c r="D276" t="n">
         <v>-3.716217027826829</v>
@@ -12310,7 +12310,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.64213</v>
+        <v>2.64218</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12329,10 +12329,10 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.35984222346859</v>
+        <v>-3.362988280493606</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.720858000324678</v>
+        <v>-3.722851010364647</v>
       </c>
       <c r="D277" t="n">
         <v>-3.388273857734614</v>
@@ -12353,7 +12353,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55371</v>
+        <v>2.55372</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12372,10 +12372,10 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.266182364072057</v>
+        <v>3.268459701625792</v>
       </c>
       <c r="C278" t="n">
-        <v>3.588312897247126</v>
+        <v>3.591360451323733</v>
       </c>
       <c r="D278" t="n">
         <v>-1.625798511291388</v>
@@ -12396,10 +12396,10 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57057</v>
+        <v>3.57081</v>
       </c>
       <c r="K278" t="n">
-        <v>2.89086</v>
+        <v>2.88074</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12415,10 +12415,10 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.119361217100411</v>
+        <v>-0.1241553659559136</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4794768917733672</v>
+        <v>0.4809295960262805</v>
       </c>
       <c r="D279" t="n">
         <v>-0.3376418332989517</v>
@@ -12439,7 +12439,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10631</v>
+        <v>3.10624</v>
       </c>
       <c r="K279" t="n">
         <v>2.73892</v>
@@ -12458,10 +12458,10 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.844672981215489</v>
+        <v>-1.847337030532969</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.142901592073687</v>
+        <v>-2.144570988208527</v>
       </c>
       <c r="D280" t="n">
         <v>-0.801070843838203</v>
@@ -12482,7 +12482,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13352</v>
+        <v>3.13348</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12501,10 +12501,10 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.175387328077627</v>
+        <v>2.170716230843128</v>
       </c>
       <c r="C281" t="n">
-        <v>1.841097754354393</v>
+        <v>1.841703542427497</v>
       </c>
       <c r="D281" t="n">
         <v>-3.091066331648129</v>
@@ -12525,10 +12525,10 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52939</v>
+        <v>2.52934</v>
       </c>
       <c r="K281" t="n">
-        <v>2.47477</v>
+        <v>2.48447</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12544,10 +12544,10 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.198063626895673</v>
+        <v>1.202603607217623</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625317647265567</v>
+        <v>1.624574625164343</v>
       </c>
       <c r="D282" t="n">
         <v>0.2886836619601985</v>
@@ -12568,10 +12568,10 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46755</v>
+        <v>2.46746</v>
       </c>
       <c r="K282" t="n">
-        <v>2.69275</v>
+        <v>2.70244</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12587,10 +12587,10 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.121732448148927</v>
+        <v>1.132212293371126</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5733067092592137</v>
+        <v>0.5723380683481327</v>
       </c>
       <c r="D283" t="n">
         <v>0.1559827866278729</v>
@@ -12611,7 +12611,7 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.70802</v>
+        <v>1.70785</v>
       </c>
       <c r="K283" t="n">
         <v>2.46068</v>
@@ -12630,10 +12630,10 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.532762581492931</v>
+        <v>2.540187229438318</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0527058516678669</v>
+        <v>-0.05273550615292333</v>
       </c>
       <c r="D284" t="n">
         <v>2.829248572920484</v>
@@ -12654,10 +12654,10 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26787</v>
+        <v>1.26774</v>
       </c>
       <c r="K284" t="n">
-        <v>2.66834</v>
+        <v>2.67797</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12673,10 +12673,10 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4717123205917106</v>
+        <v>0.4599139226774795</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7773819375735402</v>
+        <v>-0.7789085784740246</v>
       </c>
       <c r="D285" t="n">
         <v>-1.491988221217611</v>
@@ -12697,7 +12697,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.5518</v>
+        <v>0.55166</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12716,10 +12716,10 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.658864690669295</v>
+        <v>4.656541436156125</v>
       </c>
       <c r="C286" t="n">
-        <v>1.836134917285559</v>
+        <v>1.835510400393514</v>
       </c>
       <c r="D286" t="n">
         <v>2.955690723048998</v>
@@ -12740,10 +12740,10 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35733</v>
+        <v>1.35723</v>
       </c>
       <c r="K286" t="n">
-        <v>3.246</v>
+        <v>3.24569</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12759,10 +12759,10 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.816405112246281</v>
+        <v>5.821834185545716</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936288327568338</v>
+        <v>3.936547954010572</v>
       </c>
       <c r="D287" t="n">
         <v>4.871296070878484</v>
@@ -12783,10 +12783,10 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.27691</v>
+        <v>1.27739</v>
       </c>
       <c r="K287" t="n">
-        <v>3.50101</v>
+        <v>3.51063</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12802,10 +12802,10 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480733807609582</v>
+        <v>3.480227024225613</v>
       </c>
       <c r="C288" t="n">
-        <v>2.924189297711632</v>
+        <v>2.9252222228352</v>
       </c>
       <c r="D288" t="n">
         <v>2.109403820450528</v>
@@ -12826,7 +12826,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.52999</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12845,10 +12845,10 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.842979004964489</v>
+        <v>6.848012322360719</v>
       </c>
       <c r="C289" t="n">
-        <v>5.981600899687334</v>
+        <v>5.982507466958076</v>
       </c>
       <c r="D289" t="n">
         <v>2.234870657038535</v>
@@ -12869,10 +12869,10 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27377</v>
+        <v>-0.27373</v>
       </c>
       <c r="K289" t="n">
-        <v>3.50206</v>
+        <v>3.51163</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12888,10 +12888,10 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8746913845547155</v>
+        <v>0.8727960074835117</v>
       </c>
       <c r="C290" t="n">
-        <v>1.18505024651836</v>
+        <v>1.185768164295276</v>
       </c>
       <c r="D290" t="n">
         <v>-2.215741702760299</v>
@@ -12912,10 +12912,10 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.04054</v>
+        <v>-0.04026</v>
       </c>
       <c r="K290" t="n">
-        <v>3.82263</v>
+        <v>3.83219</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12931,10 +12931,10 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.296336936091016</v>
+        <v>3.291320288742683</v>
       </c>
       <c r="C291" t="n">
-        <v>3.350677637341315</v>
+        <v>3.352316146671219</v>
       </c>
       <c r="D291" t="n">
         <v>-1.259458908317534</v>
@@ -12955,10 +12955,10 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23617</v>
+        <v>-0.23625</v>
       </c>
       <c r="K291" t="n">
-        <v>3.84652</v>
+        <v>3.85604</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -12974,10 +12974,10 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.312842702850019</v>
+        <v>6.308801714265133</v>
       </c>
       <c r="C292" t="n">
-        <v>5.58960534895534</v>
+        <v>5.590485985562266</v>
       </c>
       <c r="D292" t="n">
         <v>2.173896387517238</v>
@@ -12998,7 +12998,7 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.7377899999999999</v>
+        <v>-0.73797</v>
       </c>
       <c r="K292" t="n">
         <v>3.62291</v>
@@ -13017,10 +13017,10 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.542891400384729</v>
+        <v>3.539393337908803</v>
       </c>
       <c r="C293" t="n">
-        <v>2.389185997778576</v>
+        <v>2.38871484742762</v>
       </c>
       <c r="D293" t="n">
         <v>2.532383705481922</v>
@@ -13041,10 +13041,10 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52172</v>
+        <v>-0.52197</v>
       </c>
       <c r="K293" t="n">
-        <v>3.88294</v>
+        <v>3.87311</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13060,10 +13060,10 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.367393998561568</v>
+        <v>8.373170617045677</v>
       </c>
       <c r="C294" t="n">
-        <v>5.933111448051087</v>
+        <v>5.931472775877356</v>
       </c>
       <c r="D294" t="n">
         <v>4.202638094986089</v>
@@ -13084,10 +13084,10 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.8229</v>
+        <v>-0.82324</v>
       </c>
       <c r="K294" t="n">
-        <v>3.88606</v>
+        <v>3.87626</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13103,10 +13103,10 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.587530810036468</v>
+        <v>6.599621729171545</v>
       </c>
       <c r="C295" t="n">
-        <v>5.39341256147321</v>
+        <v>5.393820396323501</v>
       </c>
       <c r="D295" t="n">
         <v>6.116918737561194</v>
@@ -13127,10 +13127,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05906</v>
+        <v>-0.05949</v>
       </c>
       <c r="K295" t="n">
-        <v>4.14391</v>
+        <v>4.15332</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13146,10 +13146,10 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.121424556052157</v>
+        <v>5.130333046462776</v>
       </c>
       <c r="C296" t="n">
-        <v>5.699787258220601</v>
+        <v>5.702264226128473</v>
       </c>
       <c r="D296" t="n">
         <v>0.116665678683292</v>
@@ -13170,10 +13170,10 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.27712</v>
+        <v>0.27693</v>
       </c>
       <c r="K296" t="n">
-        <v>4.18465</v>
+        <v>4.17488</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.875864836824761</v>
+        <v>3.8613724367216</v>
       </c>
       <c r="C297" t="n">
-        <v>3.991566189393403</v>
+        <v>3.991510762169881</v>
       </c>
       <c r="D297" t="n">
         <v>2.952449532182566</v>
@@ -13232,10 +13232,10 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.455182843208514</v>
+        <v>2.449324981586942</v>
       </c>
       <c r="C298" t="n">
-        <v>1.081718516394115</v>
+        <v>1.078829924297886</v>
       </c>
       <c r="D298" t="n">
         <v>0.4378171643498963</v>
@@ -13256,10 +13256,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.38244</v>
+        <v>0.38255</v>
       </c>
       <c r="K298" t="n">
-        <v>4.13285</v>
+        <v>4.13246</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13275,10 +13275,10 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.29852780660973</v>
+        <v>3.296911038272543</v>
       </c>
       <c r="C299" t="n">
-        <v>2.776923421928812</v>
+        <v>2.776262654204076</v>
       </c>
       <c r="D299" t="n">
         <v>1.828727090665172</v>
@@ -13299,10 +13299,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.008840000000000001</v>
+        <v>-0.00831</v>
       </c>
       <c r="K299" t="n">
-        <v>3.93086</v>
+        <v>3.9212</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13318,10 +13318,10 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.507148824291041</v>
+        <v>4.510675690432042</v>
       </c>
       <c r="C300" t="n">
-        <v>3.663366517196165</v>
+        <v>3.664212601137939</v>
       </c>
       <c r="D300" t="n">
         <v>3.904539751263902</v>
@@ -13342,10 +13342,10 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.00172</v>
+        <v>1.00327</v>
       </c>
       <c r="K300" t="n">
-        <v>3.58035</v>
+        <v>3.5896</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13361,10 +13361,10 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.774012956170615</v>
+        <v>4.7793905145185</v>
       </c>
       <c r="C301" t="n">
-        <v>3.147061090304804</v>
+        <v>3.146602281688526</v>
       </c>
       <c r="D301" t="n">
         <v>5.337421755280891</v>
@@ -13385,10 +13385,10 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95501</v>
+        <v>1.955</v>
       </c>
       <c r="K301" t="n">
-        <v>3.95673</v>
+        <v>3.94713</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.333938822239714</v>
+        <v>5.340872670830765</v>
       </c>
       <c r="C302" t="n">
-        <v>3.376029845755468</v>
+        <v>3.379377252546112</v>
       </c>
       <c r="D302" t="n">
         <v>4.099657622411113</v>
@@ -13428,10 +13428,10 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47719</v>
+        <v>1.4773</v>
       </c>
       <c r="K302" t="n">
-        <v>3.58984</v>
+        <v>3.5803</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13447,10 +13447,10 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.232475676184145</v>
+        <v>5.233610268768474</v>
       </c>
       <c r="C303" t="n">
-        <v>3.220016491119737</v>
+        <v>3.223346787862069</v>
       </c>
       <c r="D303" t="n">
         <v>1.615584479312737</v>
@@ -13471,10 +13471,10 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98082</v>
+        <v>1.98055</v>
       </c>
       <c r="K303" t="n">
-        <v>3.34647</v>
+        <v>3.337</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13490,10 +13490,10 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.06661365322267</v>
+        <v>1.05862000908199</v>
       </c>
       <c r="C304" t="n">
-        <v>0.527380804591937</v>
+        <v>0.5263821121240353</v>
       </c>
       <c r="D304" t="n">
         <v>-0.6800849329557712</v>
@@ -13514,7 +13514,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.73019</v>
+        <v>2.72963</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13533,10 +13533,10 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.073470692332035</v>
+        <v>1.073078239061331</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1582839158669636</v>
+        <v>0.1566979343816444</v>
       </c>
       <c r="D305" t="n">
         <v>2.199355223074062</v>
@@ -13557,7 +13557,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.50477</v>
+        <v>2.50391</v>
       </c>
       <c r="K305" t="n">
         <v>3.30021</v>
@@ -13576,10 +13576,10 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6398987556194724</v>
+        <v>0.6332972969580686</v>
       </c>
       <c r="C306" t="n">
-        <v>0.04723926447629534</v>
+        <v>0.04300490061863727</v>
       </c>
       <c r="D306" t="n">
         <v>-1.26268922806676</v>
@@ -13600,7 +13600,7 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97813</v>
+        <v>2.97719</v>
       </c>
       <c r="K306" t="n">
         <v>3.02342</v>
@@ -13619,10 +13619,10 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.189253214403819</v>
+        <v>2.193262395584439</v>
       </c>
       <c r="C307" t="n">
-        <v>1.362015803784788</v>
+        <v>1.36069010576938</v>
       </c>
       <c r="D307" t="n">
         <v>-2.598306211624946</v>
@@ -13643,10 +13643,10 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.47011</v>
+        <v>3.46935</v>
       </c>
       <c r="K307" t="n">
-        <v>2.73105</v>
+        <v>2.72177</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.742001287556616</v>
+        <v>1.750954741763722</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2718725485006956</v>
+        <v>0.2731072043035576</v>
       </c>
       <c r="D308" t="n">
         <v>1.607220618499916</v>
@@ -13686,7 +13686,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.01415</v>
+        <v>3.01393</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13705,10 +13705,10 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.151905566839441</v>
+        <v>3.139502431460994</v>
       </c>
       <c r="C309" t="n">
-        <v>2.23072510820308</v>
+        <v>2.230032552554273</v>
       </c>
       <c r="D309" t="n">
         <v>0.5613617013826566</v>
@@ -13729,7 +13729,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06809</v>
+        <v>3.06854</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13748,10 +13748,10 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.761156202062323</v>
+        <v>5.758231885683585</v>
       </c>
       <c r="C310" t="n">
-        <v>6.604917101322871</v>
+        <v>6.603704477140093</v>
       </c>
       <c r="D310" t="n">
         <v>2.766224148008734</v>
@@ -13772,10 +13772,10 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.6111</v>
+        <v>2.61201</v>
       </c>
       <c r="K310" t="n">
-        <v>2.77728</v>
+        <v>2.76807</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13791,10 +13791,10 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.921638192517118</v>
+        <v>3.916782527288909</v>
       </c>
       <c r="C311" t="n">
-        <v>3.166624863163792</v>
+        <v>3.166606561509133</v>
       </c>
       <c r="D311" t="n">
         <v>0.6448082791826071</v>
@@ -13815,7 +13815,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99353</v>
+        <v>2.99484</v>
       </c>
       <c r="K311" t="n">
         <v>2.70029</v>
@@ -13834,10 +13834,10 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.030480413239279</v>
+        <v>4.036763914902686</v>
       </c>
       <c r="C312" t="n">
-        <v>2.312819139401978</v>
+        <v>2.31228020858274</v>
       </c>
       <c r="D312" t="n">
         <v>-1.060076307130675</v>
@@ -13858,10 +13858,10 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.74941</v>
+        <v>2.75154</v>
       </c>
       <c r="K312" t="n">
-        <v>2.99214</v>
+        <v>2.99187</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13877,10 +13877,10 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.255876496723409</v>
+        <v>3.254219056310048</v>
       </c>
       <c r="C313" t="n">
-        <v>2.328283252241636</v>
+        <v>2.327155045646001</v>
       </c>
       <c r="D313" t="n">
         <v>0.04651505529889022</v>
@@ -13901,7 +13901,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.39374</v>
+        <v>2.39412</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13920,10 +13920,10 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.280870412332449</v>
+        <v>4.288954028843039</v>
       </c>
       <c r="C314" t="n">
-        <v>3.90204207327014</v>
+        <v>3.907047530824315</v>
       </c>
       <c r="D314" t="n">
         <v>1.486473133164656</v>
@@ -13944,7 +13944,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.92627</v>
+        <v>1.9261</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13963,10 +13963,10 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.69210020754611</v>
+        <v>1.691892973914011</v>
       </c>
       <c r="C315" t="n">
-        <v>2.793266663314764</v>
+        <v>2.797287299910334</v>
       </c>
       <c r="D315" t="n">
         <v>0.929398768095524</v>
@@ -13987,10 +13987,10 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.41007</v>
+        <v>2.40944</v>
       </c>
       <c r="K315" t="n">
-        <v>3.23811</v>
+        <v>3.24698</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -14006,10 +14006,10 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.663489614591952</v>
+        <v>2.659745679347592</v>
       </c>
       <c r="C316" t="n">
-        <v>2.931067677534194</v>
+        <v>2.92970314533656</v>
       </c>
       <c r="D316" t="n">
         <v>0.3951649989932138</v>
@@ -14030,7 +14030,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62675</v>
+        <v>2.6256</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14049,10 +14049,10 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.781550433858376</v>
+        <v>8.796177555618279</v>
       </c>
       <c r="C317" t="n">
-        <v>9.061030871850662</v>
+        <v>9.062544996217392</v>
       </c>
       <c r="D317" t="n">
         <v>0.3890882456791589</v>
@@ -14073,10 +14073,10 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43649</v>
+        <v>3.43489</v>
       </c>
       <c r="K317" t="n">
-        <v>3.2742</v>
+        <v>3.28303</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14092,10 +14092,10 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.388750156357846</v>
+        <v>4.378877795226699</v>
       </c>
       <c r="C318" t="n">
-        <v>5.426745017323142</v>
+        <v>5.421119442579703</v>
       </c>
       <c r="D318" t="n">
         <v>2.155876237899257</v>
@@ -14116,7 +14116,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.3741</v>
+        <v>3.37222</v>
       </c>
       <c r="K318" t="n">
         <v>3.52516</v>
@@ -14135,10 +14135,10 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.195805572068401</v>
+        <v>4.198228149712757</v>
       </c>
       <c r="C319" t="n">
-        <v>3.372432010235737</v>
+        <v>3.369927838198983</v>
       </c>
       <c r="D319" t="n">
         <v>2.731103489499276</v>
@@ -14159,7 +14159,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.14975</v>
+        <v>3.14745</v>
       </c>
       <c r="K319" t="n">
         <v>3.82042</v>
@@ -14178,10 +14178,10 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.70279877123956</v>
+        <v>6.718978810694409</v>
       </c>
       <c r="C320" t="n">
-        <v>6.737448771960697</v>
+        <v>6.742990995989895</v>
       </c>
       <c r="D320" t="n">
         <v>2.225586470392193</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.12855</v>
+        <v>3.12935</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14221,10 +14221,10 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.940580547132179</v>
+        <v>5.926731583746414</v>
       </c>
       <c r="C321" t="n">
-        <v>4.639648531501028</v>
+        <v>4.638320708335786</v>
       </c>
       <c r="D321" t="n">
         <v>1.456914561131661</v>
@@ -14245,10 +14245,10 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.1808</v>
+        <v>3.18136</v>
       </c>
       <c r="K321" t="n">
-        <v>3.63923</v>
+        <v>3.64797</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14264,10 +14264,10 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.567800262076816</v>
+        <v>5.554598867748339</v>
       </c>
       <c r="C322" t="n">
-        <v>3.518447967887606</v>
+        <v>3.512072447780423</v>
       </c>
       <c r="D322" t="n">
         <v>0.05176696023512228</v>
@@ -14288,10 +14288,10 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.7925</v>
+        <v>3.79411</v>
       </c>
       <c r="K322" t="n">
-        <v>3.73954</v>
+        <v>3.74826</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14307,10 +14307,10 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.357518645060354</v>
+        <v>4.345299315395645</v>
       </c>
       <c r="C323" t="n">
-        <v>5.142997428163198</v>
+        <v>5.142395751446327</v>
       </c>
       <c r="D323" t="n">
         <v>0.8392621864982575</v>
@@ -14331,7 +14331,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.92538</v>
+        <v>3.93054</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14350,10 +14350,10 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.530497463953711</v>
+        <v>7.536889264484126</v>
       </c>
       <c r="C324" t="n">
-        <v>6.855869521063851</v>
+        <v>6.857449660046333</v>
       </c>
       <c r="D324" t="n">
         <v>3.827801042999801</v>
@@ -14374,10 +14374,10 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.68468</v>
+        <v>3.68577</v>
       </c>
       <c r="K324" t="n">
-        <v>3.46024</v>
+        <v>3.45127</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.087071758128282</v>
+        <v>6.078861755020615</v>
       </c>
       <c r="C325" t="n">
-        <v>5.481874184301461</v>
+        <v>5.480415106447212</v>
       </c>
       <c r="D325" t="n">
         <v>0.1503669738298852</v>
@@ -14417,7 +14417,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.30291</v>
+        <v>3.30316</v>
       </c>
       <c r="K325" t="n">
         <v>3.22274</v>
@@ -14436,10 +14436,10 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.849968951153572</v>
+        <v>5.860255383749835</v>
       </c>
       <c r="C326" t="n">
-        <v>5.008590792978262</v>
+        <v>5.016333324139066</v>
       </c>
       <c r="D326" t="n">
         <v>0.7927646448653736</v>
@@ -14460,7 +14460,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86511</v>
+        <v>2.86446</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14479,10 +14479,10 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.911702370517418</v>
+        <v>9.921611367934524</v>
       </c>
       <c r="C327" t="n">
-        <v>9.489640194264304</v>
+        <v>9.501315535404498</v>
       </c>
       <c r="D327" t="n">
         <v>2.693741657212567</v>
@@ -14503,10 +14503,10 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05802</v>
+        <v>2.05678</v>
       </c>
       <c r="K327" t="n">
-        <v>2.64673</v>
+        <v>2.63791</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14522,10 +14522,10 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41313513434003</v>
+        <v>10.4205278011535</v>
       </c>
       <c r="C328" t="n">
-        <v>9.139774390820987</v>
+        <v>9.139903981101426</v>
       </c>
       <c r="D328" t="n">
         <v>3.151038356959646</v>
@@ -14546,7 +14546,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82602</v>
+        <v>1.82405</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14565,10 +14565,10 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>3.993981550817516</v>
+        <v>4.008837887086214</v>
       </c>
       <c r="C329" t="n">
-        <v>3.08301901705974</v>
+        <v>3.080268260884211</v>
       </c>
       <c r="D329" t="n">
         <v>2.844223187267447</v>
@@ -14589,10 +14589,10 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.16177</v>
+        <v>1.15963</v>
       </c>
       <c r="K329" t="n">
-        <v>2.05948</v>
+        <v>2.05076</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.289365991827944</v>
+        <v>6.276804612492626</v>
       </c>
       <c r="C330" t="n">
-        <v>5.625741731906175</v>
+        <v>5.615220690104561</v>
       </c>
       <c r="D330" t="n">
         <v>1.31770281312058</v>
@@ -14632,7 +14632,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15674</v>
+        <v>1.15422</v>
       </c>
       <c r="K330" t="n">
         <v>1.53231</v>
@@ -14651,10 +14651,10 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.977540468050813</v>
+        <v>5.985072414941195</v>
       </c>
       <c r="C331" t="n">
-        <v>7.430773285762582</v>
+        <v>7.429645294190146</v>
       </c>
       <c r="D331" t="n">
         <v>-1.070689312365636</v>
@@ -14675,7 +14675,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.72941</v>
+        <v>0.72582</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14694,10 +14694,10 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.181968216917786</v>
+        <v>4.203658185789694</v>
       </c>
       <c r="C332" t="n">
-        <v>3.980846405336713</v>
+        <v>3.9881421902773</v>
       </c>
       <c r="D332" t="n">
         <v>-1.621570342275713</v>
@@ -14718,10 +14718,10 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13298</v>
+        <v>1.13501</v>
       </c>
       <c r="K332" t="n">
-        <v>0.94835</v>
+        <v>0.95682</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14737,10 +14737,10 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.840057874906622</v>
+        <v>3.822530549240288</v>
       </c>
       <c r="C333" t="n">
-        <v>3.747406521106345</v>
+        <v>3.744803605080782</v>
       </c>
       <c r="D333" t="n">
         <v>-3.153381595054594</v>
@@ -14761,10 +14761,10 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.19602</v>
+        <v>1.19734</v>
       </c>
       <c r="K333" t="n">
-        <v>0.54866</v>
+        <v>0.54018</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14780,10 +14780,10 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.930319961613503</v>
+        <v>2.908821669985628</v>
       </c>
       <c r="C334" t="n">
-        <v>4.880860571832457</v>
+        <v>4.872329212059445</v>
       </c>
       <c r="D334" t="n">
         <v>-1.619057547866032</v>
@@ -14804,10 +14804,10 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05157</v>
+        <v>1.05357</v>
       </c>
       <c r="K334" t="n">
-        <v>-0.05882</v>
+        <v>-0.06722</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -14823,10 +14823,10 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.733729659563378</v>
+        <v>3.721592466319734</v>
       </c>
       <c r="C335" t="n">
-        <v>1.692856454797731</v>
+        <v>1.691361795650437</v>
       </c>
       <c r="D335" t="n">
         <v>-2.585151904762928</v>
@@ -14847,7 +14847,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.72674</v>
+        <v>1.73386</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14866,10 +14866,10 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.721525143497573</v>
+        <v>3.723077387273244</v>
       </c>
       <c r="C336" t="n">
-        <v>3.654203292557034</v>
+        <v>3.655272537933896</v>
       </c>
       <c r="D336" t="n">
         <v>-3.339432220793237</v>
@@ -14890,10 +14890,10 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.43287</v>
+        <v>-2.43255</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.29338</v>
+        <v>-0.285</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14909,10 +14909,10 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>2.006968217291893</v>
+        <v>1.995187360762318</v>
       </c>
       <c r="C337" t="n">
-        <v>1.175067476344638</v>
+        <v>1.172767511735096</v>
       </c>
       <c r="D337" t="n">
         <v>-3.148156875061581</v>
@@ -14933,7 +14933,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74486</v>
+        <v>2.74526</v>
       </c>
       <c r="K337" t="n">
         <v>-0.32644</v>
@@ -14952,10 +14952,10 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.286215676239923</v>
+        <v>3.300039119203513</v>
       </c>
       <c r="C338" t="n">
-        <v>2.200069060009247</v>
+        <v>2.213333195991507</v>
       </c>
       <c r="D338" t="n">
         <v>-2.366256641533082</v>
@@ -14976,7 +14976,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.53278</v>
+        <v>-0.5337499999999999</v>
       </c>
       <c r="K338" t="n">
         <v>-0.36041</v>
@@ -14995,10 +14995,10 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6679553744755484</v>
+        <v>0.6719703568728974</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.817122363537726</v>
+        <v>-1.803994441336998</v>
       </c>
       <c r="D339" t="n">
         <v>-2.151869165047848</v>
@@ -15019,7 +15019,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09285</v>
+        <v>-0.09507</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15038,10 +15038,10 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.599961705733601</v>
+        <v>3.598956854496516</v>
       </c>
       <c r="C340" t="n">
-        <v>0.6050004031228795</v>
+        <v>0.6011472950610219</v>
       </c>
       <c r="D340" t="n">
         <v>-2.719537247988635</v>
@@ -15062,7 +15062,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.52616</v>
+        <v>-0.52865</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15081,10 +15081,10 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.777309525822537</v>
+        <v>4.799086566477251</v>
       </c>
       <c r="C341" t="n">
-        <v>1.370883904466114</v>
+        <v>1.368736117834279</v>
       </c>
       <c r="D341" t="n">
         <v>-3.052231994705401</v>
@@ -15105,7 +15105,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.22507</v>
+        <v>-1.2271</v>
       </c>
       <c r="K341" t="n">
         <v>0.40191</v>
@@ -15124,10 +15124,10 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.698364804732381</v>
+        <v>5.679955075877263</v>
       </c>
       <c r="C342" t="n">
-        <v>2.855425029556269</v>
+        <v>2.838173940538624</v>
       </c>
       <c r="D342" t="n">
         <v>-0.7365119753634963</v>
@@ -15148,7 +15148,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44273</v>
+        <v>-1.44528</v>
       </c>
       <c r="K342" t="n">
         <v>0.6959</v>
@@ -15167,10 +15167,10 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.830956941078957</v>
+        <v>5.839725556624953</v>
       </c>
       <c r="C343" t="n">
-        <v>1.570987213651387</v>
+        <v>1.565773907326062</v>
       </c>
       <c r="D343" t="n">
         <v>2.369853309271819</v>
@@ -15191,7 +15191,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09171</v>
+        <v>-1.09516</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15210,10 +15210,10 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.845789041174831</v>
+        <v>5.881017771588892</v>
       </c>
       <c r="C344" t="n">
-        <v>3.797159027002373</v>
+        <v>3.811994757426285</v>
       </c>
       <c r="D344" t="n">
         <v>0.9097426024377464</v>
@@ -15234,10 +15234,10 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.75704</v>
+        <v>-0.75488</v>
       </c>
       <c r="K344" t="n">
-        <v>1.21624</v>
+        <v>1.21614</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15253,10 +15253,10 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.28568771086413</v>
+        <v>10.26087705149679</v>
       </c>
       <c r="C345" t="n">
-        <v>7.476373754715726</v>
+        <v>7.473883304403328</v>
       </c>
       <c r="D345" t="n">
         <v>7.754180384352938</v>
@@ -15277,10 +15277,10 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.69376</v>
+        <v>-0.69286</v>
       </c>
       <c r="K345" t="n">
-        <v>1.66219</v>
+        <v>1.67058</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15296,10 +15296,10 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.176187913093863</v>
+        <v>2.153702541897307</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4339555451200905</v>
+        <v>-0.4492616811482386</v>
       </c>
       <c r="D346" t="n">
         <v>1.64248815946122</v>
@@ -15320,7 +15320,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.13945</v>
+        <v>-0.13859</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15339,10 +15339,10 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.187509255304668</v>
+        <v>5.175389996808422</v>
       </c>
       <c r="C347" t="n">
-        <v>2.979746961710084</v>
+        <v>2.975947327557393</v>
       </c>
       <c r="D347" t="n">
         <v>4.056609662098487</v>
@@ -15363,7 +15363,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.0381</v>
+        <v>-1.02748</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15382,10 +15382,10 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.563809027496179</v>
+        <v>3.564351375755259</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.9902217463757967</v>
+        <v>-0.989066238031977</v>
       </c>
       <c r="D348" t="n">
         <v>4.251388859809024</v>
@@ -15406,10 +15406,10 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.99158</v>
+        <v>2.99022</v>
       </c>
       <c r="K348" t="n">
-        <v>2.53047</v>
+        <v>2.52186</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15425,10 +15425,10 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.729473966297195</v>
+        <v>6.718935941014892</v>
       </c>
       <c r="C349" t="n">
-        <v>5.744190011743489</v>
+        <v>5.740042561890668</v>
       </c>
       <c r="D349" t="n">
         <v>6.30803281768717</v>
@@ -15468,10 +15468,10 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.359516451788293</v>
+        <v>5.387388834629525</v>
       </c>
       <c r="C350" t="n">
-        <v>3.211239386081077</v>
+        <v>3.236400271263618</v>
       </c>
       <c r="D350" t="n">
         <v>6.18293662343028</v>
@@ -15492,7 +15492,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.56005</v>
+        <v>2.55932</v>
       </c>
       <c r="K350" t="n">
         <v>3.17127</v>
@@ -15511,10 +15511,10 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.024875457947099</v>
+        <v>6.038117044689684</v>
       </c>
       <c r="C351" t="n">
-        <v>4.999637360041986</v>
+        <v>5.026196688104334</v>
       </c>
       <c r="D351" t="n">
         <v>1.67322672676109</v>
@@ -15535,10 +15535,10 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.78134</v>
+        <v>1.77967</v>
       </c>
       <c r="K351" t="n">
-        <v>2.90815</v>
+        <v>2.91653</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15554,10 +15554,10 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.25730204644301</v>
+        <v>-53.25950499184664</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.16200988497865</v>
+        <v>-49.16308921254059</v>
       </c>
       <c r="D352" t="n">
         <v>-44.32528934742422</v>
@@ -15578,7 +15578,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.56742</v>
+        <v>1.56529</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15597,10 +15597,10 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.4023541634936</v>
+        <v>-99.40219541457353</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.1156363733736</v>
+        <v>-98.11570130656493</v>
       </c>
       <c r="D353" t="n">
         <v>-88.69187496442042</v>
@@ -15621,7 +15621,7 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.2774</v>
+        <v>-49.28299</v>
       </c>
       <c r="K353" t="n">
         <v>-38.87916</v>
@@ -15640,10 +15640,10 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80374195675941</v>
+        <v>-98.8041012195028</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.97728545435696</v>
+        <v>-95.97834932258931</v>
       </c>
       <c r="D354" t="n">
         <v>-82.16210606402635</v>
@@ -15664,7 +15664,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.48389</v>
+        <v>-69.49267</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15683,10 +15683,10 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13265454252182</v>
+        <v>-98.13255113157695</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.3483444070967</v>
+        <v>-94.34871943757237</v>
       </c>
       <c r="D355" t="n">
         <v>-81.4135402616682</v>
@@ -15707,7 +15707,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.07268000000001</v>
+        <v>-70.08372</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15726,10 +15726,10 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74478418491439</v>
+        <v>-97.74393577796083</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.63623064463859</v>
+        <v>-93.63494708426666</v>
       </c>
       <c r="D356" t="n">
         <v>-75.6410413187379</v>
@@ -15750,10 +15750,10 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73842</v>
+        <v>-74.73495</v>
       </c>
       <c r="K356" t="n">
-        <v>-30.14005</v>
+        <v>-30.14584</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15769,10 +15769,10 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.4605015414472</v>
+        <v>-97.46169864336983</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99866131205272</v>
+        <v>-90.99945076771941</v>
       </c>
       <c r="D357" t="n">
         <v>-74.18830410898344</v>
@@ -15793,10 +15793,10 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.86150000000001</v>
+        <v>-74.85814999999999</v>
       </c>
       <c r="K357" t="n">
-        <v>-25.53262</v>
+        <v>-25.53877</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15812,10 +15812,10 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.42997751119337</v>
+        <v>-97.43045649273667</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90932809237329</v>
+        <v>-89.9118075030146</v>
       </c>
       <c r="D358" t="n">
         <v>-74.97394533937062</v>
@@ -15836,7 +15836,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.53857000000001</v>
+        <v>-76.53267</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15855,10 +15855,10 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07583923556761</v>
+        <v>-90.07666420566936</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.42335315371349</v>
+        <v>-81.42429583492053</v>
       </c>
       <c r="D359" t="n">
         <v>-74.9707985908163</v>
@@ -15879,7 +15879,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.67775</v>
+        <v>-66.65222</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15898,10 +15898,10 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76676105394999</v>
+        <v>-76.76640642417856</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.7554469954448</v>
+        <v>-65.75428576796367</v>
       </c>
       <c r="D360" t="n">
         <v>-71.85536775820167</v>
@@ -15922,7 +15922,7 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.85972</v>
+        <v>-56.85709</v>
       </c>
       <c r="K360" t="n">
         <v>-20.39193</v>
@@ -15941,10 +15941,10 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.81613376888623</v>
+        <v>-74.81948627100397</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.51257288463721</v>
+        <v>-66.51647329444049</v>
       </c>
       <c r="D361" t="n">
         <v>-70.13490669416275</v>
@@ -15965,7 +15965,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.25212</v>
+        <v>-53.24996</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68911330649644</v>
+        <v>11.67417778382043</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37937307453389</v>
+        <v>11.37074238807041</v>
       </c>
       <c r="D242" t="n">
-        <v>10.14543498162801</v>
+        <v>10.14503721815558</v>
       </c>
       <c r="E242" t="n">
-        <v>7.262183868821204</v>
+        <v>7.262872976688017</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.27654650609951</v>
+        <v>12.26209756792835</v>
       </c>
       <c r="C243" t="n">
-        <v>12.44398934109574</v>
+        <v>12.43449556747156</v>
       </c>
       <c r="D243" t="n">
-        <v>7.820798380506711</v>
+        <v>7.820167887085905</v>
       </c>
       <c r="E243" t="n">
-        <v>8.994846680981784</v>
+        <v>8.995076033640981</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.977875906744632</v>
+        <v>3.972901415826313</v>
       </c>
       <c r="C244" t="n">
-        <v>7.189460065581077</v>
+        <v>7.191181621875664</v>
       </c>
       <c r="D244" t="n">
-        <v>6.051273333379537</v>
+        <v>6.051095308572063</v>
       </c>
       <c r="E244" t="n">
-        <v>8.71046286593289</v>
+        <v>8.711423834889587</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.844599589489639</v>
+        <v>3.845644042406327</v>
       </c>
       <c r="C245" t="n">
-        <v>7.420828697506776</v>
+        <v>7.413460331270105</v>
       </c>
       <c r="D245" t="n">
-        <v>4.806639006996449</v>
+        <v>4.806713145499408</v>
       </c>
       <c r="E245" t="n">
-        <v>8.576970772713576</v>
+        <v>8.570555122347322</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.174418257055553</v>
+        <v>0.1788136033900933</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.690099596383642</v>
+        <v>-0.6935244988788947</v>
       </c>
       <c r="D246" t="n">
-        <v>1.811413989725974</v>
+        <v>1.811626162882729</v>
       </c>
       <c r="E246" t="n">
-        <v>9.481912029521444</v>
+        <v>9.479263021670526</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,16 +11039,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3590411891583267</v>
+        <v>-0.347141210321722</v>
       </c>
       <c r="C247" t="n">
-        <v>2.261827670306493</v>
+        <v>2.284044807873609</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.62500891141667</v>
+        <v>-1.624692766657598</v>
       </c>
       <c r="E247" t="n">
-        <v>9.099672204091602</v>
+        <v>9.101746752017847</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.558968536427696</v>
+        <v>-1.544467291889984</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.326599870244672</v>
+        <v>-2.317855527533808</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.091911712012352</v>
+        <v>-3.091872500069637</v>
       </c>
       <c r="E248" t="n">
-        <v>8.14296684344853</v>
+        <v>8.145625017041414</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.451543310516401</v>
+        <v>1.450391980051258</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2370429305133648</v>
+        <v>-0.236877565936966</v>
       </c>
       <c r="D249" t="n">
-        <v>2.500126526245938</v>
+        <v>2.499899079010315</v>
       </c>
       <c r="E249" t="n">
-        <v>7.140442191043905</v>
+        <v>7.144247299620488</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,16 +11168,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.833632113260689</v>
+        <v>4.826511775231634</v>
       </c>
       <c r="C250" t="n">
-        <v>4.676824619482112</v>
+        <v>4.687080695301771</v>
       </c>
       <c r="D250" t="n">
-        <v>6.342706597823766</v>
+        <v>6.342316644573742</v>
       </c>
       <c r="E250" t="n">
-        <v>8.281670722906821</v>
+        <v>8.28312778415885</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.836814420640275</v>
+        <v>0.8324416811904101</v>
       </c>
       <c r="C251" t="n">
-        <v>1.476043369311753</v>
+        <v>1.477418830945543</v>
       </c>
       <c r="D251" t="n">
-        <v>2.657911122927659</v>
+        <v>2.657816797714219</v>
       </c>
       <c r="E251" t="n">
-        <v>8.429360840016486</v>
+        <v>8.43011939551106</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.655411175645695</v>
+        <v>3.654033653859368</v>
       </c>
       <c r="C252" t="n">
-        <v>2.983273299164213</v>
+        <v>2.968810336078143</v>
       </c>
       <c r="D252" t="n">
-        <v>3.945867355537014</v>
+        <v>3.945807579967586</v>
       </c>
       <c r="E252" t="n">
-        <v>10.20488947387723</v>
+        <v>10.19879533224208</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.12410902743903</v>
+        <v>7.117049051357038</v>
       </c>
       <c r="C253" t="n">
-        <v>8.441800707981638</v>
+        <v>8.446068288753805</v>
       </c>
       <c r="D253" t="n">
-        <v>3.63063193221731</v>
+        <v>3.630215279256932</v>
       </c>
       <c r="E253" t="n">
-        <v>7.929826335525414</v>
+        <v>7.932993375049024</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.374043821481857</v>
+        <v>7.371096258452314</v>
       </c>
       <c r="C254" t="n">
-        <v>7.324410676291282</v>
+        <v>7.314251708787101</v>
       </c>
       <c r="D254" t="n">
-        <v>5.753737798037961</v>
+        <v>5.753361883797137</v>
       </c>
       <c r="E254" t="n">
-        <v>8.195554870273591</v>
+        <v>8.193739605182371</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449987618814034</v>
+        <v>5.449166834524122</v>
       </c>
       <c r="C255" t="n">
-        <v>5.902285441346011</v>
+        <v>5.86913443731174</v>
       </c>
       <c r="D255" t="n">
-        <v>2.5496167573414</v>
+        <v>2.549620812493503</v>
       </c>
       <c r="E255" t="n">
-        <v>6.402910688139607</v>
+        <v>6.401510569421354</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.70562412902412</v>
+        <v>11.70138421818683</v>
       </c>
       <c r="C256" t="n">
-        <v>9.870408179800783</v>
+        <v>9.84502028133738</v>
       </c>
       <c r="D256" t="n">
-        <v>5.668221117197425</v>
+        <v>5.668087532520971</v>
       </c>
       <c r="E256" t="n">
-        <v>7.16769495670293</v>
+        <v>7.1647155964361</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.775738786770294</v>
+        <v>8.777498104875914</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537647421051918</v>
+        <v>8.536667628968786</v>
       </c>
       <c r="D257" t="n">
-        <v>5.103875682899162</v>
+        <v>5.103768045569579</v>
       </c>
       <c r="E257" t="n">
-        <v>7.453365129835721</v>
+        <v>7.456264638848564</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92080083298512</v>
+        <v>11.91992389308072</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74548844153562</v>
+        <v>11.7507009140221</v>
       </c>
       <c r="D258" t="n">
-        <v>8.78628225027307</v>
+        <v>8.786089336321412</v>
       </c>
       <c r="E258" t="n">
-        <v>7.927439136188053</v>
+        <v>7.927117373357873</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45462942192885</v>
+        <v>11.45070257278276</v>
       </c>
       <c r="C259" t="n">
-        <v>9.113716765363321</v>
+        <v>9.100509329200746</v>
       </c>
       <c r="D259" t="n">
-        <v>7.833268737162702</v>
+        <v>7.833094809149532</v>
       </c>
       <c r="E259" t="n">
-        <v>8.263316664787235</v>
+        <v>8.26126865264516</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.842333246179933</v>
+        <v>8.849563691567663</v>
       </c>
       <c r="C260" t="n">
-        <v>9.291681922094174</v>
+        <v>9.290839253703552</v>
       </c>
       <c r="D260" t="n">
-        <v>8.068875265934516</v>
+        <v>8.069120360173244</v>
       </c>
       <c r="E260" t="n">
-        <v>8.668859823558627</v>
+        <v>8.665967256418238</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52692880096462</v>
+        <v>12.52850306372788</v>
       </c>
       <c r="C261" t="n">
-        <v>10.29897066398668</v>
+        <v>10.31190247450662</v>
       </c>
       <c r="D261" t="n">
-        <v>5.621509916156309</v>
+        <v>5.621550978623069</v>
       </c>
       <c r="E261" t="n">
-        <v>10.41295647616063</v>
+        <v>10.40858540517957</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,16 +11684,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.794376136294922</v>
+        <v>6.795860620270666</v>
       </c>
       <c r="C262" t="n">
-        <v>6.491845963722187</v>
+        <v>6.466847670750786</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8224428994861976</v>
+        <v>-0.8221656546746114</v>
       </c>
       <c r="E262" t="n">
-        <v>8.713576103934951</v>
+        <v>8.713928250245907</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.093636916397617</v>
+        <v>9.094026357819285</v>
       </c>
       <c r="C263" t="n">
-        <v>7.446232128706032</v>
+        <v>7.43320844702946</v>
       </c>
       <c r="D263" t="n">
-        <v>3.149496711978794</v>
+        <v>3.149711747763284</v>
       </c>
       <c r="E263" t="n">
-        <v>8.713258057301299</v>
+        <v>8.716270071275801</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42229760293836</v>
+        <v>13.42001305954179</v>
       </c>
       <c r="C264" t="n">
-        <v>11.22794659482602</v>
+        <v>11.2691537903866</v>
       </c>
       <c r="D264" t="n">
-        <v>4.656561367290268</v>
+        <v>4.656529273757815</v>
       </c>
       <c r="E264" t="n">
-        <v>6.29647412590626</v>
+        <v>6.305037092874644</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.054015075647136</v>
+        <v>8.053791661854493</v>
       </c>
       <c r="C265" t="n">
-        <v>5.782162287273795</v>
+        <v>5.793953499978488</v>
       </c>
       <c r="D265" t="n">
-        <v>2.715952801444366</v>
+        <v>2.715987449112234</v>
       </c>
       <c r="E265" t="n">
-        <v>7.341020583474456</v>
+        <v>7.346489997066752</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.580064370440938</v>
+        <v>2.579874543289828</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.193199008265299</v>
+        <v>-0.2238938122266609</v>
       </c>
       <c r="D266" t="n">
-        <v>2.196002033035582</v>
+        <v>2.195884540302706</v>
       </c>
       <c r="E266" t="n">
-        <v>12.02053043608271</v>
+        <v>12.01831523953998</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.100192370174628</v>
+        <v>5.102282139233827</v>
       </c>
       <c r="C267" t="n">
-        <v>1.665188106374371</v>
+        <v>1.659364537596941</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454390362819426</v>
+        <v>3.454352212990863</v>
       </c>
       <c r="E267" t="n">
-        <v>13.54258448826731</v>
+        <v>13.53884482000609</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.828987054342027</v>
+        <v>5.826236906040161</v>
       </c>
       <c r="C268" t="n">
-        <v>3.406459149236429</v>
+        <v>3.421776881770167</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9116235281249274</v>
+        <v>0.9115311538112625</v>
       </c>
       <c r="E268" t="n">
-        <v>15.11466247455921</v>
+        <v>15.11116677266673</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.375757299990089</v>
+        <v>2.377073358679538</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7181679971187238</v>
+        <v>0.7171744779741251</v>
       </c>
       <c r="D269" t="n">
-        <v>2.950804489409142</v>
+        <v>2.950664219008026</v>
       </c>
       <c r="E269" t="n">
-        <v>10.12571727299405</v>
+        <v>10.12965752915582</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.699686467660989</v>
+        <v>2.696182041422213</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3531951763503294</v>
+        <v>0.3387059353884503</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.516121644751112</v>
+        <v>-1.51628555858796</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77205505955776</v>
+        <v>11.77437654043329</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.117917337361399</v>
+        <v>4.111379805751558</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272528868167313</v>
+        <v>3.272260905837565</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.168113995728171</v>
+        <v>-1.168268294446173</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72709295286176</v>
+        <v>12.72620617854612</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.808453791943722</v>
+        <v>3.813325831448267</v>
       </c>
       <c r="C272" t="n">
-        <v>2.825870227905769</v>
+        <v>2.834296649385015</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.928436964250214</v>
+        <v>-2.928192867229007</v>
       </c>
       <c r="E272" t="n">
-        <v>12.5029475525436</v>
+        <v>12.49979856125165</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.044718954209523</v>
+        <v>2.047212337226734</v>
       </c>
       <c r="C273" t="n">
-        <v>2.703649900494898</v>
+        <v>2.703449335132557</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1130744319375987</v>
+        <v>-0.112985705228652</v>
       </c>
       <c r="E273" t="n">
-        <v>12.1713443693628</v>
+        <v>12.16656668560827</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1455883840135286</v>
+        <v>-0.1431895005270412</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2202494481804429</v>
+        <v>0.2300568167537431</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0340605841581576</v>
+        <v>0.03414248396977904</v>
       </c>
       <c r="E274" t="n">
-        <v>11.93580649836579</v>
+        <v>11.93158694929319</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3202473682087592</v>
+        <v>-0.3202841500441811</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4730857855368975</v>
+        <v>-0.4544030122679121</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.020893191590689</v>
+        <v>-2.020930134371879</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91531657047879</v>
+        <v>10.91070982127855</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.993504255110503</v>
+        <v>-3.992938493259157</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.153405723170822</v>
+        <v>-4.153920932076172</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.716217027826829</v>
+        <v>-3.716138521700141</v>
       </c>
       <c r="E276" t="n">
-        <v>8.911737780661833</v>
+        <v>8.912259939665601</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.362988280493606</v>
+        <v>-3.362806020865849</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.722851010364647</v>
+        <v>-3.722172215660724</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.388273857734614</v>
+        <v>-3.388192651975697</v>
       </c>
       <c r="E277" t="n">
-        <v>10.80489978480064</v>
+        <v>10.79838468688952</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.268459701625792</v>
+        <v>3.26958010024232</v>
       </c>
       <c r="C278" t="n">
-        <v>3.591360451323733</v>
+        <v>3.634415056134621</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.625798511291388</v>
+        <v>-1.625641162206082</v>
       </c>
       <c r="E278" t="n">
-        <v>6.12740961722531</v>
+        <v>6.127535330481204</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1241553659559136</v>
+        <v>-0.1223998913677304</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4809295960262805</v>
+        <v>0.4632017938779098</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3376418332989517</v>
+        <v>-0.3375735819763581</v>
       </c>
       <c r="E279" t="n">
-        <v>3.998608744615306</v>
+        <v>4.000374626462189</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.847337030532969</v>
+        <v>-1.848757771308174</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.144570988208527</v>
+        <v>-2.182671780197332</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.801070843838203</v>
+        <v>-0.8010610306848465</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4603670650394909</v>
+        <v>0.4654844867560959</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.170716230843128</v>
+        <v>2.170734603535518</v>
       </c>
       <c r="C281" t="n">
-        <v>1.841703542427497</v>
+        <v>1.855749304249943</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.091066331648129</v>
+        <v>-3.091125359924174</v>
       </c>
       <c r="E281" t="n">
-        <v>3.985676223464241</v>
+        <v>3.989790622950595</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.202603607217623</v>
+        <v>1.197049698802144</v>
       </c>
       <c r="C282" t="n">
-        <v>1.624574625164343</v>
+        <v>1.625571521305536</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2886836619601985</v>
+        <v>0.2884290791133948</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9892668931037463</v>
+        <v>0.9934998077412827</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.132212293371126</v>
+        <v>1.124776389948368</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5723380683481327</v>
+        <v>0.5623694666740953</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1559827866278729</v>
+        <v>0.1556496330499701</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1352059543915929</v>
+        <v>-0.1320300546426845</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.540187229438318</v>
+        <v>2.545943508344473</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05273550615292333</v>
+        <v>-0.05024414324593662</v>
       </c>
       <c r="D284" t="n">
-        <v>2.829248572920484</v>
+        <v>2.829503895713636</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7750691128424192</v>
+        <v>0.7776552759529265</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4599139226774795</v>
+        <v>0.465409105268777</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7789085784740246</v>
+        <v>-0.7821571132131666</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.491988221217611</v>
+        <v>-1.491765105435916</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2694048064056931</v>
+        <v>0.272319257543141</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656541436156125</v>
+        <v>4.658391496247716</v>
       </c>
       <c r="C286" t="n">
-        <v>1.835510400393514</v>
+        <v>1.850385822394318</v>
       </c>
       <c r="D286" t="n">
-        <v>2.955690723048998</v>
+        <v>2.95566447840907</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268020625516786</v>
+        <v>1.268338709067685</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.821834185545716</v>
+        <v>5.821088376513384</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936547954010572</v>
+        <v>3.944480047187504</v>
       </c>
       <c r="D287" t="n">
-        <v>4.871296070878484</v>
+        <v>4.871027505889147</v>
       </c>
       <c r="E287" t="n">
-        <v>2.680106155787643</v>
+        <v>2.677997110659414</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480227024225613</v>
+        <v>3.481672733543917</v>
       </c>
       <c r="C288" t="n">
-        <v>2.9252222228352</v>
+        <v>2.952007842839421</v>
       </c>
       <c r="D288" t="n">
-        <v>2.109403820450528</v>
+        <v>2.10933096575785</v>
       </c>
       <c r="E288" t="n">
-        <v>3.368335329948735</v>
+        <v>3.365416013016942</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.848012322360719</v>
+        <v>6.846540253566302</v>
       </c>
       <c r="C289" t="n">
-        <v>5.982507466958076</v>
+        <v>6.018191396424233</v>
       </c>
       <c r="D289" t="n">
-        <v>2.234870657038535</v>
+        <v>2.234766755201378</v>
       </c>
       <c r="E289" t="n">
-        <v>3.829622109295161</v>
+        <v>3.823807652120359</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8727960074835117</v>
+        <v>0.8724868681492248</v>
       </c>
       <c r="C290" t="n">
-        <v>1.185768164295276</v>
+        <v>1.163758535435733</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.215741702760299</v>
+        <v>-2.215450370993666</v>
       </c>
       <c r="E290" t="n">
-        <v>2.401475414146992</v>
+        <v>2.40425150969048</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.291320288742683</v>
+        <v>3.291652167213965</v>
       </c>
       <c r="C291" t="n">
-        <v>3.352316146671219</v>
+        <v>3.302308536550891</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.259458908317534</v>
+        <v>-1.259168126566723</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627450913030428</v>
+        <v>3.627918218153314</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.308801714265133</v>
+        <v>6.308338902728816</v>
       </c>
       <c r="C292" t="n">
-        <v>5.590485985562266</v>
+        <v>5.588023794436281</v>
       </c>
       <c r="D292" t="n">
-        <v>2.173896387517238</v>
+        <v>2.174009925544484</v>
       </c>
       <c r="E292" t="n">
-        <v>4.879886563603586</v>
+        <v>4.880457147628769</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.539393337908803</v>
+        <v>3.537248739384835</v>
       </c>
       <c r="C293" t="n">
-        <v>2.38871484742762</v>
+        <v>2.370946837778853</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532383705481922</v>
+        <v>2.532175217009258</v>
       </c>
       <c r="E293" t="n">
-        <v>4.243071502053164</v>
+        <v>4.242435856993199</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.373170617045677</v>
+        <v>8.366257760757879</v>
       </c>
       <c r="C294" t="n">
-        <v>5.931472775877356</v>
+        <v>5.91073075869466</v>
       </c>
       <c r="D294" t="n">
-        <v>4.202638094986089</v>
+        <v>4.202245571270824</v>
       </c>
       <c r="E294" t="n">
-        <v>6.255420209753604</v>
+        <v>6.252825307944976</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.599621729171545</v>
+        <v>6.591583816699242</v>
       </c>
       <c r="C295" t="n">
-        <v>5.393820396323501</v>
+        <v>5.38562212394702</v>
       </c>
       <c r="D295" t="n">
-        <v>6.116918737561194</v>
+        <v>6.116514181377131</v>
       </c>
       <c r="E295" t="n">
-        <v>6.954135403436901</v>
+        <v>6.950052682368035</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.130333046462776</v>
+        <v>5.140540504680757</v>
       </c>
       <c r="C296" t="n">
-        <v>5.702264226128473</v>
+        <v>5.711497630897933</v>
       </c>
       <c r="D296" t="n">
-        <v>0.116665678683292</v>
+        <v>0.1170929138635257</v>
       </c>
       <c r="E296" t="n">
-        <v>4.682455408621822</v>
+        <v>4.68094742113101</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.8613724367216</v>
+        <v>3.869350867023336</v>
       </c>
       <c r="C297" t="n">
-        <v>3.991510762169881</v>
+        <v>4.005672286808082</v>
       </c>
       <c r="D297" t="n">
-        <v>2.952449532182566</v>
+        <v>2.952794057407426</v>
       </c>
       <c r="E297" t="n">
-        <v>4.085327346884982</v>
+        <v>4.086353980277679</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.449324981586942</v>
+        <v>2.451160893303284</v>
       </c>
       <c r="C298" t="n">
-        <v>1.078829924297886</v>
+        <v>1.069559544520438</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4378171643498963</v>
+        <v>0.4379621808341172</v>
       </c>
       <c r="E298" t="n">
-        <v>3.051579777303193</v>
+        <v>3.051045978282674</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.296911038272543</v>
+        <v>3.298103544743647</v>
       </c>
       <c r="C299" t="n">
-        <v>2.776262654204076</v>
+        <v>2.792202549686595</v>
       </c>
       <c r="D299" t="n">
-        <v>1.828727090665172</v>
+        <v>1.828676786280892</v>
       </c>
       <c r="E299" t="n">
-        <v>2.81148178790589</v>
+        <v>2.813069752395103</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.510675690432042</v>
+        <v>4.510585650790411</v>
       </c>
       <c r="C300" t="n">
-        <v>3.664212601137939</v>
+        <v>3.716155251072495</v>
       </c>
       <c r="D300" t="n">
-        <v>3.904539751263902</v>
+        <v>3.904433616436154</v>
       </c>
       <c r="E300" t="n">
-        <v>3.749958253980878</v>
+        <v>3.748846656720173</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.7793905145185</v>
+        <v>4.777216434015896</v>
       </c>
       <c r="C301" t="n">
-        <v>3.146602281688526</v>
+        <v>3.181889447921193</v>
       </c>
       <c r="D301" t="n">
-        <v>5.337421755280891</v>
+        <v>5.337133110640191</v>
       </c>
       <c r="E301" t="n">
-        <v>1.882203427512041</v>
+        <v>1.882908913557069</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.340872670830765</v>
+        <v>5.339085999979409</v>
       </c>
       <c r="C302" t="n">
-        <v>3.379377252546112</v>
+        <v>3.379359890217737</v>
       </c>
       <c r="D302" t="n">
-        <v>4.099657622411113</v>
+        <v>4.099624258750834</v>
       </c>
       <c r="E302" t="n">
-        <v>1.196128226786874</v>
+        <v>1.198777630932901</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.233610268768474</v>
+        <v>5.232001707127099</v>
       </c>
       <c r="C303" t="n">
-        <v>3.223346787862069</v>
+        <v>3.151789490397139</v>
       </c>
       <c r="D303" t="n">
-        <v>1.615584479312737</v>
+        <v>1.615689959109745</v>
       </c>
       <c r="E303" t="n">
-        <v>3.115392809325668</v>
+        <v>3.117679996963196</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.05862000908199</v>
+        <v>1.057212314034772</v>
       </c>
       <c r="C304" t="n">
-        <v>0.5263821121240353</v>
+        <v>0.4991038895259425</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6800849329557712</v>
+        <v>-0.6799848833401123</v>
       </c>
       <c r="E304" t="n">
-        <v>3.834513152060848</v>
+        <v>3.83528644661657</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.073078239061331</v>
+        <v>1.067397687800531</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1566979343816444</v>
+        <v>0.1449046722070912</v>
       </c>
       <c r="D305" t="n">
-        <v>2.199355223074062</v>
+        <v>2.198972546736533</v>
       </c>
       <c r="E305" t="n">
-        <v>1.963544907674075</v>
+        <v>1.964971628781709</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6332972969580686</v>
+        <v>0.6279798808265902</v>
       </c>
       <c r="C306" t="n">
-        <v>0.04300490061863727</v>
+        <v>0.02991696792322696</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.26268922806676</v>
+        <v>-1.263019604324134</v>
       </c>
       <c r="E306" t="n">
-        <v>2.320441003712248</v>
+        <v>2.321850890826838</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.193262395584439</v>
+        <v>2.185688208859826</v>
       </c>
       <c r="C307" t="n">
-        <v>1.36069010576938</v>
+        <v>1.364177536606537</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.598306211624946</v>
+        <v>-2.598516696530573</v>
       </c>
       <c r="E307" t="n">
-        <v>3.142176610305869</v>
+        <v>3.143029664210872</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.750954741763722</v>
+        <v>1.766862087109256</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2731072043035576</v>
+        <v>0.2728758903609796</v>
       </c>
       <c r="D308" t="n">
-        <v>1.607220618499916</v>
+        <v>1.607862901272283</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799310163578485</v>
+        <v>4.799621112894981</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.139502431460994</v>
+        <v>3.148163744612664</v>
       </c>
       <c r="C309" t="n">
-        <v>2.230032552554273</v>
+        <v>2.244138458642841</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5613617013826566</v>
+        <v>0.5617255091661555</v>
       </c>
       <c r="E309" t="n">
-        <v>5.406169580966647</v>
+        <v>5.405826507579725</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.758231885683585</v>
+        <v>5.761024197083708</v>
       </c>
       <c r="C310" t="n">
-        <v>6.603704477140093</v>
+        <v>6.635470076961036</v>
       </c>
       <c r="D310" t="n">
-        <v>2.766224148008734</v>
+        <v>2.76644057159714</v>
       </c>
       <c r="E310" t="n">
-        <v>8.394809457964737</v>
+        <v>8.393130051120433</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.916782527288909</v>
+        <v>3.920797950301669</v>
       </c>
       <c r="C311" t="n">
-        <v>3.166606561509133</v>
+        <v>3.198125997370593</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6448082791826071</v>
+        <v>0.6449837666081537</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879402945409383</v>
+        <v>4.879477432584811</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.036763914902686</v>
+        <v>4.035571229356205</v>
       </c>
       <c r="C312" t="n">
-        <v>2.31228020858274</v>
+        <v>2.369259863783291</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.060076307130675</v>
+        <v>-1.060046943711968</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824698459307132</v>
+        <v>5.824394028289137</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.254219056310048</v>
+        <v>3.254482519696711</v>
       </c>
       <c r="C313" t="n">
-        <v>2.327155045646001</v>
+        <v>2.40550835351383</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04651505529889022</v>
+        <v>0.0465141287606663</v>
       </c>
       <c r="E313" t="n">
-        <v>6.337004881377073</v>
+        <v>6.33552882178392</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.288954028843039</v>
+        <v>4.285560693520374</v>
       </c>
       <c r="C314" t="n">
-        <v>3.907047530824315</v>
+        <v>3.915519331641204</v>
       </c>
       <c r="D314" t="n">
-        <v>1.486473133164656</v>
+        <v>1.486352769967336</v>
       </c>
       <c r="E314" t="n">
-        <v>8.654099506296408</v>
+        <v>8.647363602378167</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.691892973914011</v>
+        <v>1.687583811783</v>
       </c>
       <c r="C315" t="n">
-        <v>2.797287299910334</v>
+        <v>2.645790006529514</v>
       </c>
       <c r="D315" t="n">
-        <v>0.929398768095524</v>
+        <v>0.9292594932999165</v>
       </c>
       <c r="E315" t="n">
-        <v>4.026214553035445</v>
+        <v>4.024648519717222</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.659745679347592</v>
+        <v>2.654256216015249</v>
       </c>
       <c r="C316" t="n">
-        <v>2.92970314533656</v>
+        <v>2.861382335892171</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3951649989932138</v>
+        <v>0.3950284895924527</v>
       </c>
       <c r="E316" t="n">
-        <v>3.650707115185936</v>
+        <v>3.649603874751084</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.796177555618279</v>
+        <v>8.784372839960275</v>
       </c>
       <c r="C317" t="n">
-        <v>9.062544996217392</v>
+        <v>9.067974656528799</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3890882456791589</v>
+        <v>0.3884412932526837</v>
       </c>
       <c r="E317" t="n">
-        <v>7.31681592747766</v>
+        <v>7.313253160445821</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.378877795226699</v>
+        <v>4.371759682058407</v>
       </c>
       <c r="C318" t="n">
-        <v>5.421119442579703</v>
+        <v>5.380193983054515</v>
       </c>
       <c r="D318" t="n">
-        <v>2.155876237899257</v>
+        <v>2.155182839914915</v>
       </c>
       <c r="E318" t="n">
-        <v>5.21254844273713</v>
+        <v>5.210636075747987</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.198228149712757</v>
+        <v>4.188158145027487</v>
       </c>
       <c r="C319" t="n">
-        <v>3.369927838198983</v>
+        <v>3.331393133802307</v>
       </c>
       <c r="D319" t="n">
-        <v>2.731103489499276</v>
+        <v>2.730661951055935</v>
       </c>
       <c r="E319" t="n">
-        <v>3.719646736501181</v>
+        <v>3.721768378030532</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.718978810694409</v>
+        <v>6.744227583387619</v>
       </c>
       <c r="C320" t="n">
-        <v>6.742990995989895</v>
+        <v>6.783664726158567</v>
       </c>
       <c r="D320" t="n">
-        <v>2.225586470392193</v>
+        <v>2.226563024488648</v>
       </c>
       <c r="E320" t="n">
-        <v>3.06178143459146</v>
+        <v>3.065080674672971</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.926731583746414</v>
+        <v>5.938008995783051</v>
       </c>
       <c r="C321" t="n">
-        <v>4.638320708335786</v>
+        <v>4.671226700815057</v>
       </c>
       <c r="D321" t="n">
-        <v>1.456914561131661</v>
+        <v>1.457511056310956</v>
       </c>
       <c r="E321" t="n">
-        <v>2.660654702382237</v>
+        <v>2.665046596757659</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.554598867748339</v>
+        <v>5.560450120250859</v>
       </c>
       <c r="C322" t="n">
-        <v>3.512072447780423</v>
+        <v>3.513077382926211</v>
       </c>
       <c r="D322" t="n">
-        <v>0.05176696023512228</v>
+        <v>0.0522723614494458</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5248481033391816</v>
+        <v>-0.5174417683821098</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.345299315395645</v>
+        <v>4.352154979531986</v>
       </c>
       <c r="C323" t="n">
-        <v>5.142395751446327</v>
+        <v>5.205111148019004</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8392621864982575</v>
+        <v>0.8396843287395317</v>
       </c>
       <c r="E323" t="n">
-        <v>4.167263467812532</v>
+        <v>4.169876004873996</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.536889264484126</v>
+        <v>7.537145949207691</v>
       </c>
       <c r="C324" t="n">
-        <v>6.857449660046333</v>
+        <v>7.00329651338949</v>
       </c>
       <c r="D324" t="n">
-        <v>3.827801042999801</v>
+        <v>3.827891511573278</v>
       </c>
       <c r="E324" t="n">
-        <v>2.182968812025621</v>
+        <v>2.187601286782881</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.078861755020615</v>
+        <v>6.0813984348836</v>
       </c>
       <c r="C325" t="n">
-        <v>5.480415106447212</v>
+        <v>5.608487516785732</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1503669738298852</v>
+        <v>0.1505652360996645</v>
       </c>
       <c r="E325" t="n">
-        <v>2.891483701435416</v>
+        <v>2.892522877339787</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.860255383749835</v>
+        <v>5.855069795208823</v>
       </c>
       <c r="C326" t="n">
-        <v>5.016333324139066</v>
+        <v>4.981160331785328</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7927646448653736</v>
+        <v>0.7926405222000499</v>
       </c>
       <c r="E326" t="n">
-        <v>4.479071304120197</v>
+        <v>4.47420851619964</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.921611367934524</v>
+        <v>9.914352380372748</v>
       </c>
       <c r="C327" t="n">
-        <v>9.501315535404498</v>
+        <v>9.270357904157201</v>
       </c>
       <c r="D327" t="n">
-        <v>2.693741657212567</v>
+        <v>2.693361703760355</v>
       </c>
       <c r="E327" t="n">
-        <v>7.803906150491247</v>
+        <v>7.798841588088656</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.4205278011535</v>
+        <v>10.4084300614121</v>
       </c>
       <c r="C328" t="n">
-        <v>9.139903981101426</v>
+        <v>9.05247344091087</v>
       </c>
       <c r="D328" t="n">
-        <v>3.151038356959646</v>
+        <v>3.150486017591381</v>
       </c>
       <c r="E328" t="n">
-        <v>7.364618306906068</v>
+        <v>7.360729243128317</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.008837887086214</v>
+        <v>3.991242624240243</v>
       </c>
       <c r="C329" t="n">
-        <v>3.080268260884211</v>
+        <v>3.007642466097527</v>
       </c>
       <c r="D329" t="n">
-        <v>2.844223187267447</v>
+        <v>2.843137803485751</v>
       </c>
       <c r="E329" t="n">
-        <v>3.600234102263089</v>
+        <v>3.597084927111083</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.276804612492626</v>
+        <v>6.264882897876145</v>
       </c>
       <c r="C330" t="n">
-        <v>5.615220690104561</v>
+        <v>5.545755289621979</v>
       </c>
       <c r="D330" t="n">
-        <v>1.31770281312058</v>
+        <v>1.31657039925952</v>
       </c>
       <c r="E330" t="n">
-        <v>5.632036892698911</v>
+        <v>5.629468917603697</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.985072414941195</v>
+        <v>5.970100249401056</v>
       </c>
       <c r="C331" t="n">
-        <v>7.429645294190146</v>
+        <v>7.424433291960453</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.070689312365636</v>
+        <v>-1.071400937391465</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981337839832478</v>
+        <v>4.981041089729987</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.203658185789694</v>
+        <v>4.239961224961108</v>
       </c>
       <c r="C332" t="n">
-        <v>3.9881421902773</v>
+        <v>4.01229300518291</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.621570342275713</v>
+        <v>-1.619918262847964</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511618361274494</v>
+        <v>4.511817873939861</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.822530549240288</v>
+        <v>3.836740365494751</v>
       </c>
       <c r="C333" t="n">
-        <v>3.744803605080782</v>
+        <v>3.782883195468245</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.153381595054594</v>
+        <v>-3.152584957824534</v>
       </c>
       <c r="E333" t="n">
-        <v>4.436327493515702</v>
+        <v>4.43574375930218</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.908821669985628</v>
+        <v>2.918611795310566</v>
       </c>
       <c r="C334" t="n">
-        <v>4.872329212059445</v>
+        <v>4.913928658838307</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.619057547866032</v>
+        <v>-1.618283059074233</v>
       </c>
       <c r="E334" t="n">
-        <v>5.108127798093842</v>
+        <v>5.110263871537835</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.721592466319734</v>
+        <v>3.730170697602397</v>
       </c>
       <c r="C335" t="n">
-        <v>1.691361795650437</v>
+        <v>1.784085327517682</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.585151904762928</v>
+        <v>-2.584529331332897</v>
       </c>
       <c r="E335" t="n">
-        <v>3.83257002224815</v>
+        <v>3.832554158811807</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.723077387273244</v>
+        <v>3.726156133627789</v>
       </c>
       <c r="C336" t="n">
-        <v>3.655272537933896</v>
+        <v>3.878777858930182</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.339432220793237</v>
+        <v>-3.339140867682577</v>
       </c>
       <c r="E336" t="n">
-        <v>3.491745596834739</v>
+        <v>3.492837859478848</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.995187360762318</v>
+        <v>1.998785112860468</v>
       </c>
       <c r="C337" t="n">
-        <v>1.172767511735096</v>
+        <v>1.407502135335736</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.148156875061581</v>
+        <v>-3.147907997333987</v>
       </c>
       <c r="E337" t="n">
-        <v>3.634217958397801</v>
+        <v>3.632381935538587</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.300039119203513</v>
+        <v>3.293521044890291</v>
       </c>
       <c r="C338" t="n">
-        <v>2.213333195991507</v>
+        <v>2.202494166606739</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.366256641533082</v>
+        <v>-2.366441244591222</v>
       </c>
       <c r="E338" t="n">
-        <v>1.874920141598069</v>
+        <v>1.875800216351253</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6719703568728974</v>
+        <v>0.6624309183083543</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.803994441336998</v>
+        <v>-2.193095890286378</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.151869165047848</v>
+        <v>-2.152306563442785</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6064107766733717</v>
+        <v>-0.6040832774020122</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.598956854496516</v>
+        <v>3.584101643503979</v>
       </c>
       <c r="C340" t="n">
-        <v>0.6011472950610219</v>
+        <v>0.4405170500976219</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.719537247988635</v>
+        <v>-2.720239526674251</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.14885138367633</v>
+        <v>-1.147287960112153</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.799086566477251</v>
+        <v>4.774896480550828</v>
       </c>
       <c r="C341" t="n">
-        <v>1.368736117834279</v>
+        <v>1.320843199035071</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.052231994705401</v>
+        <v>-3.053624086391915</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702448893405673</v>
+        <v>1.702127535508491</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.679955075877263</v>
+        <v>5.66320886767282</v>
       </c>
       <c r="C342" t="n">
-        <v>2.838173940538624</v>
+        <v>2.741537674938543</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7365119753634963</v>
+        <v>-0.7381110432418847</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1299857670260862</v>
+        <v>-0.1299269124699798</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.839725556624953</v>
+        <v>5.81766645129671</v>
       </c>
       <c r="C343" t="n">
-        <v>1.565773907326062</v>
+        <v>1.501310019516966</v>
       </c>
       <c r="D343" t="n">
-        <v>2.369853309271819</v>
+        <v>2.368682165404246</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6821502298575588</v>
+        <v>0.6818346767176298</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.881017771588892</v>
+        <v>5.936078390687793</v>
       </c>
       <c r="C344" t="n">
-        <v>3.811994757426285</v>
+        <v>3.892678631925794</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9097426024377464</v>
+        <v>0.9124328564630968</v>
       </c>
       <c r="E344" t="n">
-        <v>2.711161116581229</v>
+        <v>2.712615569937293</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26087705149679</v>
+        <v>10.28424166284039</v>
       </c>
       <c r="C345" t="n">
-        <v>7.473883304403328</v>
+        <v>7.573296663610596</v>
       </c>
       <c r="D345" t="n">
-        <v>7.754180384352938</v>
+        <v>7.755506846652316</v>
       </c>
       <c r="E345" t="n">
-        <v>2.756002186615447</v>
+        <v>2.755125628905408</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.153702541897307</v>
+        <v>2.164110812302722</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4492616811482386</v>
+        <v>-0.4071841360058337</v>
       </c>
       <c r="D346" t="n">
-        <v>1.64248815946122</v>
+        <v>1.643607464902375</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254187099149063</v>
+        <v>2.254317602949008</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.175389996808422</v>
+        <v>5.184245504404705</v>
       </c>
       <c r="C347" t="n">
-        <v>2.975947327557393</v>
+        <v>3.125140334761323</v>
       </c>
       <c r="D347" t="n">
-        <v>4.056609662098487</v>
+        <v>4.057549016855422</v>
       </c>
       <c r="E347" t="n">
-        <v>2.13000504836971</v>
+        <v>2.133485649630718</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.564351375755259</v>
+        <v>3.569562126281434</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.989066238031977</v>
+        <v>-0.626262515831999</v>
       </c>
       <c r="D348" t="n">
-        <v>4.251388859809024</v>
+        <v>4.251872568691728</v>
       </c>
       <c r="E348" t="n">
-        <v>3.131712790794072</v>
+        <v>3.13122373567265</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.718935941014892</v>
+        <v>6.721811786696774</v>
       </c>
       <c r="C349" t="n">
-        <v>5.740042561890668</v>
+        <v>6.145890206084914</v>
       </c>
       <c r="D349" t="n">
-        <v>6.30803281768717</v>
+        <v>6.308217403783112</v>
       </c>
       <c r="E349" t="n">
-        <v>6.031576692280116</v>
+        <v>6.032294844828079</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.387388834629525</v>
+        <v>5.376015800385581</v>
       </c>
       <c r="C350" t="n">
-        <v>3.236400271263618</v>
+        <v>3.2071524030159</v>
       </c>
       <c r="D350" t="n">
-        <v>6.18293662343028</v>
+        <v>6.182525142567585</v>
       </c>
       <c r="E350" t="n">
-        <v>6.709190894919859</v>
+        <v>6.714613911160683</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.038117044689684</v>
+        <v>6.02185047910373</v>
       </c>
       <c r="C351" t="n">
-        <v>5.026196688104334</v>
+        <v>4.301009519763532</v>
       </c>
       <c r="D351" t="n">
-        <v>1.67322672676109</v>
+        <v>1.672362518358539</v>
       </c>
       <c r="E351" t="n">
-        <v>8.079498574279098</v>
+        <v>8.0810859661681</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.25950499184664</v>
+        <v>-53.26822356775096</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.16308921254059</v>
+        <v>-49.30765609672081</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.32528934742422</v>
+        <v>-44.32608657175283</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.874646057648111</v>
+        <v>-1.877236574219499</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40219541457353</v>
+        <v>-99.40238948262554</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11570130656493</v>
+        <v>-98.11770564815239</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69187496442042</v>
+        <v>-88.69214423593424</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.5058412797337</v>
+        <v>-52.50753598135462</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.8041012195028</v>
+        <v>-98.80436312853557</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.97834932258931</v>
+        <v>-95.98521054666811</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16210606402635</v>
+        <v>-82.1625615954102</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.69981154542833</v>
+        <v>-50.7020401721777</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13255113157695</v>
+        <v>-98.13303777027078</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.34871943757237</v>
+        <v>-94.35228584115593</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.4135402616682</v>
+        <v>-81.4139188173727</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98296443895493</v>
+        <v>-42.98618006929963</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74393577796083</v>
+        <v>-97.74232454064828</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.63494708426666</v>
+        <v>-93.62892665725434</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.6410413187379</v>
+        <v>-75.63997206461602</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11485718758562</v>
+        <v>-43.11247797422947</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46169864336983</v>
+        <v>-97.4608484956877</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99945076771941</v>
+        <v>-90.9883096882117</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18830410898344</v>
+        <v>-74.18774077150916</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.6578780942826</v>
+        <v>-45.65823865225113</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43045649273667</v>
+        <v>-97.43020060194051</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.9118075030146</v>
+        <v>-89.90265698270781</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.97394533937062</v>
+        <v>-74.9735378875063</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17007727392687</v>
+        <v>-40.1716685391618</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07666420566936</v>
+        <v>-90.07562559331848</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.42429583492053</v>
+        <v>-81.37415372440897</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.9707985908163</v>
+        <v>-74.97044379696993</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34861236515414</v>
+        <v>-31.34870252499049</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76640642417856</v>
+        <v>-76.76486148708817</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.75428576796367</v>
+        <v>-65.56947576505473</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85536775820167</v>
+        <v>-71.85512670806699</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.57580863095149</v>
+        <v>-12.5807336214706</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.81948627100397</v>
+        <v>-74.81876460319985</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.51647329444049</v>
+        <v>-66.34600932902188</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13490669416275</v>
+        <v>-70.13476792127949</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80582558663232</v>
+        <v>-16.80230250634978</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -528,7 +528,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87342</v>
+        <v>6.87349</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -571,7 +571,7 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15349</v>
+        <v>4.15341</v>
       </c>
       <c r="K3" t="n">
         <v>2.43838</v>
@@ -614,7 +614,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55463</v>
+        <v>7.55487</v>
       </c>
       <c r="K4" t="n">
         <v>2.13214</v>
@@ -657,7 +657,7 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74252</v>
+        <v>0.7425</v>
       </c>
       <c r="K5" t="n">
         <v>2.02286</v>
@@ -700,7 +700,7 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77779</v>
+        <v>1.77778</v>
       </c>
       <c r="K6" t="n">
         <v>1.99344</v>
@@ -743,7 +743,7 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0214</v>
+        <v>2.02134</v>
       </c>
       <c r="K7" t="n">
         <v>1.70179</v>
@@ -786,7 +786,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61377</v>
+        <v>4.61374</v>
       </c>
       <c r="K8" t="n">
         <v>1.47346</v>
@@ -829,7 +829,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05476</v>
+        <v>7.05474</v>
       </c>
       <c r="K9" t="n">
         <v>1.21062</v>
@@ -872,7 +872,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.034689999999999</v>
+        <v>8.03464</v>
       </c>
       <c r="K10" t="n">
         <v>0.7003</v>
@@ -915,7 +915,7 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.90069</v>
+        <v>5.90064</v>
       </c>
       <c r="K11" t="n">
         <v>0.36237</v>
@@ -958,7 +958,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.00204</v>
+        <v>3.00208</v>
       </c>
       <c r="K12" t="n">
         <v>0.05167</v>
@@ -1001,7 +1001,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56814</v>
+        <v>3.56818</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1044,7 +1044,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.00313</v>
+        <v>2.00325</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1087,7 +1087,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.20171</v>
+        <v>3.20155</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1130,7 +1130,7 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72055</v>
+        <v>4.72087</v>
       </c>
       <c r="K16" t="n">
         <v>-1.22423</v>
@@ -1173,7 +1173,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26336</v>
+        <v>5.26329</v>
       </c>
       <c r="K17" t="n">
         <v>-1.68662</v>
@@ -1216,7 +1216,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22922</v>
+        <v>4.22917</v>
       </c>
       <c r="K18" t="n">
         <v>-1.9802</v>
@@ -1259,7 +1259,7 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76141</v>
+        <v>3.76132</v>
       </c>
       <c r="K19" t="n">
         <v>-2.25254</v>
@@ -1302,7 +1302,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94779</v>
+        <v>0.94776</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53148</v>
@@ -1345,7 +1345,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13364</v>
+        <v>-1.13366</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1388,7 +1388,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.86873</v>
+        <v>-2.86878</v>
       </c>
       <c r="K22" t="n">
         <v>-2.39536</v>
@@ -1431,7 +1431,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.60396</v>
+        <v>-2.60403</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1474,7 +1474,7 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90628</v>
+        <v>-2.90621</v>
       </c>
       <c r="K24" t="n">
         <v>-2.19496</v>
@@ -1517,7 +1517,7 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.7221</v>
+        <v>-3.72208</v>
       </c>
       <c r="K25" t="n">
         <v>-1.93924</v>
@@ -1560,7 +1560,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68672</v>
+        <v>-6.68666</v>
       </c>
       <c r="K26" t="n">
         <v>-1.50532</v>
@@ -1603,7 +1603,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29533</v>
+        <v>-7.29543</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1646,7 +1646,7 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.18811</v>
+        <v>-7.18782</v>
       </c>
       <c r="K28" t="n">
         <v>-0.45662</v>
@@ -1689,7 +1689,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.49593</v>
+        <v>-8.495990000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.3143</v>
@@ -1732,7 +1732,7 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96447</v>
+        <v>-7.96451</v>
       </c>
       <c r="K30" t="n">
         <v>0.61656</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24768</v>
+        <v>-7.24778</v>
       </c>
       <c r="K31" t="n">
         <v>1.1193</v>
@@ -1818,7 +1818,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.58166</v>
+        <v>-7.58168</v>
       </c>
       <c r="K32" t="n">
         <v>1.33158</v>
@@ -1861,7 +1861,7 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.44014</v>
+        <v>-8.440160000000001</v>
       </c>
       <c r="K33" t="n">
         <v>1.54476</v>
@@ -1904,7 +1904,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.62433</v>
+        <v>-7.62437</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1947,7 +1947,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.8949</v>
+        <v>-5.89495</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1990,7 +1990,7 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24305</v>
+        <v>-7.24299</v>
       </c>
       <c r="K36" t="n">
         <v>1.34653</v>
@@ -2033,7 +2033,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.38125</v>
+        <v>-7.38123</v>
       </c>
       <c r="K37" t="n">
         <v>1.02835</v>
@@ -2076,7 +2076,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.30767</v>
+        <v>-3.30761</v>
       </c>
       <c r="K38" t="n">
         <v>0.59289</v>
@@ -2119,7 +2119,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.16399</v>
+        <v>-2.1641</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2162,7 +2162,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.56165</v>
+        <v>-1.56136</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2205,7 +2205,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.60247</v>
+        <v>-0.60254</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2248,7 +2248,7 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01648</v>
+        <v>-1.01652</v>
       </c>
       <c r="K42" t="n">
         <v>-1.08214</v>
@@ -2291,7 +2291,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.0039</v>
+        <v>-1.00401</v>
       </c>
       <c r="K43" t="n">
         <v>-1.06785</v>
@@ -2334,7 +2334,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.32006</v>
+        <v>1.32003</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2377,7 +2377,7 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68581</v>
+        <v>0.6857799999999999</v>
       </c>
       <c r="K45" t="n">
         <v>-1.24821</v>
@@ -2420,7 +2420,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35214</v>
+        <v>1.35211</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2463,7 +2463,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09787</v>
+        <v>1.09785</v>
       </c>
       <c r="K47" t="n">
         <v>-1.00117</v>
@@ -2506,7 +2506,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.67589</v>
+        <v>2.676</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2549,7 +2549,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51927</v>
+        <v>2.51937</v>
       </c>
       <c r="K49" t="n">
         <v>0.11745</v>
@@ -2592,7 +2592,7 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.41013</v>
+        <v>1.41006</v>
       </c>
       <c r="K50" t="n">
         <v>0.60249</v>
@@ -2635,7 +2635,7 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.18323</v>
+        <v>0.1832</v>
       </c>
       <c r="K51" t="n">
         <v>0.87903</v>
@@ -2678,7 +2678,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.83546</v>
+        <v>-0.8353</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2721,7 +2721,7 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6409899999999999</v>
+        <v>-0.6410400000000001</v>
       </c>
       <c r="K53" t="n">
         <v>0.84188</v>
@@ -2764,7 +2764,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46431</v>
+        <v>-0.46434</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2807,7 +2807,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.25783</v>
+        <v>-1.25792</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2850,7 +2850,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05592</v>
+        <v>-2.05594</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2979,7 +2979,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11228</v>
+        <v>-2.11225</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3022,7 +3022,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08791</v>
+        <v>-1.08786</v>
       </c>
       <c r="K60" t="n">
         <v>-0.30089</v>
@@ -3065,7 +3065,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03248</v>
+        <v>-1.03239</v>
       </c>
       <c r="K61" t="n">
         <v>-0.57351</v>
@@ -3108,7 +3108,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.7448399999999999</v>
+        <v>-0.7448900000000001</v>
       </c>
       <c r="K62" t="n">
         <v>-0.80719</v>
@@ -3151,7 +3151,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.24703</v>
+        <v>1.247</v>
       </c>
       <c r="K63" t="n">
         <v>-0.76733</v>
@@ -3194,7 +3194,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.93801</v>
+        <v>1.938</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.72115</v>
+        <v>0.72113</v>
       </c>
       <c r="K65" t="n">
         <v>-0.28698</v>
@@ -3280,7 +3280,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.08774</v>
+        <v>1.08772</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.17106</v>
+        <v>2.17103</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3366,7 +3366,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45746</v>
+        <v>2.45744</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3409,7 +3409,7 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.30562</v>
+        <v>2.30561</v>
       </c>
       <c r="K69" t="n">
         <v>1.11578</v>
@@ -3452,7 +3452,7 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95784</v>
+        <v>2.95785</v>
       </c>
       <c r="K70" t="n">
         <v>1.12816</v>
@@ -3495,7 +3495,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.1382</v>
+        <v>3.13823</v>
       </c>
       <c r="K71" t="n">
         <v>1.15592</v>
@@ -3538,7 +3538,7 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.07512</v>
+        <v>2.07517</v>
       </c>
       <c r="K72" t="n">
         <v>0.91851</v>
@@ -3581,7 +3581,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.72578</v>
+        <v>3.72589</v>
       </c>
       <c r="K73" t="n">
         <v>0.957</v>
@@ -3624,7 +3624,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.27721</v>
+        <v>3.27714</v>
       </c>
       <c r="K74" t="n">
         <v>0.95813</v>
@@ -3667,7 +3667,7 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52735</v>
+        <v>1.52731</v>
       </c>
       <c r="K75" t="n">
         <v>0.93054</v>
@@ -3710,7 +3710,7 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.24677</v>
+        <v>1.24674</v>
       </c>
       <c r="K76" t="n">
         <v>0.94253</v>
@@ -3753,7 +3753,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.24293</v>
+        <v>1.24292</v>
       </c>
       <c r="K77" t="n">
         <v>0.98116</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03916</v>
+        <v>-0.03917</v>
       </c>
       <c r="K78" t="n">
         <v>1.20199</v>
@@ -3925,7 +3925,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.3861</v>
+        <v>-1.38611</v>
       </c>
       <c r="K81" t="n">
         <v>1.19434</v>
@@ -3968,7 +3968,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.81176</v>
+        <v>-1.81175</v>
       </c>
       <c r="K82" t="n">
         <v>1.45285</v>
@@ -4011,7 +4011,7 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15054</v>
+        <v>-1.15053</v>
       </c>
       <c r="K83" t="n">
         <v>1.71406</v>
@@ -4054,7 +4054,7 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.2921</v>
+        <v>-1.29208</v>
       </c>
       <c r="K84" t="n">
         <v>2.22338</v>
@@ -4097,7 +4097,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01275</v>
+        <v>-2.01271</v>
       </c>
       <c r="K85" t="n">
         <v>2.22049</v>
@@ -4183,7 +4183,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27078</v>
+        <v>-1.27081</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4226,7 +4226,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.97201</v>
+        <v>-0.9720299999999999</v>
       </c>
       <c r="K88" t="n">
         <v>2.45104</v>
@@ -4269,7 +4269,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.5702199999999999</v>
+        <v>-0.57023</v>
       </c>
       <c r="K89" t="n">
         <v>2.48737</v>
@@ -4312,7 +4312,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J90" t="n">
-        <v>0.1742</v>
+        <v>0.17419</v>
       </c>
       <c r="K90" t="n">
         <v>2.01394</v>
@@ -4441,7 +4441,7 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.93906</v>
+        <v>-0.93907</v>
       </c>
       <c r="K93" t="n">
         <v>1.48813</v>
@@ -4484,7 +4484,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.38794</v>
+        <v>-1.38795</v>
       </c>
       <c r="K94" t="n">
         <v>1.26582</v>
@@ -4527,7 +4527,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.0274</v>
+        <v>-2.02736</v>
       </c>
       <c r="K95" t="n">
         <v>1.21282</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.2739</v>
+        <v>-1.27388</v>
       </c>
       <c r="K96" t="n">
         <v>1.20834</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95333</v>
+        <v>-1.95332</v>
       </c>
       <c r="K97" t="n">
         <v>1.47358</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.9598</v>
+        <v>-1.95979</v>
       </c>
       <c r="K98" t="n">
         <v>1.68739</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.0214</v>
+        <v>-2.02142</v>
       </c>
       <c r="K99" t="n">
         <v>1.96426</v>
@@ -4742,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.22754</v>
+        <v>-2.22755</v>
       </c>
       <c r="K100" t="n">
         <v>2.26582</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.63679</v>
+        <v>-1.6368</v>
       </c>
       <c r="K104" t="n">
         <v>3.40463</v>
@@ -4957,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.31031</v>
+        <v>-1.31033</v>
       </c>
       <c r="K105" t="n">
         <v>3.72898</v>
@@ -5000,7 +5000,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.71542</v>
+        <v>-1.71544</v>
       </c>
       <c r="K106" t="n">
         <v>4.01515</v>
@@ -5043,7 +5043,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61228</v>
+        <v>0.61231</v>
       </c>
       <c r="K107" t="n">
         <v>4.36428</v>
@@ -5086,7 +5086,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.65035</v>
+        <v>1.65037</v>
       </c>
       <c r="K108" t="n">
         <v>4.39864</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.3291</v>
+        <v>2.32912</v>
       </c>
       <c r="K109" t="n">
         <v>4.68202</v>
@@ -5172,7 +5172,7 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.66645</v>
+        <v>0.6664600000000001</v>
       </c>
       <c r="K110" t="n">
         <v>4.75359</v>
@@ -5215,7 +5215,7 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.90563</v>
+        <v>0.90561</v>
       </c>
       <c r="K111" t="n">
         <v>4.52399</v>
@@ -5258,7 +5258,7 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.75482</v>
+        <v>1.75481</v>
       </c>
       <c r="K112" t="n">
         <v>4.53026</v>
@@ -5344,7 +5344,7 @@
         <v>0.14859</v>
       </c>
       <c r="J114" t="n">
-        <v>2.87431</v>
+        <v>2.8743</v>
       </c>
       <c r="K114" t="n">
         <v>4.56672</v>
@@ -5430,7 +5430,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.93852</v>
+        <v>3.93851</v>
       </c>
       <c r="K116" t="n">
         <v>4.58996</v>
@@ -5473,7 +5473,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.90908</v>
+        <v>3.90907</v>
       </c>
       <c r="K117" t="n">
         <v>4.53327</v>
@@ -5516,7 +5516,7 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.25932</v>
+        <v>5.25931</v>
       </c>
       <c r="K118" t="n">
         <v>4.33358</v>
@@ -5559,7 +5559,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.59825</v>
+        <v>3.59827</v>
       </c>
       <c r="K119" t="n">
         <v>4.27846</v>
@@ -5602,7 +5602,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.8863</v>
+        <v>1.88631</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5645,7 +5645,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.47363</v>
+        <v>1.47364</v>
       </c>
       <c r="K121" t="n">
         <v>3.50395</v>
@@ -5731,7 +5731,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J123" t="n">
-        <v>3.28843</v>
+        <v>3.28842</v>
       </c>
       <c r="K123" t="n">
         <v>2.88942</v>
@@ -5817,7 +5817,7 @@
         <v>-0.2963</v>
       </c>
       <c r="J125" t="n">
-        <v>0.86489</v>
+        <v>0.86488</v>
       </c>
       <c r="K125" t="n">
         <v>2.26897</v>
@@ -6075,7 +6075,7 @@
         <v>-0.29806</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.44727</v>
+        <v>-6.44726</v>
       </c>
       <c r="K131" t="n">
         <v>0.37089</v>
@@ -6204,7 +6204,7 @@
         <v>-1.3373</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.87933</v>
+        <v>-7.87932</v>
       </c>
       <c r="K134" t="n">
         <v>0.53247</v>
@@ -6376,7 +6376,7 @@
         <v>-2.08024</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.62404</v>
+        <v>-6.62405</v>
       </c>
       <c r="K138" t="n">
         <v>1.69726</v>
@@ -6462,7 +6462,7 @@
         <v>-1.93741</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.06328</v>
+        <v>-5.06327</v>
       </c>
       <c r="K140" t="n">
         <v>2.02625</v>
@@ -6505,7 +6505,7 @@
         <v>-1.79104</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.3158</v>
+        <v>-5.31579</v>
       </c>
       <c r="K141" t="n">
         <v>2.5242</v>
@@ -6634,7 +6634,7 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.45736</v>
+        <v>1.45735</v>
       </c>
       <c r="K144" t="n">
         <v>3.63258</v>
@@ -6720,7 +6720,7 @@
         <v>-1.35542</v>
       </c>
       <c r="J146" t="n">
-        <v>3.67651</v>
+        <v>3.6765</v>
       </c>
       <c r="K146" t="n">
         <v>3.7536</v>
@@ -6763,7 +6763,7 @@
         <v>-1.20664</v>
       </c>
       <c r="J147" t="n">
-        <v>3.14864</v>
+        <v>3.14863</v>
       </c>
       <c r="K147" t="n">
         <v>3.73606</v>
@@ -6806,7 +6806,7 @@
         <v>-0.75643</v>
       </c>
       <c r="J148" t="n">
-        <v>2.77777</v>
+        <v>2.77776</v>
       </c>
       <c r="K148" t="n">
         <v>3.1826</v>
@@ -6978,7 +6978,7 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.63307</v>
+        <v>0.63308</v>
       </c>
       <c r="K152" t="n">
         <v>1.47822</v>
@@ -7021,7 +7021,7 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>0.95986</v>
+        <v>0.95987</v>
       </c>
       <c r="K153" t="n">
         <v>1.21417</v>
@@ -7064,7 +7064,7 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.12166</v>
+        <v>1.12169</v>
       </c>
       <c r="K154" t="n">
         <v>1.42536</v>
@@ -7107,7 +7107,7 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.58975</v>
+        <v>2.58973</v>
       </c>
       <c r="K155" t="n">
         <v>1.45333</v>
@@ -7150,7 +7150,7 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.93552</v>
+        <v>1.9355</v>
       </c>
       <c r="K156" t="n">
         <v>1.45122</v>
@@ -7236,7 +7236,7 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.34562</v>
+        <v>1.34561</v>
       </c>
       <c r="K158" t="n">
         <v>1.70902</v>
@@ -7279,7 +7279,7 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.65366</v>
+        <v>1.65365</v>
       </c>
       <c r="K159" t="n">
         <v>1.97252</v>
@@ -7451,7 +7451,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J163" t="n">
-        <v>4.06002</v>
+        <v>4.06003</v>
       </c>
       <c r="K163" t="n">
         <v>3.95512</v>
@@ -7494,7 +7494,7 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.68899</v>
+        <v>3.68901</v>
       </c>
       <c r="K164" t="n">
         <v>4.25887</v>
@@ -7537,7 +7537,7 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.90114</v>
+        <v>2.90115</v>
       </c>
       <c r="K165" t="n">
         <v>4.28746</v>
@@ -7580,7 +7580,7 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53602</v>
+        <v>2.53605</v>
       </c>
       <c r="K166" t="n">
         <v>4.07215</v>
@@ -7623,7 +7623,7 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.64581</v>
+        <v>3.64578</v>
       </c>
       <c r="K167" t="n">
         <v>3.83471</v>
@@ -7666,7 +7666,7 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.48906</v>
+        <v>3.48904</v>
       </c>
       <c r="K168" t="n">
         <v>4.12632</v>
@@ -7752,7 +7752,7 @@
         <v>-0.15337</v>
       </c>
       <c r="J170" t="n">
-        <v>2.85951</v>
+        <v>2.8595</v>
       </c>
       <c r="K170" t="n">
         <v>3.55701</v>
@@ -7967,7 +7967,7 @@
         <v>1.23267</v>
       </c>
       <c r="J175" t="n">
-        <v>2.85248</v>
+        <v>2.85249</v>
       </c>
       <c r="K175" t="n">
         <v>3.03516</v>
@@ -8053,7 +8053,7 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.89897</v>
+        <v>2.89899</v>
       </c>
       <c r="K177" t="n">
         <v>3.04612</v>
@@ -8096,7 +8096,7 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.84427</v>
+        <v>3.84429</v>
       </c>
       <c r="K178" t="n">
         <v>2.99841</v>
@@ -8139,7 +8139,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.50142</v>
+        <v>2.5014</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8182,7 +8182,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78983</v>
+        <v>1.78981</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8268,7 +8268,7 @@
         <v>1.07527</v>
       </c>
       <c r="J182" t="n">
-        <v>1.44835</v>
+        <v>1.44834</v>
       </c>
       <c r="K182" t="n">
         <v>2.89748</v>
@@ -8311,7 +8311,7 @@
         <v>0.92025</v>
       </c>
       <c r="J183" t="n">
-        <v>1.73083</v>
+        <v>1.73082</v>
       </c>
       <c r="K183" t="n">
         <v>2.6871</v>
@@ -8483,7 +8483,7 @@
         <v>0.30441</v>
       </c>
       <c r="J187" t="n">
-        <v>1.01778</v>
+        <v>1.01779</v>
       </c>
       <c r="K187" t="n">
         <v>2.09522</v>
@@ -8526,7 +8526,7 @@
         <v>0.15198</v>
       </c>
       <c r="J188" t="n">
-        <v>1.00865</v>
+        <v>1.00866</v>
       </c>
       <c r="K188" t="n">
         <v>2.29861</v>
@@ -8569,7 +8569,7 @@
         <v>-0.15152</v>
       </c>
       <c r="J189" t="n">
-        <v>1.05816</v>
+        <v>1.05817</v>
       </c>
       <c r="K189" t="n">
         <v>2.56331</v>
@@ -8612,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.38503</v>
+        <v>0.38504</v>
       </c>
       <c r="K190" t="n">
         <v>2.8595</v>
@@ -8698,7 +8698,7 @@
         <v>0.15175</v>
       </c>
       <c r="J192" t="n">
-        <v>1.49477</v>
+        <v>1.49476</v>
       </c>
       <c r="K192" t="n">
         <v>3.16201</v>
@@ -8956,7 +8956,7 @@
         <v>-0.45593</v>
       </c>
       <c r="J198" t="n">
-        <v>0.25298</v>
+        <v>0.25299</v>
       </c>
       <c r="K198" t="n">
         <v>2.20341</v>
@@ -9558,7 +9558,7 @@
         <v>0.46012</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.24895</v>
+        <v>-3.24896</v>
       </c>
       <c r="K212" t="n">
         <v>-2.26615</v>
@@ -10074,7 +10074,7 @@
         <v>-2.29008</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.54205</v>
+        <v>-7.54206</v>
       </c>
       <c r="K224" t="n">
         <v>-5.60776</v>
@@ -10117,7 +10117,7 @@
         <v>-2.29358</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.08702</v>
+        <v>-7.08703</v>
       </c>
       <c r="K225" t="n">
         <v>-5.37381</v>
@@ -10676,7 +10676,7 @@
         <v>-1.09718</v>
       </c>
       <c r="J238" t="n">
-        <v>0.24352</v>
+        <v>0.24351</v>
       </c>
       <c r="K238" t="n">
         <v>1.44095</v>
@@ -10719,7 +10719,7 @@
         <v>-0.78616</v>
       </c>
       <c r="J239" t="n">
-        <v>1.33085</v>
+        <v>1.33084</v>
       </c>
       <c r="K239" t="n">
         <v>1.48268</v>
@@ -10848,7 +10848,7 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30201</v>
+        <v>2.30206</v>
       </c>
       <c r="K242" t="n">
         <v>2.02206</v>
@@ -10977,7 +10977,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J245" t="n">
-        <v>2.90205</v>
+        <v>2.90206</v>
       </c>
       <c r="K245" t="n">
         <v>1.88152</v>
@@ -11020,7 +11020,7 @@
         <v>-0.47319</v>
       </c>
       <c r="J246" t="n">
-        <v>3.10311</v>
+        <v>3.1031</v>
       </c>
       <c r="K246" t="n">
         <v>1.57793</v>
@@ -11063,7 +11063,7 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46114</v>
+        <v>3.46115</v>
       </c>
       <c r="K247" t="n">
         <v>1.05894</v>
@@ -11106,7 +11106,7 @@
         <v>-0.31646</v>
       </c>
       <c r="J248" t="n">
-        <v>3.4372</v>
+        <v>3.43719</v>
       </c>
       <c r="K248" t="n">
         <v>1.05713</v>
@@ -11149,7 +11149,7 @@
         <v>-0.31696</v>
       </c>
       <c r="J249" t="n">
-        <v>4.28997</v>
+        <v>4.28995</v>
       </c>
       <c r="K249" t="n">
         <v>0.82133</v>
@@ -11192,7 +11192,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36586</v>
+        <v>5.36584</v>
       </c>
       <c r="K250" t="n">
         <v>1.10007</v>
@@ -11235,7 +11235,7 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.69154</v>
+        <v>4.69151</v>
       </c>
       <c r="K251" t="n">
         <v>1.33305</v>
@@ -11278,7 +11278,7 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.78753</v>
+        <v>4.78751</v>
       </c>
       <c r="K252" t="n">
         <v>1.53273</v>
@@ -11321,7 +11321,7 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94874</v>
+        <v>4.94873</v>
       </c>
       <c r="K253" t="n">
         <v>2.11657</v>
@@ -11364,7 +11364,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.60823</v>
+        <v>5.60838</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11407,7 +11407,7 @@
         <v>-2.36967</v>
       </c>
       <c r="J255" t="n">
-        <v>5.94848</v>
+        <v>5.94847</v>
       </c>
       <c r="K255" t="n">
         <v>2.39078</v>
@@ -11493,7 +11493,7 @@
         <v>-2.8481</v>
       </c>
       <c r="J257" t="n">
-        <v>6.14194</v>
+        <v>6.14193</v>
       </c>
       <c r="K257" t="n">
         <v>2.75433</v>
@@ -11536,7 +11536,7 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59274</v>
+        <v>6.59272</v>
       </c>
       <c r="K258" t="n">
         <v>3.32875</v>
@@ -11579,7 +11579,7 @@
         <v>-3.01109</v>
       </c>
       <c r="J259" t="n">
-        <v>6.62992</v>
+        <v>6.62991</v>
       </c>
       <c r="K259" t="n">
         <v>3.92676</v>
@@ -11622,7 +11622,7 @@
         <v>-3.01587</v>
       </c>
       <c r="J260" t="n">
-        <v>6.90734</v>
+        <v>6.90732</v>
       </c>
       <c r="K260" t="n">
         <v>4.4273</v>
@@ -11665,7 +11665,7 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46888</v>
+        <v>5.46886</v>
       </c>
       <c r="K261" t="n">
         <v>5.34278</v>
@@ -11708,7 +11708,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06064</v>
+        <v>4.06061</v>
       </c>
       <c r="K262" t="n">
         <v>5.81027</v>
@@ -11751,7 +11751,7 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.98677</v>
+        <v>3.98671</v>
       </c>
       <c r="K263" t="n">
         <v>5.86192</v>
@@ -11794,7 +11794,7 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.80943</v>
+        <v>3.80941</v>
       </c>
       <c r="K264" t="n">
         <v>5.94402</v>
@@ -11837,7 +11837,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70186</v>
+        <v>3.70187</v>
       </c>
       <c r="K265" t="n">
         <v>5.63483</v>
@@ -11880,7 +11880,7 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87391</v>
+        <v>2.87409</v>
       </c>
       <c r="K266" t="n">
         <v>5.6398</v>
@@ -11923,7 +11923,7 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68869</v>
+        <v>2.68872</v>
       </c>
       <c r="K267" t="n">
         <v>5.62042</v>
@@ -11966,7 +11966,7 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.18501</v>
+        <v>2.18502</v>
       </c>
       <c r="K268" t="n">
         <v>5.87932</v>
@@ -12009,7 +12009,7 @@
         <v>-1.30293</v>
       </c>
       <c r="J269" t="n">
-        <v>2.61293</v>
+        <v>2.61292</v>
       </c>
       <c r="K269" t="n">
         <v>5.82315</v>
@@ -12052,7 +12052,7 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24406</v>
+        <v>2.24404</v>
       </c>
       <c r="K270" t="n">
         <v>5.58396</v>
@@ -12095,7 +12095,7 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.02544</v>
+        <v>2.02541</v>
       </c>
       <c r="K271" t="n">
         <v>5.54028</v>
@@ -12138,7 +12138,7 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.06774</v>
+        <v>2.06772</v>
       </c>
       <c r="K272" t="n">
         <v>5.03896</v>
@@ -12181,7 +12181,7 @@
         <v>-0.32787</v>
       </c>
       <c r="J273" t="n">
-        <v>2.87071</v>
+        <v>2.87066</v>
       </c>
       <c r="K273" t="n">
         <v>4.36879</v>
@@ -12224,7 +12224,7 @@
         <v>-0.16393</v>
       </c>
       <c r="J274" t="n">
-        <v>2.13197</v>
+        <v>2.13193</v>
       </c>
       <c r="K274" t="n">
         <v>3.66414</v>
@@ -12267,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.59078</v>
+        <v>2.59072</v>
       </c>
       <c r="K275" t="n">
         <v>3.36017</v>
@@ -12310,7 +12310,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.64218</v>
+        <v>2.64211</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12353,7 +12353,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55372</v>
+        <v>2.55363</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12396,7 +12396,7 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57081</v>
+        <v>3.57137</v>
       </c>
       <c r="K278" t="n">
         <v>2.88074</v>
@@ -12439,7 +12439,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10624</v>
+        <v>3.10616</v>
       </c>
       <c r="K279" t="n">
         <v>2.73892</v>
@@ -12482,7 +12482,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13348</v>
+        <v>3.13342</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12525,7 +12525,7 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52934</v>
+        <v>2.52931</v>
       </c>
       <c r="K281" t="n">
         <v>2.48447</v>
@@ -12568,7 +12568,7 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46746</v>
+        <v>2.46744</v>
       </c>
       <c r="K282" t="n">
         <v>2.70244</v>
@@ -12611,7 +12611,7 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.70785</v>
+        <v>1.70778</v>
       </c>
       <c r="K283" t="n">
         <v>2.46068</v>
@@ -12654,7 +12654,7 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26774</v>
+        <v>1.26768</v>
       </c>
       <c r="K284" t="n">
         <v>2.67797</v>
@@ -12697,7 +12697,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55166</v>
+        <v>0.55162</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12740,7 +12740,7 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35723</v>
+        <v>1.35726</v>
       </c>
       <c r="K286" t="n">
         <v>3.24569</v>
@@ -12783,7 +12783,7 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.27739</v>
+        <v>1.27727</v>
       </c>
       <c r="K287" t="n">
         <v>3.51063</v>
@@ -12826,7 +12826,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.52999</v>
+        <v>0.5299199999999999</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12869,7 +12869,7 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27373</v>
+        <v>-0.27367</v>
       </c>
       <c r="K289" t="n">
         <v>3.51163</v>
@@ -12912,7 +12912,7 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.04026</v>
+        <v>-0.03973</v>
       </c>
       <c r="K290" t="n">
         <v>3.83219</v>
@@ -12955,7 +12955,7 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23625</v>
+        <v>-0.2363</v>
       </c>
       <c r="K291" t="n">
         <v>3.85604</v>
@@ -12998,7 +12998,7 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.73797</v>
+        <v>-0.73803</v>
       </c>
       <c r="K292" t="n">
         <v>3.62291</v>
@@ -13041,7 +13041,7 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52197</v>
+        <v>-0.52202</v>
       </c>
       <c r="K293" t="n">
         <v>3.87311</v>
@@ -13084,7 +13084,7 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82324</v>
+        <v>-0.82335</v>
       </c>
       <c r="K294" t="n">
         <v>3.87626</v>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05949</v>
+        <v>-0.05969</v>
       </c>
       <c r="K295" t="n">
         <v>4.15332</v>
@@ -13170,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.27693</v>
+        <v>0.27681</v>
       </c>
       <c r="K296" t="n">
         <v>4.17488</v>
@@ -13213,7 +13213,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.31426</v>
+        <v>0.31422</v>
       </c>
       <c r="K297" t="n">
         <v>3.95179</v>
@@ -13256,7 +13256,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.38255</v>
+        <v>0.38257</v>
       </c>
       <c r="K298" t="n">
         <v>4.13246</v>
@@ -13299,7 +13299,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.00831</v>
+        <v>-0.00847</v>
       </c>
       <c r="K299" t="n">
         <v>3.9212</v>
@@ -13342,7 +13342,7 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.00327</v>
+        <v>1.00398</v>
       </c>
       <c r="K300" t="n">
         <v>3.5896</v>
@@ -13385,7 +13385,7 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.955</v>
+        <v>1.95493</v>
       </c>
       <c r="K301" t="n">
         <v>3.94713</v>
@@ -13428,7 +13428,7 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.4773</v>
+        <v>1.47766</v>
       </c>
       <c r="K302" t="n">
         <v>3.5803</v>
@@ -13471,7 +13471,7 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98055</v>
+        <v>1.98045</v>
       </c>
       <c r="K303" t="n">
         <v>3.337</v>
@@ -13514,7 +13514,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.72963</v>
+        <v>2.72947</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13557,7 +13557,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.50391</v>
+        <v>2.50372</v>
       </c>
       <c r="K305" t="n">
         <v>3.30021</v>
@@ -13600,7 +13600,7 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97719</v>
+        <v>2.97691</v>
       </c>
       <c r="K306" t="n">
         <v>3.02342</v>
@@ -13643,7 +13643,7 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.46935</v>
+        <v>3.46899</v>
       </c>
       <c r="K307" t="n">
         <v>2.72177</v>
@@ -13686,7 +13686,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.01393</v>
+        <v>3.0137</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13729,7 +13729,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06854</v>
+        <v>3.06856</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13772,7 +13772,7 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.61201</v>
+        <v>2.61226</v>
       </c>
       <c r="K310" t="n">
         <v>2.76807</v>
@@ -13815,7 +13815,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99484</v>
+        <v>2.99505</v>
       </c>
       <c r="K311" t="n">
         <v>2.70029</v>
@@ -13858,7 +13858,7 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.75154</v>
+        <v>2.75263</v>
       </c>
       <c r="K312" t="n">
         <v>2.99187</v>
@@ -13901,7 +13901,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.39412</v>
+        <v>2.39437</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13944,7 +13944,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.9261</v>
+        <v>1.92594</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13987,7 +13987,7 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.40944</v>
+        <v>2.40939</v>
       </c>
       <c r="K315" t="n">
         <v>3.24698</v>
@@ -14030,7 +14030,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.6256</v>
+        <v>2.62531</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14073,7 +14073,7 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43489</v>
+        <v>3.4343</v>
       </c>
       <c r="K317" t="n">
         <v>3.28303</v>
@@ -14116,7 +14116,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.37222</v>
+        <v>3.37161</v>
       </c>
       <c r="K318" t="n">
         <v>3.52516</v>
@@ -14159,7 +14159,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.14745</v>
+        <v>3.14675</v>
       </c>
       <c r="K319" t="n">
         <v>3.82042</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.12935</v>
+        <v>3.13</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14245,7 +14245,7 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.18136</v>
+        <v>3.17867</v>
       </c>
       <c r="K321" t="n">
         <v>3.64797</v>
@@ -14288,7 +14288,7 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.79411</v>
+        <v>3.79744</v>
       </c>
       <c r="K322" t="n">
         <v>3.74826</v>
@@ -14331,7 +14331,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.93054</v>
+        <v>3.93143</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14374,7 +14374,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.68577</v>
+        <v>3.6868</v>
       </c>
       <c r="K324" t="n">
         <v>3.45127</v>
@@ -14417,7 +14417,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.30316</v>
+        <v>3.30338</v>
       </c>
       <c r="K325" t="n">
         <v>3.22274</v>
@@ -14460,7 +14460,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86446</v>
+        <v>2.86408</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14503,7 +14503,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05678</v>
+        <v>2.05627</v>
       </c>
       <c r="K327" t="n">
         <v>2.63791</v>
@@ -14546,7 +14546,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82405</v>
+        <v>1.82324</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14589,7 +14589,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.15963</v>
+        <v>1.15874</v>
       </c>
       <c r="K329" t="n">
         <v>2.05076</v>
@@ -14632,7 +14632,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15422</v>
+        <v>1.15327</v>
       </c>
       <c r="K330" t="n">
         <v>1.53231</v>
@@ -14675,7 +14675,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.72582</v>
+        <v>0.72461</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14718,7 +14718,7 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13501</v>
+        <v>1.13645</v>
       </c>
       <c r="K332" t="n">
         <v>0.95682</v>
@@ -14761,7 +14761,7 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.19734</v>
+        <v>1.1944</v>
       </c>
       <c r="K333" t="n">
         <v>0.54018</v>
@@ -14804,7 +14804,7 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05357</v>
+        <v>1.05802</v>
       </c>
       <c r="K334" t="n">
         <v>-0.06722</v>
@@ -14847,7 +14847,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.73386</v>
+        <v>1.73509</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14890,7 +14890,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.43255</v>
+        <v>-2.4314</v>
       </c>
       <c r="K336" t="n">
         <v>-0.285</v>
@@ -14933,7 +14933,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74526</v>
+        <v>2.74565</v>
       </c>
       <c r="K337" t="n">
         <v>-0.32644</v>
@@ -14976,7 +14976,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.5337499999999999</v>
+        <v>-0.53399</v>
       </c>
       <c r="K338" t="n">
         <v>-0.36041</v>
@@ -15019,7 +15019,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09507</v>
+        <v>-0.09637999999999999</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15062,7 +15062,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.52865</v>
+        <v>-0.53061</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15105,7 +15105,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.2271</v>
+        <v>-1.22779</v>
       </c>
       <c r="K341" t="n">
         <v>0.40191</v>
@@ -15148,7 +15148,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44528</v>
+        <v>-1.44619</v>
       </c>
       <c r="K342" t="n">
         <v>0.6959</v>
@@ -15191,7 +15191,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09516</v>
+        <v>-1.09637</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15234,7 +15234,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.75488</v>
+        <v>-0.75388</v>
       </c>
       <c r="K344" t="n">
         <v>1.21614</v>
@@ -15277,7 +15277,7 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.69286</v>
+        <v>-0.69712</v>
       </c>
       <c r="K345" t="n">
         <v>1.67058</v>
@@ -15320,7 +15320,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.13859</v>
+        <v>-0.13102</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15363,7 +15363,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.02748</v>
+        <v>-1.02479</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15406,7 +15406,7 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.99022</v>
+        <v>2.98994</v>
       </c>
       <c r="K348" t="n">
         <v>2.52186</v>
@@ -15449,7 +15449,7 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.39386</v>
+        <v>-1.39401</v>
       </c>
       <c r="K349" t="n">
         <v>2.79644</v>
@@ -15492,7 +15492,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.55932</v>
+        <v>2.55899</v>
       </c>
       <c r="K350" t="n">
         <v>3.17127</v>
@@ -15535,7 +15535,7 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.77967</v>
+        <v>1.77797</v>
       </c>
       <c r="K351" t="n">
         <v>2.91653</v>
@@ -15578,7 +15578,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.56529</v>
+        <v>1.56283</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15621,7 +15621,7 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.28299</v>
+        <v>-49.28514</v>
       </c>
       <c r="K353" t="n">
         <v>-38.87916</v>
@@ -15664,7 +15664,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.49267</v>
+        <v>-69.49581000000001</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15707,7 +15707,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.08372</v>
+        <v>-70.08741999999999</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15750,7 +15750,7 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73495</v>
+        <v>-74.73260000000001</v>
       </c>
       <c r="K356" t="n">
         <v>-30.14584</v>
@@ -15793,7 +15793,7 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.85814999999999</v>
+        <v>-74.86651999999999</v>
       </c>
       <c r="K357" t="n">
         <v>-25.53877</v>
@@ -15836,7 +15836,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.53267</v>
+        <v>-76.51528</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15879,7 +15879,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.65222</v>
+        <v>-66.64610999999999</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15922,7 +15922,7 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.85709</v>
+        <v>-56.85545</v>
       </c>
       <c r="K360" t="n">
         <v>-20.39193</v>
@@ -15965,7 +15965,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.24996</v>
+        <v>-53.24953</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -617,7 +617,7 @@
         <v>7.55487</v>
       </c>
       <c r="K4" t="n">
-        <v>2.13214</v>
+        <v>2.14558</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>4.61374</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47346</v>
+        <v>1.46043</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>7.05474</v>
       </c>
       <c r="K9" t="n">
-        <v>1.21062</v>
+        <v>1.2238</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>8.03464</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7003</v>
+        <v>0.70039</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>3.00208</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05167</v>
+        <v>0.0646</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>5.26329</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.68662</v>
+        <v>-1.6995</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>4.22917</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9802</v>
+        <v>-1.99306</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>0.94776</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.53148</v>
+        <v>-2.53181</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>-2.86878</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.39536</v>
+        <v>-2.38279</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>-3.72208</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.93924</v>
+        <v>-1.95217</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>-6.68666</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.50532</v>
+        <v>-1.5183</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>-8.495990000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3143</v>
+        <v>0.32744</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>-7.96451</v>
       </c>
       <c r="K30" t="n">
-        <v>0.61656</v>
+        <v>0.62976</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>-7.24778</v>
       </c>
       <c r="K31" t="n">
-        <v>1.1193</v>
+        <v>1.10614</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>-7.58168</v>
       </c>
       <c r="K32" t="n">
-        <v>1.33158</v>
+        <v>1.34494</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>-7.38123</v>
       </c>
       <c r="K37" t="n">
-        <v>1.02835</v>
+        <v>1.04167</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>-3.30761</v>
       </c>
       <c r="K38" t="n">
-        <v>0.59289</v>
+        <v>0.59296</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>-1.00401</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.06785</v>
+        <v>-1.05496</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>1.41006</v>
       </c>
       <c r="K50" t="n">
-        <v>0.60249</v>
+        <v>0.6156700000000001</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>1.08772</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-0.01307</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>1.24292</v>
       </c>
       <c r="K77" t="n">
-        <v>0.98116</v>
+        <v>0.9680800000000001</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>-0.03917</v>
       </c>
       <c r="K78" t="n">
-        <v>1.20199</v>
+        <v>1.21521</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>-0.57023</v>
       </c>
       <c r="K89" t="n">
-        <v>2.48737</v>
+        <v>2.50065</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>-1.95979</v>
       </c>
       <c r="K98" t="n">
-        <v>1.68739</v>
+        <v>1.6747</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>-1.13135</v>
       </c>
       <c r="K102" t="n">
-        <v>2.80942</v>
+        <v>2.79676</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>0.61231</v>
       </c>
       <c r="K107" t="n">
-        <v>4.36428</v>
+        <v>4.35166</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>2.32912</v>
       </c>
       <c r="K109" t="n">
-        <v>4.68202</v>
+        <v>4.6695</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>0.6664600000000001</v>
       </c>
       <c r="K110" t="n">
-        <v>4.75359</v>
+        <v>4.75418</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>2.8743</v>
       </c>
       <c r="K114" t="n">
-        <v>4.56672</v>
+        <v>4.57959</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>3.59827</v>
       </c>
       <c r="K119" t="n">
-        <v>4.27846</v>
+        <v>4.29107</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>1.47364</v>
       </c>
       <c r="K121" t="n">
-        <v>3.50395</v>
+        <v>3.51633</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>3.3177</v>
       </c>
       <c r="K122" t="n">
-        <v>2.89424</v>
+        <v>2.90649</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>0.86488</v>
       </c>
       <c r="K125" t="n">
-        <v>2.26897</v>
+        <v>2.25715</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>-0.16224</v>
       </c>
       <c r="K128" t="n">
-        <v>1.65009</v>
+        <v>1.63839</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>-6.82901</v>
       </c>
       <c r="K137" t="n">
-        <v>1.2942</v>
+        <v>1.30591</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>-5.06327</v>
       </c>
       <c r="K140" t="n">
-        <v>2.02625</v>
+        <v>2.038</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>-7.54206</v>
       </c>
       <c r="K224" t="n">
-        <v>-5.60776</v>
+        <v>-5.59755</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>-1.42159</v>
       </c>
       <c r="K236" t="n">
-        <v>1.34185</v>
+        <v>1.33088</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>0.24351</v>
       </c>
       <c r="K238" t="n">
-        <v>1.44095</v>
+        <v>1.45179</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>5.36584</v>
       </c>
       <c r="K250" t="n">
-        <v>1.10007</v>
+        <v>1.08928</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>4.94873</v>
       </c>
       <c r="K253" t="n">
-        <v>2.11657</v>
+        <v>2.12721</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>5.66685</v>
       </c>
       <c r="K256" t="n">
-        <v>2.43001</v>
+        <v>2.44057</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>4.06061</v>
       </c>
       <c r="K262" t="n">
-        <v>5.81027</v>
+        <v>5.82083</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>3.70187</v>
       </c>
       <c r="K265" t="n">
-        <v>5.63483</v>
+        <v>5.62383</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>2.68872</v>
       </c>
       <c r="K267" t="n">
-        <v>5.62042</v>
+        <v>5.63075</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>2.18502</v>
       </c>
       <c r="K268" t="n">
-        <v>5.87932</v>
+        <v>5.8684</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>2.02541</v>
       </c>
       <c r="K271" t="n">
-        <v>5.54028</v>
+        <v>5.55046</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>2.13193</v>
       </c>
       <c r="K274" t="n">
-        <v>3.66414</v>
+        <v>3.65379</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>2.59072</v>
       </c>
       <c r="K275" t="n">
-        <v>3.36017</v>
+        <v>3.37012</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>3.10616</v>
       </c>
       <c r="K279" t="n">
-        <v>2.73892</v>
+        <v>2.72887</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>1.70778</v>
       </c>
       <c r="K283" t="n">
-        <v>2.46068</v>
+        <v>2.45079</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>1.27727</v>
       </c>
       <c r="K287" t="n">
-        <v>3.51063</v>
+        <v>3.50067</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>-0.00847</v>
       </c>
       <c r="K299" t="n">
-        <v>3.9212</v>
+        <v>3.9305</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>1.98045</v>
       </c>
       <c r="K303" t="n">
-        <v>3.337</v>
+        <v>3.34617</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>2.50372</v>
       </c>
       <c r="K305" t="n">
-        <v>3.30021</v>
+        <v>3.30933</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>3.46899</v>
       </c>
       <c r="K307" t="n">
-        <v>2.72177</v>
+        <v>2.73081</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>2.99505</v>
       </c>
       <c r="K311" t="n">
-        <v>2.70029</v>
+        <v>2.6911</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>2.40939</v>
       </c>
       <c r="K315" t="n">
-        <v>3.24698</v>
+        <v>3.23782</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>3.4343</v>
       </c>
       <c r="K317" t="n">
-        <v>3.28303</v>
+        <v>3.27391</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>3.37161</v>
       </c>
       <c r="K318" t="n">
-        <v>3.52516</v>
+        <v>3.53397</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>3.14675</v>
       </c>
       <c r="K319" t="n">
-        <v>3.82042</v>
+        <v>3.81128</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>3.6868</v>
       </c>
       <c r="K324" t="n">
-        <v>3.45127</v>
+        <v>3.45994</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>3.30338</v>
       </c>
       <c r="K325" t="n">
-        <v>3.22274</v>
+        <v>3.23138</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>1.15327</v>
       </c>
       <c r="K330" t="n">
-        <v>1.53231</v>
+        <v>1.53218</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>-2.4314</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.285</v>
+        <v>-0.29335</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>2.74565</v>
       </c>
       <c r="K337" t="n">
-        <v>-0.32644</v>
+        <v>-0.33478</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>-0.53399</v>
       </c>
       <c r="K338" t="n">
-        <v>-0.36041</v>
+        <v>-0.35202</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>-1.22779</v>
       </c>
       <c r="K341" t="n">
-        <v>0.40191</v>
+        <v>0.41028</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>-1.44619</v>
       </c>
       <c r="K342" t="n">
-        <v>0.6959</v>
+        <v>0.68746</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>2.55899</v>
       </c>
       <c r="K350" t="n">
-        <v>3.17127</v>
+        <v>3.16259</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>-49.28514</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.87916</v>
+        <v>-38.87592</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>-56.85545</v>
       </c>
       <c r="K360" t="n">
-        <v>-20.39193</v>
+        <v>-20.38373</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.67417778382043</v>
+        <v>11.68189845408354</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37074238807041</v>
+        <v>11.37704061536031</v>
       </c>
       <c r="D242" t="n">
-        <v>10.14503721815558</v>
+        <v>10.14547716866296</v>
       </c>
       <c r="E242" t="n">
-        <v>7.262872976688017</v>
+        <v>7.26289064612049</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.26209756792835</v>
+        <v>12.26877426688637</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43449556747156</v>
+        <v>12.43870169460124</v>
       </c>
       <c r="D243" t="n">
-        <v>7.820167887085905</v>
+        <v>7.82059357985958</v>
       </c>
       <c r="E243" t="n">
-        <v>8.995076033640981</v>
+        <v>8.995099556990628</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.972901415826313</v>
+        <v>3.971671261934961</v>
       </c>
       <c r="C244" t="n">
-        <v>7.191181621875664</v>
+        <v>7.190944498220309</v>
       </c>
       <c r="D244" t="n">
-        <v>6.051095308572063</v>
+        <v>6.051581228743275</v>
       </c>
       <c r="E244" t="n">
-        <v>8.711423834889587</v>
+        <v>8.711435554023206</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.845644042406327</v>
+        <v>3.844230959048445</v>
       </c>
       <c r="C245" t="n">
-        <v>7.413460331270105</v>
+        <v>7.412568764707506</v>
       </c>
       <c r="D245" t="n">
-        <v>4.806713145499408</v>
+        <v>4.807345503318827</v>
       </c>
       <c r="E245" t="n">
-        <v>8.570555122347322</v>
+        <v>8.570664447331144</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1788136033900933</v>
+        <v>0.1746059586783977</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6935244988788947</v>
+        <v>-0.6970826731663493</v>
       </c>
       <c r="D246" t="n">
-        <v>1.811626162882729</v>
+        <v>1.812248346328871</v>
       </c>
       <c r="E246" t="n">
-        <v>9.479263021670526</v>
+        <v>9.479326783347464</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,13 +11039,13 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.347141210321722</v>
+        <v>-0.3575387800912155</v>
       </c>
       <c r="C247" t="n">
-        <v>2.284044807873609</v>
+        <v>2.276265546612177</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.624692766657598</v>
+        <v>-1.624088088035447</v>
       </c>
       <c r="E247" t="n">
         <v>9.101746752017847</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.544467291889984</v>
+        <v>-1.549391102962039</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.317855527533808</v>
+        <v>-2.321810077167796</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.091872500069637</v>
+        <v>-3.091308659376135</v>
       </c>
       <c r="E248" t="n">
-        <v>8.145625017041414</v>
+        <v>8.145613608571045</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.450391980051258</v>
+        <v>1.449506209440443</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.236877565936966</v>
+        <v>-0.2396204609760533</v>
       </c>
       <c r="D249" t="n">
-        <v>2.499899079010315</v>
+        <v>2.499873962137689</v>
       </c>
       <c r="E249" t="n">
-        <v>7.144247299620488</v>
+        <v>7.144218945607261</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,13 +11168,13 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.826511775231634</v>
+        <v>4.830715185770695</v>
       </c>
       <c r="C250" t="n">
-        <v>4.687080695301771</v>
+        <v>4.689235317940166</v>
       </c>
       <c r="D250" t="n">
-        <v>6.342316644573742</v>
+        <v>6.342549223833593</v>
       </c>
       <c r="E250" t="n">
         <v>8.28312778415885</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8324416811904101</v>
+        <v>0.8343685950976454</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477418830945543</v>
+        <v>1.477722527224135</v>
       </c>
       <c r="D251" t="n">
-        <v>2.657816797714219</v>
+        <v>2.658102547625552</v>
       </c>
       <c r="E251" t="n">
-        <v>8.43011939551106</v>
+        <v>8.430136252299825</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.654033653859368</v>
+        <v>3.652688404469995</v>
       </c>
       <c r="C252" t="n">
-        <v>2.968810336078143</v>
+        <v>2.969030747979962</v>
       </c>
       <c r="D252" t="n">
-        <v>3.945807579967586</v>
+        <v>3.946127309757541</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19879533224208</v>
+        <v>10.19891167494602</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.117049051357038</v>
+        <v>7.119844406445042</v>
       </c>
       <c r="C253" t="n">
-        <v>8.446068288753805</v>
+        <v>8.449334944398167</v>
       </c>
       <c r="D253" t="n">
-        <v>3.630215279256932</v>
+        <v>3.630548601625216</v>
       </c>
       <c r="E253" t="n">
-        <v>7.932993375049024</v>
+        <v>7.932982359259388</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.371096258452314</v>
+        <v>7.373408662070369</v>
       </c>
       <c r="C254" t="n">
-        <v>7.314251708787101</v>
+        <v>7.315520843279044</v>
       </c>
       <c r="D254" t="n">
-        <v>5.753361883797137</v>
+        <v>5.753289658935645</v>
       </c>
       <c r="E254" t="n">
-        <v>8.193739605182371</v>
+        <v>8.193760219446933</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449166834524122</v>
+        <v>5.449742892210274</v>
       </c>
       <c r="C255" t="n">
-        <v>5.86913443731174</v>
+        <v>5.869509497095571</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549620812493503</v>
+        <v>2.549617529964032</v>
       </c>
       <c r="E255" t="n">
-        <v>6.401510569421354</v>
+        <v>6.40151997885825</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.70138421818683</v>
+        <v>11.7053001485655</v>
       </c>
       <c r="C256" t="n">
-        <v>9.84502028133738</v>
+        <v>9.848919637091157</v>
       </c>
       <c r="D256" t="n">
-        <v>5.668087532520971</v>
+        <v>5.668065689639246</v>
       </c>
       <c r="E256" t="n">
-        <v>7.1647155964361</v>
+        <v>7.164752554208631</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.777498104875914</v>
+        <v>8.775354100800925</v>
       </c>
       <c r="C257" t="n">
-        <v>8.536667628968786</v>
+        <v>8.537266855787106</v>
       </c>
       <c r="D257" t="n">
-        <v>5.103768045569579</v>
+        <v>5.10388011464753</v>
       </c>
       <c r="E257" t="n">
-        <v>7.456264638848564</v>
+        <v>7.456230632155414</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.91992389308072</v>
+        <v>11.92018340905716</v>
       </c>
       <c r="C258" t="n">
-        <v>11.7507009140221</v>
+        <v>11.75119549773758</v>
       </c>
       <c r="D258" t="n">
-        <v>8.786089336321412</v>
+        <v>8.786242632180663</v>
       </c>
       <c r="E258" t="n">
-        <v>7.927117373357873</v>
+        <v>7.927118051159909</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45070257278276</v>
+        <v>11.45305995524801</v>
       </c>
       <c r="C259" t="n">
-        <v>9.100509329200746</v>
+        <v>9.101881555303937</v>
       </c>
       <c r="D259" t="n">
-        <v>7.833094809149532</v>
+        <v>7.833268389272141</v>
       </c>
       <c r="E259" t="n">
-        <v>8.26126865264516</v>
+        <v>8.261295135653924</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.849563691567663</v>
+        <v>8.847505634475006</v>
       </c>
       <c r="C260" t="n">
-        <v>9.290839253703552</v>
+        <v>9.290142441579107</v>
       </c>
       <c r="D260" t="n">
-        <v>8.069120360173244</v>
+        <v>8.069362232347309</v>
       </c>
       <c r="E260" t="n">
-        <v>8.665967256418238</v>
+        <v>8.66601036730752</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52850306372788</v>
+        <v>12.52715500892678</v>
       </c>
       <c r="C261" t="n">
-        <v>10.31190247450662</v>
+        <v>10.3124796851737</v>
       </c>
       <c r="D261" t="n">
-        <v>5.621550978623069</v>
+        <v>5.62124196839362</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40858540517957</v>
+        <v>10.40864637914667</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,13 +11684,13 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.795860620270666</v>
+        <v>6.793904142935547</v>
       </c>
       <c r="C262" t="n">
-        <v>6.466847670750786</v>
+        <v>6.466551096859718</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8221656546746114</v>
+        <v>-0.8223236309656046</v>
       </c>
       <c r="E262" t="n">
         <v>8.713928250245907</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.094026357819285</v>
+        <v>9.093716544207563</v>
       </c>
       <c r="C263" t="n">
-        <v>7.43320844702946</v>
+        <v>7.433643811964363</v>
       </c>
       <c r="D263" t="n">
-        <v>3.149711747763284</v>
+        <v>3.149611097634941</v>
       </c>
       <c r="E263" t="n">
-        <v>8.716270071275801</v>
+        <v>8.716227259635478</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42001305954179</v>
+        <v>13.42330074304803</v>
       </c>
       <c r="C264" t="n">
-        <v>11.2691537903866</v>
+        <v>11.27168616393612</v>
       </c>
       <c r="D264" t="n">
-        <v>4.656529273757815</v>
+        <v>4.656474829981638</v>
       </c>
       <c r="E264" t="n">
-        <v>6.305037092874644</v>
+        <v>6.304904751577078</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.053791661854493</v>
+        <v>8.05431026041199</v>
       </c>
       <c r="C265" t="n">
-        <v>5.793953499978488</v>
+        <v>5.794201852986847</v>
       </c>
       <c r="D265" t="n">
-        <v>2.715987449112234</v>
+        <v>2.715965531109465</v>
       </c>
       <c r="E265" t="n">
-        <v>7.346489997066752</v>
+        <v>7.346403994682604</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.579874543289828</v>
+        <v>2.578804747448493</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2238938122266609</v>
+        <v>-0.2263985029172688</v>
       </c>
       <c r="D266" t="n">
-        <v>2.195884540302706</v>
+        <v>2.195865627700488</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01831523953998</v>
+        <v>12.01834649601139</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.102282139233827</v>
+        <v>5.100448051616002</v>
       </c>
       <c r="C267" t="n">
-        <v>1.659364537596941</v>
+        <v>1.656602329508838</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454352212990863</v>
+        <v>3.454399544308417</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53884482000609</v>
+        <v>13.53891169325403</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.826236906040161</v>
+        <v>5.82847199666281</v>
       </c>
       <c r="C268" t="n">
-        <v>3.421776881770167</v>
+        <v>3.42243740751873</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9115311538112625</v>
+        <v>0.9115792515223875</v>
       </c>
       <c r="E268" t="n">
-        <v>15.11116677266673</v>
+        <v>15.11122531784159</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.377073358679538</v>
+        <v>2.374639694572434</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7171744779741251</v>
+        <v>0.7155894083662906</v>
       </c>
       <c r="D269" t="n">
-        <v>2.950664219008026</v>
+        <v>2.950853096392159</v>
       </c>
       <c r="E269" t="n">
-        <v>10.12965752915582</v>
+        <v>10.1296012150043</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.696182041422213</v>
+        <v>2.697653183493065</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3387059353884503</v>
+        <v>0.3388202160738318</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.51628555858796</v>
+        <v>-1.516127893222219</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77437654043329</v>
+        <v>11.7743401745648</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.111379805751558</v>
+        <v>4.115679230827718</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272260905837565</v>
+        <v>3.274796397510915</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.168268294446173</v>
+        <v>-1.168144710278418</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72620617854612</v>
+        <v>12.72621774271867</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.813325831448267</v>
+        <v>3.815043508503257</v>
       </c>
       <c r="C272" t="n">
-        <v>2.834296649385015</v>
+        <v>2.835808238413495</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.928192867229007</v>
+        <v>-2.927982069196322</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49979856125165</v>
+        <v>12.49983860635102</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.047212337226734</v>
+        <v>2.04477691281213</v>
       </c>
       <c r="C273" t="n">
-        <v>2.703449335132557</v>
+        <v>2.704360480784773</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.112985705228652</v>
+        <v>-0.1134281553907934</v>
       </c>
       <c r="E273" t="n">
-        <v>12.16656668560827</v>
+        <v>12.16663029830747</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1431895005270412</v>
+        <v>-0.145442471719881</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2300568167537431</v>
+        <v>0.2291508214349314</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03414248396977904</v>
+        <v>0.03398004400991805</v>
       </c>
       <c r="E274" t="n">
-        <v>11.93158694929319</v>
+        <v>11.93164931638233</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3202841500441811</v>
+        <v>-0.3204171502744435</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4544030122679121</v>
+        <v>-0.4546589423060965</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.020930134371879</v>
+        <v>-2.021102015694498</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91070982127855</v>
+        <v>10.91076962089756</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.992938493259157</v>
+        <v>-3.994491257617216</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.153920932076172</v>
+        <v>-4.156301146443575</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.716138521700141</v>
+        <v>-3.716279810981526</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912259939665601</v>
+        <v>8.912261625586094</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.362806020865849</v>
+        <v>-3.363641638177017</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.722172215660724</v>
+        <v>-3.723770770618429</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.388192651975697</v>
+        <v>-3.388277445736598</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79838468688952</v>
+        <v>10.79848476313192</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.26958010024232</v>
+        <v>3.269212320680381</v>
       </c>
       <c r="C278" t="n">
-        <v>3.634415056134621</v>
+        <v>3.63461414632662</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.625641162206082</v>
+        <v>-1.625612031945745</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127535330481204</v>
+        <v>6.127535974490628</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1223998913677304</v>
+        <v>-0.1241802798627178</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4632017938779098</v>
+        <v>0.4624836676842436</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3375735819763581</v>
+        <v>-0.3374723554858794</v>
       </c>
       <c r="E279" t="n">
-        <v>4.000374626462189</v>
+        <v>4.000344255864463</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848757771308174</v>
+        <v>-1.848896414616275</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.182671780197332</v>
+        <v>-2.18338305873127</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.8010610306848465</v>
+        <v>-0.8009939152742396</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4654844867560959</v>
+        <v>0.4654053903133004</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.170734603535518</v>
+        <v>2.169754960659076</v>
       </c>
       <c r="C281" t="n">
-        <v>1.855749304249943</v>
+        <v>1.855187645178535</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.091125359924174</v>
+        <v>-3.09086060246524</v>
       </c>
       <c r="E281" t="n">
-        <v>3.989790622950595</v>
+        <v>3.989736168090596</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.197049698802144</v>
+        <v>1.200296684709268</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625571521305536</v>
+        <v>1.627602972208142</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2884290791133948</v>
+        <v>0.2887142767602491</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9934998077412827</v>
+        <v>0.993451267487333</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.124776389948368</v>
+        <v>1.129111911851144</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5623694666740953</v>
+        <v>0.5645595502538958</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1556496330499701</v>
+        <v>0.1559405555013216</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1320300546426845</v>
+        <v>-0.1320777498381775</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.545943508344473</v>
+        <v>2.548746889557174</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05024414324593662</v>
+        <v>-0.04998568629892564</v>
       </c>
       <c r="D284" t="n">
-        <v>2.829503895713636</v>
+        <v>2.829903224989549</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7776552759529265</v>
+        <v>0.7776159410491257</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.465409105268777</v>
+        <v>0.4599822718321933</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7821571132131666</v>
+        <v>-0.7844449170859358</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.491765105435916</v>
+        <v>-1.492528723863185</v>
       </c>
       <c r="E285" t="n">
-        <v>0.272319257543141</v>
+        <v>0.2722762872863882</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.658391496247716</v>
+        <v>4.656852198358163</v>
       </c>
       <c r="C286" t="n">
-        <v>1.850385822394318</v>
+        <v>1.8487811934224</v>
       </c>
       <c r="D286" t="n">
-        <v>2.95566447840907</v>
+        <v>2.955312431803603</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268338709067685</v>
+        <v>1.268329430224058</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.821088376513384</v>
+        <v>5.822157399778005</v>
       </c>
       <c r="C287" t="n">
-        <v>3.944480047187504</v>
+        <v>3.945721672335889</v>
       </c>
       <c r="D287" t="n">
-        <v>4.871027505889147</v>
+        <v>4.870763859969229</v>
       </c>
       <c r="E287" t="n">
-        <v>2.677997110659414</v>
+        <v>2.678026388872889</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.481672733543917</v>
+        <v>3.480731262063119</v>
       </c>
       <c r="C288" t="n">
-        <v>2.952007842839421</v>
+        <v>2.951518100974782</v>
       </c>
       <c r="D288" t="n">
-        <v>2.10933096575785</v>
+        <v>2.109169409283584</v>
       </c>
       <c r="E288" t="n">
-        <v>3.365416013016942</v>
+        <v>3.365455677591411</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.846540253566302</v>
+        <v>6.847844725889329</v>
       </c>
       <c r="C289" t="n">
-        <v>6.018191396424233</v>
+        <v>6.019160212858465</v>
       </c>
       <c r="D289" t="n">
-        <v>2.234766755201378</v>
+        <v>2.234630496816625</v>
       </c>
       <c r="E289" t="n">
-        <v>3.823807652120359</v>
+        <v>3.823880590995388</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8724868681492248</v>
+        <v>0.8711801953830811</v>
       </c>
       <c r="C290" t="n">
-        <v>1.163758535435733</v>
+        <v>1.16349677236236</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.215450370993666</v>
+        <v>-2.215471094205357</v>
       </c>
       <c r="E290" t="n">
-        <v>2.40425150969048</v>
+        <v>2.40421154855377</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.291652167213965</v>
+        <v>3.289937083842664</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302308536550891</v>
+        <v>3.302120033490108</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.259168126566723</v>
+        <v>-1.259081783484006</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627918218153314</v>
+        <v>3.627907448132062</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.308338902728816</v>
+        <v>6.307785238483987</v>
       </c>
       <c r="C292" t="n">
-        <v>5.588023794436281</v>
+        <v>5.587643674928744</v>
       </c>
       <c r="D292" t="n">
-        <v>2.174009925544484</v>
+        <v>2.174140995030638</v>
       </c>
       <c r="E292" t="n">
-        <v>4.880457147628769</v>
+        <v>4.880451949448639</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.537248739384835</v>
+        <v>3.53705819514667</v>
       </c>
       <c r="C293" t="n">
-        <v>2.370946837778853</v>
+        <v>2.370317647741405</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532175217009258</v>
+        <v>2.532707832349734</v>
       </c>
       <c r="E293" t="n">
-        <v>4.242435856993199</v>
+        <v>4.242445931660499</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.366257760757879</v>
+        <v>8.370705943341283</v>
       </c>
       <c r="C294" t="n">
-        <v>5.91073075869466</v>
+        <v>5.913184055952003</v>
       </c>
       <c r="D294" t="n">
-        <v>4.202245571270824</v>
+        <v>4.202829574659805</v>
       </c>
       <c r="E294" t="n">
-        <v>6.252825307944976</v>
+        <v>6.252865778754546</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.591583816699242</v>
+        <v>6.596650331756115</v>
       </c>
       <c r="C295" t="n">
-        <v>5.38562212394702</v>
+        <v>5.388552717182438</v>
       </c>
       <c r="D295" t="n">
-        <v>6.116514181377131</v>
+        <v>6.117076337746696</v>
       </c>
       <c r="E295" t="n">
-        <v>6.950052682368035</v>
+        <v>6.950118775994052</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.140540504680757</v>
+        <v>5.143931891709608</v>
       </c>
       <c r="C296" t="n">
-        <v>5.711497630897933</v>
+        <v>5.713340902815034</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1170929138635257</v>
+        <v>0.1177198665293089</v>
       </c>
       <c r="E296" t="n">
-        <v>4.68094742113101</v>
+        <v>4.680976188007291</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.869350867023336</v>
+        <v>3.861946860263799</v>
       </c>
       <c r="C297" t="n">
-        <v>4.005672286808082</v>
+        <v>4.00306292724788</v>
       </c>
       <c r="D297" t="n">
-        <v>2.952794057407426</v>
+        <v>2.951454812038334</v>
       </c>
       <c r="E297" t="n">
-        <v>4.086353980277679</v>
+        <v>4.086339452181464</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.451160893303284</v>
+        <v>2.448542829499956</v>
       </c>
       <c r="C298" t="n">
-        <v>1.069559544520438</v>
+        <v>1.067958353462228</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4379621808341172</v>
+        <v>0.4373474175102032</v>
       </c>
       <c r="E298" t="n">
-        <v>3.051045978282674</v>
+        <v>3.05104879021818</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.298103544743647</v>
+        <v>3.297022600415822</v>
       </c>
       <c r="C299" t="n">
-        <v>2.792202549686595</v>
+        <v>2.792061226609222</v>
       </c>
       <c r="D299" t="n">
-        <v>1.828676786280892</v>
+        <v>1.828181530799533</v>
       </c>
       <c r="E299" t="n">
-        <v>2.813069752395103</v>
+        <v>2.813051361570218</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.510585650790411</v>
+        <v>4.510604166929966</v>
       </c>
       <c r="C300" t="n">
-        <v>3.716155251072495</v>
+        <v>3.716049052595638</v>
       </c>
       <c r="D300" t="n">
-        <v>3.904433616436154</v>
+        <v>3.904118403374013</v>
       </c>
       <c r="E300" t="n">
-        <v>3.748846656720173</v>
+        <v>3.748862672698472</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.777216434015896</v>
+        <v>4.778680526868495</v>
       </c>
       <c r="C301" t="n">
-        <v>3.181889447921193</v>
+        <v>3.182579111568984</v>
       </c>
       <c r="D301" t="n">
-        <v>5.337133110640191</v>
+        <v>5.336966463626558</v>
       </c>
       <c r="E301" t="n">
-        <v>1.882908913557069</v>
+        <v>1.88289106076569</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.339085999979409</v>
+        <v>5.339564188427071</v>
       </c>
       <c r="C302" t="n">
-        <v>3.379359890217737</v>
+        <v>3.379811137912725</v>
       </c>
       <c r="D302" t="n">
-        <v>4.099624258750834</v>
+        <v>4.099661095823071</v>
       </c>
       <c r="E302" t="n">
-        <v>1.198777630932901</v>
+        <v>1.198735642744952</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.232001707127099</v>
+        <v>5.231828339361866</v>
       </c>
       <c r="C303" t="n">
-        <v>3.151789490397139</v>
+        <v>3.152331764355254</v>
       </c>
       <c r="D303" t="n">
-        <v>1.615689959109745</v>
+        <v>1.615873470175533</v>
       </c>
       <c r="E303" t="n">
-        <v>3.117679996963196</v>
+        <v>3.117653582093083</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.057212314034772</v>
+        <v>1.05607040557123</v>
       </c>
       <c r="C304" t="n">
-        <v>0.4991038895259425</v>
+        <v>0.497723822021956</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6799848833401123</v>
+        <v>-0.6797943758173663</v>
       </c>
       <c r="E304" t="n">
-        <v>3.83528644661657</v>
+        <v>3.83528182272932</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.067397687800531</v>
+        <v>1.068720701747328</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1449046722070912</v>
+        <v>0.1446349818202908</v>
       </c>
       <c r="D305" t="n">
-        <v>2.198972546736533</v>
+        <v>2.199798512478579</v>
       </c>
       <c r="E305" t="n">
-        <v>1.964971628781709</v>
+        <v>1.964955590808048</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6279798808265902</v>
+        <v>0.6299400603555716</v>
       </c>
       <c r="C306" t="n">
-        <v>0.02991696792322696</v>
+        <v>0.0302151389178773</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.263019604324134</v>
+        <v>-1.262182460074612</v>
       </c>
       <c r="E306" t="n">
-        <v>2.321850890826838</v>
+        <v>2.321825970681801</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.185688208859826</v>
+        <v>2.189099781752635</v>
       </c>
       <c r="C307" t="n">
-        <v>1.364177536606537</v>
+        <v>1.364608796333511</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.598516696530573</v>
+        <v>-2.597713748156238</v>
       </c>
       <c r="E307" t="n">
-        <v>3.143029664210872</v>
+        <v>3.143020004793207</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.766862087109256</v>
+        <v>1.770539994405262</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2728758903609796</v>
+        <v>0.2733561948081498</v>
       </c>
       <c r="D308" t="n">
-        <v>1.607862901272283</v>
+        <v>1.608920511624889</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799621112894981</v>
+        <v>4.799622650893021</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.148163744612664</v>
+        <v>3.139950878859032</v>
       </c>
       <c r="C309" t="n">
-        <v>2.244138458642841</v>
+        <v>2.240759559282801</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5617255091661555</v>
+        <v>0.5596051493185872</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405826507579725</v>
+        <v>5.405824958069072</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.761024197083708</v>
+        <v>5.758402248185401</v>
       </c>
       <c r="C310" t="n">
-        <v>6.635470076961036</v>
+        <v>6.636099455735489</v>
       </c>
       <c r="D310" t="n">
-        <v>2.76644057159714</v>
+        <v>2.76549707231315</v>
       </c>
       <c r="E310" t="n">
-        <v>8.393130051120433</v>
+        <v>8.393158771209318</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.920797950301669</v>
+        <v>3.91816944655301</v>
       </c>
       <c r="C311" t="n">
-        <v>3.198125997370593</v>
+        <v>3.197650006796549</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6449837666081537</v>
+        <v>0.6442598286695356</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879477432584811</v>
+        <v>4.879471375029154</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.035571229356205</v>
+        <v>4.036058739567983</v>
       </c>
       <c r="C312" t="n">
-        <v>2.369259863783291</v>
+        <v>2.368900511044503</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.060046943711968</v>
+        <v>-1.060594834522255</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824394028289137</v>
+        <v>5.824387856737467</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.254482519696711</v>
+        <v>3.253746424275916</v>
       </c>
       <c r="C313" t="n">
-        <v>2.40550835351383</v>
+        <v>2.404123369015831</v>
       </c>
       <c r="D313" t="n">
-        <v>0.0465141287606663</v>
+        <v>0.04620825673125051</v>
       </c>
       <c r="E313" t="n">
-        <v>6.33552882178392</v>
+        <v>6.335553873975153</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.285560693520374</v>
+        <v>4.28593663798722</v>
       </c>
       <c r="C314" t="n">
-        <v>3.915519331641204</v>
+        <v>3.915571785482741</v>
       </c>
       <c r="D314" t="n">
-        <v>1.486352769967336</v>
+        <v>1.486334832780245</v>
       </c>
       <c r="E314" t="n">
-        <v>8.647363602378167</v>
+        <v>8.647459774679955</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.687583811783</v>
+        <v>1.687342990189755</v>
       </c>
       <c r="C315" t="n">
-        <v>2.645790006529514</v>
+        <v>2.646338681866145</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9292594932999165</v>
+        <v>0.9295256736113533</v>
       </c>
       <c r="E315" t="n">
-        <v>4.024648519717222</v>
+        <v>4.024659605629077</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.654256216015249</v>
+        <v>2.655128323708245</v>
       </c>
       <c r="C316" t="n">
-        <v>2.861382335892171</v>
+        <v>2.861654929391655</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3950284895924527</v>
+        <v>0.3953134546281989</v>
       </c>
       <c r="E316" t="n">
-        <v>3.649603874751084</v>
+        <v>3.649611570450584</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.784372839960275</v>
+        <v>8.79053333382933</v>
       </c>
       <c r="C317" t="n">
-        <v>9.067974656528799</v>
+        <v>9.072207290747315</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3884412932526837</v>
+        <v>0.389782245057213</v>
       </c>
       <c r="E317" t="n">
-        <v>7.313253160445821</v>
+        <v>7.313312846583009</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.371759682058407</v>
+        <v>4.374646991795661</v>
       </c>
       <c r="C318" t="n">
-        <v>5.380193983054515</v>
+        <v>5.382412590552943</v>
       </c>
       <c r="D318" t="n">
-        <v>2.155182839914915</v>
+        <v>2.156681916595327</v>
       </c>
       <c r="E318" t="n">
-        <v>5.210636075747987</v>
+        <v>5.210676464698194</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.188158145027487</v>
+        <v>4.192217064205694</v>
       </c>
       <c r="C319" t="n">
-        <v>3.331393133802307</v>
+        <v>3.332798399506109</v>
       </c>
       <c r="D319" t="n">
-        <v>2.730661951055935</v>
+        <v>2.732181154468671</v>
       </c>
       <c r="E319" t="n">
-        <v>3.721768378030532</v>
+        <v>3.721747213807114</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.744227583387619</v>
+        <v>6.750261529506529</v>
       </c>
       <c r="C320" t="n">
-        <v>6.783664726158567</v>
+        <v>6.785626492930619</v>
       </c>
       <c r="D320" t="n">
-        <v>2.226563024488648</v>
+        <v>2.22834444450053</v>
       </c>
       <c r="E320" t="n">
-        <v>3.065080674672971</v>
+        <v>3.065047779428598</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.938008995783051</v>
+        <v>5.9270651928095</v>
       </c>
       <c r="C321" t="n">
-        <v>4.671226700815057</v>
+        <v>4.665414285502378</v>
       </c>
       <c r="D321" t="n">
-        <v>1.457511056310956</v>
+        <v>1.453880921071615</v>
       </c>
       <c r="E321" t="n">
-        <v>2.665046596757659</v>
+        <v>2.664960406208206</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.560450120250859</v>
+        <v>5.554212216083387</v>
       </c>
       <c r="C322" t="n">
-        <v>3.513077382926211</v>
+        <v>3.510495413474279</v>
       </c>
       <c r="D322" t="n">
-        <v>0.0522723614494458</v>
+        <v>0.05067715541509088</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5174417683821098</v>
+        <v>-0.5175512589487119</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.352154979531986</v>
+        <v>4.346929079851702</v>
       </c>
       <c r="C323" t="n">
-        <v>5.205111148019004</v>
+        <v>5.202365513068719</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8396843287395317</v>
+        <v>0.8384898561793808</v>
       </c>
       <c r="E323" t="n">
-        <v>4.169876004873996</v>
+        <v>4.169839613043513</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.537145949207691</v>
+        <v>7.536716339400984</v>
       </c>
       <c r="C324" t="n">
-        <v>7.00329651338949</v>
+        <v>7.003314846655972</v>
       </c>
       <c r="D324" t="n">
-        <v>3.827891511573278</v>
+        <v>3.827015893249608</v>
       </c>
       <c r="E324" t="n">
-        <v>2.187601286782881</v>
+        <v>2.187535571725507</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.0813984348836</v>
+        <v>6.078546372599836</v>
       </c>
       <c r="C325" t="n">
-        <v>5.608487516785732</v>
+        <v>5.606345794054546</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1505652360996645</v>
+        <v>0.1501059311637576</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892522877339787</v>
+        <v>2.892497783893777</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.855069795208823</v>
+        <v>5.85523605522269</v>
       </c>
       <c r="C326" t="n">
-        <v>4.981160331785328</v>
+        <v>4.981603318139105</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7926405222000499</v>
+        <v>0.7925817929019141</v>
       </c>
       <c r="E326" t="n">
-        <v>4.47420851619964</v>
+        <v>4.474269749795323</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.914352380372748</v>
+        <v>9.91637715666085</v>
       </c>
       <c r="C327" t="n">
-        <v>9.270357904157201</v>
+        <v>9.272798543509886</v>
       </c>
       <c r="D327" t="n">
-        <v>2.693361703760355</v>
+        <v>2.693797890469218</v>
       </c>
       <c r="E327" t="n">
-        <v>7.798841588088656</v>
+        <v>7.798920005822785</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.4084300614121</v>
+        <v>10.41356439825318</v>
       </c>
       <c r="C328" t="n">
-        <v>9.05247344091087</v>
+        <v>9.055530592767113</v>
       </c>
       <c r="D328" t="n">
-        <v>3.150486017591381</v>
+        <v>3.150994762927239</v>
       </c>
       <c r="E328" t="n">
-        <v>7.360729243128317</v>
+        <v>7.360797462364754</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>3.991242624240243</v>
+        <v>3.998850424192235</v>
       </c>
       <c r="C329" t="n">
-        <v>3.007642466097527</v>
+        <v>3.011411127452912</v>
       </c>
       <c r="D329" t="n">
-        <v>2.843137803485751</v>
+        <v>2.845499663330253</v>
       </c>
       <c r="E329" t="n">
-        <v>3.597084927111083</v>
+        <v>3.597133465778968</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.264882897876145</v>
+        <v>6.270035672976948</v>
       </c>
       <c r="C330" t="n">
-        <v>5.545755289621979</v>
+        <v>5.548933310935666</v>
       </c>
       <c r="D330" t="n">
-        <v>1.31657039925952</v>
+        <v>1.319044113729628</v>
       </c>
       <c r="E330" t="n">
-        <v>5.629468917603697</v>
+        <v>5.629508998554345</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.970100249401056</v>
+        <v>5.977062345857886</v>
       </c>
       <c r="C331" t="n">
-        <v>7.424433291960453</v>
+        <v>7.428627857385428</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.071400937391465</v>
+        <v>-1.06903381078044</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981041089729987</v>
+        <v>4.981062933200953</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.239961224961108</v>
+        <v>4.248222464529139</v>
       </c>
       <c r="C332" t="n">
-        <v>4.01229300518291</v>
+        <v>4.015431279075732</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.619918262847964</v>
+        <v>-1.617113906715195</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511817873939861</v>
+        <v>4.511847141031922</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.836740365494751</v>
+        <v>3.821899960124497</v>
       </c>
       <c r="C333" t="n">
-        <v>3.782883195468245</v>
+        <v>3.774978281070585</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.152584957824534</v>
+        <v>-3.158390982991255</v>
       </c>
       <c r="E333" t="n">
-        <v>4.43574375930218</v>
+        <v>4.435697085413026</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.918611795310566</v>
+        <v>2.908789620704688</v>
       </c>
       <c r="C334" t="n">
-        <v>4.913928658838307</v>
+        <v>4.909638142963191</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.618283059074233</v>
+        <v>-1.620857506476825</v>
       </c>
       <c r="E334" t="n">
-        <v>5.110263871537835</v>
+        <v>5.110231344346339</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.730170697602397</v>
+        <v>3.724116331453486</v>
       </c>
       <c r="C335" t="n">
-        <v>1.784085327517682</v>
+        <v>1.780644777987694</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.584529331332897</v>
+        <v>-2.586457792999886</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832554158811807</v>
+        <v>3.832546706221551</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.726156133627789</v>
+        <v>3.723254619881855</v>
       </c>
       <c r="C336" t="n">
-        <v>3.878777858930182</v>
+        <v>3.87721549605422</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.339140867682577</v>
+        <v>-3.340515664104726</v>
       </c>
       <c r="E336" t="n">
-        <v>3.492837859478848</v>
+        <v>3.492816570750312</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.998785112860468</v>
+        <v>1.994708805344225</v>
       </c>
       <c r="C337" t="n">
-        <v>1.407502135335736</v>
+        <v>1.405237928077185</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.147907997333987</v>
+        <v>-3.148651035124272</v>
       </c>
       <c r="E337" t="n">
-        <v>3.632381935538587</v>
+        <v>3.632398586433583</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.293521044890291</v>
+        <v>3.293304044554057</v>
       </c>
       <c r="C338" t="n">
-        <v>2.202494166606739</v>
+        <v>2.203016424240611</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.366441244591222</v>
+        <v>-2.366495153001569</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875800216351253</v>
+        <v>1.875779619611517</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6624309183083543</v>
+        <v>0.6629817420018336</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.193095890286378</v>
+        <v>-2.193244531954541</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.152306563442785</v>
+        <v>-2.151619197975918</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6040832774020122</v>
+        <v>-0.6041292173951329</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.584101643503979</v>
+        <v>3.588291544598698</v>
       </c>
       <c r="C340" t="n">
-        <v>0.4405170500976219</v>
+        <v>0.4418959461722549</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.720239526674251</v>
+        <v>-2.719521287272963</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.147287960112153</v>
+        <v>-1.147301409546964</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.774896480550828</v>
+        <v>4.785744018977622</v>
       </c>
       <c r="C341" t="n">
-        <v>1.320843199035071</v>
+        <v>1.327143518241636</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.053624086391915</v>
+        <v>-3.0499819667822</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702127535508491</v>
+        <v>1.702166569742891</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.66320886767282</v>
+        <v>5.67070774648426</v>
       </c>
       <c r="C342" t="n">
-        <v>2.741537674938543</v>
+        <v>2.745743068175854</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7381110432418847</v>
+        <v>-0.7340795162031899</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1299269124699798</v>
+        <v>-0.1298944525745971</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.81766645129671</v>
+        <v>5.827439361410325</v>
       </c>
       <c r="C343" t="n">
-        <v>1.501310019516966</v>
+        <v>1.50618391452142</v>
       </c>
       <c r="D343" t="n">
-        <v>2.368682165404246</v>
+        <v>2.372804159713393</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6818346767176298</v>
+        <v>0.6818814396501782</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.936078390687793</v>
+        <v>5.948826942067398</v>
       </c>
       <c r="C344" t="n">
-        <v>3.892678631925794</v>
+        <v>3.897483161713189</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9124328564630968</v>
+        <v>0.9172868329252459</v>
       </c>
       <c r="E344" t="n">
-        <v>2.712615569937293</v>
+        <v>2.712679408935537</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.28424166284039</v>
+        <v>10.26134861402348</v>
       </c>
       <c r="C345" t="n">
-        <v>7.573296663610596</v>
+        <v>7.559162940716613</v>
       </c>
       <c r="D345" t="n">
-        <v>7.755506846652316</v>
+        <v>7.744826118357517</v>
       </c>
       <c r="E345" t="n">
-        <v>2.755125628905408</v>
+        <v>2.755001610173413</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.164110812302722</v>
+        <v>2.152593761168631</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4071841360058337</v>
+        <v>-0.4137102870201192</v>
       </c>
       <c r="D346" t="n">
-        <v>1.643607464902375</v>
+        <v>1.639155722462848</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254317602949008</v>
+        <v>2.254286460953625</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.184245504404705</v>
+        <v>5.177383265308189</v>
       </c>
       <c r="C347" t="n">
-        <v>3.125140334761323</v>
+        <v>3.120591789141325</v>
       </c>
       <c r="D347" t="n">
-        <v>4.057549016855422</v>
+        <v>4.054073905615696</v>
       </c>
       <c r="E347" t="n">
-        <v>2.133485649630718</v>
+        <v>2.133414027673108</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.569562126281434</v>
+        <v>3.56473479421977</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.626262515831999</v>
+        <v>-0.6294406240571759</v>
       </c>
       <c r="D348" t="n">
-        <v>4.251872568691728</v>
+        <v>4.249441206464155</v>
       </c>
       <c r="E348" t="n">
-        <v>3.13122373567265</v>
+        <v>3.131185637755718</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.721811786696774</v>
+        <v>6.717834867279948</v>
       </c>
       <c r="C349" t="n">
-        <v>6.145890206084914</v>
+        <v>6.143163332919821</v>
       </c>
       <c r="D349" t="n">
-        <v>6.308217403783112</v>
+        <v>6.306883916164163</v>
       </c>
       <c r="E349" t="n">
-        <v>6.032294844828079</v>
+        <v>6.032262126468568</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.376015800385581</v>
+        <v>5.377590874073435</v>
       </c>
       <c r="C350" t="n">
-        <v>3.2071524030159</v>
+        <v>3.21111640742886</v>
       </c>
       <c r="D350" t="n">
-        <v>6.182525142567585</v>
+        <v>6.18244034232498</v>
       </c>
       <c r="E350" t="n">
-        <v>6.714613911160683</v>
+        <v>6.714528123720997</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.02185047910373</v>
+        <v>6.024693668014303</v>
       </c>
       <c r="C351" t="n">
-        <v>4.301009519763532</v>
+        <v>4.305335427011481</v>
       </c>
       <c r="D351" t="n">
-        <v>1.672362518358539</v>
+        <v>1.673494699697042</v>
       </c>
       <c r="E351" t="n">
-        <v>8.0810859661681</v>
+        <v>8.081055773753686</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26822356775096</v>
+        <v>-53.26612231914265</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.30765609672081</v>
+        <v>-49.30523771346016</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.32608657175283</v>
+        <v>-44.32509283422183</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.877236574219499</v>
+        <v>-1.877166368574956</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40238948262554</v>
+        <v>-99.40230498886675</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11770564815239</v>
+        <v>-98.1174828070718</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69214423593424</v>
+        <v>-88.69149983367343</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50753598135462</v>
+        <v>-52.50747971378924</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80436312853557</v>
+        <v>-98.8042621053352</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98521054666811</v>
+        <v>-95.98495974911418</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.1625615954102</v>
+        <v>-82.16139941854617</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.7020401721777</v>
+        <v>-50.70197103635</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13303777027078</v>
+        <v>-98.13282276520955</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.35228584115593</v>
+        <v>-94.3519063685369</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.4139188173727</v>
+        <v>-81.41263348346014</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98618006929963</v>
+        <v>-42.98608549980295</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74232454064828</v>
+        <v>-97.74199970422606</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62892665725434</v>
+        <v>-93.6285602172082</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.63997206461602</v>
+        <v>-75.63797025889781</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11247797422947</v>
+        <v>-43.11242225600495</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.4608484956877</v>
+        <v>-97.46166901367718</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.9883096882117</v>
+        <v>-90.99088037182241</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18774077150916</v>
+        <v>-74.1919545779833</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65823865225113</v>
+        <v>-45.65836828852478</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43020060194051</v>
+        <v>-97.43050525173668</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90265698270781</v>
+        <v>-89.90359987578471</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.9735378875063</v>
+        <v>-74.9753138013957</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.1716685391618</v>
+        <v>-40.17169280064977</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07562559331848</v>
+        <v>-90.07628068129887</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.37415372440897</v>
+        <v>-81.37500045267475</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.97044379696993</v>
+        <v>-74.97179206954705</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34870252499049</v>
+        <v>-31.3487267586022</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76486148708817</v>
+        <v>-76.7661788098419</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.56947576505473</v>
+        <v>-65.57069286413977</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85512670806699</v>
+        <v>-71.85619619720553</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.5807336214706</v>
+        <v>-12.58070650746849</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.81876460319985</v>
+        <v>-74.8198269919889</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.34600932902188</v>
+        <v>-66.34781411612703</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13476792127949</v>
+        <v>-70.13541291491849</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80230250634978</v>
+        <v>-16.80238736262967</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68189845408354</v>
+        <v>11.68260252288602</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37704061536031</v>
+        <v>11.37087360113893</v>
       </c>
       <c r="D242" t="n">
-        <v>10.14547716866296</v>
+        <v>10.14354861849365</v>
       </c>
       <c r="E242" t="n">
-        <v>7.26289064612049</v>
+        <v>7.262825858201394</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.26877426688637</v>
+        <v>12.26944858761676</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43870169460124</v>
+        <v>12.43502059596318</v>
       </c>
       <c r="D243" t="n">
-        <v>7.82059357985958</v>
+        <v>7.816611670134788</v>
       </c>
       <c r="E243" t="n">
-        <v>8.995099556990628</v>
+        <v>8.995052510291313</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.971671261934961</v>
+        <v>3.971689220385932</v>
       </c>
       <c r="C244" t="n">
-        <v>7.190944498220309</v>
+        <v>7.192114693820351</v>
       </c>
       <c r="D244" t="n">
-        <v>6.051581228743275</v>
+        <v>6.051512645415791</v>
       </c>
       <c r="E244" t="n">
-        <v>8.711435554023206</v>
+        <v>8.711365239221491</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.844230959048445</v>
+        <v>3.843953608526007</v>
       </c>
       <c r="C245" t="n">
-        <v>7.412568764707506</v>
+        <v>7.413625223150477</v>
       </c>
       <c r="D245" t="n">
-        <v>4.807345503318827</v>
+        <v>4.809584195369077</v>
       </c>
       <c r="E245" t="n">
-        <v>8.570664447331144</v>
+        <v>8.570871589405748</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1746059586783977</v>
+        <v>0.1741036830395393</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6970826731663493</v>
+        <v>-0.6934259142654997</v>
       </c>
       <c r="D246" t="n">
-        <v>1.812248346328871</v>
+        <v>1.815590073547679</v>
       </c>
       <c r="E246" t="n">
-        <v>9.479326783347464</v>
+        <v>9.47939054502438</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,16 +11039,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3575387800912155</v>
+        <v>-0.3586227967598998</v>
       </c>
       <c r="C247" t="n">
-        <v>2.276265546612177</v>
+        <v>2.284770151265425</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.624088088035447</v>
+        <v>-1.620148013177891</v>
       </c>
       <c r="E247" t="n">
-        <v>9.101746752017847</v>
+        <v>9.101631178317216</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.549391102962039</v>
+        <v>-1.549916376604021</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.321810077167796</v>
+        <v>-2.317781047226819</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.091308659376135</v>
+        <v>-3.091293785880622</v>
       </c>
       <c r="E248" t="n">
-        <v>8.145613608571045</v>
+        <v>8.145476706926779</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.449506209440443</v>
+        <v>1.449790615477942</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2396204609760533</v>
+        <v>-0.2372891799369392</v>
       </c>
       <c r="D249" t="n">
-        <v>2.499873962137689</v>
+        <v>2.498295785306448</v>
       </c>
       <c r="E249" t="n">
-        <v>7.144218945607261</v>
+        <v>7.144037479922516</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,16 +11168,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.830715185770695</v>
+        <v>4.830711813600197</v>
       </c>
       <c r="C250" t="n">
-        <v>4.689235317940166</v>
+        <v>4.687089702921488</v>
       </c>
       <c r="D250" t="n">
-        <v>6.342549223833593</v>
+        <v>6.340993588903965</v>
       </c>
       <c r="E250" t="n">
-        <v>8.28312778415885</v>
+        <v>8.283037423771145</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8343685950976454</v>
+        <v>0.8343999942093339</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477722527224135</v>
+        <v>1.477641306126354</v>
       </c>
       <c r="D251" t="n">
-        <v>2.658102547625552</v>
+        <v>2.658665724635223</v>
       </c>
       <c r="E251" t="n">
-        <v>8.430136252299825</v>
+        <v>8.430068825144765</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.652688404469995</v>
+        <v>3.652579697448655</v>
       </c>
       <c r="C252" t="n">
-        <v>2.969030747979962</v>
+        <v>2.968960861279379</v>
       </c>
       <c r="D252" t="n">
-        <v>3.946127309757541</v>
+        <v>3.946919683584849</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19891167494602</v>
+        <v>10.19910003932385</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.119844406445042</v>
+        <v>7.120069398439921</v>
       </c>
       <c r="C253" t="n">
-        <v>8.449334944398167</v>
+        <v>8.446283032690305</v>
       </c>
       <c r="D253" t="n">
-        <v>3.630548601625216</v>
+        <v>3.628301407789758</v>
       </c>
       <c r="E253" t="n">
-        <v>7.932982359259388</v>
+        <v>7.9328226303095</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.373408662070369</v>
+        <v>7.373614346434576</v>
       </c>
       <c r="C254" t="n">
-        <v>7.315520843279044</v>
+        <v>7.314348598559883</v>
       </c>
       <c r="D254" t="n">
-        <v>5.753289658935645</v>
+        <v>5.750021199399136</v>
       </c>
       <c r="E254" t="n">
-        <v>8.193760219446933</v>
+        <v>8.193831060668998</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449742892210274</v>
+        <v>5.449807247245553</v>
       </c>
       <c r="C255" t="n">
-        <v>5.869509497095571</v>
+        <v>5.869173489670954</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549617529964032</v>
+        <v>2.549656064040895</v>
       </c>
       <c r="E255" t="n">
-        <v>6.40151997885825</v>
+        <v>6.401576697100575</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.7053001485655</v>
+        <v>11.70557448586542</v>
       </c>
       <c r="C256" t="n">
-        <v>9.848919637091157</v>
+        <v>9.844738548773302</v>
       </c>
       <c r="D256" t="n">
-        <v>5.668065689639246</v>
+        <v>5.666891538783125</v>
       </c>
       <c r="E256" t="n">
-        <v>7.164752554208631</v>
+        <v>7.164864988835373</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.775354100800925</v>
+        <v>8.775120596850815</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537266855787106</v>
+        <v>8.537593441204416</v>
       </c>
       <c r="D257" t="n">
-        <v>5.10388011464753</v>
+        <v>5.103217689620099</v>
       </c>
       <c r="E257" t="n">
-        <v>7.456230632155414</v>
+        <v>7.456115711852385</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92018340905716</v>
+        <v>11.92013907973419</v>
       </c>
       <c r="C258" t="n">
-        <v>11.75119549773758</v>
+        <v>11.75164521095293</v>
       </c>
       <c r="D258" t="n">
-        <v>8.786242632180663</v>
+        <v>8.785017910246019</v>
       </c>
       <c r="E258" t="n">
-        <v>7.927118051159909</v>
+        <v>7.927129318198212</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45305995524801</v>
+        <v>11.4532574300735</v>
       </c>
       <c r="C259" t="n">
-        <v>9.101881555303937</v>
+        <v>9.1011448199664</v>
       </c>
       <c r="D259" t="n">
-        <v>7.833268389272141</v>
+        <v>7.832121121588376</v>
       </c>
       <c r="E259" t="n">
-        <v>8.261295135653924</v>
+        <v>8.261372742916983</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.847505634475006</v>
+        <v>8.847286920480336</v>
       </c>
       <c r="C260" t="n">
-        <v>9.290142441579107</v>
+        <v>9.291703570333688</v>
       </c>
       <c r="D260" t="n">
-        <v>8.069362232347309</v>
+        <v>8.070754866380092</v>
       </c>
       <c r="E260" t="n">
-        <v>8.66601036730752</v>
+        <v>8.66611628033076</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52715500892678</v>
+        <v>12.52716548783277</v>
       </c>
       <c r="C261" t="n">
-        <v>10.3124796851737</v>
+        <v>10.31196123614533</v>
       </c>
       <c r="D261" t="n">
-        <v>5.62124196839362</v>
+        <v>5.620958226393125</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40864637914667</v>
+        <v>10.40881220320906</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,16 +11684,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.793904142935547</v>
+        <v>6.793655061241965</v>
       </c>
       <c r="C262" t="n">
-        <v>6.466551096859718</v>
+        <v>6.467351327895488</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8223236309656046</v>
+        <v>-0.8198787653179607</v>
       </c>
       <c r="E262" t="n">
-        <v>8.713928250245907</v>
+        <v>8.713914659790811</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.093716544207563</v>
+        <v>9.093620294632721</v>
       </c>
       <c r="C263" t="n">
-        <v>7.433643811964363</v>
+        <v>7.433787219016663</v>
       </c>
       <c r="D263" t="n">
-        <v>3.149611097634941</v>
+        <v>3.15144227618569</v>
       </c>
       <c r="E263" t="n">
-        <v>8.716227259635478</v>
+        <v>8.716113492045153</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42330074304803</v>
+        <v>13.42333448522501</v>
       </c>
       <c r="C264" t="n">
-        <v>11.27168616393612</v>
+        <v>11.26971509547989</v>
       </c>
       <c r="D264" t="n">
-        <v>4.656474829981638</v>
+        <v>4.656347057436538</v>
       </c>
       <c r="E264" t="n">
-        <v>6.304904751577078</v>
+        <v>6.304587304294107</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.05431026041199</v>
+        <v>8.054294934555116</v>
       </c>
       <c r="C265" t="n">
-        <v>5.794201852986847</v>
+        <v>5.794022576852109</v>
       </c>
       <c r="D265" t="n">
-        <v>2.715965531109465</v>
+        <v>2.71641594606542</v>
       </c>
       <c r="E265" t="n">
-        <v>7.346403994682604</v>
+        <v>7.346200537343783</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.578804747448493</v>
+        <v>2.578846898154352</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2263985029172688</v>
+        <v>-0.2241211116561725</v>
       </c>
       <c r="D266" t="n">
-        <v>2.195865627700488</v>
+        <v>2.194968155063637</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01834649601139</v>
+        <v>12.01842708859775</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.100448051616002</v>
+        <v>5.100266055854341</v>
       </c>
       <c r="C267" t="n">
-        <v>1.656602329508838</v>
+        <v>1.659179416797363</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454399544308417</v>
+        <v>3.454303548915094</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53891169325403</v>
+        <v>13.53904723423938</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.82847199666281</v>
+        <v>5.828622124273997</v>
       </c>
       <c r="C268" t="n">
-        <v>3.42243740751873</v>
+        <v>3.421387480517191</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9115792515223875</v>
+        <v>0.911014414903244</v>
       </c>
       <c r="E268" t="n">
-        <v>15.11122531784159</v>
+        <v>15.1113500085152</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.374639694572434</v>
+        <v>2.374487960633398</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7155894083662906</v>
+        <v>0.7172955387181545</v>
       </c>
       <c r="D269" t="n">
-        <v>2.950853096392159</v>
+        <v>2.950098696797943</v>
       </c>
       <c r="E269" t="n">
-        <v>10.1296012150043</v>
+        <v>10.12945462651837</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.697653183493065</v>
+        <v>2.697873951287644</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3388202160738318</v>
+        <v>0.3383589182023083</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.516127893222219</v>
+        <v>-1.517208324774577</v>
       </c>
       <c r="E270" t="n">
-        <v>11.7743401745648</v>
+        <v>11.774253596161</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.115679230827718</v>
+        <v>4.116074780302426</v>
       </c>
       <c r="C271" t="n">
-        <v>3.274796397510915</v>
+        <v>3.272021473100417</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.168144710278418</v>
+        <v>-1.16949369604179</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72621774271867</v>
+        <v>12.72625145561899</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.815043508503257</v>
+        <v>3.815137303658545</v>
       </c>
       <c r="C272" t="n">
-        <v>2.835808238413495</v>
+        <v>2.834388349028183</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.927982069196322</v>
+        <v>-2.927431334603503</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49983860635102</v>
+        <v>12.49996359540693</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.04477691281213</v>
+        <v>2.044820516362389</v>
       </c>
       <c r="C273" t="n">
-        <v>2.704360480784773</v>
+        <v>2.702663636126212</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1134281553907934</v>
+        <v>-0.1135088307588905</v>
       </c>
       <c r="E273" t="n">
-        <v>12.16663029830747</v>
+        <v>12.1668099989358</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.145442471719881</v>
+        <v>-0.1458328881010051</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2291508214349314</v>
+        <v>0.2302787624065772</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03398004400991805</v>
+        <v>0.03529489346314474</v>
       </c>
       <c r="E274" t="n">
-        <v>11.93164931638233</v>
+        <v>11.93180948639836</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3204171502744435</v>
+        <v>-0.3204684112767198</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4546589423060965</v>
+        <v>-0.4549534610838402</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.021102015694498</v>
+        <v>-2.021317034944414</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91076962089756</v>
+        <v>10.91094988835399</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994491257617216</v>
+        <v>-3.994474031963757</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.156301146443575</v>
+        <v>-4.154708767584547</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.716279810981526</v>
+        <v>-3.715637542524752</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912261625586094</v>
+        <v>8.912239901004115</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.363641638177017</v>
+        <v>-3.363624742266402</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.723770770618429</v>
+        <v>-3.722746143251687</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.388277445736598</v>
+        <v>-3.387554482510191</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79848476313192</v>
+        <v>10.79873037991243</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.269212320680381</v>
+        <v>3.268991308012525</v>
       </c>
       <c r="C278" t="n">
-        <v>3.63461414632662</v>
+        <v>3.63478035862872</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.625612031945745</v>
+        <v>-1.624000035643847</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127535974490628</v>
+        <v>6.127531255002117</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1241802798627178</v>
+        <v>-0.1243786339276909</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4624836676842436</v>
+        <v>0.4633741787321455</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3374723554858794</v>
+        <v>-0.3364836307661156</v>
       </c>
       <c r="E279" t="n">
-        <v>4.000344255864463</v>
+        <v>4.000276547684467</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848896414616275</v>
+        <v>-1.848811494188396</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.18338305873127</v>
+        <v>-2.182782165693842</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.8009939152742396</v>
+        <v>-0.8006503748713034</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4654053903133004</v>
+        <v>0.4652168154958281</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.169754960659076</v>
+        <v>2.169635046127283</v>
       </c>
       <c r="C281" t="n">
-        <v>1.855187645178535</v>
+        <v>1.856290110130976</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.09086060246524</v>
+        <v>-3.090850812002355</v>
       </c>
       <c r="E281" t="n">
-        <v>3.989736168090596</v>
+        <v>3.989581391316244</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.200296684709268</v>
+        <v>1.200625130209043</v>
       </c>
       <c r="C282" t="n">
-        <v>1.627602972208142</v>
+        <v>1.62540112062437</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2887142767602491</v>
+        <v>0.2871446070950023</v>
       </c>
       <c r="E282" t="n">
-        <v>0.993451267487333</v>
+        <v>0.9932889629297836</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.129111911851144</v>
+        <v>1.129584428047914</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5645595502538958</v>
+        <v>0.5619671036124929</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1559405555013216</v>
+        <v>0.1533572566756236</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1320777498381775</v>
+        <v>-0.1321949381217546</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.548746889557174</v>
+        <v>2.5490529398984</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.04998568629892564</v>
+        <v>-0.05079932328950765</v>
       </c>
       <c r="D284" t="n">
-        <v>2.829903224989549</v>
+        <v>2.829531067683511</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7776159410491257</v>
+        <v>0.7775203819404997</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4599822718321933</v>
+        <v>0.4599469162709147</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7844449170859358</v>
+        <v>-0.7836782932882591</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.492528723863185</v>
+        <v>-1.492171094257544</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2722762872863882</v>
+        <v>0.2721647859632581</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656852198358163</v>
+        <v>4.656342964633464</v>
       </c>
       <c r="C286" t="n">
-        <v>1.8487811934224</v>
+        <v>1.850906588888157</v>
       </c>
       <c r="D286" t="n">
-        <v>2.955312431803603</v>
+        <v>2.955943571908004</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268329430224058</v>
+        <v>1.268320260112876</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.822157399778005</v>
+        <v>5.822053697348983</v>
       </c>
       <c r="C287" t="n">
-        <v>3.945721672335889</v>
+        <v>3.944626523417405</v>
       </c>
       <c r="D287" t="n">
-        <v>4.870763859969229</v>
+        <v>4.86885647382258</v>
       </c>
       <c r="E287" t="n">
-        <v>2.678026388872889</v>
+        <v>2.678103862462433</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480731262063119</v>
+        <v>3.480554173040229</v>
       </c>
       <c r="C288" t="n">
-        <v>2.951518100974782</v>
+        <v>2.95242412292458</v>
       </c>
       <c r="D288" t="n">
-        <v>2.109169409283584</v>
+        <v>2.108896313123276</v>
       </c>
       <c r="E288" t="n">
-        <v>3.365455677591411</v>
+        <v>3.365564859802772</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.847844725889329</v>
+        <v>6.847878879761771</v>
       </c>
       <c r="C289" t="n">
-        <v>6.019160212858465</v>
+        <v>6.018260851900581</v>
       </c>
       <c r="D289" t="n">
-        <v>2.234630496816625</v>
+        <v>2.233920494575048</v>
       </c>
       <c r="E289" t="n">
-        <v>3.823880590995388</v>
+        <v>3.824099547091975</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8711801953830811</v>
+        <v>0.8711220332354275</v>
       </c>
       <c r="C290" t="n">
-        <v>1.16349677236236</v>
+        <v>1.164266514520418</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.215471094205357</v>
+        <v>-2.212796487900004</v>
       </c>
       <c r="E290" t="n">
-        <v>2.40421154855377</v>
+        <v>2.404111615381765</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.289937083842664</v>
+        <v>3.289829428954261</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302120033490108</v>
+        <v>3.302512225884957</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.259081783484006</v>
+        <v>-1.256276738462503</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627907448132062</v>
+        <v>3.627896522326624</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.307785238483987</v>
+        <v>6.307673867279795</v>
       </c>
       <c r="C292" t="n">
-        <v>5.587643674928744</v>
+        <v>5.588654503852486</v>
       </c>
       <c r="D292" t="n">
-        <v>2.174140995030638</v>
+        <v>2.175583891336719</v>
       </c>
       <c r="E292" t="n">
-        <v>4.880451949448639</v>
+        <v>4.880427764878936</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.53705819514667</v>
+        <v>3.537075714295468</v>
       </c>
       <c r="C293" t="n">
-        <v>2.370317647741405</v>
+        <v>2.372021712951278</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532707832349734</v>
+        <v>2.532099393556697</v>
       </c>
       <c r="E293" t="n">
-        <v>4.242445931660499</v>
+        <v>4.242467255579663</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.370705943341283</v>
+        <v>8.371049123193908</v>
       </c>
       <c r="C294" t="n">
-        <v>5.913184055952003</v>
+        <v>5.91078434973995</v>
       </c>
       <c r="D294" t="n">
-        <v>4.202829574659805</v>
+        <v>4.200848378436817</v>
       </c>
       <c r="E294" t="n">
-        <v>6.252865778754546</v>
+        <v>6.252958946703191</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.596650331756115</v>
+        <v>6.597059652133686</v>
       </c>
       <c r="C295" t="n">
-        <v>5.388552717182438</v>
+        <v>5.385979176157019</v>
       </c>
       <c r="D295" t="n">
-        <v>6.117076337746696</v>
+        <v>6.114208461704473</v>
       </c>
       <c r="E295" t="n">
-        <v>6.950118775994052</v>
+        <v>6.950266300005281</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.143931891709608</v>
+        <v>5.144273295526047</v>
       </c>
       <c r="C296" t="n">
-        <v>5.713340902815034</v>
+        <v>5.711607260717977</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1177198665293089</v>
+        <v>0.1171567512838978</v>
       </c>
       <c r="E296" t="n">
-        <v>4.680976188007291</v>
+        <v>4.681028165210943</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.861946860263799</v>
+        <v>3.861897319185847</v>
       </c>
       <c r="C297" t="n">
-        <v>4.00306292724788</v>
+        <v>4.003598833455047</v>
       </c>
       <c r="D297" t="n">
-        <v>2.951454812038334</v>
+        <v>2.951685863700693</v>
       </c>
       <c r="E297" t="n">
-        <v>4.086339452181464</v>
+        <v>4.086295611590907</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.448542829499956</v>
+        <v>2.447950405697386</v>
       </c>
       <c r="C298" t="n">
-        <v>1.067958353462228</v>
+        <v>1.07006429895169</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4373474175102032</v>
+        <v>0.4397667630828606</v>
       </c>
       <c r="E298" t="n">
-        <v>3.05104879021818</v>
+        <v>3.051073022352457</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.297022600415822</v>
+        <v>3.296773051608981</v>
       </c>
       <c r="C299" t="n">
-        <v>2.792061226609222</v>
+        <v>2.792192891017886</v>
       </c>
       <c r="D299" t="n">
-        <v>1.828181530799533</v>
+        <v>1.828000376345029</v>
       </c>
       <c r="E299" t="n">
-        <v>2.813051361570218</v>
+        <v>2.812994947144243</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.510604166929966</v>
+        <v>4.51053011873892</v>
       </c>
       <c r="C300" t="n">
-        <v>3.716049052595638</v>
+        <v>3.71608160592094</v>
       </c>
       <c r="D300" t="n">
-        <v>3.904118403374013</v>
+        <v>3.903624196849131</v>
       </c>
       <c r="E300" t="n">
-        <v>3.748862672698472</v>
+        <v>3.748910456895849</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.778680526868495</v>
+        <v>4.778752949139919</v>
       </c>
       <c r="C301" t="n">
-        <v>3.182579111568984</v>
+        <v>3.181706807484774</v>
       </c>
       <c r="D301" t="n">
-        <v>5.336966463626558</v>
+        <v>5.335078299739093</v>
       </c>
       <c r="E301" t="n">
-        <v>1.88289106076569</v>
+        <v>1.882868608645127</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.339564188427071</v>
+        <v>5.3394559751065</v>
       </c>
       <c r="C302" t="n">
-        <v>3.379811137912725</v>
+        <v>3.380357695727665</v>
       </c>
       <c r="D302" t="n">
-        <v>4.099661095823071</v>
+        <v>4.100154430881031</v>
       </c>
       <c r="E302" t="n">
-        <v>1.198735642744952</v>
+        <v>1.198635890549404</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.231828339361866</v>
+        <v>5.231753857958599</v>
       </c>
       <c r="C303" t="n">
-        <v>3.152331764355254</v>
+        <v>3.151943095958987</v>
       </c>
       <c r="D303" t="n">
-        <v>1.615873470175533</v>
+        <v>1.617592694161174</v>
       </c>
       <c r="E303" t="n">
-        <v>3.117653582093083</v>
+        <v>3.117560732807223</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.05607040557123</v>
+        <v>1.056024315622528</v>
       </c>
       <c r="C304" t="n">
-        <v>0.497723822021956</v>
+        <v>0.499462026439379</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6797943758173663</v>
+        <v>-0.6782142743698594</v>
       </c>
       <c r="E304" t="n">
-        <v>3.83528182272932</v>
+        <v>3.835246887414656</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.068720701747328</v>
+        <v>1.068998287672951</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1446349818202908</v>
+        <v>0.1455991788466893</v>
       </c>
       <c r="D305" t="n">
-        <v>2.199798512478579</v>
+        <v>2.19828885705915</v>
       </c>
       <c r="E305" t="n">
-        <v>1.964955590808048</v>
+        <v>1.964897112425512</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6299400603555716</v>
+        <v>0.6301968249906587</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0302151389178773</v>
+        <v>0.02936540384361752</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.262182460074612</v>
+        <v>-1.263269290334657</v>
       </c>
       <c r="E306" t="n">
-        <v>2.321825970681801</v>
+        <v>2.32177060924541</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.189099781752635</v>
+        <v>2.18948114395574</v>
       </c>
       <c r="C307" t="n">
-        <v>1.364608796333511</v>
+        <v>1.363954757505947</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.597713748156238</v>
+        <v>-2.598957314655193</v>
       </c>
       <c r="E307" t="n">
-        <v>3.143020004793207</v>
+        <v>3.142978859727719</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.770539994405262</v>
+        <v>1.770958678423629</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2733561948081498</v>
+        <v>0.2721422211753088</v>
       </c>
       <c r="D308" t="n">
-        <v>1.608920511624889</v>
+        <v>1.607295577333989</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799622650893021</v>
+        <v>4.799612704436385</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.139950878859032</v>
+        <v>3.140088229121929</v>
       </c>
       <c r="C309" t="n">
-        <v>2.240759559282801</v>
+        <v>2.240271243494263</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5596051493185872</v>
+        <v>0.5585843538538748</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405824958069072</v>
+        <v>5.405833811778549</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.758402248185401</v>
+        <v>5.757405261988979</v>
       </c>
       <c r="C310" t="n">
-        <v>6.636099455735489</v>
+        <v>6.63687121117309</v>
       </c>
       <c r="D310" t="n">
-        <v>2.76549707231315</v>
+        <v>2.769750793261272</v>
       </c>
       <c r="E310" t="n">
-        <v>8.393158771209318</v>
+        <v>8.393243956209684</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.91816944655301</v>
+        <v>3.917584488213244</v>
       </c>
       <c r="C311" t="n">
-        <v>3.197650006796549</v>
+        <v>3.198657320743914</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6442598286695356</v>
+        <v>0.646418826480244</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879471375029154</v>
+        <v>4.879478722600861</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.036058739567983</v>
+        <v>4.036051333399393</v>
       </c>
       <c r="C312" t="n">
-        <v>2.368900511044503</v>
+        <v>2.36872419624099</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.060594834522255</v>
+        <v>-1.059904600167316</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824387856737467</v>
+        <v>5.824407866180348</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.253746424275916</v>
+        <v>3.253612330708755</v>
       </c>
       <c r="C313" t="n">
-        <v>2.404123369015831</v>
+        <v>2.405124441017548</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04620825673125051</v>
+        <v>0.04681182992634092</v>
       </c>
       <c r="E313" t="n">
-        <v>6.335553873975153</v>
+        <v>6.335610090243082</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.28593663798722</v>
+        <v>4.285895104154136</v>
       </c>
       <c r="C314" t="n">
-        <v>3.915571785482741</v>
+        <v>3.916891341435891</v>
       </c>
       <c r="D314" t="n">
-        <v>1.486334832780245</v>
+        <v>1.486304821221496</v>
       </c>
       <c r="E314" t="n">
-        <v>8.647459774679955</v>
+        <v>8.647713509526112</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.687342990189755</v>
+        <v>1.687480559507604</v>
       </c>
       <c r="C315" t="n">
-        <v>2.646338681866145</v>
+        <v>2.645823961249261</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9295256736113533</v>
+        <v>0.9296600667297206</v>
       </c>
       <c r="E315" t="n">
-        <v>4.024659605629077</v>
+        <v>4.024721343156634</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.655128323708245</v>
+        <v>2.65528832242059</v>
       </c>
       <c r="C316" t="n">
-        <v>2.861654929391655</v>
+        <v>2.86230471885256</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3953134546281989</v>
+        <v>0.3953314295453314</v>
       </c>
       <c r="E316" t="n">
-        <v>3.649611570450584</v>
+        <v>3.649647017308832</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.79053333382933</v>
+        <v>8.79104761809295</v>
       </c>
       <c r="C317" t="n">
-        <v>9.072207290747315</v>
+        <v>9.070329246478348</v>
       </c>
       <c r="D317" t="n">
-        <v>0.389782245057213</v>
+        <v>0.3871137182933193</v>
       </c>
       <c r="E317" t="n">
-        <v>7.313312846583009</v>
+        <v>7.313431324008568</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.374646991795661</v>
+        <v>4.374911996349851</v>
       </c>
       <c r="C318" t="n">
-        <v>5.382412590552943</v>
+        <v>5.380307394361195</v>
       </c>
       <c r="D318" t="n">
-        <v>2.156681916595327</v>
+        <v>2.154021522064054</v>
       </c>
       <c r="E318" t="n">
-        <v>5.210676464698194</v>
+        <v>5.210731513265499</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.192217064205694</v>
+        <v>4.192690202599625</v>
       </c>
       <c r="C319" t="n">
-        <v>3.332798399506109</v>
+        <v>3.331751263426797</v>
       </c>
       <c r="D319" t="n">
-        <v>2.732181154468671</v>
+        <v>2.72978591836901</v>
       </c>
       <c r="E319" t="n">
-        <v>3.721747213807114</v>
+        <v>3.721653543136472</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.750261529506529</v>
+        <v>6.750808422634536</v>
       </c>
       <c r="C320" t="n">
-        <v>6.785626492930619</v>
+        <v>6.783096197641592</v>
       </c>
       <c r="D320" t="n">
-        <v>2.22834444450053</v>
+        <v>2.224871373074144</v>
       </c>
       <c r="E320" t="n">
-        <v>3.065047779428598</v>
+        <v>3.064929864881161</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.9270651928095</v>
+        <v>5.927411505468494</v>
       </c>
       <c r="C321" t="n">
-        <v>4.665414285502378</v>
+        <v>4.664202750414792</v>
       </c>
       <c r="D321" t="n">
-        <v>1.453880921071615</v>
+        <v>1.45177496874942</v>
       </c>
       <c r="E321" t="n">
-        <v>2.664960406208206</v>
+        <v>2.664781808458483</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.554212216083387</v>
+        <v>5.552686575637411</v>
       </c>
       <c r="C322" t="n">
-        <v>3.510495413474279</v>
+        <v>3.514871968219735</v>
       </c>
       <c r="D322" t="n">
-        <v>0.05067715541509088</v>
+        <v>0.0586130417141506</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5175512589487119</v>
+        <v>-0.5177892437046472</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.346929079851702</v>
+        <v>4.346038976920652</v>
       </c>
       <c r="C323" t="n">
-        <v>5.202365513068719</v>
+        <v>5.205975750928782</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8384898561793808</v>
+        <v>0.8432042113313498</v>
       </c>
       <c r="E323" t="n">
-        <v>4.169839613043513</v>
+        <v>4.16976489006553</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.536716339400984</v>
+        <v>7.536522747343555</v>
       </c>
       <c r="C324" t="n">
-        <v>7.003314846655972</v>
+        <v>7.002884399921361</v>
       </c>
       <c r="D324" t="n">
-        <v>3.827015893249608</v>
+        <v>3.828836263805502</v>
       </c>
       <c r="E324" t="n">
-        <v>2.187535571725507</v>
+        <v>2.187370542862621</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.078546372599836</v>
+        <v>6.078179228986191</v>
       </c>
       <c r="C325" t="n">
-        <v>5.606345794054546</v>
+        <v>5.608264317024858</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1501059311637576</v>
+        <v>0.1529497590927242</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892497783893777</v>
+        <v>2.892471256168938</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.85523605522269</v>
+        <v>5.855193979626327</v>
       </c>
       <c r="C326" t="n">
-        <v>4.981603318139105</v>
+        <v>4.984027565055649</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7925817929019141</v>
+        <v>0.7930485060161585</v>
       </c>
       <c r="E326" t="n">
-        <v>4.474269749795323</v>
+        <v>4.474454408740747</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.91637715666085</v>
+        <v>9.916455915459021</v>
       </c>
       <c r="C327" t="n">
-        <v>9.272798543509886</v>
+        <v>9.271569512034317</v>
       </c>
       <c r="D327" t="n">
-        <v>2.693797890469218</v>
+        <v>2.692775875550191</v>
       </c>
       <c r="E327" t="n">
-        <v>7.798920005822785</v>
+        <v>7.799103636565241</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41356439825318</v>
+        <v>10.41396890619559</v>
       </c>
       <c r="C328" t="n">
-        <v>9.055530592767113</v>
+        <v>9.054345282061105</v>
       </c>
       <c r="D328" t="n">
-        <v>3.150994762927239</v>
+        <v>3.148485567460546</v>
       </c>
       <c r="E328" t="n">
-        <v>7.360797462364754</v>
+        <v>7.360913736661878</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>3.998850424192235</v>
+        <v>3.999767224119832</v>
       </c>
       <c r="C329" t="n">
-        <v>3.011411127452912</v>
+        <v>3.010941864946504</v>
       </c>
       <c r="D329" t="n">
-        <v>2.845499663330253</v>
+        <v>2.841342968378302</v>
       </c>
       <c r="E329" t="n">
-        <v>3.597133465778968</v>
+        <v>3.597224784867126</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.270035672976948</v>
+        <v>6.270540906116095</v>
       </c>
       <c r="C330" t="n">
-        <v>5.548933310935666</v>
+        <v>5.5455624575657</v>
       </c>
       <c r="D330" t="n">
-        <v>1.319044113729628</v>
+        <v>1.314713179146154</v>
       </c>
       <c r="E330" t="n">
-        <v>5.629508998554345</v>
+        <v>5.62957449231154</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.977062345857886</v>
+        <v>5.977701124544832</v>
       </c>
       <c r="C331" t="n">
-        <v>7.428627857385428</v>
+        <v>7.425259287378982</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.06903381078044</v>
+        <v>-1.073143724705927</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981062933200953</v>
+        <v>4.981045819530672</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.248222464529139</v>
+        <v>4.249059791098464</v>
       </c>
       <c r="C332" t="n">
-        <v>4.015431279075732</v>
+        <v>4.011248351377028</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.617113906715195</v>
+        <v>-1.622163239212038</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511847141031922</v>
+        <v>4.511854856918562</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.821899960124497</v>
+        <v>3.822610816149385</v>
       </c>
       <c r="C333" t="n">
-        <v>3.774978281070585</v>
+        <v>3.770494100556143</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.158390982991255</v>
+        <v>-3.163123162085235</v>
       </c>
       <c r="E333" t="n">
-        <v>4.435697085413026</v>
+        <v>4.435674702355308</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.908789620704688</v>
+        <v>2.906484997996461</v>
       </c>
       <c r="C334" t="n">
-        <v>4.909638142963191</v>
+        <v>4.917574697929994</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.620857506476825</v>
+        <v>-1.60814433831129</v>
       </c>
       <c r="E334" t="n">
-        <v>5.110231344346339</v>
+        <v>5.110251640010643</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.724116331453486</v>
+        <v>3.722892619018814</v>
       </c>
       <c r="C335" t="n">
-        <v>1.780644777987694</v>
+        <v>1.785264433197198</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.586457792999886</v>
+        <v>-2.579336178991032</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832546706221551</v>
+        <v>3.832604457232436</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.723254619881855</v>
+        <v>3.72279885007456</v>
       </c>
       <c r="C336" t="n">
-        <v>3.87721549605422</v>
+        <v>3.877817628007629</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.340515664104726</v>
+        <v>-3.336511024344813</v>
       </c>
       <c r="E336" t="n">
-        <v>3.492816570750312</v>
+        <v>3.492810176767258</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.994708805344225</v>
+        <v>1.99420003203703</v>
       </c>
       <c r="C337" t="n">
-        <v>1.405237928077185</v>
+        <v>1.406554331476717</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.148651035124272</v>
+        <v>-3.144661900411705</v>
       </c>
       <c r="E337" t="n">
-        <v>3.632398586433583</v>
+        <v>3.632483923988228</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.293304044554057</v>
+        <v>3.293169958190312</v>
       </c>
       <c r="C338" t="n">
-        <v>2.203016424240611</v>
+        <v>2.206490287610241</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.366495153001569</v>
+        <v>-2.365461419332715</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875779619611517</v>
+        <v>1.875752466522385</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6629817420018336</v>
+        <v>0.663219449907948</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.193244531954541</v>
+        <v>-2.192676207821453</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.151619197975918</v>
+        <v>-2.151899351101028</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6041292173951329</v>
+        <v>-0.6042176432110913</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.588291544598698</v>
+        <v>3.588821701094558</v>
       </c>
       <c r="C340" t="n">
-        <v>0.4418959461722549</v>
+        <v>0.4423091010969493</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.719521287272963</v>
+        <v>-2.722406091486917</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.147301409546964</v>
+        <v>-1.147415716336653</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.785744018977622</v>
+        <v>4.7869032102692</v>
       </c>
       <c r="C341" t="n">
-        <v>1.327143518241636</v>
+        <v>1.326256945608106</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.0499819667822</v>
+        <v>-3.054190773451726</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702166569742891</v>
+        <v>1.702101590217375</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.67070774648426</v>
+        <v>5.671359088322458</v>
       </c>
       <c r="C342" t="n">
-        <v>2.745743068175854</v>
+        <v>2.741103529710287</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7340795162031899</v>
+        <v>-0.7391082132028992</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1298944525745971</v>
+        <v>-0.129980803571117</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.827439361410325</v>
+        <v>5.828406794674401</v>
       </c>
       <c r="C343" t="n">
-        <v>1.50618391452142</v>
+        <v>1.502274794058511</v>
       </c>
       <c r="D343" t="n">
-        <v>2.372804159713393</v>
+        <v>2.366313493768146</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6818814396501782</v>
+        <v>0.681809967252156</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.948826942067398</v>
+        <v>5.949982966841039</v>
       </c>
       <c r="C344" t="n">
-        <v>3.897483161713189</v>
+        <v>3.891256509584196</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9172868329252459</v>
+        <v>0.9078509364062626</v>
       </c>
       <c r="E344" t="n">
-        <v>2.712679408935537</v>
+        <v>2.712656209761466</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26134861402348</v>
+        <v>10.26229908864658</v>
       </c>
       <c r="C345" t="n">
-        <v>7.559162940716613</v>
+        <v>7.55155252138302</v>
       </c>
       <c r="D345" t="n">
-        <v>7.744826118357517</v>
+        <v>7.735068700801961</v>
       </c>
       <c r="E345" t="n">
-        <v>2.755001610173413</v>
+        <v>2.75493463512706</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.152593761168631</v>
+        <v>2.149509157114426</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4137102870201192</v>
+        <v>-0.4013910119870623</v>
       </c>
       <c r="D346" t="n">
-        <v>1.639155722462848</v>
+        <v>1.659197072299334</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254286460953625</v>
+        <v>2.254541910006469</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.177383265308189</v>
+        <v>5.175899407127571</v>
       </c>
       <c r="C347" t="n">
-        <v>3.120591789141325</v>
+        <v>3.126628164388201</v>
       </c>
       <c r="D347" t="n">
-        <v>4.054073905615696</v>
+        <v>4.065169927606838</v>
       </c>
       <c r="E347" t="n">
-        <v>2.133414027673108</v>
+        <v>2.133421052055473</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.56473479421977</v>
+        <v>3.56400634689511</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.6294406240571759</v>
+        <v>-0.6278121693587435</v>
       </c>
       <c r="D348" t="n">
-        <v>4.249441206464155</v>
+        <v>4.256437140203251</v>
       </c>
       <c r="E348" t="n">
-        <v>3.131185637755718</v>
+        <v>3.131287853295173</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.717834867279948</v>
+        <v>6.71721641499925</v>
       </c>
       <c r="C349" t="n">
-        <v>6.143163332919821</v>
+        <v>6.144475619017276</v>
       </c>
       <c r="D349" t="n">
-        <v>6.306883916164163</v>
+        <v>6.312040487001069</v>
       </c>
       <c r="E349" t="n">
-        <v>6.032262126468568</v>
+        <v>6.032283316659037</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.377590874073435</v>
+        <v>5.377441030180896</v>
       </c>
       <c r="C350" t="n">
-        <v>3.21111640742886</v>
+        <v>3.214961521479931</v>
       </c>
       <c r="D350" t="n">
-        <v>6.18244034232498</v>
+        <v>6.183706810830847</v>
       </c>
       <c r="E350" t="n">
-        <v>6.714528123720997</v>
+        <v>6.714336106492524</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.024693668014303</v>
+        <v>6.025100106245129</v>
       </c>
       <c r="C351" t="n">
-        <v>4.305335427011481</v>
+        <v>4.302728165243375</v>
       </c>
       <c r="D351" t="n">
-        <v>1.673494699697042</v>
+        <v>1.671882742630815</v>
       </c>
       <c r="E351" t="n">
-        <v>8.081055773753686</v>
+        <v>8.080968001200217</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26612231914265</v>
+        <v>-53.26587501949599</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.30523771346016</v>
+        <v>-49.30534339974876</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.32509283422183</v>
+        <v>-44.32824723716157</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.877166368574956</v>
+        <v>-1.877178554837333</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40230498886675</v>
+        <v>-99.40229582195985</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.1174828070718</v>
+        <v>-98.11754410888805</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69149983367343</v>
+        <v>-88.69238543028338</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50747971378924</v>
+        <v>-52.50749298003448</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.8042621053352</v>
+        <v>-98.80425257657224</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98495974911418</v>
+        <v>-95.9852018807061</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16139941854617</v>
+        <v>-82.16286694982972</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70197103635</v>
+        <v>-50.70197899773139</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13282276520955</v>
+        <v>-98.13280177970366</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.3519063685369</v>
+        <v>-94.35218863611217</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41263348346014</v>
+        <v>-81.41436557611279</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98608549980295</v>
+        <v>-42.98608935280991</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74199970422606</v>
+        <v>-97.74196480815228</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.6285602172082</v>
+        <v>-93.62903307855966</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.63797025889781</v>
+        <v>-75.64141218243185</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11242225600495</v>
+        <v>-43.11248752149447</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46166901367718</v>
+        <v>-97.46164401368378</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99088037182241</v>
+        <v>-90.99128471396874</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.1919545779833</v>
+        <v>-74.19502849462474</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65836828852478</v>
+        <v>-45.65843261822262</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43050525173668</v>
+        <v>-97.43060236836762</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90359987578471</v>
+        <v>-89.90187970295483</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.9753138013957</v>
+        <v>-74.96841964775037</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17169280064977</v>
+        <v>-40.17129844860493</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07628068129887</v>
+        <v>-90.07647278193744</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.37500045267475</v>
+        <v>-81.37366181696632</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.97179206954705</v>
+        <v>-74.96776404735463</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.3487267586022</v>
+        <v>-31.3485150388641</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.7661788098419</v>
+        <v>-76.76638039393484</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.57069286413977</v>
+        <v>-65.5702111755181</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85619619720553</v>
+        <v>-71.85311996017079</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.58070650746849</v>
+        <v>-12.58036494458561</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.8198269919889</v>
+        <v>-74.8199737523375</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.34781411612703</v>
+        <v>-66.34714291983755</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13541291491849</v>
+        <v>-70.13298332197402</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80238736262967</v>
+        <v>-16.80245118944989</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68260252288602</v>
+        <v>11.68464061678798</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37087360113893</v>
+        <v>11.37179992623476</v>
       </c>
       <c r="D242" t="n">
-        <v>10.14354861849365</v>
+        <v>10.13809594422586</v>
       </c>
       <c r="E242" t="n">
-        <v>7.262825858201394</v>
+        <v>7.26294365441793</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.26944858761676</v>
+        <v>12.27182441353265</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43502059596318</v>
+        <v>12.43549056528717</v>
       </c>
       <c r="D243" t="n">
-        <v>7.816611670134788</v>
+        <v>7.804148087895557</v>
       </c>
       <c r="E243" t="n">
-        <v>8.995052510291313</v>
+        <v>8.995146603689941</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.971689220385932</v>
+        <v>3.973684404288536</v>
       </c>
       <c r="C244" t="n">
-        <v>7.192114693820351</v>
+        <v>7.19171370422429</v>
       </c>
       <c r="D244" t="n">
-        <v>6.051512645415791</v>
+        <v>6.053111950243517</v>
       </c>
       <c r="E244" t="n">
-        <v>8.711365239221491</v>
+        <v>8.711494149691301</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.843953608526007</v>
+        <v>3.842514194422342</v>
       </c>
       <c r="C245" t="n">
-        <v>7.413625223150477</v>
+        <v>7.413548529252623</v>
       </c>
       <c r="D245" t="n">
-        <v>4.809584195369077</v>
+        <v>4.819802225512837</v>
       </c>
       <c r="E245" t="n">
-        <v>8.570871589405748</v>
+        <v>8.570647185491588</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1741036830395393</v>
+        <v>0.1729062162050266</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6934259142654997</v>
+        <v>-0.6940393296377745</v>
       </c>
       <c r="D246" t="n">
-        <v>1.815590073547679</v>
+        <v>1.829842948712579</v>
       </c>
       <c r="E246" t="n">
-        <v>9.47939054502438</v>
+        <v>9.4793499694118</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,16 +11039,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3586227967598998</v>
+        <v>-0.3602099216432286</v>
       </c>
       <c r="C247" t="n">
-        <v>2.284770151265425</v>
+        <v>2.283317599845813</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.620148013177891</v>
+        <v>-1.603676733175974</v>
       </c>
       <c r="E247" t="n">
-        <v>9.101631178317216</v>
+        <v>9.101816096238235</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.549916376604021</v>
+        <v>-1.550579261871043</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.317781047226819</v>
+        <v>-2.318524076956241</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.091293785880622</v>
+        <v>-3.088612500280563</v>
       </c>
       <c r="E248" t="n">
-        <v>8.145476706926779</v>
+        <v>8.145687763628363</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.449790615477942</v>
+        <v>1.450330301633485</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2372891799369392</v>
+        <v>-0.2377493248451823</v>
       </c>
       <c r="D249" t="n">
-        <v>2.498295785306448</v>
+        <v>2.495848285605295</v>
       </c>
       <c r="E249" t="n">
-        <v>7.144037479922516</v>
+        <v>7.144304007646962</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,16 +11168,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.830711813600197</v>
+        <v>4.831640846575325</v>
       </c>
       <c r="C250" t="n">
-        <v>4.687089702921488</v>
+        <v>4.687457213806301</v>
       </c>
       <c r="D250" t="n">
-        <v>6.340993588903965</v>
+        <v>6.334332351779226</v>
       </c>
       <c r="E250" t="n">
-        <v>8.283037423771145</v>
+        <v>8.283189906925426</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8343999942093339</v>
+        <v>0.8317492481482835</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477641306126354</v>
+        <v>1.477763137773014</v>
       </c>
       <c r="D251" t="n">
-        <v>2.658665724635223</v>
+        <v>2.659686656357207</v>
       </c>
       <c r="E251" t="n">
-        <v>8.430068825144765</v>
+        <v>8.430192441595707</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.652579697448655</v>
+        <v>3.651794968638167</v>
       </c>
       <c r="C252" t="n">
         <v>2.968960861279379</v>
       </c>
       <c r="D252" t="n">
-        <v>3.946919683584849</v>
+        <v>3.949783350399261</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19910003932385</v>
+        <v>10.19888951443098</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.120069398439921</v>
+        <v>7.120527904853757</v>
       </c>
       <c r="C253" t="n">
-        <v>8.446283032690305</v>
+        <v>8.446779855526465</v>
       </c>
       <c r="D253" t="n">
-        <v>3.628301407789758</v>
+        <v>3.620981976439896</v>
       </c>
       <c r="E253" t="n">
-        <v>7.9328226303095</v>
+        <v>7.933059469786929</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.373614346434576</v>
+        <v>7.373468175150966</v>
       </c>
       <c r="C254" t="n">
-        <v>7.314348598559883</v>
+        <v>7.314620106886993</v>
       </c>
       <c r="D254" t="n">
-        <v>5.750021199399136</v>
+        <v>5.738175888361385</v>
       </c>
       <c r="E254" t="n">
-        <v>8.193831060668998</v>
+        <v>8.193739697163526</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449807247245553</v>
+        <v>5.449515851324405</v>
       </c>
       <c r="C255" t="n">
-        <v>5.869173489670954</v>
+        <v>5.869304610353132</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549656064040895</v>
+        <v>2.549865349298619</v>
       </c>
       <c r="E255" t="n">
-        <v>6.401576697100575</v>
+        <v>6.401511820200234</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.70557448586542</v>
+        <v>11.70537404485221</v>
       </c>
       <c r="C256" t="n">
-        <v>9.844738548773302</v>
+        <v>9.845550526731595</v>
       </c>
       <c r="D256" t="n">
-        <v>5.666891538783125</v>
+        <v>5.66284201789431</v>
       </c>
       <c r="E256" t="n">
-        <v>7.164864988835373</v>
+        <v>7.164721742316171</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.775120596850815</v>
+        <v>8.77542818036976</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537593441204416</v>
+        <v>8.537560266776122</v>
       </c>
       <c r="D257" t="n">
-        <v>5.103217689620099</v>
+        <v>5.101334752693742</v>
       </c>
       <c r="E257" t="n">
-        <v>7.456115711852385</v>
+        <v>7.456253016537628</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92013907973419</v>
+        <v>11.92068582296475</v>
       </c>
       <c r="C258" t="n">
-        <v>11.75164521095293</v>
+        <v>11.75159830514207</v>
       </c>
       <c r="D258" t="n">
-        <v>8.785017910246019</v>
+        <v>8.781324570704886</v>
       </c>
       <c r="E258" t="n">
-        <v>7.927129318198212</v>
+        <v>7.92711107769617</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.4532574300735</v>
+        <v>11.45407666270382</v>
       </c>
       <c r="C259" t="n">
-        <v>9.1011448199664</v>
+        <v>9.101299589791578</v>
       </c>
       <c r="D259" t="n">
-        <v>7.832121121588376</v>
+        <v>7.828928562078286</v>
       </c>
       <c r="E259" t="n">
-        <v>8.261372742916983</v>
+        <v>8.261273995047258</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.847286920480336</v>
+        <v>8.847605594092322</v>
       </c>
       <c r="C260" t="n">
-        <v>9.291703570333688</v>
+        <v>9.291474702900949</v>
       </c>
       <c r="D260" t="n">
-        <v>8.070754866380092</v>
+        <v>8.076791962944153</v>
       </c>
       <c r="E260" t="n">
-        <v>8.66611628033076</v>
+        <v>8.665978052139355</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52716548783277</v>
+        <v>12.52765277214047</v>
       </c>
       <c r="C261" t="n">
-        <v>10.31196123614533</v>
+        <v>10.3120736612776</v>
       </c>
       <c r="D261" t="n">
-        <v>5.620958226393125</v>
+        <v>5.621018933552402</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40881220320906</v>
+        <v>10.40860106696149</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,16 +11684,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.793655061241965</v>
+        <v>6.794189953421315</v>
       </c>
       <c r="C262" t="n">
-        <v>6.467351327895488</v>
+        <v>6.467276998132876</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8198787653179607</v>
+        <v>-0.812815685298629</v>
       </c>
       <c r="E262" t="n">
-        <v>8.713914659790811</v>
+        <v>8.713933682035591</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.093620294632721</v>
+        <v>9.092185984173472</v>
       </c>
       <c r="C263" t="n">
-        <v>7.433787219016663</v>
+        <v>7.433948810621849</v>
       </c>
       <c r="D263" t="n">
-        <v>3.15144227618569</v>
+        <v>3.15627524797657</v>
       </c>
       <c r="E263" t="n">
-        <v>8.716113492045153</v>
+        <v>8.716259017321804</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42333448522501</v>
+        <v>13.42257415197752</v>
       </c>
       <c r="C264" t="n">
-        <v>11.26971509547989</v>
+        <v>11.27019889830092</v>
       </c>
       <c r="D264" t="n">
-        <v>4.656347057436538</v>
+        <v>4.654979096594181</v>
       </c>
       <c r="E264" t="n">
-        <v>6.304587304294107</v>
+        <v>6.305006567280524</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.054294934555116</v>
+        <v>8.053819701879238</v>
       </c>
       <c r="C265" t="n">
-        <v>5.794022576852109</v>
+        <v>5.794106788654574</v>
       </c>
       <c r="D265" t="n">
-        <v>2.71641594606542</v>
+        <v>2.717560983108203</v>
       </c>
       <c r="E265" t="n">
-        <v>7.346200537343783</v>
+        <v>7.346465086049925</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.578846898154352</v>
+        <v>2.578820343783894</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2241211116561725</v>
+        <v>-0.2245512661486315</v>
       </c>
       <c r="D266" t="n">
-        <v>2.194968155063637</v>
+        <v>2.191586365425113</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01842708859775</v>
+        <v>12.01832253568254</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.100266055854341</v>
+        <v>5.099772737898189</v>
       </c>
       <c r="C267" t="n">
-        <v>1.659179416797363</v>
+        <v>1.658699619594484</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454303548915094</v>
+        <v>3.454108351003771</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53904723423938</v>
+        <v>13.53886632032826</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.828622124273997</v>
+        <v>5.828475895128959</v>
       </c>
       <c r="C268" t="n">
-        <v>3.421387480517191</v>
+        <v>3.421548541412056</v>
       </c>
       <c r="D268" t="n">
-        <v>0.911014414903244</v>
+        <v>0.9093427411662747</v>
       </c>
       <c r="E268" t="n">
-        <v>15.1113500085152</v>
+        <v>15.11118128038824</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.374487960633398</v>
+        <v>2.374814092490851</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7172955387181545</v>
+        <v>0.7169262339075333</v>
       </c>
       <c r="D269" t="n">
-        <v>2.950098696797943</v>
+        <v>2.948239610933534</v>
       </c>
       <c r="E269" t="n">
-        <v>10.12945462651837</v>
+        <v>10.12965003525876</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.697873951287644</v>
+        <v>2.698728572058817</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3383589182023083</v>
+        <v>0.338323313496347</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.517208324774577</v>
+        <v>-1.520108238084339</v>
       </c>
       <c r="E270" t="n">
-        <v>11.774253596161</v>
+        <v>11.77436787613366</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.116074780302426</v>
+        <v>4.1170286148702</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272021473100417</v>
+        <v>3.272427561831059</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.16949369604179</v>
+        <v>-1.173129380273774</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72625145561899</v>
+        <v>12.72620724671418</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.815137303658545</v>
+        <v>3.815701510398828</v>
       </c>
       <c r="C272" t="n">
-        <v>2.834388349028183</v>
+        <v>2.83458859835799</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.927431334603503</v>
+        <v>-2.924067858742574</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49996359540693</v>
+        <v>12.49980948275904</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.044820516362389</v>
+        <v>2.045383087702635</v>
       </c>
       <c r="C273" t="n">
-        <v>2.702663636126212</v>
+        <v>2.702892209386887</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1135088307588905</v>
+        <v>-0.1120085590475717</v>
       </c>
       <c r="E273" t="n">
-        <v>12.1668099989358</v>
+        <v>12.16657769524911</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1458328881010051</v>
+        <v>-0.1454392921755532</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2302787624065772</v>
+        <v>0.2300987024659751</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03529489346314474</v>
+        <v>0.03731093430758836</v>
       </c>
       <c r="E274" t="n">
-        <v>11.93180948639836</v>
+        <v>11.9316034952414</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3204684112767198</v>
+        <v>-0.3224386192231865</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4549534610838402</v>
+        <v>-0.4547999913968703</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.021317034944414</v>
+        <v>-2.024834462133818</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91094988835399</v>
+        <v>10.91071788024265</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994474031963757</v>
+        <v>-3.994996269437201</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.154708767584547</v>
+        <v>-4.155036353267983</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.715637542524752</v>
+        <v>-3.714823441797976</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912239901004115</v>
+        <v>8.912259611121499</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.363624742266402</v>
+        <v>-3.36398150404067</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.722746143251687</v>
+        <v>-3.722971987700585</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.387554482510191</v>
+        <v>-3.385806427301685</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79873037991243</v>
+        <v>10.79841385698834</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.268991308012525</v>
+        <v>3.268299826000476</v>
       </c>
       <c r="C278" t="n">
-        <v>3.63478035862872</v>
+        <v>3.634761527665509</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.624000035643847</v>
+        <v>-1.618476029695604</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127531255002117</v>
+        <v>6.127539949905514</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1243786339276909</v>
+        <v>-0.1248149338431426</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4633741787321455</v>
+        <v>0.4631999798629938</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3364836307661156</v>
+        <v>-0.3326610515336004</v>
       </c>
       <c r="E279" t="n">
-        <v>4.000276547684467</v>
+        <v>4.000362299389892</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848811494188396</v>
+        <v>-1.848675231143027</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.182782165693842</v>
+        <v>-2.182937024782661</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.8006503748713034</v>
+        <v>-0.7988691568516337</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4652168154958281</v>
+        <v>0.4654666227630555</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.169635046127283</v>
+        <v>2.169835752018945</v>
       </c>
       <c r="C281" t="n">
-        <v>1.856290110130976</v>
+        <v>1.856071836568662</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.090850812002355</v>
+        <v>-3.089522496670549</v>
       </c>
       <c r="E281" t="n">
-        <v>3.989581391316244</v>
+        <v>3.989778986114589</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.200625130209043</v>
+        <v>1.201594201999434</v>
       </c>
       <c r="C282" t="n">
-        <v>1.62540112062437</v>
+        <v>1.625684581826459</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2871446070950023</v>
+        <v>0.283189305931586</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9932889629297836</v>
+        <v>0.9934947647115777</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.129584428047914</v>
+        <v>1.130787456887816</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5619671036124929</v>
+        <v>0.562303764508143</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1533572566756236</v>
+        <v>0.1462385870216965</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1321949381217546</v>
+        <v>-0.1320386431446274</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.5490529398984</v>
+        <v>2.550113790153818</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05079932328950765</v>
+        <v>-0.05080133246483376</v>
       </c>
       <c r="D284" t="n">
-        <v>2.829531067683511</v>
+        <v>2.830764590627677</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7775203819404997</v>
+        <v>0.7776460427552312</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4599469162709147</v>
+        <v>0.460707648489378</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7836782932882591</v>
+        <v>-0.7839513086775662</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.492171094257544</v>
+        <v>-1.487965150005688</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2721647859632581</v>
+        <v>0.2723105005556503</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656342964633464</v>
+        <v>4.657009621450636</v>
       </c>
       <c r="C286" t="n">
-        <v>1.850906588888157</v>
+        <v>1.850599923955465</v>
       </c>
       <c r="D286" t="n">
-        <v>2.955943571908004</v>
+        <v>2.953478767329853</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268320260112876</v>
+        <v>1.268342016622737</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.822053697348983</v>
+        <v>5.818921236283425</v>
       </c>
       <c r="C287" t="n">
-        <v>3.944626523417405</v>
+        <v>3.94516131425473</v>
       </c>
       <c r="D287" t="n">
-        <v>4.86885647382258</v>
+        <v>4.857197010275716</v>
       </c>
       <c r="E287" t="n">
-        <v>2.678103862462433</v>
+        <v>2.677999681970755</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480554173040229</v>
+        <v>3.479289448574963</v>
       </c>
       <c r="C288" t="n">
-        <v>2.95242412292458</v>
+        <v>2.952421376744319</v>
       </c>
       <c r="D288" t="n">
-        <v>2.108896313123276</v>
+        <v>2.10541467384231</v>
       </c>
       <c r="E288" t="n">
-        <v>3.365564859802772</v>
+        <v>3.365422797723139</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.847878879761771</v>
+        <v>6.84725276116831</v>
       </c>
       <c r="C289" t="n">
-        <v>6.018260851900581</v>
+        <v>6.018493034916461</v>
       </c>
       <c r="D289" t="n">
-        <v>2.233920494575048</v>
+        <v>2.229873552892614</v>
       </c>
       <c r="E289" t="n">
-        <v>3.824099547091975</v>
+        <v>3.823818062760176</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8711220332354275</v>
+        <v>0.8710200345882546</v>
       </c>
       <c r="C290" t="n">
-        <v>1.164266514520418</v>
+        <v>1.164137096514128</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.212796487900004</v>
+        <v>-2.203764345332337</v>
       </c>
       <c r="E290" t="n">
-        <v>2.404111615381765</v>
+        <v>2.404241124067608</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.289829428954261</v>
+        <v>3.289708031672234</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302512225884957</v>
+        <v>3.302402419068073</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.256276738462503</v>
+        <v>-1.245855577294008</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627896522326624</v>
+        <v>3.627915569584772</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.307673867279795</v>
+        <v>6.307625136017281</v>
       </c>
       <c r="C292" t="n">
-        <v>5.588654503852486</v>
+        <v>5.588465923850117</v>
       </c>
       <c r="D292" t="n">
-        <v>2.175583891336719</v>
+        <v>2.181732420371274</v>
       </c>
       <c r="E292" t="n">
-        <v>4.880427764878936</v>
+        <v>4.880453963756404</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.537075714295468</v>
+        <v>3.537623971663129</v>
       </c>
       <c r="C293" t="n">
-        <v>2.372021712951278</v>
+        <v>2.371741330923061</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532099393556697</v>
+        <v>2.532303075130748</v>
       </c>
       <c r="E293" t="n">
-        <v>4.242467255579663</v>
+        <v>4.24243778839708</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.371049123193908</v>
+        <v>8.372202411176243</v>
       </c>
       <c r="C294" t="n">
-        <v>5.91078434973995</v>
+        <v>5.911089667085023</v>
       </c>
       <c r="D294" t="n">
-        <v>4.200848378436817</v>
+        <v>4.196747882438312</v>
       </c>
       <c r="E294" t="n">
-        <v>6.252958946703191</v>
+        <v>6.252838886817402</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.597059652133686</v>
+        <v>6.598349417584903</v>
       </c>
       <c r="C295" t="n">
-        <v>5.385979176157019</v>
+        <v>5.386362779603315</v>
       </c>
       <c r="D295" t="n">
-        <v>6.114208461704473</v>
+        <v>6.107721442050784</v>
       </c>
       <c r="E295" t="n">
-        <v>6.950266300005281</v>
+        <v>6.950074528828254</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.144273295526047</v>
+        <v>5.14566062488464</v>
       </c>
       <c r="C296" t="n">
-        <v>5.711607260717977</v>
+        <v>5.711798727705042</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1171567512838978</v>
+        <v>0.1193348333601518</v>
       </c>
       <c r="E296" t="n">
-        <v>4.681028165210943</v>
+        <v>4.680961339939604</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.861897319185847</v>
+        <v>3.862907485922151</v>
       </c>
       <c r="C297" t="n">
-        <v>4.003598833455047</v>
+        <v>4.003352453704156</v>
       </c>
       <c r="D297" t="n">
-        <v>2.951685863700693</v>
+        <v>2.957618943838569</v>
       </c>
       <c r="E297" t="n">
-        <v>4.086295611590907</v>
+        <v>4.086346931474183</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.447950405697386</v>
+        <v>2.449217048959418</v>
       </c>
       <c r="C298" t="n">
-        <v>1.07006429895169</v>
+        <v>1.069781436897532</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4397667630828606</v>
+        <v>0.4407108509185909</v>
       </c>
       <c r="E298" t="n">
-        <v>3.051073022352457</v>
+        <v>3.051051989548026</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.296773051608981</v>
+        <v>3.292262972139737</v>
       </c>
       <c r="C299" t="n">
-        <v>2.792192891017886</v>
+        <v>2.792711363540645</v>
       </c>
       <c r="D299" t="n">
-        <v>1.828000376345029</v>
+        <v>1.819410034055413</v>
       </c>
       <c r="E299" t="n">
-        <v>2.812994947144243</v>
+        <v>2.813055311686097</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.51053011873892</v>
+        <v>4.508892651518348</v>
       </c>
       <c r="C300" t="n">
-        <v>3.71608160592094</v>
+        <v>3.716257357514818</v>
       </c>
       <c r="D300" t="n">
-        <v>3.903624196849131</v>
+        <v>3.897508212151379</v>
       </c>
       <c r="E300" t="n">
-        <v>3.748910456895849</v>
+        <v>3.748844294470466</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.778752949139919</v>
+        <v>4.778010473638417</v>
       </c>
       <c r="C301" t="n">
-        <v>3.181706807484774</v>
+        <v>3.181932621226702</v>
       </c>
       <c r="D301" t="n">
-        <v>5.335078299739093</v>
+        <v>5.325802069325136</v>
       </c>
       <c r="E301" t="n">
-        <v>1.882868608645127</v>
+        <v>1.88289511545523</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.3394559751065</v>
+        <v>5.339074327576609</v>
       </c>
       <c r="C302" t="n">
-        <v>3.380357695727665</v>
+        <v>3.380262217806895</v>
       </c>
       <c r="D302" t="n">
-        <v>4.100154430881031</v>
+        <v>4.101048762309722</v>
       </c>
       <c r="E302" t="n">
-        <v>1.198635890549404</v>
+        <v>1.198764324836388</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.231753857958599</v>
+        <v>5.231598900479395</v>
       </c>
       <c r="C303" t="n">
-        <v>3.151943095958987</v>
+        <v>3.151893340493417</v>
       </c>
       <c r="D303" t="n">
-        <v>1.617592694161174</v>
+        <v>1.624484739531495</v>
       </c>
       <c r="E303" t="n">
-        <v>3.117560732807223</v>
+        <v>3.117673656498843</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.056024315622528</v>
+        <v>1.05630887912378</v>
       </c>
       <c r="C304" t="n">
-        <v>0.499462026439379</v>
+        <v>0.4990242613022389</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6782142743698594</v>
+        <v>-0.6709775930660133</v>
       </c>
       <c r="E304" t="n">
-        <v>3.835246887414656</v>
+        <v>3.83529235454052</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.068998287672951</v>
+        <v>1.069971846592255</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1455991788466893</v>
+        <v>0.1453421817021683</v>
       </c>
       <c r="D305" t="n">
-        <v>2.19828885705915</v>
+        <v>2.196735029316299</v>
       </c>
       <c r="E305" t="n">
-        <v>1.964897112425512</v>
+        <v>1.964970492289275</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6301968249906587</v>
+        <v>0.6315513373286175</v>
       </c>
       <c r="C306" t="n">
-        <v>0.02936540384361752</v>
+        <v>0.02922225480648244</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.263269290334657</v>
+        <v>-1.262580363733534</v>
       </c>
       <c r="E306" t="n">
-        <v>2.32177060924541</v>
+        <v>2.321841001370695</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.18948114395574</v>
+        <v>2.191100081864938</v>
       </c>
       <c r="C307" t="n">
-        <v>1.363954757505947</v>
+        <v>1.363826001296409</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.598957314655193</v>
+        <v>-2.597756008844454</v>
       </c>
       <c r="E307" t="n">
-        <v>3.142978859727719</v>
+        <v>3.143031173341049</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.770958678423629</v>
+        <v>1.772799963021554</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2721422211753088</v>
+        <v>0.2720460003526215</v>
       </c>
       <c r="D308" t="n">
-        <v>1.607295577333989</v>
+        <v>1.608607897115233</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799612704436385</v>
+        <v>4.799629456566978</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.140088229121929</v>
+        <v>3.141711538041103</v>
       </c>
       <c r="C309" t="n">
-        <v>2.240271243494263</v>
+        <v>2.240057684526509</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5585843538538748</v>
+        <v>0.5633827939527603</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405833811778549</v>
+        <v>5.405823187200864</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.757405261988979</v>
+        <v>5.758981335663704</v>
       </c>
       <c r="C310" t="n">
-        <v>6.63687121117309</v>
+        <v>6.636959422151056</v>
       </c>
       <c r="D310" t="n">
-        <v>2.769750793261272</v>
+        <v>2.772027040968195</v>
       </c>
       <c r="E310" t="n">
-        <v>8.393243956209684</v>
+        <v>8.393180311257421</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.917584488213244</v>
+        <v>3.910517937951496</v>
       </c>
       <c r="C311" t="n">
-        <v>3.198657320743914</v>
+        <v>3.199476036062299</v>
       </c>
       <c r="D311" t="n">
-        <v>0.646418826480244</v>
+        <v>0.6411447137107507</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879478722600861</v>
+        <v>4.8794544947659</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.036051333399393</v>
+        <v>4.033823553989091</v>
       </c>
       <c r="C312" t="n">
-        <v>2.36872419624099</v>
+        <v>2.369017577636989</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.059904600167316</v>
+        <v>-1.064438653188882</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824407866180348</v>
+        <v>5.824374294578827</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.253612330708755</v>
+        <v>3.252311136701436</v>
       </c>
       <c r="C313" t="n">
-        <v>2.405124441017548</v>
+        <v>2.405041856907353</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04681182992634092</v>
+        <v>0.04488891843321685</v>
       </c>
       <c r="E313" t="n">
-        <v>6.335610090243082</v>
+        <v>6.335529023254516</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.285895104154136</v>
+        <v>4.285651398645185</v>
       </c>
       <c r="C314" t="n">
-        <v>3.916891341435891</v>
+        <v>3.916612947176867</v>
       </c>
       <c r="D314" t="n">
-        <v>1.486304821221496</v>
+        <v>1.484681993990433</v>
       </c>
       <c r="E314" t="n">
-        <v>8.647713509526112</v>
+        <v>8.64737544926717</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.687480559507604</v>
+        <v>1.68786180769418</v>
       </c>
       <c r="C315" t="n">
-        <v>2.645823961249261</v>
+        <v>2.645682029253482</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9296600667297206</v>
+        <v>0.931362086009635</v>
       </c>
       <c r="E315" t="n">
-        <v>4.024721343156634</v>
+        <v>4.024641913058113</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.65528832242059</v>
+        <v>2.656070001187616</v>
       </c>
       <c r="C316" t="n">
-        <v>2.86230471885256</v>
+        <v>2.862006885288504</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3953314295453314</v>
+        <v>0.398035388607787</v>
       </c>
       <c r="E316" t="n">
-        <v>3.649647017308832</v>
+        <v>3.649593409796625</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.79104761809295</v>
+        <v>8.792325447121097</v>
       </c>
       <c r="C317" t="n">
-        <v>9.070329246478348</v>
+        <v>9.070661360225563</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3871137182933193</v>
+        <v>0.3838344546402084</v>
       </c>
       <c r="E317" t="n">
-        <v>7.313431324008568</v>
+        <v>7.313277373653326</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.374911996349851</v>
+        <v>4.376753233042874</v>
       </c>
       <c r="C318" t="n">
-        <v>5.380307394361195</v>
+        <v>5.380300658861925</v>
       </c>
       <c r="D318" t="n">
-        <v>2.154021522064054</v>
+        <v>2.152426702935206</v>
       </c>
       <c r="E318" t="n">
-        <v>5.210731513265499</v>
+        <v>5.210660723896221</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.192690202599625</v>
+        <v>4.195058856682277</v>
       </c>
       <c r="C319" t="n">
-        <v>3.331751263426797</v>
+        <v>3.331614097118418</v>
       </c>
       <c r="D319" t="n">
-        <v>2.72978591836901</v>
+        <v>2.731265948804995</v>
       </c>
       <c r="E319" t="n">
-        <v>3.721653543136472</v>
+        <v>3.72178105734382</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.750808422634536</v>
+        <v>6.753412737577769</v>
       </c>
       <c r="C320" t="n">
-        <v>6.783096197641592</v>
+        <v>6.783079114265256</v>
       </c>
       <c r="D320" t="n">
-        <v>2.224871373074144</v>
+        <v>2.224419474154682</v>
       </c>
       <c r="E320" t="n">
-        <v>3.064929864881161</v>
+        <v>3.065093533777863</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.927411505468494</v>
+        <v>5.929999717528878</v>
       </c>
       <c r="C321" t="n">
-        <v>4.664202750414792</v>
+        <v>4.663888514003567</v>
       </c>
       <c r="D321" t="n">
-        <v>1.45177496874942</v>
+        <v>1.458410121513554</v>
       </c>
       <c r="E321" t="n">
-        <v>2.664781808458483</v>
+        <v>2.665013965305785</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.552686575637411</v>
+        <v>5.555130225893157</v>
       </c>
       <c r="C322" t="n">
-        <v>3.514871968219735</v>
+        <v>3.514408466523489</v>
       </c>
       <c r="D322" t="n">
-        <v>0.0586130417141506</v>
+        <v>0.06596630917723445</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5177892437046472</v>
+        <v>-0.5173918244369746</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.346038976920652</v>
+        <v>4.335645049934356</v>
       </c>
       <c r="C323" t="n">
-        <v>5.205975750928782</v>
+        <v>5.207094281189084</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8432042113313498</v>
+        <v>0.8383204505718389</v>
       </c>
       <c r="E323" t="n">
-        <v>4.16976489006553</v>
+        <v>4.169804839820901</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.536522747343555</v>
+        <v>7.53284820641047</v>
       </c>
       <c r="C324" t="n">
-        <v>7.002884399921361</v>
+        <v>7.003507480409454</v>
       </c>
       <c r="D324" t="n">
-        <v>3.828836263805502</v>
+        <v>3.823169999398357</v>
       </c>
       <c r="E324" t="n">
-        <v>2.187370542862621</v>
+        <v>2.187558277838741</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.078179228986191</v>
+        <v>6.076104730675058</v>
       </c>
       <c r="C325" t="n">
-        <v>5.608264317024858</v>
+        <v>5.608153746293887</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1529497590927242</v>
+        <v>0.1563772586133938</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892471256168938</v>
+        <v>2.892486781843306</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.855193979626327</v>
+        <v>5.855039749993973</v>
       </c>
       <c r="C326" t="n">
-        <v>4.984027565055649</v>
+        <v>4.983576960166158</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7930485060161585</v>
+        <v>0.7921929310791054</v>
       </c>
       <c r="E326" t="n">
-        <v>4.474454408740747</v>
+        <v>4.474198049111999</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.916455915459021</v>
+        <v>9.916634867190499</v>
       </c>
       <c r="C327" t="n">
-        <v>9.271569512034317</v>
+        <v>9.271490908973679</v>
       </c>
       <c r="D327" t="n">
-        <v>2.692775875550191</v>
+        <v>2.691234769073936</v>
       </c>
       <c r="E327" t="n">
-        <v>7.799103636565241</v>
+        <v>7.798856385208341</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41396890619559</v>
+        <v>10.41527252165593</v>
       </c>
       <c r="C328" t="n">
-        <v>9.054345282061105</v>
+        <v>9.05424600970488</v>
       </c>
       <c r="D328" t="n">
-        <v>3.148485567460546</v>
+        <v>3.14408055269213</v>
       </c>
       <c r="E328" t="n">
-        <v>7.360913736661878</v>
+        <v>7.360744253916307</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>3.999767224119832</v>
+        <v>4.002121928070879</v>
       </c>
       <c r="C329" t="n">
-        <v>3.010941864946504</v>
+        <v>3.010953462551091</v>
       </c>
       <c r="D329" t="n">
-        <v>2.841342968378302</v>
+        <v>2.837263624024722</v>
       </c>
       <c r="E329" t="n">
-        <v>3.597224784867126</v>
+        <v>3.597097177237329</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.270540906116095</v>
+        <v>6.273420223920079</v>
       </c>
       <c r="C330" t="n">
-        <v>5.5455624575657</v>
+        <v>5.545457903266682</v>
       </c>
       <c r="D330" t="n">
-        <v>1.314713179146154</v>
+        <v>1.312273500675532</v>
       </c>
       <c r="E330" t="n">
-        <v>5.62957449231154</v>
+        <v>5.629501991082808</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.977701124544832</v>
+        <v>5.980956679410476</v>
       </c>
       <c r="C331" t="n">
-        <v>7.425259287378982</v>
+        <v>7.42530406681301</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.073143724705927</v>
+        <v>-1.071865682251916</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981045819530672</v>
+        <v>4.981093333470077</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.249059791098464</v>
+        <v>4.252937942369184</v>
       </c>
       <c r="C332" t="n">
-        <v>4.011248351377028</v>
+        <v>4.011192518133977</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.622163239212038</v>
+        <v>-1.621079774974354</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511854856918562</v>
+        <v>4.511885205010402</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.822610816149385</v>
+        <v>3.826669114195069</v>
       </c>
       <c r="C333" t="n">
-        <v>3.770494100556143</v>
+        <v>3.770353410187033</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.163123162085235</v>
+        <v>-3.157520180689366</v>
       </c>
       <c r="E333" t="n">
-        <v>4.435674702355308</v>
+        <v>4.435689608851456</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.906484997996461</v>
+        <v>2.909809007942465</v>
       </c>
       <c r="C334" t="n">
-        <v>4.917574697929994</v>
+        <v>4.916761875932263</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.60814433831129</v>
+        <v>-1.596966748340245</v>
       </c>
       <c r="E334" t="n">
-        <v>5.110251640010643</v>
+        <v>5.110456393327523</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.722892619018814</v>
+        <v>3.707591046071368</v>
       </c>
       <c r="C335" t="n">
-        <v>1.785264433197198</v>
+        <v>1.787361094299178</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.579336178991032</v>
+        <v>-2.588982707762622</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832604457232436</v>
+        <v>3.832399082481452</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.72279885007456</v>
+        <v>3.717355354321761</v>
       </c>
       <c r="C336" t="n">
-        <v>3.877817628007629</v>
+        <v>3.878580264747566</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.336511024344813</v>
+        <v>-3.341147503474262</v>
       </c>
       <c r="E336" t="n">
-        <v>3.492810176767258</v>
+        <v>3.492747996437973</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.99420003203703</v>
+        <v>1.991213026347172</v>
       </c>
       <c r="C337" t="n">
-        <v>1.406554331476717</v>
+        <v>1.406628680699473</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.144661900411705</v>
+        <v>-3.141292466286627</v>
       </c>
       <c r="E337" t="n">
-        <v>3.632483923988228</v>
+        <v>3.632314262773928</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.293169958190312</v>
+        <v>3.292728556475866</v>
       </c>
       <c r="C338" t="n">
-        <v>2.206490287610241</v>
+        <v>2.205717340324154</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.365461419332715</v>
+        <v>-2.365763768115781</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875752466522385</v>
+        <v>1.875748386403253</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.663219449907948</v>
+        <v>0.6638893592867623</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.192676207821453</v>
+        <v>-2.193440293407145</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.151899351101028</v>
+        <v>-2.149489736240007</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6042176432110913</v>
+        <v>-0.6041222662902967</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.588821701094558</v>
+        <v>3.590804488102206</v>
       </c>
       <c r="C340" t="n">
-        <v>0.4423091010969493</v>
+        <v>0.441568173415896</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.722406091486917</v>
+        <v>-2.725641578788351</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.147415716336653</v>
+        <v>-1.147305080712302</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.7869032102692</v>
+        <v>4.7899001827854</v>
       </c>
       <c r="C341" t="n">
-        <v>1.326256945608106</v>
+        <v>1.326249366479848</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.054190773451726</v>
+        <v>-3.052421289763574</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702101590217375</v>
+        <v>1.702169717902913</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.671359088322458</v>
+        <v>5.675370630167498</v>
       </c>
       <c r="C342" t="n">
-        <v>2.741103529710287</v>
+        <v>2.740708584144858</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7391082132028992</v>
+        <v>-0.7358097197996849</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.129980803571117</v>
+        <v>-0.129858419290263</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.828406794674401</v>
+        <v>5.833347734579153</v>
       </c>
       <c r="C343" t="n">
-        <v>1.502274794058511</v>
+        <v>1.501998643147884</v>
       </c>
       <c r="D343" t="n">
-        <v>2.366313493768146</v>
+        <v>2.370704340660446</v>
       </c>
       <c r="E343" t="n">
-        <v>0.681809967252156</v>
+        <v>0.6819458485371577</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.949982966841039</v>
+        <v>5.955584219633137</v>
       </c>
       <c r="C344" t="n">
-        <v>3.891256509584196</v>
+        <v>3.891012980110053</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9078509364062626</v>
+        <v>0.9068888306149825</v>
       </c>
       <c r="E344" t="n">
-        <v>2.712656209761466</v>
+        <v>2.712770463128944</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26229908864658</v>
+        <v>10.26830585583041</v>
       </c>
       <c r="C345" t="n">
-        <v>7.55155252138302</v>
+        <v>7.551274078968584</v>
       </c>
       <c r="D345" t="n">
-        <v>7.735068700801961</v>
+        <v>7.742113413812213</v>
       </c>
       <c r="E345" t="n">
-        <v>2.75493463512706</v>
+        <v>2.754999513941048</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.149509157114426</v>
+        <v>2.154794311888142</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4013910119870623</v>
+        <v>-0.4026203272377682</v>
       </c>
       <c r="D346" t="n">
-        <v>1.659197072299334</v>
+        <v>1.671961082064066</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254541910006469</v>
+        <v>2.254791288810232</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.175899407127571</v>
+        <v>5.153576622093459</v>
       </c>
       <c r="C347" t="n">
-        <v>3.126628164388201</v>
+        <v>3.130635406483639</v>
       </c>
       <c r="D347" t="n">
-        <v>4.065169927606838</v>
+        <v>4.042137955409042</v>
       </c>
       <c r="E347" t="n">
-        <v>2.133421052055473</v>
+        <v>2.133091278589716</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.56400634689511</v>
+        <v>3.555983695348042</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.6278121693587435</v>
+        <v>-0.6266508040841279</v>
       </c>
       <c r="D348" t="n">
-        <v>4.256437140203251</v>
+        <v>4.247368744673352</v>
       </c>
       <c r="E348" t="n">
-        <v>3.131287853295173</v>
+        <v>3.130994907114748</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.71721641499925</v>
+        <v>6.712832365634469</v>
       </c>
       <c r="C349" t="n">
-        <v>6.144475619017276</v>
+        <v>6.144847590650748</v>
       </c>
       <c r="D349" t="n">
-        <v>6.312040487001069</v>
+        <v>6.310587745295893</v>
       </c>
       <c r="E349" t="n">
-        <v>6.032283316659037</v>
+        <v>6.032114776682218</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.377441030180896</v>
+        <v>5.376802255152047</v>
       </c>
       <c r="C350" t="n">
-        <v>3.214961521479931</v>
+        <v>3.214114320747186</v>
       </c>
       <c r="D350" t="n">
-        <v>6.183706810830847</v>
+        <v>6.181032512370188</v>
       </c>
       <c r="E350" t="n">
-        <v>6.714336106492524</v>
+        <v>6.714474739190224</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.025100106245129</v>
+        <v>6.026140916321499</v>
       </c>
       <c r="C351" t="n">
-        <v>4.302728165243375</v>
+        <v>4.302099760790679</v>
       </c>
       <c r="D351" t="n">
-        <v>1.671882742630815</v>
+        <v>1.672072193293306</v>
       </c>
       <c r="E351" t="n">
-        <v>8.080968001200217</v>
+        <v>8.081014837646471</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26587501949599</v>
+        <v>-53.26472279422453</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.30534339974876</v>
+        <v>-49.30582797114101</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.32824723716157</v>
+        <v>-44.33240913416352</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.877178554837333</v>
+        <v>-1.87722829099457</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40229582195985</v>
+        <v>-99.40227129976248</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11754410888805</v>
+        <v>-98.11754011816366</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69238543028338</v>
+        <v>-88.69243400132918</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50749298003448</v>
+        <v>-52.50749144713836</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80425257657224</v>
+        <v>-98.804188105946</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.9852018807061</v>
+        <v>-95.98523689595045</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16286694982972</v>
+        <v>-82.16183977649882</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70197899773139</v>
+        <v>-50.70194521934952</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13280177970366</v>
+        <v>-98.13268119192371</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.35218863611217</v>
+        <v>-94.35223505167092</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41436557611279</v>
+        <v>-81.41235866622122</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98608935280991</v>
+        <v>-42.98602008543648</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74196480815228</v>
+        <v>-97.74179040478023</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62903307855966</v>
+        <v>-93.62910002098272</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64141218243185</v>
+        <v>-75.64092595377102</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11248752149447</v>
+        <v>-43.11230936221288</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46164401368378</v>
+        <v>-97.46143843275581</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99128471396874</v>
+        <v>-90.99143960237021</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.19502849462474</v>
+        <v>-74.19054326846633</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65843261822262</v>
+        <v>-45.65830274436793</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43060236836762</v>
+        <v>-97.43041878021316</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90187970295483</v>
+        <v>-89.90203431166331</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.96841964775037</v>
+        <v>-74.96446406787328</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17129844860493</v>
+        <v>-40.17109091356239</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07647278193744</v>
+        <v>-90.07932079533042</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.37366181696632</v>
+        <v>-81.37245532908499</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.96776404735463</v>
+        <v>-74.9754547965089</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.3485150388641</v>
+        <v>-31.3491069586332</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76638039393484</v>
+        <v>-76.76889976772023</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.5702111755181</v>
+        <v>-65.56938573496045</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85311996017079</v>
+        <v>-71.85610207279434</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.58036494458561</v>
+        <v>-12.58103205836592</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.8199737523375</v>
+        <v>-74.82118804983253</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.34714291983755</v>
+        <v>-66.34700286822289</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13298332197402</v>
+        <v>-70.13350907334875</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80245118944989</v>
+        <v>-16.80258393849409</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -528,7 +528,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87349</v>
+        <v>6.87352</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -571,7 +571,7 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15341</v>
+        <v>4.15339</v>
       </c>
       <c r="K3" t="n">
         <v>2.43838</v>
@@ -614,7 +614,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55487</v>
+        <v>7.55497</v>
       </c>
       <c r="K4" t="n">
         <v>2.14558</v>
@@ -657,7 +657,7 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7425</v>
+        <v>0.74249</v>
       </c>
       <c r="K5" t="n">
         <v>2.02286</v>
@@ -700,7 +700,7 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77778</v>
+        <v>1.77777</v>
       </c>
       <c r="K6" t="n">
         <v>1.99344</v>
@@ -743,7 +743,7 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02134</v>
+        <v>2.02132</v>
       </c>
       <c r="K7" t="n">
         <v>1.70179</v>
@@ -786,7 +786,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61374</v>
+        <v>4.61372</v>
       </c>
       <c r="K8" t="n">
         <v>1.46043</v>
@@ -829,7 +829,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05474</v>
+        <v>7.05473</v>
       </c>
       <c r="K9" t="n">
         <v>1.2238</v>
@@ -872,7 +872,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.03464</v>
+        <v>8.034610000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.70039</v>
@@ -915,7 +915,7 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.90064</v>
+        <v>5.90062</v>
       </c>
       <c r="K11" t="n">
         <v>0.36237</v>
@@ -958,7 +958,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.00208</v>
+        <v>3.0021</v>
       </c>
       <c r="K12" t="n">
         <v>0.0646</v>
@@ -1001,7 +1001,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56818</v>
+        <v>3.5682</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1044,7 +1044,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.00325</v>
+        <v>2.00329</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1087,7 +1087,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.20155</v>
+        <v>3.2015</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1130,7 +1130,7 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72087</v>
+        <v>4.721</v>
       </c>
       <c r="K16" t="n">
         <v>-1.22423</v>
@@ -1173,7 +1173,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26329</v>
+        <v>5.26326</v>
       </c>
       <c r="K17" t="n">
         <v>-1.6995</v>
@@ -1216,7 +1216,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22917</v>
+        <v>4.22915</v>
       </c>
       <c r="K18" t="n">
         <v>-1.99306</v>
@@ -1259,7 +1259,7 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76132</v>
+        <v>3.76128</v>
       </c>
       <c r="K19" t="n">
         <v>-2.25254</v>
@@ -1302,7 +1302,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94776</v>
+        <v>0.94774</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53181</v>
@@ -1345,7 +1345,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13366</v>
+        <v>-1.13367</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1388,7 +1388,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.86878</v>
+        <v>-2.86881</v>
       </c>
       <c r="K22" t="n">
         <v>-2.38279</v>
@@ -1431,7 +1431,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.60403</v>
+        <v>-2.60407</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1474,7 +1474,7 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90621</v>
+        <v>-2.90616</v>
       </c>
       <c r="K24" t="n">
         <v>-2.19496</v>
@@ -1517,7 +1517,7 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.72208</v>
+        <v>-3.72206</v>
       </c>
       <c r="K25" t="n">
         <v>-1.95217</v>
@@ -1560,7 +1560,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68666</v>
+        <v>-6.68665</v>
       </c>
       <c r="K26" t="n">
         <v>-1.5183</v>
@@ -1603,7 +1603,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29543</v>
+        <v>-7.29546</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1646,7 +1646,7 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.18782</v>
+        <v>-7.1877</v>
       </c>
       <c r="K28" t="n">
         <v>-0.45662</v>
@@ -1689,7 +1689,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.495990000000001</v>
+        <v>-8.49601</v>
       </c>
       <c r="K29" t="n">
         <v>0.32744</v>
@@ -1732,7 +1732,7 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96451</v>
+        <v>-7.96452</v>
       </c>
       <c r="K30" t="n">
         <v>0.62976</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24778</v>
+        <v>-7.24781</v>
       </c>
       <c r="K31" t="n">
         <v>1.10614</v>
@@ -1818,7 +1818,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.58168</v>
+        <v>-7.5817</v>
       </c>
       <c r="K32" t="n">
         <v>1.34494</v>
@@ -1861,7 +1861,7 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.440160000000001</v>
+        <v>-8.44017</v>
       </c>
       <c r="K33" t="n">
         <v>1.54476</v>
@@ -1904,7 +1904,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.62437</v>
+        <v>-7.6244</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1947,7 +1947,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.89495</v>
+        <v>-5.89498</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1990,7 +1990,7 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24299</v>
+        <v>-7.24295</v>
       </c>
       <c r="K36" t="n">
         <v>1.34653</v>
@@ -2033,7 +2033,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.38123</v>
+        <v>-7.38122</v>
       </c>
       <c r="K37" t="n">
         <v>1.04167</v>
@@ -2076,7 +2076,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.30761</v>
+        <v>-3.3076</v>
       </c>
       <c r="K38" t="n">
         <v>0.59296</v>
@@ -2119,7 +2119,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.1641</v>
+        <v>-2.16413</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2162,7 +2162,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.56136</v>
+        <v>-1.56125</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2205,7 +2205,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.60254</v>
+        <v>-0.6025700000000001</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2248,7 +2248,7 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01652</v>
+        <v>-1.01654</v>
       </c>
       <c r="K42" t="n">
         <v>-1.08214</v>
@@ -2291,7 +2291,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.00401</v>
+        <v>-1.00405</v>
       </c>
       <c r="K43" t="n">
         <v>-1.05496</v>
@@ -2334,7 +2334,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.32003</v>
+        <v>1.32001</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2377,7 +2377,7 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6857799999999999</v>
+        <v>0.68577</v>
       </c>
       <c r="K45" t="n">
         <v>-1.24821</v>
@@ -2420,7 +2420,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35211</v>
+        <v>1.35209</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2463,7 +2463,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09785</v>
+        <v>1.09783</v>
       </c>
       <c r="K47" t="n">
         <v>-1.00117</v>
@@ -2506,7 +2506,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.676</v>
+        <v>2.67607</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2549,7 +2549,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51937</v>
+        <v>2.51944</v>
       </c>
       <c r="K49" t="n">
         <v>0.11745</v>
@@ -2592,7 +2592,7 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.41006</v>
+        <v>1.41002</v>
       </c>
       <c r="K50" t="n">
         <v>0.6156700000000001</v>
@@ -2635,7 +2635,7 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1832</v>
+        <v>0.18319</v>
       </c>
       <c r="K51" t="n">
         <v>0.87903</v>
@@ -2678,7 +2678,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8353</v>
+        <v>-0.83524</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2721,7 +2721,7 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6410400000000001</v>
+        <v>-0.64107</v>
       </c>
       <c r="K53" t="n">
         <v>0.84188</v>
@@ -2764,7 +2764,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46434</v>
+        <v>-0.46436</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2807,7 +2807,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.25792</v>
+        <v>-1.25796</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2850,7 +2850,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05594</v>
+        <v>-2.05596</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2893,7 +2893,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.07045</v>
+        <v>-0.07045999999999999</v>
       </c>
       <c r="K57" t="n">
         <v>0.30283</v>
@@ -2979,7 +2979,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11225</v>
+        <v>-2.11224</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3022,7 +3022,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08786</v>
+        <v>-1.08783</v>
       </c>
       <c r="K60" t="n">
         <v>-0.30089</v>
@@ -3065,7 +3065,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03239</v>
+        <v>-1.03232</v>
       </c>
       <c r="K61" t="n">
         <v>-0.57351</v>
@@ -3108,7 +3108,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.7448900000000001</v>
+        <v>-0.74492</v>
       </c>
       <c r="K62" t="n">
         <v>-0.80719</v>
@@ -3151,7 +3151,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.247</v>
+        <v>1.24698</v>
       </c>
       <c r="K63" t="n">
         <v>-0.76733</v>
@@ -3194,7 +3194,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.938</v>
+        <v>1.93798</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.72113</v>
+        <v>0.72112</v>
       </c>
       <c r="K65" t="n">
         <v>-0.28698</v>
@@ -3280,7 +3280,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.08772</v>
+        <v>1.08771</v>
       </c>
       <c r="K66" t="n">
         <v>-0.01307</v>
@@ -3323,7 +3323,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.17103</v>
+        <v>2.17102</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3366,7 +3366,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45744</v>
+        <v>2.45743</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3409,7 +3409,7 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.30561</v>
+        <v>2.3056</v>
       </c>
       <c r="K69" t="n">
         <v>1.11578</v>
@@ -3452,7 +3452,7 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95785</v>
+        <v>2.95786</v>
       </c>
       <c r="K70" t="n">
         <v>1.12816</v>
@@ -3495,7 +3495,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.13823</v>
+        <v>3.13824</v>
       </c>
       <c r="K71" t="n">
         <v>1.15592</v>
@@ -3538,7 +3538,7 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.07517</v>
+        <v>2.0752</v>
       </c>
       <c r="K72" t="n">
         <v>0.91851</v>
@@ -3581,7 +3581,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.72589</v>
+        <v>3.72597</v>
       </c>
       <c r="K73" t="n">
         <v>0.957</v>
@@ -3624,7 +3624,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.27714</v>
+        <v>3.2771</v>
       </c>
       <c r="K74" t="n">
         <v>0.95813</v>
@@ -3667,7 +3667,7 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52731</v>
+        <v>1.52728</v>
       </c>
       <c r="K75" t="n">
         <v>0.93054</v>
@@ -3710,7 +3710,7 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.24674</v>
+        <v>1.24672</v>
       </c>
       <c r="K76" t="n">
         <v>0.94253</v>
@@ -3753,7 +3753,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.24292</v>
+        <v>1.24291</v>
       </c>
       <c r="K77" t="n">
         <v>0.9680800000000001</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03917</v>
+        <v>-0.03918</v>
       </c>
       <c r="K78" t="n">
         <v>1.21521</v>
@@ -3925,7 +3925,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.38611</v>
+        <v>-1.38612</v>
       </c>
       <c r="K81" t="n">
         <v>1.19434</v>
@@ -3968,7 +3968,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.81175</v>
+        <v>-1.81174</v>
       </c>
       <c r="K82" t="n">
         <v>1.45285</v>
@@ -4011,7 +4011,7 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15053</v>
+        <v>-1.15052</v>
       </c>
       <c r="K83" t="n">
         <v>1.71406</v>
@@ -4054,7 +4054,7 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.29208</v>
+        <v>-1.29206</v>
       </c>
       <c r="K84" t="n">
         <v>2.22338</v>
@@ -4097,7 +4097,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01271</v>
+        <v>-2.01267</v>
       </c>
       <c r="K85" t="n">
         <v>2.22049</v>
@@ -4140,7 +4140,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.71983</v>
+        <v>-1.71984</v>
       </c>
       <c r="K86" t="n">
         <v>2.4701</v>
@@ -4183,7 +4183,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27081</v>
+        <v>-1.27083</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4226,7 +4226,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.9720299999999999</v>
+        <v>-0.97205</v>
       </c>
       <c r="K88" t="n">
         <v>2.45104</v>
@@ -4441,7 +4441,7 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.93907</v>
+        <v>-0.93909</v>
       </c>
       <c r="K93" t="n">
         <v>1.48813</v>
@@ -4484,7 +4484,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.38795</v>
+        <v>-1.38797</v>
       </c>
       <c r="K94" t="n">
         <v>1.26582</v>
@@ -4527,7 +4527,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.02736</v>
+        <v>-2.02734</v>
       </c>
       <c r="K95" t="n">
         <v>1.21282</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.27388</v>
+        <v>-1.27386</v>
       </c>
       <c r="K96" t="n">
         <v>1.20834</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95332</v>
+        <v>-1.9533</v>
       </c>
       <c r="K97" t="n">
         <v>1.47358</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.95979</v>
+        <v>-1.95978</v>
       </c>
       <c r="K98" t="n">
         <v>1.6747</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.02142</v>
+        <v>-2.02144</v>
       </c>
       <c r="K99" t="n">
         <v>1.96426</v>
@@ -4742,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.22755</v>
+        <v>-2.22756</v>
       </c>
       <c r="K100" t="n">
         <v>2.26582</v>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.70106</v>
+        <v>-0.70107</v>
       </c>
       <c r="K103" t="n">
         <v>3.13567</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.6368</v>
+        <v>-1.63681</v>
       </c>
       <c r="K104" t="n">
         <v>3.40463</v>
@@ -4957,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.31033</v>
+        <v>-1.31034</v>
       </c>
       <c r="K105" t="n">
         <v>3.72898</v>
@@ -5000,7 +5000,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.71544</v>
+        <v>-1.71546</v>
       </c>
       <c r="K106" t="n">
         <v>4.01515</v>
@@ -5043,7 +5043,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61231</v>
+        <v>0.61232</v>
       </c>
       <c r="K107" t="n">
         <v>4.35166</v>
@@ -5086,7 +5086,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.65037</v>
+        <v>1.65039</v>
       </c>
       <c r="K108" t="n">
         <v>4.39864</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32912</v>
+        <v>2.32913</v>
       </c>
       <c r="K109" t="n">
         <v>4.6695</v>
@@ -5172,7 +5172,7 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.6664600000000001</v>
+        <v>0.66647</v>
       </c>
       <c r="K110" t="n">
         <v>4.75418</v>
@@ -5215,7 +5215,7 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.90561</v>
+        <v>0.9056</v>
       </c>
       <c r="K111" t="n">
         <v>4.52399</v>
@@ -5258,7 +5258,7 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.75481</v>
+        <v>1.7548</v>
       </c>
       <c r="K112" t="n">
         <v>4.53026</v>
@@ -5473,7 +5473,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.90907</v>
+        <v>3.90906</v>
       </c>
       <c r="K117" t="n">
         <v>4.53327</v>
@@ -5516,7 +5516,7 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.25931</v>
+        <v>5.25929</v>
       </c>
       <c r="K118" t="n">
         <v>4.33358</v>
@@ -5559,7 +5559,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.59827</v>
+        <v>3.59829</v>
       </c>
       <c r="K119" t="n">
         <v>4.29107</v>
@@ -5602,7 +5602,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.88631</v>
+        <v>1.88632</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5645,7 +5645,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.47364</v>
+        <v>1.47365</v>
       </c>
       <c r="K121" t="n">
         <v>3.51633</v>
@@ -5860,7 +5860,7 @@
         <v>-0.14837</v>
       </c>
       <c r="J126" t="n">
-        <v>0.27474</v>
+        <v>0.27473</v>
       </c>
       <c r="K126" t="n">
         <v>1.95409</v>
@@ -6118,7 +6118,7 @@
         <v>-0.59613</v>
       </c>
       <c r="J132" t="n">
-        <v>-7.12005</v>
+        <v>-7.12004</v>
       </c>
       <c r="K132" t="n">
         <v>0.02314</v>
@@ -6161,7 +6161,7 @@
         <v>-0.89286</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.86328</v>
+        <v>-7.86327</v>
       </c>
       <c r="K133" t="n">
         <v>-0.05777</v>
@@ -6419,7 +6419,7 @@
         <v>-1.93452</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.48699</v>
+        <v>-5.48698</v>
       </c>
       <c r="K139" t="n">
         <v>2.02858</v>
@@ -6849,7 +6849,7 @@
         <v>-0.45455</v>
       </c>
       <c r="J149" t="n">
-        <v>2.01722</v>
+        <v>2.01721</v>
       </c>
       <c r="K149" t="n">
         <v>2.64659</v>
@@ -6935,7 +6935,7 @@
         <v>-0.30349</v>
       </c>
       <c r="J151" t="n">
-        <v>0.24068</v>
+        <v>0.24069</v>
       </c>
       <c r="K151" t="n">
         <v>1.68324</v>
@@ -6978,7 +6978,7 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.63308</v>
+        <v>0.63309</v>
       </c>
       <c r="K152" t="n">
         <v>1.47822</v>
@@ -7021,7 +7021,7 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>0.95987</v>
+        <v>0.95989</v>
       </c>
       <c r="K153" t="n">
         <v>1.21417</v>
@@ -7064,7 +7064,7 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.12169</v>
+        <v>1.12171</v>
       </c>
       <c r="K154" t="n">
         <v>1.42536</v>
@@ -7107,7 +7107,7 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.58973</v>
+        <v>2.58971</v>
       </c>
       <c r="K155" t="n">
         <v>1.45333</v>
@@ -7150,7 +7150,7 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.9355</v>
+        <v>1.93548</v>
       </c>
       <c r="K156" t="n">
         <v>1.45122</v>
@@ -7236,7 +7236,7 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.34561</v>
+        <v>1.3456</v>
       </c>
       <c r="K158" t="n">
         <v>1.70902</v>
@@ -7279,7 +7279,7 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.65365</v>
+        <v>1.65364</v>
       </c>
       <c r="K159" t="n">
         <v>1.97252</v>
@@ -7322,7 +7322,7 @@
         <v>-0.9146300000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>1.57829</v>
+        <v>1.57828</v>
       </c>
       <c r="K160" t="n">
         <v>2.50749</v>
@@ -7408,7 +7408,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J162" t="n">
-        <v>3.24553</v>
+        <v>3.24554</v>
       </c>
       <c r="K162" t="n">
         <v>3.6489</v>
@@ -7537,7 +7537,7 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.90115</v>
+        <v>2.90117</v>
       </c>
       <c r="K165" t="n">
         <v>4.28746</v>
@@ -7580,7 +7580,7 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53605</v>
+        <v>2.53607</v>
       </c>
       <c r="K166" t="n">
         <v>4.07215</v>
@@ -7623,7 +7623,7 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.64578</v>
+        <v>3.64576</v>
       </c>
       <c r="K167" t="n">
         <v>3.83471</v>
@@ -7666,7 +7666,7 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.48904</v>
+        <v>3.48902</v>
       </c>
       <c r="K168" t="n">
         <v>4.12632</v>
@@ -7795,7 +7795,7 @@
         <v>0.15361</v>
       </c>
       <c r="J171" t="n">
-        <v>2.90365</v>
+        <v>2.90364</v>
       </c>
       <c r="K171" t="n">
         <v>3.53184</v>
@@ -8010,7 +8010,7 @@
         <v>1.54321</v>
       </c>
       <c r="J176" t="n">
-        <v>2.54942</v>
+        <v>2.54943</v>
       </c>
       <c r="K176" t="n">
         <v>3.00768</v>
@@ -8053,7 +8053,7 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.89899</v>
+        <v>2.899</v>
       </c>
       <c r="K177" t="n">
         <v>3.04612</v>
@@ -8096,7 +8096,7 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.84429</v>
+        <v>3.84431</v>
       </c>
       <c r="K178" t="n">
         <v>2.99841</v>
@@ -8139,7 +8139,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.5014</v>
+        <v>2.50138</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8182,7 +8182,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78981</v>
+        <v>1.7898</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8225,7 +8225,7 @@
         <v>1.07527</v>
       </c>
       <c r="J181" t="n">
-        <v>1.81115</v>
+        <v>1.81114</v>
       </c>
       <c r="K181" t="n">
         <v>2.92317</v>
@@ -8397,7 +8397,7 @@
         <v>0.6116200000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>1.47008</v>
+        <v>1.47009</v>
       </c>
       <c r="K185" t="n">
         <v>1.88385</v>
@@ -8741,7 +8741,7 @@
         <v>0.30395</v>
       </c>
       <c r="J193" t="n">
-        <v>1.29023</v>
+        <v>1.29022</v>
       </c>
       <c r="K193" t="n">
         <v>2.85041</v>
@@ -8827,7 +8827,7 @@
         <v>0.15198</v>
       </c>
       <c r="J195" t="n">
-        <v>0.9156</v>
+        <v>0.91559</v>
       </c>
       <c r="K195" t="n">
         <v>2.29991</v>
@@ -9128,7 +9128,7 @@
         <v>-1.36364</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.66879</v>
+        <v>-0.66878</v>
       </c>
       <c r="K202" t="n">
         <v>0.28101</v>
@@ -9859,7 +9859,7 @@
         <v>-1.67939</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.30184</v>
+        <v>-9.301830000000001</v>
       </c>
       <c r="K219" t="n">
         <v>-6.41604</v>
@@ -10633,7 +10633,7 @@
         <v>-1.25196</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.25726</v>
+        <v>-0.25727</v>
       </c>
       <c r="K237" t="n">
         <v>1.60399</v>
@@ -10805,7 +10805,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J241" t="n">
-        <v>2.18762</v>
+        <v>2.18761</v>
       </c>
       <c r="K241" t="n">
         <v>1.83039</v>
@@ -10848,7 +10848,7 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30206</v>
+        <v>2.30207</v>
       </c>
       <c r="K242" t="n">
         <v>2.02206</v>
@@ -11020,7 +11020,7 @@
         <v>-0.47319</v>
       </c>
       <c r="J246" t="n">
-        <v>3.1031</v>
+        <v>3.10311</v>
       </c>
       <c r="K246" t="n">
         <v>1.57793</v>
@@ -11063,7 +11063,7 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46115</v>
+        <v>3.46114</v>
       </c>
       <c r="K247" t="n">
         <v>1.05894</v>
@@ -11149,7 +11149,7 @@
         <v>-0.31696</v>
       </c>
       <c r="J249" t="n">
-        <v>4.28995</v>
+        <v>4.28994</v>
       </c>
       <c r="K249" t="n">
         <v>0.82133</v>
@@ -11192,7 +11192,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36584</v>
+        <v>5.36583</v>
       </c>
       <c r="K250" t="n">
         <v>1.08928</v>
@@ -11278,7 +11278,7 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.78751</v>
+        <v>4.7875</v>
       </c>
       <c r="K252" t="n">
         <v>1.53273</v>
@@ -11364,7 +11364,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.60838</v>
+        <v>5.6084</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11407,7 +11407,7 @@
         <v>-2.36967</v>
       </c>
       <c r="J255" t="n">
-        <v>5.94847</v>
+        <v>5.94848</v>
       </c>
       <c r="K255" t="n">
         <v>2.39078</v>
@@ -11665,7 +11665,7 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46886</v>
+        <v>5.46885</v>
       </c>
       <c r="K261" t="n">
         <v>5.34278</v>
@@ -11708,7 +11708,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06061</v>
+        <v>4.06059</v>
       </c>
       <c r="K262" t="n">
         <v>5.82083</v>
@@ -11794,7 +11794,7 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.80941</v>
+        <v>3.8094</v>
       </c>
       <c r="K264" t="n">
         <v>5.94402</v>
@@ -11837,7 +11837,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70187</v>
+        <v>3.70188</v>
       </c>
       <c r="K265" t="n">
         <v>5.62383</v>
@@ -11880,7 +11880,7 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87409</v>
+        <v>2.87412</v>
       </c>
       <c r="K266" t="n">
         <v>5.6398</v>
@@ -11923,7 +11923,7 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68872</v>
+        <v>2.68873</v>
       </c>
       <c r="K267" t="n">
         <v>5.63075</v>
@@ -11966,7 +11966,7 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.18502</v>
+        <v>2.18503</v>
       </c>
       <c r="K268" t="n">
         <v>5.8684</v>
@@ -12095,7 +12095,7 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.02541</v>
+        <v>2.02538</v>
       </c>
       <c r="K271" t="n">
         <v>5.55046</v>
@@ -12138,7 +12138,7 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.06772</v>
+        <v>2.0677</v>
       </c>
       <c r="K272" t="n">
         <v>5.03896</v>
@@ -12181,7 +12181,7 @@
         <v>-0.32787</v>
       </c>
       <c r="J273" t="n">
-        <v>2.87066</v>
+        <v>2.87064</v>
       </c>
       <c r="K273" t="n">
         <v>4.36879</v>
@@ -12224,7 +12224,7 @@
         <v>-0.16393</v>
       </c>
       <c r="J274" t="n">
-        <v>2.13193</v>
+        <v>2.13192</v>
       </c>
       <c r="K274" t="n">
         <v>3.65379</v>
@@ -12267,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.59072</v>
+        <v>2.59073</v>
       </c>
       <c r="K275" t="n">
         <v>3.37012</v>
@@ -12310,7 +12310,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.64211</v>
+        <v>2.6421</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12353,7 +12353,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55363</v>
+        <v>2.55361</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12396,7 +12396,7 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57137</v>
+        <v>3.57155</v>
       </c>
       <c r="K278" t="n">
         <v>2.88074</v>
@@ -12439,7 +12439,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10616</v>
+        <v>3.10613</v>
       </c>
       <c r="K279" t="n">
         <v>2.72887</v>
@@ -12482,7 +12482,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13342</v>
+        <v>3.1334</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12525,7 +12525,7 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52931</v>
+        <v>2.5293</v>
       </c>
       <c r="K281" t="n">
         <v>2.48447</v>
@@ -12568,7 +12568,7 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46744</v>
+        <v>2.46743</v>
       </c>
       <c r="K282" t="n">
         <v>2.70244</v>
@@ -12611,7 +12611,7 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.70778</v>
+        <v>1.70773</v>
       </c>
       <c r="K283" t="n">
         <v>2.45079</v>
@@ -12654,7 +12654,7 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26768</v>
+        <v>1.26764</v>
       </c>
       <c r="K284" t="n">
         <v>2.67797</v>
@@ -12697,7 +12697,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55162</v>
+        <v>0.55159</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12740,7 +12740,7 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35726</v>
+        <v>1.35725</v>
       </c>
       <c r="K286" t="n">
         <v>3.24569</v>
@@ -12783,7 +12783,7 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.27727</v>
+        <v>1.27733</v>
       </c>
       <c r="K287" t="n">
         <v>3.50067</v>
@@ -12826,7 +12826,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.5299199999999999</v>
+        <v>0.52986</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12869,7 +12869,7 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27367</v>
+        <v>-0.27365</v>
       </c>
       <c r="K289" t="n">
         <v>3.51163</v>
@@ -12912,7 +12912,7 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.03973</v>
+        <v>-0.03952</v>
       </c>
       <c r="K290" t="n">
         <v>3.83219</v>
@@ -13041,7 +13041,7 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52202</v>
+        <v>-0.522</v>
       </c>
       <c r="K293" t="n">
         <v>3.87311</v>
@@ -13084,7 +13084,7 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82335</v>
+        <v>-0.82338</v>
       </c>
       <c r="K294" t="n">
         <v>3.87626</v>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05969</v>
+        <v>-0.05983</v>
       </c>
       <c r="K295" t="n">
         <v>4.15332</v>
@@ -13170,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.27681</v>
+        <v>0.27666</v>
       </c>
       <c r="K296" t="n">
         <v>4.17488</v>
@@ -13213,7 +13213,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.31422</v>
+        <v>0.31411</v>
       </c>
       <c r="K297" t="n">
         <v>3.95179</v>
@@ -13256,7 +13256,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.38257</v>
+        <v>0.38253</v>
       </c>
       <c r="K298" t="n">
         <v>4.13246</v>
@@ -13299,7 +13299,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.00847</v>
+        <v>-0.00844</v>
       </c>
       <c r="K299" t="n">
         <v>3.9305</v>
@@ -13342,7 +13342,7 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.00398</v>
+        <v>1.00443</v>
       </c>
       <c r="K300" t="n">
         <v>3.5896</v>
@@ -13385,7 +13385,7 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95493</v>
+        <v>1.95487</v>
       </c>
       <c r="K301" t="n">
         <v>3.94713</v>
@@ -13428,7 +13428,7 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47766</v>
+        <v>1.47778</v>
       </c>
       <c r="K302" t="n">
         <v>3.5803</v>
@@ -13471,7 +13471,7 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98045</v>
+        <v>1.98043</v>
       </c>
       <c r="K303" t="n">
         <v>3.34617</v>
@@ -13514,7 +13514,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.72947</v>
+        <v>2.7295</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13557,7 +13557,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.50372</v>
+        <v>2.50376</v>
       </c>
       <c r="K305" t="n">
         <v>3.30933</v>
@@ -13600,7 +13600,7 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97691</v>
+        <v>2.97686</v>
       </c>
       <c r="K306" t="n">
         <v>3.02342</v>
@@ -13643,7 +13643,7 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.46899</v>
+        <v>3.46872</v>
       </c>
       <c r="K307" t="n">
         <v>2.73081</v>
@@ -13686,7 +13686,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.0137</v>
+        <v>3.01332</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13729,7 +13729,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06856</v>
+        <v>3.06831</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13772,7 +13772,7 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.61226</v>
+        <v>2.61227</v>
       </c>
       <c r="K310" t="n">
         <v>2.76807</v>
@@ -13815,7 +13815,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99505</v>
+        <v>2.99532</v>
       </c>
       <c r="K311" t="n">
         <v>2.6911</v>
@@ -13858,7 +13858,7 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.75263</v>
+        <v>2.75337</v>
       </c>
       <c r="K312" t="n">
         <v>2.99187</v>
@@ -13901,7 +13901,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.39437</v>
+        <v>2.39452</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13944,7 +13944,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.92594</v>
+        <v>1.92589</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13987,7 +13987,7 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.40939</v>
+        <v>2.40942</v>
       </c>
       <c r="K315" t="n">
         <v>3.23782</v>
@@ -14030,7 +14030,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62531</v>
+        <v>2.62542</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14073,7 +14073,7 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.4343</v>
+        <v>3.43419</v>
       </c>
       <c r="K317" t="n">
         <v>3.27391</v>
@@ -14116,7 +14116,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.37161</v>
+        <v>3.3713</v>
       </c>
       <c r="K318" t="n">
         <v>3.53397</v>
@@ -14159,7 +14159,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.14675</v>
+        <v>3.1465</v>
       </c>
       <c r="K319" t="n">
         <v>3.81128</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.13</v>
+        <v>3.12978</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14245,7 +14245,7 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.17867</v>
+        <v>3.17643</v>
       </c>
       <c r="K321" t="n">
         <v>3.64797</v>
@@ -14288,7 +14288,7 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.79744</v>
+        <v>3.79738</v>
       </c>
       <c r="K322" t="n">
         <v>3.74826</v>
@@ -14331,7 +14331,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.93143</v>
+        <v>3.93511</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14374,7 +14374,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.6868</v>
+        <v>3.68709</v>
       </c>
       <c r="K324" t="n">
         <v>3.45994</v>
@@ -14417,7 +14417,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.30338</v>
+        <v>3.30324</v>
       </c>
       <c r="K325" t="n">
         <v>3.23138</v>
@@ -14460,7 +14460,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86408</v>
+        <v>2.86395</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14503,7 +14503,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05627</v>
+        <v>2.05623</v>
       </c>
       <c r="K327" t="n">
         <v>2.63791</v>
@@ -14546,7 +14546,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82324</v>
+        <v>1.82304</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14589,7 +14589,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.15874</v>
+        <v>1.15832</v>
       </c>
       <c r="K329" t="n">
         <v>2.05076</v>
@@ -14632,7 +14632,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15327</v>
+        <v>1.15264</v>
       </c>
       <c r="K330" t="n">
         <v>1.53218</v>
@@ -14675,7 +14675,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.72461</v>
+        <v>0.72404</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14718,7 +14718,7 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13645</v>
+        <v>1.13585</v>
       </c>
       <c r="K332" t="n">
         <v>0.95682</v>
@@ -14761,7 +14761,7 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.1944</v>
+        <v>1.19176</v>
       </c>
       <c r="K333" t="n">
         <v>0.54018</v>
@@ -14804,7 +14804,7 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05802</v>
+        <v>1.05854</v>
       </c>
       <c r="K334" t="n">
         <v>-0.06722</v>
@@ -14847,7 +14847,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.73509</v>
+        <v>1.74048</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14890,7 +14890,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.4314</v>
+        <v>-2.43111</v>
       </c>
       <c r="K336" t="n">
         <v>-0.29335</v>
@@ -14933,7 +14933,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74565</v>
+        <v>2.74591</v>
       </c>
       <c r="K337" t="n">
         <v>-0.33478</v>
@@ -14976,7 +14976,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.53399</v>
+        <v>-0.53445</v>
       </c>
       <c r="K338" t="n">
         <v>-0.35202</v>
@@ -15019,7 +15019,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09637999999999999</v>
+        <v>-0.09644999999999999</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15062,7 +15062,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.53061</v>
+        <v>-0.53128</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15105,7 +15105,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.22779</v>
+        <v>-1.22873</v>
       </c>
       <c r="K341" t="n">
         <v>0.41028</v>
@@ -15148,7 +15148,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44619</v>
+        <v>-1.44737</v>
       </c>
       <c r="K342" t="n">
         <v>0.68746</v>
@@ -15191,7 +15191,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09637</v>
+        <v>-1.09735</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15234,7 +15234,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.75388</v>
+        <v>-0.75537</v>
       </c>
       <c r="K344" t="n">
         <v>1.21614</v>
@@ -15277,7 +15277,7 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.69712</v>
+        <v>-0.70168</v>
       </c>
       <c r="K345" t="n">
         <v>1.67058</v>
@@ -15320,7 +15320,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.13102</v>
+        <v>-0.12797</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15363,7 +15363,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.02479</v>
+        <v>-1.01446</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15406,7 +15406,7 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.98994</v>
+        <v>2.98854</v>
       </c>
       <c r="K348" t="n">
         <v>2.52186</v>
@@ -15449,7 +15449,7 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.39401</v>
+        <v>-1.39419</v>
       </c>
       <c r="K349" t="n">
         <v>2.79644</v>
@@ -15492,7 +15492,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.55899</v>
+        <v>2.55869</v>
       </c>
       <c r="K350" t="n">
         <v>3.16259</v>
@@ -15535,7 +15535,7 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.77797</v>
+        <v>1.77768</v>
       </c>
       <c r="K351" t="n">
         <v>2.91653</v>
@@ -15578,7 +15578,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.56283</v>
+        <v>1.56104</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15621,7 +15621,7 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.28514</v>
+        <v>-49.28801</v>
       </c>
       <c r="K353" t="n">
         <v>-38.87592</v>
@@ -15664,7 +15664,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.49581000000001</v>
+        <v>-69.49959</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15707,7 +15707,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.08741999999999</v>
+        <v>-70.09114</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15750,7 +15750,7 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73260000000001</v>
+        <v>-74.73712999999999</v>
       </c>
       <c r="K356" t="n">
         <v>-30.14584</v>
@@ -15793,7 +15793,7 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.86651999999999</v>
+        <v>-74.87692</v>
       </c>
       <c r="K357" t="n">
         <v>-25.53877</v>
@@ -15836,7 +15836,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.51528</v>
+        <v>-76.50669000000001</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15879,7 +15879,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.64610999999999</v>
+        <v>-66.62361</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15922,7 +15922,7 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.85545</v>
+        <v>-56.85495</v>
       </c>
       <c r="K360" t="n">
         <v>-20.38373</v>
@@ -15965,7 +15965,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.24953</v>
+        <v>-53.24831</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -574,7 +574,7 @@
         <v>4.15339</v>
       </c>
       <c r="K3" t="n">
-        <v>2.43838</v>
+        <v>2.42488</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>7.55497</v>
       </c>
       <c r="K4" t="n">
-        <v>2.14558</v>
+        <v>2.13214</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         <v>0.74249</v>
       </c>
       <c r="K5" t="n">
-        <v>2.02286</v>
+        <v>2.00946</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>1.77777</v>
       </c>
       <c r="K6" t="n">
-        <v>1.99344</v>
+        <v>1.98007</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>2.02132</v>
       </c>
       <c r="K7" t="n">
-        <v>1.70179</v>
+        <v>1.71488</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>4.61372</v>
       </c>
       <c r="K8" t="n">
-        <v>1.46043</v>
+        <v>1.47346</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>7.05473</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2238</v>
+        <v>1.21062</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>8.034610000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.70039</v>
+        <v>0.7003</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>5.90062</v>
       </c>
       <c r="K11" t="n">
-        <v>0.36237</v>
+        <v>0.34938</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>3.0021</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0646</v>
+        <v>0.05167</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>4.721</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.22423</v>
+        <v>-1.21134</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>5.26326</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6995</v>
+        <v>-1.68662</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>4.22915</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.99306</v>
+        <v>-1.9802</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>3.76128</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.25254</v>
+        <v>-2.26512</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>0.94774</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.53181</v>
+        <v>-2.53148</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>-2.86881</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.38279</v>
+        <v>-2.39536</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>-2.90616</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.19496</v>
+        <v>-2.18205</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>-3.72206</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.95217</v>
+        <v>-1.93924</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>-6.68665</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5183</v>
+        <v>-1.50532</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-7.1877</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.45662</v>
+        <v>-0.46961</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>-8.49601</v>
       </c>
       <c r="K29" t="n">
-        <v>0.32744</v>
+        <v>0.3143</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>-7.96452</v>
       </c>
       <c r="K30" t="n">
-        <v>0.62976</v>
+        <v>0.62967</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>-7.24781</v>
       </c>
       <c r="K31" t="n">
-        <v>1.10614</v>
+        <v>1.1193</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>-7.5817</v>
       </c>
       <c r="K32" t="n">
-        <v>1.34494</v>
+        <v>1.33158</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>-8.44017</v>
       </c>
       <c r="K33" t="n">
-        <v>1.54476</v>
+        <v>1.55796</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>-7.24295</v>
       </c>
       <c r="K36" t="n">
-        <v>1.34653</v>
+        <v>1.33316</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>-7.38122</v>
       </c>
       <c r="K37" t="n">
-        <v>1.04167</v>
+        <v>1.04153</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>-3.3076</v>
       </c>
       <c r="K38" t="n">
-        <v>0.59296</v>
+        <v>0.59289</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>-1.01654</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.08214</v>
+        <v>-1.09503</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>-1.00405</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.05496</v>
+        <v>-1.06785</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>0.68577</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.24821</v>
+        <v>-1.26105</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>1.09783</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.00117</v>
+        <v>-0.98817</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>2.51944</v>
       </c>
       <c r="K49" t="n">
-        <v>0.11745</v>
+        <v>0.10438</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>1.41002</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6156700000000001</v>
+        <v>0.61559</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>0.18319</v>
       </c>
       <c r="K51" t="n">
-        <v>0.87903</v>
+        <v>0.89215</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>-0.64107</v>
       </c>
       <c r="K53" t="n">
-        <v>0.84188</v>
+        <v>0.85504</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>-0.9904500000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>0.24987</v>
+        <v>0.26302</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>-1.08783</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.30089</v>
+        <v>-0.28781</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>-1.03232</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.57351</v>
+        <v>-0.56048</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>-0.74492</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.80719</v>
+        <v>-0.80708</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>1.24698</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.76733</v>
+        <v>-0.76723</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>0.72112</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.28698</v>
+        <v>-0.29999</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>1.08771</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.01307</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>2.95786</v>
       </c>
       <c r="K70" t="n">
-        <v>1.12816</v>
+        <v>1.12802</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>3.13824</v>
       </c>
       <c r="K71" t="n">
-        <v>1.15592</v>
+        <v>1.14263</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>2.0752</v>
       </c>
       <c r="K72" t="n">
-        <v>0.91851</v>
+        <v>0.90527</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>3.72597</v>
       </c>
       <c r="K73" t="n">
-        <v>0.957</v>
+        <v>0.94377</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>3.2771</v>
       </c>
       <c r="K74" t="n">
-        <v>0.95813</v>
+        <v>0.95801</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>1.52728</v>
       </c>
       <c r="K75" t="n">
-        <v>0.93054</v>
+        <v>0.91731</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>1.24291</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9680800000000001</v>
+        <v>0.98116</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>-0.03918</v>
       </c>
       <c r="K78" t="n">
-        <v>1.21521</v>
+        <v>1.20199</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>-1.38612</v>
       </c>
       <c r="K81" t="n">
-        <v>1.19434</v>
+        <v>1.20732</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>-1.81174</v>
       </c>
       <c r="K82" t="n">
-        <v>1.45285</v>
+        <v>1.45266</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>-1.15052</v>
       </c>
       <c r="K83" t="n">
-        <v>1.71406</v>
+        <v>1.72705</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>-2.01267</v>
       </c>
       <c r="K85" t="n">
-        <v>2.22049</v>
+        <v>2.23348</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>-1.71984</v>
       </c>
       <c r="K86" t="n">
-        <v>2.4701</v>
+        <v>2.46978</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>-0.97205</v>
       </c>
       <c r="K88" t="n">
-        <v>2.45104</v>
+        <v>2.46401</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>-0.57023</v>
       </c>
       <c r="K89" t="n">
-        <v>2.50065</v>
+        <v>2.48737</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>0.17419</v>
       </c>
       <c r="K90" t="n">
-        <v>2.01394</v>
+        <v>2.02685</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>-0.93909</v>
       </c>
       <c r="K93" t="n">
-        <v>1.48813</v>
+        <v>1.47512</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>-1.38797</v>
       </c>
       <c r="K94" t="n">
-        <v>1.26582</v>
+        <v>1.25288</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>-2.02734</v>
       </c>
       <c r="K95" t="n">
-        <v>1.21282</v>
+        <v>1.1999</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>-1.27386</v>
       </c>
       <c r="K96" t="n">
-        <v>1.20834</v>
+        <v>1.22106</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>-1.9533</v>
       </c>
       <c r="K97" t="n">
-        <v>1.47358</v>
+        <v>1.46069</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>-1.95978</v>
       </c>
       <c r="K98" t="n">
-        <v>1.6747</v>
+        <v>1.67449</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>-2.02144</v>
       </c>
       <c r="K99" t="n">
-        <v>1.96426</v>
+        <v>1.97694</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>-2.22756</v>
       </c>
       <c r="K100" t="n">
-        <v>2.26582</v>
+        <v>2.25288</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>-1.13135</v>
       </c>
       <c r="K102" t="n">
-        <v>2.79676</v>
+        <v>2.79641</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>-1.63681</v>
       </c>
       <c r="K104" t="n">
-        <v>3.40463</v>
+        <v>3.41729</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>0.61232</v>
       </c>
       <c r="K107" t="n">
-        <v>4.35166</v>
+        <v>4.36428</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>1.65039</v>
       </c>
       <c r="K108" t="n">
-        <v>4.39864</v>
+        <v>4.38552</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>2.32913</v>
       </c>
       <c r="K109" t="n">
-        <v>4.6695</v>
+        <v>4.68202</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>0.66647</v>
       </c>
       <c r="K110" t="n">
-        <v>4.75418</v>
+        <v>4.75359</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>0.9056</v>
       </c>
       <c r="K111" t="n">
-        <v>4.52399</v>
+        <v>4.511</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>2.8743</v>
       </c>
       <c r="K114" t="n">
-        <v>4.57959</v>
+        <v>4.56672</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>3.93851</v>
       </c>
       <c r="K116" t="n">
-        <v>4.58996</v>
+        <v>4.57716</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>5.25929</v>
       </c>
       <c r="K118" t="n">
-        <v>4.33358</v>
+        <v>4.34571</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>3.59829</v>
       </c>
       <c r="K119" t="n">
-        <v>4.29107</v>
+        <v>4.27846</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>1.47365</v>
       </c>
       <c r="K121" t="n">
-        <v>3.51633</v>
+        <v>3.50395</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>3.3177</v>
       </c>
       <c r="K122" t="n">
-        <v>2.90649</v>
+        <v>2.89424</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>3.28842</v>
       </c>
       <c r="K123" t="n">
-        <v>2.88942</v>
+        <v>2.90131</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>0.86488</v>
       </c>
       <c r="K125" t="n">
-        <v>2.25715</v>
+        <v>2.26897</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>-0.16224</v>
       </c>
       <c r="K128" t="n">
-        <v>1.63839</v>
+        <v>1.65009</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>0.37904</v>
       </c>
       <c r="K130" t="n">
-        <v>0.81443</v>
+        <v>0.8027</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>-7.84518</v>
       </c>
       <c r="K135" t="n">
-        <v>0.53161</v>
+        <v>0.51999</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>-6.82901</v>
       </c>
       <c r="K137" t="n">
-        <v>1.30591</v>
+        <v>1.2942</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>-5.48698</v>
       </c>
       <c r="K139" t="n">
-        <v>2.02858</v>
+        <v>2.04011</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>-5.06327</v>
       </c>
       <c r="K140" t="n">
-        <v>2.038</v>
+        <v>2.02625</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>3.6765</v>
       </c>
       <c r="K146" t="n">
-        <v>3.7536</v>
+        <v>3.76511</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>1.69823</v>
       </c>
       <c r="K150" t="n">
-        <v>2.05495</v>
+        <v>2.0663</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>0.24069</v>
       </c>
       <c r="K151" t="n">
-        <v>1.68324</v>
+        <v>1.67175</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>0.63309</v>
       </c>
       <c r="K152" t="n">
-        <v>1.47822</v>
+        <v>1.48951</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>2.58971</v>
       </c>
       <c r="K155" t="n">
-        <v>1.45333</v>
+        <v>1.46451</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>1.3456</v>
       </c>
       <c r="K158" t="n">
-        <v>1.70902</v>
+        <v>1.69774</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>3.24554</v>
       </c>
       <c r="K162" t="n">
-        <v>3.6489</v>
+        <v>3.6485</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>3.68901</v>
       </c>
       <c r="K164" t="n">
-        <v>4.25887</v>
+        <v>4.24728</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>2.90117</v>
       </c>
       <c r="K165" t="n">
-        <v>4.28746</v>
+        <v>4.29857</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>3.64576</v>
       </c>
       <c r="K167" t="n">
-        <v>3.83471</v>
+        <v>3.82327</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>2.57146</v>
       </c>
       <c r="K174" t="n">
-        <v>3.30579</v>
+        <v>3.30543</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>2.899</v>
       </c>
       <c r="K177" t="n">
-        <v>3.04612</v>
+        <v>3.03514</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>1.51106</v>
       </c>
       <c r="K186" t="n">
-        <v>1.84935</v>
+        <v>1.83877</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>-5.03658</v>
       </c>
       <c r="K214" t="n">
-        <v>-3.15252</v>
+        <v>-3.16253</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>-7.54206</v>
       </c>
       <c r="K224" t="n">
-        <v>-5.59755</v>
+        <v>-5.60776</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>-6.15033</v>
       </c>
       <c r="K226" t="n">
-        <v>-4.6192</v>
+        <v>-4.60934</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>-1.42159</v>
       </c>
       <c r="K236" t="n">
-        <v>1.33088</v>
+        <v>1.34185</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>0.24351</v>
       </c>
       <c r="K238" t="n">
-        <v>1.45179</v>
+        <v>1.44095</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>2.90206</v>
       </c>
       <c r="K245" t="n">
-        <v>1.88152</v>
+        <v>1.87077</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>4.28994</v>
       </c>
       <c r="K249" t="n">
-        <v>0.82133</v>
+        <v>0.81067</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>5.36583</v>
       </c>
       <c r="K250" t="n">
-        <v>1.08928</v>
+        <v>1.10007</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>4.94873</v>
       </c>
       <c r="K253" t="n">
-        <v>2.12721</v>
+        <v>2.11657</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>5.66685</v>
       </c>
       <c r="K256" t="n">
-        <v>2.44057</v>
+        <v>2.43001</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>6.14193</v>
       </c>
       <c r="K257" t="n">
-        <v>2.75433</v>
+        <v>2.76517</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>6.62991</v>
       </c>
       <c r="K259" t="n">
-        <v>3.92676</v>
+        <v>3.91617</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>5.46885</v>
       </c>
       <c r="K261" t="n">
-        <v>5.34278</v>
+        <v>5.35393</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>4.06059</v>
       </c>
       <c r="K262" t="n">
-        <v>5.82083</v>
+        <v>5.81027</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>3.70188</v>
       </c>
       <c r="K265" t="n">
-        <v>5.62383</v>
+        <v>5.63483</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>2.87412</v>
       </c>
       <c r="K266" t="n">
-        <v>5.6398</v>
+        <v>5.62941</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>2.68873</v>
       </c>
       <c r="K267" t="n">
-        <v>5.63075</v>
+        <v>5.62042</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>2.18503</v>
       </c>
       <c r="K268" t="n">
-        <v>5.8684</v>
+        <v>5.87932</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>2.02538</v>
       </c>
       <c r="K271" t="n">
-        <v>5.55046</v>
+        <v>5.55103</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>2.13192</v>
       </c>
       <c r="K274" t="n">
-        <v>3.65379</v>
+        <v>3.65415</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>2.59073</v>
       </c>
       <c r="K275" t="n">
-        <v>3.37012</v>
+        <v>3.36017</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>3.57155</v>
       </c>
       <c r="K278" t="n">
-        <v>2.88074</v>
+        <v>2.89086</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>3.10613</v>
       </c>
       <c r="K279" t="n">
-        <v>2.72887</v>
+        <v>2.73892</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>2.5293</v>
       </c>
       <c r="K281" t="n">
-        <v>2.48447</v>
+        <v>2.47477</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>2.46743</v>
       </c>
       <c r="K282" t="n">
-        <v>2.70244</v>
+        <v>2.69275</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>1.70773</v>
       </c>
       <c r="K283" t="n">
-        <v>2.45079</v>
+        <v>2.46068</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>1.26764</v>
       </c>
       <c r="K284" t="n">
-        <v>2.67797</v>
+        <v>2.66834</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>1.35725</v>
       </c>
       <c r="K286" t="n">
-        <v>3.24569</v>
+        <v>3.246</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>1.27733</v>
       </c>
       <c r="K287" t="n">
-        <v>3.50067</v>
+        <v>3.50101</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>-0.27365</v>
       </c>
       <c r="K289" t="n">
-        <v>3.51163</v>
+        <v>3.50206</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>-0.03952</v>
       </c>
       <c r="K290" t="n">
-        <v>3.83219</v>
+        <v>3.82263</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>-0.2363</v>
       </c>
       <c r="K291" t="n">
-        <v>3.85604</v>
+        <v>3.84652</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>-0.522</v>
       </c>
       <c r="K293" t="n">
-        <v>3.87311</v>
+        <v>3.88294</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>-0.82338</v>
       </c>
       <c r="K294" t="n">
-        <v>3.87626</v>
+        <v>3.87663</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>-0.05983</v>
       </c>
       <c r="K295" t="n">
-        <v>4.15332</v>
+        <v>4.14391</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>0.27666</v>
       </c>
       <c r="K296" t="n">
-        <v>4.17488</v>
+        <v>4.18465</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>0.38253</v>
       </c>
       <c r="K298" t="n">
-        <v>4.13246</v>
+        <v>4.13285</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>-0.00844</v>
       </c>
       <c r="K299" t="n">
-        <v>3.9305</v>
+        <v>3.93086</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>1.00443</v>
       </c>
       <c r="K300" t="n">
-        <v>3.5896</v>
+        <v>3.58035</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>1.95487</v>
       </c>
       <c r="K301" t="n">
-        <v>3.94713</v>
+        <v>3.95673</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>1.47778</v>
       </c>
       <c r="K302" t="n">
-        <v>3.5803</v>
+        <v>3.58984</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>1.98043</v>
       </c>
       <c r="K303" t="n">
-        <v>3.34617</v>
+        <v>3.34647</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>2.50376</v>
       </c>
       <c r="K305" t="n">
-        <v>3.30933</v>
+        <v>3.30021</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>2.97686</v>
       </c>
       <c r="K306" t="n">
-        <v>3.02342</v>
+        <v>3.03278</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>3.46872</v>
       </c>
       <c r="K307" t="n">
-        <v>2.73081</v>
+        <v>2.73105</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>2.61227</v>
       </c>
       <c r="K310" t="n">
-        <v>2.76807</v>
+        <v>2.77728</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>2.99532</v>
       </c>
       <c r="K311" t="n">
-        <v>2.6911</v>
+        <v>2.70029</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>2.75337</v>
       </c>
       <c r="K312" t="n">
-        <v>2.99187</v>
+        <v>2.99214</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>2.40942</v>
       </c>
       <c r="K315" t="n">
-        <v>3.23782</v>
+        <v>3.23811</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>3.43419</v>
       </c>
       <c r="K317" t="n">
-        <v>3.27391</v>
+        <v>3.2742</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>3.3713</v>
       </c>
       <c r="K318" t="n">
-        <v>3.53397</v>
+        <v>3.52516</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>3.1465</v>
       </c>
       <c r="K319" t="n">
-        <v>3.81128</v>
+        <v>3.82042</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>3.17643</v>
       </c>
       <c r="K321" t="n">
-        <v>3.64797</v>
+        <v>3.63923</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>3.79738</v>
       </c>
       <c r="K322" t="n">
-        <v>3.74826</v>
+        <v>3.73954</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>3.68709</v>
       </c>
       <c r="K324" t="n">
-        <v>3.45994</v>
+        <v>3.46024</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>3.30324</v>
       </c>
       <c r="K325" t="n">
-        <v>3.23138</v>
+        <v>3.22274</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>2.05623</v>
       </c>
       <c r="K327" t="n">
-        <v>2.63791</v>
+        <v>2.64673</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>1.15832</v>
       </c>
       <c r="K329" t="n">
-        <v>2.05076</v>
+        <v>2.05948</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>1.15264</v>
       </c>
       <c r="K330" t="n">
-        <v>1.53218</v>
+        <v>1.53231</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>1.13585</v>
       </c>
       <c r="K332" t="n">
-        <v>0.95682</v>
+        <v>0.94835</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>1.19176</v>
       </c>
       <c r="K333" t="n">
-        <v>0.54018</v>
+        <v>0.54866</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>1.05854</v>
       </c>
       <c r="K334" t="n">
-        <v>-0.06722</v>
+        <v>-0.05882</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>-2.43111</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.29335</v>
+        <v>-0.29338</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>2.74591</v>
       </c>
       <c r="K337" t="n">
-        <v>-0.33478</v>
+        <v>-0.32644</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>-0.53445</v>
       </c>
       <c r="K338" t="n">
-        <v>-0.35202</v>
+        <v>-0.36041</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>-1.22873</v>
       </c>
       <c r="K341" t="n">
-        <v>0.41028</v>
+        <v>0.40191</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>-1.44737</v>
       </c>
       <c r="K342" t="n">
-        <v>0.68746</v>
+        <v>0.6959</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>-0.75537</v>
       </c>
       <c r="K344" t="n">
-        <v>1.21614</v>
+        <v>1.21624</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>-0.70168</v>
       </c>
       <c r="K345" t="n">
-        <v>1.67058</v>
+        <v>1.66219</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>2.98854</v>
       </c>
       <c r="K348" t="n">
-        <v>2.52186</v>
+        <v>2.53047</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>2.55869</v>
       </c>
       <c r="K350" t="n">
-        <v>3.16259</v>
+        <v>3.17127</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>1.77768</v>
       </c>
       <c r="K351" t="n">
-        <v>2.91653</v>
+        <v>2.90815</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>-49.28801</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.87592</v>
+        <v>-38.87916</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>-74.73712999999999</v>
       </c>
       <c r="K356" t="n">
-        <v>-30.14584</v>
+        <v>-30.14005</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>-74.87692</v>
       </c>
       <c r="K357" t="n">
-        <v>-25.53877</v>
+        <v>-25.53262</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>-56.85495</v>
       </c>
       <c r="K360" t="n">
-        <v>-20.38373</v>
+        <v>-20.39193</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -528,7 +528,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87352</v>
+        <v>6.87356</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -571,10 +571,10 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15339</v>
+        <v>4.15334</v>
       </c>
       <c r="K3" t="n">
-        <v>2.42488</v>
+        <v>2.43838</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55497</v>
+        <v>7.55513</v>
       </c>
       <c r="K4" t="n">
         <v>2.13214</v>
@@ -657,10 +657,10 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74249</v>
+        <v>0.74247</v>
       </c>
       <c r="K5" t="n">
-        <v>2.00946</v>
+        <v>2.02286</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77777</v>
+        <v>1.77776</v>
       </c>
       <c r="K6" t="n">
         <v>1.98007</v>
@@ -743,10 +743,10 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02132</v>
+        <v>2.02128</v>
       </c>
       <c r="K7" t="n">
-        <v>1.71488</v>
+        <v>1.70179</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61372</v>
+        <v>4.61371</v>
       </c>
       <c r="K8" t="n">
         <v>1.47346</v>
@@ -829,7 +829,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05473</v>
+        <v>7.05472</v>
       </c>
       <c r="K9" t="n">
         <v>1.21062</v>
@@ -872,7 +872,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.034610000000001</v>
+        <v>8.034599999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.7003</v>
@@ -915,10 +915,10 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.90062</v>
+        <v>5.9006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.34938</v>
+        <v>0.36237</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0021</v>
+        <v>3.00211</v>
       </c>
       <c r="K12" t="n">
         <v>0.05167</v>
@@ -1001,7 +1001,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5682</v>
+        <v>3.56821</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1044,7 +1044,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.00329</v>
+        <v>2.00337</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1087,7 +1087,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2015</v>
+        <v>3.20138</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1130,7 +1130,7 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.721</v>
+        <v>4.72119</v>
       </c>
       <c r="K16" t="n">
         <v>-1.21134</v>
@@ -1173,7 +1173,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26326</v>
+        <v>5.26322</v>
       </c>
       <c r="K17" t="n">
         <v>-1.68662</v>
@@ -1216,7 +1216,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22915</v>
+        <v>4.22913</v>
       </c>
       <c r="K18" t="n">
         <v>-1.9802</v>
@@ -1259,10 +1259,10 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76128</v>
+        <v>3.76122</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.26512</v>
+        <v>-2.25254</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94774</v>
+        <v>0.94772</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53148</v>
@@ -1345,7 +1345,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13367</v>
+        <v>-1.13368</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1388,7 +1388,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.86881</v>
+        <v>-2.86882</v>
       </c>
       <c r="K22" t="n">
         <v>-2.39536</v>
@@ -1431,7 +1431,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.60407</v>
+        <v>-2.60409</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1474,10 +1474,10 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90616</v>
+        <v>-2.90614</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.18205</v>
+        <v>-2.19496</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.72206</v>
+        <v>-3.72205</v>
       </c>
       <c r="K25" t="n">
         <v>-1.93924</v>
@@ -1560,7 +1560,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68665</v>
+        <v>-6.68661</v>
       </c>
       <c r="K26" t="n">
         <v>-1.50532</v>
@@ -1603,7 +1603,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29546</v>
+        <v>-7.29554</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1646,7 +1646,7 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.1877</v>
+        <v>-7.18752</v>
       </c>
       <c r="K28" t="n">
         <v>-0.46961</v>
@@ -1689,7 +1689,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.49601</v>
+        <v>-8.49605</v>
       </c>
       <c r="K29" t="n">
         <v>0.3143</v>
@@ -1732,10 +1732,10 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96452</v>
+        <v>-7.96454</v>
       </c>
       <c r="K30" t="n">
-        <v>0.62967</v>
+        <v>0.61656</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24781</v>
+        <v>-7.24787</v>
       </c>
       <c r="K31" t="n">
         <v>1.1193</v>
@@ -1818,7 +1818,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.5817</v>
+        <v>-7.58171</v>
       </c>
       <c r="K32" t="n">
         <v>1.33158</v>
@@ -1864,7 +1864,7 @@
         <v>-8.44017</v>
       </c>
       <c r="K33" t="n">
-        <v>1.55796</v>
+        <v>1.54476</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.6244</v>
+        <v>-7.62441</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1947,7 +1947,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.89498</v>
+        <v>-5.89499</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1990,10 +1990,10 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24295</v>
+        <v>-7.24294</v>
       </c>
       <c r="K36" t="n">
-        <v>1.33316</v>
+        <v>1.34653</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>-7.38122</v>
       </c>
       <c r="K37" t="n">
-        <v>1.04153</v>
+        <v>1.02835</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.3076</v>
+        <v>-3.30755</v>
       </c>
       <c r="K38" t="n">
         <v>0.59289</v>
@@ -2119,7 +2119,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.16413</v>
+        <v>-2.16421</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2162,7 +2162,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.56125</v>
+        <v>-1.56107</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2205,7 +2205,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6025700000000001</v>
+        <v>-0.60261</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2248,10 +2248,10 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01654</v>
+        <v>-1.01657</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.09503</v>
+        <v>-1.08214</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.00405</v>
+        <v>-1.00412</v>
       </c>
       <c r="K43" t="n">
         <v>-1.06785</v>
@@ -2334,7 +2334,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.32001</v>
+        <v>1.31999</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2377,10 +2377,10 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68577</v>
+        <v>0.68576</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.26105</v>
+        <v>-1.24821</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35209</v>
+        <v>1.35208</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2466,7 +2466,7 @@
         <v>1.09783</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.98817</v>
+        <v>-1.00117</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.67607</v>
+        <v>2.67611</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2549,10 +2549,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51944</v>
+        <v>2.51947</v>
       </c>
       <c r="K49" t="n">
-        <v>0.10438</v>
+        <v>0.11745</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.41002</v>
+        <v>1.40999</v>
       </c>
       <c r="K50" t="n">
-        <v>0.61559</v>
+        <v>0.60249</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.18319</v>
+        <v>0.18317</v>
       </c>
       <c r="K51" t="n">
         <v>0.89215</v>
@@ -2678,7 +2678,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.83524</v>
+        <v>-0.83514</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2721,10 +2721,10 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.64107</v>
+        <v>-0.64109</v>
       </c>
       <c r="K53" t="n">
-        <v>0.85504</v>
+        <v>0.84188</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46436</v>
+        <v>-0.46438</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2807,7 +2807,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.25796</v>
+        <v>-1.25802</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2850,7 +2850,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05596</v>
+        <v>-2.05597</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2939,7 +2939,7 @@
         <v>-0.9904500000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>0.26302</v>
+        <v>0.24987</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11224</v>
+        <v>-2.11223</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3022,10 +3022,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08783</v>
+        <v>-1.08781</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.28781</v>
+        <v>-0.30089</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03232</v>
+        <v>-1.03229</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.56048</v>
+        <v>-0.57351</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.74492</v>
+        <v>-0.74494</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.80708</v>
+        <v>-0.80719</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>1.24698</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.76723</v>
+        <v>-0.78023</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.93798</v>
+        <v>1.93799</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3240,7 +3240,7 @@
         <v>0.72112</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.29999</v>
+        <v>-0.28698</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.08771</v>
+        <v>1.0877</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.17102</v>
+        <v>2.17101</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3366,7 +3366,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45743</v>
+        <v>2.45742</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3452,10 +3452,10 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95786</v>
+        <v>2.95787</v>
       </c>
       <c r="K70" t="n">
-        <v>1.12802</v>
+        <v>1.12816</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.13824</v>
+        <v>3.13825</v>
       </c>
       <c r="K71" t="n">
-        <v>1.14263</v>
+        <v>1.15592</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3538,10 +3538,10 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.0752</v>
+        <v>2.07521</v>
       </c>
       <c r="K72" t="n">
-        <v>0.90527</v>
+        <v>0.91851</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3581,10 +3581,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.72597</v>
+        <v>3.726</v>
       </c>
       <c r="K73" t="n">
-        <v>0.94377</v>
+        <v>0.957</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.2771</v>
+        <v>3.27708</v>
       </c>
       <c r="K74" t="n">
-        <v>0.95801</v>
+        <v>0.95813</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52728</v>
+        <v>1.52727</v>
       </c>
       <c r="K75" t="n">
-        <v>0.91731</v>
+        <v>0.93054</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.24291</v>
+        <v>1.2429</v>
       </c>
       <c r="K77" t="n">
         <v>0.98116</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03918</v>
+        <v>-0.03919</v>
       </c>
       <c r="K78" t="n">
         <v>1.20199</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.24424</v>
+        <v>-1.24425</v>
       </c>
       <c r="K80" t="n">
         <v>0.93592</v>
@@ -3928,7 +3928,7 @@
         <v>-1.38612</v>
       </c>
       <c r="K81" t="n">
-        <v>1.20732</v>
+        <v>1.19434</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>-1.81174</v>
       </c>
       <c r="K82" t="n">
-        <v>1.45266</v>
+        <v>1.45285</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15052</v>
+        <v>-1.15051</v>
       </c>
       <c r="K83" t="n">
         <v>1.72705</v>
@@ -4097,10 +4097,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01267</v>
+        <v>-2.01266</v>
       </c>
       <c r="K85" t="n">
-        <v>2.23348</v>
+        <v>2.22049</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>-1.71984</v>
       </c>
       <c r="K86" t="n">
-        <v>2.46978</v>
+        <v>2.4701</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27083</v>
+        <v>-1.27084</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4229,7 +4229,7 @@
         <v>-0.97205</v>
       </c>
       <c r="K88" t="n">
-        <v>2.46401</v>
+        <v>2.45104</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.57023</v>
+        <v>-0.57024</v>
       </c>
       <c r="K89" t="n">
         <v>2.48737</v>
@@ -4315,7 +4315,7 @@
         <v>0.17419</v>
       </c>
       <c r="K90" t="n">
-        <v>2.02685</v>
+        <v>2.01394</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>-0.93909</v>
       </c>
       <c r="K93" t="n">
-        <v>1.47512</v>
+        <v>1.48813</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>-1.38797</v>
       </c>
       <c r="K94" t="n">
-        <v>1.25288</v>
+        <v>1.26582</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.02734</v>
+        <v>-2.02733</v>
       </c>
       <c r="K95" t="n">
         <v>1.1999</v>
@@ -4570,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.27386</v>
+        <v>-1.27385</v>
       </c>
       <c r="K96" t="n">
-        <v>1.22106</v>
+        <v>1.20834</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>-1.9533</v>
       </c>
       <c r="K97" t="n">
-        <v>1.46069</v>
+        <v>1.47358</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>-1.95978</v>
       </c>
       <c r="K98" t="n">
-        <v>1.67449</v>
+        <v>1.68739</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>-2.02144</v>
       </c>
       <c r="K99" t="n">
-        <v>1.97694</v>
+        <v>1.96426</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4742,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.22756</v>
+        <v>-2.22757</v>
       </c>
       <c r="K100" t="n">
-        <v>2.25288</v>
+        <v>2.26582</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>-1.13135</v>
       </c>
       <c r="K102" t="n">
-        <v>2.79641</v>
+        <v>2.80942</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>-1.63681</v>
       </c>
       <c r="K104" t="n">
-        <v>3.41729</v>
+        <v>3.40463</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61232</v>
+        <v>0.61233</v>
       </c>
       <c r="K107" t="n">
         <v>4.36428</v>
@@ -5089,7 +5089,7 @@
         <v>1.65039</v>
       </c>
       <c r="K108" t="n">
-        <v>4.38552</v>
+        <v>4.39864</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32913</v>
+        <v>2.32914</v>
       </c>
       <c r="K109" t="n">
         <v>4.68202</v>
@@ -5218,7 +5218,7 @@
         <v>0.9056</v>
       </c>
       <c r="K111" t="n">
-        <v>4.511</v>
+        <v>4.52399</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>3.93851</v>
       </c>
       <c r="K116" t="n">
-        <v>4.57716</v>
+        <v>4.58996</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.88632</v>
+        <v>1.88633</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5774,7 +5774,7 @@
         <v>-0.29586</v>
       </c>
       <c r="J124" t="n">
-        <v>2.21631</v>
+        <v>2.2163</v>
       </c>
       <c r="K124" t="n">
         <v>2.38011</v>
@@ -6422,7 +6422,7 @@
         <v>-5.48698</v>
       </c>
       <c r="K139" t="n">
-        <v>2.04011</v>
+        <v>2.02858</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.45735</v>
+        <v>1.45734</v>
       </c>
       <c r="K144" t="n">
         <v>3.63258</v>
@@ -6723,7 +6723,7 @@
         <v>3.6765</v>
       </c>
       <c r="K146" t="n">
-        <v>3.76511</v>
+        <v>3.7536</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>1.69823</v>
       </c>
       <c r="K150" t="n">
-        <v>2.0663</v>
+        <v>2.05495</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>0.24069</v>
       </c>
       <c r="K151" t="n">
-        <v>1.67175</v>
+        <v>1.68324</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>0.63309</v>
       </c>
       <c r="K152" t="n">
-        <v>1.48951</v>
+        <v>1.47822</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7107,10 +7107,10 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.58971</v>
+        <v>2.5897</v>
       </c>
       <c r="K155" t="n">
-        <v>1.46451</v>
+        <v>1.45333</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>1.3456</v>
       </c>
       <c r="K158" t="n">
-        <v>1.69774</v>
+        <v>1.70902</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>3.24554</v>
       </c>
       <c r="K162" t="n">
-        <v>3.6485</v>
+        <v>3.6489</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J163" t="n">
-        <v>4.06003</v>
+        <v>4.06004</v>
       </c>
       <c r="K163" t="n">
         <v>3.95512</v>
@@ -7494,10 +7494,10 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.68901</v>
+        <v>3.68902</v>
       </c>
       <c r="K164" t="n">
-        <v>4.24728</v>
+        <v>4.25887</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>2.90117</v>
       </c>
       <c r="K165" t="n">
-        <v>4.29857</v>
+        <v>4.28746</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>3.64576</v>
       </c>
       <c r="K167" t="n">
-        <v>3.82327</v>
+        <v>3.83471</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>2.57146</v>
       </c>
       <c r="K174" t="n">
-        <v>3.30543</v>
+        <v>3.30579</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>2.899</v>
       </c>
       <c r="K177" t="n">
-        <v>3.03514</v>
+        <v>3.04612</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.50138</v>
+        <v>2.50137</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8182,7 +8182,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.7898</v>
+        <v>1.78979</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8443,7 +8443,7 @@
         <v>1.51106</v>
       </c>
       <c r="K186" t="n">
-        <v>1.83877</v>
+        <v>1.84935</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>-1.21212</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.05949</v>
+        <v>-1.0595</v>
       </c>
       <c r="K204" t="n">
         <v>-0.55911</v>
@@ -9647,7 +9647,7 @@
         <v>-5.03658</v>
       </c>
       <c r="K214" t="n">
-        <v>-3.16253</v>
+        <v>-3.15252</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>-1.67939</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.301830000000001</v>
+        <v>-9.30184</v>
       </c>
       <c r="K219" t="n">
         <v>-6.41604</v>
@@ -10163,7 +10163,7 @@
         <v>-6.15033</v>
       </c>
       <c r="K226" t="n">
-        <v>-4.60934</v>
+        <v>-4.6192</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10824,16 +10824,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68464061678798</v>
+        <v>11.6863211178508</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37179992623476</v>
+        <v>11.37196834897944</v>
       </c>
       <c r="D242" t="n">
-        <v>10.13809594422586</v>
+        <v>10.13816525149755</v>
       </c>
       <c r="E242" t="n">
-        <v>7.26294365441793</v>
+        <v>7.264280641475795</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10867,16 +10867,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.27182441353265</v>
+        <v>12.27305481793386</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43549056528717</v>
+        <v>12.43629678881366</v>
       </c>
       <c r="D243" t="n">
-        <v>7.804148087895557</v>
+        <v>7.804143699310284</v>
       </c>
       <c r="E243" t="n">
-        <v>8.995146603689941</v>
+        <v>8.996193392749795</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10910,16 +10910,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.973684404288536</v>
+        <v>3.97259073462457</v>
       </c>
       <c r="C244" t="n">
-        <v>7.19171370422429</v>
+        <v>7.193780342911649</v>
       </c>
       <c r="D244" t="n">
-        <v>6.053111950243517</v>
+        <v>6.053196584988063</v>
       </c>
       <c r="E244" t="n">
-        <v>8.711494149691301</v>
+        <v>8.71295318182681</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10953,16 +10953,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.842514194422342</v>
+        <v>3.842126254767564</v>
       </c>
       <c r="C245" t="n">
-        <v>7.413548529252623</v>
+        <v>7.413878313013411</v>
       </c>
       <c r="D245" t="n">
-        <v>4.819802225512837</v>
+        <v>4.819873456623536</v>
       </c>
       <c r="E245" t="n">
-        <v>8.570647185491588</v>
+        <v>8.567660887249339</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10977,7 +10977,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J245" t="n">
-        <v>2.90206</v>
+        <v>2.90205</v>
       </c>
       <c r="K245" t="n">
         <v>1.87077</v>
@@ -10996,16 +10996,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1729062162050266</v>
+        <v>0.1716305403610008</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6940393296377745</v>
+        <v>-0.6928179758161734</v>
       </c>
       <c r="D246" t="n">
-        <v>1.829842948712579</v>
+        <v>1.829888823989712</v>
       </c>
       <c r="E246" t="n">
-        <v>9.4793499694118</v>
+        <v>9.478648590965498</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11039,16 +11039,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3602099216432286</v>
+        <v>-0.3633184734299966</v>
       </c>
       <c r="C247" t="n">
-        <v>2.283317599845813</v>
+        <v>2.285661447258458</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.603676733175974</v>
+        <v>-1.603646361190381</v>
       </c>
       <c r="E247" t="n">
-        <v>9.101816096238235</v>
+        <v>9.103948431014786</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11082,16 +11082,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.550579261871043</v>
+        <v>-1.552354787472365</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.318524076956241</v>
+        <v>-2.316860683433075</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.088612500280563</v>
+        <v>-3.088701741253641</v>
       </c>
       <c r="E248" t="n">
-        <v>8.145687763628363</v>
+        <v>8.148209035576981</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11125,16 +11125,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.450330301633485</v>
+        <v>1.450612994381628</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2377493248451823</v>
+        <v>-0.2363814722077473</v>
       </c>
       <c r="D249" t="n">
-        <v>2.495848285605295</v>
+        <v>2.495805028769071</v>
       </c>
       <c r="E249" t="n">
-        <v>7.144304007646962</v>
+        <v>7.147542035958776</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11168,16 +11168,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.831640846575325</v>
+        <v>4.83264238121639</v>
       </c>
       <c r="C250" t="n">
-        <v>4.687457213806301</v>
+        <v>4.687979655750385</v>
       </c>
       <c r="D250" t="n">
-        <v>6.334332351779226</v>
+        <v>6.334200046212235</v>
       </c>
       <c r="E250" t="n">
-        <v>8.283189906925426</v>
+        <v>8.285042294873723</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11192,7 +11192,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36583</v>
+        <v>5.36584</v>
       </c>
       <c r="K250" t="n">
         <v>1.10007</v>
@@ -11211,16 +11211,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8317492481482835</v>
+        <v>0.8317426378089632</v>
       </c>
       <c r="C251" t="n">
-        <v>1.477763137773014</v>
+        <v>1.478822543395952</v>
       </c>
       <c r="D251" t="n">
-        <v>2.659686656357207</v>
+        <v>2.659575685517845</v>
       </c>
       <c r="E251" t="n">
-        <v>8.430192441595707</v>
+        <v>8.431535365767573</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11235,7 +11235,7 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.69151</v>
+        <v>4.69152</v>
       </c>
       <c r="K251" t="n">
         <v>1.33305</v>
@@ -11254,16 +11254,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.651794968638167</v>
+        <v>3.652593285826322</v>
       </c>
       <c r="C252" t="n">
-        <v>2.968960861279379</v>
+        <v>2.969197400881329</v>
       </c>
       <c r="D252" t="n">
-        <v>3.949783350399261</v>
+        <v>3.949986309309406</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19888951443098</v>
+        <v>10.19609174940759</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11297,16 +11297,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.120527904853757</v>
+        <v>7.121646046888941</v>
       </c>
       <c r="C253" t="n">
-        <v>8.446779855526465</v>
+        <v>8.446736178793612</v>
       </c>
       <c r="D253" t="n">
-        <v>3.620981976439896</v>
+        <v>3.621032521225254</v>
       </c>
       <c r="E253" t="n">
-        <v>7.933059469786929</v>
+        <v>7.935802401409098</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11340,16 +11340,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.373468175150966</v>
+        <v>7.374180065245906</v>
       </c>
       <c r="C254" t="n">
-        <v>7.314620106886993</v>
+        <v>7.313967216435602</v>
       </c>
       <c r="D254" t="n">
-        <v>5.738175888361385</v>
+        <v>5.738079254101436</v>
       </c>
       <c r="E254" t="n">
-        <v>8.193739697163526</v>
+        <v>8.192682144438134</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11364,7 +11364,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.6084</v>
+        <v>5.60839</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11383,16 +11383,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449515851324405</v>
+        <v>5.449711182515982</v>
       </c>
       <c r="C255" t="n">
-        <v>5.869304610353132</v>
+        <v>5.868765836839662</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549865349298619</v>
+        <v>2.549842384738854</v>
       </c>
       <c r="E255" t="n">
-        <v>6.401511820200234</v>
+        <v>6.400754327368396</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11407,7 +11407,7 @@
         <v>-2.36967</v>
       </c>
       <c r="J255" t="n">
-        <v>5.94848</v>
+        <v>5.94847</v>
       </c>
       <c r="K255" t="n">
         <v>2.39078</v>
@@ -11426,16 +11426,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.70537404485221</v>
+        <v>11.7065369637184</v>
       </c>
       <c r="C256" t="n">
-        <v>9.845550526731595</v>
+        <v>9.844090998784893</v>
       </c>
       <c r="D256" t="n">
-        <v>5.66284201789431</v>
+        <v>5.6627687021235</v>
       </c>
       <c r="E256" t="n">
-        <v>7.164721742316171</v>
+        <v>7.163013991754474</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11469,16 +11469,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.77542818036976</v>
+        <v>8.774637722575051</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537560266776122</v>
+        <v>8.537535839634792</v>
       </c>
       <c r="D257" t="n">
-        <v>5.101334752693742</v>
+        <v>5.10133683345102</v>
       </c>
       <c r="E257" t="n">
-        <v>7.456253016537628</v>
+        <v>7.458021572808948</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11512,16 +11512,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92068582296475</v>
+        <v>11.92055482669161</v>
       </c>
       <c r="C258" t="n">
-        <v>11.75159830514207</v>
+        <v>11.75146480548337</v>
       </c>
       <c r="D258" t="n">
-        <v>8.781324570704886</v>
+        <v>8.78139100666424</v>
       </c>
       <c r="E258" t="n">
-        <v>7.92711107769617</v>
+        <v>7.926934192846335</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11536,7 +11536,7 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59272</v>
+        <v>6.59273</v>
       </c>
       <c r="K258" t="n">
         <v>3.32875</v>
@@ -11555,16 +11555,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45407666270382</v>
+        <v>11.45446004492012</v>
       </c>
       <c r="C259" t="n">
-        <v>9.101299589791578</v>
+        <v>9.100965251183446</v>
       </c>
       <c r="D259" t="n">
-        <v>7.828928562078286</v>
+        <v>7.829038389098208</v>
       </c>
       <c r="E259" t="n">
-        <v>8.261273995047258</v>
+        <v>8.260079719662894</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11582,7 +11582,7 @@
         <v>6.62991</v>
       </c>
       <c r="K259" t="n">
-        <v>3.91617</v>
+        <v>3.92676</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11598,16 +11598,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.847605594092322</v>
+        <v>8.846745780285392</v>
       </c>
       <c r="C260" t="n">
-        <v>9.291474702900949</v>
+        <v>9.291525254496523</v>
       </c>
       <c r="D260" t="n">
-        <v>8.076791962944153</v>
+        <v>8.076966828130638</v>
       </c>
       <c r="E260" t="n">
-        <v>8.665978052139355</v>
+        <v>8.664220055157145</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11641,16 +11641,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52765277214047</v>
+        <v>12.52757226638814</v>
       </c>
       <c r="C261" t="n">
-        <v>10.3120736612776</v>
+        <v>10.31175390479724</v>
       </c>
       <c r="D261" t="n">
-        <v>5.621018933552402</v>
+        <v>5.620960042647871</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40860106696149</v>
+        <v>10.40590488318911</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11684,16 +11684,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.794189953421315</v>
+        <v>6.79351386766549</v>
       </c>
       <c r="C262" t="n">
-        <v>6.467276998132876</v>
+        <v>6.467315278281371</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.812815685298629</v>
+        <v>-0.8130118463050895</v>
       </c>
       <c r="E262" t="n">
-        <v>8.713933682035591</v>
+        <v>8.714087110934576</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11708,7 +11708,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06059</v>
+        <v>4.0606</v>
       </c>
       <c r="K262" t="n">
         <v>5.81027</v>
@@ -11727,16 +11727,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.092185984173472</v>
+        <v>9.091878457084434</v>
       </c>
       <c r="C263" t="n">
-        <v>7.433948810621849</v>
+        <v>7.433742446679803</v>
       </c>
       <c r="D263" t="n">
-        <v>3.15627524797657</v>
+        <v>3.15614894464713</v>
       </c>
       <c r="E263" t="n">
-        <v>8.716259017321804</v>
+        <v>8.718125411095091</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11770,16 +11770,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42257415197752</v>
+        <v>13.4243896821107</v>
       </c>
       <c r="C264" t="n">
-        <v>11.27019889830092</v>
+        <v>11.26859630224437</v>
       </c>
       <c r="D264" t="n">
-        <v>4.654979096594181</v>
+        <v>4.655150544226738</v>
       </c>
       <c r="E264" t="n">
-        <v>6.305006567280524</v>
+        <v>6.310304768666519</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11813,16 +11813,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.053819701879238</v>
+        <v>8.054337096948338</v>
       </c>
       <c r="C265" t="n">
-        <v>5.794106788654574</v>
+        <v>5.793577158911845</v>
       </c>
       <c r="D265" t="n">
-        <v>2.717560983108203</v>
+        <v>2.717654577847073</v>
       </c>
       <c r="E265" t="n">
-        <v>7.346465086049925</v>
+        <v>7.34989637468042</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11837,7 +11837,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70188</v>
+        <v>3.70187</v>
       </c>
       <c r="K265" t="n">
         <v>5.63483</v>
@@ -11856,16 +11856,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.578820343783894</v>
+        <v>2.578460076738254</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2245512661486315</v>
+        <v>-0.2238886640106963</v>
       </c>
       <c r="D266" t="n">
-        <v>2.191586365425113</v>
+        <v>2.191618039304122</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01832253568254</v>
+        <v>12.01694022028965</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11880,10 +11880,10 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87412</v>
+        <v>2.87411</v>
       </c>
       <c r="K266" t="n">
-        <v>5.62941</v>
+        <v>5.6398</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11899,16 +11899,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.099772737898189</v>
+        <v>5.099289199428814</v>
       </c>
       <c r="C267" t="n">
-        <v>1.658699619594484</v>
+        <v>1.659332168311223</v>
       </c>
       <c r="D267" t="n">
-        <v>3.454108351003771</v>
+        <v>3.45418998167959</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53886632032826</v>
+        <v>13.53639865861087</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11942,16 +11942,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.828475895128959</v>
+        <v>5.829093467945223</v>
       </c>
       <c r="C268" t="n">
-        <v>3.421548541412056</v>
+        <v>3.42137249615786</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9093427411662747</v>
+        <v>0.9094038494481316</v>
       </c>
       <c r="E268" t="n">
-        <v>15.11118128038824</v>
+        <v>15.10894084300953</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11966,7 +11966,7 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.18503</v>
+        <v>2.18502</v>
       </c>
       <c r="K268" t="n">
         <v>5.87932</v>
@@ -11985,16 +11985,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.374814092490851</v>
+        <v>2.373878252572181</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7169262339075333</v>
+        <v>0.7177349822713674</v>
       </c>
       <c r="D269" t="n">
-        <v>2.948239610933534</v>
+        <v>2.948258661669012</v>
       </c>
       <c r="E269" t="n">
-        <v>10.12965003525876</v>
+        <v>10.13206520747363</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12028,16 +12028,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.698728572058817</v>
+        <v>2.698820356083442</v>
       </c>
       <c r="C270" t="n">
-        <v>0.338323313496347</v>
+        <v>0.3387324665286906</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.520108238084339</v>
+        <v>-1.520177805470047</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77436787613366</v>
+        <v>11.77583131820379</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12052,7 +12052,7 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24404</v>
+        <v>2.24405</v>
       </c>
       <c r="K270" t="n">
         <v>5.58396</v>
@@ -12071,16 +12071,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.1170286148702</v>
+        <v>4.117904207579803</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272427561831059</v>
+        <v>3.272158753235188</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.173129380273774</v>
+        <v>-1.173285265493673</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72620724671418</v>
+        <v>12.72565370518555</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12098,7 +12098,7 @@
         <v>2.02538</v>
       </c>
       <c r="K271" t="n">
-        <v>5.55103</v>
+        <v>5.54028</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12114,16 +12114,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.815701510398828</v>
+        <v>3.815838055866561</v>
       </c>
       <c r="C272" t="n">
-        <v>2.83458859835799</v>
+        <v>2.834414438875421</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.924067858742574</v>
+        <v>-2.924132950243519</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49980948275904</v>
+        <v>12.49788551640993</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12157,16 +12157,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.045383087702635</v>
+        <v>2.045087700193582</v>
       </c>
       <c r="C273" t="n">
-        <v>2.702892209386887</v>
+        <v>2.702753555099546</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1120085590475717</v>
+        <v>-0.1120112466762357</v>
       </c>
       <c r="E273" t="n">
-        <v>12.16657769524911</v>
+        <v>12.16368843444913</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12200,16 +12200,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1454392921755532</v>
+        <v>-0.146149676956242</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2300987024659751</v>
+        <v>0.2306163096418734</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03731093430758836</v>
+        <v>0.03723050616573076</v>
       </c>
       <c r="E274" t="n">
-        <v>11.9316034952414</v>
+        <v>11.92905102230655</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12227,7 +12227,7 @@
         <v>2.13192</v>
       </c>
       <c r="K274" t="n">
-        <v>3.65415</v>
+        <v>3.66414</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12243,16 +12243,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3224386192231865</v>
+        <v>-0.322773073270366</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4547999913968703</v>
+        <v>-0.4541823068153872</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.024834462133818</v>
+        <v>-2.025036918682122</v>
       </c>
       <c r="E275" t="n">
-        <v>10.91071788024265</v>
+        <v>10.90796931752909</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12286,16 +12286,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994996269437201</v>
+        <v>-3.994609716694453</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.155036353267983</v>
+        <v>-4.155016270866419</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.714823441797976</v>
+        <v>-3.71469893258195</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912259611121499</v>
+        <v>8.912476788405321</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12310,7 +12310,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.6421</v>
+        <v>2.64211</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12329,16 +12329,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.36398150404067</v>
+        <v>-3.363846347012356</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.722971987700585</v>
+        <v>-3.722803365233152</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.385806427301685</v>
+        <v>-3.385776021505427</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79841385698834</v>
+        <v>10.79436698078313</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12353,7 +12353,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55361</v>
+        <v>2.55363</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12372,16 +12372,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.268299826000476</v>
+        <v>3.268354928370831</v>
       </c>
       <c r="C278" t="n">
-        <v>3.634761527665509</v>
+        <v>3.634716234291346</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.618476029695604</v>
+        <v>-1.61832406775857</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127539949905514</v>
+        <v>6.127549245347397</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12396,10 +12396,10 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57155</v>
+        <v>3.57148</v>
       </c>
       <c r="K278" t="n">
-        <v>2.89086</v>
+        <v>2.88074</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12415,16 +12415,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1248149338431426</v>
+        <v>-0.1253157540679006</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4631999798629938</v>
+        <v>0.463339132479712</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3326610515336004</v>
+        <v>-0.3324830902674103</v>
       </c>
       <c r="E279" t="n">
-        <v>4.000362299389892</v>
+        <v>4.001555880732077</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12439,7 +12439,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10613</v>
+        <v>3.10615</v>
       </c>
       <c r="K279" t="n">
         <v>2.73892</v>
@@ -12458,16 +12458,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848675231143027</v>
+        <v>-1.848892567628702</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.182937024782661</v>
+        <v>-2.182615785265929</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7988691568516337</v>
+        <v>-0.7988053574945364</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4654666227630555</v>
+        <v>0.4686534685211186</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12482,7 +12482,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.1334</v>
+        <v>3.13341</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12501,16 +12501,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.169835752018945</v>
+        <v>2.169322343353408</v>
       </c>
       <c r="C281" t="n">
-        <v>1.856071836568662</v>
+        <v>1.85650232694512</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.089522496670549</v>
+        <v>-3.089574879455415</v>
       </c>
       <c r="E281" t="n">
-        <v>3.989778986114589</v>
+        <v>3.992216543843452</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12525,10 +12525,10 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.5293</v>
+        <v>2.52931</v>
       </c>
       <c r="K281" t="n">
-        <v>2.47477</v>
+        <v>2.48447</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12544,16 +12544,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.201594201999434</v>
+        <v>1.202136641397211</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625684581826459</v>
+        <v>1.625532019542919</v>
       </c>
       <c r="D282" t="n">
-        <v>0.283189305931586</v>
+        <v>0.2831090410712278</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9934947647115777</v>
+        <v>0.9960353367786778</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12568,10 +12568,10 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46743</v>
+        <v>2.46744</v>
       </c>
       <c r="K282" t="n">
-        <v>2.69275</v>
+        <v>2.70244</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12587,16 +12587,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.130787456887816</v>
+        <v>1.131519600763942</v>
       </c>
       <c r="C283" t="n">
-        <v>0.562303764508143</v>
+        <v>0.5622180221450668</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1462385870216965</v>
+        <v>0.1461635760984459</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1320386431446274</v>
+        <v>-0.1300330518576254</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12630,16 +12630,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.550113790153818</v>
+        <v>2.550321392217225</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05080133246483376</v>
+        <v>-0.05039994069987452</v>
       </c>
       <c r="D284" t="n">
-        <v>2.830764590627677</v>
+        <v>2.830723290095638</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7776460427552312</v>
+        <v>0.7792631638080971</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12654,7 +12654,7 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26764</v>
+        <v>1.26765</v>
       </c>
       <c r="K284" t="n">
         <v>2.66834</v>
@@ -12673,16 +12673,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.460707648489378</v>
+        <v>0.4597255982823789</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7839513086775662</v>
+        <v>-0.7832346176889549</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.487965150005688</v>
+        <v>-1.488053104305276</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2723105005556503</v>
+        <v>0.2741194938582936</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12697,7 +12697,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55159</v>
+        <v>0.5516</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12716,16 +12716,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.657009621450636</v>
+        <v>4.656495330986199</v>
       </c>
       <c r="C286" t="n">
-        <v>1.850599923955465</v>
+        <v>1.851346451228109</v>
       </c>
       <c r="D286" t="n">
-        <v>2.953478767329853</v>
+        <v>2.953192343805777</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268342016622737</v>
+        <v>1.268596045896109</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12740,10 +12740,10 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35725</v>
+        <v>1.35727</v>
       </c>
       <c r="K286" t="n">
-        <v>3.246</v>
+        <v>3.24569</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12759,16 +12759,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.818921236283425</v>
+        <v>5.818814359454194</v>
       </c>
       <c r="C287" t="n">
-        <v>3.94516131425473</v>
+        <v>3.945317982665042</v>
       </c>
       <c r="D287" t="n">
-        <v>4.857197010275716</v>
+        <v>4.856940163032397</v>
       </c>
       <c r="E287" t="n">
-        <v>2.677999681970755</v>
+        <v>2.676744879570858</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12783,10 +12783,10 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.27733</v>
+        <v>1.27722</v>
       </c>
       <c r="K287" t="n">
-        <v>3.50101</v>
+        <v>3.51063</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12802,16 +12802,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.479289448574963</v>
+        <v>3.480530770468682</v>
       </c>
       <c r="C288" t="n">
-        <v>2.952421376744319</v>
+        <v>2.95066472650416</v>
       </c>
       <c r="D288" t="n">
-        <v>2.10541467384231</v>
+        <v>2.105850303771151</v>
       </c>
       <c r="E288" t="n">
-        <v>3.365422797723139</v>
+        <v>3.363540513565488</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12826,7 +12826,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.52986</v>
+        <v>0.52998</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12845,16 +12845,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.84725276116831</v>
+        <v>6.848322935538254</v>
       </c>
       <c r="C289" t="n">
-        <v>6.018493034916461</v>
+        <v>6.017279382417651</v>
       </c>
       <c r="D289" t="n">
-        <v>2.229873552892614</v>
+        <v>2.229970692714822</v>
       </c>
       <c r="E289" t="n">
-        <v>3.823818062760176</v>
+        <v>3.820293115301698</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12872,7 +12872,7 @@
         <v>-0.27365</v>
       </c>
       <c r="K289" t="n">
-        <v>3.50206</v>
+        <v>3.51163</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12888,16 +12888,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8710200345882546</v>
+        <v>0.870593908024575</v>
       </c>
       <c r="C290" t="n">
-        <v>1.164137096514128</v>
+        <v>1.164236615156611</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.203764345332337</v>
+        <v>-2.203668233578993</v>
       </c>
       <c r="E290" t="n">
-        <v>2.404241124067608</v>
+        <v>2.405924795847292</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12912,7 +12912,7 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.03952</v>
+        <v>-0.03961</v>
       </c>
       <c r="K290" t="n">
         <v>3.82263</v>
@@ -12931,16 +12931,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.289708031672234</v>
+        <v>3.28909692597561</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302402419068073</v>
+        <v>3.302415712610096</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.245855577294008</v>
+        <v>-1.245748751424136</v>
       </c>
       <c r="E291" t="n">
-        <v>3.627915569584772</v>
+        <v>3.628210025536993</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12955,10 +12955,10 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.2363</v>
+        <v>-0.23631</v>
       </c>
       <c r="K291" t="n">
-        <v>3.84652</v>
+        <v>3.85604</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -12974,16 +12974,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.307625136017281</v>
+        <v>6.30728442171864</v>
       </c>
       <c r="C292" t="n">
-        <v>5.588465923850117</v>
+        <v>5.588600005263178</v>
       </c>
       <c r="D292" t="n">
-        <v>2.181732420371274</v>
+        <v>2.181868659433284</v>
       </c>
       <c r="E292" t="n">
-        <v>4.880453963756404</v>
+        <v>4.880784790353032</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13017,16 +13017,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.537623971663129</v>
+        <v>3.537164750821242</v>
       </c>
       <c r="C293" t="n">
-        <v>2.371741330923061</v>
+        <v>2.372082247313734</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532303075130748</v>
+        <v>2.532364367060747</v>
       </c>
       <c r="E293" t="n">
-        <v>4.24243778839708</v>
+        <v>4.242051023227078</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13041,10 +13041,10 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.522</v>
+        <v>-0.52199</v>
       </c>
       <c r="K293" t="n">
-        <v>3.88294</v>
+        <v>3.87311</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13060,16 +13060,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.372202411176243</v>
+        <v>8.372964511997738</v>
       </c>
       <c r="C294" t="n">
-        <v>5.911089667085023</v>
+        <v>5.910774873927327</v>
       </c>
       <c r="D294" t="n">
-        <v>4.196747882438312</v>
+        <v>4.196812654410698</v>
       </c>
       <c r="E294" t="n">
-        <v>6.252838886817402</v>
+        <v>6.251215969423951</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13084,10 +13084,10 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82338</v>
+        <v>-0.82336</v>
       </c>
       <c r="K294" t="n">
-        <v>3.87663</v>
+        <v>3.87626</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13103,16 +13103,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.598349417584903</v>
+        <v>6.599152337015557</v>
       </c>
       <c r="C295" t="n">
-        <v>5.386362779603315</v>
+        <v>5.385907638923459</v>
       </c>
       <c r="D295" t="n">
-        <v>6.107721442050784</v>
+        <v>6.107678900772995</v>
       </c>
       <c r="E295" t="n">
-        <v>6.950074528828254</v>
+        <v>6.947532808508461</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13127,10 +13127,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05983</v>
+        <v>-0.05978</v>
       </c>
       <c r="K295" t="n">
-        <v>4.14391</v>
+        <v>4.15332</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13146,16 +13146,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.14566062488464</v>
+        <v>5.145781303816488</v>
       </c>
       <c r="C296" t="n">
-        <v>5.711798727705042</v>
+        <v>5.711633843076758</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1193348333601518</v>
+        <v>0.1192262460792959</v>
       </c>
       <c r="E296" t="n">
-        <v>4.680961339939604</v>
+        <v>4.680025245988717</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13170,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.27666</v>
+        <v>0.27671</v>
       </c>
       <c r="K296" t="n">
         <v>4.18465</v>
@@ -13189,16 +13189,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.862907485922151</v>
+        <v>3.861727476192867</v>
       </c>
       <c r="C297" t="n">
-        <v>4.003352453704156</v>
+        <v>4.003907561709252</v>
       </c>
       <c r="D297" t="n">
-        <v>2.957618943838569</v>
+        <v>2.957450346048596</v>
       </c>
       <c r="E297" t="n">
-        <v>4.086346931474183</v>
+        <v>4.087011140283647</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13213,7 +13213,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.31411</v>
+        <v>0.31412</v>
       </c>
       <c r="K297" t="n">
         <v>3.95179</v>
@@ -13232,16 +13232,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.449217048959418</v>
+        <v>2.44825143220806</v>
       </c>
       <c r="C298" t="n">
-        <v>1.069781436897532</v>
+        <v>1.070848483216258</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4407108509185909</v>
+        <v>0.4401330553479132</v>
       </c>
       <c r="E298" t="n">
-        <v>3.051051989548026</v>
+        <v>3.050866955338583</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13256,10 +13256,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.38253</v>
+        <v>0.3825</v>
       </c>
       <c r="K298" t="n">
-        <v>4.13285</v>
+        <v>4.12313</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13275,16 +13275,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.292262972139737</v>
+        <v>3.291305466989769</v>
       </c>
       <c r="C299" t="n">
-        <v>2.792711363540645</v>
+        <v>2.793684973416188</v>
       </c>
       <c r="D299" t="n">
-        <v>1.819410034055413</v>
+        <v>1.818814267202851</v>
       </c>
       <c r="E299" t="n">
-        <v>2.813055311686097</v>
+        <v>2.814114307218873</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13299,10 +13299,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.00844</v>
+        <v>-0.00859</v>
       </c>
       <c r="K299" t="n">
-        <v>3.93086</v>
+        <v>3.9212</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.508892651518348</v>
+        <v>4.51109410811168</v>
       </c>
       <c r="C300" t="n">
-        <v>3.716257357514818</v>
+        <v>3.713313697350351</v>
       </c>
       <c r="D300" t="n">
-        <v>3.897508212151379</v>
+        <v>3.89815881668325</v>
       </c>
       <c r="E300" t="n">
-        <v>3.748844294470466</v>
+        <v>3.747998470400171</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13342,10 +13342,10 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.00443</v>
+        <v>1.00447</v>
       </c>
       <c r="K300" t="n">
-        <v>3.58035</v>
+        <v>3.5896</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13361,16 +13361,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.778010473638417</v>
+        <v>4.779386350855752</v>
       </c>
       <c r="C301" t="n">
-        <v>3.181932621226702</v>
+        <v>3.180336507802806</v>
       </c>
       <c r="D301" t="n">
-        <v>5.325802069325136</v>
+        <v>5.326134837319318</v>
       </c>
       <c r="E301" t="n">
-        <v>1.88289511545523</v>
+        <v>1.883299976733732</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13385,10 +13385,10 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95487</v>
+        <v>1.9549</v>
       </c>
       <c r="K301" t="n">
-        <v>3.95673</v>
+        <v>3.94713</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13404,16 +13404,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.339074327576609</v>
+        <v>5.339260208809637</v>
       </c>
       <c r="C302" t="n">
-        <v>3.380262217806895</v>
+        <v>3.380303501039306</v>
       </c>
       <c r="D302" t="n">
-        <v>4.101048762309722</v>
+        <v>4.101425147433124</v>
       </c>
       <c r="E302" t="n">
-        <v>1.198764324836388</v>
+        <v>1.200377743609327</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13428,7 +13428,7 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47778</v>
+        <v>1.47771</v>
       </c>
       <c r="K302" t="n">
         <v>3.58984</v>
@@ -13447,16 +13447,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.231598900479395</v>
+        <v>5.231415951270257</v>
       </c>
       <c r="C303" t="n">
-        <v>3.151893340493417</v>
+        <v>3.151931291387977</v>
       </c>
       <c r="D303" t="n">
-        <v>1.624484739531495</v>
+        <v>1.624776814622297</v>
       </c>
       <c r="E303" t="n">
-        <v>3.117673656498843</v>
+        <v>3.118981990323189</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13471,10 +13471,10 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98043</v>
+        <v>1.98044</v>
       </c>
       <c r="K303" t="n">
-        <v>3.34647</v>
+        <v>3.337</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13490,16 +13490,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.05630887912378</v>
+        <v>1.055609824894632</v>
       </c>
       <c r="C304" t="n">
-        <v>0.4990242613022389</v>
+        <v>0.4998935330313925</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6709775930660133</v>
+        <v>-0.6707962877153251</v>
       </c>
       <c r="E304" t="n">
-        <v>3.83529235454052</v>
+        <v>3.835682444900579</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13514,7 +13514,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.7295</v>
+        <v>2.72951</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13533,16 +13533,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.069971846592255</v>
+        <v>1.069720819667541</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1453421817021683</v>
+        <v>0.1461271871531222</v>
       </c>
       <c r="D305" t="n">
-        <v>2.196735029316299</v>
+        <v>2.196707161832978</v>
       </c>
       <c r="E305" t="n">
-        <v>1.964970492289275</v>
+        <v>1.965889419215916</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13557,7 +13557,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.50376</v>
+        <v>2.50379</v>
       </c>
       <c r="K305" t="n">
         <v>3.30021</v>
@@ -13576,16 +13576,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6315513373286175</v>
+        <v>0.6313796907830405</v>
       </c>
       <c r="C306" t="n">
-        <v>0.02922225480648244</v>
+        <v>0.02997290191932844</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.262580363733534</v>
+        <v>-1.262692074741378</v>
       </c>
       <c r="E306" t="n">
-        <v>2.321841001370695</v>
+        <v>2.322849285880579</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13600,10 +13600,10 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97686</v>
+        <v>2.97693</v>
       </c>
       <c r="K306" t="n">
-        <v>3.03278</v>
+        <v>3.02342</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13619,16 +13619,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.191100081864938</v>
+        <v>2.191129529396618</v>
       </c>
       <c r="C307" t="n">
-        <v>1.363826001296409</v>
+        <v>1.36460493563928</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.597756008844454</v>
+        <v>-2.597971519336439</v>
       </c>
       <c r="E307" t="n">
-        <v>3.143031173341049</v>
+        <v>3.143681576061064</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13643,10 +13643,10 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.46872</v>
+        <v>3.46887</v>
       </c>
       <c r="K307" t="n">
-        <v>2.73105</v>
+        <v>2.72177</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13662,16 +13662,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.772799963021554</v>
+        <v>1.772644918006594</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2720460003526215</v>
+        <v>0.2728252964299793</v>
       </c>
       <c r="D308" t="n">
-        <v>1.608607897115233</v>
+        <v>1.608422948790578</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799629456566978</v>
+        <v>4.799814973146765</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13686,7 +13686,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.01332</v>
+        <v>3.01344</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13705,16 +13705,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.141711538041103</v>
+        <v>3.14075015813986</v>
       </c>
       <c r="C309" t="n">
-        <v>2.240057684526509</v>
+        <v>2.240883722870657</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5633827939527603</v>
+        <v>0.56323974859116</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405823187200864</v>
+        <v>5.405561561029848</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13729,7 +13729,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06831</v>
+        <v>3.06829</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13748,16 +13748,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.758981335663704</v>
+        <v>5.758046773060155</v>
       </c>
       <c r="C310" t="n">
-        <v>6.636959422151056</v>
+        <v>6.637851820273277</v>
       </c>
       <c r="D310" t="n">
-        <v>2.772027040968195</v>
+        <v>2.771267881514272</v>
       </c>
       <c r="E310" t="n">
-        <v>8.393180311257421</v>
+        <v>8.392253348831291</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13772,7 +13772,7 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.61227</v>
+        <v>2.6121</v>
       </c>
       <c r="K310" t="n">
         <v>2.77728</v>
@@ -13791,16 +13791,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.910517937951496</v>
+        <v>3.908904345920017</v>
       </c>
       <c r="C311" t="n">
-        <v>3.199476036062299</v>
+        <v>3.201083945147398</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6411447137107507</v>
+        <v>0.6403401416306798</v>
       </c>
       <c r="E311" t="n">
-        <v>4.8794544947659</v>
+        <v>4.879741848641417</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13815,7 +13815,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99532</v>
+        <v>2.99497</v>
       </c>
       <c r="K311" t="n">
         <v>2.70029</v>
@@ -13834,16 +13834,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.033823553989091</v>
+        <v>4.037144665817372</v>
       </c>
       <c r="C312" t="n">
-        <v>2.369017577636989</v>
+        <v>2.364189410435502</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.064438653188882</v>
+        <v>-1.063527794374852</v>
       </c>
       <c r="E312" t="n">
-        <v>5.824374294578827</v>
+        <v>5.823847445899255</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13858,10 +13858,10 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.75337</v>
+        <v>2.75324</v>
       </c>
       <c r="K312" t="n">
-        <v>2.99214</v>
+        <v>2.99187</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13877,16 +13877,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.252311136701436</v>
+        <v>3.253506139499907</v>
       </c>
       <c r="C313" t="n">
-        <v>2.405041856907353</v>
+        <v>2.403026370583339</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04488891843321685</v>
+        <v>0.04528839111523908</v>
       </c>
       <c r="E313" t="n">
-        <v>6.335529023254516</v>
+        <v>6.334329432668739</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13901,7 +13901,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.39452</v>
+        <v>2.3945</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13920,16 +13920,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.285651398645185</v>
+        <v>4.285721815568477</v>
       </c>
       <c r="C314" t="n">
-        <v>3.916612947176867</v>
+        <v>3.917028427398539</v>
       </c>
       <c r="D314" t="n">
-        <v>1.484681993990433</v>
+        <v>1.485126607810217</v>
       </c>
       <c r="E314" t="n">
-        <v>8.64737544926717</v>
+        <v>8.643075227423447</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13944,7 +13944,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.92589</v>
+        <v>1.92599</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13963,16 +13963,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.68786180769418</v>
+        <v>1.687417985445228</v>
       </c>
       <c r="C315" t="n">
-        <v>2.645682029253482</v>
+        <v>2.64593741877599</v>
       </c>
       <c r="D315" t="n">
-        <v>0.931362086009635</v>
+        <v>0.9317884579545854</v>
       </c>
       <c r="E315" t="n">
-        <v>4.024641913058113</v>
+        <v>4.023702458425382</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13987,10 +13987,10 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.40942</v>
+        <v>2.40951</v>
       </c>
       <c r="K315" t="n">
-        <v>3.23811</v>
+        <v>3.24698</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -14006,16 +14006,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.656070001187616</v>
+        <v>2.655707893401171</v>
       </c>
       <c r="C316" t="n">
-        <v>2.862006885288504</v>
+        <v>2.862717871896181</v>
       </c>
       <c r="D316" t="n">
-        <v>0.398035388607787</v>
+        <v>0.3982860815165967</v>
       </c>
       <c r="E316" t="n">
-        <v>3.649593409796625</v>
+        <v>3.649025454529764</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14030,7 +14030,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62542</v>
+        <v>2.62545</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14049,16 +14049,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.792325447121097</v>
+        <v>8.793253614969498</v>
       </c>
       <c r="C317" t="n">
-        <v>9.070661360225563</v>
+        <v>9.070376163717997</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3838344546402084</v>
+        <v>0.383773611397964</v>
       </c>
       <c r="E317" t="n">
-        <v>7.313277373653326</v>
+        <v>7.311095553416358</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14073,10 +14073,10 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43419</v>
+        <v>3.43439</v>
       </c>
       <c r="K317" t="n">
-        <v>3.2742</v>
+        <v>3.28303</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14092,16 +14092,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.376753233042874</v>
+        <v>4.376528170527849</v>
       </c>
       <c r="C318" t="n">
-        <v>5.380300658861925</v>
+        <v>5.380693007912907</v>
       </c>
       <c r="D318" t="n">
-        <v>2.152426702935206</v>
+        <v>2.152373987453626</v>
       </c>
       <c r="E318" t="n">
-        <v>5.210660723896221</v>
+        <v>5.209576276321748</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14116,7 +14116,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.3713</v>
+        <v>3.3716</v>
       </c>
       <c r="K318" t="n">
         <v>3.52516</v>
@@ -14135,16 +14135,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.195058856682277</v>
+        <v>4.194789103861862</v>
       </c>
       <c r="C319" t="n">
-        <v>3.331614097118418</v>
+        <v>3.332426339182448</v>
       </c>
       <c r="D319" t="n">
-        <v>2.731265948804995</v>
+        <v>2.731130799617776</v>
       </c>
       <c r="E319" t="n">
-        <v>3.72178105734382</v>
+        <v>3.723266747459419</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14159,7 +14159,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.1465</v>
+        <v>3.14665</v>
       </c>
       <c r="K319" t="n">
         <v>3.82042</v>
@@ -14178,16 +14178,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.753412737577769</v>
+        <v>6.753347921463604</v>
       </c>
       <c r="C320" t="n">
-        <v>6.783079114265256</v>
+        <v>6.783856992963422</v>
       </c>
       <c r="D320" t="n">
-        <v>2.224419474154682</v>
+        <v>2.22413311079992</v>
       </c>
       <c r="E320" t="n">
-        <v>3.065093533777863</v>
+        <v>3.067079392964822</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.12978</v>
+        <v>3.12982</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14221,16 +14221,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.929999717528878</v>
+        <v>5.928975762070676</v>
       </c>
       <c r="C321" t="n">
-        <v>4.663888514003567</v>
+        <v>4.665266040489957</v>
       </c>
       <c r="D321" t="n">
-        <v>1.458410121513554</v>
+        <v>1.458018836021591</v>
       </c>
       <c r="E321" t="n">
-        <v>2.665013965305785</v>
+        <v>2.667825166224835</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14245,10 +14245,10 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.17643</v>
+        <v>3.17703</v>
       </c>
       <c r="K321" t="n">
-        <v>3.63923</v>
+        <v>3.64797</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14264,16 +14264,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.555130225893157</v>
+        <v>5.552992793690392</v>
       </c>
       <c r="C322" t="n">
-        <v>3.514408466523489</v>
+        <v>3.517011588870123</v>
       </c>
       <c r="D322" t="n">
-        <v>0.06596630917723445</v>
+        <v>0.06456408498720645</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5173918244369746</v>
+        <v>-0.5123699594380415</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14288,7 +14288,7 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.79738</v>
+        <v>3.79708</v>
       </c>
       <c r="K322" t="n">
         <v>3.73954</v>
@@ -14307,16 +14307,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.335645049934356</v>
+        <v>4.332827258365679</v>
       </c>
       <c r="C323" t="n">
-        <v>5.207094281189084</v>
+        <v>5.210423283965082</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8383204505718389</v>
+        <v>0.8369877519067925</v>
       </c>
       <c r="E323" t="n">
-        <v>4.169804839820901</v>
+        <v>4.171982430236088</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14331,7 +14331,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.93511</v>
+        <v>3.93272</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14350,16 +14350,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.53284820641047</v>
+        <v>7.537648170077049</v>
       </c>
       <c r="C324" t="n">
-        <v>7.003507480409454</v>
+        <v>6.994318239842823</v>
       </c>
       <c r="D324" t="n">
-        <v>3.823169999398357</v>
+        <v>3.824966203956781</v>
       </c>
       <c r="E324" t="n">
-        <v>2.187558277838741</v>
+        <v>2.189378793936991</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14374,10 +14374,10 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.68709</v>
+        <v>3.68735</v>
       </c>
       <c r="K324" t="n">
-        <v>3.46024</v>
+        <v>3.45127</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14393,16 +14393,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.076104730675058</v>
+        <v>6.077428659383544</v>
       </c>
       <c r="C325" t="n">
-        <v>5.608153746293887</v>
+        <v>5.60425117356147</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1563772586133938</v>
+        <v>0.1571476996986343</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892486781843306</v>
+        <v>2.892633545482748</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14417,7 +14417,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.30324</v>
+        <v>3.30365</v>
       </c>
       <c r="K325" t="n">
         <v>3.22274</v>
@@ -14436,16 +14436,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.855039749993973</v>
+        <v>5.854969678039268</v>
       </c>
       <c r="C326" t="n">
-        <v>4.983576960166158</v>
+        <v>4.984020264298961</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7921929310791054</v>
+        <v>0.7928695940304875</v>
       </c>
       <c r="E326" t="n">
-        <v>4.474198049111999</v>
+        <v>4.470868138703077</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14460,7 +14460,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86395</v>
+        <v>2.86421</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14479,16 +14479,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.916634867190499</v>
+        <v>9.916815172012639</v>
       </c>
       <c r="C327" t="n">
-        <v>9.271490908973679</v>
+        <v>9.271172289205797</v>
       </c>
       <c r="D327" t="n">
-        <v>2.691234769073936</v>
+        <v>2.691940082080446</v>
       </c>
       <c r="E327" t="n">
-        <v>7.798856385208341</v>
+        <v>7.795424121030936</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14503,10 +14503,10 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05623</v>
+        <v>2.05652</v>
       </c>
       <c r="K327" t="n">
-        <v>2.64673</v>
+        <v>2.63791</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14522,16 +14522,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41527252165593</v>
+        <v>10.41583027803883</v>
       </c>
       <c r="C328" t="n">
-        <v>9.05424600970488</v>
+        <v>9.054822735522938</v>
       </c>
       <c r="D328" t="n">
-        <v>3.14408055269213</v>
+        <v>3.144581916910494</v>
       </c>
       <c r="E328" t="n">
-        <v>7.360744253916307</v>
+        <v>7.358269334768885</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14546,7 +14546,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82304</v>
+        <v>1.82336</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14565,16 +14565,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.002121928070879</v>
+        <v>4.002915736085866</v>
       </c>
       <c r="C329" t="n">
-        <v>3.010953462551091</v>
+        <v>3.011478636301446</v>
       </c>
       <c r="D329" t="n">
-        <v>2.837263624024722</v>
+        <v>2.837327572664994</v>
       </c>
       <c r="E329" t="n">
-        <v>3.597097177237329</v>
+        <v>3.595377905760699</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14589,10 +14589,10 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.15832</v>
+        <v>1.15874</v>
       </c>
       <c r="K329" t="n">
-        <v>2.05948</v>
+        <v>2.05076</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14608,16 +14608,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.273420223920079</v>
+        <v>6.273280616022237</v>
       </c>
       <c r="C330" t="n">
-        <v>5.545457903266682</v>
+        <v>5.546430152401305</v>
       </c>
       <c r="D330" t="n">
-        <v>1.312273500675532</v>
+        <v>1.312178171523914</v>
       </c>
       <c r="E330" t="n">
-        <v>5.629501991082808</v>
+        <v>5.628383318639862</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14632,7 +14632,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15264</v>
+        <v>1.15309</v>
       </c>
       <c r="K330" t="n">
         <v>1.53231</v>
@@ -14651,16 +14651,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.980956679410476</v>
+        <v>5.980896209812481</v>
       </c>
       <c r="C331" t="n">
-        <v>7.42530406681301</v>
+        <v>7.426262108607196</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.071865682251916</v>
+        <v>-1.072232535238149</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981093333470077</v>
+        <v>4.981442962538485</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14675,7 +14675,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.72404</v>
+        <v>0.72428</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14694,16 +14694,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.252937942369184</v>
+        <v>4.252654482153928</v>
       </c>
       <c r="C332" t="n">
-        <v>4.011192518133977</v>
+        <v>4.012586608928848</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.621079774974354</v>
+        <v>-1.621655467496796</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511885205010402</v>
+        <v>4.512034174940216</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14718,10 +14718,10 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13585</v>
+        <v>1.13596</v>
       </c>
       <c r="K332" t="n">
-        <v>0.94835</v>
+        <v>0.95682</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14737,16 +14737,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.826669114195069</v>
+        <v>3.825407961648764</v>
       </c>
       <c r="C333" t="n">
-        <v>3.770353410187033</v>
+        <v>3.772285754869964</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.157520180689366</v>
+        <v>-3.158220126836675</v>
       </c>
       <c r="E333" t="n">
-        <v>4.435689608851456</v>
+        <v>4.43559720351947</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14761,10 +14761,10 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.19176</v>
+        <v>1.19219</v>
       </c>
       <c r="K333" t="n">
-        <v>0.54866</v>
+        <v>0.54018</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14780,16 +14780,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.909809007942465</v>
+        <v>2.906540538136748</v>
       </c>
       <c r="C334" t="n">
-        <v>4.916761875932263</v>
+        <v>4.921163165443709</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.596966748340245</v>
+        <v>-1.599191963386126</v>
       </c>
       <c r="E334" t="n">
-        <v>5.110456393327523</v>
+        <v>5.112953084893501</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14804,7 +14804,7 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05854</v>
+        <v>1.05794</v>
       </c>
       <c r="K334" t="n">
         <v>-0.05882</v>
@@ -14823,16 +14823,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.707591046071368</v>
+        <v>3.703972466781558</v>
       </c>
       <c r="C335" t="n">
-        <v>1.787361094299178</v>
+        <v>1.79281352475662</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.588982707762622</v>
+        <v>-2.591160717022412</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832399082481452</v>
+        <v>3.833862552785328</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14847,7 +14847,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.74048</v>
+        <v>1.73723</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14866,16 +14866,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.717355354321761</v>
+        <v>3.723558437886698</v>
       </c>
       <c r="C336" t="n">
-        <v>3.878580264747566</v>
+        <v>3.863691346764586</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.341147503474262</v>
+        <v>-3.338404904162029</v>
       </c>
       <c r="E336" t="n">
-        <v>3.492747996437973</v>
+        <v>3.490905640757491</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14890,10 +14890,10 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.43111</v>
+        <v>-2.431</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.29338</v>
+        <v>-0.285</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14909,16 +14909,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.991213026347172</v>
+        <v>1.993092881985126</v>
       </c>
       <c r="C337" t="n">
-        <v>1.406628680699473</v>
+        <v>1.400085676157103</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.141292466286627</v>
+        <v>-3.140048076028057</v>
       </c>
       <c r="E337" t="n">
-        <v>3.632314262773928</v>
+        <v>3.629676879858912</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14933,7 +14933,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74591</v>
+        <v>2.74639</v>
       </c>
       <c r="K337" t="n">
         <v>-0.32644</v>
@@ -14952,16 +14952,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.292728556475866</v>
+        <v>3.292548216096258</v>
       </c>
       <c r="C338" t="n">
-        <v>2.205717340324154</v>
+        <v>2.206970323087787</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.365763768115781</v>
+        <v>-2.364579912264286</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875748386403253</v>
+        <v>1.875273428151503</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14976,7 +14976,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.53445</v>
+        <v>-0.53448</v>
       </c>
       <c r="K338" t="n">
         <v>-0.36041</v>
@@ -14995,16 +14995,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6638893592867623</v>
+        <v>0.6633177768283094</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.193440293407145</v>
+        <v>-2.192234717572195</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.149489736240007</v>
+        <v>-2.148381568819957</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6041222662902967</v>
+        <v>-0.603085014146465</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15019,7 +15019,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09644999999999999</v>
+        <v>-0.09538000000000001</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15038,16 +15038,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.590804488102206</v>
+        <v>3.590619821141483</v>
       </c>
       <c r="C340" t="n">
-        <v>0.441568173415896</v>
+        <v>0.443995546326148</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.725641578788351</v>
+        <v>-2.725039901989845</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.147305080712302</v>
+        <v>-1.14634254007232</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15062,7 +15062,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.53128</v>
+        <v>-0.5298</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15081,16 +15081,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.7899001827854</v>
+        <v>4.791076972711572</v>
       </c>
       <c r="C341" t="n">
-        <v>1.326249366479848</v>
+        <v>1.327364983590518</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.052421289763574</v>
+        <v>-3.052493784463195</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702169717902913</v>
+        <v>1.702223438164374</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15105,7 +15105,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.22873</v>
+        <v>-1.2286</v>
       </c>
       <c r="K341" t="n">
         <v>0.40191</v>
@@ -15124,16 +15124,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.675370630167498</v>
+        <v>5.675197612433514</v>
       </c>
       <c r="C342" t="n">
-        <v>2.740708584144858</v>
+        <v>2.74278502805958</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7358097197996849</v>
+        <v>-0.7359936492112307</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.129858419290263</v>
+        <v>-0.1288867859752463</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15148,7 +15148,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44737</v>
+        <v>-1.44703</v>
       </c>
       <c r="K342" t="n">
         <v>0.6959</v>
@@ -15167,16 +15167,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.833347734579153</v>
+        <v>5.833047027059246</v>
       </c>
       <c r="C343" t="n">
-        <v>1.501998643147884</v>
+        <v>1.504300528068891</v>
       </c>
       <c r="D343" t="n">
-        <v>2.370704340660446</v>
+        <v>2.370154051051321</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6819458485371577</v>
+        <v>0.6831017748200496</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15191,7 +15191,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09735</v>
+        <v>-1.09714</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15210,16 +15210,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.955584219633137</v>
+        <v>5.955323343851515</v>
       </c>
       <c r="C344" t="n">
-        <v>3.891012980110053</v>
+        <v>3.893506573478422</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9068888306149825</v>
+        <v>0.9060527112732641</v>
       </c>
       <c r="E344" t="n">
-        <v>2.712770463128944</v>
+        <v>2.71363390478887</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15234,10 +15234,10 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.75537</v>
+        <v>-0.75504</v>
       </c>
       <c r="K344" t="n">
-        <v>1.21624</v>
+        <v>1.21614</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15253,16 +15253,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26830585583041</v>
+        <v>10.26659078567886</v>
       </c>
       <c r="C345" t="n">
-        <v>7.551274078968584</v>
+        <v>7.55455530243907</v>
       </c>
       <c r="D345" t="n">
-        <v>7.742113413812213</v>
+        <v>7.740984769976977</v>
       </c>
       <c r="E345" t="n">
-        <v>2.754999513941048</v>
+        <v>2.755084098846816</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15277,10 +15277,10 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.70168</v>
+        <v>-0.7005</v>
       </c>
       <c r="K345" t="n">
-        <v>1.66219</v>
+        <v>1.67058</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15296,16 +15296,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.154794311888142</v>
+        <v>2.150774314412018</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4026203272377682</v>
+        <v>-0.3954263203203134</v>
       </c>
       <c r="D346" t="n">
-        <v>1.671961082064066</v>
+        <v>1.668064470904307</v>
       </c>
       <c r="E346" t="n">
-        <v>2.254791288810232</v>
+        <v>2.258028224129904</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15320,7 +15320,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.12797</v>
+        <v>-0.13013</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15339,16 +15339,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.153576622093459</v>
+        <v>5.148673845296492</v>
       </c>
       <c r="C347" t="n">
-        <v>3.130635406483639</v>
+        <v>3.140020784124942</v>
       </c>
       <c r="D347" t="n">
-        <v>4.042137955409042</v>
+        <v>4.038146997584735</v>
       </c>
       <c r="E347" t="n">
-        <v>2.133091278589716</v>
+        <v>2.138983335260414</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15363,7 +15363,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.01446</v>
+        <v>-1.01931</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15382,16 +15382,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.555983695348042</v>
+        <v>3.564977224024757</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.6266508040841279</v>
+        <v>-0.651297271513307</v>
       </c>
       <c r="D348" t="n">
-        <v>4.247368744673352</v>
+        <v>4.252432373094073</v>
       </c>
       <c r="E348" t="n">
-        <v>3.130994907114748</v>
+        <v>3.124660704508875</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15406,10 +15406,10 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.98854</v>
+        <v>2.98953</v>
       </c>
       <c r="K348" t="n">
-        <v>2.53047</v>
+        <v>2.52186</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15425,16 +15425,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.712832365634469</v>
+        <v>6.716395979144019</v>
       </c>
       <c r="C349" t="n">
-        <v>6.144847590650748</v>
+        <v>6.132418487760538</v>
       </c>
       <c r="D349" t="n">
-        <v>6.310587745295893</v>
+        <v>6.31296140340325</v>
       </c>
       <c r="E349" t="n">
-        <v>6.032114776682218</v>
+        <v>6.028787457515983</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15449,7 +15449,7 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.39419</v>
+        <v>-1.39323</v>
       </c>
       <c r="K349" t="n">
         <v>2.79644</v>
@@ -15468,16 +15468,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.376802255152047</v>
+        <v>5.37712030615578</v>
       </c>
       <c r="C350" t="n">
-        <v>3.214114320747186</v>
+        <v>3.215166680155868</v>
       </c>
       <c r="D350" t="n">
-        <v>6.181032512370188</v>
+        <v>6.183234028769236</v>
       </c>
       <c r="E350" t="n">
-        <v>6.714474739190224</v>
+        <v>6.715042785558123</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15492,7 +15492,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.55869</v>
+        <v>2.55891</v>
       </c>
       <c r="K350" t="n">
         <v>3.17127</v>
@@ -15511,16 +15511,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.026140916321499</v>
+        <v>6.025881695023294</v>
       </c>
       <c r="C351" t="n">
-        <v>4.302099760790679</v>
+        <v>4.302728417201873</v>
       </c>
       <c r="D351" t="n">
-        <v>1.672072193293306</v>
+        <v>1.67389903059989</v>
       </c>
       <c r="E351" t="n">
-        <v>8.081014837646471</v>
+        <v>8.080534669008266</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15535,10 +15535,10 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.77768</v>
+        <v>1.77915</v>
       </c>
       <c r="K351" t="n">
-        <v>2.90815</v>
+        <v>2.91653</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15554,16 +15554,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26472279422453</v>
+        <v>-53.26500601512263</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.30582797114101</v>
+        <v>-49.30428639421412</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.33240913416352</v>
+        <v>-44.33170543451237</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.87722829099457</v>
+        <v>-1.879076594088713</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15578,7 +15578,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.56104</v>
+        <v>1.563</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15597,16 +15597,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40227129976248</v>
+        <v>-99.40226336867063</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11754011816366</v>
+        <v>-98.11751099598803</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69243400132918</v>
+        <v>-88.69240566802783</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50749144713836</v>
+        <v>-52.50816779483103</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15621,7 +15621,7 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.28801</v>
+        <v>-49.2874</v>
       </c>
       <c r="K353" t="n">
         <v>-38.87916</v>
@@ -15640,16 +15640,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.804188105946</v>
+        <v>-98.80419835319115</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98523689595045</v>
+        <v>-95.98508662280753</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16183977649882</v>
+        <v>-82.16187156344282</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70194521934952</v>
+        <v>-50.7022057696763</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15664,7 +15664,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.49959</v>
+        <v>-69.4986</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15683,16 +15683,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13268119192371</v>
+        <v>-98.13270030323417</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.35223505167092</v>
+        <v>-94.35198040598169</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41235866622122</v>
+        <v>-81.41248703177605</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98602008543648</v>
+        <v>-42.98588359988828</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15707,7 +15707,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.09114</v>
+        <v>-70.09050999999999</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15726,16 +15726,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74179040478023</v>
+        <v>-97.74181767164347</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62910002098272</v>
+        <v>-93.62874179485657</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64092595377102</v>
+        <v>-75.64127402101019</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11230936221288</v>
+        <v>-43.11068925099725</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15750,10 +15750,10 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73712999999999</v>
+        <v>-74.73656</v>
       </c>
       <c r="K356" t="n">
-        <v>-30.14005</v>
+        <v>-30.14584</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15769,16 +15769,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46143843275581</v>
+        <v>-97.46153281144258</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99143960237021</v>
+        <v>-90.99077289678384</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.19054326846633</v>
+        <v>-74.19111487501441</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65830274436793</v>
+        <v>-45.65723640903332</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15793,10 +15793,10 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.87692</v>
+        <v>-74.87519</v>
       </c>
       <c r="K357" t="n">
-        <v>-25.53262</v>
+        <v>-25.53877</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15812,16 +15812,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43041878021316</v>
+        <v>-97.43053592994563</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90203431166331</v>
+        <v>-89.90083800460579</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.96446406787328</v>
+        <v>-74.96592074306385</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17109091356239</v>
+        <v>-40.1678490103718</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15836,7 +15836,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.50669000000001</v>
+        <v>-76.51188</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15855,16 +15855,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07932079533042</v>
+        <v>-90.07988089365546</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.37245532908499</v>
+        <v>-81.37010146957549</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.9754547965089</v>
+        <v>-74.97695924187204</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.3491069586332</v>
+        <v>-31.34405166701689</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15879,7 +15879,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.62361</v>
+        <v>-66.63415999999999</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15898,16 +15898,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76889976772023</v>
+        <v>-76.76606622717814</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.56938573496045</v>
+        <v>-65.58312468143366</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85610207279434</v>
+        <v>-71.85387471523372</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.58103205836592</v>
+        <v>-12.59340514612708</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15922,7 +15922,7 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.85495</v>
+        <v>-56.85376</v>
       </c>
       <c r="K360" t="n">
         <v>-20.39193</v>
@@ -15941,16 +15941,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.82118804983253</v>
+        <v>-74.82004103124542</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.34700286822289</v>
+        <v>-66.35263017179476</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13350907334875</v>
+        <v>-70.13263492840348</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80258393849409</v>
+        <v>-16.80569329592696</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>
@@ -15965,7 +15965,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.24831</v>
+        <v>-53.24671</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,74 +421,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Visitor Arrivals</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Visitor Days</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Mean Daily Rate</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Revenue per Available Room</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Leisure Emp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Unemp Rate</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>LFP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Accommodation Emp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Econ Activity Index</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Mandatory Quarantine</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>33239</v>
       </c>
       <c r="B2" t="n">
@@ -543,7 +531,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>33270</v>
       </c>
       <c r="B3" t="n">
@@ -586,7 +574,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>33298</v>
       </c>
       <c r="B4" t="n">
@@ -629,7 +617,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>33329</v>
       </c>
       <c r="B5" t="n">
@@ -672,7 +660,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>33359</v>
       </c>
       <c r="B6" t="n">
@@ -715,7 +703,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>33390</v>
       </c>
       <c r="B7" t="n">
@@ -758,7 +746,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>33420</v>
       </c>
       <c r="B8" t="n">
@@ -801,7 +789,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>33451</v>
       </c>
       <c r="B9" t="n">
@@ -844,7 +832,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>33482</v>
       </c>
       <c r="B10" t="n">
@@ -887,7 +875,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>33512</v>
       </c>
       <c r="B11" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>33543</v>
       </c>
       <c r="B12" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>33573</v>
       </c>
       <c r="B13" t="n">
@@ -1016,7 +1004,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>33604</v>
       </c>
       <c r="B14" t="n">
@@ -1059,7 +1047,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>33635</v>
       </c>
       <c r="B15" t="n">
@@ -1102,7 +1090,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>33664</v>
       </c>
       <c r="B16" t="n">
@@ -1145,7 +1133,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>33695</v>
       </c>
       <c r="B17" t="n">
@@ -1188,7 +1176,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>33725</v>
       </c>
       <c r="B18" t="n">
@@ -1231,7 +1219,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>33756</v>
       </c>
       <c r="B19" t="n">
@@ -1274,7 +1262,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>33786</v>
       </c>
       <c r="B20" t="n">
@@ -1317,7 +1305,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>33817</v>
       </c>
       <c r="B21" t="n">
@@ -1360,7 +1348,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>33848</v>
       </c>
       <c r="B22" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>33878</v>
       </c>
       <c r="B23" t="n">
@@ -1446,7 +1434,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>33909</v>
       </c>
       <c r="B24" t="n">
@@ -1489,7 +1477,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>33939</v>
       </c>
       <c r="B25" t="n">
@@ -1532,7 +1520,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>33970</v>
       </c>
       <c r="B26" t="n">
@@ -1575,7 +1563,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>34001</v>
       </c>
       <c r="B27" t="n">
@@ -1618,7 +1606,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>34029</v>
       </c>
       <c r="B28" t="n">
@@ -1661,7 +1649,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>34060</v>
       </c>
       <c r="B29" t="n">
@@ -1704,7 +1692,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>34090</v>
       </c>
       <c r="B30" t="n">
@@ -1747,7 +1735,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>34121</v>
       </c>
       <c r="B31" t="n">
@@ -1790,7 +1778,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>34151</v>
       </c>
       <c r="B32" t="n">
@@ -1833,7 +1821,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>34182</v>
       </c>
       <c r="B33" t="n">
@@ -1876,7 +1864,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>34213</v>
       </c>
       <c r="B34" t="n">
@@ -1919,7 +1907,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>34243</v>
       </c>
       <c r="B35" t="n">
@@ -1962,7 +1950,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>34274</v>
       </c>
       <c r="B36" t="n">
@@ -2005,7 +1993,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>34304</v>
       </c>
       <c r="B37" t="n">
@@ -2048,7 +2036,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>34335</v>
       </c>
       <c r="B38" t="n">
@@ -2091,7 +2079,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>34366</v>
       </c>
       <c r="B39" t="n">
@@ -2134,7 +2122,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>34394</v>
       </c>
       <c r="B40" t="n">
@@ -2177,7 +2165,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>34425</v>
       </c>
       <c r="B41" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>34455</v>
       </c>
       <c r="B42" t="n">
@@ -2263,7 +2251,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>34486</v>
       </c>
       <c r="B43" t="n">
@@ -2306,7 +2294,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>34516</v>
       </c>
       <c r="B44" t="n">
@@ -2349,7 +2337,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>34547</v>
       </c>
       <c r="B45" t="n">
@@ -2392,7 +2380,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>34578</v>
       </c>
       <c r="B46" t="n">
@@ -2435,7 +2423,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>34608</v>
       </c>
       <c r="B47" t="n">
@@ -2478,7 +2466,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>34639</v>
       </c>
       <c r="B48" t="n">
@@ -2521,7 +2509,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>34669</v>
       </c>
       <c r="B49" t="n">
@@ -2564,7 +2552,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>34700</v>
       </c>
       <c r="B50" t="n">
@@ -2607,7 +2595,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>34731</v>
       </c>
       <c r="B51" t="n">
@@ -2650,7 +2638,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>34759</v>
       </c>
       <c r="B52" t="n">
@@ -2693,7 +2681,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>34790</v>
       </c>
       <c r="B53" t="n">
@@ -2736,7 +2724,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>34820</v>
       </c>
       <c r="B54" t="n">
@@ -2779,7 +2767,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>34851</v>
       </c>
       <c r="B55" t="n">
@@ -2822,7 +2810,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>34881</v>
       </c>
       <c r="B56" t="n">
@@ -2865,7 +2853,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>34912</v>
       </c>
       <c r="B57" t="n">
@@ -2908,7 +2896,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>34943</v>
       </c>
       <c r="B58" t="n">
@@ -2951,7 +2939,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>34973</v>
       </c>
       <c r="B59" t="n">
@@ -2994,7 +2982,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>35004</v>
       </c>
       <c r="B60" t="n">
@@ -3037,7 +3025,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>35034</v>
       </c>
       <c r="B61" t="n">
@@ -3080,7 +3068,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>35065</v>
       </c>
       <c r="B62" t="n">
@@ -3123,7 +3111,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>35096</v>
       </c>
       <c r="B63" t="n">
@@ -3166,7 +3154,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>35125</v>
       </c>
       <c r="B64" t="n">
@@ -3209,7 +3197,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>35156</v>
       </c>
       <c r="B65" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>35186</v>
       </c>
       <c r="B66" t="n">
@@ -3295,7 +3283,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>35217</v>
       </c>
       <c r="B67" t="n">
@@ -3338,7 +3326,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>35247</v>
       </c>
       <c r="B68" t="n">
@@ -3381,7 +3369,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>35278</v>
       </c>
       <c r="B69" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>35309</v>
       </c>
       <c r="B70" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>35339</v>
       </c>
       <c r="B71" t="n">
@@ -3510,7 +3498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>35370</v>
       </c>
       <c r="B72" t="n">
@@ -3553,7 +3541,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>35400</v>
       </c>
       <c r="B73" t="n">
@@ -3596,7 +3584,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>35431</v>
       </c>
       <c r="B74" t="n">
@@ -3639,7 +3627,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>35462</v>
       </c>
       <c r="B75" t="n">
@@ -3682,7 +3670,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>35490</v>
       </c>
       <c r="B76" t="n">
@@ -3725,7 +3713,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>35521</v>
       </c>
       <c r="B77" t="n">
@@ -3768,7 +3756,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>35551</v>
       </c>
       <c r="B78" t="n">
@@ -3811,7 +3799,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>35582</v>
       </c>
       <c r="B79" t="n">
@@ -3854,7 +3842,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>35612</v>
       </c>
       <c r="B80" t="n">
@@ -3897,7 +3885,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>35643</v>
       </c>
       <c r="B81" t="n">
@@ -3940,7 +3928,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>35674</v>
       </c>
       <c r="B82" t="n">
@@ -3983,7 +3971,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>35704</v>
       </c>
       <c r="B83" t="n">
@@ -4026,7 +4014,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>35735</v>
       </c>
       <c r="B84" t="n">
@@ -4069,7 +4057,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>35765</v>
       </c>
       <c r="B85" t="n">
@@ -4112,7 +4100,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>35796</v>
       </c>
       <c r="B86" t="n">
@@ -4155,7 +4143,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>35827</v>
       </c>
       <c r="B87" t="n">
@@ -4198,7 +4186,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>35855</v>
       </c>
       <c r="B88" t="n">
@@ -4241,7 +4229,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>35886</v>
       </c>
       <c r="B89" t="n">
@@ -4284,7 +4272,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>35916</v>
       </c>
       <c r="B90" t="n">
@@ -4327,7 +4315,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>35947</v>
       </c>
       <c r="B91" t="n">
@@ -4370,7 +4358,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>35977</v>
       </c>
       <c r="B92" t="n">
@@ -4413,7 +4401,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>36008</v>
       </c>
       <c r="B93" t="n">
@@ -4456,7 +4444,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>36039</v>
       </c>
       <c r="B94" t="n">
@@ -4499,7 +4487,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>36069</v>
       </c>
       <c r="B95" t="n">
@@ -4542,7 +4530,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>36100</v>
       </c>
       <c r="B96" t="n">
@@ -4585,7 +4573,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>36130</v>
       </c>
       <c r="B97" t="n">
@@ -4628,7 +4616,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>36161</v>
       </c>
       <c r="B98" t="n">
@@ -4671,7 +4659,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>36192</v>
       </c>
       <c r="B99" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>36220</v>
       </c>
       <c r="B100" t="n">
@@ -4757,7 +4745,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>36251</v>
       </c>
       <c r="B101" t="n">
@@ -4800,7 +4788,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>36281</v>
       </c>
       <c r="B102" t="n">
@@ -4843,7 +4831,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>36312</v>
       </c>
       <c r="B103" t="n">
@@ -4886,7 +4874,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>36342</v>
       </c>
       <c r="B104" t="n">
@@ -4929,7 +4917,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>36373</v>
       </c>
       <c r="B105" t="n">
@@ -4972,7 +4960,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>36404</v>
       </c>
       <c r="B106" t="n">
@@ -5015,7 +5003,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>36434</v>
       </c>
       <c r="B107" t="n">
@@ -5058,7 +5046,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>36465</v>
       </c>
       <c r="B108" t="n">
@@ -5101,7 +5089,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>36495</v>
       </c>
       <c r="B109" t="n">
@@ -5144,7 +5132,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>36526</v>
       </c>
       <c r="B110" t="n">
@@ -5187,7 +5175,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>36557</v>
       </c>
       <c r="B111" t="n">
@@ -5230,7 +5218,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>36586</v>
       </c>
       <c r="B112" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>36617</v>
       </c>
       <c r="B113" t="n">
@@ -5316,7 +5304,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>36647</v>
       </c>
       <c r="B114" t="n">
@@ -5359,7 +5347,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>36678</v>
       </c>
       <c r="B115" t="n">
@@ -5402,7 +5390,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>36708</v>
       </c>
       <c r="B116" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>36739</v>
       </c>
       <c r="B117" t="n">
@@ -5488,7 +5476,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>36770</v>
       </c>
       <c r="B118" t="n">
@@ -5531,7 +5519,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>36800</v>
       </c>
       <c r="B119" t="n">
@@ -5574,7 +5562,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>36831</v>
       </c>
       <c r="B120" t="n">
@@ -5617,7 +5605,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>36861</v>
       </c>
       <c r="B121" t="n">
@@ -5660,7 +5648,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>36892</v>
       </c>
       <c r="B122" t="n">
@@ -5703,7 +5691,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>36923</v>
       </c>
       <c r="B123" t="n">
@@ -5746,7 +5734,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>36951</v>
       </c>
       <c r="B124" t="n">
@@ -5789,7 +5777,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>36982</v>
       </c>
       <c r="B125" t="n">
@@ -5832,7 +5820,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>37012</v>
       </c>
       <c r="B126" t="n">
@@ -5875,7 +5863,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>37043</v>
       </c>
       <c r="B127" t="n">
@@ -5918,7 +5906,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>37073</v>
       </c>
       <c r="B128" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>37104</v>
       </c>
       <c r="B129" t="n">
@@ -6004,7 +5992,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>37135</v>
       </c>
       <c r="B130" t="n">
@@ -6047,7 +6035,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>37165</v>
       </c>
       <c r="B131" t="n">
@@ -6090,7 +6078,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>37196</v>
       </c>
       <c r="B132" t="n">
@@ -6133,7 +6121,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>37226</v>
       </c>
       <c r="B133" t="n">
@@ -6176,7 +6164,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>37257</v>
       </c>
       <c r="B134" t="n">
@@ -6219,7 +6207,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>37288</v>
       </c>
       <c r="B135" t="n">
@@ -6262,7 +6250,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>37316</v>
       </c>
       <c r="B136" t="n">
@@ -6305,7 +6293,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>37347</v>
       </c>
       <c r="B137" t="n">
@@ -6348,7 +6336,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>37377</v>
       </c>
       <c r="B138" t="n">
@@ -6391,7 +6379,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>37408</v>
       </c>
       <c r="B139" t="n">
@@ -6434,7 +6422,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>37438</v>
       </c>
       <c r="B140" t="n">
@@ -6477,7 +6465,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>37469</v>
       </c>
       <c r="B141" t="n">
@@ -6520,7 +6508,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>37500</v>
       </c>
       <c r="B142" t="n">
@@ -6563,7 +6551,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>37530</v>
       </c>
       <c r="B143" t="n">
@@ -6606,7 +6594,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>37561</v>
       </c>
       <c r="B144" t="n">
@@ -6649,7 +6637,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>37591</v>
       </c>
       <c r="B145" t="n">
@@ -6692,7 +6680,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>37622</v>
       </c>
       <c r="B146" t="n">
@@ -6735,7 +6723,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>37653</v>
       </c>
       <c r="B147" t="n">
@@ -6778,7 +6766,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>37681</v>
       </c>
       <c r="B148" t="n">
@@ -6821,7 +6809,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>37712</v>
       </c>
       <c r="B149" t="n">
@@ -6864,7 +6852,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>37742</v>
       </c>
       <c r="B150" t="n">
@@ -6907,7 +6895,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>37773</v>
       </c>
       <c r="B151" t="n">
@@ -6950,7 +6938,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>37803</v>
       </c>
       <c r="B152" t="n">
@@ -6993,7 +6981,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>37834</v>
       </c>
       <c r="B153" t="n">
@@ -7036,7 +7024,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>37865</v>
       </c>
       <c r="B154" t="n">
@@ -7079,7 +7067,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>37895</v>
       </c>
       <c r="B155" t="n">
@@ -7122,7 +7110,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>37926</v>
       </c>
       <c r="B156" t="n">
@@ -7165,7 +7153,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>37956</v>
       </c>
       <c r="B157" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>37987</v>
       </c>
       <c r="B158" t="n">
@@ -7251,7 +7239,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>38018</v>
       </c>
       <c r="B159" t="n">
@@ -7294,7 +7282,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>38047</v>
       </c>
       <c r="B160" t="n">
@@ -7337,7 +7325,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>38078</v>
       </c>
       <c r="B161" t="n">
@@ -7380,7 +7368,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>38108</v>
       </c>
       <c r="B162" t="n">
@@ -7423,7 +7411,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>38139</v>
       </c>
       <c r="B163" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>38169</v>
       </c>
       <c r="B164" t="n">
@@ -7509,7 +7497,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>38200</v>
       </c>
       <c r="B165" t="n">
@@ -7552,7 +7540,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>38231</v>
       </c>
       <c r="B166" t="n">
@@ -7595,7 +7583,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>38261</v>
       </c>
       <c r="B167" t="n">
@@ -7638,7 +7626,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>38292</v>
       </c>
       <c r="B168" t="n">
@@ -7681,7 +7669,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>38322</v>
       </c>
       <c r="B169" t="n">
@@ -7724,7 +7712,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B170" t="n">
@@ -7767,7 +7755,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B171" t="n">
@@ -7810,7 +7798,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B172" t="n">
@@ -7853,7 +7841,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B173" t="n">
@@ -7896,7 +7884,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B174" t="n">
@@ -7939,7 +7927,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B175" t="n">
@@ -7982,7 +7970,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B176" t="n">
@@ -8025,7 +8013,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B177" t="n">
@@ -8068,7 +8056,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B178" t="n">
@@ -8111,7 +8099,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B179" t="n">
@@ -8154,7 +8142,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B180" t="n">
@@ -8197,7 +8185,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B181" t="n">
@@ -8240,7 +8228,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B182" t="n">
@@ -8283,7 +8271,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B183" t="n">
@@ -8326,7 +8314,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B184" t="n">
@@ -8369,7 +8357,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B185" t="n">
@@ -8412,7 +8400,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B186" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B187" t="n">
@@ -8498,7 +8486,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B188" t="n">
@@ -8541,7 +8529,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B189" t="n">
@@ -8584,7 +8572,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B190" t="n">
@@ -8627,7 +8615,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B191" t="n">
@@ -8670,7 +8658,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B192" t="n">
@@ -8713,7 +8701,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B193" t="n">
@@ -8756,7 +8744,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B194" t="n">
@@ -8799,7 +8787,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B195" t="n">
@@ -8842,7 +8830,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B196" t="n">
@@ -8885,7 +8873,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B197" t="n">
@@ -8928,7 +8916,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B198" t="n">
@@ -8971,7 +8959,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B199" t="n">
@@ -9014,7 +9002,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B200" t="n">
@@ -9057,7 +9045,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B201" t="n">
@@ -9100,7 +9088,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B202" t="n">
@@ -9143,7 +9131,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B203" t="n">
@@ -9186,7 +9174,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B204" t="n">
@@ -9229,7 +9217,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B205" t="n">
@@ -9272,7 +9260,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B206" t="n">
@@ -9315,7 +9303,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B207" t="n">
@@ -9358,7 +9346,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B208" t="n">
@@ -9401,7 +9389,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B209" t="n">
@@ -9444,7 +9432,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B210" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B211" t="n">
@@ -9530,7 +9518,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B212" t="n">
@@ -9573,7 +9561,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B213" t="n">
@@ -9616,7 +9604,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B214" t="n">
@@ -9659,7 +9647,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B215" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B216" t="n">
@@ -9745,7 +9733,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B217" t="n">
@@ -9788,7 +9776,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B218" t="n">
@@ -9831,7 +9819,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B219" t="n">
@@ -9874,7 +9862,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B220" t="n">
@@ -9917,7 +9905,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B221" t="n">
@@ -9960,7 +9948,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B222" t="n">
@@ -10003,7 +9991,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B223" t="n">
@@ -10046,7 +10034,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B224" t="n">
@@ -10089,7 +10077,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B225" t="n">
@@ -10132,7 +10120,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B226" t="n">
@@ -10175,7 +10163,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B227" t="n">
@@ -10218,7 +10206,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B228" t="n">
@@ -10261,7 +10249,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B229" t="n">
@@ -10304,7 +10292,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B230" t="n">
@@ -10347,7 +10335,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B231" t="n">
@@ -10390,7 +10378,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B232" t="n">
@@ -10433,7 +10421,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B233" t="n">
@@ -10476,7 +10464,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B234" t="n">
@@ -10519,7 +10507,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B235" t="n">
@@ -10562,7 +10550,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B236" t="n">
@@ -10605,7 +10593,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B237" t="n">
@@ -10648,7 +10636,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B238" t="n">
@@ -10691,7 +10679,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B239" t="n">
@@ -10734,7 +10722,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B240" t="n">
@@ -10777,7 +10765,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B241" t="n">
@@ -10820,7 +10808,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B242" t="n">
@@ -10863,7 +10851,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B243" t="n">
@@ -10906,7 +10894,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B244" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B245" t="n">
@@ -10992,7 +10980,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B246" t="n">
@@ -11035,7 +11023,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B247" t="n">
@@ -11078,7 +11066,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B248" t="n">
@@ -11121,7 +11109,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B249" t="n">
@@ -11164,7 +11152,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B250" t="n">
@@ -11207,7 +11195,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B251" t="n">
@@ -11250,7 +11238,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B252" t="n">
@@ -11293,7 +11281,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B253" t="n">
@@ -11336,7 +11324,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B254" t="n">
@@ -11379,7 +11367,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B255" t="n">
@@ -11422,7 +11410,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B256" t="n">
@@ -11465,7 +11453,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B257" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B258" t="n">
@@ -11551,7 +11539,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B259" t="n">
@@ -11594,7 +11582,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B260" t="n">
@@ -11637,7 +11625,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B261" t="n">
@@ -11680,7 +11668,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B262" t="n">
@@ -11723,7 +11711,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B263" t="n">
@@ -11766,7 +11754,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B264" t="n">
@@ -11809,7 +11797,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B265" t="n">
@@ -11852,7 +11840,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B266" t="n">
@@ -11895,7 +11883,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B267" t="n">
@@ -11938,7 +11926,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B268" t="n">
@@ -11981,7 +11969,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B269" t="n">
@@ -12024,7 +12012,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B270" t="n">
@@ -12067,7 +12055,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B271" t="n">
@@ -12110,7 +12098,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B272" t="n">
@@ -12153,7 +12141,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B273" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B274" t="n">
@@ -12239,7 +12227,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B275" t="n">
@@ -12282,7 +12270,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B276" t="n">
@@ -12325,7 +12313,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B277" t="n">
@@ -12368,7 +12356,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B278" t="n">
@@ -12411,7 +12399,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B279" t="n">
@@ -12454,7 +12442,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B280" t="n">
@@ -12497,7 +12485,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B281" t="n">
@@ -12540,7 +12528,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B282" t="n">
@@ -12583,7 +12571,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B283" t="n">
@@ -12626,7 +12614,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B284" t="n">
@@ -12669,7 +12657,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B285" t="n">
@@ -12712,7 +12700,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B286" t="n">
@@ -12755,7 +12743,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B287" t="n">
@@ -12798,7 +12786,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B288" t="n">
@@ -12841,7 +12829,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B289" t="n">
@@ -12884,7 +12872,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B290" t="n">
@@ -12927,7 +12915,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B291" t="n">
@@ -12970,7 +12958,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B292" t="n">
@@ -13013,7 +13001,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B293" t="n">
@@ -13056,7 +13044,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B294" t="n">
@@ -13099,7 +13087,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B295" t="n">
@@ -13142,7 +13130,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B296" t="n">
@@ -13185,7 +13173,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B297" t="n">
@@ -13228,7 +13216,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B298" t="n">
@@ -13271,7 +13259,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B299" t="n">
@@ -13314,7 +13302,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B300" t="n">
@@ -13357,7 +13345,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B301" t="n">
@@ -13400,7 +13388,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B302" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B303" t="n">
@@ -13486,7 +13474,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B304" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B305" t="n">
@@ -13572,7 +13560,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B306" t="n">
@@ -13615,7 +13603,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B307" t="n">
@@ -13658,7 +13646,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B308" t="n">
@@ -13701,7 +13689,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B309" t="n">
@@ -13744,7 +13732,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B310" t="n">
@@ -13787,7 +13775,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B311" t="n">
@@ -13830,7 +13818,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B312" t="n">
@@ -13873,7 +13861,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B313" t="n">
@@ -13916,7 +13904,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B314" t="n">
@@ -13959,7 +13947,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B315" t="n">
@@ -14002,7 +13990,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B316" t="n">
@@ -14045,7 +14033,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B317" t="n">
@@ -14088,7 +14076,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B318" t="n">
@@ -14131,7 +14119,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B319" t="n">
@@ -14174,7 +14162,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B320" t="n">
@@ -14217,7 +14205,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B321" t="n">
@@ -14260,7 +14248,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B322" t="n">
@@ -14303,7 +14291,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B323" t="n">
@@ -14346,7 +14334,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B324" t="n">
@@ -14389,7 +14377,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B325" t="n">
@@ -14432,7 +14420,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B326" t="n">
@@ -14475,7 +14463,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B327" t="n">
@@ -14518,7 +14506,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B328" t="n">
@@ -14561,7 +14549,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B329" t="n">
@@ -14604,7 +14592,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B330" t="n">
@@ -14647,7 +14635,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B331" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B332" t="n">
@@ -14733,7 +14721,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B333" t="n">
@@ -14776,7 +14764,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B334" t="n">
@@ -14819,7 +14807,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B335" t="n">
@@ -14862,7 +14850,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B336" t="n">
@@ -14905,7 +14893,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B337" t="n">
@@ -14948,7 +14936,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B338" t="n">
@@ -14991,7 +14979,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B339" t="n">
@@ -15034,7 +15022,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B340" t="n">
@@ -15077,7 +15065,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B341" t="n">
@@ -15120,7 +15108,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B342" t="n">
@@ -15163,7 +15151,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B343" t="n">
@@ -15206,7 +15194,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B344" t="n">
@@ -15249,7 +15237,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B345" t="n">
@@ -15292,7 +15280,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B346" t="n">
@@ -15335,7 +15323,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B347" t="n">
@@ -15378,7 +15366,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B348" t="n">
@@ -15421,7 +15409,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B349" t="n">
@@ -15464,7 +15452,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B350" t="n">
@@ -15507,7 +15495,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B351" t="n">
@@ -15550,7 +15538,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B352" t="n">
@@ -15593,7 +15581,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B353" t="n">
@@ -15636,7 +15624,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B354" t="n">
@@ -15679,7 +15667,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B355" t="n">
@@ -15722,7 +15710,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B356" t="n">
@@ -15765,7 +15753,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B357" t="n">
@@ -15808,7 +15796,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B358" t="n">
@@ -15851,7 +15839,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B359" t="n">
@@ -15894,7 +15882,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B360" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B361" t="n">

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -516,7 +516,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87356</v>
+        <v>6.87396</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -559,7 +559,7 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15334</v>
+        <v>4.15286</v>
       </c>
       <c r="K3" t="n">
         <v>2.43838</v>
@@ -602,7 +602,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55513</v>
+        <v>7.55652</v>
       </c>
       <c r="K4" t="n">
         <v>2.13214</v>
@@ -645,7 +645,7 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74247</v>
+        <v>0.74233</v>
       </c>
       <c r="K5" t="n">
         <v>2.02286</v>
@@ -688,10 +688,10 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77776</v>
+        <v>1.77767</v>
       </c>
       <c r="K6" t="n">
-        <v>1.98007</v>
+        <v>1.99344</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02128</v>
+        <v>2.02094</v>
       </c>
       <c r="K7" t="n">
         <v>1.70179</v>
@@ -774,7 +774,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61371</v>
+        <v>4.61358</v>
       </c>
       <c r="K8" t="n">
         <v>1.47346</v>
@@ -817,7 +817,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05472</v>
+        <v>7.05463</v>
       </c>
       <c r="K9" t="n">
         <v>1.21062</v>
@@ -860,7 +860,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.034599999999999</v>
+        <v>8.03444</v>
       </c>
       <c r="K10" t="n">
         <v>0.7003</v>
@@ -903,7 +903,7 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9006</v>
+        <v>5.90044</v>
       </c>
       <c r="K11" t="n">
         <v>0.36237</v>
@@ -946,7 +946,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.00211</v>
+        <v>3.00219</v>
       </c>
       <c r="K12" t="n">
         <v>0.05167</v>
@@ -989,7 +989,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56821</v>
+        <v>3.5683</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1032,7 +1032,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.00337</v>
+        <v>2.0041</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1075,7 +1075,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.20138</v>
+        <v>3.20036</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1118,10 +1118,10 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72119</v>
+        <v>4.72296</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.21134</v>
+        <v>-1.22423</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26322</v>
+        <v>5.26285</v>
       </c>
       <c r="K17" t="n">
         <v>-1.68662</v>
@@ -1204,7 +1204,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22913</v>
+        <v>4.22891</v>
       </c>
       <c r="K18" t="n">
         <v>-1.9802</v>
@@ -1247,7 +1247,7 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76122</v>
+        <v>3.76074</v>
       </c>
       <c r="K19" t="n">
         <v>-2.25254</v>
@@ -1290,7 +1290,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94772</v>
+        <v>0.94757</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53148</v>
@@ -1333,7 +1333,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13368</v>
+        <v>-1.13377</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1376,7 +1376,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.86882</v>
+        <v>-2.86898</v>
       </c>
       <c r="K22" t="n">
         <v>-2.39536</v>
@@ -1419,7 +1419,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.60409</v>
+        <v>-2.6043</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1462,7 +1462,7 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90614</v>
+        <v>-2.90597</v>
       </c>
       <c r="K24" t="n">
         <v>-2.19496</v>
@@ -1505,10 +1505,10 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.72205</v>
+        <v>-3.72199</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.93924</v>
+        <v>-1.95217</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68661</v>
+        <v>-6.68621</v>
       </c>
       <c r="K26" t="n">
         <v>-1.50532</v>
@@ -1591,7 +1591,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29554</v>
+        <v>-7.29626</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1634,10 +1634,10 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.18752</v>
+        <v>-7.18594</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.46961</v>
+        <v>-0.45662</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.49605</v>
+        <v>-8.496359999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.3143</v>
@@ -1720,7 +1720,7 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96454</v>
+        <v>-7.96469</v>
       </c>
       <c r="K30" t="n">
         <v>0.61656</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24787</v>
+        <v>-7.24837</v>
       </c>
       <c r="K31" t="n">
         <v>1.1193</v>
@@ -1806,7 +1806,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.58171</v>
+        <v>-7.58179</v>
       </c>
       <c r="K32" t="n">
         <v>1.33158</v>
@@ -1849,7 +1849,7 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.44017</v>
+        <v>-8.44023</v>
       </c>
       <c r="K33" t="n">
         <v>1.54476</v>
@@ -1892,7 +1892,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.62441</v>
+        <v>-7.62456</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1935,7 +1935,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.89499</v>
+        <v>-5.89514</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1978,7 +1978,7 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24294</v>
+        <v>-7.24278</v>
       </c>
       <c r="K36" t="n">
         <v>1.34653</v>
@@ -2021,10 +2021,10 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.38122</v>
+        <v>-7.38118</v>
       </c>
       <c r="K37" t="n">
-        <v>1.02835</v>
+        <v>1.04167</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.30755</v>
+        <v>-3.30715</v>
       </c>
       <c r="K38" t="n">
         <v>0.59289</v>
@@ -2107,7 +2107,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.16421</v>
+        <v>-2.1649</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2150,7 +2150,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.56107</v>
+        <v>-1.55947</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2193,7 +2193,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.60261</v>
+        <v>-0.60295</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2236,7 +2236,7 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01657</v>
+        <v>-1.01677</v>
       </c>
       <c r="K42" t="n">
         <v>-1.08214</v>
@@ -2279,7 +2279,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.00412</v>
+        <v>-1.00472</v>
       </c>
       <c r="K43" t="n">
         <v>-1.06785</v>
@@ -2322,7 +2322,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.31999</v>
+        <v>1.31985</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2365,7 +2365,7 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68576</v>
+        <v>0.68566</v>
       </c>
       <c r="K45" t="n">
         <v>-1.24821</v>
@@ -2408,7 +2408,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35208</v>
+        <v>1.35198</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2451,7 +2451,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09783</v>
+        <v>1.09778</v>
       </c>
       <c r="K47" t="n">
         <v>-1.00117</v>
@@ -2494,7 +2494,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.67611</v>
+        <v>2.67642</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2537,7 +2537,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51947</v>
+        <v>2.51976</v>
       </c>
       <c r="K49" t="n">
         <v>0.11745</v>
@@ -2580,7 +2580,7 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.40999</v>
+        <v>1.40978</v>
       </c>
       <c r="K50" t="n">
         <v>0.60249</v>
@@ -2623,10 +2623,10 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.18317</v>
+        <v>0.18303</v>
       </c>
       <c r="K51" t="n">
-        <v>0.89215</v>
+        <v>0.87903</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.83514</v>
+        <v>-0.83422</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2709,7 +2709,7 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.64109</v>
+        <v>-0.64128</v>
       </c>
       <c r="K53" t="n">
         <v>0.84188</v>
@@ -2752,7 +2752,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46438</v>
+        <v>-0.46451</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2795,7 +2795,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.25802</v>
+        <v>-1.25853</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2838,7 +2838,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05597</v>
+        <v>-2.05606</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2881,7 +2881,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.07045999999999999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="K57" t="n">
         <v>0.30283</v>
@@ -2924,7 +2924,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.9904500000000001</v>
+        <v>-0.99044</v>
       </c>
       <c r="K58" t="n">
         <v>0.24987</v>
@@ -2967,7 +2967,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11223</v>
+        <v>-2.11214</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3010,7 +3010,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08781</v>
+        <v>-1.08765</v>
       </c>
       <c r="K60" t="n">
         <v>-0.30089</v>
@@ -3053,7 +3053,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03229</v>
+        <v>-1.03202</v>
       </c>
       <c r="K61" t="n">
         <v>-0.57351</v>
@@ -3096,7 +3096,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.74494</v>
+        <v>-0.74507</v>
       </c>
       <c r="K62" t="n">
         <v>-0.80719</v>
@@ -3139,10 +3139,10 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.24698</v>
+        <v>1.24695</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.78023</v>
+        <v>-0.76733</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.93799</v>
+        <v>1.938</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.72112</v>
+        <v>0.72111</v>
       </c>
       <c r="K65" t="n">
         <v>-0.28698</v>
@@ -3268,7 +3268,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.0877</v>
+        <v>1.08762</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.17101</v>
+        <v>2.1709</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3354,7 +3354,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45742</v>
+        <v>2.45732</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3397,7 +3397,7 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.3056</v>
+        <v>2.30554</v>
       </c>
       <c r="K69" t="n">
         <v>1.11578</v>
@@ -3440,7 +3440,7 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95787</v>
+        <v>2.95793</v>
       </c>
       <c r="K70" t="n">
         <v>1.12816</v>
@@ -3483,7 +3483,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.13825</v>
+        <v>3.13836</v>
       </c>
       <c r="K71" t="n">
         <v>1.15592</v>
@@ -3526,7 +3526,7 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.07521</v>
+        <v>2.07536</v>
       </c>
       <c r="K72" t="n">
         <v>0.91851</v>
@@ -3569,7 +3569,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.726</v>
+        <v>3.7263</v>
       </c>
       <c r="K73" t="n">
         <v>0.957</v>
@@ -3612,7 +3612,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.27708</v>
+        <v>3.2769</v>
       </c>
       <c r="K74" t="n">
         <v>0.95813</v>
@@ -3655,7 +3655,7 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52727</v>
+        <v>1.52716</v>
       </c>
       <c r="K75" t="n">
         <v>0.93054</v>
@@ -3698,7 +3698,7 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.24672</v>
+        <v>1.24666</v>
       </c>
       <c r="K76" t="n">
         <v>0.94253</v>
@@ -3741,7 +3741,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.2429</v>
+        <v>1.24286</v>
       </c>
       <c r="K77" t="n">
         <v>0.98116</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03919</v>
+        <v>-0.03923</v>
       </c>
       <c r="K78" t="n">
         <v>1.20199</v>
@@ -3827,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.36339</v>
+        <v>-1.3634</v>
       </c>
       <c r="K79" t="n">
         <v>1.22683</v>
@@ -3913,7 +3913,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.38612</v>
+        <v>-1.38613</v>
       </c>
       <c r="K81" t="n">
         <v>1.19434</v>
@@ -3956,7 +3956,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.81174</v>
+        <v>-1.81168</v>
       </c>
       <c r="K82" t="n">
         <v>1.45285</v>
@@ -3999,10 +3999,10 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15051</v>
+        <v>-1.15045</v>
       </c>
       <c r="K83" t="n">
-        <v>1.72705</v>
+        <v>1.71406</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.29206</v>
+        <v>-1.29201</v>
       </c>
       <c r="K84" t="n">
         <v>2.22338</v>
@@ -4085,7 +4085,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01266</v>
+        <v>-2.01257</v>
       </c>
       <c r="K85" t="n">
         <v>2.22049</v>
@@ -4128,7 +4128,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.71984</v>
+        <v>-1.71985</v>
       </c>
       <c r="K86" t="n">
         <v>2.4701</v>
@@ -4171,7 +4171,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27084</v>
+        <v>-1.27095</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4214,7 +4214,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.97205</v>
+        <v>-0.97214</v>
       </c>
       <c r="K88" t="n">
         <v>2.45104</v>
@@ -4257,7 +4257,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.57024</v>
+        <v>-0.57026</v>
       </c>
       <c r="K89" t="n">
         <v>2.48737</v>
@@ -4343,7 +4343,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J91" t="n">
-        <v>0.38877</v>
+        <v>0.38879</v>
       </c>
       <c r="K91" t="n">
         <v>1.97267</v>
@@ -4386,7 +4386,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.22582</v>
+        <v>-0.2258</v>
       </c>
       <c r="K92" t="n">
         <v>1.75145</v>
@@ -4429,7 +4429,7 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.93909</v>
+        <v>-0.9391</v>
       </c>
       <c r="K93" t="n">
         <v>1.48813</v>
@@ -4472,7 +4472,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.38797</v>
+        <v>-1.38793</v>
       </c>
       <c r="K94" t="n">
         <v>1.26582</v>
@@ -4515,10 +4515,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.02733</v>
+        <v>-2.02731</v>
       </c>
       <c r="K95" t="n">
-        <v>1.1999</v>
+        <v>1.21282</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.27385</v>
+        <v>-1.27383</v>
       </c>
       <c r="K96" t="n">
         <v>1.20834</v>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.9533</v>
+        <v>-1.95325</v>
       </c>
       <c r="K97" t="n">
         <v>1.47358</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.95978</v>
+        <v>-1.95977</v>
       </c>
       <c r="K98" t="n">
         <v>1.68739</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.02144</v>
+        <v>-2.02152</v>
       </c>
       <c r="K99" t="n">
         <v>1.96426</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.22757</v>
+        <v>-2.22762</v>
       </c>
       <c r="K100" t="n">
         <v>2.26582</v>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.70107</v>
+        <v>-0.70106</v>
       </c>
       <c r="K103" t="n">
         <v>3.13567</v>
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.63681</v>
+        <v>-1.63679</v>
       </c>
       <c r="K104" t="n">
         <v>3.40463</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.31034</v>
+        <v>-1.31032</v>
       </c>
       <c r="K105" t="n">
         <v>3.72898</v>
@@ -4988,7 +4988,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.71546</v>
+        <v>-1.71544</v>
       </c>
       <c r="K106" t="n">
         <v>4.01515</v>
@@ -5031,7 +5031,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61233</v>
+        <v>0.61232</v>
       </c>
       <c r="K107" t="n">
         <v>4.36428</v>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32914</v>
+        <v>2.32918</v>
       </c>
       <c r="K109" t="n">
         <v>4.68202</v>
@@ -5160,7 +5160,7 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.66647</v>
+        <v>0.66648</v>
       </c>
       <c r="K110" t="n">
         <v>4.75359</v>
@@ -5203,7 +5203,7 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9056</v>
+        <v>0.9055299999999999</v>
       </c>
       <c r="K111" t="n">
         <v>4.52399</v>
@@ -5246,7 +5246,7 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.7548</v>
+        <v>1.75477</v>
       </c>
       <c r="K112" t="n">
         <v>4.53026</v>
@@ -5289,7 +5289,7 @@
         <v>0.29718</v>
       </c>
       <c r="J113" t="n">
-        <v>2.68802</v>
+        <v>2.68804</v>
       </c>
       <c r="K113" t="n">
         <v>4.5595</v>
@@ -5332,7 +5332,7 @@
         <v>0.14859</v>
       </c>
       <c r="J114" t="n">
-        <v>2.8743</v>
+        <v>2.87431</v>
       </c>
       <c r="K114" t="n">
         <v>4.56672</v>
@@ -5418,7 +5418,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.93851</v>
+        <v>3.93852</v>
       </c>
       <c r="K116" t="n">
         <v>4.58996</v>
@@ -5461,7 +5461,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.90906</v>
+        <v>3.90907</v>
       </c>
       <c r="K117" t="n">
         <v>4.53327</v>
@@ -5504,10 +5504,10 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.25929</v>
+        <v>5.2593</v>
       </c>
       <c r="K118" t="n">
-        <v>4.34571</v>
+        <v>4.33358</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.88633</v>
+        <v>1.88632</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5633,7 +5633,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.47365</v>
+        <v>1.47368</v>
       </c>
       <c r="K121" t="n">
         <v>3.50395</v>
@@ -5676,7 +5676,7 @@
         <v>-0.2963</v>
       </c>
       <c r="J122" t="n">
-        <v>3.3177</v>
+        <v>3.31769</v>
       </c>
       <c r="K122" t="n">
         <v>2.89424</v>
@@ -5719,10 +5719,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J123" t="n">
-        <v>3.28842</v>
+        <v>3.28841</v>
       </c>
       <c r="K123" t="n">
-        <v>2.90131</v>
+        <v>2.88942</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>-0.29586</v>
       </c>
       <c r="J124" t="n">
-        <v>2.2163</v>
+        <v>2.21629</v>
       </c>
       <c r="K124" t="n">
         <v>2.38011</v>
@@ -5977,7 +5977,7 @@
         <v>-0.14903</v>
       </c>
       <c r="J129" t="n">
-        <v>0.60938</v>
+        <v>0.60939</v>
       </c>
       <c r="K129" t="n">
         <v>1.14246</v>
@@ -6023,7 +6023,7 @@
         <v>0.37904</v>
       </c>
       <c r="K130" t="n">
-        <v>0.8027</v>
+        <v>0.81443</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6235,10 +6235,10 @@
         <v>-1.63205</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.84518</v>
+        <v>-7.84519</v>
       </c>
       <c r="K135" t="n">
-        <v>0.51999</v>
+        <v>0.53161</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>-1.92878</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.1485</v>
+        <v>-7.14851</v>
       </c>
       <c r="K136" t="n">
         <v>1.02938</v>
@@ -6321,7 +6321,7 @@
         <v>-1.93165</v>
       </c>
       <c r="J137" t="n">
-        <v>-6.82901</v>
+        <v>-6.82902</v>
       </c>
       <c r="K137" t="n">
         <v>1.2942</v>
@@ -6622,7 +6622,7 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.45734</v>
+        <v>1.45735</v>
       </c>
       <c r="K144" t="n">
         <v>3.63258</v>
@@ -7009,7 +7009,7 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>0.95989</v>
+        <v>0.95988</v>
       </c>
       <c r="K153" t="n">
         <v>1.21417</v>
@@ -7052,7 +7052,7 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.12171</v>
+        <v>1.1217</v>
       </c>
       <c r="K154" t="n">
         <v>1.42536</v>
@@ -7095,7 +7095,7 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.5897</v>
+        <v>2.58971</v>
       </c>
       <c r="K155" t="n">
         <v>1.45333</v>
@@ -7138,7 +7138,7 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.93548</v>
+        <v>1.93549</v>
       </c>
       <c r="K156" t="n">
         <v>1.45122</v>
@@ -7181,7 +7181,7 @@
         <v>-0.30534</v>
       </c>
       <c r="J157" t="n">
-        <v>2.43276</v>
+        <v>2.43277</v>
       </c>
       <c r="K157" t="n">
         <v>1.44509</v>
@@ -7267,7 +7267,7 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.65364</v>
+        <v>1.65365</v>
       </c>
       <c r="K159" t="n">
         <v>1.97252</v>
@@ -7439,7 +7439,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J163" t="n">
-        <v>4.06004</v>
+        <v>4.06003</v>
       </c>
       <c r="K163" t="n">
         <v>3.95512</v>
@@ -7482,7 +7482,7 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.68902</v>
+        <v>3.68901</v>
       </c>
       <c r="K164" t="n">
         <v>4.25887</v>
@@ -7525,7 +7525,7 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.90117</v>
+        <v>2.90116</v>
       </c>
       <c r="K165" t="n">
         <v>4.28746</v>
@@ -7568,7 +7568,7 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53607</v>
+        <v>2.53606</v>
       </c>
       <c r="K166" t="n">
         <v>4.07215</v>
@@ -7611,7 +7611,7 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.64576</v>
+        <v>3.64577</v>
       </c>
       <c r="K167" t="n">
         <v>3.83471</v>
@@ -7654,7 +7654,7 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.48902</v>
+        <v>3.48903</v>
       </c>
       <c r="K168" t="n">
         <v>4.12632</v>
@@ -8041,7 +8041,7 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.899</v>
+        <v>2.89899</v>
       </c>
       <c r="K177" t="n">
         <v>3.04612</v>
@@ -8084,7 +8084,7 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.84431</v>
+        <v>3.8443</v>
       </c>
       <c r="K178" t="n">
         <v>2.99841</v>
@@ -8127,7 +8127,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.50137</v>
+        <v>2.50138</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8170,7 +8170,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78979</v>
+        <v>1.7898</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8385,7 +8385,7 @@
         <v>0.6116200000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>1.47009</v>
+        <v>1.47008</v>
       </c>
       <c r="K185" t="n">
         <v>1.88385</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>1.2688</v>
+        <v>1.26881</v>
       </c>
       <c r="K196" t="n">
         <v>2.24513</v>
@@ -9116,7 +9116,7 @@
         <v>-1.36364</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.66878</v>
+        <v>-0.66879</v>
       </c>
       <c r="K202" t="n">
         <v>0.28101</v>
@@ -9202,7 +9202,7 @@
         <v>-1.21212</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.0595</v>
+        <v>-1.05949</v>
       </c>
       <c r="K204" t="n">
         <v>-0.55911</v>
@@ -9417,7 +9417,7 @@
         <v>-0.15221</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.79127</v>
+        <v>-0.79128</v>
       </c>
       <c r="K209" t="n">
         <v>-0.57994</v>
@@ -9460,7 +9460,7 @@
         <v>0.15267</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.95663</v>
+        <v>-0.95664</v>
       </c>
       <c r="K210" t="n">
         <v>-1.14782</v>
@@ -9546,7 +9546,7 @@
         <v>0.46012</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.24896</v>
+        <v>-3.24895</v>
       </c>
       <c r="K212" t="n">
         <v>-2.26615</v>
@@ -9589,7 +9589,7 @@
         <v>0.30675</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.50816</v>
+        <v>-4.50817</v>
       </c>
       <c r="K213" t="n">
         <v>-2.51924</v>
@@ -9718,7 +9718,7 @@
         <v>-0.46012</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.64559</v>
+        <v>-7.64558</v>
       </c>
       <c r="K216" t="n">
         <v>-4.17671</v>
@@ -9761,7 +9761,7 @@
         <v>-0.91884</v>
       </c>
       <c r="J217" t="n">
-        <v>-7.87333</v>
+        <v>-7.87332</v>
       </c>
       <c r="K217" t="n">
         <v>-5.06266</v>
@@ -9804,7 +9804,7 @@
         <v>-1.37615</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.35885</v>
+        <v>-8.358840000000001</v>
       </c>
       <c r="K218" t="n">
         <v>-5.83817</v>
@@ -9847,7 +9847,7 @@
         <v>-1.67939</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.30184</v>
+        <v>-9.301830000000001</v>
       </c>
       <c r="K219" t="n">
         <v>-6.41604</v>
@@ -9933,7 +9933,7 @@
         <v>-2.13415</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.13441</v>
+        <v>-10.13443</v>
       </c>
       <c r="K221" t="n">
         <v>-6.77864</v>
@@ -9976,7 +9976,7 @@
         <v>-2.28659</v>
       </c>
       <c r="J222" t="n">
-        <v>-10.12145</v>
+        <v>-10.12146</v>
       </c>
       <c r="K222" t="n">
         <v>-6.5933</v>
@@ -10019,7 +10019,7 @@
         <v>-2.28659</v>
       </c>
       <c r="J223" t="n">
-        <v>-8.699949999999999</v>
+        <v>-8.699960000000001</v>
       </c>
       <c r="K223" t="n">
         <v>-6.08925</v>
@@ -10062,7 +10062,7 @@
         <v>-2.29008</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.54206</v>
+        <v>-7.54204</v>
       </c>
       <c r="K224" t="n">
         <v>-5.60776</v>
@@ -10191,7 +10191,7 @@
         <v>-2.30415</v>
       </c>
       <c r="J227" t="n">
-        <v>-5.44062</v>
+        <v>-5.44063</v>
       </c>
       <c r="K227" t="n">
         <v>-3.8001</v>
@@ -10234,7 +10234,7 @@
         <v>-2.15716</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.18348</v>
+        <v>-4.18349</v>
       </c>
       <c r="K228" t="n">
         <v>-3.34241</v>
@@ -10277,7 +10277,7 @@
         <v>-1.85471</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.2065</v>
+        <v>-4.20643</v>
       </c>
       <c r="K229" t="n">
         <v>-2.50264</v>
@@ -10320,7 +10320,7 @@
         <v>-1.70543</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.39893</v>
+        <v>-4.39894</v>
       </c>
       <c r="K230" t="n">
         <v>-1.64841</v>
@@ -10363,7 +10363,7 @@
         <v>-1.39752</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.84445</v>
+        <v>-3.84446</v>
       </c>
       <c r="K231" t="n">
         <v>-0.84628</v>
@@ -10406,7 +10406,7 @@
         <v>-1.09034</v>
       </c>
       <c r="J232" t="n">
-        <v>-3.53798</v>
+        <v>-3.538</v>
       </c>
       <c r="K232" t="n">
         <v>-0.25834</v>
@@ -10449,7 +10449,7 @@
         <v>-1.09034</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.63804</v>
+        <v>-1.63806</v>
       </c>
       <c r="K233" t="n">
         <v>0.34524</v>
@@ -10492,7 +10492,7 @@
         <v>-1.09204</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.38277</v>
+        <v>-1.38278</v>
       </c>
       <c r="K234" t="n">
         <v>0.70263</v>
@@ -10535,7 +10535,7 @@
         <v>-1.24805</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.35654</v>
+        <v>-1.35651</v>
       </c>
       <c r="K235" t="n">
         <v>1.20156</v>
@@ -10578,7 +10578,7 @@
         <v>-1.25</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.42159</v>
+        <v>-1.42153</v>
       </c>
       <c r="K236" t="n">
         <v>1.34185</v>
@@ -10621,7 +10621,7 @@
         <v>-1.25196</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.25727</v>
+        <v>-0.25722</v>
       </c>
       <c r="K237" t="n">
         <v>1.60399</v>
@@ -10664,7 +10664,7 @@
         <v>-1.09718</v>
       </c>
       <c r="J238" t="n">
-        <v>0.24351</v>
+        <v>0.24343</v>
       </c>
       <c r="K238" t="n">
         <v>1.44095</v>
@@ -10707,7 +10707,7 @@
         <v>-0.78616</v>
       </c>
       <c r="J239" t="n">
-        <v>1.33084</v>
+        <v>1.33073</v>
       </c>
       <c r="K239" t="n">
         <v>1.48268</v>
@@ -10750,7 +10750,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J240" t="n">
-        <v>1.67509</v>
+        <v>1.67506</v>
       </c>
       <c r="K240" t="n">
         <v>1.84282</v>
@@ -10793,7 +10793,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J241" t="n">
-        <v>2.18761</v>
+        <v>2.18778</v>
       </c>
       <c r="K241" t="n">
         <v>1.83039</v>
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.6863211178508</v>
+        <v>11.68992483843196</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37196834897944</v>
+        <v>11.36348062600854</v>
       </c>
       <c r="D242" t="n">
-        <v>10.13816525149755</v>
+        <v>10.12827691184035</v>
       </c>
       <c r="E242" t="n">
-        <v>7.264280641475795</v>
+        <v>7.269157404840976</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10836,7 +10836,7 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30207</v>
+        <v>2.30182</v>
       </c>
       <c r="K242" t="n">
         <v>2.02206</v>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.27305481793386</v>
+        <v>12.27626754053708</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43629678881366</v>
+        <v>12.43403543014179</v>
       </c>
       <c r="D243" t="n">
-        <v>7.804143699310284</v>
+        <v>7.786750272922438</v>
       </c>
       <c r="E243" t="n">
-        <v>8.996193392749795</v>
+        <v>8.999786584410208</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10879,7 +10879,7 @@
         <v>-0.31496</v>
       </c>
       <c r="J243" t="n">
-        <v>2.64173</v>
+        <v>2.64182</v>
       </c>
       <c r="K243" t="n">
         <v>2.12835</v>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.97259073462457</v>
+        <v>3.974043573307928</v>
       </c>
       <c r="C244" t="n">
-        <v>7.193780342911649</v>
+        <v>7.191370549666143</v>
       </c>
       <c r="D244" t="n">
-        <v>6.053196584988063</v>
+        <v>6.050921661423803</v>
       </c>
       <c r="E244" t="n">
-        <v>8.71295318182681</v>
+        <v>8.717951392315104</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10922,7 +10922,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J244" t="n">
-        <v>3.88744</v>
+        <v>3.88753</v>
       </c>
       <c r="K244" t="n">
         <v>2.14764</v>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.842126254767564</v>
+        <v>3.843821954797022</v>
       </c>
       <c r="C245" t="n">
-        <v>7.413878313013411</v>
+        <v>7.420447145364917</v>
       </c>
       <c r="D245" t="n">
-        <v>4.819873456623536</v>
+        <v>4.826980577035078</v>
       </c>
       <c r="E245" t="n">
-        <v>8.567660887249339</v>
+        <v>8.555894066622404</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10965,10 +10965,10 @@
         <v>-0.47244</v>
       </c>
       <c r="J245" t="n">
-        <v>2.90205</v>
+        <v>2.90227</v>
       </c>
       <c r="K245" t="n">
-        <v>1.87077</v>
+        <v>1.88152</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1716305403610008</v>
+        <v>0.1726177118588135</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6928179758161734</v>
+        <v>-0.6839599657378459</v>
       </c>
       <c r="D246" t="n">
-        <v>1.829888823989712</v>
+        <v>1.841584152454345</v>
       </c>
       <c r="E246" t="n">
-        <v>9.478648590965498</v>
+        <v>9.475524268795589</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11008,7 +11008,7 @@
         <v>-0.47319</v>
       </c>
       <c r="J246" t="n">
-        <v>3.10311</v>
+        <v>3.10265</v>
       </c>
       <c r="K246" t="n">
         <v>1.57793</v>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3633184734299966</v>
+        <v>-0.363678083425345</v>
       </c>
       <c r="C247" t="n">
-        <v>2.285661447258458</v>
+        <v>2.279991089277633</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.603646361190381</v>
+        <v>-1.589513724078673</v>
       </c>
       <c r="E247" t="n">
-        <v>9.103948431014786</v>
+        <v>9.111535844460917</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11051,7 +11051,7 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46114</v>
+        <v>3.46143</v>
       </c>
       <c r="K247" t="n">
         <v>1.05894</v>
@@ -11070,16 +11070,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.552354787472365</v>
+        <v>-1.551727144206871</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.316860683433075</v>
+        <v>-2.317795233951958</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.088701741253641</v>
+        <v>-3.089253412723547</v>
       </c>
       <c r="E248" t="n">
-        <v>8.148209035576981</v>
+        <v>8.157455600800279</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11094,7 +11094,7 @@
         <v>-0.31646</v>
       </c>
       <c r="J248" t="n">
-        <v>3.43719</v>
+        <v>3.43742</v>
       </c>
       <c r="K248" t="n">
         <v>1.05713</v>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.450612994381628</v>
+        <v>1.452831704132174</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2363814722077473</v>
+        <v>-0.233331214749477</v>
       </c>
       <c r="D249" t="n">
-        <v>2.495805028769071</v>
+        <v>2.489415575444354</v>
       </c>
       <c r="E249" t="n">
-        <v>7.147542035958776</v>
+        <v>7.159705907638059</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11137,10 +11137,10 @@
         <v>-0.31696</v>
       </c>
       <c r="J249" t="n">
-        <v>4.28994</v>
+        <v>4.29012</v>
       </c>
       <c r="K249" t="n">
-        <v>0.81067</v>
+        <v>0.82133</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.83264238121639</v>
+        <v>4.835365408902148</v>
       </c>
       <c r="C250" t="n">
-        <v>4.687979655750385</v>
+        <v>4.669575287126904</v>
       </c>
       <c r="D250" t="n">
-        <v>6.334200046212235</v>
+        <v>6.323190830349601</v>
       </c>
       <c r="E250" t="n">
-        <v>8.285042294873723</v>
+        <v>8.292084757591889</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11180,7 +11180,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36584</v>
+        <v>5.36585</v>
       </c>
       <c r="K250" t="n">
         <v>1.10007</v>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8317426378089632</v>
+        <v>0.8337934955781723</v>
       </c>
       <c r="C251" t="n">
-        <v>1.478822543395952</v>
+        <v>1.474362445723343</v>
       </c>
       <c r="D251" t="n">
-        <v>2.659575685517845</v>
+        <v>2.65919699752859</v>
       </c>
       <c r="E251" t="n">
-        <v>8.431535365767573</v>
+        <v>8.436154125890095</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11223,7 +11223,7 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.69152</v>
+        <v>4.69036</v>
       </c>
       <c r="K251" t="n">
         <v>1.33305</v>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.652593285826322</v>
+        <v>3.654106691389369</v>
       </c>
       <c r="C252" t="n">
-        <v>2.969197400881329</v>
+        <v>2.980363145273546</v>
       </c>
       <c r="D252" t="n">
-        <v>3.949986309309406</v>
+        <v>3.950759221323397</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19609174940759</v>
+        <v>10.18488406892764</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11266,7 +11266,7 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.7875</v>
+        <v>4.78797</v>
       </c>
       <c r="K252" t="n">
         <v>1.53273</v>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.121646046888941</v>
+        <v>7.125343074441304</v>
       </c>
       <c r="C253" t="n">
-        <v>8.446736178793612</v>
+        <v>8.434242813334825</v>
       </c>
       <c r="D253" t="n">
-        <v>3.621032521225254</v>
+        <v>3.608400423111768</v>
       </c>
       <c r="E253" t="n">
-        <v>7.935802401409098</v>
+        <v>7.945468756824625</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11309,7 +11309,7 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94873</v>
+        <v>4.94894</v>
       </c>
       <c r="K253" t="n">
         <v>2.11657</v>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.374180065245906</v>
+        <v>7.374789826971839</v>
       </c>
       <c r="C254" t="n">
-        <v>7.313967216435602</v>
+        <v>7.321333841067479</v>
       </c>
       <c r="D254" t="n">
-        <v>5.738079254101436</v>
+        <v>5.725297777085103</v>
       </c>
       <c r="E254" t="n">
-        <v>8.192682144438134</v>
+        <v>8.188927420071291</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11352,7 +11352,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.60839</v>
+        <v>5.60807</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449711182515982</v>
+        <v>5.449910660088575</v>
       </c>
       <c r="C255" t="n">
-        <v>5.868765836839662</v>
+        <v>5.900527365288899</v>
       </c>
       <c r="D255" t="n">
-        <v>2.549842384738854</v>
+        <v>2.550029914993224</v>
       </c>
       <c r="E255" t="n">
-        <v>6.400754327368396</v>
+        <v>6.398471540386952</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11395,7 +11395,7 @@
         <v>-2.36967</v>
       </c>
       <c r="J255" t="n">
-        <v>5.94847</v>
+        <v>5.9486</v>
       </c>
       <c r="K255" t="n">
         <v>2.39078</v>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.7065369637184</v>
+        <v>11.70729571480387</v>
       </c>
       <c r="C256" t="n">
-        <v>9.844090998784893</v>
+        <v>9.859853126744422</v>
       </c>
       <c r="D256" t="n">
-        <v>5.6627687021235</v>
+        <v>5.658353630827739</v>
       </c>
       <c r="E256" t="n">
-        <v>7.163013991754474</v>
+        <v>7.15711173318978</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11438,7 +11438,7 @@
         <v>-2.53165</v>
       </c>
       <c r="J256" t="n">
-        <v>5.66685</v>
+        <v>5.66697</v>
       </c>
       <c r="K256" t="n">
         <v>2.43001</v>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.774637722575051</v>
+        <v>8.774012672675703</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537535839634792</v>
+        <v>8.539223469662982</v>
       </c>
       <c r="D257" t="n">
-        <v>5.10133683345102</v>
+        <v>5.099067537245383</v>
       </c>
       <c r="E257" t="n">
-        <v>7.458021572808948</v>
+        <v>7.46478767977059</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11481,10 +11481,10 @@
         <v>-2.8481</v>
       </c>
       <c r="J257" t="n">
-        <v>6.14193</v>
+        <v>6.14219</v>
       </c>
       <c r="K257" t="n">
-        <v>2.76517</v>
+        <v>2.75433</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92055482669161</v>
+        <v>11.92035233898017</v>
       </c>
       <c r="C258" t="n">
-        <v>11.75146480548337</v>
+        <v>11.74811892381931</v>
       </c>
       <c r="D258" t="n">
-        <v>8.78139100666424</v>
+        <v>8.776974575011899</v>
       </c>
       <c r="E258" t="n">
-        <v>7.926934192846335</v>
+        <v>7.926318545559274</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11524,7 +11524,7 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59273</v>
+        <v>6.59243</v>
       </c>
       <c r="K258" t="n">
         <v>3.32875</v>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45446004492012</v>
+        <v>11.45468184795004</v>
       </c>
       <c r="C259" t="n">
-        <v>9.100965251183446</v>
+        <v>9.112585063312938</v>
       </c>
       <c r="D259" t="n">
-        <v>7.829038389098208</v>
+        <v>7.825112590440408</v>
       </c>
       <c r="E259" t="n">
-        <v>8.260079719662894</v>
+        <v>8.255702710197443</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11567,7 +11567,7 @@
         <v>-3.01109</v>
       </c>
       <c r="J259" t="n">
-        <v>6.62991</v>
+        <v>6.63025</v>
       </c>
       <c r="K259" t="n">
         <v>3.92676</v>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.846745780285392</v>
+        <v>8.846068889422032</v>
       </c>
       <c r="C260" t="n">
-        <v>9.291525254496523</v>
+        <v>9.297392625404054</v>
       </c>
       <c r="D260" t="n">
-        <v>8.076966828130638</v>
+        <v>8.082914665307639</v>
       </c>
       <c r="E260" t="n">
-        <v>8.664220055157145</v>
+        <v>8.65748806069584</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11610,7 +11610,7 @@
         <v>-3.01587</v>
       </c>
       <c r="J260" t="n">
-        <v>6.90732</v>
+        <v>6.90762</v>
       </c>
       <c r="K260" t="n">
         <v>4.4273</v>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52757226638814</v>
+        <v>12.52739962152307</v>
       </c>
       <c r="C261" t="n">
-        <v>10.31175390479724</v>
+        <v>10.29910637514733</v>
       </c>
       <c r="D261" t="n">
-        <v>5.620960042647871</v>
+        <v>5.620813524353463</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40590488318911</v>
+        <v>10.39530937181559</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11653,10 +11653,10 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46885</v>
+        <v>5.46924</v>
       </c>
       <c r="K261" t="n">
-        <v>5.35393</v>
+        <v>5.34278</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.79351386766549</v>
+        <v>6.793118679594712</v>
       </c>
       <c r="C262" t="n">
-        <v>6.467315278281371</v>
+        <v>6.493047727893364</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8130118463050895</v>
+        <v>-0.8049473598035095</v>
       </c>
       <c r="E262" t="n">
-        <v>8.714087110934576</v>
+        <v>8.714271387702311</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11696,7 +11696,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.0606</v>
+        <v>4.06101</v>
       </c>
       <c r="K262" t="n">
         <v>5.81027</v>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.091878457084434</v>
+        <v>9.091675509320908</v>
       </c>
       <c r="C263" t="n">
-        <v>7.433742446679803</v>
+        <v>7.4469470830135</v>
       </c>
       <c r="D263" t="n">
-        <v>3.15614894464713</v>
+        <v>3.162900394096302</v>
       </c>
       <c r="E263" t="n">
-        <v>8.718125411095091</v>
+        <v>8.725412748696581</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11739,7 +11739,7 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.98671</v>
+        <v>3.98382</v>
       </c>
       <c r="K263" t="n">
         <v>5.86192</v>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.4243896821107</v>
+        <v>13.42474591010869</v>
       </c>
       <c r="C264" t="n">
-        <v>11.26859630224437</v>
+        <v>11.22466013091263</v>
       </c>
       <c r="D264" t="n">
-        <v>4.655150544226738</v>
+        <v>4.654483390387076</v>
       </c>
       <c r="E264" t="n">
-        <v>6.310304768666519</v>
+        <v>6.331375519106341</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11782,7 +11782,7 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.8094</v>
+        <v>3.81029</v>
       </c>
       <c r="K264" t="n">
         <v>5.94402</v>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.054337096948338</v>
+        <v>8.05502016385149</v>
       </c>
       <c r="C265" t="n">
-        <v>5.793577158911845</v>
+        <v>5.782483068233213</v>
       </c>
       <c r="D265" t="n">
-        <v>2.717654577847073</v>
+        <v>2.718104583412195</v>
       </c>
       <c r="E265" t="n">
-        <v>7.34989637468042</v>
+        <v>7.363759857542873</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11825,7 +11825,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70187</v>
+        <v>3.70227</v>
       </c>
       <c r="K265" t="n">
         <v>5.63483</v>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.578460076738254</v>
+        <v>2.578522914629833</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2238886640106963</v>
+        <v>-0.1897500901190008</v>
       </c>
       <c r="D266" t="n">
-        <v>2.191618039304122</v>
+        <v>2.187857389933012</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01694022028965</v>
+        <v>12.01143640852598</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11868,7 +11868,7 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87411</v>
+        <v>2.87392</v>
       </c>
       <c r="K266" t="n">
         <v>5.6398</v>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.099289199428814</v>
+        <v>5.09897291766519</v>
       </c>
       <c r="C267" t="n">
-        <v>1.659332168311223</v>
+        <v>1.670013766977574</v>
       </c>
       <c r="D267" t="n">
-        <v>3.45418998167959</v>
+        <v>3.453551296123103</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53639865861087</v>
+        <v>13.52574624839236</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11911,7 +11911,7 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68873</v>
+        <v>2.68895</v>
       </c>
       <c r="K267" t="n">
         <v>5.62042</v>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.829093467945223</v>
+        <v>5.829507406188172</v>
       </c>
       <c r="C268" t="n">
-        <v>3.42137249615786</v>
+        <v>3.403417167034517</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9094038494481316</v>
+        <v>0.9072527018248566</v>
       </c>
       <c r="E268" t="n">
-        <v>15.10894084300953</v>
+        <v>15.09962253005856</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11954,7 +11954,7 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.18502</v>
+        <v>2.1853</v>
       </c>
       <c r="K268" t="n">
         <v>5.87932</v>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.373878252572181</v>
+        <v>2.373301440416831</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7177349822713674</v>
+        <v>0.721419468322293</v>
       </c>
       <c r="D269" t="n">
-        <v>2.948258661669012</v>
+        <v>2.945918902381228</v>
       </c>
       <c r="E269" t="n">
-        <v>10.13206520747363</v>
+        <v>10.14146272868868</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -11997,7 +11997,7 @@
         <v>-1.30293</v>
       </c>
       <c r="J269" t="n">
-        <v>2.61292</v>
+        <v>2.61321</v>
       </c>
       <c r="K269" t="n">
         <v>5.82315</v>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.698820356083442</v>
+        <v>2.698975364867739</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3387324665286906</v>
+        <v>0.351676338410245</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.520177805470047</v>
+        <v>-1.523443829445303</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77583131820379</v>
+        <v>11.78179299915805</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12040,7 +12040,7 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24405</v>
+        <v>2.24366</v>
       </c>
       <c r="K270" t="n">
         <v>5.58396</v>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.117904207579803</v>
+        <v>4.118510270104681</v>
       </c>
       <c r="C271" t="n">
-        <v>3.272158753235188</v>
+        <v>3.26607030578332</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.173285265493673</v>
+        <v>-1.177173178113866</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72565370518555</v>
+        <v>12.72337530367955</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12083,7 +12083,7 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.02538</v>
+        <v>2.02601</v>
       </c>
       <c r="K271" t="n">
         <v>5.54028</v>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.815838055866561</v>
+        <v>3.81583745826688</v>
       </c>
       <c r="C272" t="n">
-        <v>2.834414438875421</v>
+        <v>2.8252403248477</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.924132950243519</v>
+        <v>-2.92070980245891</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49788551640993</v>
+        <v>12.49043195947355</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12126,7 +12126,7 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.0677</v>
+        <v>2.0678</v>
       </c>
       <c r="K272" t="n">
         <v>5.03896</v>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.045087700193582</v>
+        <v>2.044852516298779</v>
       </c>
       <c r="C273" t="n">
-        <v>2.702753555099546</v>
+        <v>2.700532332379479</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1120112466762357</v>
+        <v>-0.1108363405218582</v>
       </c>
       <c r="E273" t="n">
-        <v>12.16368843444913</v>
+        <v>12.15264147623145</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12169,7 +12169,7 @@
         <v>-0.32787</v>
       </c>
       <c r="J273" t="n">
-        <v>2.87064</v>
+        <v>2.87074</v>
       </c>
       <c r="K273" t="n">
         <v>4.36879</v>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.146149676956242</v>
+        <v>-0.1466298514992359</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2306163096418734</v>
+        <v>0.2223891517783239</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03723050616573076</v>
+        <v>0.0392952665049906</v>
       </c>
       <c r="E274" t="n">
-        <v>11.92905102230655</v>
+        <v>11.91912623343714</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12212,7 +12212,7 @@
         <v>-0.16393</v>
       </c>
       <c r="J274" t="n">
-        <v>2.13192</v>
+        <v>2.13217</v>
       </c>
       <c r="K274" t="n">
         <v>3.66414</v>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.322773073270366</v>
+        <v>-0.3229098304281308</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4541823068153872</v>
+        <v>-0.4741188085669812</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.025036918682122</v>
+        <v>-2.026644695937407</v>
       </c>
       <c r="E275" t="n">
-        <v>10.90796931752909</v>
+        <v>10.8975420006656</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12255,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.59073</v>
+        <v>2.58798</v>
       </c>
       <c r="K275" t="n">
         <v>3.36017</v>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994609716694453</v>
+        <v>-3.994881246073345</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.155016270866419</v>
+        <v>-4.152100101828338</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.71469893258195</v>
+        <v>-3.712178964755786</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912476788405321</v>
+        <v>8.912969444179385</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12298,7 +12298,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.64211</v>
+        <v>2.64296</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.363846347012356</v>
+        <v>-3.363111156896126</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.722803365233152</v>
+        <v>-3.720825651898196</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.385776021505427</v>
+        <v>-3.384945572229514</v>
       </c>
       <c r="E277" t="n">
-        <v>10.79436698078313</v>
+        <v>10.77848099160279</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12341,7 +12341,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55363</v>
+        <v>2.55402</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.268354928370831</v>
+        <v>3.268371992848951</v>
       </c>
       <c r="C278" t="n">
-        <v>3.634716234291346</v>
+        <v>3.592827003630594</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.61832406775857</v>
+        <v>-1.612570285423376</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127549245347397</v>
+        <v>6.127317719603864</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12384,7 +12384,7 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57148</v>
+        <v>3.57185</v>
       </c>
       <c r="K278" t="n">
         <v>2.88074</v>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1253157540679006</v>
+        <v>-0.1256523063747905</v>
       </c>
       <c r="C279" t="n">
-        <v>0.463339132479712</v>
+        <v>0.482547579104553</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3324830902674103</v>
+        <v>-0.3290458246748562</v>
       </c>
       <c r="E279" t="n">
-        <v>4.001555880732077</v>
+        <v>4.006950494299444</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12427,7 +12427,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10615</v>
+        <v>3.1063</v>
       </c>
       <c r="K279" t="n">
         <v>2.73892</v>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848892567628702</v>
+        <v>-1.848876163615176</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.182615785265929</v>
+        <v>-2.144670495986445</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7988053574945364</v>
+        <v>-0.7972816355882872</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4686534685211186</v>
+        <v>0.481390173681695</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12470,7 +12470,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13341</v>
+        <v>3.13352</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.169322343353408</v>
+        <v>2.168929065183001</v>
       </c>
       <c r="C281" t="n">
-        <v>1.85650232694512</v>
+        <v>1.844332531119064</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.089574879455415</v>
+        <v>-3.088332124160353</v>
       </c>
       <c r="E281" t="n">
-        <v>3.992216543843452</v>
+        <v>4.001147830820528</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12513,7 +12513,7 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52931</v>
+        <v>2.52943</v>
       </c>
       <c r="K281" t="n">
         <v>2.48447</v>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.202136641397211</v>
+        <v>1.202547802466469</v>
       </c>
       <c r="C282" t="n">
-        <v>1.625532019542919</v>
+        <v>1.619941276425929</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2831090410712278</v>
+        <v>0.2785466269759951</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9960353367786778</v>
+        <v>1.005509421825823</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12556,7 +12556,7 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46744</v>
+        <v>2.46751</v>
       </c>
       <c r="K282" t="n">
         <v>2.70244</v>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.131519600763942</v>
+        <v>1.132112961074849</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5622180221450668</v>
+        <v>0.5654923817485891</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1461635760984459</v>
+        <v>0.13805697499083</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1300330518576254</v>
+        <v>-0.1219898035134337</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12599,7 +12599,7 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.70773</v>
+        <v>1.70799</v>
       </c>
       <c r="K283" t="n">
         <v>2.46068</v>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.550321392217225</v>
+        <v>2.550509574981996</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05039994069987452</v>
+        <v>-0.05202725790229845</v>
       </c>
       <c r="D284" t="n">
-        <v>2.830723290095638</v>
+        <v>2.831506382942739</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7792631638080971</v>
+        <v>0.7857040040428531</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12642,10 +12642,10 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26765</v>
+        <v>1.26743</v>
       </c>
       <c r="K284" t="n">
-        <v>2.66834</v>
+        <v>2.67797</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4597255982823789</v>
+        <v>0.4590760942307703</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7832346176889549</v>
+        <v>-0.7771591340667627</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.488053104305276</v>
+        <v>-1.483964813671079</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2741194938582936</v>
+        <v>0.2812410990183922</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12685,7 +12685,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.5516</v>
+        <v>0.55165</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656495330986199</v>
+        <v>4.656058063469892</v>
       </c>
       <c r="C286" t="n">
-        <v>1.851346451228109</v>
+        <v>1.839552744075301</v>
       </c>
       <c r="D286" t="n">
-        <v>2.953192343805777</v>
+        <v>2.95050563048096</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268596045896109</v>
+        <v>1.269673999922505</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12728,7 +12728,7 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35727</v>
+        <v>1.35781</v>
       </c>
       <c r="K286" t="n">
         <v>3.24569</v>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.818814359454194</v>
+        <v>5.818713311471413</v>
       </c>
       <c r="C287" t="n">
-        <v>3.945317982665042</v>
+        <v>3.934385631063386</v>
       </c>
       <c r="D287" t="n">
-        <v>4.856940163032397</v>
+        <v>4.847911274119054</v>
       </c>
       <c r="E287" t="n">
-        <v>2.676744879570858</v>
+        <v>2.671696411680302</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12771,7 +12771,7 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.27722</v>
+        <v>1.2737</v>
       </c>
       <c r="K287" t="n">
         <v>3.51063</v>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480530770468682</v>
+        <v>3.480101152003923</v>
       </c>
       <c r="C288" t="n">
-        <v>2.95066472650416</v>
+        <v>2.926255752545615</v>
       </c>
       <c r="D288" t="n">
-        <v>2.105850303771151</v>
+        <v>2.104392884165129</v>
       </c>
       <c r="E288" t="n">
-        <v>3.363540513565488</v>
+        <v>3.356284558607592</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12814,7 +12814,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.52998</v>
+        <v>0.53188</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.848322935538254</v>
+        <v>6.849816652790142</v>
       </c>
       <c r="C289" t="n">
-        <v>6.017279382417651</v>
+        <v>5.982595885154107</v>
       </c>
       <c r="D289" t="n">
-        <v>2.229970692714822</v>
+        <v>2.223343544138534</v>
       </c>
       <c r="E289" t="n">
-        <v>3.820293115301698</v>
+        <v>3.807208091587611</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12857,7 +12857,7 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27365</v>
+        <v>-0.27306</v>
       </c>
       <c r="K289" t="n">
         <v>3.51163</v>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.870593908024575</v>
+        <v>0.8706666638469862</v>
       </c>
       <c r="C290" t="n">
-        <v>1.164236615156611</v>
+        <v>1.186587143743356</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.203668233578993</v>
+        <v>-2.19399149010876</v>
       </c>
       <c r="E290" t="n">
-        <v>2.405924795847292</v>
+        <v>2.412652559332029</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12900,10 +12900,10 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.03961</v>
+        <v>-0.03921</v>
       </c>
       <c r="K290" t="n">
-        <v>3.82263</v>
+        <v>3.83219</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.28909692597561</v>
+        <v>3.288810935500774</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302415712610096</v>
+        <v>3.351876745997329</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.245748751424136</v>
+        <v>-1.235056573228765</v>
       </c>
       <c r="E291" t="n">
-        <v>3.628210025536993</v>
+        <v>3.629587402705048</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12943,7 +12943,7 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23631</v>
+        <v>-0.23633</v>
       </c>
       <c r="K291" t="n">
         <v>3.85604</v>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.30728442171864</v>
+        <v>6.307030970224381</v>
       </c>
       <c r="C292" t="n">
-        <v>5.588600005263178</v>
+        <v>5.59268724930444</v>
       </c>
       <c r="D292" t="n">
-        <v>2.181868659433284</v>
+        <v>2.187866051305876</v>
       </c>
       <c r="E292" t="n">
-        <v>4.880784790353032</v>
+        <v>4.881988604638576</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -12986,7 +12986,7 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.73803</v>
+        <v>-0.73795</v>
       </c>
       <c r="K292" t="n">
         <v>3.62291</v>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.537164750821242</v>
+        <v>3.53689787502427</v>
       </c>
       <c r="C293" t="n">
-        <v>2.372082247313734</v>
+        <v>2.391409858104665</v>
       </c>
       <c r="D293" t="n">
-        <v>2.532364367060747</v>
+        <v>2.531849210898507</v>
       </c>
       <c r="E293" t="n">
-        <v>4.242051023227078</v>
+        <v>4.240518532609761</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13029,7 +13029,7 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52199</v>
+        <v>-0.52179</v>
       </c>
       <c r="K293" t="n">
         <v>3.87311</v>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.372964511997738</v>
+        <v>8.373397879887111</v>
       </c>
       <c r="C294" t="n">
-        <v>5.910774873927327</v>
+        <v>5.92657458166419</v>
       </c>
       <c r="D294" t="n">
-        <v>4.196812654410698</v>
+        <v>4.191466141362055</v>
       </c>
       <c r="E294" t="n">
-        <v>6.251215969423951</v>
+        <v>6.24447484806363</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13072,7 +13072,7 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82336</v>
+        <v>-0.82343</v>
       </c>
       <c r="K294" t="n">
         <v>3.87626</v>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.599152337015557</v>
+        <v>6.599619646518229</v>
       </c>
       <c r="C295" t="n">
-        <v>5.385907638923459</v>
+        <v>5.387843812041671</v>
       </c>
       <c r="D295" t="n">
-        <v>6.107678900772995</v>
+        <v>6.099813954185485</v>
       </c>
       <c r="E295" t="n">
-        <v>6.947532808508461</v>
+        <v>6.937099734491081</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13115,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05978</v>
+        <v>-0.05965</v>
       </c>
       <c r="K295" t="n">
         <v>4.15332</v>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.145781303816488</v>
+        <v>5.145866701308233</v>
       </c>
       <c r="C296" t="n">
-        <v>5.711633843076758</v>
+        <v>5.704541872107005</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1192262460792959</v>
+        <v>0.1208859620484892</v>
       </c>
       <c r="E296" t="n">
-        <v>4.680025245988717</v>
+        <v>4.676124350213628</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.27671</v>
+        <v>0.2765</v>
       </c>
       <c r="K296" t="n">
-        <v>4.18465</v>
+        <v>4.17488</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.861727476192867</v>
+        <v>3.860867390924683</v>
       </c>
       <c r="C297" t="n">
-        <v>4.003907561709252</v>
+        <v>3.99439278070115</v>
       </c>
       <c r="D297" t="n">
-        <v>2.957450346048596</v>
+        <v>2.963130911970113</v>
       </c>
       <c r="E297" t="n">
-        <v>4.087011140283647</v>
+        <v>4.089489702880766</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13201,7 +13201,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.31412</v>
+        <v>0.31366</v>
       </c>
       <c r="K297" t="n">
         <v>3.95179</v>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.44825143220806</v>
+        <v>2.447688568263784</v>
       </c>
       <c r="C298" t="n">
-        <v>1.070848483216258</v>
+        <v>1.080774310747556</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4401330553479132</v>
+        <v>0.4415338083751497</v>
       </c>
       <c r="E298" t="n">
-        <v>3.050866955338583</v>
+        <v>3.050164986972326</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13244,10 +13244,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.3825</v>
+        <v>0.38168</v>
       </c>
       <c r="K298" t="n">
-        <v>4.12313</v>
+        <v>4.13246</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.291305466989769</v>
+        <v>3.290765188280131</v>
       </c>
       <c r="C299" t="n">
-        <v>2.793684973416188</v>
+        <v>2.776448761234218</v>
       </c>
       <c r="D299" t="n">
-        <v>1.818814267202851</v>
+        <v>1.815992753390172</v>
       </c>
       <c r="E299" t="n">
-        <v>2.814114307218873</v>
+        <v>2.817724826808377</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13287,7 +13287,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.00859</v>
+        <v>-0.01211</v>
       </c>
       <c r="K299" t="n">
         <v>3.9212</v>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.51109410811168</v>
+        <v>4.510780893755384</v>
       </c>
       <c r="C300" t="n">
-        <v>3.713313697350351</v>
+        <v>3.661414965268328</v>
       </c>
       <c r="D300" t="n">
-        <v>3.89815881668325</v>
+        <v>3.895660906759169</v>
       </c>
       <c r="E300" t="n">
-        <v>3.747998470400171</v>
+        <v>3.745316448379565</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13330,7 +13330,7 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.00447</v>
+        <v>1.01079</v>
       </c>
       <c r="K300" t="n">
         <v>3.5896</v>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.779386350855752</v>
+        <v>4.781496650373596</v>
       </c>
       <c r="C301" t="n">
-        <v>3.180336507802806</v>
+        <v>3.146867624464611</v>
       </c>
       <c r="D301" t="n">
-        <v>5.326134837319318</v>
+        <v>5.311685154975243</v>
       </c>
       <c r="E301" t="n">
-        <v>1.883299976733732</v>
+        <v>1.885569388650987</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13373,7 +13373,7 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.9549</v>
+        <v>1.95363</v>
       </c>
       <c r="K301" t="n">
         <v>3.94713</v>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.339260208809637</v>
+        <v>5.339652535911354</v>
       </c>
       <c r="C302" t="n">
-        <v>3.380303501039306</v>
+        <v>3.380442580213749</v>
       </c>
       <c r="D302" t="n">
-        <v>4.101425147433124</v>
+        <v>4.101351007604359</v>
       </c>
       <c r="E302" t="n">
-        <v>1.200377743609327</v>
+        <v>1.207275946417541</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13416,10 +13416,10 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47771</v>
+        <v>1.47763</v>
       </c>
       <c r="K302" t="n">
-        <v>3.58984</v>
+        <v>3.5803</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.231415951270257</v>
+        <v>5.23134019791216</v>
       </c>
       <c r="C303" t="n">
-        <v>3.151931291387977</v>
+        <v>3.220991847048249</v>
       </c>
       <c r="D303" t="n">
-        <v>1.624776814622297</v>
+        <v>1.630777631710933</v>
       </c>
       <c r="E303" t="n">
-        <v>3.118981990323189</v>
+        <v>3.123896614544042</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13459,7 +13459,7 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98044</v>
+        <v>1.98012</v>
       </c>
       <c r="K303" t="n">
         <v>3.337</v>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.055609824894632</v>
+        <v>1.055273865723239</v>
       </c>
       <c r="C304" t="n">
-        <v>0.4998935330313925</v>
+        <v>0.528981008772611</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6707962877153251</v>
+        <v>-0.663975782577908</v>
       </c>
       <c r="E304" t="n">
-        <v>3.835682444900579</v>
+        <v>3.836890859937414</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13502,7 +13502,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.72951</v>
+        <v>2.72928</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.069720819667541</v>
+        <v>1.06977406242188</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1461271871531222</v>
+        <v>0.1560786331189723</v>
       </c>
       <c r="D305" t="n">
-        <v>2.196707161832978</v>
+        <v>2.194012201958939</v>
       </c>
       <c r="E305" t="n">
-        <v>1.965889419215916</v>
+        <v>1.969607590720801</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13545,7 +13545,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.50379</v>
+        <v>2.5036</v>
       </c>
       <c r="K305" t="n">
         <v>3.30021</v>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6313796907830405</v>
+        <v>0.6313286561376419</v>
       </c>
       <c r="C306" t="n">
-        <v>0.02997290191932844</v>
+        <v>0.04127286596800062</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.262692074741378</v>
+        <v>-1.262793889282587</v>
       </c>
       <c r="E306" t="n">
-        <v>2.322849285880579</v>
+        <v>2.327139126735855</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13588,7 +13588,7 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97693</v>
+        <v>2.97758</v>
       </c>
       <c r="K306" t="n">
         <v>3.02342</v>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.191129529396618</v>
+        <v>2.191196339512969</v>
       </c>
       <c r="C307" t="n">
-        <v>1.36460493563928</v>
+        <v>1.358058067827517</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.597971519336439</v>
+        <v>-2.597429826157605</v>
       </c>
       <c r="E307" t="n">
-        <v>3.143681576061064</v>
+        <v>3.146230529149419</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13631,7 +13631,7 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.46887</v>
+        <v>3.4689</v>
       </c>
       <c r="K307" t="n">
         <v>2.72177</v>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.772644918006594</v>
+        <v>1.772592391049477</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2728252964299793</v>
+        <v>0.2788478033717512</v>
       </c>
       <c r="D308" t="n">
-        <v>1.608422948790578</v>
+        <v>1.608667728129265</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799814973146765</v>
+        <v>4.800137520842451</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13674,7 +13674,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.01344</v>
+        <v>3.01338</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.14075015813986</v>
+        <v>3.139998427522106</v>
       </c>
       <c r="C309" t="n">
-        <v>2.240883722870657</v>
+        <v>2.231229734542306</v>
       </c>
       <c r="D309" t="n">
-        <v>0.56323974859116</v>
+        <v>0.5668899723477283</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405561561029848</v>
+        <v>5.403529239881988</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13717,7 +13717,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06829</v>
+        <v>3.06764</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.758046773060155</v>
+        <v>5.757295740506874</v>
       </c>
       <c r="C310" t="n">
-        <v>6.637851820273277</v>
+        <v>6.602631322277985</v>
       </c>
       <c r="D310" t="n">
-        <v>2.771267881514272</v>
+        <v>2.773925378445186</v>
       </c>
       <c r="E310" t="n">
-        <v>8.392253348831291</v>
+        <v>8.387094786854421</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13760,10 +13760,10 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.6121</v>
+        <v>2.6109</v>
       </c>
       <c r="K310" t="n">
-        <v>2.77728</v>
+        <v>2.76807</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.908904345920017</v>
+        <v>3.907813658183934</v>
       </c>
       <c r="C311" t="n">
-        <v>3.201083945147398</v>
+        <v>3.169538313783016</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6403401416306798</v>
+        <v>0.6451402837420961</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879741848641417</v>
+        <v>4.879856431537832</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13803,7 +13803,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99497</v>
+        <v>2.99259</v>
       </c>
       <c r="K311" t="n">
         <v>2.70029</v>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.037144665817372</v>
+        <v>4.036816938864241</v>
       </c>
       <c r="C312" t="n">
-        <v>2.364189410435502</v>
+        <v>2.305312357188627</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.063527794374852</v>
+        <v>-1.061464176900706</v>
       </c>
       <c r="E312" t="n">
-        <v>5.823847445899255</v>
+        <v>5.823903706846068</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13846,7 +13846,7 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.75324</v>
+        <v>2.75884</v>
       </c>
       <c r="K312" t="n">
         <v>2.99187</v>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.253506139499907</v>
+        <v>3.256030287451095</v>
       </c>
       <c r="C313" t="n">
-        <v>2.403026370583339</v>
+        <v>2.332860926407987</v>
       </c>
       <c r="D313" t="n">
-        <v>0.04528839111523908</v>
+        <v>0.03669194524609232</v>
       </c>
       <c r="E313" t="n">
-        <v>6.334329432668739</v>
+        <v>6.330242596771996</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13889,7 +13889,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.3945</v>
+        <v>2.39341</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.285721815568477</v>
+        <v>4.28634251119473</v>
       </c>
       <c r="C314" t="n">
-        <v>3.917028427398539</v>
+        <v>3.909115303044142</v>
       </c>
       <c r="D314" t="n">
-        <v>1.485126607810217</v>
+        <v>1.48200128056144</v>
       </c>
       <c r="E314" t="n">
-        <v>8.643075227423447</v>
+        <v>8.627127536158707</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13932,7 +13932,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.92599</v>
+        <v>1.92588</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.687417985445228</v>
+        <v>1.687481633591226</v>
       </c>
       <c r="C315" t="n">
-        <v>2.64593741877599</v>
+        <v>2.793195451491526</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9317884579545854</v>
+        <v>0.9311845343388914</v>
       </c>
       <c r="E315" t="n">
-        <v>4.023702458425382</v>
+        <v>4.02132527677832</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13975,7 +13975,7 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.40951</v>
+        <v>2.40892</v>
       </c>
       <c r="K315" t="n">
         <v>3.24698</v>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.655707893401171</v>
+        <v>2.655682016779926</v>
       </c>
       <c r="C316" t="n">
-        <v>2.862717871896181</v>
+        <v>2.929113531206951</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3982860815165967</v>
+        <v>0.3994381390890922</v>
       </c>
       <c r="E316" t="n">
-        <v>3.649025454529764</v>
+        <v>3.647840794773849</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14018,7 +14018,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62545</v>
+        <v>2.62454</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.793253614969498</v>
+        <v>8.793905174479555</v>
       </c>
       <c r="C317" t="n">
-        <v>9.070376163717997</v>
+        <v>9.055549295619647</v>
       </c>
       <c r="D317" t="n">
-        <v>0.383773611397964</v>
+        <v>0.3785335478807328</v>
       </c>
       <c r="E317" t="n">
-        <v>7.311095553416358</v>
+        <v>7.302275682025261</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14061,7 +14061,7 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43439</v>
+        <v>3.4343</v>
       </c>
       <c r="K317" t="n">
         <v>3.28303</v>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.376528170527849</v>
+        <v>4.37632473313867</v>
       </c>
       <c r="C318" t="n">
-        <v>5.380693007912907</v>
+        <v>5.418302814901543</v>
       </c>
       <c r="D318" t="n">
-        <v>2.152373987453626</v>
+        <v>2.148714148316766</v>
       </c>
       <c r="E318" t="n">
-        <v>5.209576276321748</v>
+        <v>5.204643896845873</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14104,7 +14104,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.3716</v>
+        <v>3.37305</v>
       </c>
       <c r="K318" t="n">
         <v>3.52516</v>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.194789103861862</v>
+        <v>4.194661943946154</v>
       </c>
       <c r="C319" t="n">
-        <v>3.332426339182448</v>
+        <v>3.365579613308212</v>
       </c>
       <c r="D319" t="n">
-        <v>2.731130799617776</v>
+        <v>2.730735513659965</v>
       </c>
       <c r="E319" t="n">
-        <v>3.723266747459419</v>
+        <v>3.728200291499939</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14147,7 +14147,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.14665</v>
+        <v>3.14713</v>
       </c>
       <c r="K319" t="n">
         <v>3.82042</v>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.753347921463604</v>
+        <v>6.753226661757461</v>
       </c>
       <c r="C320" t="n">
-        <v>6.783856992963422</v>
+        <v>6.754802518520941</v>
       </c>
       <c r="D320" t="n">
-        <v>2.22413311079992</v>
+        <v>2.221568560954479</v>
       </c>
       <c r="E320" t="n">
-        <v>3.067079392964822</v>
+        <v>3.07360151915308</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14190,7 +14190,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.12982</v>
+        <v>3.13086</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.928975762070676</v>
+        <v>5.928141263290732</v>
       </c>
       <c r="C321" t="n">
-        <v>4.665266040489957</v>
+        <v>4.639185570815196</v>
       </c>
       <c r="D321" t="n">
-        <v>1.458018836021591</v>
+        <v>1.463002621569554</v>
       </c>
       <c r="E321" t="n">
-        <v>2.667825166224835</v>
+        <v>2.677858528989496</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14233,7 +14233,7 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.17703</v>
+        <v>3.17612</v>
       </c>
       <c r="K321" t="n">
         <v>3.64797</v>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.552992793690392</v>
+        <v>5.551552429852813</v>
       </c>
       <c r="C322" t="n">
-        <v>3.517011588870123</v>
+        <v>3.514440966278354</v>
       </c>
       <c r="D322" t="n">
-        <v>0.06456408498720645</v>
+        <v>0.0733496059205363</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5123699594380415</v>
+        <v>-0.4949157708735497</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14276,10 +14276,10 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.79708</v>
+        <v>3.79717</v>
       </c>
       <c r="K322" t="n">
-        <v>3.73954</v>
+        <v>3.74826</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.332827258365679</v>
+        <v>4.331036508712982</v>
       </c>
       <c r="C323" t="n">
-        <v>5.210423283965082</v>
+        <v>5.151075606369759</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8369877519067925</v>
+        <v>0.8493659008953491</v>
       </c>
       <c r="E323" t="n">
-        <v>4.171982430236088</v>
+        <v>4.177642499901313</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14319,7 +14319,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.93272</v>
+        <v>3.92594</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14338,16 +14338,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.537648170077049</v>
+        <v>7.536859056493306</v>
       </c>
       <c r="C324" t="n">
-        <v>6.994318239842823</v>
+        <v>6.845369550336788</v>
       </c>
       <c r="D324" t="n">
-        <v>3.824966203956781</v>
+        <v>3.83073629634465</v>
       </c>
       <c r="E324" t="n">
-        <v>2.189378793936991</v>
+        <v>2.200279136578231</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14362,10 +14362,10 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.68735</v>
+        <v>3.69244</v>
       </c>
       <c r="K324" t="n">
-        <v>3.45127</v>
+        <v>3.45994</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14381,16 +14381,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.077428659383544</v>
+        <v>6.080899979734644</v>
       </c>
       <c r="C325" t="n">
-        <v>5.60425117356147</v>
+        <v>5.490674436099141</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1571476996986343</v>
+        <v>0.1497167215731565</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892633545482748</v>
+        <v>2.895939967957251</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14405,7 +14405,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.30365</v>
+        <v>3.3053</v>
       </c>
       <c r="K325" t="n">
         <v>3.22274</v>
@@ -14424,16 +14424,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.854969678039268</v>
+        <v>5.855836356597321</v>
       </c>
       <c r="C326" t="n">
-        <v>4.984020264298961</v>
+        <v>5.019799316268281</v>
       </c>
       <c r="D326" t="n">
-        <v>0.7928695940304875</v>
+        <v>0.789879275205041</v>
       </c>
       <c r="E326" t="n">
-        <v>4.470868138703077</v>
+        <v>4.460239918311548</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14448,7 +14448,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86421</v>
+        <v>2.86364</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14467,16 +14467,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.916815172012639</v>
+        <v>9.917091185680892</v>
       </c>
       <c r="C327" t="n">
-        <v>9.271172289205797</v>
+        <v>9.497299830602568</v>
       </c>
       <c r="D327" t="n">
-        <v>2.691940082080446</v>
+        <v>2.686125129780526</v>
       </c>
       <c r="E327" t="n">
-        <v>7.795424121030936</v>
+        <v>7.782870651083984</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14491,7 +14491,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05652</v>
+        <v>2.05531</v>
       </c>
       <c r="K327" t="n">
         <v>2.63791</v>
@@ -14510,16 +14510,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41583027803883</v>
+        <v>10.41635031678989</v>
       </c>
       <c r="C328" t="n">
-        <v>9.054822735522938</v>
+        <v>9.135368328714799</v>
       </c>
       <c r="D328" t="n">
-        <v>3.144581916910494</v>
+        <v>3.136416770461659</v>
       </c>
       <c r="E328" t="n">
-        <v>7.358269334768885</v>
+        <v>7.349175226322102</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14534,7 +14534,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82336</v>
+        <v>1.82223</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14553,16 +14553,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.002915736085866</v>
+        <v>4.00383784380387</v>
       </c>
       <c r="C329" t="n">
-        <v>3.011478636301446</v>
+        <v>3.071700808509514</v>
       </c>
       <c r="D329" t="n">
-        <v>2.837327572664994</v>
+        <v>2.829617772323245</v>
       </c>
       <c r="E329" t="n">
-        <v>3.595377905760699</v>
+        <v>3.589189447127805</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14577,7 +14577,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.15874</v>
+        <v>1.159</v>
       </c>
       <c r="K329" t="n">
         <v>2.05076</v>
@@ -14596,16 +14596,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.273280616022237</v>
+        <v>6.273159306019549</v>
       </c>
       <c r="C330" t="n">
-        <v>5.546430152401305</v>
+        <v>5.610714510300019</v>
       </c>
       <c r="D330" t="n">
-        <v>1.312178171523914</v>
+        <v>1.306260262502579</v>
       </c>
       <c r="E330" t="n">
-        <v>5.628383318639862</v>
+        <v>5.623718439720138</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14620,7 +14620,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15309</v>
+        <v>1.15519</v>
       </c>
       <c r="K330" t="n">
         <v>1.53231</v>
@@ -14639,16 +14639,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.980896209812481</v>
+        <v>5.980763659023691</v>
       </c>
       <c r="C331" t="n">
-        <v>7.426262108607196</v>
+        <v>7.420528558521355</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.072232535238149</v>
+        <v>-1.073852345042514</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981442962538485</v>
+        <v>4.981104429525818</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14663,7 +14663,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.72428</v>
+        <v>0.7251300000000001</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14682,16 +14682,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.252654482153928</v>
+        <v>4.252462891781494</v>
       </c>
       <c r="C332" t="n">
-        <v>4.012586608928848</v>
+        <v>4.006877743507342</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.621655467496796</v>
+        <v>-1.623509131253398</v>
       </c>
       <c r="E332" t="n">
-        <v>4.512034174940216</v>
+        <v>4.510285228801303</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14706,7 +14706,7 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13596</v>
+        <v>1.13796</v>
       </c>
       <c r="K332" t="n">
         <v>0.95682</v>
@@ -14725,16 +14725,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.825407961648764</v>
+        <v>3.824500000890207</v>
       </c>
       <c r="C333" t="n">
-        <v>3.772285754869964</v>
+        <v>3.740294025494917</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.158220126836675</v>
+        <v>-3.155536287875604</v>
       </c>
       <c r="E333" t="n">
-        <v>4.43559720351947</v>
+        <v>4.432508998310891</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14749,7 +14749,7 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.19219</v>
+        <v>1.19144</v>
       </c>
       <c r="K333" t="n">
         <v>0.54018</v>
@@ -14768,16 +14768,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.906540538136748</v>
+        <v>2.904296048588884</v>
       </c>
       <c r="C334" t="n">
-        <v>4.921163165443709</v>
+        <v>4.878701228408611</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.599191963386126</v>
+        <v>-1.585815246689759</v>
       </c>
       <c r="E334" t="n">
-        <v>5.112953084893501</v>
+        <v>5.116649687179353</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14792,10 +14792,10 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05794</v>
+        <v>1.05912</v>
       </c>
       <c r="K334" t="n">
-        <v>-0.05882</v>
+        <v>-0.06722</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -14811,16 +14811,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.703972466781558</v>
+        <v>3.701639304893045</v>
       </c>
       <c r="C335" t="n">
-        <v>1.79281352475662</v>
+        <v>1.701798191537263</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.591160717022412</v>
+        <v>-2.572997658478371</v>
       </c>
       <c r="E335" t="n">
-        <v>3.833862552785328</v>
+        <v>3.832846775515364</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14835,7 +14835,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.73723</v>
+        <v>1.72879</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14854,16 +14854,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.723558437886698</v>
+        <v>3.722021378273421</v>
       </c>
       <c r="C336" t="n">
-        <v>3.863691346764586</v>
+        <v>3.636130442555086</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.338404904162029</v>
+        <v>-3.324563565049932</v>
       </c>
       <c r="E336" t="n">
-        <v>3.490905640757491</v>
+        <v>3.49375262278353</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14878,10 +14878,10 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.431</v>
+        <v>-2.42959</v>
       </c>
       <c r="K336" t="n">
-        <v>-0.285</v>
+        <v>-0.29335</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14897,16 +14897,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.993092881985126</v>
+        <v>1.998037942838171</v>
       </c>
       <c r="C337" t="n">
-        <v>1.400085676157103</v>
+        <v>1.184265316227751</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.140048076028057</v>
+        <v>-3.154691047912772</v>
       </c>
       <c r="E337" t="n">
-        <v>3.629676879858912</v>
+        <v>3.624568214251456</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14921,7 +14921,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74639</v>
+        <v>2.75018</v>
       </c>
       <c r="K337" t="n">
         <v>-0.32644</v>
@@ -14940,16 +14940,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.292548216096258</v>
+        <v>3.293704835338374</v>
       </c>
       <c r="C338" t="n">
-        <v>2.206970323087787</v>
+        <v>2.21792411589905</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.364579912264286</v>
+        <v>-2.36842517331709</v>
       </c>
       <c r="E338" t="n">
-        <v>1.875273428151503</v>
+        <v>1.878061967794076</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14964,7 +14964,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.53448</v>
+        <v>-0.53416</v>
       </c>
       <c r="K338" t="n">
         <v>-0.36041</v>
@@ -14983,16 +14983,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6633177768283094</v>
+        <v>0.6635308280274366</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.192234717572195</v>
+        <v>-1.805457119459419</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.148381568819957</v>
+        <v>-2.152154547381979</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.603085014146465</v>
+        <v>-0.5948637049804639</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15007,7 +15007,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09538000000000001</v>
+        <v>-0.09662999999999999</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15026,16 +15026,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.590619821141483</v>
+        <v>3.590958068009598</v>
       </c>
       <c r="C340" t="n">
-        <v>0.443995546326148</v>
+        <v>0.5976065562043997</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.725039901989845</v>
+        <v>-2.733397907849533</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.14634254007232</v>
+        <v>-1.139999364031108</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15050,7 +15050,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.5298</v>
+        <v>-0.53141</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15069,16 +15069,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.791076972711572</v>
+        <v>4.792246381631826</v>
       </c>
       <c r="C341" t="n">
-        <v>1.327364983590518</v>
+        <v>1.355830416664272</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.052493784463195</v>
+        <v>-3.055263807324626</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702223438164374</v>
+        <v>1.702079041667393</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15093,10 +15093,10 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.2286</v>
+        <v>-1.22722</v>
       </c>
       <c r="K341" t="n">
-        <v>0.40191</v>
+        <v>0.41028</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15112,16 +15112,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.675197612433514</v>
+        <v>5.674946672858061</v>
       </c>
       <c r="C342" t="n">
-        <v>2.74278502805958</v>
+        <v>2.834022788052959</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7359936492112307</v>
+        <v>-0.7376028715414873</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1288867859752463</v>
+        <v>-0.1267502614134219</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15136,7 +15136,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44703</v>
+        <v>-1.44475</v>
       </c>
       <c r="K342" t="n">
         <v>0.6959</v>
@@ -15155,16 +15155,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.833047027059246</v>
+        <v>5.83279510236614</v>
       </c>
       <c r="C343" t="n">
-        <v>1.504300528068891</v>
+        <v>1.552891112871024</v>
       </c>
       <c r="D343" t="n">
-        <v>2.370154051051321</v>
+        <v>2.369545528151518</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6831017748200496</v>
+        <v>0.6839609689418547</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15179,7 +15179,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09714</v>
+        <v>-1.09603</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15198,16 +15198,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.955323343851515</v>
+        <v>5.954981614044619</v>
       </c>
       <c r="C344" t="n">
-        <v>3.893506573478422</v>
+        <v>3.848104243802264</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9060527112732641</v>
+        <v>0.8993683671500774</v>
       </c>
       <c r="E344" t="n">
-        <v>2.71363390478887</v>
+        <v>2.710593865805677</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15222,7 +15222,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.75504</v>
+        <v>-0.7524</v>
       </c>
       <c r="K344" t="n">
         <v>1.21614</v>
@@ -15241,16 +15241,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26659078567886</v>
+        <v>10.26509147409811</v>
       </c>
       <c r="C345" t="n">
-        <v>7.55455530243907</v>
+        <v>7.467941414539792</v>
       </c>
       <c r="D345" t="n">
-        <v>7.740984769976977</v>
+        <v>7.741972262528818</v>
       </c>
       <c r="E345" t="n">
-        <v>2.755084098846816</v>
+        <v>2.748527636587594</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15265,7 +15265,7 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.7005</v>
+        <v>-0.69997</v>
       </c>
       <c r="K345" t="n">
         <v>1.67058</v>
@@ -15284,16 +15284,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.150774314412018</v>
+        <v>2.148064370770197</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.3954263203203134</v>
+        <v>-0.4417575299695775</v>
       </c>
       <c r="D346" t="n">
-        <v>1.668064470904307</v>
+        <v>1.684197168800416</v>
       </c>
       <c r="E346" t="n">
-        <v>2.258028224129904</v>
+        <v>2.257585157175046</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15308,7 +15308,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.13013</v>
+        <v>-0.1283</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15327,16 +15327,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.148673845296492</v>
+        <v>5.145725989344085</v>
       </c>
       <c r="C347" t="n">
-        <v>3.140020784124942</v>
+        <v>2.987522981652257</v>
       </c>
       <c r="D347" t="n">
-        <v>4.038146997584735</v>
+        <v>4.064518958398611</v>
       </c>
       <c r="E347" t="n">
-        <v>2.138983335260414</v>
+        <v>2.146288953073427</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15351,7 +15351,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.01931</v>
+        <v>-1.03404</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15370,16 +15370,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.564977224024757</v>
+        <v>3.562587603286316</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.651297271513307</v>
+        <v>-1.021789069174361</v>
       </c>
       <c r="D348" t="n">
-        <v>4.252432373094073</v>
+        <v>4.276620242947704</v>
       </c>
       <c r="E348" t="n">
-        <v>3.124660704508875</v>
+        <v>3.126459976472895</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15394,7 +15394,7 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.98953</v>
+        <v>2.99028</v>
       </c>
       <c r="K348" t="n">
         <v>2.52186</v>
@@ -15413,16 +15413,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.716395979144019</v>
+        <v>6.724435193395806</v>
       </c>
       <c r="C349" t="n">
-        <v>6.132418487760538</v>
+        <v>5.756116802183286</v>
       </c>
       <c r="D349" t="n">
-        <v>6.31296140340325</v>
+        <v>6.277076141112858</v>
       </c>
       <c r="E349" t="n">
-        <v>6.028787457515983</v>
+        <v>6.029687893440827</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15437,7 +15437,7 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.39323</v>
+        <v>-1.38906</v>
       </c>
       <c r="K349" t="n">
         <v>2.79644</v>
@@ -15456,16 +15456,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.37712030615578</v>
+        <v>5.379120842480756</v>
       </c>
       <c r="C350" t="n">
-        <v>3.215166680155868</v>
+        <v>3.240541805991537</v>
       </c>
       <c r="D350" t="n">
-        <v>6.183234028769236</v>
+        <v>6.173738971024312</v>
       </c>
       <c r="E350" t="n">
-        <v>6.715042785558123</v>
+        <v>6.728838825390659</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15480,7 +15480,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.55891</v>
+        <v>2.55949</v>
       </c>
       <c r="K350" t="n">
         <v>3.17127</v>
@@ -15499,16 +15499,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.025881695023294</v>
+        <v>6.02647082462997</v>
       </c>
       <c r="C351" t="n">
-        <v>4.302728417201873</v>
+        <v>5.020565281839207</v>
       </c>
       <c r="D351" t="n">
-        <v>1.67389903059989</v>
+        <v>1.663095094460698</v>
       </c>
       <c r="E351" t="n">
-        <v>8.080534669008266</v>
+        <v>8.087827338972065</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15523,7 +15523,7 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.77915</v>
+        <v>1.77895</v>
       </c>
       <c r="K351" t="n">
         <v>2.91653</v>
@@ -15542,16 +15542,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26500601512263</v>
+        <v>-53.26495372520469</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.30428639421412</v>
+        <v>-49.1657373028236</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.33170543451237</v>
+        <v>-44.34122311693373</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.879076594088713</v>
+        <v>-1.881649032722743</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15566,7 +15566,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.563</v>
+        <v>1.56347</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15585,16 +15585,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40226336867063</v>
+        <v>-99.40225466388813</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11751099598803</v>
+        <v>-98.11615437130587</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69240566802783</v>
+        <v>-88.69350752237378</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50816779483103</v>
+        <v>-52.51095054877089</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15609,10 +15609,10 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.2874</v>
+        <v>-49.2837</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.87916</v>
+        <v>-38.88426</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15628,16 +15628,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80419835319115</v>
+        <v>-98.80420609347949</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98508662280753</v>
+        <v>-95.97857276648647</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16187156344282</v>
+        <v>-82.16238686265498</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.7022057696763</v>
+        <v>-50.70529307249665</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15652,7 +15652,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.4986</v>
+        <v>-69.49245999999999</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15671,16 +15671,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13270030323417</v>
+        <v>-98.13271457454061</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.35198040598169</v>
+        <v>-94.34954161870294</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41248703177605</v>
+        <v>-81.41199317911291</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98588359988828</v>
+        <v>-42.99008427377383</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15695,7 +15695,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.09050999999999</v>
+        <v>-70.08623</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15714,16 +15714,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74181767164347</v>
+        <v>-97.74183645487703</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62874179485657</v>
+        <v>-93.6311989125841</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64127402101019</v>
+        <v>-75.64290756115453</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11068925099725</v>
+        <v>-43.11200391157312</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15738,7 +15738,7 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73656</v>
+        <v>-74.73094</v>
       </c>
       <c r="K356" t="n">
         <v>-30.14584</v>
@@ -15757,16 +15757,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46153281144258</v>
+        <v>-97.4616014495206</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99077289678384</v>
+        <v>-90.99932515789051</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.19111487501441</v>
+        <v>-74.18825042785828</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65723640903332</v>
+        <v>-45.66225989971122</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15781,7 +15781,7 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.87519</v>
+        <v>-74.87716</v>
       </c>
       <c r="K357" t="n">
         <v>-25.53877</v>
@@ -15800,16 +15800,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43053592994563</v>
+        <v>-97.43061663969202</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90083800460579</v>
+        <v>-89.91108623926705</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.96592074306385</v>
+        <v>-74.96053596841206</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.1678490103718</v>
+        <v>-40.17382771321311</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15824,7 +15824,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.51188</v>
+        <v>-76.51204</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15843,16 +15843,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07988089365546</v>
+        <v>-90.08025583446543</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.37010146957549</v>
+        <v>-81.42214048606569</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.97695924187204</v>
+        <v>-74.96722867510339</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34405166701689</v>
+        <v>-31.34691439353869</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15867,7 +15867,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.63415999999999</v>
+        <v>-66.67464</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15886,16 +15886,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.76606622717814</v>
+        <v>-76.7669079311802</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.58312468143366</v>
+        <v>-65.77290616070684</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.85387471523372</v>
+        <v>-71.84253630769398</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.59340514612708</v>
+        <v>-12.60294301340807</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15910,10 +15910,10 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.85376</v>
+        <v>-56.84703</v>
       </c>
       <c r="K360" t="n">
-        <v>-20.39193</v>
+        <v>-20.38373</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -15929,16 +15929,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.82004103124542</v>
+        <v>-74.81724345701373</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.35263017179476</v>
+        <v>-66.50701555901139</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.13263492840348</v>
+        <v>-70.14911584532703</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80569329592696</v>
+        <v>-16.80039716765983</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>
@@ -15953,7 +15953,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.24671</v>
+        <v>-53.23872</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68992483843196</v>
+        <v>11.71016866931627</v>
       </c>
       <c r="C242" t="n">
-        <v>11.36348062600854</v>
+        <v>11.38244581042254</v>
       </c>
       <c r="D242" t="n">
-        <v>10.12827691184035</v>
+        <v>10.12811720377944</v>
       </c>
       <c r="E242" t="n">
-        <v>7.269157404840976</v>
+        <v>7.271477990307007</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.27626754053708</v>
+        <v>12.22857736153817</v>
       </c>
       <c r="C243" t="n">
-        <v>12.43403543014179</v>
+        <v>12.44505906206748</v>
       </c>
       <c r="D243" t="n">
-        <v>7.786750272922438</v>
+        <v>7.777641032710769</v>
       </c>
       <c r="E243" t="n">
-        <v>8.999786584410208</v>
+        <v>9.003044568338003</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.974043573307928</v>
+        <v>3.854055979005855</v>
       </c>
       <c r="C244" t="n">
-        <v>7.191370549666143</v>
+        <v>7.178997707226298</v>
       </c>
       <c r="D244" t="n">
-        <v>6.050921661423803</v>
+        <v>6.056376224786963</v>
       </c>
       <c r="E244" t="n">
-        <v>8.717951392315104</v>
+        <v>8.720506163443954</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.843821954797022</v>
+        <v>3.919945896285681</v>
       </c>
       <c r="C245" t="n">
-        <v>7.420447145364917</v>
+        <v>7.411661859365326</v>
       </c>
       <c r="D245" t="n">
-        <v>4.826980577035078</v>
+        <v>4.840501404801079</v>
       </c>
       <c r="E245" t="n">
-        <v>8.555894066622404</v>
+        <v>8.568276559526655</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1726177118588135</v>
+        <v>0.1618352964142256</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6839599657378459</v>
+        <v>-0.7063295447753304</v>
       </c>
       <c r="D246" t="n">
-        <v>1.841584152454345</v>
+        <v>1.858764443741423</v>
       </c>
       <c r="E246" t="n">
-        <v>9.475524268795589</v>
+        <v>9.482856861643318</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.363678083425345</v>
+        <v>-0.4034754992091161</v>
       </c>
       <c r="C247" t="n">
-        <v>2.279991089277633</v>
+        <v>2.237749626042596</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.589513724078673</v>
+        <v>-1.570262026850711</v>
       </c>
       <c r="E247" t="n">
-        <v>9.111535844460917</v>
+        <v>9.112564450396498</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11070,16 +11070,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.551727144206871</v>
+        <v>-1.567700161856445</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.317795233951958</v>
+        <v>-2.342540429284978</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.089253412723547</v>
+        <v>-3.086830385091022</v>
       </c>
       <c r="E248" t="n">
-        <v>8.157455600800279</v>
+        <v>8.157267361039411</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.452831704132174</v>
+        <v>1.48741787690001</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.233331214749477</v>
+        <v>-0.2506136104249213</v>
       </c>
       <c r="D249" t="n">
-        <v>2.489415575444354</v>
+        <v>2.487778792576956</v>
       </c>
       <c r="E249" t="n">
-        <v>7.159705907638059</v>
+        <v>7.157624723066358</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.835365408902148</v>
+        <v>4.872531786163536</v>
       </c>
       <c r="C250" t="n">
-        <v>4.669575287126904</v>
+        <v>4.676653474707315</v>
       </c>
       <c r="D250" t="n">
-        <v>6.323190830349601</v>
+        <v>6.312100838456591</v>
       </c>
       <c r="E250" t="n">
-        <v>8.292084757591889</v>
+        <v>8.292994008993348</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8337934955781723</v>
+        <v>0.8662932287683223</v>
       </c>
       <c r="C251" t="n">
-        <v>1.474362445723343</v>
+        <v>1.469746968559371</v>
       </c>
       <c r="D251" t="n">
-        <v>2.65919699752859</v>
+        <v>2.67311135364714</v>
       </c>
       <c r="E251" t="n">
-        <v>8.436154125890095</v>
+        <v>8.438941114966436</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.654106691389369</v>
+        <v>3.670169852342897</v>
       </c>
       <c r="C252" t="n">
-        <v>2.980363145273546</v>
+        <v>2.971190067831131</v>
       </c>
       <c r="D252" t="n">
-        <v>3.950759221323397</v>
+        <v>3.946184305067924</v>
       </c>
       <c r="E252" t="n">
-        <v>10.18488406892764</v>
+        <v>10.19714437387185</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.125343074441304</v>
+        <v>7.061833970429965</v>
       </c>
       <c r="C253" t="n">
-        <v>8.434242813334825</v>
+        <v>8.442585069309061</v>
       </c>
       <c r="D253" t="n">
-        <v>3.608400423111768</v>
+        <v>3.576931512963344</v>
       </c>
       <c r="E253" t="n">
-        <v>7.945468756824625</v>
+        <v>7.945441217350524</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.374789826971839</v>
+        <v>7.417014569543912</v>
       </c>
       <c r="C254" t="n">
-        <v>7.321333841067479</v>
+        <v>7.326462717908977</v>
       </c>
       <c r="D254" t="n">
-        <v>5.725297777085103</v>
+        <v>5.713447254941295</v>
       </c>
       <c r="E254" t="n">
-        <v>8.188927420071291</v>
+        <v>8.190919043807021</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449910660088575</v>
+        <v>5.43929929457736</v>
       </c>
       <c r="C255" t="n">
-        <v>5.900527365288899</v>
+        <v>5.901274466062523</v>
       </c>
       <c r="D255" t="n">
-        <v>2.550029914993224</v>
+        <v>2.551733037113424</v>
       </c>
       <c r="E255" t="n">
-        <v>6.398471540386952</v>
+        <v>6.399370109768432</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.70729571480387</v>
+        <v>11.75202687399277</v>
       </c>
       <c r="C256" t="n">
-        <v>9.859853126744422</v>
+        <v>9.879426290628812</v>
       </c>
       <c r="D256" t="n">
-        <v>5.658353630827739</v>
+        <v>5.653819370547652</v>
       </c>
       <c r="E256" t="n">
-        <v>7.15711173318978</v>
+        <v>7.160128786987485</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.774012672675703</v>
+        <v>8.761499416147323</v>
       </c>
       <c r="C257" t="n">
-        <v>8.539223469662982</v>
+        <v>8.540541310522487</v>
       </c>
       <c r="D257" t="n">
-        <v>5.099067537245383</v>
+        <v>5.098321191432786</v>
       </c>
       <c r="E257" t="n">
-        <v>7.46478767977059</v>
+        <v>7.460745796867996</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.92035233898017</v>
+        <v>11.91515470470923</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74811892381931</v>
+        <v>11.75086674751236</v>
       </c>
       <c r="D258" t="n">
-        <v>8.776974575011899</v>
+        <v>8.776158494564656</v>
       </c>
       <c r="E258" t="n">
-        <v>7.926318545559274</v>
+        <v>7.926608321817907</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45468184795004</v>
+        <v>11.48830576637412</v>
       </c>
       <c r="C259" t="n">
-        <v>9.112585063312938</v>
+        <v>9.117604890954434</v>
       </c>
       <c r="D259" t="n">
-        <v>7.825112590440408</v>
+        <v>7.826286243254543</v>
       </c>
       <c r="E259" t="n">
-        <v>8.255702710197443</v>
+        <v>8.258114039570819</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.846068889422032</v>
+        <v>8.831230930059665</v>
       </c>
       <c r="C260" t="n">
-        <v>9.297392625404054</v>
+        <v>9.293276679624341</v>
       </c>
       <c r="D260" t="n">
-        <v>8.082914665307639</v>
+        <v>8.094111388668246</v>
       </c>
       <c r="E260" t="n">
-        <v>8.65748806069584</v>
+        <v>8.661521931139138</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52739962152307</v>
+        <v>12.53590313809032</v>
       </c>
       <c r="C261" t="n">
-        <v>10.29910637514733</v>
+        <v>10.30559749109925</v>
       </c>
       <c r="D261" t="n">
-        <v>5.620813524353463</v>
+        <v>5.620305588568786</v>
       </c>
       <c r="E261" t="n">
-        <v>10.39530937181559</v>
+        <v>10.40184581414734</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.793118679594712</v>
+        <v>6.764151242649552</v>
       </c>
       <c r="C262" t="n">
-        <v>6.493047727893364</v>
+        <v>6.489713886718906</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8049473598035095</v>
+        <v>-0.8032510361097089</v>
       </c>
       <c r="E262" t="n">
-        <v>8.714271387702311</v>
+        <v>8.714485048059739</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.091675509320908</v>
+        <v>9.080940818823224</v>
       </c>
       <c r="C263" t="n">
-        <v>7.4469470830135</v>
+        <v>7.448662236485637</v>
       </c>
       <c r="D263" t="n">
-        <v>3.162900394096302</v>
+        <v>3.175338880698386</v>
       </c>
       <c r="E263" t="n">
-        <v>8.725412748696581</v>
+        <v>8.720923996499064</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42474591010869</v>
+        <v>13.49225747515197</v>
       </c>
       <c r="C264" t="n">
-        <v>11.22466013091263</v>
+        <v>11.24244139717141</v>
       </c>
       <c r="D264" t="n">
-        <v>4.654483390387076</v>
+        <v>4.648343832907664</v>
       </c>
       <c r="E264" t="n">
-        <v>6.331375519106341</v>
+        <v>6.318243196739126</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.05502016385149</v>
+        <v>8.071761115626552</v>
       </c>
       <c r="C265" t="n">
-        <v>5.782483068233213</v>
+        <v>5.784886108924581</v>
       </c>
       <c r="D265" t="n">
-        <v>2.718104583412195</v>
+        <v>2.703670739040387</v>
       </c>
       <c r="E265" t="n">
-        <v>7.363759857542873</v>
+        <v>7.354919137933913</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.578522914629833</v>
+        <v>2.550194018006158</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.1897500901190008</v>
+        <v>-0.2087926254226602</v>
       </c>
       <c r="D266" t="n">
-        <v>2.187857389933012</v>
+        <v>2.189064805469076</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01143640852598</v>
+        <v>12.01490879643654</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.09897291766519</v>
+        <v>5.053987041299068</v>
       </c>
       <c r="C267" t="n">
-        <v>1.670013766977574</v>
+        <v>1.656602972291865</v>
       </c>
       <c r="D267" t="n">
-        <v>3.453551296123103</v>
+        <v>3.458518746272365</v>
       </c>
       <c r="E267" t="n">
-        <v>13.52574624839236</v>
+        <v>13.53312271647575</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.829507406188172</v>
+        <v>5.846291465539499</v>
       </c>
       <c r="C268" t="n">
-        <v>3.403417167034517</v>
+        <v>3.409240916096601</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9072527018248566</v>
+        <v>0.9090030300144436</v>
       </c>
       <c r="E268" t="n">
-        <v>15.09962253005856</v>
+        <v>15.10578324311751</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.373301440416831</v>
+        <v>2.351157895416933</v>
       </c>
       <c r="C269" t="n">
-        <v>0.721419468322293</v>
+        <v>0.7112370807866419</v>
       </c>
       <c r="D269" t="n">
-        <v>2.945918902381228</v>
+        <v>2.946355444815696</v>
       </c>
       <c r="E269" t="n">
-        <v>10.14146272868868</v>
+        <v>10.13571613129647</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.698975364867739</v>
+        <v>2.684665254542318</v>
       </c>
       <c r="C270" t="n">
-        <v>0.351676338410245</v>
+        <v>0.3500440403461758</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.523443829445303</v>
+        <v>-1.525791252146547</v>
       </c>
       <c r="E270" t="n">
-        <v>11.78179299915805</v>
+        <v>11.77794552759612</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.118510270104681</v>
+        <v>4.184465576043928</v>
       </c>
       <c r="C271" t="n">
-        <v>3.26607030578332</v>
+        <v>3.278671919901366</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.177173178113866</v>
+        <v>-1.181540044712059</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72337530367955</v>
+        <v>12.72485052363144</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.81583745826688</v>
+        <v>3.857776779071331</v>
       </c>
       <c r="C272" t="n">
-        <v>2.8252403248477</v>
+        <v>2.833835001272256</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.92070980245891</v>
+        <v>-2.917050632060991</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49043195947355</v>
+        <v>12.49493585235011</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.044852516298779</v>
+        <v>2.049131610697907</v>
       </c>
       <c r="C273" t="n">
-        <v>2.700532332379479</v>
+        <v>2.708698913558361</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1108363405218582</v>
+        <v>-0.1080336463552212</v>
       </c>
       <c r="E273" t="n">
-        <v>12.15264147623145</v>
+        <v>12.15917074670252</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1466298514992359</v>
+        <v>-0.1606028269651394</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2223891517783239</v>
+        <v>0.2202025010973996</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0392952665049906</v>
+        <v>0.03746964959043808</v>
       </c>
       <c r="E274" t="n">
-        <v>11.91912623343714</v>
+        <v>11.92506614952375</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3229098304281308</v>
+        <v>-0.337489526956225</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4741188085669812</v>
+        <v>-0.4732307600819996</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.026644695937407</v>
+        <v>-2.01811720341063</v>
       </c>
       <c r="E275" t="n">
-        <v>10.8975420006656</v>
+        <v>10.90355496880646</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994881246073345</v>
+        <v>-4.047987370613981</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.152100101828338</v>
+        <v>-4.16619233205039</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.712178964755786</v>
+        <v>-3.721758838446432</v>
       </c>
       <c r="E276" t="n">
-        <v>8.912969444179385</v>
+        <v>8.913007673781003</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.363111156896126</v>
+        <v>-3.39584065057964</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.720825651898196</v>
+        <v>-3.73042389983661</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.384945572229514</v>
+        <v>-3.411027757751339</v>
       </c>
       <c r="E277" t="n">
-        <v>10.77848099160279</v>
+        <v>10.78828780871561</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.268371992848951</v>
+        <v>3.309825739702332</v>
       </c>
       <c r="C278" t="n">
-        <v>3.592827003630594</v>
+        <v>3.594116246809009</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.612570285423376</v>
+        <v>-1.59727098231166</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127317719603864</v>
+        <v>6.12773418386765</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1256523063747905</v>
+        <v>-0.1762246206749363</v>
       </c>
       <c r="C279" t="n">
-        <v>0.482547579104553</v>
+        <v>0.4790631754532093</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3290458246748562</v>
+        <v>-0.3157210012724287</v>
       </c>
       <c r="E279" t="n">
-        <v>4.006950494299444</v>
+        <v>4.003102049136253</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.848876163615176</v>
+        <v>-1.895550877218843</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.144670495986445</v>
+        <v>-2.152099165602017</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7972816355882872</v>
+        <v>-0.7906263908305733</v>
       </c>
       <c r="E280" t="n">
-        <v>0.481390173681695</v>
+        <v>0.4734177886642321</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.168929065183001</v>
+        <v>2.192806142893855</v>
       </c>
       <c r="C281" t="n">
-        <v>1.844332531119064</v>
+        <v>1.84174240757371</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.088332124160353</v>
+        <v>-3.08494510862396</v>
       </c>
       <c r="E281" t="n">
-        <v>4.001147830820528</v>
+        <v>3.996156257216588</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.202547802466469</v>
+        <v>1.219358609070187</v>
       </c>
       <c r="C282" t="n">
-        <v>1.619941276425929</v>
+        <v>1.630520271018043</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2785466269759951</v>
+        <v>0.2764875404013933</v>
       </c>
       <c r="E282" t="n">
-        <v>1.005509421825823</v>
+        <v>1.000093435504112</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.132112961074849</v>
+        <v>1.196532098234027</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5654923817485891</v>
+        <v>0.5751097577238351</v>
       </c>
       <c r="D283" t="n">
-        <v>0.13805697499083</v>
+        <v>0.1339500292058426</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1219898035134337</v>
+        <v>-0.1270619576117071</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.550509574981996</v>
+        <v>2.584315334666631</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05202725790229845</v>
+        <v>-0.05113488206961447</v>
       </c>
       <c r="D284" t="n">
-        <v>2.831506382942739</v>
+        <v>2.835178353827672</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7857040040428531</v>
+        <v>0.7816667561211466</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4590760942307703</v>
+        <v>0.4286983317969284</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7771591340667627</v>
+        <v>-0.7840891063789601</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.483964813671079</v>
+        <v>-1.479184490006347</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2812410990183922</v>
+        <v>0.2768457533913526</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656058063469892</v>
+        <v>4.658741728658677</v>
       </c>
       <c r="C286" t="n">
-        <v>1.839552744075301</v>
+        <v>1.835650992226112</v>
       </c>
       <c r="D286" t="n">
-        <v>2.95050563048096</v>
+        <v>2.937865156934194</v>
       </c>
       <c r="E286" t="n">
-        <v>1.269673999922505</v>
+        <v>1.268869143990781</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.818713311471413</v>
+        <v>5.838331773101157</v>
       </c>
       <c r="C287" t="n">
-        <v>3.934385631063386</v>
+        <v>3.942895431614679</v>
       </c>
       <c r="D287" t="n">
-        <v>4.847911274119054</v>
+        <v>4.86064126008714</v>
       </c>
       <c r="E287" t="n">
-        <v>2.671696411680302</v>
+        <v>2.674764703397425</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480101152003923</v>
+        <v>3.482690638348274</v>
       </c>
       <c r="C288" t="n">
-        <v>2.926255752545615</v>
+        <v>2.925205657543972</v>
       </c>
       <c r="D288" t="n">
-        <v>2.104392884165129</v>
+        <v>2.086800902955299</v>
       </c>
       <c r="E288" t="n">
-        <v>3.356284558607592</v>
+        <v>3.360809484473526</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.849816652790142</v>
+        <v>6.849947601820672</v>
       </c>
       <c r="C289" t="n">
-        <v>5.982595885154107</v>
+        <v>5.990301681555787</v>
       </c>
       <c r="D289" t="n">
-        <v>2.223343544138534</v>
+        <v>2.169778032338399</v>
       </c>
       <c r="E289" t="n">
-        <v>3.807208091587611</v>
+        <v>3.814723224754668</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8706666638469862</v>
+        <v>0.8479777565919333</v>
       </c>
       <c r="C290" t="n">
-        <v>1.186587143743356</v>
+        <v>1.17401125864427</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.19399149010876</v>
+        <v>-2.172150151467223</v>
       </c>
       <c r="E290" t="n">
-        <v>2.412652559332029</v>
+        <v>2.408544261675316</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.288810935500774</v>
+        <v>3.190906216001643</v>
       </c>
       <c r="C291" t="n">
-        <v>3.351876745997329</v>
+        <v>3.347882794493051</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.235056573228765</v>
+        <v>-1.212660522248976</v>
       </c>
       <c r="E291" t="n">
-        <v>3.629587402705048</v>
+        <v>3.628621009358568</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.307030970224381</v>
+        <v>6.258396166371094</v>
       </c>
       <c r="C292" t="n">
-        <v>5.59268724930444</v>
+        <v>5.590825054210646</v>
       </c>
       <c r="D292" t="n">
-        <v>2.187866051305876</v>
+        <v>2.203210064262295</v>
       </c>
       <c r="E292" t="n">
-        <v>4.881988604638576</v>
+        <v>4.881336284333848</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.53689787502427</v>
+        <v>3.576952929979083</v>
       </c>
       <c r="C293" t="n">
-        <v>2.391409858104665</v>
+        <v>2.384076690519654</v>
       </c>
       <c r="D293" t="n">
-        <v>2.531849210898507</v>
+        <v>2.539255227403148</v>
       </c>
       <c r="E293" t="n">
-        <v>4.240518532609761</v>
+        <v>4.241441575662508</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.373397879887111</v>
+        <v>8.412489346218832</v>
       </c>
       <c r="C294" t="n">
-        <v>5.92657458166419</v>
+        <v>5.937710130622942</v>
       </c>
       <c r="D294" t="n">
-        <v>4.191466141362055</v>
+        <v>4.195519427261218</v>
       </c>
       <c r="E294" t="n">
-        <v>6.24447484806363</v>
+        <v>6.248852311562914</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.599619646518229</v>
+        <v>6.713061031051026</v>
       </c>
       <c r="C295" t="n">
-        <v>5.387843812041671</v>
+        <v>5.402300685334471</v>
       </c>
       <c r="D295" t="n">
-        <v>6.099813954185485</v>
+        <v>6.101017079592452</v>
       </c>
       <c r="E295" t="n">
-        <v>6.937099734491081</v>
+        <v>6.943798433443593</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.145866701308233</v>
+        <v>5.201666683625072</v>
       </c>
       <c r="C296" t="n">
-        <v>5.704541872107005</v>
+        <v>5.714946683659017</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1208859620484892</v>
+        <v>0.126414372217365</v>
       </c>
       <c r="E296" t="n">
-        <v>4.676124350213628</v>
+        <v>4.678570442398433</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.860867390924683</v>
+        <v>3.837094666921526</v>
       </c>
       <c r="C297" t="n">
-        <v>3.99439278070115</v>
+        <v>3.993294588748508</v>
       </c>
       <c r="D297" t="n">
-        <v>2.963130911970113</v>
+        <v>2.969673213346424</v>
       </c>
       <c r="E297" t="n">
-        <v>4.089489702880766</v>
+        <v>4.087912872862631</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.447688568263784</v>
+        <v>2.413254533679399</v>
       </c>
       <c r="C298" t="n">
-        <v>1.080774310747556</v>
+        <v>1.075727991021247</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4415338083751497</v>
+        <v>0.4231995468785943</v>
       </c>
       <c r="E298" t="n">
-        <v>3.050164986972326</v>
+        <v>3.050262379970348</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.290765188280131</v>
+        <v>3.265892230916112</v>
       </c>
       <c r="C299" t="n">
-        <v>2.776448761234218</v>
+        <v>2.779254560780853</v>
       </c>
       <c r="D299" t="n">
-        <v>1.815992753390172</v>
+        <v>1.843880898325123</v>
       </c>
       <c r="E299" t="n">
-        <v>2.817724826808377</v>
+        <v>2.815623184283389</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.510780893755384</v>
+        <v>4.519447967133039</v>
       </c>
       <c r="C300" t="n">
-        <v>3.661414965268328</v>
+        <v>3.663815567224993</v>
       </c>
       <c r="D300" t="n">
-        <v>3.895660906759169</v>
+        <v>3.862828058659962</v>
       </c>
       <c r="E300" t="n">
-        <v>3.745316448379565</v>
+        <v>3.746957069673384</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.781496650373596</v>
+        <v>4.767153014279857</v>
       </c>
       <c r="C301" t="n">
-        <v>3.146867624464611</v>
+        <v>3.151789876570366</v>
       </c>
       <c r="D301" t="n">
-        <v>5.311685154975243</v>
+        <v>5.219039829622019</v>
       </c>
       <c r="E301" t="n">
-        <v>1.885569388650987</v>
+        <v>1.883843138023034</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.339652535911354</v>
+        <v>5.376151784522909</v>
       </c>
       <c r="C302" t="n">
-        <v>3.380442580213749</v>
+        <v>3.367604251111267</v>
       </c>
       <c r="D302" t="n">
-        <v>4.101351007604359</v>
+        <v>4.12973790654394</v>
       </c>
       <c r="E302" t="n">
-        <v>1.207275946417541</v>
+        <v>1.202886072855125</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.23134019791216</v>
+        <v>5.13936665307102</v>
       </c>
       <c r="C303" t="n">
-        <v>3.220991847048249</v>
+        <v>3.219379389182886</v>
       </c>
       <c r="D303" t="n">
-        <v>1.630777631710933</v>
+        <v>1.661139322029626</v>
       </c>
       <c r="E303" t="n">
-        <v>3.123896614544042</v>
+        <v>3.121240544836223</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.055273865723239</v>
+        <v>0.9614096997649257</v>
       </c>
       <c r="C304" t="n">
-        <v>0.528981008772611</v>
+        <v>0.5180937275226061</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.663975782577908</v>
+        <v>-0.6422981383709225</v>
       </c>
       <c r="E304" t="n">
-        <v>3.836890859937414</v>
+        <v>3.836566822717535</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.06977406242188</v>
+        <v>1.126040353553237</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1560786331189723</v>
+        <v>0.1495208646623114</v>
       </c>
       <c r="D305" t="n">
-        <v>2.194012201958939</v>
+        <v>2.201440510932873</v>
       </c>
       <c r="E305" t="n">
-        <v>1.969607590720801</v>
+        <v>1.967298885028357</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6313286561376419</v>
+        <v>0.6160279744003905</v>
       </c>
       <c r="C306" t="n">
-        <v>0.04127286596800062</v>
+        <v>0.04160363811938073</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.262793889282587</v>
+        <v>-1.253891243082084</v>
       </c>
       <c r="E306" t="n">
-        <v>2.327139126735855</v>
+        <v>2.324178251698172</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.191196339512969</v>
+        <v>2.285166730707222</v>
       </c>
       <c r="C307" t="n">
-        <v>1.358058067827517</v>
+        <v>1.360282237916555</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.597429826157605</v>
+        <v>-2.58758370120501</v>
       </c>
       <c r="E307" t="n">
-        <v>3.146230529149419</v>
+        <v>3.144512360772644</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.772592391049477</v>
+        <v>1.834101688818524</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2788478033717512</v>
+        <v>0.2805011707363692</v>
       </c>
       <c r="D308" t="n">
-        <v>1.608667728129265</v>
+        <v>1.615754752214538</v>
       </c>
       <c r="E308" t="n">
-        <v>4.800137520842451</v>
+        <v>4.799978308121844</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.139998427522106</v>
+        <v>3.145860579001969</v>
       </c>
       <c r="C309" t="n">
-        <v>2.231229734542306</v>
+        <v>2.233800817771225</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5668899723477283</v>
+        <v>0.5759238733484828</v>
       </c>
       <c r="E309" t="n">
-        <v>5.403529239881988</v>
+        <v>5.405230555770846</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.757295740506874</v>
+        <v>5.76215061209242</v>
       </c>
       <c r="C310" t="n">
-        <v>6.602631322277985</v>
+        <v>6.618413730253603</v>
       </c>
       <c r="D310" t="n">
-        <v>2.773925378445186</v>
+        <v>2.748091632298499</v>
       </c>
       <c r="E310" t="n">
-        <v>8.387094786854421</v>
+        <v>8.390687375369899</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.907813658183934</v>
+        <v>3.888017032343116</v>
       </c>
       <c r="C311" t="n">
-        <v>3.169538313783016</v>
+        <v>3.174492543124008</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6451402837420961</v>
+        <v>0.7056105802606183</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879856431537832</v>
+        <v>4.879743948992377</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.036816938864241</v>
+        <v>4.048154027185524</v>
       </c>
       <c r="C312" t="n">
-        <v>2.305312357188627</v>
+        <v>2.30529613031758</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.061464176900706</v>
+        <v>-1.112205558450208</v>
       </c>
       <c r="E312" t="n">
-        <v>5.823903706846068</v>
+        <v>5.823419442865729</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.256030287451095</v>
+        <v>3.196518648262514</v>
       </c>
       <c r="C313" t="n">
-        <v>2.332860926407987</v>
+        <v>2.330210736476324</v>
       </c>
       <c r="D313" t="n">
-        <v>0.03669194524609232</v>
+        <v>-0.103008759850598</v>
       </c>
       <c r="E313" t="n">
-        <v>6.330242596771996</v>
+        <v>6.332713625879172</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.28634251119473</v>
+        <v>4.30141200992975</v>
       </c>
       <c r="C314" t="n">
-        <v>3.909115303044142</v>
+        <v>3.883212255751256</v>
       </c>
       <c r="D314" t="n">
-        <v>1.48200128056144</v>
+        <v>1.521987357175814</v>
       </c>
       <c r="E314" t="n">
-        <v>8.627127536158707</v>
+        <v>8.636913710936378</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.687481633591226</v>
+        <v>1.509681091159187</v>
       </c>
       <c r="C315" t="n">
-        <v>2.793195451491526</v>
+        <v>2.783551371151227</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9311845343388914</v>
+        <v>0.9709978998667657</v>
       </c>
       <c r="E315" t="n">
-        <v>4.02132527677832</v>
+        <v>4.022176212992457</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.655682016779926</v>
+        <v>2.543289560742568</v>
       </c>
       <c r="C316" t="n">
-        <v>2.929113531206951</v>
+        <v>2.921143370273693</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3994381390890922</v>
+        <v>0.4255285679336307</v>
       </c>
       <c r="E316" t="n">
-        <v>3.647840794773849</v>
+        <v>3.648012241635734</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.793905174479555</v>
+        <v>8.980945654162277</v>
       </c>
       <c r="C317" t="n">
-        <v>9.055549295619647</v>
+        <v>9.072213247930749</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3785335478807328</v>
+        <v>0.3900479907646304</v>
       </c>
       <c r="E317" t="n">
-        <v>7.302275682025261</v>
+        <v>7.308034713824196</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.37632473313867</v>
+        <v>4.373612921020475</v>
       </c>
       <c r="C318" t="n">
-        <v>5.418302814901543</v>
+        <v>5.426779475845933</v>
       </c>
       <c r="D318" t="n">
-        <v>2.148714148316766</v>
+        <v>2.164708563038764</v>
       </c>
       <c r="E318" t="n">
-        <v>5.204643896845873</v>
+        <v>5.208096981136046</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.194661943946154</v>
+        <v>4.319327254247107</v>
       </c>
       <c r="C319" t="n">
-        <v>3.365579613308212</v>
+        <v>3.368389128544491</v>
       </c>
       <c r="D319" t="n">
-        <v>2.730735513659965</v>
+        <v>2.753268503390682</v>
       </c>
       <c r="E319" t="n">
-        <v>3.728200291499939</v>
+        <v>3.725498522783122</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.753226661757461</v>
+        <v>6.871385453956225</v>
       </c>
       <c r="C320" t="n">
-        <v>6.754802518520941</v>
+        <v>6.768772104384846</v>
       </c>
       <c r="D320" t="n">
-        <v>2.221568560954479</v>
+        <v>2.231769034704989</v>
       </c>
       <c r="E320" t="n">
-        <v>3.07360151915308</v>
+        <v>3.069956441734734</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.928141263290732</v>
+        <v>5.953496818599135</v>
       </c>
       <c r="C321" t="n">
-        <v>4.639185570815196</v>
+        <v>4.645360719690128</v>
       </c>
       <c r="D321" t="n">
-        <v>1.463002621569554</v>
+        <v>1.473674851226647</v>
       </c>
       <c r="E321" t="n">
-        <v>2.677858528989496</v>
+        <v>2.671740171931991</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.551552429852813</v>
+        <v>5.501359347725976</v>
       </c>
       <c r="C322" t="n">
-        <v>3.514440966278354</v>
+        <v>3.51538038614454</v>
       </c>
       <c r="D322" t="n">
-        <v>0.0733496059205363</v>
+        <v>0.03067548598385539</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.4949157708735497</v>
+        <v>-0.5055678199546443</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.331036508712982</v>
+        <v>4.26956039949471</v>
       </c>
       <c r="C323" t="n">
-        <v>5.151075606369759</v>
+        <v>5.150783931891101</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8493659008953491</v>
+        <v>0.9570557471459074</v>
       </c>
       <c r="E323" t="n">
-        <v>4.177642499901313</v>
+        <v>4.174379777399739</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14338,16 +14338,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.536859056493306</v>
+        <v>7.556355108878088</v>
       </c>
       <c r="C324" t="n">
-        <v>6.845369550336788</v>
+        <v>6.854953300115652</v>
       </c>
       <c r="D324" t="n">
-        <v>3.83073629634465</v>
+        <v>3.746623448084963</v>
       </c>
       <c r="E324" t="n">
-        <v>2.200279136578231</v>
+        <v>2.19368000269351</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14381,16 +14381,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.080899979734644</v>
+        <v>5.967327409995704</v>
       </c>
       <c r="C325" t="n">
-        <v>5.490674436099141</v>
+        <v>5.487999357570561</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1497167215731565</v>
+        <v>-0.07942663566209429</v>
       </c>
       <c r="E325" t="n">
-        <v>2.895939967957251</v>
+        <v>2.892761628492457</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14424,16 +14424,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.855836356597321</v>
+        <v>5.862522845804263</v>
       </c>
       <c r="C326" t="n">
-        <v>5.019799316268281</v>
+        <v>4.971323573278652</v>
       </c>
       <c r="D326" t="n">
-        <v>0.789879275205041</v>
+        <v>0.8582233678292361</v>
       </c>
       <c r="E326" t="n">
-        <v>4.460239918311548</v>
+        <v>4.466564426668396</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14467,16 +14467,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.917091185680892</v>
+        <v>9.728589869977977</v>
       </c>
       <c r="C327" t="n">
-        <v>9.497299830602568</v>
+        <v>9.491074869324677</v>
       </c>
       <c r="D327" t="n">
-        <v>2.686125129780526</v>
+        <v>2.750306356248622</v>
       </c>
       <c r="E327" t="n">
-        <v>7.782870651083984</v>
+        <v>7.790954684570961</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14510,16 +14510,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.41635031678989</v>
+        <v>10.31070245881662</v>
       </c>
       <c r="C328" t="n">
-        <v>9.135368328714799</v>
+        <v>9.137669268632266</v>
       </c>
       <c r="D328" t="n">
-        <v>3.136416770461659</v>
+        <v>3.174404043224732</v>
       </c>
       <c r="E328" t="n">
-        <v>7.349175226322102</v>
+        <v>7.355079017512534</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14553,16 +14553,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.00383784380387</v>
+        <v>4.197505095659371</v>
       </c>
       <c r="C329" t="n">
-        <v>3.071700808509514</v>
+        <v>3.072434471603058</v>
       </c>
       <c r="D329" t="n">
-        <v>2.829617772323245</v>
+        <v>2.855215203963057</v>
       </c>
       <c r="E329" t="n">
-        <v>3.589189447127805</v>
+        <v>3.592831099458671</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14596,16 +14596,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.273159306019549</v>
+        <v>6.266847151383881</v>
       </c>
       <c r="C330" t="n">
-        <v>5.610714510300019</v>
+        <v>5.621111179741622</v>
       </c>
       <c r="D330" t="n">
-        <v>1.306260262502579</v>
+        <v>1.333237017601219</v>
       </c>
       <c r="E330" t="n">
-        <v>5.623718439720138</v>
+        <v>5.626459245372573</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14639,16 +14639,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>5.980763659023691</v>
+        <v>6.201032985410948</v>
       </c>
       <c r="C331" t="n">
-        <v>7.420528558521355</v>
+        <v>7.441410243289126</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.073852345042514</v>
+        <v>-1.041677046138079</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981104429525818</v>
+        <v>4.981680638490271</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14682,16 +14682,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.252462891781494</v>
+        <v>4.401325828497038</v>
       </c>
       <c r="C332" t="n">
-        <v>4.006877743507342</v>
+        <v>4.024370653483866</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.623509131253398</v>
+        <v>-1.60750202663752</v>
       </c>
       <c r="E332" t="n">
-        <v>4.510285228801303</v>
+        <v>4.511496711709473</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14725,16 +14725,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.824500000890207</v>
+        <v>3.850289813486807</v>
       </c>
       <c r="C333" t="n">
-        <v>3.740294025494917</v>
+        <v>3.760257606862782</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.155536287875604</v>
+        <v>-3.144955952578732</v>
       </c>
       <c r="E333" t="n">
-        <v>4.432508998310891</v>
+        <v>4.434571721751168</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14768,16 +14768,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.904296048588884</v>
+        <v>2.832943636831575</v>
       </c>
       <c r="C334" t="n">
-        <v>4.878701228408611</v>
+        <v>4.886972061479011</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.585815246689759</v>
+        <v>-1.656302498622575</v>
       </c>
       <c r="E334" t="n">
-        <v>5.116649687179353</v>
+        <v>5.114671238006396</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14811,16 +14811,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.701639304893045</v>
+        <v>3.645950631119899</v>
       </c>
       <c r="C335" t="n">
-        <v>1.701798191537263</v>
+        <v>1.70671591312086</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.572997658478371</v>
+        <v>-2.398012158907847</v>
       </c>
       <c r="E335" t="n">
-        <v>3.832846775515364</v>
+        <v>3.83365479390072</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14854,16 +14854,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.722021378273421</v>
+        <v>3.728312452502958</v>
       </c>
       <c r="C336" t="n">
-        <v>3.636130442555086</v>
+        <v>3.643831876808723</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.324563565049932</v>
+        <v>-3.454960042522393</v>
       </c>
       <c r="E336" t="n">
-        <v>3.49375262278353</v>
+        <v>3.491716010092993</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14897,16 +14897,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.998037942838171</v>
+        <v>1.843542009146293</v>
       </c>
       <c r="C337" t="n">
-        <v>1.184265316227751</v>
+        <v>1.19033832317228</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.154691047912772</v>
+        <v>-3.534767265741301</v>
       </c>
       <c r="E337" t="n">
-        <v>3.624568214251456</v>
+        <v>3.626056593017712</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14940,16 +14940,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.293704835338374</v>
+        <v>3.305684095529049</v>
       </c>
       <c r="C338" t="n">
-        <v>2.21792411589905</v>
+        <v>2.140067293766901</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.36842517331709</v>
+        <v>-2.252610993964677</v>
       </c>
       <c r="E338" t="n">
-        <v>1.878061967794076</v>
+        <v>1.87688412482605</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14983,16 +14983,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.6635308280274366</v>
+        <v>0.3344858354371816</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.805457119459419</v>
+        <v>-1.843819402810609</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.152154547381979</v>
+        <v>-2.043319152846146</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.5948637049804639</v>
+        <v>-0.6006589224688108</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15026,16 +15026,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.590958068009598</v>
+        <v>3.376813301236914</v>
       </c>
       <c r="C340" t="n">
-        <v>0.5976065562043997</v>
+        <v>0.5780524408740106</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.733397907849533</v>
+        <v>-2.6728732010878</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.139999364031108</v>
+        <v>-1.144050199683921</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15069,16 +15069,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.792246381631826</v>
+        <v>5.10322590898078</v>
       </c>
       <c r="C341" t="n">
-        <v>1.355830416664272</v>
+        <v>1.364297216658628</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.055263807324626</v>
+        <v>-3.009765754530558</v>
       </c>
       <c r="E341" t="n">
-        <v>1.702079041667393</v>
+        <v>1.703208875652118</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15112,16 +15112,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.674946672858061</v>
+        <v>5.683410955758017</v>
       </c>
       <c r="C342" t="n">
-        <v>2.834022788052959</v>
+        <v>2.846905946045131</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.7376028715414873</v>
+        <v>-0.6857479380183218</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1267502614134219</v>
+        <v>-0.1275204494520343</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15155,16 +15155,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>5.83279510236614</v>
+        <v>6.13173355208263</v>
       </c>
       <c r="C343" t="n">
-        <v>1.552891112871024</v>
+        <v>1.569657597219565</v>
       </c>
       <c r="D343" t="n">
-        <v>2.369545528151518</v>
+        <v>2.430556424187436</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6839609689418547</v>
+        <v>0.6840127993603007</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15198,16 +15198,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>5.954981614044619</v>
+        <v>6.198833161656014</v>
       </c>
       <c r="C344" t="n">
-        <v>3.848104243802264</v>
+        <v>3.880395784941104</v>
       </c>
       <c r="D344" t="n">
-        <v>0.8993683671500774</v>
+        <v>0.9280677508407109</v>
       </c>
       <c r="E344" t="n">
-        <v>2.710593865805677</v>
+        <v>2.713423151986105</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15241,16 +15241,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.26509147409811</v>
+        <v>10.34756215614643</v>
       </c>
       <c r="C345" t="n">
-        <v>7.467941414539792</v>
+        <v>7.508646443277933</v>
       </c>
       <c r="D345" t="n">
-        <v>7.741972262528818</v>
+        <v>7.762920246374594</v>
       </c>
       <c r="E345" t="n">
-        <v>2.748527636587594</v>
+        <v>2.753162633175554</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15284,16 +15284,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.148064370770197</v>
+        <v>2.065985002933468</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4417575299695775</v>
+        <v>-0.428417266226</v>
       </c>
       <c r="D346" t="n">
-        <v>1.684197168800416</v>
+        <v>1.552799335328037</v>
       </c>
       <c r="E346" t="n">
-        <v>2.257585157175046</v>
+        <v>2.257268586358485</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15327,16 +15327,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.145725989344085</v>
+        <v>5.05490845790102</v>
       </c>
       <c r="C347" t="n">
-        <v>2.987522981652257</v>
+        <v>3.003057459629188</v>
       </c>
       <c r="D347" t="n">
-        <v>4.064518958398611</v>
+        <v>4.375380169539622</v>
       </c>
       <c r="E347" t="n">
-        <v>2.146288953073427</v>
+        <v>2.141753132128366</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15370,16 +15370,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.562587603286316</v>
+        <v>3.560326099786293</v>
       </c>
       <c r="C348" t="n">
-        <v>-1.021789069174361</v>
+        <v>-1.00961305010332</v>
       </c>
       <c r="D348" t="n">
-        <v>4.276620242947704</v>
+        <v>4.038735397043403</v>
       </c>
       <c r="E348" t="n">
-        <v>3.126459976472895</v>
+        <v>3.123408712805209</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15413,16 +15413,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.724435193395806</v>
+        <v>6.518387295149708</v>
       </c>
       <c r="C349" t="n">
-        <v>5.756116802183286</v>
+        <v>5.775650683919764</v>
       </c>
       <c r="D349" t="n">
-        <v>6.277076141112858</v>
+        <v>5.561058318141887</v>
       </c>
       <c r="E349" t="n">
-        <v>6.029687893440827</v>
+        <v>6.024462067167646</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15456,16 +15456,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.379120842480756</v>
+        <v>5.437874710962887</v>
       </c>
       <c r="C350" t="n">
-        <v>3.240541805991537</v>
+        <v>3.120405301690554</v>
       </c>
       <c r="D350" t="n">
-        <v>6.173738971024312</v>
+        <v>6.387131223124554</v>
       </c>
       <c r="E350" t="n">
-        <v>6.728838825390659</v>
+        <v>6.722281776334715</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15499,16 +15499,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>6.02647082462997</v>
+        <v>5.574339249048754</v>
       </c>
       <c r="C351" t="n">
-        <v>5.020565281839207</v>
+        <v>4.967520141872073</v>
       </c>
       <c r="D351" t="n">
-        <v>1.663095094460698</v>
+        <v>1.849579452825645</v>
       </c>
       <c r="E351" t="n">
-        <v>8.087827338972065</v>
+        <v>8.083173111158604</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15542,16 +15542,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.26495372520469</v>
+        <v>-53.399213389145</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.1657373028236</v>
+        <v>-49.17797964434417</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.34122311693373</v>
+        <v>-44.28016386277194</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.881649032722743</v>
+        <v>-1.87952652423129</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15585,16 +15585,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40225466388813</v>
+        <v>-99.39997192571994</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11615437130587</v>
+        <v>-98.11581771182283</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.69350752237378</v>
+        <v>-88.68403882454791</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.51095054877089</v>
+        <v>-52.50847191135077</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15628,16 +15628,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80420609347949</v>
+        <v>-98.80433904321066</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.97857276648647</v>
+        <v>-95.97811079157677</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.16238686265498</v>
+        <v>-82.14603307840432</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70529307249665</v>
+        <v>-50.70281977788527</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15671,16 +15671,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.13271457454061</v>
+        <v>-98.12601072774238</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.34954161870294</v>
+        <v>-94.34825487106353</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.41199317911291</v>
+        <v>-81.39172665307731</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.99008427377383</v>
+        <v>-42.98708552025202</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15714,16 +15714,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.74183645487703</v>
+        <v>-97.73661914223526</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.6311989125841</v>
+        <v>-93.62932941736332</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64290756115453</v>
+        <v>-75.63088469718109</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11200391157312</v>
+        <v>-43.11065867944984</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15757,16 +15757,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.4616014495206</v>
+        <v>-97.46078999352001</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99932515789051</v>
+        <v>-90.99691748299652</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18825042785828</v>
+        <v>-74.1818588748355</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.66225989971122</v>
+        <v>-45.65890810073825</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15800,16 +15800,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43061663969202</v>
+        <v>-97.43036845764934</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.91108623926705</v>
+        <v>-89.90739241582686</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.96053596841206</v>
+        <v>-74.98380859433269</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17382771321311</v>
+        <v>-40.17031566637912</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15843,16 +15843,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.08025583446543</v>
+        <v>-90.08252640286771</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.42214048606569</v>
+        <v>-81.41309790086432</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.96722867510339</v>
+        <v>-74.92387641327434</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34691439353869</v>
+        <v>-31.34475673264726</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15886,16 +15886,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.7669079311802</v>
+        <v>-76.77634239784916</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.77290616070684</v>
+        <v>-65.75528121863717</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.84253630769398</v>
+        <v>-71.91178798948926</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.60294301340807</v>
+        <v>-12.59869857379001</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15929,16 +15929,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.81724345701373</v>
+        <v>-74.86512426611924</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.50701555901139</v>
+        <v>-66.49648423188974</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.14911584532703</v>
+        <v>-70.34394375972954</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.80039716765983</v>
+        <v>-16.81173262451139</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.71016866931627</v>
+        <v>11.69481255817137</v>
       </c>
       <c r="C242" t="n">
-        <v>11.38244581042254</v>
+        <v>11.41051757347398</v>
       </c>
       <c r="D242" t="n">
-        <v>10.12811720377944</v>
+        <v>10.13206922494674</v>
       </c>
       <c r="E242" t="n">
-        <v>7.271477990307007</v>
+        <v>7.270806551872688</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.22857736153817</v>
+        <v>12.27695848835397</v>
       </c>
       <c r="C243" t="n">
-        <v>12.44505906206748</v>
+        <v>12.46069389928495</v>
       </c>
       <c r="D243" t="n">
-        <v>7.777641032710769</v>
+        <v>7.785716029654477</v>
       </c>
       <c r="E243" t="n">
-        <v>9.003044568338003</v>
+        <v>9.002427080409436</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.854055979005855</v>
+        <v>3.966195730234623</v>
       </c>
       <c r="C244" t="n">
-        <v>7.178997707226298</v>
+        <v>7.18015248014956</v>
       </c>
       <c r="D244" t="n">
-        <v>6.056376224786963</v>
+        <v>6.057120426850959</v>
       </c>
       <c r="E244" t="n">
-        <v>8.720506163443954</v>
+        <v>8.719902628062592</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.919945896285681</v>
+        <v>3.841137974108566</v>
       </c>
       <c r="C245" t="n">
-        <v>7.411661859365326</v>
+        <v>7.403168010177597</v>
       </c>
       <c r="D245" t="n">
-        <v>4.840501404801079</v>
+        <v>4.836827914664021</v>
       </c>
       <c r="E245" t="n">
-        <v>8.568276559526655</v>
+        <v>8.568126956917222</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1618352964142256</v>
+        <v>0.1658500255691253</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.7063295447753304</v>
+        <v>-0.7262965802713794</v>
       </c>
       <c r="D246" t="n">
-        <v>1.858764443741423</v>
+        <v>1.852882373051257</v>
       </c>
       <c r="E246" t="n">
-        <v>9.482856861643318</v>
+        <v>9.482456902033443</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.4034754992091161</v>
+        <v>-0.3789615082278375</v>
       </c>
       <c r="C247" t="n">
-        <v>2.237749626042596</v>
+        <v>2.218068393392914</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.570262026850711</v>
+        <v>-1.577207547736603</v>
       </c>
       <c r="E247" t="n">
-        <v>9.112564450396498</v>
+        <v>9.11187100819275</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11070,16 +11070,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.567700161856445</v>
+        <v>-1.55986972475276</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.342540429284978</v>
+        <v>-2.352199815767642</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.086830385091022</v>
+        <v>-3.086906104704534</v>
       </c>
       <c r="E248" t="n">
-        <v>8.157267361039411</v>
+        <v>8.156468768114532</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.48741787690001</v>
+        <v>1.455439330572617</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2506136104249213</v>
+        <v>-0.258358783900281</v>
       </c>
       <c r="D249" t="n">
-        <v>2.487778792576956</v>
+        <v>2.490357458168568</v>
       </c>
       <c r="E249" t="n">
-        <v>7.157624723066358</v>
+        <v>7.156711723840092</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.872531786163536</v>
+        <v>4.842327254917334</v>
       </c>
       <c r="C250" t="n">
-        <v>4.676653474707315</v>
+        <v>4.700021041799696</v>
       </c>
       <c r="D250" t="n">
-        <v>6.312100838456591</v>
+        <v>6.316907012263284</v>
       </c>
       <c r="E250" t="n">
-        <v>8.292994008993348</v>
+        <v>8.292192060552317</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8662932287683223</v>
+        <v>0.836606194952183</v>
       </c>
       <c r="C251" t="n">
-        <v>1.469746968559371</v>
+        <v>1.474577858199999</v>
       </c>
       <c r="D251" t="n">
-        <v>2.67311135364714</v>
+        <v>2.673190420370175</v>
       </c>
       <c r="E251" t="n">
-        <v>8.438941114966436</v>
+        <v>8.438356746289145</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.670169852342897</v>
+        <v>3.65243022529429</v>
       </c>
       <c r="C252" t="n">
-        <v>2.971190067831131</v>
+        <v>2.960974065780131</v>
       </c>
       <c r="D252" t="n">
-        <v>3.946184305067924</v>
+        <v>3.945344666836892</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19714437387185</v>
+        <v>10.19700587065284</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.061833970429965</v>
+        <v>7.12843500988618</v>
       </c>
       <c r="C253" t="n">
-        <v>8.442585069309061</v>
+        <v>8.468893021395306</v>
       </c>
       <c r="D253" t="n">
-        <v>3.576931512963344</v>
+        <v>3.580746961220171</v>
       </c>
       <c r="E253" t="n">
-        <v>7.945441217350524</v>
+        <v>7.944785777866503</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.417014569543912</v>
+        <v>7.377965554397736</v>
       </c>
       <c r="C254" t="n">
-        <v>7.326462717908977</v>
+        <v>7.322016865856584</v>
       </c>
       <c r="D254" t="n">
-        <v>5.713447254941295</v>
+        <v>5.719362960434382</v>
       </c>
       <c r="E254" t="n">
-        <v>8.190919043807021</v>
+        <v>8.190948350695159</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.43929929457736</v>
+        <v>5.449812949259591</v>
       </c>
       <c r="C255" t="n">
-        <v>5.901274466062523</v>
+        <v>5.872785445702888</v>
       </c>
       <c r="D255" t="n">
-        <v>2.551733037113424</v>
+        <v>2.551860809285</v>
       </c>
       <c r="E255" t="n">
-        <v>6.399370109768432</v>
+        <v>6.399282273263163</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75202687399277</v>
+        <v>11.7123094943173</v>
       </c>
       <c r="C256" t="n">
-        <v>9.879426290628812</v>
+        <v>9.874842918487037</v>
       </c>
       <c r="D256" t="n">
-        <v>5.653819370547652</v>
+        <v>5.656021007831158</v>
       </c>
       <c r="E256" t="n">
-        <v>7.160128786987485</v>
+        <v>7.160130807724108</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.761499416147323</v>
+        <v>8.769492669428946</v>
       </c>
       <c r="C257" t="n">
-        <v>8.540541310522487</v>
+        <v>8.539529727104345</v>
       </c>
       <c r="D257" t="n">
-        <v>5.098321191432786</v>
+        <v>5.099534260989791</v>
       </c>
       <c r="E257" t="n">
-        <v>7.460745796867996</v>
+        <v>7.460533483834908</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.91515470470923</v>
+        <v>11.91897497907251</v>
       </c>
       <c r="C258" t="n">
-        <v>11.75086674751236</v>
+        <v>11.7510031869644</v>
       </c>
       <c r="D258" t="n">
-        <v>8.776158494564656</v>
+        <v>8.778399391398462</v>
       </c>
       <c r="E258" t="n">
-        <v>7.926608321817907</v>
+        <v>7.926600217888624</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.48830576637412</v>
+        <v>11.45639405298526</v>
       </c>
       <c r="C259" t="n">
-        <v>9.117604890954434</v>
+        <v>9.109183339682691</v>
       </c>
       <c r="D259" t="n">
-        <v>7.826286243254543</v>
+        <v>7.828256627440444</v>
       </c>
       <c r="E259" t="n">
-        <v>8.258114039570819</v>
+        <v>8.258182410960991</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.831230930059665</v>
+        <v>8.84212438184997</v>
       </c>
       <c r="C260" t="n">
-        <v>9.293276679624341</v>
+        <v>9.283773620239977</v>
       </c>
       <c r="D260" t="n">
-        <v>8.094111388668246</v>
+        <v>8.091405434949817</v>
       </c>
       <c r="E260" t="n">
-        <v>8.661521931139138</v>
+        <v>8.66173355869031</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.53590313809032</v>
+        <v>12.52735965475718</v>
       </c>
       <c r="C261" t="n">
-        <v>10.30559749109925</v>
+        <v>10.31822130294455</v>
       </c>
       <c r="D261" t="n">
-        <v>5.620305588568786</v>
+        <v>5.620489574039977</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40184581414734</v>
+        <v>10.40224137996728</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.764151242649552</v>
+        <v>6.791820069170074</v>
       </c>
       <c r="C262" t="n">
-        <v>6.489713886718906</v>
+        <v>6.464487771784433</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8032510361097089</v>
+        <v>-0.8071157325411082</v>
       </c>
       <c r="E262" t="n">
-        <v>8.714485048059739</v>
+        <v>8.714591303061736</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.080940818823224</v>
+        <v>9.092095486628127</v>
       </c>
       <c r="C263" t="n">
-        <v>7.448662236485637</v>
+        <v>7.435410614521154</v>
       </c>
       <c r="D263" t="n">
-        <v>3.175338880698386</v>
+        <v>3.172339872734709</v>
       </c>
       <c r="E263" t="n">
-        <v>8.720923996499064</v>
+        <v>8.720654910572744</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.49225747515197</v>
+        <v>13.42968739860573</v>
       </c>
       <c r="C264" t="n">
-        <v>11.24244139717141</v>
+        <v>11.28382181106698</v>
       </c>
       <c r="D264" t="n">
-        <v>4.648343832907664</v>
+        <v>4.648674263903141</v>
       </c>
       <c r="E264" t="n">
-        <v>6.318243196739126</v>
+        <v>6.317426631770617</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.071761115626552</v>
+        <v>8.057004036122418</v>
       </c>
       <c r="C265" t="n">
-        <v>5.784886108924581</v>
+        <v>5.798012578312028</v>
       </c>
       <c r="D265" t="n">
-        <v>2.703670739040387</v>
+        <v>2.702386820166991</v>
       </c>
       <c r="E265" t="n">
-        <v>7.354919137933913</v>
+        <v>7.354310675479114</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.550194018006158</v>
+        <v>2.577039247061363</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2087926254226602</v>
+        <v>-0.2452361526891988</v>
       </c>
       <c r="D266" t="n">
-        <v>2.189064805469076</v>
+        <v>2.190539564648408</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01490879643654</v>
+        <v>12.01513299401429</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.053987041299068</v>
+        <v>5.094712886118402</v>
       </c>
       <c r="C267" t="n">
-        <v>1.656602972291865</v>
+        <v>1.640075159156318</v>
       </c>
       <c r="D267" t="n">
-        <v>3.458518746272365</v>
+        <v>3.459254519249821</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53312271647575</v>
+        <v>13.53379367807621</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.846291465539499</v>
+        <v>5.831790215896882</v>
       </c>
       <c r="C268" t="n">
-        <v>3.409240916096601</v>
+        <v>3.426505765642585</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9090030300144436</v>
+        <v>0.910166643092003</v>
       </c>
       <c r="E268" t="n">
-        <v>15.10578324311751</v>
+        <v>15.10626414384517</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.351157895416933</v>
+        <v>2.36886887118688</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7112370807866419</v>
+        <v>0.706155227933225</v>
       </c>
       <c r="D269" t="n">
-        <v>2.946355444815696</v>
+        <v>2.947633198681676</v>
       </c>
       <c r="E269" t="n">
-        <v>10.13571613129647</v>
+        <v>10.13538516259818</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.684665254542318</v>
+        <v>2.699697892577957</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3500440403461758</v>
+        <v>0.3389336710717394</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.525791252146547</v>
+        <v>-1.524121823229063</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77794552759612</v>
+        <v>11.77766076235904</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.184465576043928</v>
+        <v>4.122984004858221</v>
       </c>
       <c r="C271" t="n">
-        <v>3.278671919901366</v>
+        <v>3.291968349039309</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.181540044712059</v>
+        <v>-1.17959984648065</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72485052363144</v>
+        <v>12.72495760252128</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.857776779071331</v>
+        <v>3.816889711796589</v>
       </c>
       <c r="C272" t="n">
-        <v>2.833835001272256</v>
+        <v>2.846092292474478</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.917050632060991</v>
+        <v>-2.918538031997131</v>
       </c>
       <c r="E272" t="n">
-        <v>12.49493585235011</v>
+        <v>12.4951833608786</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.049131610697907</v>
+        <v>2.044604092152569</v>
       </c>
       <c r="C273" t="n">
-        <v>2.708698913558361</v>
+        <v>2.715623507655263</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1080336463552212</v>
+        <v>-0.1084548297821675</v>
       </c>
       <c r="E273" t="n">
-        <v>12.15917074670252</v>
+        <v>12.15948483178335</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1606028269651394</v>
+        <v>-0.1476384007603859</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2202025010973996</v>
+        <v>0.2241667649974799</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03746964959043808</v>
+        <v>0.03658857459230003</v>
       </c>
       <c r="E274" t="n">
-        <v>11.92506614952375</v>
+        <v>11.9253730620148</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.337489526956225</v>
+        <v>-0.3215114691102472</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4732307600819996</v>
+        <v>-0.4548032203889552</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.01811720341063</v>
+        <v>-2.016980066900753</v>
       </c>
       <c r="E275" t="n">
-        <v>10.90355496880646</v>
+        <v>10.90379799382655</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-4.047987370613981</v>
+        <v>-3.994975521573596</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.16619233205039</v>
+        <v>-4.174746663337303</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.721758838446432</v>
+        <v>-3.722951593171753</v>
       </c>
       <c r="E276" t="n">
-        <v>8.913007673781003</v>
+        <v>8.913106247169257</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.39584065057964</v>
+        <v>-3.362195517299382</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.73042389983661</v>
+        <v>-3.729403697130496</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.411027757751339</v>
+        <v>-3.41300580917705</v>
       </c>
       <c r="E277" t="n">
-        <v>10.78828780871561</v>
+        <v>10.78887549873442</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.309825739702332</v>
+        <v>3.266772951108954</v>
       </c>
       <c r="C278" t="n">
-        <v>3.594116246809009</v>
+        <v>3.629285710556185</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.59727098231166</v>
+        <v>-1.600568413597092</v>
       </c>
       <c r="E278" t="n">
-        <v>6.12773418386765</v>
+        <v>6.127835634074041</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1762246206749363</v>
+        <v>-0.1310003949165361</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4790631754532093</v>
+        <v>0.4590142315519019</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3157210012724287</v>
+        <v>-0.3167090938409611</v>
       </c>
       <c r="E279" t="n">
-        <v>4.003102049136253</v>
+        <v>4.002720279291783</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.895550877218843</v>
+        <v>-1.850123045872343</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.152099165602017</v>
+        <v>-2.190164001059403</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7906263908305733</v>
+        <v>-0.7911591919177008</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4734177886642321</v>
+        <v>0.4729159460757026</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.192806142893855</v>
+        <v>2.166023480975299</v>
       </c>
       <c r="C281" t="n">
-        <v>1.84174240757371</v>
+        <v>1.852648279550406</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.08494510862396</v>
+        <v>-3.085353525728807</v>
       </c>
       <c r="E281" t="n">
-        <v>3.996156257216588</v>
+        <v>3.995993590497116</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.219358609070187</v>
+        <v>1.205221275978485</v>
       </c>
       <c r="C282" t="n">
-        <v>1.630520271018043</v>
+        <v>1.63894994839382</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2764875404013933</v>
+        <v>0.2788438026118722</v>
       </c>
       <c r="E282" t="n">
-        <v>1.000093435504112</v>
+        <v>0.9998890528714055</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.196532098234027</v>
+        <v>1.136539400236414</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5751097577238351</v>
+        <v>0.5800013045885732</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1339500292058426</v>
+        <v>0.1380048524821875</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1270619576117071</v>
+        <v>-0.1273923939180799</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.584315334666631</v>
+        <v>2.55294608419625</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.05113488206961447</v>
+        <v>-0.04565751573090138</v>
       </c>
       <c r="D284" t="n">
-        <v>2.835178353827672</v>
+        <v>2.835025081827891</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7816667561211466</v>
+        <v>0.7814104131995014</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4286983317969284</v>
+        <v>0.4564875386916967</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7840891063789601</v>
+        <v>-0.7898249269175595</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.479184490006347</v>
+        <v>-1.480956239818054</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2768457533913526</v>
+        <v>0.2765856449413517</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.658741728658677</v>
+        <v>4.656757421772473</v>
       </c>
       <c r="C286" t="n">
-        <v>1.835650992226112</v>
+        <v>1.839786524066422</v>
       </c>
       <c r="D286" t="n">
-        <v>2.937865156934194</v>
+        <v>2.939398737423193</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268869143990781</v>
+        <v>1.268788102409268</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.838331773101157</v>
+        <v>5.821999286162782</v>
       </c>
       <c r="C287" t="n">
-        <v>3.942895431614679</v>
+        <v>3.953862804004493</v>
       </c>
       <c r="D287" t="n">
-        <v>4.86064126008714</v>
+        <v>4.865589689224947</v>
       </c>
       <c r="E287" t="n">
-        <v>2.674764703397425</v>
+        <v>2.674943180013734</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.482690638348274</v>
+        <v>3.480901589093977</v>
       </c>
       <c r="C288" t="n">
-        <v>2.925205657543972</v>
+        <v>2.938545198365983</v>
       </c>
       <c r="D288" t="n">
-        <v>2.086800902955299</v>
+        <v>2.087636103253598</v>
       </c>
       <c r="E288" t="n">
-        <v>3.360809484473526</v>
+        <v>3.361096984723932</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.849947601820672</v>
+        <v>6.85386977176623</v>
       </c>
       <c r="C289" t="n">
-        <v>5.990301681555787</v>
+        <v>6.0318149761726</v>
       </c>
       <c r="D289" t="n">
-        <v>2.169778032338399</v>
+        <v>2.170382577376673</v>
       </c>
       <c r="E289" t="n">
-        <v>3.814723224754668</v>
+        <v>3.815039500535211</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8479777565919333</v>
+        <v>0.8675166919599464</v>
       </c>
       <c r="C290" t="n">
-        <v>1.17401125864427</v>
+        <v>1.151042072592534</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.172150151467223</v>
+        <v>-2.177707284088637</v>
       </c>
       <c r="E290" t="n">
-        <v>2.408544261675316</v>
+        <v>2.408308230736167</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.190906216001643</v>
+        <v>3.281745463965247</v>
       </c>
       <c r="C291" t="n">
-        <v>3.347882794493051</v>
+        <v>3.303444731178162</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.212660522248976</v>
+        <v>-1.216794690715339</v>
       </c>
       <c r="E291" t="n">
-        <v>3.628621009358568</v>
+        <v>3.628516195020715</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.258396166371094</v>
+        <v>6.303686272417619</v>
       </c>
       <c r="C292" t="n">
-        <v>5.590825054210646</v>
+        <v>5.579032162457875</v>
       </c>
       <c r="D292" t="n">
-        <v>2.203210064262295</v>
+        <v>2.200631134767828</v>
       </c>
       <c r="E292" t="n">
-        <v>4.881336284333848</v>
+        <v>4.881310742406209</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.576952929979083</v>
+        <v>3.534536899249741</v>
       </c>
       <c r="C293" t="n">
-        <v>2.384076690519654</v>
+        <v>2.368221742495891</v>
       </c>
       <c r="D293" t="n">
-        <v>2.539255227403148</v>
+        <v>2.539840216636047</v>
       </c>
       <c r="E293" t="n">
-        <v>4.241441575662508</v>
+        <v>4.241483792479617</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.412489346218832</v>
+        <v>8.376584776465545</v>
       </c>
       <c r="C294" t="n">
-        <v>5.937710130622942</v>
+        <v>5.925007539618687</v>
       </c>
       <c r="D294" t="n">
-        <v>4.195519427261218</v>
+        <v>4.198393493657959</v>
       </c>
       <c r="E294" t="n">
-        <v>6.248852311562914</v>
+        <v>6.249169236141339</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.713061031051026</v>
+        <v>6.604011169050494</v>
       </c>
       <c r="C295" t="n">
-        <v>5.402300685334471</v>
+        <v>5.407067295141621</v>
       </c>
       <c r="D295" t="n">
-        <v>6.101017079592452</v>
+        <v>6.105100906602212</v>
       </c>
       <c r="E295" t="n">
-        <v>6.943798433443593</v>
+        <v>6.944263023969488</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.201666683625072</v>
+        <v>5.148422868413527</v>
       </c>
       <c r="C296" t="n">
-        <v>5.714946683659017</v>
+        <v>5.727563731124197</v>
       </c>
       <c r="D296" t="n">
-        <v>0.126414372217365</v>
+        <v>0.1258974239893629</v>
       </c>
       <c r="E296" t="n">
-        <v>4.678570442398433</v>
+        <v>4.678730195697001</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.837094666921526</v>
+        <v>3.85808517685553</v>
       </c>
       <c r="C297" t="n">
-        <v>3.993294588748508</v>
+        <v>4.001840969027715</v>
       </c>
       <c r="D297" t="n">
-        <v>2.969673213346424</v>
+        <v>2.967229525560922</v>
       </c>
       <c r="E297" t="n">
-        <v>4.087912872862631</v>
+        <v>4.087800090490412</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.413254533679399</v>
+        <v>2.448647832546547</v>
       </c>
       <c r="C298" t="n">
-        <v>1.075727991021247</v>
+        <v>1.061119041186931</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4231995468785943</v>
+        <v>0.4229147577806236</v>
       </c>
       <c r="E298" t="n">
-        <v>3.050262379970348</v>
+        <v>3.05017872271558</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.265892230916112</v>
+        <v>3.292455011115147</v>
       </c>
       <c r="C299" t="n">
-        <v>2.779254560780853</v>
+        <v>2.791744792485495</v>
       </c>
       <c r="D299" t="n">
-        <v>1.843880898325123</v>
+        <v>1.846056185886802</v>
       </c>
       <c r="E299" t="n">
-        <v>2.815623184283389</v>
+        <v>2.815546366422073</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.519447967133039</v>
+        <v>4.513984571706953</v>
       </c>
       <c r="C300" t="n">
-        <v>3.663815567224993</v>
+        <v>3.700426056547945</v>
       </c>
       <c r="D300" t="n">
-        <v>3.862828058659962</v>
+        <v>3.864362483649586</v>
       </c>
       <c r="E300" t="n">
-        <v>3.746957069673384</v>
+        <v>3.747060755297982</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.767153014279857</v>
+        <v>4.786762181147819</v>
       </c>
       <c r="C301" t="n">
-        <v>3.151789876570366</v>
+        <v>3.198225307014102</v>
       </c>
       <c r="D301" t="n">
-        <v>5.219039829622019</v>
+        <v>5.22185164605653</v>
       </c>
       <c r="E301" t="n">
-        <v>1.883843138023034</v>
+        <v>1.88368422346743</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.376151784522909</v>
+        <v>5.33740872228412</v>
       </c>
       <c r="C302" t="n">
-        <v>3.367604251111267</v>
+        <v>3.363583255790337</v>
       </c>
       <c r="D302" t="n">
-        <v>4.12973790654394</v>
+        <v>4.128159108139062</v>
       </c>
       <c r="E302" t="n">
-        <v>1.202886072855125</v>
+        <v>1.202579848022078</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.13936665307102</v>
+        <v>5.223468576115398</v>
       </c>
       <c r="C303" t="n">
-        <v>3.219379389182886</v>
+        <v>3.160681841201662</v>
       </c>
       <c r="D303" t="n">
-        <v>1.661139322029626</v>
+        <v>1.659951607510535</v>
       </c>
       <c r="E303" t="n">
-        <v>3.121240544836223</v>
+        <v>3.121161660380567</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>0.9614096997649257</v>
+        <v>1.050239908704853</v>
       </c>
       <c r="C304" t="n">
-        <v>0.5180937275226061</v>
+        <v>0.4801592124206389</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6422981383709225</v>
+        <v>-0.6451422152918274</v>
       </c>
       <c r="E304" t="n">
-        <v>3.836566822717535</v>
+        <v>3.836641874171964</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.126040353553237</v>
+        <v>1.069094764923362</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1495208646623114</v>
+        <v>0.1490318638373456</v>
       </c>
       <c r="D305" t="n">
-        <v>2.201440510932873</v>
+        <v>2.203282571580778</v>
       </c>
       <c r="E305" t="n">
-        <v>1.967298885028357</v>
+        <v>1.967144313827385</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6160279744003905</v>
+        <v>0.6309636656347983</v>
       </c>
       <c r="C306" t="n">
-        <v>0.04160363811938073</v>
+        <v>0.02659628231227451</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.253891243082084</v>
+        <v>-1.253401070033022</v>
       </c>
       <c r="E306" t="n">
-        <v>2.324178251698172</v>
+        <v>2.323904328749893</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.285166730707222</v>
+        <v>2.193047980880025</v>
       </c>
       <c r="C307" t="n">
-        <v>1.360282237916555</v>
+        <v>1.367900498428765</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.58758370120501</v>
+        <v>-2.587415519215353</v>
       </c>
       <c r="E307" t="n">
-        <v>3.144512360772644</v>
+        <v>3.144369712456796</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.834101688818524</v>
+        <v>1.774990425161982</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2805011707363692</v>
+        <v>0.2820519747881001</v>
       </c>
       <c r="D308" t="n">
-        <v>1.615754752214538</v>
+        <v>1.616064401776773</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799978308121844</v>
+        <v>4.799978275311667</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.145860579001969</v>
+        <v>3.139472703330148</v>
       </c>
       <c r="C309" t="n">
-        <v>2.233800817771225</v>
+        <v>2.246426941851754</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5759238733484828</v>
+        <v>0.5746118716628557</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405230555770846</v>
+        <v>5.405462619194434</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.76215061209242</v>
+        <v>5.760145029148367</v>
       </c>
       <c r="C310" t="n">
-        <v>6.618413730253603</v>
+        <v>6.645736995497775</v>
       </c>
       <c r="D310" t="n">
-        <v>2.748091632298499</v>
+        <v>2.74757897722655</v>
       </c>
       <c r="E310" t="n">
-        <v>8.390687375369899</v>
+        <v>8.391039850835291</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.888017032343116</v>
+        <v>3.908738719425386</v>
       </c>
       <c r="C311" t="n">
-        <v>3.174492543124008</v>
+        <v>3.19418391833528</v>
       </c>
       <c r="D311" t="n">
-        <v>0.7056105802606183</v>
+        <v>0.7044590592938382</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879743948992377</v>
+        <v>4.879750510061642</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.048154027185524</v>
+        <v>4.042209898914551</v>
       </c>
       <c r="C312" t="n">
-        <v>2.30529613031758</v>
+        <v>2.342363358888422</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.112205558450208</v>
+        <v>-1.112531020653129</v>
       </c>
       <c r="E312" t="n">
-        <v>5.823419442865729</v>
+        <v>5.823294392226308</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.196518648262514</v>
+        <v>3.259937615038799</v>
       </c>
       <c r="C313" t="n">
-        <v>2.330210736476324</v>
+        <v>2.414152890669352</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.103008759850598</v>
+        <v>-0.105077714916979</v>
       </c>
       <c r="E313" t="n">
-        <v>6.332713625879172</v>
+        <v>6.332943709068872</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.30141200992975</v>
+        <v>4.282911804640377</v>
       </c>
       <c r="C314" t="n">
-        <v>3.883212255751256</v>
+        <v>3.883803423389831</v>
       </c>
       <c r="D314" t="n">
-        <v>1.521987357175814</v>
+        <v>1.520650724414274</v>
       </c>
       <c r="E314" t="n">
-        <v>8.636913710936378</v>
+        <v>8.637443143335588</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.509681091159187</v>
+        <v>1.676676126185939</v>
       </c>
       <c r="C315" t="n">
-        <v>2.783551371151227</v>
+        <v>2.658689128569791</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9709978998667657</v>
+        <v>0.9739943269364115</v>
       </c>
       <c r="E315" t="n">
-        <v>4.022176212992457</v>
+        <v>4.021975420089241</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.543289560742568</v>
+        <v>2.65128978382434</v>
       </c>
       <c r="C316" t="n">
-        <v>2.921143370273693</v>
+        <v>2.847823207923095</v>
       </c>
       <c r="D316" t="n">
-        <v>0.4255285679336307</v>
+        <v>0.4256446181034379</v>
       </c>
       <c r="E316" t="n">
-        <v>3.648012241635734</v>
+        <v>3.647818020244031</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.980945654162277</v>
+        <v>8.797575466430496</v>
       </c>
       <c r="C317" t="n">
-        <v>9.072213247930749</v>
+        <v>9.10895644107541</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3900479907646304</v>
+        <v>0.3934604364699057</v>
       </c>
       <c r="E317" t="n">
-        <v>7.308034713824196</v>
+        <v>7.308428870820283</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.373612921020475</v>
+        <v>4.375271679328252</v>
       </c>
       <c r="C318" t="n">
-        <v>5.426779475845933</v>
+        <v>5.384025018316541</v>
       </c>
       <c r="D318" t="n">
-        <v>2.164708563038764</v>
+        <v>2.167270875316096</v>
       </c>
       <c r="E318" t="n">
-        <v>5.208096981136046</v>
+        <v>5.208394409860562</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.319327254247107</v>
+        <v>4.195893319323529</v>
       </c>
       <c r="C319" t="n">
-        <v>3.368389128544491</v>
+        <v>3.340778035372804</v>
       </c>
       <c r="D319" t="n">
-        <v>2.753268503390682</v>
+        <v>2.754255411558781</v>
       </c>
       <c r="E319" t="n">
-        <v>3.725498522783122</v>
+        <v>3.725419117480211</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.871385453956225</v>
+        <v>6.757064413849045</v>
       </c>
       <c r="C320" t="n">
-        <v>6.768772104384846</v>
+        <v>6.806570420344005</v>
       </c>
       <c r="D320" t="n">
-        <v>2.231769034704989</v>
+        <v>2.233683524026309</v>
       </c>
       <c r="E320" t="n">
-        <v>3.069956441734734</v>
+        <v>3.069844622703632</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.953496818599135</v>
+        <v>5.92940774830073</v>
       </c>
       <c r="C321" t="n">
-        <v>4.645360719690128</v>
+        <v>4.67711159244999</v>
       </c>
       <c r="D321" t="n">
-        <v>1.473674851226647</v>
+        <v>1.471934942584996</v>
       </c>
       <c r="E321" t="n">
-        <v>2.671740171931991</v>
+        <v>2.671400208138053</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.501359347725976</v>
+        <v>5.553003880402319</v>
       </c>
       <c r="C322" t="n">
-        <v>3.51538038614454</v>
+        <v>3.504503795466318</v>
       </c>
       <c r="D322" t="n">
-        <v>0.03067548598385539</v>
+        <v>0.02780182529813491</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5055678199546443</v>
+        <v>-0.5061106841517837</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.26956039949471</v>
+        <v>4.330926124299861</v>
       </c>
       <c r="C323" t="n">
-        <v>5.150783931891101</v>
+        <v>5.184113192321371</v>
       </c>
       <c r="D323" t="n">
-        <v>0.9570557471459074</v>
+        <v>0.9527040922851615</v>
       </c>
       <c r="E323" t="n">
-        <v>4.174379777399739</v>
+        <v>4.174309784669883</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14338,16 +14338,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.556355108878088</v>
+        <v>7.543352664156688</v>
       </c>
       <c r="C324" t="n">
-        <v>6.854953300115652</v>
+        <v>6.958981351272731</v>
       </c>
       <c r="D324" t="n">
-        <v>3.746623448084963</v>
+        <v>3.745314506829689</v>
       </c>
       <c r="E324" t="n">
-        <v>2.19368000269351</v>
+        <v>2.193397314675249</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14381,16 +14381,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>5.967327409995704</v>
+        <v>6.084353942165555</v>
       </c>
       <c r="C325" t="n">
-        <v>5.487999357570561</v>
+        <v>5.625032126970297</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.07942663566209429</v>
+        <v>-0.08552874146275924</v>
       </c>
       <c r="E325" t="n">
-        <v>2.892761628492457</v>
+        <v>2.892475968476971</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14424,16 +14424,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.862522845804263</v>
+        <v>5.850050340457025</v>
       </c>
       <c r="C326" t="n">
-        <v>4.971323573278652</v>
+        <v>4.927899587013407</v>
       </c>
       <c r="D326" t="n">
-        <v>0.8582233678292361</v>
+        <v>0.8546137834445577</v>
       </c>
       <c r="E326" t="n">
-        <v>4.466564426668396</v>
+        <v>4.46679991682859</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14467,16 +14467,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.728589869977977</v>
+        <v>9.902119332602698</v>
       </c>
       <c r="C327" t="n">
-        <v>9.491074869324677</v>
+        <v>9.301902124581684</v>
       </c>
       <c r="D327" t="n">
-        <v>2.750306356248622</v>
+        <v>2.757527850880459</v>
       </c>
       <c r="E327" t="n">
-        <v>7.790954684570961</v>
+        <v>7.791329601447061</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14510,16 +14510,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.31070245881662</v>
+        <v>10.41367749784738</v>
       </c>
       <c r="C328" t="n">
-        <v>9.137669268632266</v>
+        <v>9.046720058553003</v>
       </c>
       <c r="D328" t="n">
-        <v>3.174404043224732</v>
+        <v>3.179385899582621</v>
       </c>
       <c r="E328" t="n">
-        <v>7.355079017512534</v>
+        <v>7.355390253737171</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14553,16 +14553,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.197505095659371</v>
+        <v>4.008121609293047</v>
       </c>
       <c r="C329" t="n">
-        <v>3.072434471603058</v>
+        <v>3.051876252638652</v>
       </c>
       <c r="D329" t="n">
-        <v>2.855215203963057</v>
+        <v>2.860430756674437</v>
       </c>
       <c r="E329" t="n">
-        <v>3.592831099458671</v>
+        <v>3.592899436877017</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14596,16 +14596,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.266847151383881</v>
+        <v>6.272727032101177</v>
       </c>
       <c r="C330" t="n">
-        <v>5.621111179741622</v>
+        <v>5.548158583055396</v>
       </c>
       <c r="D330" t="n">
-        <v>1.333237017601219</v>
+        <v>1.337391260949317</v>
       </c>
       <c r="E330" t="n">
-        <v>5.626459245372573</v>
+        <v>5.626511108756604</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14639,16 +14639,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>6.201032985410948</v>
+        <v>5.983471735801227</v>
       </c>
       <c r="C331" t="n">
-        <v>7.441410243289126</v>
+        <v>7.453006921583172</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.041677046138079</v>
+        <v>-1.039660140423071</v>
       </c>
       <c r="E331" t="n">
-        <v>4.981680638490271</v>
+        <v>4.981782124024647</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14682,16 +14682,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.401325828497038</v>
+        <v>4.257604793116387</v>
       </c>
       <c r="C332" t="n">
-        <v>4.024370653483866</v>
+        <v>4.049334575921737</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.60750202663752</v>
+        <v>-1.605582413534379</v>
       </c>
       <c r="E332" t="n">
-        <v>4.511496711709473</v>
+        <v>4.511611665092041</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14725,16 +14725,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.850289813486807</v>
+        <v>3.828043509539114</v>
       </c>
       <c r="C333" t="n">
-        <v>3.760257606862782</v>
+        <v>3.809220260642721</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.144955952578732</v>
+        <v>-3.14525659252135</v>
       </c>
       <c r="E333" t="n">
-        <v>4.434571721751168</v>
+        <v>4.434749984638797</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14768,16 +14768,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.832943636831575</v>
+        <v>2.905355080032801</v>
       </c>
       <c r="C334" t="n">
-        <v>4.886972061479011</v>
+        <v>4.899605516909578</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.656302498622575</v>
+        <v>-1.660290118992513</v>
       </c>
       <c r="E334" t="n">
-        <v>5.114671238006396</v>
+        <v>5.114785775871278</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14811,16 +14811,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.645950631119899</v>
+        <v>3.70365518439828</v>
       </c>
       <c r="C335" t="n">
-        <v>1.70671591312086</v>
+        <v>1.758471008459384</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.398012158907847</v>
+        <v>-2.404750092153451</v>
       </c>
       <c r="E335" t="n">
-        <v>3.83365479390072</v>
+        <v>3.833920989659156</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14854,16 +14854,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.728312452502958</v>
+        <v>3.728403335529662</v>
       </c>
       <c r="C336" t="n">
-        <v>3.643831876808723</v>
+        <v>3.793785040501763</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.454960042522393</v>
+        <v>-3.458919780861491</v>
       </c>
       <c r="E336" t="n">
-        <v>3.491716010092993</v>
+        <v>3.491718431888269</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14897,16 +14897,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.843542009146293</v>
+        <v>2.0030290245306</v>
       </c>
       <c r="C337" t="n">
-        <v>1.19033832317228</v>
+        <v>1.445604838146286</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.534767265741301</v>
+        <v>-3.542193217117418</v>
       </c>
       <c r="E337" t="n">
-        <v>3.626056593017712</v>
+        <v>3.626243583351441</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14940,16 +14940,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.305684095529049</v>
+        <v>3.284936091871149</v>
       </c>
       <c r="C338" t="n">
-        <v>2.140067293766901</v>
+        <v>2.113981035590728</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.252610993964677</v>
+        <v>-2.259448142184928</v>
       </c>
       <c r="E338" t="n">
-        <v>1.87688412482605</v>
+        <v>1.876759410908879</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14983,16 +14983,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.3344858354371816</v>
+        <v>0.6413261260301395</v>
       </c>
       <c r="C339" t="n">
-        <v>-1.843819402810609</v>
+        <v>-2.170864707163145</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.043319152846146</v>
+        <v>-2.034762700059101</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.6006589224688108</v>
+        <v>-0.6016794469894893</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15026,16 +15026,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.376813301236914</v>
+        <v>3.584027388589295</v>
       </c>
       <c r="C340" t="n">
-        <v>0.5780524408740106</v>
+        <v>0.4080820745031355</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.6728732010878</v>
+        <v>-2.667419931146198</v>
       </c>
       <c r="E340" t="n">
-        <v>-1.144050199683921</v>
+        <v>-1.144626352700828</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15069,16 +15069,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>5.10322590898078</v>
+        <v>4.797824667457129</v>
       </c>
       <c r="C341" t="n">
-        <v>1.364297216658628</v>
+        <v>1.394752832095802</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.009765754530558</v>
+        <v>-3.006177746938743</v>
       </c>
       <c r="E341" t="n">
-        <v>1.703208875652118</v>
+        <v>1.703329853818092</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15112,16 +15112,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.683410955758017</v>
+        <v>5.674080056761288</v>
       </c>
       <c r="C342" t="n">
-        <v>2.846905946045131</v>
+        <v>2.736953043455692</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.6857479380183218</v>
+        <v>-0.6829658740064026</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.1275204494520343</v>
+        <v>-0.1275821878822136</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15155,16 +15155,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>6.13173355208263</v>
+        <v>5.836148788163853</v>
       </c>
       <c r="C343" t="n">
-        <v>1.569657597219565</v>
+        <v>1.533360515156001</v>
       </c>
       <c r="D343" t="n">
-        <v>2.430556424187436</v>
+        <v>2.432848213039329</v>
       </c>
       <c r="E343" t="n">
-        <v>0.6840127993603007</v>
+        <v>0.6840957532189051</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15198,16 +15198,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>6.198833161656014</v>
+        <v>5.96270624228461</v>
       </c>
       <c r="C344" t="n">
-        <v>3.880395784941104</v>
+        <v>3.95023207981664</v>
       </c>
       <c r="D344" t="n">
-        <v>0.9280677508407109</v>
+        <v>0.9330207532235901</v>
       </c>
       <c r="E344" t="n">
-        <v>2.713423151986105</v>
+        <v>2.713869382906542</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15241,16 +15241,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.34756215614643</v>
+        <v>10.27072827400186</v>
       </c>
       <c r="C345" t="n">
-        <v>7.508646443277933</v>
+        <v>7.6192661604912</v>
       </c>
       <c r="D345" t="n">
-        <v>7.762920246374594</v>
+        <v>7.764205437831317</v>
       </c>
       <c r="E345" t="n">
-        <v>2.753162633175554</v>
+        <v>2.753640725257611</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15284,16 +15284,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.065985002933468</v>
+        <v>2.153371126020764</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.428417266226</v>
+        <v>-0.4260218785128833</v>
       </c>
       <c r="D346" t="n">
-        <v>1.552799335328037</v>
+        <v>1.549696919807642</v>
       </c>
       <c r="E346" t="n">
-        <v>2.257268586358485</v>
+        <v>2.257467833775251</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15327,16 +15327,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.05490845790102</v>
+        <v>5.151904297877463</v>
       </c>
       <c r="C347" t="n">
-        <v>3.003057459629188</v>
+        <v>3.093218746098358</v>
       </c>
       <c r="D347" t="n">
-        <v>4.375380169539622</v>
+        <v>4.365166961653277</v>
       </c>
       <c r="E347" t="n">
-        <v>2.141753132128366</v>
+        <v>2.141884566037611</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15370,16 +15370,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.560326099786293</v>
+        <v>3.571095814770686</v>
       </c>
       <c r="C348" t="n">
-        <v>-1.00961305010332</v>
+        <v>-0.7699888647449527</v>
       </c>
       <c r="D348" t="n">
-        <v>4.038735397043403</v>
+        <v>4.032755431378843</v>
       </c>
       <c r="E348" t="n">
-        <v>3.123408712805209</v>
+        <v>3.123181015892573</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15413,16 +15413,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.518387295149708</v>
+        <v>6.734845823559277</v>
       </c>
       <c r="C349" t="n">
-        <v>5.775650683919764</v>
+        <v>6.22369305274566</v>
       </c>
       <c r="D349" t="n">
-        <v>5.561058318141887</v>
+        <v>5.553982105540056</v>
       </c>
       <c r="E349" t="n">
-        <v>6.024462067167646</v>
+        <v>6.024291511300883</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15456,16 +15456,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.437874710962887</v>
+        <v>5.367986322416507</v>
       </c>
       <c r="C350" t="n">
-        <v>3.120405301690554</v>
+        <v>3.075011672932959</v>
       </c>
       <c r="D350" t="n">
-        <v>6.387131223124554</v>
+        <v>6.375014843399018</v>
       </c>
       <c r="E350" t="n">
-        <v>6.722281776334715</v>
+        <v>6.721902855829187</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15499,16 +15499,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>5.574339249048754</v>
+        <v>5.99412874973646</v>
       </c>
       <c r="C351" t="n">
-        <v>4.967520141872073</v>
+        <v>4.372356686073342</v>
       </c>
       <c r="D351" t="n">
-        <v>1.849579452825645</v>
+        <v>1.86615249228772</v>
       </c>
       <c r="E351" t="n">
-        <v>8.083173111158604</v>
+        <v>8.081565223636833</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15542,16 +15542,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.399213389145</v>
+        <v>-53.27051356723902</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.17797964434417</v>
+        <v>-49.32443063230615</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.28016386277194</v>
+        <v>-44.27422208835166</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.87952652423129</v>
+        <v>-1.879993111147515</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15585,16 +15585,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.39997192571994</v>
+        <v>-99.40221664092782</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11581771182283</v>
+        <v>-98.11548779154214</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.68403882454791</v>
+        <v>-88.68313116215639</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.50847191135077</v>
+        <v>-52.50839830632125</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15628,16 +15628,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80433904321066</v>
+        <v>-98.80424592194804</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.97811079157677</v>
+        <v>-95.98573062334214</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.14603307840432</v>
+        <v>-82.14523929369273</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.70281977788527</v>
+        <v>-50.70272446559626</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15671,16 +15671,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.12601072774238</v>
+        <v>-98.13267742848669</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.34825487106353</v>
+        <v>-94.35026587152609</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.39172665307731</v>
+        <v>-81.39142769487103</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.98708552025202</v>
+        <v>-42.98692025757204</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15714,16 +15714,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.73661914223526</v>
+        <v>-97.74166053437239</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62932941736332</v>
+        <v>-93.625100308621</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.63088469718109</v>
+        <v>-75.62938753461748</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.11065867944984</v>
+        <v>-43.11043191504206</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15757,16 +15757,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.46078999352001</v>
+        <v>-97.46154680035212</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.99691748299652</v>
+        <v>-90.98711664675851</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.1818588748355</v>
+        <v>-74.18241487038424</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.65890810073825</v>
+        <v>-45.65854602073681</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15800,16 +15800,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.43036845764934</v>
+        <v>-97.43029617261413</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90739241582686</v>
+        <v>-89.90337658761423</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.98380859433269</v>
+        <v>-74.98485686469493</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.17031566637912</v>
+        <v>-40.16961278621755</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15843,16 +15843,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.08252640286771</v>
+        <v>-90.07912151992275</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.41309790086432</v>
+        <v>-81.37975816197518</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.92387641327434</v>
+        <v>-74.92734799609288</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.34475673264726</v>
+        <v>-31.34380766683888</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15886,16 +15886,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.77634239784916</v>
+        <v>-76.76382791349589</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.75528121863717</v>
+        <v>-65.61740451512495</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.91178798948926</v>
+        <v>-71.9148867977347</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.59869857379001</v>
+        <v>-12.59783310878851</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15929,16 +15929,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.86512426611924</v>
+        <v>-74.81330547064385</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.49648423188974</v>
+        <v>-66.32557020611358</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.34394375972954</v>
+        <v>-70.34799799895245</v>
       </c>
       <c r="E361" t="n">
-        <v>-16.81173262451139</v>
+        <v>-16.81180257485387</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -516,7 +516,7 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.87396</v>
+        <v>6.81609</v>
       </c>
       <c r="K2" t="n">
         <v>2.30536</v>
@@ -559,7 +559,7 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.15286</v>
+        <v>4.1021</v>
       </c>
       <c r="K3" t="n">
         <v>2.43838</v>
@@ -602,7 +602,7 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.55652</v>
+        <v>7.6442</v>
       </c>
       <c r="K4" t="n">
         <v>2.13214</v>
@@ -645,7 +645,7 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74233</v>
+        <v>0.78853</v>
       </c>
       <c r="K5" t="n">
         <v>2.02286</v>
@@ -688,7 +688,7 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77767</v>
+        <v>1.8466</v>
       </c>
       <c r="K6" t="n">
         <v>1.99344</v>
@@ -731,7 +731,7 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02094</v>
+        <v>2.08452</v>
       </c>
       <c r="K7" t="n">
         <v>1.70179</v>
@@ -774,7 +774,7 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61358</v>
+        <v>4.63766</v>
       </c>
       <c r="K8" t="n">
         <v>1.47346</v>
@@ -817,7 +817,7 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>7.05463</v>
+        <v>6.97377</v>
       </c>
       <c r="K9" t="n">
         <v>1.21062</v>
@@ -860,7 +860,7 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.03444</v>
+        <v>7.98007</v>
       </c>
       <c r="K10" t="n">
         <v>0.7003</v>
@@ -903,7 +903,7 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.90044</v>
+        <v>5.82782</v>
       </c>
       <c r="K11" t="n">
         <v>0.36237</v>
@@ -946,7 +946,7 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>3.00219</v>
+        <v>2.95026</v>
       </c>
       <c r="K12" t="n">
         <v>0.05167</v>
@@ -989,7 +989,7 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5683</v>
+        <v>3.5115</v>
       </c>
       <c r="K13" t="n">
         <v>-0.19355</v>
@@ -1032,7 +1032,7 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0041</v>
+        <v>1.94709</v>
       </c>
       <c r="K14" t="n">
         <v>-0.7726</v>
@@ -1075,7 +1075,7 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.20036</v>
+        <v>3.15431</v>
       </c>
       <c r="K15" t="n">
         <v>-1.0036</v>
@@ -1118,7 +1118,7 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72296</v>
+        <v>4.82043</v>
       </c>
       <c r="K16" t="n">
         <v>-1.22423</v>
@@ -1161,7 +1161,7 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.26285</v>
+        <v>5.38343</v>
       </c>
       <c r="K17" t="n">
         <v>-1.68662</v>
@@ -1204,7 +1204,7 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.22891</v>
+        <v>4.36433</v>
       </c>
       <c r="K18" t="n">
         <v>-1.9802</v>
@@ -1247,7 +1247,7 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.76074</v>
+        <v>3.86557</v>
       </c>
       <c r="K19" t="n">
         <v>-2.25254</v>
@@ -1290,7 +1290,7 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.94757</v>
+        <v>0.97695</v>
       </c>
       <c r="K20" t="n">
         <v>-2.53148</v>
@@ -1333,7 +1333,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13377</v>
+        <v>-1.18743</v>
       </c>
       <c r="K21" t="n">
         <v>-2.58521</v>
@@ -1376,7 +1376,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.86898</v>
+        <v>-2.91307</v>
       </c>
       <c r="K22" t="n">
         <v>-2.39536</v>
@@ -1419,7 +1419,7 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6043</v>
+        <v>-2.67745</v>
       </c>
       <c r="K23" t="n">
         <v>-2.39845</v>
@@ -1462,7 +1462,7 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.90597</v>
+        <v>-2.96168</v>
       </c>
       <c r="K24" t="n">
         <v>-2.19496</v>
@@ -1505,7 +1505,7 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.72199</v>
+        <v>-3.79348</v>
       </c>
       <c r="K25" t="n">
         <v>-1.95217</v>
@@ -1548,7 +1548,7 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.68621</v>
+        <v>-6.73931</v>
       </c>
       <c r="K26" t="n">
         <v>-1.50532</v>
@@ -1591,7 +1591,7 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.29626</v>
+        <v>-7.3248</v>
       </c>
       <c r="K27" t="n">
         <v>-0.97479</v>
@@ -1634,7 +1634,7 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.18594</v>
+        <v>-7.12541</v>
       </c>
       <c r="K28" t="n">
         <v>-0.45662</v>
@@ -1677,7 +1677,7 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.496359999999999</v>
+        <v>-8.415509999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.3143</v>
@@ -1720,7 +1720,7 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.96469</v>
+        <v>-7.85283</v>
       </c>
       <c r="K30" t="n">
         <v>0.61656</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.24837</v>
+        <v>-7.16305</v>
       </c>
       <c r="K31" t="n">
         <v>1.1193</v>
@@ -1806,7 +1806,7 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.58179</v>
+        <v>-7.55991</v>
       </c>
       <c r="K32" t="n">
         <v>1.33158</v>
@@ -1849,7 +1849,7 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.44023</v>
+        <v>-8.48601</v>
       </c>
       <c r="K33" t="n">
         <v>1.54476</v>
@@ -1892,7 +1892,7 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.62456</v>
+        <v>-7.68218</v>
       </c>
       <c r="K34" t="n">
         <v>1.57013</v>
@@ -1935,7 +1935,7 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.89514</v>
+        <v>-5.99341</v>
       </c>
       <c r="K35" t="n">
         <v>1.61184</v>
@@ -1978,7 +1978,7 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.24278</v>
+        <v>-7.30628</v>
       </c>
       <c r="K36" t="n">
         <v>1.34653</v>
@@ -2021,7 +2021,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.38118</v>
+        <v>-7.43272</v>
       </c>
       <c r="K37" t="n">
         <v>1.04167</v>
@@ -2064,7 +2064,7 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.30715</v>
+        <v>-3.37111</v>
       </c>
       <c r="K38" t="n">
         <v>0.59289</v>
@@ -2107,7 +2107,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.1649</v>
+        <v>-2.19051</v>
       </c>
       <c r="K39" t="n">
         <v>0.03938</v>
@@ -2150,7 +2150,7 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.55947</v>
+        <v>-1.43984</v>
       </c>
       <c r="K40" t="n">
         <v>-0.23591</v>
@@ -2193,7 +2193,7 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.60295</v>
+        <v>-0.49025</v>
       </c>
       <c r="K41" t="n">
         <v>-0.75718</v>
@@ -2236,7 +2236,7 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.01677</v>
+        <v>-0.87713</v>
       </c>
       <c r="K42" t="n">
         <v>-1.08214</v>
@@ -2279,7 +2279,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.00472</v>
+        <v>-0.88075</v>
       </c>
       <c r="K43" t="n">
         <v>-1.06785</v>
@@ -2322,7 +2322,7 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.31985</v>
+        <v>1.33254</v>
       </c>
       <c r="K44" t="n">
         <v>-1.27505</v>
@@ -2365,7 +2365,7 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68566</v>
+        <v>0.55997</v>
       </c>
       <c r="K45" t="n">
         <v>-1.24821</v>
@@ -2408,7 +2408,7 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.35198</v>
+        <v>1.28625</v>
       </c>
       <c r="K46" t="n">
         <v>-1.2211</v>
@@ -2451,7 +2451,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09778</v>
+        <v>0.98449</v>
       </c>
       <c r="K47" t="n">
         <v>-1.00117</v>
@@ -2494,7 +2494,7 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.67642</v>
+        <v>2.60512</v>
       </c>
       <c r="K48" t="n">
         <v>-0.42986</v>
@@ -2537,7 +2537,7 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.51976</v>
+        <v>2.47552</v>
       </c>
       <c r="K49" t="n">
         <v>0.11745</v>
@@ -2580,7 +2580,7 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.40978</v>
+        <v>1.36814</v>
       </c>
       <c r="K50" t="n">
         <v>0.60249</v>
@@ -2623,7 +2623,7 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.18303</v>
+        <v>0.16896</v>
       </c>
       <c r="K51" t="n">
         <v>0.87903</v>
@@ -2666,7 +2666,7 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.83422</v>
+        <v>-0.72938</v>
       </c>
       <c r="K52" t="n">
         <v>0.88019</v>
@@ -2709,7 +2709,7 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.64128</v>
+        <v>-0.54603</v>
       </c>
       <c r="K53" t="n">
         <v>0.84188</v>
@@ -2752,7 +2752,7 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.46451</v>
+        <v>-0.36018</v>
       </c>
       <c r="K54" t="n">
         <v>0.88309</v>
@@ -2795,7 +2795,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.25853</v>
+        <v>-1.19125</v>
       </c>
       <c r="K55" t="n">
         <v>0.6186700000000001</v>
@@ -2838,7 +2838,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05606</v>
+        <v>-2.05834</v>
       </c>
       <c r="K56" t="n">
         <v>0.57986</v>
@@ -2881,7 +2881,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.18496</v>
       </c>
       <c r="K57" t="n">
         <v>0.30283</v>
@@ -2924,7 +2924,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.99044</v>
+        <v>-1.03703</v>
       </c>
       <c r="K58" t="n">
         <v>0.24987</v>
@@ -2967,7 +2967,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.11214</v>
+        <v>-2.17946</v>
       </c>
       <c r="K59" t="n">
         <v>-0.01313</v>
@@ -3010,7 +3010,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.08765</v>
+        <v>-1.12351</v>
       </c>
       <c r="K60" t="n">
         <v>-0.30089</v>
@@ -3053,7 +3053,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.03202</v>
+        <v>-1.0091</v>
       </c>
       <c r="K61" t="n">
         <v>-0.57351</v>
@@ -3096,7 +3096,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.74507</v>
+        <v>-0.7541099999999999</v>
       </c>
       <c r="K62" t="n">
         <v>-0.80719</v>
@@ -3139,7 +3139,7 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.24695</v>
+        <v>1.256</v>
       </c>
       <c r="K63" t="n">
         <v>-0.76733</v>
@@ -3182,7 +3182,7 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>1.938</v>
+        <v>2.01069</v>
       </c>
       <c r="K64" t="n">
         <v>-0.5209</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.72111</v>
+        <v>0.76275</v>
       </c>
       <c r="K65" t="n">
         <v>-0.28698</v>
@@ -3268,7 +3268,7 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.08762</v>
+        <v>1.11255</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.1709</v>
+        <v>2.19418</v>
       </c>
       <c r="K67" t="n">
         <v>0.23548</v>
@@ -3354,7 +3354,7 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.45732</v>
+        <v>2.41851</v>
       </c>
       <c r="K68" t="n">
         <v>0.79927</v>
@@ -3397,7 +3397,7 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.30554</v>
+        <v>2.18366</v>
       </c>
       <c r="K69" t="n">
         <v>1.11578</v>
@@ -3440,7 +3440,7 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.95793</v>
+        <v>2.97359</v>
       </c>
       <c r="K70" t="n">
         <v>1.12816</v>
@@ -3483,7 +3483,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.13836</v>
+        <v>3.16049</v>
       </c>
       <c r="K71" t="n">
         <v>1.15592</v>
@@ -3526,7 +3526,7 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.07536</v>
+        <v>2.06427</v>
       </c>
       <c r="K72" t="n">
         <v>0.91851</v>
@@ -3569,7 +3569,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.7263</v>
+        <v>3.76241</v>
       </c>
       <c r="K73" t="n">
         <v>0.957</v>
@@ -3612,7 +3612,7 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.2769</v>
+        <v>3.28823</v>
       </c>
       <c r="K74" t="n">
         <v>0.95813</v>
@@ -3655,7 +3655,7 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.52716</v>
+        <v>1.56011</v>
       </c>
       <c r="K75" t="n">
         <v>0.93054</v>
@@ -3698,7 +3698,7 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.24666</v>
+        <v>1.23795</v>
       </c>
       <c r="K76" t="n">
         <v>0.94253</v>
@@ -3741,7 +3741,7 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.24286</v>
+        <v>1.25017</v>
       </c>
       <c r="K77" t="n">
         <v>0.98116</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.03923</v>
+        <v>-0.04673</v>
       </c>
       <c r="K78" t="n">
         <v>1.20199</v>
@@ -3827,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.3634</v>
+        <v>-1.37349</v>
       </c>
       <c r="K79" t="n">
         <v>1.22683</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.24425</v>
+        <v>-1.29687</v>
       </c>
       <c r="K80" t="n">
         <v>0.93592</v>
@@ -3913,7 +3913,7 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.38613</v>
+        <v>-1.46389</v>
       </c>
       <c r="K81" t="n">
         <v>1.19434</v>
@@ -3956,7 +3956,7 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.81168</v>
+        <v>-1.77292</v>
       </c>
       <c r="K82" t="n">
         <v>1.45285</v>
@@ -3999,7 +3999,7 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.15045</v>
+        <v>-1.09116</v>
       </c>
       <c r="K83" t="n">
         <v>1.71406</v>
@@ -4042,7 +4042,7 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.29201</v>
+        <v>-1.28652</v>
       </c>
       <c r="K84" t="n">
         <v>2.22338</v>
@@ -4085,7 +4085,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.01257</v>
+        <v>-1.96701</v>
       </c>
       <c r="K85" t="n">
         <v>2.22049</v>
@@ -4128,7 +4128,7 @@
         <v>-0.73638</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.71985</v>
+        <v>-1.70263</v>
       </c>
       <c r="K86" t="n">
         <v>2.4701</v>
@@ -4171,7 +4171,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.27095</v>
+        <v>-1.26517</v>
       </c>
       <c r="K87" t="n">
         <v>2.46721</v>
@@ -4214,7 +4214,7 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.97214</v>
+        <v>-0.99314</v>
       </c>
       <c r="K88" t="n">
         <v>2.45104</v>
@@ -4257,7 +4257,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.57026</v>
+        <v>-0.57683</v>
       </c>
       <c r="K89" t="n">
         <v>2.48737</v>
@@ -4300,7 +4300,7 @@
         <v>-0.73746</v>
       </c>
       <c r="J90" t="n">
-        <v>0.17419</v>
+        <v>0.14622</v>
       </c>
       <c r="K90" t="n">
         <v>2.01394</v>
@@ -4343,7 +4343,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J91" t="n">
-        <v>0.38879</v>
+        <v>0.38672</v>
       </c>
       <c r="K91" t="n">
         <v>1.97267</v>
@@ -4386,7 +4386,7 @@
         <v>-0.58997</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.2258</v>
+        <v>-0.28095</v>
       </c>
       <c r="K92" t="n">
         <v>1.75145</v>
@@ -4429,7 +4429,7 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.9391</v>
+        <v>-1.01728</v>
       </c>
       <c r="K93" t="n">
         <v>1.48813</v>
@@ -4472,7 +4472,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.38793</v>
+        <v>-1.34254</v>
       </c>
       <c r="K94" t="n">
         <v>1.26582</v>
@@ -4515,7 +4515,7 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.02731</v>
+        <v>-1.92056</v>
       </c>
       <c r="K95" t="n">
         <v>1.21282</v>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.27383</v>
+        <v>-1.26395</v>
       </c>
       <c r="K96" t="n">
         <v>1.20834</v>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95325</v>
+        <v>-1.95133</v>
       </c>
       <c r="K97" t="n">
         <v>1.47358</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.95977</v>
+        <v>-1.93973</v>
       </c>
       <c r="K98" t="n">
         <v>1.68739</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.02152</v>
+        <v>-2.02239</v>
       </c>
       <c r="K99" t="n">
         <v>1.96426</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.22762</v>
+        <v>-2.2576</v>
       </c>
       <c r="K100" t="n">
         <v>2.26582</v>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.59591</v>
+        <v>-1.59827</v>
       </c>
       <c r="K101" t="n">
         <v>2.30059</v>
@@ -4816,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.13135</v>
+        <v>-1.14518</v>
       </c>
       <c r="K102" t="n">
         <v>2.80942</v>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.70106</v>
+        <v>-0.72556</v>
       </c>
       <c r="K103" t="n">
         <v>3.13567</v>
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.63679</v>
+        <v>-1.65101</v>
       </c>
       <c r="K104" t="n">
         <v>3.40463</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.31032</v>
+        <v>-1.3399</v>
       </c>
       <c r="K105" t="n">
         <v>3.72898</v>
@@ -4988,7 +4988,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.71544</v>
+        <v>-1.70895</v>
       </c>
       <c r="K106" t="n">
         <v>4.01515</v>
@@ -5031,7 +5031,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.61232</v>
+        <v>0.68676</v>
       </c>
       <c r="K107" t="n">
         <v>4.36428</v>
@@ -5074,7 +5074,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.65039</v>
+        <v>1.65398</v>
       </c>
       <c r="K108" t="n">
         <v>4.39864</v>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32918</v>
+        <v>2.32125</v>
       </c>
       <c r="K109" t="n">
         <v>4.68202</v>
@@ -5160,7 +5160,7 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.66648</v>
+        <v>0.66954</v>
       </c>
       <c r="K110" t="n">
         <v>4.75359</v>
@@ -5203,7 +5203,7 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9055299999999999</v>
+        <v>0.87768</v>
       </c>
       <c r="K111" t="n">
         <v>4.52399</v>
@@ -5246,7 +5246,7 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.75477</v>
+        <v>1.75034</v>
       </c>
       <c r="K112" t="n">
         <v>4.53026</v>
@@ -5289,7 +5289,7 @@
         <v>0.29718</v>
       </c>
       <c r="J113" t="n">
-        <v>2.68804</v>
+        <v>2.71015</v>
       </c>
       <c r="K113" t="n">
         <v>4.5595</v>
@@ -5332,7 +5332,7 @@
         <v>0.14859</v>
       </c>
       <c r="J114" t="n">
-        <v>2.87431</v>
+        <v>2.88092</v>
       </c>
       <c r="K114" t="n">
         <v>4.56672</v>
@@ -5375,7 +5375,7 @@
         <v>-0.14837</v>
       </c>
       <c r="J115" t="n">
-        <v>3.30692</v>
+        <v>3.29157</v>
       </c>
       <c r="K115" t="n">
         <v>4.36435</v>
@@ -5418,7 +5418,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.93852</v>
+        <v>3.94635</v>
       </c>
       <c r="K116" t="n">
         <v>4.58996</v>
@@ -5461,7 +5461,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.90907</v>
+        <v>3.91094</v>
       </c>
       <c r="K117" t="n">
         <v>4.53327</v>
@@ -5504,7 +5504,7 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.2593</v>
+        <v>5.2419</v>
       </c>
       <c r="K118" t="n">
         <v>4.33358</v>
@@ -5547,7 +5547,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.59829</v>
+        <v>3.63188</v>
       </c>
       <c r="K119" t="n">
         <v>4.27846</v>
@@ -5590,7 +5590,7 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.88632</v>
+        <v>1.87629</v>
       </c>
       <c r="K120" t="n">
         <v>4.03274</v>
@@ -5633,7 +5633,7 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.47368</v>
+        <v>1.44758</v>
       </c>
       <c r="K121" t="n">
         <v>3.50395</v>
@@ -5676,7 +5676,7 @@
         <v>-0.2963</v>
       </c>
       <c r="J122" t="n">
-        <v>3.31769</v>
+        <v>3.30475</v>
       </c>
       <c r="K122" t="n">
         <v>2.89424</v>
@@ -5719,7 +5719,7 @@
         <v>-0.14815</v>
       </c>
       <c r="J123" t="n">
-        <v>3.28841</v>
+        <v>3.27764</v>
       </c>
       <c r="K123" t="n">
         <v>2.88942</v>
@@ -5762,7 +5762,7 @@
         <v>-0.29586</v>
       </c>
       <c r="J124" t="n">
-        <v>2.21629</v>
+        <v>2.21596</v>
       </c>
       <c r="K124" t="n">
         <v>2.38011</v>
@@ -5805,7 +5805,7 @@
         <v>-0.2963</v>
       </c>
       <c r="J125" t="n">
-        <v>0.86488</v>
+        <v>0.87878</v>
       </c>
       <c r="K125" t="n">
         <v>2.26897</v>
@@ -5848,7 +5848,7 @@
         <v>-0.14837</v>
       </c>
       <c r="J126" t="n">
-        <v>0.27473</v>
+        <v>0.29782</v>
       </c>
       <c r="K126" t="n">
         <v>1.95409</v>
@@ -5891,7 +5891,7 @@
         <v>-0.14859</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.36777</v>
+        <v>-0.3775</v>
       </c>
       <c r="K127" t="n">
         <v>1.91472</v>
@@ -5934,7 +5934,7 @@
         <v>-0.14881</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.16224</v>
+        <v>-0.12894</v>
       </c>
       <c r="K128" t="n">
         <v>1.65009</v>
@@ -5977,7 +5977,7 @@
         <v>-0.14903</v>
       </c>
       <c r="J129" t="n">
-        <v>0.60939</v>
+        <v>0.6522</v>
       </c>
       <c r="K129" t="n">
         <v>1.14246</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0.37904</v>
+        <v>0.34641</v>
       </c>
       <c r="K130" t="n">
         <v>0.81443</v>
@@ -6063,7 +6063,7 @@
         <v>-0.29806</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.44726</v>
+        <v>-6.46202</v>
       </c>
       <c r="K131" t="n">
         <v>0.37089</v>
@@ -6106,7 +6106,7 @@
         <v>-0.59613</v>
       </c>
       <c r="J132" t="n">
-        <v>-7.12004</v>
+        <v>-7.12502</v>
       </c>
       <c r="K132" t="n">
         <v>0.02314</v>
@@ -6149,7 +6149,7 @@
         <v>-0.89286</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.86327</v>
+        <v>-7.87357</v>
       </c>
       <c r="K133" t="n">
         <v>-0.05777</v>
@@ -6192,7 +6192,7 @@
         <v>-1.3373</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.87932</v>
+        <v>-7.89684</v>
       </c>
       <c r="K134" t="n">
         <v>0.53247</v>
@@ -6235,7 +6235,7 @@
         <v>-1.63205</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.84519</v>
+        <v>-7.86888</v>
       </c>
       <c r="K135" t="n">
         <v>0.53161</v>
@@ -6278,7 +6278,7 @@
         <v>-1.92878</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.14851</v>
+        <v>-7.13323</v>
       </c>
       <c r="K136" t="n">
         <v>1.02938</v>
@@ -6321,7 +6321,7 @@
         <v>-1.93165</v>
       </c>
       <c r="J137" t="n">
-        <v>-6.82902</v>
+        <v>-6.80835</v>
       </c>
       <c r="K137" t="n">
         <v>1.2942</v>
@@ -6364,7 +6364,7 @@
         <v>-2.08024</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.62405</v>
+        <v>-6.6022</v>
       </c>
       <c r="K138" t="n">
         <v>1.69726</v>
@@ -6407,7 +6407,7 @@
         <v>-1.93452</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.48698</v>
+        <v>-5.48671</v>
       </c>
       <c r="K139" t="n">
         <v>2.02858</v>
@@ -6450,7 +6450,7 @@
         <v>-1.93741</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.06327</v>
+        <v>-5.03356</v>
       </c>
       <c r="K140" t="n">
         <v>2.02625</v>
@@ -6493,7 +6493,7 @@
         <v>-1.79104</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.31579</v>
+        <v>-5.26748</v>
       </c>
       <c r="K141" t="n">
         <v>2.5242</v>
@@ -6536,7 +6536,7 @@
         <v>-1.9403</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.47781</v>
+        <v>-5.50656</v>
       </c>
       <c r="K142" t="n">
         <v>2.82747</v>
@@ -6579,7 +6579,7 @@
         <v>-1.9432</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.53771</v>
+        <v>-0.61918</v>
       </c>
       <c r="K143" t="n">
         <v>3.29099</v>
@@ -6622,7 +6622,7 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.45735</v>
+        <v>1.44288</v>
       </c>
       <c r="K144" t="n">
         <v>3.63258</v>
@@ -6665,7 +6665,7 @@
         <v>-1.65165</v>
       </c>
       <c r="J145" t="n">
-        <v>2.53957</v>
+        <v>2.52605</v>
       </c>
       <c r="K145" t="n">
         <v>4</v>
@@ -6708,7 +6708,7 @@
         <v>-1.35542</v>
       </c>
       <c r="J146" t="n">
-        <v>3.6765</v>
+        <v>3.65906</v>
       </c>
       <c r="K146" t="n">
         <v>3.7536</v>
@@ -6751,7 +6751,7 @@
         <v>-1.20664</v>
       </c>
       <c r="J147" t="n">
-        <v>3.14863</v>
+        <v>3.11965</v>
       </c>
       <c r="K147" t="n">
         <v>3.73606</v>
@@ -6794,7 +6794,7 @@
         <v>-0.75643</v>
       </c>
       <c r="J148" t="n">
-        <v>2.77776</v>
+        <v>2.80843</v>
       </c>
       <c r="K148" t="n">
         <v>3.1826</v>
@@ -6837,7 +6837,7 @@
         <v>-0.45455</v>
       </c>
       <c r="J149" t="n">
-        <v>2.01721</v>
+        <v>2.05341</v>
       </c>
       <c r="K149" t="n">
         <v>2.64659</v>
@@ -6880,7 +6880,7 @@
         <v>-0.30349</v>
       </c>
       <c r="J150" t="n">
-        <v>1.69823</v>
+        <v>1.73333</v>
       </c>
       <c r="K150" t="n">
         <v>2.05495</v>
@@ -6923,7 +6923,7 @@
         <v>-0.30349</v>
       </c>
       <c r="J151" t="n">
-        <v>0.24069</v>
+        <v>0.23828</v>
       </c>
       <c r="K151" t="n">
         <v>1.68324</v>
@@ -6966,7 +6966,7 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.63309</v>
+        <v>0.67217</v>
       </c>
       <c r="K152" t="n">
         <v>1.47822</v>
@@ -7009,7 +7009,7 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>0.95988</v>
+        <v>1.02751</v>
       </c>
       <c r="K153" t="n">
         <v>1.21417</v>
@@ -7052,7 +7052,7 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.1217</v>
+        <v>1.08998</v>
       </c>
       <c r="K154" t="n">
         <v>1.42536</v>
@@ -7095,7 +7095,7 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.58971</v>
+        <v>2.46874</v>
       </c>
       <c r="K155" t="n">
         <v>1.45333</v>
@@ -7138,7 +7138,7 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.93549</v>
+        <v>1.92564</v>
       </c>
       <c r="K156" t="n">
         <v>1.45122</v>
@@ -7181,7 +7181,7 @@
         <v>-0.30534</v>
       </c>
       <c r="J157" t="n">
-        <v>2.43277</v>
+        <v>2.43307</v>
       </c>
       <c r="K157" t="n">
         <v>1.44509</v>
@@ -7224,7 +7224,7 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.3456</v>
+        <v>1.33273</v>
       </c>
       <c r="K158" t="n">
         <v>1.70902</v>
@@ -7267,7 +7267,7 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.65365</v>
+        <v>1.63251</v>
       </c>
       <c r="K159" t="n">
         <v>1.97252</v>
@@ -7310,7 +7310,7 @@
         <v>-0.9146300000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>1.57828</v>
+        <v>1.61073</v>
       </c>
       <c r="K160" t="n">
         <v>2.50749</v>
@@ -7353,7 +7353,7 @@
         <v>-1.06545</v>
       </c>
       <c r="J161" t="n">
-        <v>2.46817</v>
+        <v>2.49768</v>
       </c>
       <c r="K161" t="n">
         <v>3.12292</v>
@@ -7396,7 +7396,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J162" t="n">
-        <v>3.24554</v>
+        <v>3.27016</v>
       </c>
       <c r="K162" t="n">
         <v>3.6489</v>
@@ -7439,7 +7439,7 @@
         <v>-1.21766</v>
       </c>
       <c r="J163" t="n">
-        <v>4.06003</v>
+        <v>4.0691</v>
       </c>
       <c r="K163" t="n">
         <v>3.95512</v>
@@ -7482,7 +7482,7 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.68901</v>
+        <v>3.70529</v>
       </c>
       <c r="K164" t="n">
         <v>4.25887</v>
@@ -7525,7 +7525,7 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.90116</v>
+        <v>2.92963</v>
       </c>
       <c r="K165" t="n">
         <v>4.28746</v>
@@ -7568,7 +7568,7 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53606</v>
+        <v>2.53474</v>
       </c>
       <c r="K166" t="n">
         <v>4.07215</v>
@@ -7611,7 +7611,7 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.64577</v>
+        <v>3.55958</v>
       </c>
       <c r="K167" t="n">
         <v>3.83471</v>
@@ -7654,7 +7654,7 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.48903</v>
+        <v>3.47452</v>
       </c>
       <c r="K168" t="n">
         <v>4.12632</v>
@@ -7697,7 +7697,7 @@
         <v>-0.30628</v>
       </c>
       <c r="J169" t="n">
-        <v>2.88899</v>
+        <v>2.88885</v>
       </c>
       <c r="K169" t="n">
         <v>3.8352</v>
@@ -7740,7 +7740,7 @@
         <v>-0.15337</v>
       </c>
       <c r="J170" t="n">
-        <v>2.8595</v>
+        <v>2.85889</v>
       </c>
       <c r="K170" t="n">
         <v>3.55701</v>
@@ -7783,7 +7783,7 @@
         <v>0.15361</v>
       </c>
       <c r="J171" t="n">
-        <v>2.90364</v>
+        <v>2.90655</v>
       </c>
       <c r="K171" t="n">
         <v>3.53184</v>
@@ -7826,7 +7826,7 @@
         <v>0.46154</v>
       </c>
       <c r="J172" t="n">
-        <v>3.17376</v>
+        <v>3.18469</v>
       </c>
       <c r="K172" t="n">
         <v>3.53934</v>
@@ -7869,7 +7869,7 @@
         <v>0.61538</v>
       </c>
       <c r="J173" t="n">
-        <v>2.84697</v>
+        <v>2.86077</v>
       </c>
       <c r="K173" t="n">
         <v>3.54564</v>
@@ -7912,7 +7912,7 @@
         <v>1.07858</v>
       </c>
       <c r="J174" t="n">
-        <v>2.57146</v>
+        <v>2.58488</v>
       </c>
       <c r="K174" t="n">
         <v>3.30579</v>
@@ -7955,7 +7955,7 @@
         <v>1.23267</v>
       </c>
       <c r="J175" t="n">
-        <v>2.85249</v>
+        <v>2.85953</v>
       </c>
       <c r="K175" t="n">
         <v>3.03516</v>
@@ -7998,7 +7998,7 @@
         <v>1.54321</v>
       </c>
       <c r="J176" t="n">
-        <v>2.54943</v>
+        <v>2.5597</v>
       </c>
       <c r="K176" t="n">
         <v>3.00768</v>
@@ -8041,7 +8041,7 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.89899</v>
+        <v>2.90967</v>
       </c>
       <c r="K177" t="n">
         <v>3.04612</v>
@@ -8084,7 +8084,7 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.8443</v>
+        <v>3.84693</v>
       </c>
       <c r="K178" t="n">
         <v>2.99841</v>
@@ -8127,7 +8127,7 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.50138</v>
+        <v>2.44211</v>
       </c>
       <c r="K179" t="n">
         <v>2.93962</v>
@@ -8170,7 +8170,7 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.7898</v>
+        <v>1.78551</v>
       </c>
       <c r="K180" t="n">
         <v>2.5996</v>
@@ -8213,7 +8213,7 @@
         <v>1.07527</v>
       </c>
       <c r="J181" t="n">
-        <v>1.81114</v>
+        <v>1.8174</v>
       </c>
       <c r="K181" t="n">
         <v>2.92317</v>
@@ -8256,7 +8256,7 @@
         <v>1.07527</v>
       </c>
       <c r="J182" t="n">
-        <v>1.44834</v>
+        <v>1.4518</v>
       </c>
       <c r="K182" t="n">
         <v>2.89748</v>
@@ -8299,7 +8299,7 @@
         <v>0.92025</v>
       </c>
       <c r="J183" t="n">
-        <v>1.73082</v>
+        <v>1.7339</v>
       </c>
       <c r="K183" t="n">
         <v>2.6871</v>
@@ -8342,7 +8342,7 @@
         <v>0.7657</v>
       </c>
       <c r="J184" t="n">
-        <v>1.24422</v>
+        <v>1.25115</v>
       </c>
       <c r="K184" t="n">
         <v>2.43571</v>
@@ -8385,7 +8385,7 @@
         <v>0.6116200000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>1.47008</v>
+        <v>1.47674</v>
       </c>
       <c r="K185" t="n">
         <v>1.88385</v>
@@ -8428,7 +8428,7 @@
         <v>0.30488</v>
       </c>
       <c r="J186" t="n">
-        <v>1.51106</v>
+        <v>1.51615</v>
       </c>
       <c r="K186" t="n">
         <v>1.84935</v>
@@ -8471,7 +8471,7 @@
         <v>0.30441</v>
       </c>
       <c r="J187" t="n">
-        <v>1.01779</v>
+        <v>1.01808</v>
       </c>
       <c r="K187" t="n">
         <v>2.09522</v>
@@ -8514,7 +8514,7 @@
         <v>0.15198</v>
       </c>
       <c r="J188" t="n">
-        <v>1.00866</v>
+        <v>1.01257</v>
       </c>
       <c r="K188" t="n">
         <v>2.29861</v>
@@ -8557,7 +8557,7 @@
         <v>-0.15152</v>
       </c>
       <c r="J189" t="n">
-        <v>1.05817</v>
+        <v>1.06062</v>
       </c>
       <c r="K189" t="n">
         <v>2.56331</v>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.38504</v>
+        <v>0.3828</v>
       </c>
       <c r="K190" t="n">
         <v>2.8595</v>
@@ -8643,7 +8643,7 @@
         <v>0.15175</v>
       </c>
       <c r="J191" t="n">
-        <v>0.89527</v>
+        <v>0.87202</v>
       </c>
       <c r="K191" t="n">
         <v>3.06186</v>
@@ -8686,7 +8686,7 @@
         <v>0.15175</v>
       </c>
       <c r="J192" t="n">
-        <v>1.49476</v>
+        <v>1.49477</v>
       </c>
       <c r="K192" t="n">
         <v>3.16201</v>
@@ -8729,7 +8729,7 @@
         <v>0.30395</v>
       </c>
       <c r="J193" t="n">
-        <v>1.29022</v>
+        <v>1.2914</v>
       </c>
       <c r="K193" t="n">
         <v>2.85041</v>
@@ -8772,7 +8772,7 @@
         <v>0.30395</v>
       </c>
       <c r="J194" t="n">
-        <v>1.42027</v>
+        <v>1.42623</v>
       </c>
       <c r="K194" t="n">
         <v>2.60086</v>
@@ -8815,7 +8815,7 @@
         <v>0.15198</v>
       </c>
       <c r="J195" t="n">
-        <v>0.91559</v>
+        <v>0.91827</v>
       </c>
       <c r="K195" t="n">
         <v>2.29991</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>1.26881</v>
+        <v>1.27211</v>
       </c>
       <c r="K196" t="n">
         <v>2.24513</v>
@@ -8901,7 +8901,7 @@
         <v>-0.15198</v>
       </c>
       <c r="J197" t="n">
-        <v>0.67027</v>
+        <v>0.67276</v>
       </c>
       <c r="K197" t="n">
         <v>2.1657</v>
@@ -8944,7 +8944,7 @@
         <v>-0.45593</v>
       </c>
       <c r="J198" t="n">
-        <v>0.25299</v>
+        <v>0.25473</v>
       </c>
       <c r="K198" t="n">
         <v>2.20341</v>
@@ -8987,7 +8987,7 @@
         <v>-0.75873</v>
       </c>
       <c r="J199" t="n">
-        <v>1.03615</v>
+        <v>1.03418</v>
       </c>
       <c r="K199" t="n">
         <v>1.69664</v>
@@ -9030,7 +9030,7 @@
         <v>-1.06222</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.23672</v>
+        <v>-0.23442</v>
       </c>
       <c r="K200" t="n">
         <v>1.38664</v>
@@ -9073,7 +9073,7 @@
         <v>-1.06222</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.20488</v>
+        <v>-0.20364</v>
       </c>
       <c r="K201" t="n">
         <v>0.80621</v>
@@ -9116,7 +9116,7 @@
         <v>-1.36364</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.66879</v>
+        <v>-0.6785</v>
       </c>
       <c r="K202" t="n">
         <v>0.28101</v>
@@ -9159,7 +9159,7 @@
         <v>-1.21212</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.90621</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="K203" t="n">
         <v>-0.19006</v>
@@ -9202,7 +9202,7 @@
         <v>-1.21212</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.05949</v>
+        <v>-1.06044</v>
       </c>
       <c r="K204" t="n">
         <v>-0.55911</v>
@@ -9245,7 +9245,7 @@
         <v>-1.06061</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.99823</v>
+        <v>-0.9976699999999999</v>
       </c>
       <c r="K205" t="n">
         <v>-0.55827</v>
@@ -9288,7 +9288,7 @@
         <v>-0.90909</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.3367</v>
+        <v>-0.33444</v>
       </c>
       <c r="K206" t="n">
         <v>-0.33932</v>
@@ -9331,7 +9331,7 @@
         <v>-0.60698</v>
       </c>
       <c r="J207" t="n">
-        <v>0.17643</v>
+        <v>0.17909</v>
       </c>
       <c r="K207" t="n">
         <v>-0.32974</v>
@@ -9374,7 +9374,7 @@
         <v>-0.45593</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.01265</v>
+        <v>-1.01099</v>
       </c>
       <c r="K208" t="n">
         <v>-0.58888</v>
@@ -9417,7 +9417,7 @@
         <v>-0.15221</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.79128</v>
+        <v>-0.79054</v>
       </c>
       <c r="K209" t="n">
         <v>-0.57994</v>
@@ -9460,7 +9460,7 @@
         <v>0.15267</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.95664</v>
+        <v>-0.95639</v>
       </c>
       <c r="K210" t="n">
         <v>-1.14782</v>
@@ -9503,7 +9503,7 @@
         <v>0.30581</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.18673</v>
+        <v>-3.18665</v>
       </c>
       <c r="K211" t="n">
         <v>-1.72827</v>
@@ -9546,7 +9546,7 @@
         <v>0.46012</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.24895</v>
+        <v>-3.2485</v>
       </c>
       <c r="K212" t="n">
         <v>-2.26615</v>
@@ -9589,7 +9589,7 @@
         <v>0.30675</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.50817</v>
+        <v>-4.50734</v>
       </c>
       <c r="K213" t="n">
         <v>-2.51924</v>
@@ -9632,7 +9632,7 @@
         <v>0.30722</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.03658</v>
+        <v>-5.04425</v>
       </c>
       <c r="K214" t="n">
         <v>-3.15252</v>
@@ -9675,7 +9675,7 @@
         <v>-0.15337</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.3027</v>
+        <v>-6.30201</v>
       </c>
       <c r="K215" t="n">
         <v>-3.73822</v>
@@ -9718,7 +9718,7 @@
         <v>-0.46012</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.64558</v>
+        <v>-7.64505</v>
       </c>
       <c r="K216" t="n">
         <v>-4.17671</v>
@@ -9761,7 +9761,7 @@
         <v>-0.91884</v>
       </c>
       <c r="J217" t="n">
-        <v>-7.87332</v>
+        <v>-7.87262</v>
       </c>
       <c r="K217" t="n">
         <v>-5.06266</v>
@@ -9804,7 +9804,7 @@
         <v>-1.37615</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.358840000000001</v>
+        <v>-8.357839999999999</v>
       </c>
       <c r="K218" t="n">
         <v>-5.83817</v>
@@ -9847,7 +9847,7 @@
         <v>-1.67939</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.301830000000001</v>
+        <v>-9.30087</v>
       </c>
       <c r="K219" t="n">
         <v>-6.41604</v>
@@ -9890,7 +9890,7 @@
         <v>-1.98473</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.053039999999999</v>
+        <v>-9.05241</v>
       </c>
       <c r="K220" t="n">
         <v>-6.72691</v>
@@ -9933,7 +9933,7 @@
         <v>-2.13415</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.13443</v>
+        <v>-10.13408</v>
       </c>
       <c r="K221" t="n">
         <v>-6.77864</v>
@@ -9976,7 +9976,7 @@
         <v>-2.28659</v>
       </c>
       <c r="J222" t="n">
-        <v>-10.12146</v>
+        <v>-10.12126</v>
       </c>
       <c r="K222" t="n">
         <v>-6.5933</v>
@@ -10019,7 +10019,7 @@
         <v>-2.28659</v>
       </c>
       <c r="J223" t="n">
-        <v>-8.699960000000001</v>
+        <v>-8.6998</v>
       </c>
       <c r="K223" t="n">
         <v>-6.08925</v>
@@ -10062,7 +10062,7 @@
         <v>-2.29008</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.54204</v>
+        <v>-7.54171</v>
       </c>
       <c r="K224" t="n">
         <v>-5.60776</v>
@@ -10105,7 +10105,7 @@
         <v>-2.29358</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.08703</v>
+        <v>-7.08651</v>
       </c>
       <c r="K225" t="n">
         <v>-5.37381</v>
@@ -10148,7 +10148,7 @@
         <v>-2.29709</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.15033</v>
+        <v>-6.15607</v>
       </c>
       <c r="K226" t="n">
         <v>-4.6192</v>
@@ -10191,7 +10191,7 @@
         <v>-2.30415</v>
       </c>
       <c r="J227" t="n">
-        <v>-5.44063</v>
+        <v>-5.44008</v>
       </c>
       <c r="K227" t="n">
         <v>-3.8001</v>
@@ -10234,7 +10234,7 @@
         <v>-2.15716</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.18349</v>
+        <v>-4.18288</v>
       </c>
       <c r="K228" t="n">
         <v>-3.34241</v>
@@ -10277,7 +10277,7 @@
         <v>-1.85471</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.20643</v>
+        <v>-4.2057</v>
       </c>
       <c r="K229" t="n">
         <v>-2.50264</v>
@@ -10320,7 +10320,7 @@
         <v>-1.70543</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.39894</v>
+        <v>-4.39817</v>
       </c>
       <c r="K230" t="n">
         <v>-1.64841</v>
@@ -10363,7 +10363,7 @@
         <v>-1.39752</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.84446</v>
+        <v>-3.84337</v>
       </c>
       <c r="K231" t="n">
         <v>-0.84628</v>
@@ -10406,7 +10406,7 @@
         <v>-1.09034</v>
       </c>
       <c r="J232" t="n">
-        <v>-3.538</v>
+        <v>-3.53761</v>
       </c>
       <c r="K232" t="n">
         <v>-0.25834</v>
@@ -10449,7 +10449,7 @@
         <v>-1.09034</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.63806</v>
+        <v>-1.63789</v>
       </c>
       <c r="K233" t="n">
         <v>0.34524</v>
@@ -10492,7 +10492,7 @@
         <v>-1.09204</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.38278</v>
+        <v>-1.38235</v>
       </c>
       <c r="K234" t="n">
         <v>0.70263</v>
@@ -10535,7 +10535,7 @@
         <v>-1.24805</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.35651</v>
+        <v>-1.35604</v>
       </c>
       <c r="K235" t="n">
         <v>1.20156</v>
@@ -10578,7 +10578,7 @@
         <v>-1.25</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.42153</v>
+        <v>-1.42164</v>
       </c>
       <c r="K236" t="n">
         <v>1.34185</v>
@@ -10621,7 +10621,7 @@
         <v>-1.25196</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.25722</v>
+        <v>-0.25819</v>
       </c>
       <c r="K237" t="n">
         <v>1.60399</v>
@@ -10664,7 +10664,7 @@
         <v>-1.09718</v>
       </c>
       <c r="J238" t="n">
-        <v>0.24343</v>
+        <v>0.24165</v>
       </c>
       <c r="K238" t="n">
         <v>1.44095</v>
@@ -10707,7 +10707,7 @@
         <v>-0.78616</v>
       </c>
       <c r="J239" t="n">
-        <v>1.33073</v>
+        <v>1.32962</v>
       </c>
       <c r="K239" t="n">
         <v>1.48268</v>
@@ -10750,7 +10750,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J240" t="n">
-        <v>1.67506</v>
+        <v>1.6742</v>
       </c>
       <c r="K240" t="n">
         <v>1.84282</v>
@@ -10793,7 +10793,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J241" t="n">
-        <v>2.18778</v>
+        <v>2.18737</v>
       </c>
       <c r="K241" t="n">
         <v>1.83039</v>
@@ -10836,7 +10836,7 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30182</v>
+        <v>2.3057</v>
       </c>
       <c r="K242" t="n">
         <v>2.02206</v>
@@ -10879,7 +10879,7 @@
         <v>-0.31496</v>
       </c>
       <c r="J243" t="n">
-        <v>2.64182</v>
+        <v>2.642</v>
       </c>
       <c r="K243" t="n">
         <v>2.12835</v>
@@ -10922,7 +10922,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J244" t="n">
-        <v>3.88753</v>
+        <v>3.88704</v>
       </c>
       <c r="K244" t="n">
         <v>2.14764</v>
@@ -10965,7 +10965,7 @@
         <v>-0.47244</v>
       </c>
       <c r="J245" t="n">
-        <v>2.90227</v>
+        <v>2.90177</v>
       </c>
       <c r="K245" t="n">
         <v>1.88152</v>
@@ -11008,7 +11008,7 @@
         <v>-0.47319</v>
       </c>
       <c r="J246" t="n">
-        <v>3.10265</v>
+        <v>3.10559</v>
       </c>
       <c r="K246" t="n">
         <v>1.57793</v>
@@ -11051,7 +11051,7 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46143</v>
+        <v>3.46134</v>
       </c>
       <c r="K247" t="n">
         <v>1.05894</v>
@@ -11094,7 +11094,7 @@
         <v>-0.31646</v>
       </c>
       <c r="J248" t="n">
-        <v>3.43742</v>
+        <v>3.43698</v>
       </c>
       <c r="K248" t="n">
         <v>1.05713</v>
@@ -11137,7 +11137,7 @@
         <v>-0.31696</v>
       </c>
       <c r="J249" t="n">
-        <v>4.29012</v>
+        <v>4.28899</v>
       </c>
       <c r="K249" t="n">
         <v>0.82133</v>
@@ -11180,7 +11180,7 @@
         <v>-0.47544</v>
       </c>
       <c r="J250" t="n">
-        <v>5.36585</v>
+        <v>5.3641</v>
       </c>
       <c r="K250" t="n">
         <v>1.10007</v>
@@ -11223,7 +11223,7 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.69036</v>
+        <v>4.69103</v>
       </c>
       <c r="K251" t="n">
         <v>1.33305</v>
@@ -11266,7 +11266,7 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.78797</v>
+        <v>4.78307</v>
       </c>
       <c r="K252" t="n">
         <v>1.53273</v>
@@ -11309,7 +11309,7 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94894</v>
+        <v>4.94742</v>
       </c>
       <c r="K253" t="n">
         <v>2.11657</v>
@@ -11352,7 +11352,7 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.60807</v>
+        <v>5.61719</v>
       </c>
       <c r="K254" t="n">
         <v>2.04557</v>
@@ -11395,7 +11395,7 @@
         <v>-2.36967</v>
       </c>
       <c r="J255" t="n">
-        <v>5.9486</v>
+        <v>5.94722</v>
       </c>
       <c r="K255" t="n">
         <v>2.39078</v>
@@ -11438,7 +11438,7 @@
         <v>-2.53165</v>
       </c>
       <c r="J256" t="n">
-        <v>5.66697</v>
+        <v>5.66542</v>
       </c>
       <c r="K256" t="n">
         <v>2.43001</v>
@@ -11481,7 +11481,7 @@
         <v>-2.8481</v>
       </c>
       <c r="J257" t="n">
-        <v>6.14219</v>
+        <v>6.14176</v>
       </c>
       <c r="K257" t="n">
         <v>2.75433</v>
@@ -11524,7 +11524,7 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59243</v>
+        <v>6.59563</v>
       </c>
       <c r="K258" t="n">
         <v>3.32875</v>
@@ -11567,7 +11567,7 @@
         <v>-3.01109</v>
       </c>
       <c r="J259" t="n">
-        <v>6.63025</v>
+        <v>6.63027</v>
       </c>
       <c r="K259" t="n">
         <v>3.92676</v>
@@ -11610,7 +11610,7 @@
         <v>-3.01587</v>
       </c>
       <c r="J260" t="n">
-        <v>6.90762</v>
+        <v>6.90766</v>
       </c>
       <c r="K260" t="n">
         <v>4.4273</v>
@@ -11653,7 +11653,7 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46924</v>
+        <v>5.46914</v>
       </c>
       <c r="K261" t="n">
         <v>5.34278</v>
@@ -11696,7 +11696,7 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06101</v>
+        <v>4.06088</v>
       </c>
       <c r="K262" t="n">
         <v>5.81027</v>
@@ -11739,7 +11739,7 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.98382</v>
+        <v>3.97949</v>
       </c>
       <c r="K263" t="n">
         <v>5.86192</v>
@@ -11782,7 +11782,7 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.81029</v>
+        <v>3.8067</v>
       </c>
       <c r="K264" t="n">
         <v>5.94402</v>
@@ -11825,7 +11825,7 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70227</v>
+        <v>3.70119</v>
       </c>
       <c r="K265" t="n">
         <v>5.63483</v>
@@ -11868,7 +11868,7 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.87392</v>
+        <v>2.88233</v>
       </c>
       <c r="K266" t="n">
         <v>5.6398</v>
@@ -11911,7 +11911,7 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68895</v>
+        <v>2.68748</v>
       </c>
       <c r="K267" t="n">
         <v>5.62042</v>
@@ -11954,7 +11954,7 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.1853</v>
+        <v>2.18414</v>
       </c>
       <c r="K268" t="n">
         <v>5.87932</v>
@@ -11997,7 +11997,7 @@
         <v>-1.30293</v>
       </c>
       <c r="J269" t="n">
-        <v>2.61321</v>
+        <v>2.61235</v>
       </c>
       <c r="K269" t="n">
         <v>5.82315</v>
@@ -12040,7 +12040,7 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24366</v>
+        <v>2.24587</v>
       </c>
       <c r="K270" t="n">
         <v>5.58396</v>
@@ -12083,7 +12083,7 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.02601</v>
+        <v>2.03161</v>
       </c>
       <c r="K271" t="n">
         <v>5.54028</v>
@@ -12126,7 +12126,7 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.0678</v>
+        <v>2.0671</v>
       </c>
       <c r="K272" t="n">
         <v>5.03896</v>
@@ -12169,7 +12169,7 @@
         <v>-0.32787</v>
       </c>
       <c r="J273" t="n">
-        <v>2.87074</v>
+        <v>2.86984</v>
       </c>
       <c r="K273" t="n">
         <v>4.36879</v>
@@ -12212,7 +12212,7 @@
         <v>-0.16393</v>
       </c>
       <c r="J274" t="n">
-        <v>2.13217</v>
+        <v>2.1309</v>
       </c>
       <c r="K274" t="n">
         <v>3.66414</v>
@@ -12255,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.58798</v>
+        <v>2.58224</v>
       </c>
       <c r="K275" t="n">
         <v>3.36017</v>
@@ -12298,7 +12298,7 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.64296</v>
+        <v>2.63796</v>
       </c>
       <c r="K276" t="n">
         <v>2.99822</v>
@@ -12341,7 +12341,7 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55402</v>
+        <v>2.55245</v>
       </c>
       <c r="K277" t="n">
         <v>3.04674</v>
@@ -12384,7 +12384,7 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.57185</v>
+        <v>3.58146</v>
       </c>
       <c r="K278" t="n">
         <v>2.88074</v>
@@ -12427,7 +12427,7 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.1063</v>
+        <v>3.10559</v>
       </c>
       <c r="K279" t="n">
         <v>2.73892</v>
@@ -12470,7 +12470,7 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13352</v>
+        <v>3.13309</v>
       </c>
       <c r="K280" t="n">
         <v>2.71797</v>
@@ -12513,7 +12513,7 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52943</v>
+        <v>2.52892</v>
       </c>
       <c r="K281" t="n">
         <v>2.48447</v>
@@ -12556,7 +12556,7 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46751</v>
+        <v>2.46763</v>
       </c>
       <c r="K282" t="n">
         <v>2.70244</v>
@@ -12599,7 +12599,7 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.70799</v>
+        <v>1.71624</v>
       </c>
       <c r="K283" t="n">
         <v>2.46068</v>
@@ -12642,7 +12642,7 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26743</v>
+        <v>1.268</v>
       </c>
       <c r="K284" t="n">
         <v>2.67797</v>
@@ -12685,7 +12685,7 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55165</v>
+        <v>0.55141</v>
       </c>
       <c r="K285" t="n">
         <v>3.00231</v>
@@ -12728,7 +12728,7 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35781</v>
+        <v>1.35608</v>
       </c>
       <c r="K286" t="n">
         <v>3.24569</v>
@@ -12771,7 +12771,7 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.2737</v>
+        <v>1.26568</v>
       </c>
       <c r="K287" t="n">
         <v>3.51063</v>
@@ -12814,7 +12814,7 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.53188</v>
+        <v>0.5226499999999999</v>
       </c>
       <c r="K288" t="n">
         <v>3.84283</v>
@@ -12857,7 +12857,7 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27306</v>
+        <v>-0.27241</v>
       </c>
       <c r="K289" t="n">
         <v>3.51163</v>
@@ -12900,7 +12900,7 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.03921</v>
+        <v>-0.03277</v>
       </c>
       <c r="K290" t="n">
         <v>3.83219</v>
@@ -12943,7 +12943,7 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23633</v>
+        <v>-0.23599</v>
       </c>
       <c r="K291" t="n">
         <v>3.85604</v>
@@ -12986,7 +12986,7 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.73795</v>
+        <v>-0.73863</v>
       </c>
       <c r="K292" t="n">
         <v>3.62291</v>
@@ -13029,7 +13029,7 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52179</v>
+        <v>-0.52303</v>
       </c>
       <c r="K293" t="n">
         <v>3.87311</v>
@@ -13072,7 +13072,7 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82343</v>
+        <v>-0.82197</v>
       </c>
       <c r="K294" t="n">
         <v>3.87626</v>
@@ -13115,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.05965</v>
+        <v>-0.04552</v>
       </c>
       <c r="K295" t="n">
         <v>4.15332</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.2765</v>
+        <v>0.28602</v>
       </c>
       <c r="K296" t="n">
         <v>4.17488</v>
@@ -13201,7 +13201,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.31366</v>
+        <v>0.32261</v>
       </c>
       <c r="K297" t="n">
         <v>3.95179</v>
@@ -13244,7 +13244,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.38168</v>
+        <v>0.36044</v>
       </c>
       <c r="K298" t="n">
         <v>4.13246</v>
@@ -13287,7 +13287,7 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.01211</v>
+        <v>-0.01048</v>
       </c>
       <c r="K299" t="n">
         <v>3.9212</v>
@@ -13330,7 +13330,7 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>1.01079</v>
+        <v>0.97962</v>
       </c>
       <c r="K300" t="n">
         <v>3.5896</v>
@@ -13373,7 +13373,7 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95363</v>
+        <v>1.95677</v>
       </c>
       <c r="K301" t="n">
         <v>3.94713</v>
@@ -13416,7 +13416,7 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47763</v>
+        <v>1.4768</v>
       </c>
       <c r="K302" t="n">
         <v>3.5803</v>
@@ -13459,7 +13459,7 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.98012</v>
+        <v>1.99409</v>
       </c>
       <c r="K303" t="n">
         <v>3.337</v>
@@ -13502,7 +13502,7 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.72928</v>
+        <v>2.7319</v>
       </c>
       <c r="K304" t="n">
         <v>3.55116</v>
@@ -13545,7 +13545,7 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.5036</v>
+        <v>2.49429</v>
       </c>
       <c r="K305" t="n">
         <v>3.30021</v>
@@ -13588,7 +13588,7 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97758</v>
+        <v>2.97543</v>
       </c>
       <c r="K306" t="n">
         <v>3.02342</v>
@@ -13631,7 +13631,7 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.4689</v>
+        <v>3.4969</v>
       </c>
       <c r="K307" t="n">
         <v>2.72177</v>
@@ -13674,7 +13674,7 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.01338</v>
+        <v>3.03719</v>
       </c>
       <c r="K308" t="n">
         <v>2.73775</v>
@@ -13717,7 +13717,7 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.06764</v>
+        <v>3.08096</v>
       </c>
       <c r="K309" t="n">
         <v>2.73209</v>
@@ -13760,7 +13760,7 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.6109</v>
+        <v>2.58841</v>
       </c>
       <c r="K310" t="n">
         <v>2.76807</v>
@@ -13803,7 +13803,7 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.99259</v>
+        <v>2.98433</v>
       </c>
       <c r="K311" t="n">
         <v>2.70029</v>
@@ -13846,7 +13846,7 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.75884</v>
+        <v>2.69887</v>
       </c>
       <c r="K312" t="n">
         <v>2.99187</v>
@@ -13889,7 +13889,7 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.39341</v>
+        <v>2.38404</v>
       </c>
       <c r="K313" t="n">
         <v>2.92574</v>
@@ -13932,7 +13932,7 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.92588</v>
+        <v>1.9528</v>
       </c>
       <c r="K314" t="n">
         <v>3.01226</v>
@@ -13975,7 +13975,7 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.40892</v>
+        <v>2.41476</v>
       </c>
       <c r="K315" t="n">
         <v>3.24698</v>
@@ -14018,7 +14018,7 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62454</v>
+        <v>2.62046</v>
       </c>
       <c r="K316" t="n">
         <v>3.03164</v>
@@ -14061,7 +14061,7 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.4343</v>
+        <v>3.43217</v>
       </c>
       <c r="K317" t="n">
         <v>3.28303</v>
@@ -14104,7 +14104,7 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.37305</v>
+        <v>3.37863</v>
       </c>
       <c r="K318" t="n">
         <v>3.52516</v>
@@ -14147,7 +14147,7 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.14713</v>
+        <v>3.17825</v>
       </c>
       <c r="K319" t="n">
         <v>3.82042</v>
@@ -14190,7 +14190,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.13086</v>
+        <v>3.17942</v>
       </c>
       <c r="K320" t="n">
         <v>3.52384</v>
@@ -14233,7 +14233,7 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.17612</v>
+        <v>3.22843</v>
       </c>
       <c r="K321" t="n">
         <v>3.64797</v>
@@ -14276,7 +14276,7 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.79717</v>
+        <v>3.72531</v>
       </c>
       <c r="K322" t="n">
         <v>3.74826</v>
@@ -14319,7 +14319,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.92594</v>
+        <v>3.89723</v>
       </c>
       <c r="K323" t="n">
         <v>3.7611</v>
@@ -14362,7 +14362,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.69244</v>
+        <v>3.61489</v>
       </c>
       <c r="K324" t="n">
         <v>3.45994</v>
@@ -14405,7 +14405,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.3053</v>
+        <v>3.29177</v>
       </c>
       <c r="K325" t="n">
         <v>3.22274</v>
@@ -14448,7 +14448,7 @@
         <v>-1.1236</v>
       </c>
       <c r="J326" t="n">
-        <v>2.86364</v>
+        <v>2.88502</v>
       </c>
       <c r="K326" t="n">
         <v>2.91555</v>
@@ -14491,7 +14491,7 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.05531</v>
+        <v>2.0911</v>
       </c>
       <c r="K327" t="n">
         <v>2.63791</v>
@@ -14534,7 +14534,7 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82223</v>
+        <v>1.82534</v>
       </c>
       <c r="K328" t="n">
         <v>2.3591</v>
@@ -14577,7 +14577,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.159</v>
+        <v>1.16384</v>
       </c>
       <c r="K329" t="n">
         <v>2.05076</v>
@@ -14620,7 +14620,7 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15519</v>
+        <v>1.1681</v>
       </c>
       <c r="K330" t="n">
         <v>1.53231</v>
@@ -14663,7 +14663,7 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.7251300000000001</v>
+        <v>0.74731</v>
       </c>
       <c r="K331" t="n">
         <v>1.00899</v>
@@ -14706,7 +14706,7 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.13796</v>
+        <v>1.19431</v>
       </c>
       <c r="K332" t="n">
         <v>0.95682</v>
@@ -14749,7 +14749,7 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.19144</v>
+        <v>1.23915</v>
       </c>
       <c r="K333" t="n">
         <v>0.54018</v>
@@ -14792,7 +14792,7 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>1.05912</v>
+        <v>0.99666</v>
       </c>
       <c r="K334" t="n">
         <v>-0.06722</v>
@@ -14835,7 +14835,7 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.72879</v>
+        <v>1.6715</v>
       </c>
       <c r="K335" t="n">
         <v>-0.08391</v>
@@ -14878,7 +14878,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.42959</v>
+        <v>-2.54802</v>
       </c>
       <c r="K336" t="n">
         <v>-0.29335</v>
@@ -14921,7 +14921,7 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.75018</v>
+        <v>2.73802</v>
       </c>
       <c r="K337" t="n">
         <v>-0.32644</v>
@@ -14964,7 +14964,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.53416</v>
+        <v>-0.47447</v>
       </c>
       <c r="K338" t="n">
         <v>-0.36041</v>
@@ -15007,7 +15007,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.09662999999999999</v>
+        <v>-0.05104</v>
       </c>
       <c r="K339" t="n">
         <v>-0.10883</v>
@@ -15050,7 +15050,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.53141</v>
+        <v>-0.52583</v>
       </c>
       <c r="K340" t="n">
         <v>0.14247</v>
@@ -15093,7 +15093,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.22722</v>
+        <v>-1.20356</v>
       </c>
       <c r="K341" t="n">
         <v>0.41028</v>
@@ -15136,7 +15136,7 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.44475</v>
+        <v>-1.41989</v>
       </c>
       <c r="K342" t="n">
         <v>0.6959</v>
@@ -15179,7 +15179,7 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09603</v>
+        <v>-1.09182</v>
       </c>
       <c r="K343" t="n">
         <v>1.15</v>
@@ -15222,7 +15222,7 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.7524</v>
+        <v>-0.70991</v>
       </c>
       <c r="K344" t="n">
         <v>1.21614</v>
@@ -15265,7 +15265,7 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.69997</v>
+        <v>-0.66122</v>
       </c>
       <c r="K345" t="n">
         <v>1.67058</v>
@@ -15308,7 +15308,7 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.1283</v>
+        <v>-0.20806</v>
       </c>
       <c r="K346" t="n">
         <v>2.05145</v>
@@ -15351,7 +15351,7 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.03404</v>
+        <v>-1.10454</v>
       </c>
       <c r="K347" t="n">
         <v>2.04064</v>
@@ -15394,7 +15394,7 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.99028</v>
+        <v>2.90833</v>
       </c>
       <c r="K348" t="n">
         <v>2.52186</v>
@@ -15437,7 +15437,7 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.38906</v>
+        <v>-1.39197</v>
       </c>
       <c r="K349" t="n">
         <v>2.79644</v>
@@ -15480,7 +15480,7 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.55949</v>
+        <v>2.59435</v>
       </c>
       <c r="K350" t="n">
         <v>3.17127</v>
@@ -15523,7 +15523,7 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.77895</v>
+        <v>1.84968</v>
       </c>
       <c r="K351" t="n">
         <v>2.91653</v>
@@ -15566,7 +15566,7 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.56347</v>
+        <v>1.59801</v>
       </c>
       <c r="K352" t="n">
         <v>3.02954</v>
@@ -15609,7 +15609,7 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.2837</v>
+        <v>-49.24015</v>
       </c>
       <c r="K353" t="n">
         <v>-38.88426</v>
@@ -15652,7 +15652,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.49245999999999</v>
+        <v>-69.43351</v>
       </c>
       <c r="K354" t="n">
         <v>-38.41799</v>
@@ -15695,7 +15695,7 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.08623</v>
+        <v>-70.01752</v>
       </c>
       <c r="K355" t="n">
         <v>-33.26971</v>
@@ -15738,7 +15738,7 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.73094</v>
+        <v>-74.59963</v>
       </c>
       <c r="K356" t="n">
         <v>-30.14584</v>
@@ -15781,7 +15781,7 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.87716</v>
+        <v>-74.78266000000001</v>
       </c>
       <c r="K357" t="n">
         <v>-25.53877</v>
@@ -15824,7 +15824,7 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.51204</v>
+        <v>-76.75322</v>
       </c>
       <c r="K358" t="n">
         <v>-26.05866</v>
@@ -15867,7 +15867,7 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.67464</v>
+        <v>-66.87358999999999</v>
       </c>
       <c r="K359" t="n">
         <v>-22.15456</v>
@@ -15910,7 +15910,7 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-56.84703</v>
+        <v>-57.11856</v>
       </c>
       <c r="K360" t="n">
         <v>-20.38373</v>
@@ -15953,7 +15953,7 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.23872</v>
+        <v>-53.25821</v>
       </c>
       <c r="K361" t="n">
         <v>-19.72878</v>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -516,10 +516,10 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.81609</v>
+        <v>6.81605</v>
       </c>
       <c r="K2" t="n">
-        <v>2.30536</v>
+        <v>2.84008</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -559,10 +559,10 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1021</v>
+        <v>4.10206</v>
       </c>
       <c r="K3" t="n">
-        <v>2.43838</v>
+        <v>2.54439</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -602,10 +602,10 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.6442</v>
+        <v>7.64425</v>
       </c>
       <c r="K4" t="n">
-        <v>2.13214</v>
+        <v>2.01085</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -645,10 +645,10 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.78853</v>
+        <v>0.78854</v>
       </c>
       <c r="K5" t="n">
-        <v>2.02286</v>
+        <v>1.80643</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -688,10 +688,10 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8466</v>
+        <v>1.84663</v>
       </c>
       <c r="K6" t="n">
-        <v>1.99344</v>
+        <v>1.68266</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.08452</v>
+        <v>2.08457</v>
       </c>
       <c r="K7" t="n">
-        <v>1.70179</v>
+        <v>1.57501</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.63766</v>
+        <v>4.63772</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47346</v>
+        <v>1.42465</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>6.97377</v>
+        <v>6.97373</v>
       </c>
       <c r="K9" t="n">
-        <v>1.21062</v>
+        <v>1.46252</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>7.98007</v>
+        <v>7.98011</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7003</v>
+        <v>0.9501500000000001</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.82782</v>
+        <v>5.82776</v>
       </c>
       <c r="K11" t="n">
-        <v>0.36237</v>
+        <v>0.73997</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>2.95026</v>
+        <v>2.95021</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05167</v>
+        <v>0.3626</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5115</v>
+        <v>3.51145</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.19355</v>
+        <v>0.49242</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>1.94709</v>
+        <v>1.94706</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7726</v>
+        <v>-0.29681</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15431</v>
+        <v>3.15426</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0036</v>
+        <v>-0.2197</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.82043</v>
+        <v>4.82049</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.22423</v>
+        <v>-0.02594</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         <v>0.29326</v>
       </c>
       <c r="J17" t="n">
-        <v>5.38343</v>
+        <v>5.38346</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.68662</v>
+        <v>-0.46626</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.36433</v>
+        <v>4.36438</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9802</v>
+        <v>-0.69813</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1247,10 +1247,10 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.86557</v>
+        <v>3.86565</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.25254</v>
+        <v>-0.98204</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.97695</v>
+        <v>0.977</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.53148</v>
+        <v>-1.15979</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>-1.18743</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.58521</v>
+        <v>-1.287</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.91307</v>
+        <v>-2.91305</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.39536</v>
+        <v>-1.16039</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.67745</v>
+        <v>-2.67749</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.39845</v>
+        <v>-1.26289</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.96168</v>
+        <v>-2.96175</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.19496</v>
+        <v>-1.03226</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.79348</v>
+        <v>-3.79352</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.95217</v>
+        <v>-0.92843</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-6.73931</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.50532</v>
+        <v>-0.60834</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.3248</v>
+        <v>-7.32486</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.97479</v>
+        <v>-0.09066</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.12541</v>
+        <v>-7.12538</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.45662</v>
+        <v>0.22052</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
         <v>0.2924</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.415509999999999</v>
+        <v>-8.4155</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3143</v>
+        <v>0.91087</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.85283</v>
+        <v>-7.85279</v>
       </c>
       <c r="K30" t="n">
-        <v>0.61656</v>
+        <v>1.13267</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.16305</v>
+        <v>-7.16299</v>
       </c>
       <c r="K31" t="n">
-        <v>1.1193</v>
+        <v>1.23972</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.55991</v>
+        <v>-7.55984</v>
       </c>
       <c r="K32" t="n">
-        <v>1.33158</v>
+        <v>1.27771</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.48601</v>
+        <v>-8.486050000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>1.54476</v>
+        <v>1.08214</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.68218</v>
+        <v>-7.68216</v>
       </c>
       <c r="K34" t="n">
-        <v>1.57013</v>
+        <v>1.22619</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.99341</v>
+        <v>-5.99346</v>
       </c>
       <c r="K35" t="n">
-        <v>1.61184</v>
+        <v>1.29209</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.30628</v>
+        <v>-7.30635</v>
       </c>
       <c r="K36" t="n">
-        <v>1.34653</v>
+        <v>1.02999</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.43272</v>
+        <v>-7.43275</v>
       </c>
       <c r="K37" t="n">
-        <v>1.04167</v>
+        <v>0.52063</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>-0.58224</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.37111</v>
+        <v>-3.37112</v>
       </c>
       <c r="K38" t="n">
-        <v>0.59289</v>
+        <v>0.55997</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.19051</v>
+        <v>-2.19057</v>
       </c>
       <c r="K39" t="n">
-        <v>0.03938</v>
+        <v>-0.09074</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.43984</v>
+        <v>-1.43978</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.23591</v>
+        <v>-0.16826</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         <v>-0.87464</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.49025</v>
+        <v>-0.49023</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.75718</v>
+        <v>-0.59317</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.87713</v>
+        <v>-0.87709</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.08214</v>
+        <v>-1.01699</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.88075</v>
+        <v>-0.88068</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.06785</v>
+        <v>-0.72184</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.33254</v>
+        <v>1.3327</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.27505</v>
+        <v>-0.68229</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.55997</v>
+        <v>0.55987</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.24821</v>
+        <v>-0.61912</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>1.28625</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.2211</v>
+        <v>-0.3866</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>0.98449</v>
+        <v>0.98446</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.00117</v>
+        <v>-0.33501</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.60512</v>
+        <v>2.605</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.42986</v>
+        <v>0.42586</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.47552</v>
+        <v>2.47542</v>
       </c>
       <c r="K49" t="n">
-        <v>0.11745</v>
+        <v>0.86754</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.36814</v>
+        <v>1.36817</v>
       </c>
       <c r="K50" t="n">
-        <v>0.60249</v>
+        <v>0.9712499999999999</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.16896</v>
+        <v>0.16894</v>
       </c>
       <c r="K51" t="n">
-        <v>0.87903</v>
+        <v>1.10289</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.72938</v>
+        <v>-0.72934</v>
       </c>
       <c r="K52" t="n">
-        <v>0.88019</v>
+        <v>0.89459</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         <v>-0.44118</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.54603</v>
+        <v>-0.546</v>
       </c>
       <c r="K53" t="n">
-        <v>0.84188</v>
+        <v>0.71345</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.36018</v>
+        <v>-0.36014</v>
       </c>
       <c r="K54" t="n">
-        <v>0.88309</v>
+        <v>0.94941</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.19125</v>
+        <v>-1.19121</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6186700000000001</v>
+        <v>0.7141</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05834</v>
+        <v>-2.05821</v>
       </c>
       <c r="K56" t="n">
-        <v>0.57986</v>
+        <v>0.53143</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.18496</v>
+        <v>-0.18508</v>
       </c>
       <c r="K57" t="n">
-        <v>0.30283</v>
+        <v>0.38936</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>-1.03703</v>
       </c>
       <c r="K58" t="n">
-        <v>0.24987</v>
+        <v>0.18111</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>-2.17946</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.01313</v>
+        <v>0.05171</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3010,10 +3010,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.12351</v>
+        <v>-1.12358</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.30089</v>
+        <v>-0.44976</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.0091</v>
+        <v>-1.00918</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.57351</v>
+        <v>-0.46213</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.7541099999999999</v>
+        <v>-0.75408</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.80719</v>
+        <v>-0.69257</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         <v>-0.44248</v>
       </c>
       <c r="J63" t="n">
-        <v>1.256</v>
+        <v>1.25602</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.76733</v>
+        <v>-0.19251</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>2.01069</v>
+        <v>2.01072</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.5209</v>
+        <v>0.03855</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.76275</v>
+        <v>0.76276</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.28698</v>
+        <v>0.1932</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3268,10 +3268,10 @@
         <v>0.14771</v>
       </c>
       <c r="J66" t="n">
-        <v>1.11255</v>
+        <v>1.11257</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>0.3865</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.19418</v>
+        <v>2.19419</v>
       </c>
       <c r="K67" t="n">
-        <v>0.23548</v>
+        <v>0.65747</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.41851</v>
+        <v>2.41859</v>
       </c>
       <c r="K68" t="n">
-        <v>0.79927</v>
+        <v>1.07014</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.18366</v>
+        <v>2.1836</v>
       </c>
       <c r="K69" t="n">
-        <v>1.11578</v>
+        <v>1.48675</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.97359</v>
+        <v>2.97354</v>
       </c>
       <c r="K70" t="n">
-        <v>1.12816</v>
+        <v>1.20093</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.16049</v>
+        <v>3.16057</v>
       </c>
       <c r="K71" t="n">
-        <v>1.15592</v>
+        <v>1.36969</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.06427</v>
+        <v>2.06422</v>
       </c>
       <c r="K72" t="n">
-        <v>0.91851</v>
+        <v>1.05847</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.76241</v>
+        <v>3.76233</v>
       </c>
       <c r="K73" t="n">
-        <v>0.957</v>
+        <v>1.31545</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>3.28823</v>
+        <v>3.28825</v>
       </c>
       <c r="K74" t="n">
-        <v>0.95813</v>
+        <v>1.38189</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
         <v>0.59259</v>
       </c>
       <c r="J75" t="n">
-        <v>1.56011</v>
+        <v>1.56013</v>
       </c>
       <c r="K75" t="n">
-        <v>0.93054</v>
+        <v>1.10582</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         <v>0.44379</v>
       </c>
       <c r="J76" t="n">
-        <v>1.23795</v>
+        <v>1.23796</v>
       </c>
       <c r="K76" t="n">
-        <v>0.94253</v>
+        <v>1.14322</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>1.25017</v>
       </c>
       <c r="K77" t="n">
-        <v>0.98116</v>
+        <v>1.23409</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>-0.04673</v>
       </c>
       <c r="K78" t="n">
-        <v>1.20199</v>
+        <v>1.3347</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.37349</v>
+        <v>-1.37351</v>
       </c>
       <c r="K79" t="n">
-        <v>1.22683</v>
+        <v>1.16547</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -3870,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.29687</v>
+        <v>-1.29682</v>
       </c>
       <c r="K80" t="n">
-        <v>0.93592</v>
+        <v>0.82919</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         <v>-0.14749</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.46389</v>
+        <v>-1.46391</v>
       </c>
       <c r="K81" t="n">
-        <v>1.19434</v>
+        <v>1.15924</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.77292</v>
+        <v>-1.77296</v>
       </c>
       <c r="K82" t="n">
-        <v>1.45285</v>
+        <v>1.44188</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.09116</v>
+        <v>-1.09105</v>
       </c>
       <c r="K83" t="n">
-        <v>1.71406</v>
+        <v>1.4659</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.28652</v>
+        <v>-1.28656</v>
       </c>
       <c r="K84" t="n">
-        <v>2.22338</v>
+        <v>2.05646</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4085,10 +4085,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.96701</v>
+        <v>-1.96704</v>
       </c>
       <c r="K85" t="n">
-        <v>2.22049</v>
+        <v>1.73116</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.70263</v>
+        <v>-1.70266</v>
       </c>
       <c r="K86" t="n">
-        <v>2.4701</v>
+        <v>1.91083</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.26517</v>
+        <v>-1.26516</v>
       </c>
       <c r="K87" t="n">
-        <v>2.46721</v>
+        <v>1.81864</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>-0.99314</v>
       </c>
       <c r="K88" t="n">
-        <v>2.45104</v>
+        <v>1.7272</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>-0.57683</v>
       </c>
       <c r="K89" t="n">
-        <v>2.48737</v>
+        <v>1.91746</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
         <v>-0.73746</v>
       </c>
       <c r="J90" t="n">
-        <v>0.14622</v>
+        <v>0.14621</v>
       </c>
       <c r="K90" t="n">
-        <v>2.01394</v>
+        <v>1.57042</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J91" t="n">
-        <v>0.38672</v>
+        <v>0.38669</v>
       </c>
       <c r="K91" t="n">
-        <v>1.97267</v>
+        <v>1.5445</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.28095</v>
+        <v>-0.28089</v>
       </c>
       <c r="K92" t="n">
-        <v>1.75145</v>
+        <v>1.49291</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>-1.01728</v>
       </c>
       <c r="K93" t="n">
-        <v>1.48813</v>
+        <v>1.25929</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.34254</v>
+        <v>-1.34261</v>
       </c>
       <c r="K94" t="n">
-        <v>1.26582</v>
+        <v>1.22013</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.92056</v>
+        <v>-1.92039</v>
       </c>
       <c r="K95" t="n">
-        <v>1.21282</v>
+        <v>1.10553</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.26395</v>
+        <v>-1.26401</v>
       </c>
       <c r="K96" t="n">
-        <v>1.20834</v>
+        <v>1.15144</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95133</v>
+        <v>-1.95136</v>
       </c>
       <c r="K97" t="n">
-        <v>1.47358</v>
+        <v>1.46396</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.93973</v>
+        <v>-1.93977</v>
       </c>
       <c r="K98" t="n">
-        <v>1.68739</v>
+        <v>1.5125</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>-2.02239</v>
       </c>
       <c r="K99" t="n">
-        <v>1.96426</v>
+        <v>1.82363</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.2576</v>
+        <v>-2.25761</v>
       </c>
       <c r="K100" t="n">
-        <v>2.26582</v>
+        <v>2.22222</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>-1.59827</v>
       </c>
       <c r="K101" t="n">
-        <v>2.30059</v>
+        <v>2.15549</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>-1.14518</v>
       </c>
       <c r="K102" t="n">
-        <v>2.80942</v>
+        <v>2.55611</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4859,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.72556</v>
+        <v>-0.72557</v>
       </c>
       <c r="K103" t="n">
-        <v>3.13567</v>
+        <v>2.89241</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.65101</v>
+        <v>-1.651</v>
       </c>
       <c r="K104" t="n">
-        <v>3.40463</v>
+        <v>3.1289</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -4945,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.3399</v>
+        <v>-1.33988</v>
       </c>
       <c r="K105" t="n">
-        <v>3.72898</v>
+        <v>3.33292</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.70895</v>
+        <v>-1.70899</v>
       </c>
       <c r="K106" t="n">
-        <v>4.01515</v>
+        <v>3.70324</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.68676</v>
+        <v>0.6869</v>
       </c>
       <c r="K107" t="n">
-        <v>4.36428</v>
+        <v>3.93887</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5074,10 +5074,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.65398</v>
+        <v>1.65392</v>
       </c>
       <c r="K108" t="n">
-        <v>4.39864</v>
+        <v>3.95942</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32125</v>
+        <v>2.32122</v>
       </c>
       <c r="K109" t="n">
-        <v>4.68202</v>
+        <v>3.99556</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5160,10 +5160,10 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.66954</v>
+        <v>0.66951</v>
       </c>
       <c r="K110" t="n">
-        <v>4.75359</v>
+        <v>4.24825</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         <v>0.29718</v>
       </c>
       <c r="J111" t="n">
-        <v>0.87768</v>
+        <v>0.87769</v>
       </c>
       <c r="K111" t="n">
-        <v>4.52399</v>
+        <v>3.75368</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
         <v>0.44577</v>
       </c>
       <c r="J112" t="n">
-        <v>1.75034</v>
+        <v>1.75033</v>
       </c>
       <c r="K112" t="n">
-        <v>4.53026</v>
+        <v>3.90816</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5289,10 +5289,10 @@
         <v>0.29718</v>
       </c>
       <c r="J113" t="n">
-        <v>2.71015</v>
+        <v>2.71016</v>
       </c>
       <c r="K113" t="n">
-        <v>4.5595</v>
+        <v>3.9395</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>2.88092</v>
       </c>
       <c r="K114" t="n">
-        <v>4.56672</v>
+        <v>4.02432</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>3.29157</v>
       </c>
       <c r="K115" t="n">
-        <v>4.36435</v>
+        <v>3.92585</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -5418,10 +5418,10 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.94635</v>
+        <v>3.94636</v>
       </c>
       <c r="K116" t="n">
-        <v>4.58996</v>
+        <v>4.02514</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5461,10 +5461,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.91094</v>
+        <v>3.91096</v>
       </c>
       <c r="K117" t="n">
-        <v>4.53327</v>
+        <v>3.74293</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.2419</v>
+        <v>5.24186</v>
       </c>
       <c r="K118" t="n">
-        <v>4.33358</v>
+        <v>3.63092</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5547,10 +5547,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.63188</v>
+        <v>3.63198</v>
       </c>
       <c r="K119" t="n">
-        <v>4.27846</v>
+        <v>3.63419</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.87629</v>
+        <v>1.87625</v>
       </c>
       <c r="K120" t="n">
-        <v>4.03274</v>
+        <v>3.29683</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.44758</v>
+        <v>1.44755</v>
       </c>
       <c r="K121" t="n">
-        <v>3.50395</v>
+        <v>3.08313</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
         <v>-0.2963</v>
       </c>
       <c r="J122" t="n">
-        <v>3.30475</v>
+        <v>3.30474</v>
       </c>
       <c r="K122" t="n">
-        <v>2.89424</v>
+        <v>2.27971</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>3.27764</v>
       </c>
       <c r="K123" t="n">
-        <v>2.88942</v>
+        <v>2.63656</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>2.21596</v>
       </c>
       <c r="K124" t="n">
-        <v>2.38011</v>
+        <v>2.23319</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
         <v>-0.2963</v>
       </c>
       <c r="J125" t="n">
-        <v>0.87878</v>
+        <v>0.87879</v>
       </c>
       <c r="K125" t="n">
-        <v>2.26897</v>
+        <v>1.86576</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5848,10 +5848,10 @@
         <v>-0.14837</v>
       </c>
       <c r="J126" t="n">
-        <v>0.29782</v>
+        <v>0.29783</v>
       </c>
       <c r="K126" t="n">
-        <v>1.95409</v>
+        <v>1.56615</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>-0.3775</v>
       </c>
       <c r="K127" t="n">
-        <v>1.91472</v>
+        <v>1.43407</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -5934,10 +5934,10 @@
         <v>-0.14881</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.12894</v>
+        <v>-0.12893</v>
       </c>
       <c r="K128" t="n">
-        <v>1.65009</v>
+        <v>1.42924</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>0.6522</v>
       </c>
       <c r="K129" t="n">
-        <v>1.14246</v>
+        <v>0.96288</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6020,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0.34641</v>
+        <v>0.34642</v>
       </c>
       <c r="K130" t="n">
-        <v>0.81443</v>
+        <v>0.71693</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         <v>-0.29806</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.46202</v>
+        <v>-6.462</v>
       </c>
       <c r="K131" t="n">
-        <v>0.37089</v>
+        <v>-0.20764</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         <v>-0.59613</v>
       </c>
       <c r="J132" t="n">
-        <v>-7.12502</v>
+        <v>-7.12504</v>
       </c>
       <c r="K132" t="n">
-        <v>0.02314</v>
+        <v>-0.48393</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
         <v>-0.89286</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.87357</v>
+        <v>-7.87359</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.05777</v>
+        <v>-0.55217</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>-1.3373</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.89684</v>
+        <v>-7.89685</v>
       </c>
       <c r="K134" t="n">
-        <v>0.53247</v>
+        <v>0.4504</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>-7.86888</v>
       </c>
       <c r="K135" t="n">
-        <v>0.53161</v>
+        <v>0.4723</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>-7.13323</v>
       </c>
       <c r="K136" t="n">
-        <v>1.02938</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>-6.80835</v>
       </c>
       <c r="K137" t="n">
-        <v>1.2942</v>
+        <v>1.19802</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
         <v>-2.08024</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.6022</v>
+        <v>-6.60219</v>
       </c>
       <c r="K138" t="n">
-        <v>1.69726</v>
+        <v>1.53049</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6407,10 +6407,10 @@
         <v>-1.93452</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.48671</v>
+        <v>-5.4867</v>
       </c>
       <c r="K139" t="n">
-        <v>2.02858</v>
+        <v>2.41379</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>-5.03356</v>
       </c>
       <c r="K140" t="n">
-        <v>2.02625</v>
+        <v>1.74132</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -6493,10 +6493,10 @@
         <v>-1.79104</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.26748</v>
+        <v>-5.26749</v>
       </c>
       <c r="K141" t="n">
-        <v>2.5242</v>
+        <v>2.20614</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>-1.9403</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.50656</v>
+        <v>-5.50657</v>
       </c>
       <c r="K142" t="n">
-        <v>2.82747</v>
+        <v>2.45695</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         <v>-1.9432</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.61918</v>
+        <v>-0.61922</v>
       </c>
       <c r="K143" t="n">
-        <v>3.29099</v>
+        <v>3.41001</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -6622,10 +6622,10 @@
         <v>-1.64918</v>
       </c>
       <c r="J144" t="n">
-        <v>1.44288</v>
+        <v>1.44287</v>
       </c>
       <c r="K144" t="n">
-        <v>3.63258</v>
+        <v>3.72815</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
         <v>-1.65165</v>
       </c>
       <c r="J145" t="n">
-        <v>2.52605</v>
+        <v>2.52604</v>
       </c>
       <c r="K145" t="n">
-        <v>4</v>
+        <v>4.02545</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -6708,10 +6708,10 @@
         <v>-1.35542</v>
       </c>
       <c r="J146" t="n">
-        <v>3.65906</v>
+        <v>3.65909</v>
       </c>
       <c r="K146" t="n">
-        <v>3.7536</v>
+        <v>3.75948</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6751,10 +6751,10 @@
         <v>-1.20664</v>
       </c>
       <c r="J147" t="n">
-        <v>3.11965</v>
+        <v>3.11967</v>
       </c>
       <c r="K147" t="n">
-        <v>3.73606</v>
+        <v>3.38225</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         <v>-0.75643</v>
       </c>
       <c r="J148" t="n">
-        <v>2.80843</v>
+        <v>2.80844</v>
       </c>
       <c r="K148" t="n">
-        <v>3.1826</v>
+        <v>2.93346</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         <v>-0.45455</v>
       </c>
       <c r="J149" t="n">
-        <v>2.05341</v>
+        <v>2.05343</v>
       </c>
       <c r="K149" t="n">
-        <v>2.64659</v>
+        <v>2.25384</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -6880,10 +6880,10 @@
         <v>-0.30349</v>
       </c>
       <c r="J150" t="n">
-        <v>1.73333</v>
+        <v>1.73334</v>
       </c>
       <c r="K150" t="n">
-        <v>2.05495</v>
+        <v>2.06279</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>0.23828</v>
       </c>
       <c r="K151" t="n">
-        <v>1.68324</v>
+        <v>1.25701</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.67217</v>
+        <v>0.67216</v>
       </c>
       <c r="K152" t="n">
-        <v>1.47822</v>
+        <v>1.64396</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7009,10 +7009,10 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>1.02751</v>
+        <v>1.02749</v>
       </c>
       <c r="K153" t="n">
-        <v>1.21417</v>
+        <v>1.57392</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7052,10 +7052,10 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.08998</v>
+        <v>1.09003</v>
       </c>
       <c r="K154" t="n">
-        <v>1.42536</v>
+        <v>1.69207</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7095,10 +7095,10 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.46874</v>
+        <v>2.46859</v>
       </c>
       <c r="K155" t="n">
-        <v>1.45333</v>
+        <v>1.87793</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7138,10 +7138,10 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.92564</v>
+        <v>1.92568</v>
       </c>
       <c r="K156" t="n">
-        <v>1.45122</v>
+        <v>1.85289</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -7181,10 +7181,10 @@
         <v>-0.30534</v>
       </c>
       <c r="J157" t="n">
-        <v>2.43307</v>
+        <v>2.43306</v>
       </c>
       <c r="K157" t="n">
-        <v>1.44509</v>
+        <v>1.82364</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -7224,10 +7224,10 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.33273</v>
+        <v>1.33276</v>
       </c>
       <c r="K158" t="n">
-        <v>1.70902</v>
+        <v>2.0277</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7267,10 +7267,10 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.63251</v>
+        <v>1.63254</v>
       </c>
       <c r="K159" t="n">
-        <v>1.97252</v>
+        <v>2.34002</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -7310,10 +7310,10 @@
         <v>-0.9146300000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>1.61073</v>
+        <v>1.61075</v>
       </c>
       <c r="K160" t="n">
-        <v>2.50749</v>
+        <v>2.72788</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         <v>-1.06545</v>
       </c>
       <c r="J161" t="n">
-        <v>2.49768</v>
+        <v>2.49769</v>
       </c>
       <c r="K161" t="n">
-        <v>3.12292</v>
+        <v>3.40643</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>3.27016</v>
       </c>
       <c r="K162" t="n">
-        <v>3.6489</v>
+        <v>3.66463</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>4.0691</v>
       </c>
       <c r="K163" t="n">
-        <v>3.95512</v>
+        <v>3.67989</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.70529</v>
+        <v>3.70528</v>
       </c>
       <c r="K164" t="n">
-        <v>4.25887</v>
+        <v>4.02127</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7525,10 +7525,10 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.92963</v>
+        <v>2.92961</v>
       </c>
       <c r="K165" t="n">
-        <v>4.28746</v>
+        <v>3.9513</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7568,10 +7568,10 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53474</v>
+        <v>2.53478</v>
       </c>
       <c r="K166" t="n">
-        <v>4.07215</v>
+        <v>3.77961</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.55958</v>
+        <v>3.55944</v>
       </c>
       <c r="K167" t="n">
-        <v>3.83471</v>
+        <v>3.6208</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.47452</v>
+        <v>3.47456</v>
       </c>
       <c r="K168" t="n">
-        <v>4.12632</v>
+        <v>4.01096</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>2.88885</v>
       </c>
       <c r="K169" t="n">
-        <v>3.8352</v>
+        <v>3.66932</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -7740,10 +7740,10 @@
         <v>-0.15337</v>
       </c>
       <c r="J170" t="n">
-        <v>2.85889</v>
+        <v>2.85892</v>
       </c>
       <c r="K170" t="n">
-        <v>3.55701</v>
+        <v>3.18202</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         <v>0.15361</v>
       </c>
       <c r="J171" t="n">
-        <v>2.90655</v>
+        <v>2.90657</v>
       </c>
       <c r="K171" t="n">
-        <v>3.53184</v>
+        <v>3.33767</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         <v>0.46154</v>
       </c>
       <c r="J172" t="n">
-        <v>3.18469</v>
+        <v>3.18471</v>
       </c>
       <c r="K172" t="n">
-        <v>3.53934</v>
+        <v>3.21675</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         <v>0.61538</v>
       </c>
       <c r="J173" t="n">
-        <v>2.86077</v>
+        <v>2.86078</v>
       </c>
       <c r="K173" t="n">
-        <v>3.54564</v>
+        <v>3.488</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>2.58488</v>
       </c>
       <c r="K174" t="n">
-        <v>3.30579</v>
+        <v>3.1173</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -7955,10 +7955,10 @@
         <v>1.23267</v>
       </c>
       <c r="J175" t="n">
-        <v>2.85953</v>
+        <v>2.85952</v>
       </c>
       <c r="K175" t="n">
-        <v>3.03516</v>
+        <v>3.13235</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -7998,10 +7998,10 @@
         <v>1.54321</v>
       </c>
       <c r="J176" t="n">
-        <v>2.5597</v>
+        <v>2.55969</v>
       </c>
       <c r="K176" t="n">
-        <v>3.00768</v>
+        <v>2.9606</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8041,10 +8041,10 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.90967</v>
+        <v>2.90965</v>
       </c>
       <c r="K177" t="n">
-        <v>3.04612</v>
+        <v>3.26874</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8084,10 +8084,10 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.84693</v>
+        <v>3.84696</v>
       </c>
       <c r="K178" t="n">
-        <v>2.99841</v>
+        <v>2.95179</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -8127,10 +8127,10 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.44211</v>
+        <v>2.44199</v>
       </c>
       <c r="K179" t="n">
-        <v>2.93962</v>
+        <v>2.77425</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -8170,10 +8170,10 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78551</v>
+        <v>1.78555</v>
       </c>
       <c r="K180" t="n">
-        <v>2.5996</v>
+        <v>2.21262</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>1.8174</v>
       </c>
       <c r="K181" t="n">
-        <v>2.92317</v>
+        <v>2.80206</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         <v>1.07527</v>
       </c>
       <c r="J182" t="n">
-        <v>1.4518</v>
+        <v>1.45182</v>
       </c>
       <c r="K182" t="n">
-        <v>2.89748</v>
+        <v>2.92601</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         <v>0.92025</v>
       </c>
       <c r="J183" t="n">
-        <v>1.7339</v>
+        <v>1.73391</v>
       </c>
       <c r="K183" t="n">
-        <v>2.6871</v>
+        <v>2.56921</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
         <v>0.7657</v>
       </c>
       <c r="J184" t="n">
-        <v>1.25115</v>
+        <v>1.25116</v>
       </c>
       <c r="K184" t="n">
-        <v>2.43571</v>
+        <v>2.72955</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>1.47674</v>
       </c>
       <c r="K185" t="n">
-        <v>1.88385</v>
+        <v>1.94528</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
         <v>0.30488</v>
       </c>
       <c r="J186" t="n">
-        <v>1.51615</v>
+        <v>1.51614</v>
       </c>
       <c r="K186" t="n">
-        <v>1.84935</v>
+        <v>2.14004</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>1.01808</v>
       </c>
       <c r="K187" t="n">
-        <v>2.09522</v>
+        <v>2.2805</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>1.01257</v>
       </c>
       <c r="K188" t="n">
-        <v>2.29861</v>
+        <v>2.42036</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>1.06062</v>
       </c>
       <c r="K189" t="n">
-        <v>2.56331</v>
+        <v>2.37138</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -8600,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.3828</v>
+        <v>0.38279</v>
       </c>
       <c r="K190" t="n">
-        <v>2.8595</v>
+        <v>2.84653</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -8643,10 +8643,10 @@
         <v>0.15175</v>
       </c>
       <c r="J191" t="n">
-        <v>0.87202</v>
+        <v>0.872</v>
       </c>
       <c r="K191" t="n">
-        <v>3.06186</v>
+        <v>2.73027</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>1.49477</v>
       </c>
       <c r="K192" t="n">
-        <v>3.16201</v>
+        <v>3.05123</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -8729,10 +8729,10 @@
         <v>0.30395</v>
       </c>
       <c r="J193" t="n">
-        <v>1.2914</v>
+        <v>1.29141</v>
       </c>
       <c r="K193" t="n">
-        <v>2.85041</v>
+        <v>2.58223</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -8772,10 +8772,10 @@
         <v>0.30395</v>
       </c>
       <c r="J194" t="n">
-        <v>1.42623</v>
+        <v>1.42624</v>
       </c>
       <c r="K194" t="n">
-        <v>2.60086</v>
+        <v>2.27017</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -8815,10 +8815,10 @@
         <v>0.15198</v>
       </c>
       <c r="J195" t="n">
-        <v>0.91827</v>
+        <v>0.91828</v>
       </c>
       <c r="K195" t="n">
-        <v>2.29991</v>
+        <v>2.10612</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -8858,10 +8858,10 @@
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>1.27211</v>
+        <v>1.27212</v>
       </c>
       <c r="K196" t="n">
-        <v>2.24513</v>
+        <v>1.84261</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>0.67276</v>
       </c>
       <c r="K197" t="n">
-        <v>2.1657</v>
+        <v>1.70408</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>0.25473</v>
       </c>
       <c r="K198" t="n">
-        <v>2.20341</v>
+        <v>1.88161</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>1.03418</v>
       </c>
       <c r="K199" t="n">
-        <v>1.69664</v>
+        <v>1.6013</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>-0.23442</v>
       </c>
       <c r="K200" t="n">
-        <v>1.38664</v>
+        <v>1.11089</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>-0.20364</v>
       </c>
       <c r="K201" t="n">
-        <v>0.80621</v>
+        <v>0.75536</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>-0.6785</v>
       </c>
       <c r="K202" t="n">
-        <v>0.28101</v>
+        <v>0.27076</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>-0.9078000000000001</v>
       </c>
       <c r="K203" t="n">
-        <v>-0.19006</v>
+        <v>0.29084</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>-1.06044</v>
       </c>
       <c r="K204" t="n">
-        <v>-0.55911</v>
+        <v>-0.26008</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>-0.9976699999999999</v>
       </c>
       <c r="K205" t="n">
-        <v>-0.55827</v>
+        <v>0.01998</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>-0.33444</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.33932</v>
+        <v>0.18998</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -9331,10 +9331,10 @@
         <v>-0.60698</v>
       </c>
       <c r="J207" t="n">
-        <v>0.17909</v>
+        <v>0.1791</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.32974</v>
+        <v>0.34044</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>-1.01099</v>
       </c>
       <c r="K208" t="n">
-        <v>-0.58888</v>
+        <v>0.01999</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>-0.79054</v>
       </c>
       <c r="K209" t="n">
-        <v>-0.57994</v>
+        <v>0.1806</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -9460,10 +9460,10 @@
         <v>0.15267</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.95639</v>
+        <v>-0.9564</v>
       </c>
       <c r="K210" t="n">
-        <v>-1.14782</v>
+        <v>-0.57902</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>-3.18665</v>
       </c>
       <c r="K211" t="n">
-        <v>-1.72827</v>
+        <v>-1.31671</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>-3.2485</v>
       </c>
       <c r="K212" t="n">
-        <v>-2.26615</v>
+        <v>-1.59808</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>-4.50734</v>
       </c>
       <c r="K213" t="n">
-        <v>-2.51924</v>
+        <v>-1.66933</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>-5.04425</v>
       </c>
       <c r="K214" t="n">
-        <v>-3.15252</v>
+        <v>-2.42024</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>-6.30201</v>
       </c>
       <c r="K215" t="n">
-        <v>-3.73822</v>
+        <v>-3.15</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>-7.64505</v>
       </c>
       <c r="K216" t="n">
-        <v>-4.17671</v>
+        <v>-2.98867</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>-7.87262</v>
       </c>
       <c r="K217" t="n">
-        <v>-5.06266</v>
+        <v>-4.12464</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -9804,10 +9804,10 @@
         <v>-1.37615</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.357839999999999</v>
+        <v>-8.357849999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>-5.83817</v>
+        <v>-4.78044</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>-9.30087</v>
       </c>
       <c r="K219" t="n">
-        <v>-6.41604</v>
+        <v>-5.16914</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>-9.05241</v>
       </c>
       <c r="K220" t="n">
-        <v>-6.72691</v>
+        <v>-5.45673</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>-10.13408</v>
       </c>
       <c r="K221" t="n">
-        <v>-6.77864</v>
+        <v>-5.29795</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>-10.12126</v>
       </c>
       <c r="K222" t="n">
-        <v>-6.5933</v>
+        <v>-5.23145</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>-8.6998</v>
       </c>
       <c r="K223" t="n">
-        <v>-6.08925</v>
+        <v>-4.47791</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>-7.54171</v>
       </c>
       <c r="K224" t="n">
-        <v>-5.60776</v>
+        <v>-4.13114</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>-7.08651</v>
       </c>
       <c r="K225" t="n">
-        <v>-5.37381</v>
+        <v>-4.11711</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>-6.15607</v>
       </c>
       <c r="K226" t="n">
-        <v>-4.6192</v>
+        <v>-3.37194</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10191,10 +10191,10 @@
         <v>-2.30415</v>
       </c>
       <c r="J227" t="n">
-        <v>-5.44008</v>
+        <v>-5.44007</v>
       </c>
       <c r="K227" t="n">
-        <v>-3.8001</v>
+        <v>-2.50903</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>-4.18288</v>
       </c>
       <c r="K228" t="n">
-        <v>-3.34241</v>
+        <v>-2.48113</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>-4.2057</v>
       </c>
       <c r="K229" t="n">
-        <v>-2.50264</v>
+        <v>-1.65625</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>-4.39817</v>
       </c>
       <c r="K230" t="n">
-        <v>-1.64841</v>
+        <v>-0.59742</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -10363,10 +10363,10 @@
         <v>-1.39752</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.84337</v>
+        <v>-3.84338</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.84628</v>
+        <v>-0.21046</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>-3.53761</v>
       </c>
       <c r="K232" t="n">
-        <v>-0.25834</v>
+        <v>0.3277</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>-1.63789</v>
       </c>
       <c r="K233" t="n">
-        <v>0.34524</v>
+        <v>0.82487</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>-1.38235</v>
       </c>
       <c r="K234" t="n">
-        <v>0.70263</v>
+        <v>1.19729</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -10535,10 +10535,10 @@
         <v>-1.24805</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.35604</v>
+        <v>-1.35605</v>
       </c>
       <c r="K235" t="n">
-        <v>1.20156</v>
+        <v>1.30159</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
         <v>-1.25</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.42164</v>
+        <v>-1.42165</v>
       </c>
       <c r="K236" t="n">
-        <v>1.34185</v>
+        <v>1.54579</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>-0.25819</v>
       </c>
       <c r="K237" t="n">
-        <v>1.60399</v>
+        <v>1.75997</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -10664,10 +10664,10 @@
         <v>-1.09718</v>
       </c>
       <c r="J238" t="n">
-        <v>0.24165</v>
+        <v>0.24166</v>
       </c>
       <c r="K238" t="n">
-        <v>1.44095</v>
+        <v>1.60161</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -10707,10 +10707,10 @@
         <v>-0.78616</v>
       </c>
       <c r="J239" t="n">
-        <v>1.32962</v>
+        <v>1.32964</v>
       </c>
       <c r="K239" t="n">
-        <v>1.48268</v>
+        <v>1.81106</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -10750,10 +10750,10 @@
         <v>-0.47244</v>
       </c>
       <c r="J240" t="n">
-        <v>1.6742</v>
+        <v>1.67421</v>
       </c>
       <c r="K240" t="n">
-        <v>1.84282</v>
+        <v>2.26863</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>2.18737</v>
       </c>
       <c r="K241" t="n">
-        <v>1.83039</v>
+        <v>2.06546</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.69481255817137</v>
+        <v>11.68991186874351</v>
       </c>
       <c r="C242" t="n">
-        <v>11.41051757347398</v>
+        <v>11.41080154205516</v>
       </c>
       <c r="D242" t="n">
-        <v>10.13206922494674</v>
+        <v>10.12851798061152</v>
       </c>
       <c r="E242" t="n">
-        <v>7.270806551872688</v>
+        <v>7.276543227618681</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10836,10 +10836,10 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.3057</v>
+        <v>2.30568</v>
       </c>
       <c r="K242" t="n">
-        <v>2.02206</v>
+        <v>1.82412</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.27695848835397</v>
+        <v>12.21713053620785</v>
       </c>
       <c r="C243" t="n">
-        <v>12.46069389928495</v>
+        <v>12.45850529737036</v>
       </c>
       <c r="D243" t="n">
-        <v>7.785716029654477</v>
+        <v>7.777646884157829</v>
       </c>
       <c r="E243" t="n">
-        <v>9.002427080409436</v>
+        <v>9.006667164185522</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10879,10 +10879,10 @@
         <v>-0.31496</v>
       </c>
       <c r="J243" t="n">
-        <v>2.642</v>
+        <v>2.64199</v>
       </c>
       <c r="K243" t="n">
-        <v>2.12835</v>
+        <v>2.24612</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.966195730234623</v>
+        <v>3.87144873876899</v>
       </c>
       <c r="C244" t="n">
-        <v>7.18015248014956</v>
+        <v>7.18201091270052</v>
       </c>
       <c r="D244" t="n">
-        <v>6.057120426850959</v>
+        <v>6.058687628844539</v>
       </c>
       <c r="E244" t="n">
-        <v>8.719902628062592</v>
+        <v>8.727150912205662</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10925,7 +10925,7 @@
         <v>3.88704</v>
       </c>
       <c r="K244" t="n">
-        <v>2.14764</v>
+        <v>2.13887</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.841137974108566</v>
+        <v>3.88852102886581</v>
       </c>
       <c r="C245" t="n">
-        <v>7.403168010177597</v>
+        <v>7.405039341285313</v>
       </c>
       <c r="D245" t="n">
-        <v>4.836827914664021</v>
+        <v>4.843647203240553</v>
       </c>
       <c r="E245" t="n">
-        <v>8.568126956917222</v>
+        <v>8.55297681573839</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10968,7 +10968,7 @@
         <v>2.90177</v>
       </c>
       <c r="K245" t="n">
-        <v>1.88152</v>
+        <v>1.81456</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1658500255691253</v>
+        <v>0.1542246907998202</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.7262965802713794</v>
+        <v>-0.7232587136657753</v>
       </c>
       <c r="D246" t="n">
-        <v>1.852882373051257</v>
+        <v>1.862417262683302</v>
       </c>
       <c r="E246" t="n">
-        <v>9.482456902033443</v>
+        <v>9.478625404901141</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11011,7 +11011,7 @@
         <v>3.10559</v>
       </c>
       <c r="K246" t="n">
-        <v>1.57793</v>
+        <v>1.44487</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3789615082278375</v>
+        <v>-0.3753014391885912</v>
       </c>
       <c r="C247" t="n">
-        <v>2.218068393392914</v>
+        <v>2.220863482710023</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.577207547736603</v>
+        <v>-1.566487617369083</v>
       </c>
       <c r="E247" t="n">
-        <v>9.11187100819275</v>
+        <v>9.122220633083856</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11051,10 +11051,10 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46134</v>
+        <v>3.46132</v>
       </c>
       <c r="K247" t="n">
-        <v>1.05894</v>
+        <v>1.10728</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -11070,16 +11070,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.55986972475276</v>
+        <v>-1.549305515244015</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.352199815767642</v>
+        <v>-2.351336198874476</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.086906104704534</v>
+        <v>-3.084959028928402</v>
       </c>
       <c r="E248" t="n">
-        <v>8.156468768114532</v>
+        <v>8.168008435879326</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11094,10 +11094,10 @@
         <v>-0.31646</v>
       </c>
       <c r="J248" t="n">
-        <v>3.43698</v>
+        <v>3.43697</v>
       </c>
       <c r="K248" t="n">
-        <v>1.05713</v>
+        <v>1.32416</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.455439330572617</v>
+        <v>1.48396388550458</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.258358783900281</v>
+        <v>-0.2574798352278584</v>
       </c>
       <c r="D249" t="n">
-        <v>2.490357458168568</v>
+        <v>2.48884625966439</v>
       </c>
       <c r="E249" t="n">
-        <v>7.156711723840092</v>
+        <v>7.171597580790223</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11140,7 +11140,7 @@
         <v>4.28899</v>
       </c>
       <c r="K249" t="n">
-        <v>0.82133</v>
+        <v>1.18775</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.842327254917334</v>
+        <v>4.864160372875737</v>
       </c>
       <c r="C250" t="n">
-        <v>4.700021041799696</v>
+        <v>4.702002718139342</v>
       </c>
       <c r="D250" t="n">
-        <v>6.316907012263284</v>
+        <v>6.312401659535194</v>
       </c>
       <c r="E250" t="n">
-        <v>8.292192060552317</v>
+        <v>8.299957406372238</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11183,7 +11183,7 @@
         <v>5.3641</v>
       </c>
       <c r="K250" t="n">
-        <v>1.10007</v>
+        <v>1.57636</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.836606194952183</v>
+        <v>0.868449851966413</v>
       </c>
       <c r="C251" t="n">
-        <v>1.474577858199999</v>
+        <v>1.477085118174304</v>
       </c>
       <c r="D251" t="n">
-        <v>2.673190420370175</v>
+        <v>2.674559523100606</v>
       </c>
       <c r="E251" t="n">
-        <v>8.438356746289145</v>
+        <v>8.445003939993434</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11223,10 +11223,10 @@
         <v>-0.79239</v>
       </c>
       <c r="J251" t="n">
-        <v>4.69103</v>
+        <v>4.69112</v>
       </c>
       <c r="K251" t="n">
-        <v>1.33305</v>
+        <v>1.76844</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.65243022529429</v>
+        <v>3.684427457613526</v>
       </c>
       <c r="C252" t="n">
-        <v>2.960974065780131</v>
+        <v>2.965866134820505</v>
       </c>
       <c r="D252" t="n">
-        <v>3.945344666836892</v>
+        <v>3.94781631712624</v>
       </c>
       <c r="E252" t="n">
-        <v>10.19700587065284</v>
+        <v>10.18283976141547</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11266,10 +11266,10 @@
         <v>-1.26582</v>
       </c>
       <c r="J252" t="n">
-        <v>4.78307</v>
+        <v>4.78309</v>
       </c>
       <c r="K252" t="n">
-        <v>1.53273</v>
+        <v>1.56525</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.12843500988618</v>
+        <v>7.072715401455421</v>
       </c>
       <c r="C253" t="n">
-        <v>8.468893021395306</v>
+        <v>8.468272447816094</v>
       </c>
       <c r="D253" t="n">
-        <v>3.580746961220171</v>
+        <v>3.577111834900282</v>
       </c>
       <c r="E253" t="n">
-        <v>7.944785777866503</v>
+        <v>7.958764814928942</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11309,10 +11309,10 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94742</v>
+        <v>4.94743</v>
       </c>
       <c r="K253" t="n">
-        <v>2.11657</v>
+        <v>2.43877</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.377965554397736</v>
+        <v>7.410856608097394</v>
       </c>
       <c r="C254" t="n">
-        <v>7.322016865856584</v>
+        <v>7.323075748310703</v>
       </c>
       <c r="D254" t="n">
-        <v>5.719362960434382</v>
+        <v>5.711653391502836</v>
       </c>
       <c r="E254" t="n">
-        <v>8.190948350695159</v>
+        <v>8.184668649033288</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11352,10 +11352,10 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.61719</v>
+        <v>5.61709</v>
       </c>
       <c r="K254" t="n">
-        <v>2.04557</v>
+        <v>1.895</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.449812949259591</v>
+        <v>5.440886379164156</v>
       </c>
       <c r="C255" t="n">
-        <v>5.872785445702888</v>
+        <v>5.872053437799929</v>
       </c>
       <c r="D255" t="n">
-        <v>2.551860809285</v>
+        <v>2.551939207577703</v>
       </c>
       <c r="E255" t="n">
-        <v>6.399282273263163</v>
+        <v>6.393983699423633</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11398,7 +11398,7 @@
         <v>5.94722</v>
       </c>
       <c r="K255" t="n">
-        <v>2.39078</v>
+        <v>2.32054</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.7123094943173</v>
+        <v>11.74476858705304</v>
       </c>
       <c r="C256" t="n">
-        <v>9.874842918487037</v>
+        <v>9.876973976645797</v>
       </c>
       <c r="D256" t="n">
-        <v>5.656021007831158</v>
+        <v>5.653792463530749</v>
       </c>
       <c r="E256" t="n">
-        <v>7.160130807724108</v>
+        <v>7.150518717018173</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11441,7 +11441,7 @@
         <v>5.66542</v>
       </c>
       <c r="K256" t="n">
-        <v>2.43001</v>
+        <v>2.78523</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.769492669428946</v>
+        <v>8.751397639527859</v>
       </c>
       <c r="C257" t="n">
-        <v>8.539529727104345</v>
+        <v>8.539912918307779</v>
       </c>
       <c r="D257" t="n">
-        <v>5.099534260989791</v>
+        <v>5.098204267983264</v>
       </c>
       <c r="E257" t="n">
-        <v>7.460533483834908</v>
+        <v>7.469605100862253</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11481,10 +11481,10 @@
         <v>-2.8481</v>
       </c>
       <c r="J257" t="n">
-        <v>6.14176</v>
+        <v>6.14175</v>
       </c>
       <c r="K257" t="n">
-        <v>2.75433</v>
+        <v>2.85361</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.91897497907251</v>
+        <v>11.90259765297663</v>
       </c>
       <c r="C258" t="n">
-        <v>11.7510031869644</v>
+        <v>11.75347373711397</v>
       </c>
       <c r="D258" t="n">
-        <v>8.778399391398462</v>
+        <v>8.775627040505718</v>
       </c>
       <c r="E258" t="n">
-        <v>7.926600217888624</v>
+        <v>7.925643975714469</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11527,7 +11527,7 @@
         <v>6.59563</v>
       </c>
       <c r="K258" t="n">
-        <v>3.32875</v>
+        <v>3.7878</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.45639405298526</v>
+        <v>11.4760049669437</v>
       </c>
       <c r="C259" t="n">
-        <v>9.109183339682691</v>
+        <v>9.110471998637749</v>
       </c>
       <c r="D259" t="n">
-        <v>7.828256627440444</v>
+        <v>7.825686007965937</v>
       </c>
       <c r="E259" t="n">
-        <v>8.258182410960991</v>
+        <v>8.251764642210446</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11567,10 +11567,10 @@
         <v>-3.01109</v>
       </c>
       <c r="J259" t="n">
-        <v>6.63027</v>
+        <v>6.63026</v>
       </c>
       <c r="K259" t="n">
-        <v>3.92676</v>
+        <v>3.92603</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.84212438184997</v>
+        <v>8.838927214073845</v>
       </c>
       <c r="C260" t="n">
-        <v>9.283773620239977</v>
+        <v>9.285227884836566</v>
       </c>
       <c r="D260" t="n">
-        <v>8.091405434949817</v>
+        <v>8.094670823083728</v>
       </c>
       <c r="E260" t="n">
-        <v>8.66173355869031</v>
+        <v>8.653305316305836</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11613,7 +11613,7 @@
         <v>6.90766</v>
       </c>
       <c r="K260" t="n">
-        <v>4.4273</v>
+        <v>4.28072</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.52735965475718</v>
+        <v>12.5389381211497</v>
       </c>
       <c r="C261" t="n">
-        <v>10.31822130294455</v>
+        <v>10.31909989656055</v>
       </c>
       <c r="D261" t="n">
-        <v>5.620489574039977</v>
+        <v>5.620248412073292</v>
       </c>
       <c r="E261" t="n">
-        <v>10.40224137996728</v>
+        <v>10.38961595581445</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11653,10 +11653,10 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46914</v>
+        <v>5.46913</v>
       </c>
       <c r="K261" t="n">
-        <v>5.34278</v>
+        <v>5.03501</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.791820069170074</v>
+        <v>6.770682176277631</v>
       </c>
       <c r="C262" t="n">
-        <v>6.464487771784433</v>
+        <v>6.466048186247653</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.8071157325411082</v>
+        <v>-0.802213864930823</v>
       </c>
       <c r="E262" t="n">
-        <v>8.714591303061736</v>
+        <v>8.716271347636972</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11696,10 +11696,10 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06088</v>
+        <v>4.06086</v>
       </c>
       <c r="K262" t="n">
-        <v>5.81027</v>
+        <v>5.26208</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.092095486628127</v>
+        <v>9.08621222064545</v>
       </c>
       <c r="C263" t="n">
-        <v>7.435410614521154</v>
+        <v>7.437861225360787</v>
       </c>
       <c r="D263" t="n">
-        <v>3.172339872734709</v>
+        <v>3.175980403335754</v>
       </c>
       <c r="E263" t="n">
-        <v>8.720654910572744</v>
+        <v>8.729177396406417</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11739,10 +11739,10 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.97949</v>
+        <v>3.9797</v>
       </c>
       <c r="K263" t="n">
-        <v>5.86192</v>
+        <v>4.71226</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.42968739860573</v>
+        <v>13.48894908615739</v>
       </c>
       <c r="C264" t="n">
-        <v>11.28382181106698</v>
+        <v>11.28891573205073</v>
       </c>
       <c r="D264" t="n">
-        <v>4.648674263903141</v>
+        <v>4.647905760317594</v>
       </c>
       <c r="E264" t="n">
-        <v>6.317426631770617</v>
+        <v>6.341745332908766</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11782,10 +11782,10 @@
         <v>-2.40385</v>
       </c>
       <c r="J264" t="n">
-        <v>3.8067</v>
+        <v>3.80669</v>
       </c>
       <c r="K264" t="n">
-        <v>5.94402</v>
+        <v>5.28679</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.057004036122418</v>
+        <v>8.077475537832758</v>
       </c>
       <c r="C265" t="n">
-        <v>5.798012578312028</v>
+        <v>5.797210213479631</v>
       </c>
       <c r="D265" t="n">
-        <v>2.702386820166991</v>
+        <v>2.703540736899335</v>
       </c>
       <c r="E265" t="n">
-        <v>7.354310675479114</v>
+        <v>7.369189445026314</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11825,10 +11825,10 @@
         <v>-2.2508</v>
       </c>
       <c r="J265" t="n">
-        <v>3.70119</v>
+        <v>3.70118</v>
       </c>
       <c r="K265" t="n">
-        <v>5.63483</v>
+        <v>4.52842</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.577039247061363</v>
+        <v>2.556203655008282</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2452361526891988</v>
+        <v>-0.2460733401052018</v>
       </c>
       <c r="D266" t="n">
-        <v>2.190539564648408</v>
+        <v>2.188181581544901</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01513299401429</v>
+        <v>12.00835700411917</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11868,10 +11868,10 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.88233</v>
+        <v>2.88222</v>
       </c>
       <c r="K266" t="n">
-        <v>5.6398</v>
+        <v>4.66463</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.094712886118402</v>
+        <v>5.066678558049875</v>
       </c>
       <c r="C267" t="n">
-        <v>1.640075159156318</v>
+        <v>1.636516334865235</v>
       </c>
       <c r="D267" t="n">
-        <v>3.459254519249821</v>
+        <v>3.458584399130316</v>
       </c>
       <c r="E267" t="n">
-        <v>13.53379367807621</v>
+        <v>13.52422573760115</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11911,10 +11911,10 @@
         <v>-1.94175</v>
       </c>
       <c r="J267" t="n">
-        <v>2.68748</v>
+        <v>2.68747</v>
       </c>
       <c r="K267" t="n">
-        <v>5.62042</v>
+        <v>4.50559</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.831790215896882</v>
+        <v>5.848017646704795</v>
       </c>
       <c r="C268" t="n">
-        <v>3.426505765642585</v>
+        <v>3.427727125325419</v>
       </c>
       <c r="D268" t="n">
-        <v>0.910166643092003</v>
+        <v>0.9094249086843531</v>
       </c>
       <c r="E268" t="n">
-        <v>15.10626414384517</v>
+        <v>15.09819257895977</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11954,10 +11954,10 @@
         <v>-1.62338</v>
       </c>
       <c r="J268" t="n">
-        <v>2.18414</v>
+        <v>2.18413</v>
       </c>
       <c r="K268" t="n">
-        <v>5.87932</v>
+        <v>4.71698</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.36886887118688</v>
+        <v>2.336808383250766</v>
       </c>
       <c r="C269" t="n">
-        <v>0.706155227933225</v>
+        <v>0.7036125276272509</v>
       </c>
       <c r="D269" t="n">
-        <v>2.947633198681676</v>
+        <v>2.946363986895717</v>
       </c>
       <c r="E269" t="n">
-        <v>10.13538516259818</v>
+        <v>10.1476727559457</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -11997,10 +11997,10 @@
         <v>-1.30293</v>
       </c>
       <c r="J269" t="n">
-        <v>2.61235</v>
+        <v>2.61233</v>
       </c>
       <c r="K269" t="n">
-        <v>5.82315</v>
+        <v>4.41707</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.699697892577957</v>
+        <v>2.664741286320305</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3389336710717394</v>
+        <v>0.3384748039963359</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.524121823229063</v>
+        <v>-1.52589407753001</v>
       </c>
       <c r="E270" t="n">
-        <v>11.77766076235904</v>
+        <v>11.78448130886145</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12040,10 +12040,10 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24587</v>
+        <v>2.24586</v>
       </c>
       <c r="K270" t="n">
-        <v>5.58396</v>
+        <v>4.17661</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.122984004858221</v>
+        <v>4.165008269555326</v>
       </c>
       <c r="C271" t="n">
-        <v>3.291968349039309</v>
+        <v>3.291110544551756</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.17959984648065</v>
+        <v>-1.181765362947107</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72495760252128</v>
+        <v>12.7230423581562</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12083,10 +12083,10 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.03161</v>
+        <v>2.03159</v>
       </c>
       <c r="K271" t="n">
-        <v>5.54028</v>
+        <v>4.24495</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.816889711796589</v>
+        <v>3.853878004032785</v>
       </c>
       <c r="C272" t="n">
-        <v>2.846092292474478</v>
+        <v>2.845605503513582</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.918538031997131</v>
+        <v>-2.916544243888786</v>
       </c>
       <c r="E272" t="n">
-        <v>12.4951833608786</v>
+        <v>12.48602978723343</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12126,10 +12126,10 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.0671</v>
+        <v>2.06709</v>
       </c>
       <c r="K272" t="n">
-        <v>5.03896</v>
+        <v>3.78922</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.044604092152569</v>
+        <v>2.054705591282535</v>
       </c>
       <c r="C273" t="n">
-        <v>2.715623507655263</v>
+        <v>2.714743222673532</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1084548297821675</v>
+        <v>-0.1080287124733181</v>
       </c>
       <c r="E273" t="n">
-        <v>12.15948483178335</v>
+        <v>12.14483520990293</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12172,7 +12172,7 @@
         <v>2.86984</v>
       </c>
       <c r="K273" t="n">
-        <v>4.36879</v>
+        <v>2.96049</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1476384007603859</v>
+        <v>-0.1506938917004819</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2241667649974799</v>
+        <v>0.2249042686591984</v>
       </c>
       <c r="D274" t="n">
-        <v>0.03658857459230003</v>
+        <v>0.03735558090358637</v>
       </c>
       <c r="E274" t="n">
-        <v>11.9253730620148</v>
+        <v>11.91221745033195</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12215,7 +12215,7 @@
         <v>2.1309</v>
       </c>
       <c r="K274" t="n">
-        <v>3.66414</v>
+        <v>2.62644</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3215114691102472</v>
+        <v>-0.3287895759479853</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4548032203889552</v>
+        <v>-0.4551832500415354</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.016980066900753</v>
+        <v>-2.018754468134409</v>
       </c>
       <c r="E275" t="n">
-        <v>10.90379799382655</v>
+        <v>10.88865555448917</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12255,10 +12255,10 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.58224</v>
+        <v>2.58248</v>
       </c>
       <c r="K275" t="n">
-        <v>3.36017</v>
+        <v>2.72355</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-3.994975521573596</v>
+        <v>-4.033751949021635</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.174746663337303</v>
+        <v>-4.172807498594599</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.722951593171753</v>
+        <v>-3.7218194982092</v>
       </c>
       <c r="E276" t="n">
-        <v>8.913106247169257</v>
+        <v>8.914478487135714</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12298,10 +12298,10 @@
         <v>0.32841</v>
       </c>
       <c r="J276" t="n">
-        <v>2.63796</v>
+        <v>2.638</v>
       </c>
       <c r="K276" t="n">
-        <v>2.99822</v>
+        <v>2.18108</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.362195517299382</v>
+        <v>-3.382276251869609</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.729403697130496</v>
+        <v>-3.733214952841524</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.41300580917705</v>
+        <v>-3.411116029515038</v>
       </c>
       <c r="E277" t="n">
-        <v>10.78887549873442</v>
+        <v>10.76883477073527</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12341,10 +12341,10 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55245</v>
+        <v>2.55249</v>
       </c>
       <c r="K277" t="n">
-        <v>3.04674</v>
+        <v>2.52956</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.266772951108954</v>
+        <v>3.317602141794929</v>
       </c>
       <c r="C278" t="n">
-        <v>3.629285710556185</v>
+        <v>3.629952507640555</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.600568413597092</v>
+        <v>-1.597235157007992</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127835634074041</v>
+        <v>6.127522985494549</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12384,10 +12384,10 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.58146</v>
+        <v>3.58126</v>
       </c>
       <c r="K278" t="n">
-        <v>2.88074</v>
+        <v>2.9129</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1310003949165361</v>
+        <v>-0.1621187848670158</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4590142315519019</v>
+        <v>0.4542519682659396</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.3167090938409611</v>
+        <v>-0.3150459707117359</v>
       </c>
       <c r="E279" t="n">
-        <v>4.002720279291783</v>
+        <v>4.005039793923726</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12427,10 +12427,10 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10559</v>
+        <v>3.10558</v>
       </c>
       <c r="K279" t="n">
-        <v>2.73892</v>
+        <v>2.29552</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.850123045872343</v>
+        <v>-1.88475162265368</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.190164001059403</v>
+        <v>-2.187821302131288</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7911591919177008</v>
+        <v>-0.7891761834719624</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4729159460757026</v>
+        <v>0.4902295804751766</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12470,10 +12470,10 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13309</v>
+        <v>3.13305</v>
       </c>
       <c r="K280" t="n">
-        <v>2.71797</v>
+        <v>2.27142</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.166023480975299</v>
+        <v>2.163796844707755</v>
       </c>
       <c r="C281" t="n">
-        <v>1.852648279550406</v>
+        <v>1.8500659685593</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.085353525728807</v>
+        <v>-3.084153449192351</v>
       </c>
       <c r="E281" t="n">
-        <v>3.995993590497116</v>
+        <v>4.011243356480332</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12513,10 +12513,10 @@
         <v>1.65017</v>
       </c>
       <c r="J281" t="n">
-        <v>2.52892</v>
+        <v>2.52887</v>
       </c>
       <c r="K281" t="n">
-        <v>2.48447</v>
+        <v>2.17746</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.205221275978485</v>
+        <v>1.187428124051815</v>
       </c>
       <c r="C282" t="n">
-        <v>1.63894994839382</v>
+        <v>1.640074807495129</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2788438026118722</v>
+        <v>0.2764096284688877</v>
       </c>
       <c r="E282" t="n">
-        <v>0.9998890528714055</v>
+        <v>1.014666054653968</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12556,10 +12556,10 @@
         <v>1.65017</v>
       </c>
       <c r="J282" t="n">
-        <v>2.46763</v>
+        <v>2.46758</v>
       </c>
       <c r="K282" t="n">
-        <v>2.70244</v>
+        <v>2.37686</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.136539400236414</v>
+        <v>1.175415342738351</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5800013045885732</v>
+        <v>0.5786448740411787</v>
       </c>
       <c r="D283" t="n">
-        <v>0.1380048524821875</v>
+        <v>0.1331416970415722</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1273923939180799</v>
+        <v>-0.1170960593890769</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12599,10 +12599,10 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.71624</v>
+        <v>1.7162</v>
       </c>
       <c r="K283" t="n">
-        <v>2.46068</v>
+        <v>2.24108</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.55294608419625</v>
+        <v>2.578005617875445</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.04565751573090138</v>
+        <v>-0.04835020360761666</v>
       </c>
       <c r="D284" t="n">
-        <v>2.835025081827891</v>
+        <v>2.835294898282581</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7814104131995014</v>
+        <v>0.7893731502066847</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12642,10 +12642,10 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.268</v>
+        <v>1.26801</v>
       </c>
       <c r="K284" t="n">
-        <v>2.67797</v>
+        <v>2.4054</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4564875386916967</v>
+        <v>0.4425114829305965</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7898249269175595</v>
+        <v>-0.7921642015235708</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.480956239818054</v>
+        <v>-1.478789130751812</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2765856449413517</v>
+        <v>0.2851078709545041</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12685,10 +12685,10 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55141</v>
+        <v>0.55146</v>
       </c>
       <c r="K285" t="n">
-        <v>3.00231</v>
+        <v>2.94202</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.656757421772473</v>
+        <v>4.66713793508633</v>
       </c>
       <c r="C286" t="n">
-        <v>1.839786524066422</v>
+        <v>1.841618782027354</v>
       </c>
       <c r="D286" t="n">
-        <v>2.939398737423193</v>
+        <v>2.936968772484572</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268788102409268</v>
+        <v>1.268736651348723</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12728,10 +12728,10 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35608</v>
+        <v>1.35617</v>
       </c>
       <c r="K286" t="n">
-        <v>3.24569</v>
+        <v>2.96832</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.821999286162782</v>
+        <v>5.845201125493271</v>
       </c>
       <c r="C287" t="n">
-        <v>3.953862804004493</v>
+        <v>3.956579439020302</v>
       </c>
       <c r="D287" t="n">
-        <v>4.865589689224947</v>
+        <v>4.858542775542274</v>
       </c>
       <c r="E287" t="n">
-        <v>2.674943180013734</v>
+        <v>2.667431440848134</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12771,10 +12771,10 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.26568</v>
+        <v>1.26592</v>
       </c>
       <c r="K287" t="n">
-        <v>3.51063</v>
+        <v>3.21201</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.480901589093977</v>
+        <v>3.498575514516933</v>
       </c>
       <c r="C288" t="n">
-        <v>2.938545198365983</v>
+        <v>2.947697915534708</v>
       </c>
       <c r="D288" t="n">
-        <v>2.087636103253598</v>
+        <v>2.085608805208916</v>
       </c>
       <c r="E288" t="n">
-        <v>3.361096984723932</v>
+        <v>3.350715766396428</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12814,10 +12814,10 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.5226499999999999</v>
+        <v>0.52274</v>
       </c>
       <c r="K288" t="n">
-        <v>3.84283</v>
+        <v>3.6524</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.85386977176623</v>
+        <v>6.862895154903237</v>
       </c>
       <c r="C289" t="n">
-        <v>6.0318149761726</v>
+        <v>6.028307246580789</v>
       </c>
       <c r="D289" t="n">
-        <v>2.170382577376673</v>
+        <v>2.168401590825653</v>
       </c>
       <c r="E289" t="n">
-        <v>3.815039500535211</v>
+        <v>3.794455114207107</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12857,10 +12857,10 @@
         <v>0.81699</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.27241</v>
+        <v>-0.27237</v>
       </c>
       <c r="K289" t="n">
-        <v>3.51163</v>
+        <v>2.94924</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8675166919599464</v>
+        <v>0.8600435919174476</v>
       </c>
       <c r="C290" t="n">
-        <v>1.151042072592534</v>
+        <v>1.151724006042865</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.177707284088637</v>
+        <v>-2.171915229494803</v>
       </c>
       <c r="E290" t="n">
-        <v>2.408308230736167</v>
+        <v>2.41326212552524</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12900,10 +12900,10 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.03277</v>
+        <v>-0.03294</v>
       </c>
       <c r="K290" t="n">
-        <v>3.83219</v>
+        <v>3.34937</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.281745463965247</v>
+        <v>3.208404212609084</v>
       </c>
       <c r="C291" t="n">
-        <v>3.303444731178162</v>
+        <v>3.294805262682732</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.216794690715339</v>
+        <v>-1.210613693592066</v>
       </c>
       <c r="E291" t="n">
-        <v>3.628516195020715</v>
+        <v>3.625151675718752</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12943,10 +12943,10 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23599</v>
+        <v>-0.23609</v>
       </c>
       <c r="K291" t="n">
-        <v>3.85604</v>
+        <v>3.70545</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.303686272417619</v>
+        <v>6.277476831094742</v>
       </c>
       <c r="C292" t="n">
-        <v>5.579032162457875</v>
+        <v>5.58543354917409</v>
       </c>
       <c r="D292" t="n">
-        <v>2.200631134767828</v>
+        <v>2.20618839597122</v>
       </c>
       <c r="E292" t="n">
-        <v>4.881310742406209</v>
+        <v>4.88972146506137</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -12986,10 +12986,10 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.73863</v>
+        <v>-0.73876</v>
       </c>
       <c r="K292" t="n">
-        <v>3.62291</v>
+        <v>3.04564</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.534536899249741</v>
+        <v>3.528585944335361</v>
       </c>
       <c r="C293" t="n">
-        <v>2.368221742495891</v>
+        <v>2.36469681800191</v>
       </c>
       <c r="D293" t="n">
-        <v>2.539840216636047</v>
+        <v>2.540132802154327</v>
       </c>
       <c r="E293" t="n">
-        <v>4.241483792479617</v>
+        <v>4.244988018272711</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13029,10 +13029,10 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52303</v>
+        <v>-0.52316</v>
       </c>
       <c r="K293" t="n">
-        <v>3.87311</v>
+        <v>3.68945</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.376584776465545</v>
+        <v>8.363871382129219</v>
       </c>
       <c r="C294" t="n">
-        <v>5.925007539618687</v>
+        <v>5.928222658148719</v>
       </c>
       <c r="D294" t="n">
-        <v>4.198393493657959</v>
+        <v>4.19549538331947</v>
       </c>
       <c r="E294" t="n">
-        <v>6.249169236141339</v>
+        <v>6.245593245161962</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13072,10 +13072,10 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82197</v>
+        <v>-0.82204</v>
       </c>
       <c r="K294" t="n">
-        <v>3.87626</v>
+        <v>3.31935</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.604011169050494</v>
+        <v>6.68611406954549</v>
       </c>
       <c r="C295" t="n">
-        <v>5.407067295141621</v>
+        <v>5.407679862738735</v>
       </c>
       <c r="D295" t="n">
-        <v>6.105100906602212</v>
+        <v>6.100341301827528</v>
       </c>
       <c r="E295" t="n">
-        <v>6.944263023969488</v>
+        <v>6.93582337365577</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13115,10 +13115,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.04552</v>
+        <v>-0.04557</v>
       </c>
       <c r="K295" t="n">
-        <v>4.15332</v>
+        <v>3.72167</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.148422868413527</v>
+        <v>5.194367625090912</v>
       </c>
       <c r="C296" t="n">
-        <v>5.727563731124197</v>
+        <v>5.726098710514971</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1258974239893629</v>
+        <v>0.1267336789519291</v>
       </c>
       <c r="E296" t="n">
-        <v>4.678730195697001</v>
+        <v>4.675372877949302</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.28602</v>
+        <v>0.28601</v>
       </c>
       <c r="K296" t="n">
-        <v>4.17488</v>
+        <v>3.52799</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.85808517685553</v>
+        <v>3.855631923769343</v>
       </c>
       <c r="C297" t="n">
-        <v>4.001840969027715</v>
+        <v>3.999866626921911</v>
       </c>
       <c r="D297" t="n">
-        <v>2.967229525560922</v>
+        <v>2.970209453861061</v>
       </c>
       <c r="E297" t="n">
-        <v>4.087800090490412</v>
+        <v>4.090204899585337</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13201,10 +13201,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.32261</v>
+        <v>0.32266</v>
       </c>
       <c r="K297" t="n">
-        <v>3.95179</v>
+        <v>3.48687</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.448647832546547</v>
+        <v>2.427107277955809</v>
       </c>
       <c r="C298" t="n">
-        <v>1.061119041186931</v>
+        <v>1.063479011026436</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4229147577806236</v>
+        <v>0.4226402335814949</v>
       </c>
       <c r="E298" t="n">
-        <v>3.05017872271558</v>
+        <v>3.045731641767135</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13244,10 +13244,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.36044</v>
+        <v>0.36078</v>
       </c>
       <c r="K298" t="n">
-        <v>4.13246</v>
+        <v>3.32625</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.292455011115147</v>
+        <v>3.284914812798068</v>
       </c>
       <c r="C299" t="n">
-        <v>2.791744792485495</v>
+        <v>2.795304284934752</v>
       </c>
       <c r="D299" t="n">
-        <v>1.846056185886802</v>
+        <v>1.842294130002697</v>
       </c>
       <c r="E299" t="n">
-        <v>2.815546366422073</v>
+        <v>2.817304836708923</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13287,10 +13287,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.01048</v>
+        <v>-0.01033</v>
       </c>
       <c r="K299" t="n">
-        <v>3.9212</v>
+        <v>3.21333</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.513984571706953</v>
+        <v>4.53884906300519</v>
       </c>
       <c r="C300" t="n">
-        <v>3.700426056547945</v>
+        <v>3.714164031128608</v>
       </c>
       <c r="D300" t="n">
-        <v>3.864362483649586</v>
+        <v>3.860845685935854</v>
       </c>
       <c r="E300" t="n">
-        <v>3.747060755297982</v>
+        <v>3.739063054796743</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13330,10 +13330,10 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>0.97962</v>
+        <v>0.97976</v>
       </c>
       <c r="K300" t="n">
-        <v>3.5896</v>
+        <v>2.73659</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.786762181147819</v>
+        <v>4.786016504132884</v>
       </c>
       <c r="C301" t="n">
-        <v>3.198225307014102</v>
+        <v>3.191298952342314</v>
       </c>
       <c r="D301" t="n">
-        <v>5.22185164605653</v>
+        <v>5.21594503671523</v>
       </c>
       <c r="E301" t="n">
-        <v>1.88368422346743</v>
+        <v>1.879239904304875</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13373,10 +13373,10 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95677</v>
+        <v>1.95716</v>
       </c>
       <c r="K301" t="n">
-        <v>3.94713</v>
+        <v>3.47994</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.33740872228412</v>
+        <v>5.386675161856824</v>
       </c>
       <c r="C302" t="n">
-        <v>3.363583255790337</v>
+        <v>3.364895976918536</v>
       </c>
       <c r="D302" t="n">
-        <v>4.128159108139062</v>
+        <v>4.127538595556501</v>
       </c>
       <c r="E302" t="n">
-        <v>1.202579848022078</v>
+        <v>1.201907294145754</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13416,10 +13416,10 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.4768</v>
+        <v>1.47651</v>
       </c>
       <c r="K302" t="n">
-        <v>3.5803</v>
+        <v>2.92131</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.223468576115398</v>
+        <v>5.156272074903789</v>
       </c>
       <c r="C303" t="n">
-        <v>3.160681841201662</v>
+        <v>3.145192843396649</v>
       </c>
       <c r="D303" t="n">
-        <v>1.659951607510535</v>
+        <v>1.662894845455964</v>
       </c>
       <c r="E303" t="n">
-        <v>3.121161660380567</v>
+        <v>3.11776881133754</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13459,10 +13459,10 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.99409</v>
+        <v>1.99361</v>
       </c>
       <c r="K303" t="n">
-        <v>3.337</v>
+        <v>2.38203</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>1.050239908704853</v>
+        <v>0.9882413934172662</v>
       </c>
       <c r="C304" t="n">
-        <v>0.4801592124206389</v>
+        <v>0.4883065590934876</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6451422152918274</v>
+        <v>-0.6377214781228213</v>
       </c>
       <c r="E304" t="n">
-        <v>3.836641874171964</v>
+        <v>3.856917130384341</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13502,10 +13502,10 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.7319</v>
+        <v>2.73193</v>
       </c>
       <c r="K304" t="n">
-        <v>3.55116</v>
+        <v>3.07385</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.069094764923362</v>
+        <v>1.053923022698267</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1490318638373456</v>
+        <v>0.1403410791539494</v>
       </c>
       <c r="D305" t="n">
-        <v>2.203282571580778</v>
+        <v>2.202857696440441</v>
       </c>
       <c r="E305" t="n">
-        <v>1.967144313827385</v>
+        <v>1.98560149828666</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13545,10 +13545,10 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.49429</v>
+        <v>2.49396</v>
       </c>
       <c r="K305" t="n">
-        <v>3.30021</v>
+        <v>2.40833</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6309636656347983</v>
+        <v>0.5654902569060427</v>
       </c>
       <c r="C306" t="n">
-        <v>0.02659628231227451</v>
+        <v>0.02953371550316053</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.253401070033022</v>
+        <v>-1.252506920234131</v>
       </c>
       <c r="E306" t="n">
-        <v>2.323904328749893</v>
+        <v>2.336454999416682</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13588,10 +13588,10 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.97543</v>
+        <v>2.97527</v>
       </c>
       <c r="K306" t="n">
-        <v>3.02342</v>
+        <v>2.41855</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.193047980880025</v>
+        <v>2.262331000464912</v>
       </c>
       <c r="C307" t="n">
-        <v>1.367900498428765</v>
+        <v>1.366044418660572</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.587415519215353</v>
+        <v>-2.58672444631195</v>
       </c>
       <c r="E307" t="n">
-        <v>3.144369712456796</v>
+        <v>3.153929784224441</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13631,10 +13631,10 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.4969</v>
+        <v>3.49698</v>
       </c>
       <c r="K307" t="n">
-        <v>2.72177</v>
+        <v>1.88849</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.774990425161982</v>
+        <v>1.828676411274377</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2820519747881001</v>
+        <v>0.2768538646624519</v>
       </c>
       <c r="D308" t="n">
-        <v>1.616064401776773</v>
+        <v>1.61597996643521</v>
       </c>
       <c r="E308" t="n">
-        <v>4.799978275311667</v>
+        <v>4.803471911570889</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13674,10 +13674,10 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.03719</v>
+        <v>3.03724</v>
       </c>
       <c r="K308" t="n">
-        <v>2.73775</v>
+        <v>2.3944</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.139472703330148</v>
+        <v>3.163245574044349</v>
       </c>
       <c r="C309" t="n">
-        <v>2.246426941851754</v>
+        <v>2.24237782701795</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5746118716628557</v>
+        <v>0.5758874072326003</v>
       </c>
       <c r="E309" t="n">
-        <v>5.405462619194434</v>
+        <v>5.404342138515594</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13717,10 +13717,10 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.08096</v>
+        <v>3.08102</v>
       </c>
       <c r="K309" t="n">
-        <v>2.73209</v>
+        <v>2.19859</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.760145029148367</v>
+        <v>5.777882111780475</v>
       </c>
       <c r="C310" t="n">
-        <v>6.645736995497775</v>
+        <v>6.651724771353673</v>
       </c>
       <c r="D310" t="n">
-        <v>2.74757897722655</v>
+        <v>2.746845997019176</v>
       </c>
       <c r="E310" t="n">
-        <v>8.391039850835291</v>
+        <v>8.38139308621364</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13760,10 +13760,10 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.58841</v>
+        <v>2.5888</v>
       </c>
       <c r="K310" t="n">
-        <v>2.76807</v>
+        <v>2.63793</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.908738719425386</v>
+        <v>3.918204011434478</v>
       </c>
       <c r="C311" t="n">
-        <v>3.19418391833528</v>
+        <v>3.201625399434538</v>
       </c>
       <c r="D311" t="n">
-        <v>0.7044590592938382</v>
+        <v>0.7040591690570253</v>
       </c>
       <c r="E311" t="n">
-        <v>4.879750510061642</v>
+        <v>4.871178548813604</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13803,10 +13803,10 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.98433</v>
+        <v>2.98452</v>
       </c>
       <c r="K311" t="n">
-        <v>2.70029</v>
+        <v>2.23015</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.042209898914551</v>
+        <v>4.074393610902449</v>
       </c>
       <c r="C312" t="n">
-        <v>2.342363358888422</v>
+        <v>2.364401321406406</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.112531020653129</v>
+        <v>-1.114484821177775</v>
       </c>
       <c r="E312" t="n">
-        <v>5.823294392226308</v>
+        <v>5.808872124810716</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13846,10 +13846,10 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.69887</v>
+        <v>2.6988</v>
       </c>
       <c r="K312" t="n">
-        <v>2.99187</v>
+        <v>2.61024</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.259937615038799</v>
+        <v>3.233887971216309</v>
       </c>
       <c r="C313" t="n">
-        <v>2.414152890669352</v>
+        <v>2.401724593983601</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.105077714916979</v>
+        <v>-0.1059951518853186</v>
       </c>
       <c r="E313" t="n">
-        <v>6.332943709068872</v>
+        <v>6.31232199547056</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13889,10 +13889,10 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.38404</v>
+        <v>2.38459</v>
       </c>
       <c r="K313" t="n">
-        <v>2.92574</v>
+        <v>2.36025</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.282911804640377</v>
+        <v>4.319274764855185</v>
       </c>
       <c r="C314" t="n">
-        <v>3.883803423389831</v>
+        <v>3.884905665838434</v>
       </c>
       <c r="D314" t="n">
-        <v>1.520650724414274</v>
+        <v>1.518182553514991</v>
       </c>
       <c r="E314" t="n">
-        <v>8.637443143335588</v>
+        <v>8.594876297629783</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13932,10 +13932,10 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.9528</v>
+        <v>1.95268</v>
       </c>
       <c r="K314" t="n">
-        <v>3.01226</v>
+        <v>2.45698</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.676676126185939</v>
+        <v>1.532049832572469</v>
       </c>
       <c r="C315" t="n">
-        <v>2.658689128569791</v>
+        <v>2.631586299048916</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9739943269364115</v>
+        <v>0.9726512886542693</v>
       </c>
       <c r="E315" t="n">
-        <v>4.021975420089241</v>
+        <v>3.987280071533328</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13975,10 +13975,10 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.41476</v>
+        <v>2.4141</v>
       </c>
       <c r="K315" t="n">
-        <v>3.24698</v>
+        <v>3.01039</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.65128978382434</v>
+        <v>2.573570758149057</v>
       </c>
       <c r="C316" t="n">
-        <v>2.847823207923095</v>
+        <v>2.863221987777242</v>
       </c>
       <c r="D316" t="n">
-        <v>0.4256446181034379</v>
+        <v>0.4320834916362815</v>
       </c>
       <c r="E316" t="n">
-        <v>3.647818020244031</v>
+        <v>3.686666702060926</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14021,7 +14021,7 @@
         <v>2.62046</v>
       </c>
       <c r="K316" t="n">
-        <v>3.03164</v>
+        <v>2.52338</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.797575466430496</v>
+        <v>8.854902099264649</v>
       </c>
       <c r="C317" t="n">
-        <v>9.10895644107541</v>
+        <v>9.096466350702359</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3934604364699057</v>
+        <v>0.3923324984203669</v>
       </c>
       <c r="E317" t="n">
-        <v>7.308428870820283</v>
+        <v>7.337128279366878</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14061,10 +14061,10 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43217</v>
+        <v>3.43186</v>
       </c>
       <c r="K317" t="n">
-        <v>3.28303</v>
+        <v>3.08549</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.375271679328252</v>
+        <v>4.295971319590675</v>
       </c>
       <c r="C318" t="n">
-        <v>5.384025018316541</v>
+        <v>5.392745256756681</v>
       </c>
       <c r="D318" t="n">
-        <v>2.167270875316096</v>
+        <v>2.166491422908212</v>
       </c>
       <c r="E318" t="n">
-        <v>5.208394409860562</v>
+        <v>5.227782067067599</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14104,10 +14104,10 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.37863</v>
+        <v>3.37849</v>
       </c>
       <c r="K318" t="n">
-        <v>3.52516</v>
+        <v>3.05754</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.195893319323529</v>
+        <v>4.288663303451457</v>
       </c>
       <c r="C319" t="n">
-        <v>3.340778035372804</v>
+        <v>3.339824987548679</v>
       </c>
       <c r="D319" t="n">
-        <v>2.754255411558781</v>
+        <v>2.754326867237888</v>
       </c>
       <c r="E319" t="n">
-        <v>3.725419117480211</v>
+        <v>3.751556923714894</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14147,10 +14147,10 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.17825</v>
+        <v>3.17833</v>
       </c>
       <c r="K319" t="n">
-        <v>3.82042</v>
+        <v>3.53045</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.757064413849045</v>
+        <v>6.862867233237879</v>
       </c>
       <c r="C320" t="n">
-        <v>6.806570420344005</v>
+        <v>6.799495110374121</v>
       </c>
       <c r="D320" t="n">
-        <v>2.233683524026309</v>
+        <v>2.23172627731747</v>
       </c>
       <c r="E320" t="n">
-        <v>3.069844622703632</v>
+        <v>3.086924885855402</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14190,10 +14190,10 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.17942</v>
+        <v>3.17949</v>
       </c>
       <c r="K320" t="n">
-        <v>3.52384</v>
+        <v>2.83762</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.92940774830073</v>
+        <v>5.97482193918355</v>
       </c>
       <c r="C321" t="n">
-        <v>4.67711159244999</v>
+        <v>4.669820107401401</v>
       </c>
       <c r="D321" t="n">
-        <v>1.471934942584996</v>
+        <v>1.473647173424442</v>
       </c>
       <c r="E321" t="n">
-        <v>2.671400208138053</v>
+        <v>2.681939008732215</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14233,10 +14233,10 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.22843</v>
+        <v>3.22847</v>
       </c>
       <c r="K321" t="n">
-        <v>3.64797</v>
+        <v>2.61478</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.553003880402319</v>
+        <v>5.531912963774954</v>
       </c>
       <c r="C322" t="n">
-        <v>3.504503795466318</v>
+        <v>3.512519589355523</v>
       </c>
       <c r="D322" t="n">
-        <v>0.02780182529813491</v>
+        <v>0.0293621819173806</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5061106841517837</v>
+        <v>-0.4969389205218278</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14276,10 +14276,10 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.72531</v>
+        <v>3.72556</v>
       </c>
       <c r="K322" t="n">
-        <v>3.74826</v>
+        <v>2.87507</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.330926124299861</v>
+        <v>4.318391733447324</v>
       </c>
       <c r="C323" t="n">
-        <v>5.184113192321371</v>
+        <v>5.19669465748922</v>
       </c